--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC651"/>
+  <dimension ref="A1:AC654"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50400,6 +50400,143 @@
       </c>
       <c r="AC651" t="inlineStr"/>
     </row>
+    <row r="652">
+      <c r="A652" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B652" t="n">
+        <v>0.4900347015</v>
+      </c>
+      <c r="C652" t="n">
+        <v>0.07050845850000001</v>
+      </c>
+      <c r="D652" t="inlineStr"/>
+      <c r="E652" t="inlineStr"/>
+      <c r="F652" t="inlineStr"/>
+      <c r="G652" t="inlineStr"/>
+      <c r="H652" t="inlineStr"/>
+      <c r="I652" t="n">
+        <v>0.03704316</v>
+      </c>
+      <c r="J652" t="inlineStr"/>
+      <c r="K652" t="n">
+        <v>1597.582114482361</v>
+      </c>
+      <c r="L652" t="inlineStr"/>
+      <c r="M652" t="inlineStr"/>
+      <c r="N652" t="inlineStr"/>
+      <c r="O652" t="n">
+        <v>0.1161208636</v>
+      </c>
+      <c r="P652" t="inlineStr"/>
+      <c r="Q652" t="n">
+        <v>8.279999999999999e-07</v>
+      </c>
+      <c r="R652" t="inlineStr"/>
+      <c r="S652" t="inlineStr"/>
+      <c r="T652" t="inlineStr"/>
+      <c r="U652" t="inlineStr"/>
+      <c r="V652" t="inlineStr"/>
+      <c r="W652" t="inlineStr"/>
+      <c r="X652" t="inlineStr"/>
+      <c r="Y652" t="inlineStr"/>
+      <c r="Z652" t="n">
+        <v>32.326888690276</v>
+      </c>
+      <c r="AA652" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="AB652" t="n">
+        <v>1630.630912954237</v>
+      </c>
+      <c r="AC652" t="inlineStr"/>
+    </row>
+    <row r="653">
+      <c r="A653" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B653" t="inlineStr"/>
+      <c r="C653" t="inlineStr"/>
+      <c r="D653" t="inlineStr"/>
+      <c r="E653" t="inlineStr"/>
+      <c r="F653" t="inlineStr"/>
+      <c r="G653" t="inlineStr"/>
+      <c r="H653" t="inlineStr"/>
+      <c r="I653" t="inlineStr"/>
+      <c r="J653" t="inlineStr"/>
+      <c r="K653" t="inlineStr"/>
+      <c r="L653" t="inlineStr"/>
+      <c r="M653" t="inlineStr"/>
+      <c r="N653" t="inlineStr"/>
+      <c r="O653" t="inlineStr"/>
+      <c r="P653" t="inlineStr"/>
+      <c r="Q653" t="inlineStr"/>
+      <c r="R653" t="inlineStr"/>
+      <c r="S653" t="inlineStr"/>
+      <c r="T653" t="inlineStr"/>
+      <c r="U653" t="inlineStr"/>
+      <c r="V653" t="inlineStr"/>
+      <c r="W653" t="inlineStr"/>
+      <c r="X653" t="inlineStr"/>
+      <c r="Y653" t="inlineStr"/>
+      <c r="Z653" t="n">
+        <v>31.162375408926</v>
+      </c>
+      <c r="AA653" t="inlineStr"/>
+      <c r="AB653" t="n">
+        <v>31.162375408926</v>
+      </c>
+      <c r="AC653" t="inlineStr"/>
+    </row>
+    <row r="654">
+      <c r="A654" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B654" t="n">
+        <v>0.5091181</v>
+      </c>
+      <c r="C654" t="n">
+        <v>0.07207478</v>
+      </c>
+      <c r="D654" t="inlineStr"/>
+      <c r="E654" t="inlineStr"/>
+      <c r="F654" t="inlineStr"/>
+      <c r="G654" t="inlineStr"/>
+      <c r="H654" t="inlineStr"/>
+      <c r="I654" t="n">
+        <v>0.03853640699999999</v>
+      </c>
+      <c r="J654" t="inlineStr"/>
+      <c r="K654" t="n">
+        <v>1596.443830111515</v>
+      </c>
+      <c r="L654" t="inlineStr"/>
+      <c r="M654" t="inlineStr"/>
+      <c r="N654" t="inlineStr"/>
+      <c r="O654" t="n">
+        <v>0.1190522596</v>
+      </c>
+      <c r="P654" t="inlineStr"/>
+      <c r="Q654" t="n">
+        <v>8.279999999999999e-07</v>
+      </c>
+      <c r="R654" t="inlineStr"/>
+      <c r="S654" t="inlineStr"/>
+      <c r="T654" t="inlineStr"/>
+      <c r="U654" t="inlineStr"/>
+      <c r="V654" t="inlineStr"/>
+      <c r="W654" t="inlineStr"/>
+      <c r="X654" t="inlineStr"/>
+      <c r="Y654" t="inlineStr"/>
+      <c r="Z654" t="inlineStr"/>
+      <c r="AA654" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="AB654" t="n">
+        <v>1597.190814256115</v>
+      </c>
+      <c r="AC654" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC654"/>
+  <dimension ref="A1:AD656"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,6 +573,11 @@
       <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>ZECUSDT</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>MANTRAUSDT</t>
         </is>
       </c>
     </row>
@@ -634,6 +639,7 @@
         <v>414.2028191822986</v>
       </c>
       <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -693,6 +699,7 @@
         <v>440.976657956838</v>
       </c>
       <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -752,6 +759,7 @@
         <v>482.4115240062466</v>
       </c>
       <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -811,6 +819,7 @@
         <v>475.1937465567585</v>
       </c>
       <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -870,6 +879,7 @@
         <v>458.9198783501148</v>
       </c>
       <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -929,6 +939,7 @@
         <v>924.4148503678907</v>
       </c>
       <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -998,6 +1009,7 @@
         <v>1398.683796258023</v>
       </c>
       <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1077,6 +1089,7 @@
         <v>2001.744690249562</v>
       </c>
       <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1156,6 +1169,7 @@
         <v>2025.291278707344</v>
       </c>
       <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1235,6 +1249,7 @@
         <v>1978.061693749934</v>
       </c>
       <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1314,6 +1329,7 @@
         <v>2018.210319210885</v>
       </c>
       <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1393,6 +1409,7 @@
         <v>2032.327032580222</v>
       </c>
       <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1472,6 +1489,7 @@
         <v>2083.189494512772</v>
       </c>
       <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1551,6 +1569,7 @@
         <v>2044.811962882468</v>
       </c>
       <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1630,6 +1649,7 @@
         <v>2046.539007685213</v>
       </c>
       <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1709,6 +1729,7 @@
         <v>2124.218449637598</v>
       </c>
       <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1788,6 +1809,7 @@
         <v>2185.074910599765</v>
       </c>
       <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1867,6 +1889,7 @@
         <v>2150.712631632542</v>
       </c>
       <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1946,6 +1969,7 @@
         <v>2053.893645518443</v>
       </c>
       <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -2025,6 +2049,7 @@
         <v>2002.784202629362</v>
       </c>
       <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -2104,6 +2129,7 @@
         <v>2037.220086254237</v>
       </c>
       <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -2183,6 +2209,7 @@
         <v>1995.540188620737</v>
       </c>
       <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -2262,6 +2289,7 @@
         <v>1895.323153052511</v>
       </c>
       <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -2341,6 +2369,7 @@
         <v>1959.431378152241</v>
       </c>
       <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -2420,6 +2449,7 @@
         <v>1866.105980793153</v>
       </c>
       <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -2501,6 +2531,7 @@
         <v>1844.123938369321</v>
       </c>
       <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -2582,6 +2613,7 @@
         <v>1881.094680427435</v>
       </c>
       <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -2663,6 +2695,7 @@
         <v>1947.481403260267</v>
       </c>
       <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -2744,6 +2777,7 @@
         <v>1863.695979417305</v>
       </c>
       <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -2825,6 +2859,7 @@
         <v>1783.929569351773</v>
       </c>
       <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -2906,6 +2941,7 @@
         <v>1774.511031343084</v>
       </c>
       <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -2987,6 +3023,7 @@
         <v>1747.892242268062</v>
       </c>
       <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -3068,6 +3105,7 @@
         <v>1748.983233372654</v>
       </c>
       <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -3149,6 +3187,7 @@
         <v>1769.219080619711</v>
       </c>
       <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -3230,6 +3269,7 @@
         <v>1707.32295914646</v>
       </c>
       <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -3311,6 +3351,7 @@
         <v>1676.997401562272</v>
       </c>
       <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -3392,6 +3433,7 @@
         <v>1748.396925472729</v>
       </c>
       <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -3473,6 +3515,7 @@
         <v>1727.0491551811</v>
       </c>
       <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -3554,6 +3597,7 @@
         <v>1789.171040149333</v>
       </c>
       <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -3635,6 +3679,7 @@
         <v>1724.731448289987</v>
       </c>
       <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -3716,6 +3761,7 @@
         <v>1719.760020017194</v>
       </c>
       <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -3797,6 +3843,7 @@
         <v>1768.990049339296</v>
       </c>
       <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -3878,6 +3925,7 @@
         <v>1756.973307325313</v>
       </c>
       <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -3959,6 +4007,7 @@
         <v>1755.089859964948</v>
       </c>
       <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -4040,6 +4089,7 @@
         <v>1643.44898702745</v>
       </c>
       <c r="AC46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -4121,6 +4171,7 @@
         <v>1516.727386300405</v>
       </c>
       <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -4202,6 +4253,7 @@
         <v>1523.881757983055</v>
       </c>
       <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -4285,6 +4337,7 @@
         <v>1615.573126373096</v>
       </c>
       <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -4368,6 +4421,7 @@
         <v>1563.057926854914</v>
       </c>
       <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -4451,6 +4505,7 @@
         <v>1598.582504829355</v>
       </c>
       <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -4534,6 +4589,7 @@
         <v>1635.825870428052</v>
       </c>
       <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -4617,6 +4673,7 @@
         <v>1662.413210793567</v>
       </c>
       <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -4700,6 +4757,7 @@
         <v>1658.462329568884</v>
       </c>
       <c r="AC54" t="inlineStr"/>
+      <c r="AD54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -4783,6 +4841,7 @@
         <v>1696.094620103681</v>
       </c>
       <c r="AC55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -4866,6 +4925,7 @@
         <v>1736.43209753843</v>
       </c>
       <c r="AC56" t="inlineStr"/>
+      <c r="AD56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -4951,6 +5011,7 @@
         <v>2047.915363158605</v>
       </c>
       <c r="AC57" t="inlineStr"/>
+      <c r="AD57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -5036,6 +5097,7 @@
         <v>2208.468451581036</v>
       </c>
       <c r="AC58" t="inlineStr"/>
+      <c r="AD58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -5121,6 +5183,7 @@
         <v>2188.694973581518</v>
       </c>
       <c r="AC59" t="inlineStr"/>
+      <c r="AD59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -5206,6 +5269,7 @@
         <v>2148.555618956184</v>
       </c>
       <c r="AC60" t="inlineStr"/>
+      <c r="AD60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -5291,6 +5355,7 @@
         <v>2166.049618497707</v>
       </c>
       <c r="AC61" t="inlineStr"/>
+      <c r="AD61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -5376,6 +5441,7 @@
         <v>2217.603099576304</v>
       </c>
       <c r="AC62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -5461,6 +5527,7 @@
         <v>2243.740276005894</v>
       </c>
       <c r="AC63" t="inlineStr"/>
+      <c r="AD63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -5546,6 +5613,7 @@
         <v>2296.055487460086</v>
       </c>
       <c r="AC64" t="inlineStr"/>
+      <c r="AD64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -5631,6 +5699,7 @@
         <v>2202.520933018481</v>
       </c>
       <c r="AC65" t="inlineStr"/>
+      <c r="AD65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -5716,6 +5785,7 @@
         <v>2147.894872443838</v>
       </c>
       <c r="AC66" t="inlineStr"/>
+      <c r="AD66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -5801,6 +5871,7 @@
         <v>2123.107528507743</v>
       </c>
       <c r="AC67" t="inlineStr"/>
+      <c r="AD67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -5886,6 +5957,7 @@
         <v>2106.691437310398</v>
       </c>
       <c r="AC68" t="inlineStr"/>
+      <c r="AD68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -5971,6 +6043,7 @@
         <v>2178.200606951446</v>
       </c>
       <c r="AC69" t="inlineStr"/>
+      <c r="AD69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -6056,6 +6129,7 @@
         <v>2214.265767905552</v>
       </c>
       <c r="AC70" t="inlineStr"/>
+      <c r="AD70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -6141,6 +6215,7 @@
         <v>2205.220285868259</v>
       </c>
       <c r="AC71" t="inlineStr"/>
+      <c r="AD71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -6226,6 +6301,7 @@
         <v>2179.507170052449</v>
       </c>
       <c r="AC72" t="inlineStr"/>
+      <c r="AD72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -6311,6 +6387,7 @@
         <v>2160.633108506514</v>
       </c>
       <c r="AC73" t="inlineStr"/>
+      <c r="AD73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -6396,6 +6473,7 @@
         <v>2100.894883890049</v>
       </c>
       <c r="AC74" t="inlineStr"/>
+      <c r="AD74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -6481,6 +6559,7 @@
         <v>2106.60682668133</v>
       </c>
       <c r="AC75" t="inlineStr"/>
+      <c r="AD75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -6566,6 +6645,7 @@
         <v>1947.660429315914</v>
       </c>
       <c r="AC76" t="inlineStr"/>
+      <c r="AD76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -6651,6 +6731,7 @@
         <v>1864.557470712303</v>
       </c>
       <c r="AC77" t="inlineStr"/>
+      <c r="AD77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -6736,6 +6817,7 @@
         <v>1773.854515639015</v>
       </c>
       <c r="AC78" t="inlineStr"/>
+      <c r="AD78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -6821,6 +6903,7 @@
         <v>1638.700429052418</v>
       </c>
       <c r="AC79" t="inlineStr"/>
+      <c r="AD79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -6906,6 +6989,7 @@
         <v>1728.311347301672</v>
       </c>
       <c r="AC80" t="inlineStr"/>
+      <c r="AD80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -6991,6 +7075,7 @@
         <v>1678.161891512216</v>
       </c>
       <c r="AC81" t="inlineStr"/>
+      <c r="AD81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -7076,6 +7161,7 @@
         <v>1884.338580626695</v>
       </c>
       <c r="AC82" t="inlineStr"/>
+      <c r="AD82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -7161,6 +7247,7 @@
         <v>1846.134847903824</v>
       </c>
       <c r="AC83" t="inlineStr"/>
+      <c r="AD83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -7246,6 +7333,7 @@
         <v>1841.035843902293</v>
       </c>
       <c r="AC84" t="inlineStr"/>
+      <c r="AD84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -7331,6 +7419,7 @@
         <v>1788.254192413208</v>
       </c>
       <c r="AC85" t="inlineStr"/>
+      <c r="AD85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -7416,6 +7505,7 @@
         <v>1819.967678508065</v>
       </c>
       <c r="AC86" t="inlineStr"/>
+      <c r="AD86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -7501,6 +7591,7 @@
         <v>1849.931592212988</v>
       </c>
       <c r="AC87" t="inlineStr"/>
+      <c r="AD87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -7586,6 +7677,7 @@
         <v>1804.322382743667</v>
       </c>
       <c r="AC88" t="inlineStr"/>
+      <c r="AD88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -7671,6 +7763,7 @@
         <v>1757.263476931514</v>
       </c>
       <c r="AC89" t="inlineStr"/>
+      <c r="AD89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -7756,6 +7849,7 @@
         <v>1758.29569435307</v>
       </c>
       <c r="AC90" t="inlineStr"/>
+      <c r="AD90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
@@ -7841,6 +7935,7 @@
         <v>1814.077851075459</v>
       </c>
       <c r="AC91" t="inlineStr"/>
+      <c r="AD91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -7926,6 +8021,7 @@
         <v>1799.425152668883</v>
       </c>
       <c r="AC92" t="inlineStr"/>
+      <c r="AD92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
@@ -8011,6 +8107,7 @@
         <v>1811.69593184484</v>
       </c>
       <c r="AC93" t="inlineStr"/>
+      <c r="AD93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -8096,6 +8193,7 @@
         <v>1782.967894516827</v>
       </c>
       <c r="AC94" t="inlineStr"/>
+      <c r="AD94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
@@ -8181,6 +8279,7 @@
         <v>1829.669631904936</v>
       </c>
       <c r="AC95" t="inlineStr"/>
+      <c r="AD95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -8266,6 +8365,7 @@
         <v>1839.65671112973</v>
       </c>
       <c r="AC96" t="inlineStr"/>
+      <c r="AD96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
@@ -8351,6 +8451,7 @@
         <v>1966.666085285657</v>
       </c>
       <c r="AC97" t="inlineStr"/>
+      <c r="AD97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -8436,6 +8537,7 @@
         <v>1978.92809330597</v>
       </c>
       <c r="AC98" t="inlineStr"/>
+      <c r="AD98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -8521,6 +8623,7 @@
         <v>1954.423936384552</v>
       </c>
       <c r="AC99" t="inlineStr"/>
+      <c r="AD99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -8606,6 +8709,7 @@
         <v>1890.679191920299</v>
       </c>
       <c r="AC100" t="inlineStr"/>
+      <c r="AD100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -8691,6 +8795,7 @@
         <v>1793.88565582832</v>
       </c>
       <c r="AC101" t="inlineStr"/>
+      <c r="AD101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -8776,6 +8881,7 @@
         <v>1782.054677750944</v>
       </c>
       <c r="AC102" t="inlineStr"/>
+      <c r="AD102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
@@ -8861,6 +8967,7 @@
         <v>1788.549230577692</v>
       </c>
       <c r="AC103" t="inlineStr"/>
+      <c r="AD103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -8946,6 +9053,7 @@
         <v>1787.505122272422</v>
       </c>
       <c r="AC104" t="inlineStr"/>
+      <c r="AD104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
@@ -9031,6 +9139,7 @@
         <v>1765.332854031751</v>
       </c>
       <c r="AC105" t="inlineStr"/>
+      <c r="AD105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -9116,6 +9225,7 @@
         <v>1708.36268931473</v>
       </c>
       <c r="AC106" t="inlineStr"/>
+      <c r="AD106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
@@ -9201,6 +9311,7 @@
         <v>1791.782200077807</v>
       </c>
       <c r="AC107" t="inlineStr"/>
+      <c r="AD107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -9286,6 +9397,7 @@
         <v>1728.362009296126</v>
       </c>
       <c r="AC108" t="inlineStr"/>
+      <c r="AD108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
@@ -9371,6 +9483,7 @@
         <v>1758.054650898895</v>
       </c>
       <c r="AC109" t="inlineStr"/>
+      <c r="AD109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -9456,6 +9569,7 @@
         <v>1704.312100401506</v>
       </c>
       <c r="AC110" t="inlineStr"/>
+      <c r="AD110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
@@ -9541,6 +9655,7 @@
         <v>1659.614114406377</v>
       </c>
       <c r="AC111" t="inlineStr"/>
+      <c r="AD111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -9626,6 +9741,7 @@
         <v>1671.106062509911</v>
       </c>
       <c r="AC112" t="inlineStr"/>
+      <c r="AD112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
@@ -9711,6 +9827,7 @@
         <v>1693.928595075216</v>
       </c>
       <c r="AC113" t="inlineStr"/>
+      <c r="AD113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -9796,6 +9913,7 @@
         <v>1772.7199894362</v>
       </c>
       <c r="AC114" t="inlineStr"/>
+      <c r="AD114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
@@ -9881,6 +9999,7 @@
         <v>1804.089697725326</v>
       </c>
       <c r="AC115" t="inlineStr"/>
+      <c r="AD115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -9966,6 +10085,7 @@
         <v>1791.893198358887</v>
       </c>
       <c r="AC116" t="inlineStr"/>
+      <c r="AD116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
@@ -10051,6 +10171,7 @@
         <v>1827.717367101255</v>
       </c>
       <c r="AC117" t="inlineStr"/>
+      <c r="AD117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -10136,6 +10257,7 @@
         <v>1865.580878471853</v>
       </c>
       <c r="AC118" t="inlineStr"/>
+      <c r="AD118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
@@ -10221,6 +10343,7 @@
         <v>1839.399276753622</v>
       </c>
       <c r="AC119" t="inlineStr"/>
+      <c r="AD119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -10306,6 +10429,7 @@
         <v>1798.636209273403</v>
       </c>
       <c r="AC120" t="inlineStr"/>
+      <c r="AD120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
@@ -10391,6 +10515,7 @@
         <v>1779.332509492657</v>
       </c>
       <c r="AC121" t="inlineStr"/>
+      <c r="AD121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
@@ -10476,6 +10601,7 @@
         <v>1814.257735874993</v>
       </c>
       <c r="AC122" t="inlineStr"/>
+      <c r="AD122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
@@ -10561,6 +10687,7 @@
         <v>1867.044037449003</v>
       </c>
       <c r="AC123" t="inlineStr"/>
+      <c r="AD123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
@@ -10646,6 +10773,7 @@
         <v>1903.88761876635</v>
       </c>
       <c r="AC124" t="inlineStr"/>
+      <c r="AD124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
@@ -10731,6 +10859,7 @@
         <v>1932.033767786053</v>
       </c>
       <c r="AC125" t="inlineStr"/>
+      <c r="AD125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -10816,6 +10945,7 @@
         <v>1951.108540692605</v>
       </c>
       <c r="AC126" t="inlineStr"/>
+      <c r="AD126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
@@ -10901,6 +11031,7 @@
         <v>1924.603525782934</v>
       </c>
       <c r="AC127" t="inlineStr"/>
+      <c r="AD127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
@@ -10986,6 +11117,7 @@
         <v>1959.112394769655</v>
       </c>
       <c r="AC128" t="inlineStr"/>
+      <c r="AD128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
@@ -11071,6 +11203,7 @@
         <v>1982.615733601117</v>
       </c>
       <c r="AC129" t="inlineStr"/>
+      <c r="AD129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
@@ -11156,6 +11289,7 @@
         <v>1954.489288395226</v>
       </c>
       <c r="AC130" t="inlineStr"/>
+      <c r="AD130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
@@ -11241,6 +11375,7 @@
         <v>2040.188505816031</v>
       </c>
       <c r="AC131" t="inlineStr"/>
+      <c r="AD131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
@@ -11326,6 +11461,7 @@
         <v>2066.172974482463</v>
       </c>
       <c r="AC132" t="inlineStr"/>
+      <c r="AD132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
@@ -11411,6 +11547,7 @@
         <v>2052.263681986443</v>
       </c>
       <c r="AC133" t="inlineStr"/>
+      <c r="AD133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
@@ -11496,6 +11633,7 @@
         <v>2042.780054462572</v>
       </c>
       <c r="AC134" t="inlineStr"/>
+      <c r="AD134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
@@ -11581,6 +11719,7 @@
         <v>1974.825605745772</v>
       </c>
       <c r="AC135" t="inlineStr"/>
+      <c r="AD135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
@@ -11666,6 +11805,7 @@
         <v>1909.659985546733</v>
       </c>
       <c r="AC136" t="inlineStr"/>
+      <c r="AD136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
@@ -11751,6 +11891,7 @@
         <v>1903.560005579571</v>
       </c>
       <c r="AC137" t="inlineStr"/>
+      <c r="AD137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
@@ -11836,6 +11977,7 @@
         <v>1897.949166887349</v>
       </c>
       <c r="AC138" t="inlineStr"/>
+      <c r="AD138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
@@ -11921,6 +12063,7 @@
         <v>1974.997598918299</v>
       </c>
       <c r="AC139" t="inlineStr"/>
+      <c r="AD139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
@@ -12006,6 +12149,7 @@
         <v>1960.078079167852</v>
       </c>
       <c r="AC140" t="inlineStr"/>
+      <c r="AD140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
@@ -12091,6 +12235,7 @@
         <v>1994.453855387927</v>
       </c>
       <c r="AC141" t="inlineStr"/>
+      <c r="AD141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
@@ -12176,6 +12321,7 @@
         <v>1979.320483813515</v>
       </c>
       <c r="AC142" t="inlineStr"/>
+      <c r="AD142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
@@ -12261,6 +12407,7 @@
         <v>1972.640845011033</v>
       </c>
       <c r="AC143" t="inlineStr"/>
+      <c r="AD143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
@@ -12346,6 +12493,7 @@
         <v>1941.205857739591</v>
       </c>
       <c r="AC144" t="inlineStr"/>
+      <c r="AD144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
@@ -12431,6 +12579,7 @@
         <v>1968.895198184082</v>
       </c>
       <c r="AC145" t="inlineStr"/>
+      <c r="AD145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
@@ -12516,6 +12665,7 @@
         <v>2013.864573698098</v>
       </c>
       <c r="AC146" t="inlineStr"/>
+      <c r="AD146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
@@ -12601,6 +12751,7 @@
         <v>2040.154275340067</v>
       </c>
       <c r="AC147" t="inlineStr"/>
+      <c r="AD147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
@@ -12686,6 +12837,7 @@
         <v>2050.913552467494</v>
       </c>
       <c r="AC148" t="inlineStr"/>
+      <c r="AD148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
@@ -12771,6 +12923,7 @@
         <v>2174.488994447901</v>
       </c>
       <c r="AC149" t="inlineStr"/>
+      <c r="AD149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
@@ -12856,6 +13009,7 @@
         <v>2153.372857627961</v>
       </c>
       <c r="AC150" t="inlineStr"/>
+      <c r="AD150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
@@ -12941,6 +13095,7 @@
         <v>2148.396921010869</v>
       </c>
       <c r="AC151" t="inlineStr"/>
+      <c r="AD151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
@@ -13026,6 +13181,7 @@
         <v>2133.486482307773</v>
       </c>
       <c r="AC152" t="inlineStr"/>
+      <c r="AD152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
@@ -13111,6 +13267,7 @@
         <v>2140.436029363304</v>
       </c>
       <c r="AC153" t="inlineStr"/>
+      <c r="AD153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
@@ -13196,6 +13353,7 @@
         <v>2135.864189933008</v>
       </c>
       <c r="AC154" t="inlineStr"/>
+      <c r="AD154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
@@ -13281,6 +13439,7 @@
         <v>2172.883573141069</v>
       </c>
       <c r="AC155" t="inlineStr"/>
+      <c r="AD155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
@@ -13366,6 +13525,7 @@
         <v>2130.506652155042</v>
       </c>
       <c r="AC156" t="inlineStr"/>
+      <c r="AD156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
@@ -13451,6 +13611,7 @@
         <v>2114.885537744549</v>
       </c>
       <c r="AC157" t="inlineStr"/>
+      <c r="AD157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
@@ -13536,6 +13697,7 @@
         <v>2065.916524084465</v>
       </c>
       <c r="AC158" t="inlineStr"/>
+      <c r="AD158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
@@ -13621,6 +13783,7 @@
         <v>2082.712947896893</v>
       </c>
       <c r="AC159" t="inlineStr"/>
+      <c r="AD159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
@@ -13706,6 +13869,7 @@
         <v>1977.5150042717</v>
       </c>
       <c r="AC160" t="inlineStr"/>
+      <c r="AD160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
@@ -13791,6 +13955,7 @@
         <v>1994.517272634397</v>
       </c>
       <c r="AC161" t="inlineStr"/>
+      <c r="AD161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
@@ -13876,6 +14041,7 @@
         <v>2116.519855752097</v>
       </c>
       <c r="AC162" t="inlineStr"/>
+      <c r="AD162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
@@ -13961,6 +14127,7 @@
         <v>2094.706767282208</v>
       </c>
       <c r="AC163" t="inlineStr"/>
+      <c r="AD163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
@@ -14046,6 +14213,7 @@
         <v>2156.912085067692</v>
       </c>
       <c r="AC164" t="inlineStr"/>
+      <c r="AD164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
@@ -14131,6 +14299,7 @@
         <v>2161.720775759261</v>
       </c>
       <c r="AC165" t="inlineStr"/>
+      <c r="AD165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
@@ -14216,6 +14385,7 @@
         <v>2091.875591509711</v>
       </c>
       <c r="AC166" t="inlineStr"/>
+      <c r="AD166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
@@ -14301,6 +14471,7 @@
         <v>2092.090742405129</v>
       </c>
       <c r="AC167" t="inlineStr"/>
+      <c r="AD167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
@@ -14386,6 +14557,7 @@
         <v>2061.130141621632</v>
       </c>
       <c r="AC168" t="inlineStr"/>
+      <c r="AD168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
@@ -14471,6 +14643,7 @@
         <v>2023.309721719824</v>
       </c>
       <c r="AC169" t="inlineStr"/>
+      <c r="AD169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
@@ -14556,6 +14729,7 @@
         <v>1961.892920094047</v>
       </c>
       <c r="AC170" t="inlineStr"/>
+      <c r="AD170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
@@ -14641,6 +14815,7 @@
         <v>2021.376754376715</v>
       </c>
       <c r="AC171" t="inlineStr"/>
+      <c r="AD171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
@@ -14726,6 +14901,7 @@
         <v>2239.082677776151</v>
       </c>
       <c r="AC172" t="inlineStr"/>
+      <c r="AD172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
@@ -14811,6 +14987,7 @@
         <v>2259.045359940857</v>
       </c>
       <c r="AC173" t="inlineStr"/>
+      <c r="AD173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
@@ -14896,6 +15073,7 @@
         <v>2252.575326503827</v>
       </c>
       <c r="AC174" t="inlineStr"/>
+      <c r="AD174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
@@ -14981,6 +15159,7 @@
         <v>2298.126463476916</v>
       </c>
       <c r="AC175" t="inlineStr"/>
+      <c r="AD175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
@@ -15066,6 +15245,7 @@
         <v>2386.992051961975</v>
       </c>
       <c r="AC176" t="inlineStr"/>
+      <c r="AD176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
@@ -15151,6 +15331,7 @@
         <v>2545.469570580479</v>
       </c>
       <c r="AC177" t="inlineStr"/>
+      <c r="AD177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
@@ -15236,6 +15417,7 @@
         <v>2492.349413082396</v>
       </c>
       <c r="AC178" t="inlineStr"/>
+      <c r="AD178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
@@ -15321,6 +15503,7 @@
         <v>2436.594575187656</v>
       </c>
       <c r="AC179" t="inlineStr"/>
+      <c r="AD179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
@@ -15406,6 +15589,7 @@
         <v>2528.280023111007</v>
       </c>
       <c r="AC180" t="inlineStr"/>
+      <c r="AD180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
@@ -15491,6 +15675,7 @@
         <v>2951.683596514364</v>
       </c>
       <c r="AC181" t="inlineStr"/>
+      <c r="AD181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
@@ -15576,6 +15761,7 @@
         <v>3027.894268540831</v>
       </c>
       <c r="AC182" t="inlineStr"/>
+      <c r="AD182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
@@ -15661,6 +15847,7 @@
         <v>3808.569108247888</v>
       </c>
       <c r="AC183" t="inlineStr"/>
+      <c r="AD183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
@@ -15746,6 +15933,7 @@
         <v>3634.965801965276</v>
       </c>
       <c r="AC184" t="inlineStr"/>
+      <c r="AD184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
@@ -15831,6 +16019,7 @@
         <v>3655.196673489481</v>
       </c>
       <c r="AC185" t="inlineStr"/>
+      <c r="AD185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
@@ -15916,6 +16105,7 @@
         <v>3620.975326277958</v>
       </c>
       <c r="AC186" t="inlineStr"/>
+      <c r="AD186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
@@ -16001,6 +16191,7 @@
         <v>3691.856112529579</v>
       </c>
       <c r="AC187" t="inlineStr"/>
+      <c r="AD187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
@@ -16086,6 +16277,7 @@
         <v>3751.394210964366</v>
       </c>
       <c r="AC188" t="inlineStr"/>
+      <c r="AD188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
@@ -16171,6 +16363,7 @@
         <v>3735.810054974407</v>
       </c>
       <c r="AC189" t="inlineStr"/>
+      <c r="AD189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
@@ -16256,6 +16449,7 @@
         <v>3722.744323097606</v>
       </c>
       <c r="AC190" t="inlineStr"/>
+      <c r="AD190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
@@ -16341,6 +16535,7 @@
         <v>3552.503504069224</v>
       </c>
       <c r="AC191" t="inlineStr"/>
+      <c r="AD191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
@@ -16426,6 +16621,7 @@
         <v>3597.730120016881</v>
       </c>
       <c r="AC192" t="inlineStr"/>
+      <c r="AD192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
@@ -16511,6 +16707,7 @@
         <v>3643.664395245971</v>
       </c>
       <c r="AC193" t="inlineStr"/>
+      <c r="AD193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
@@ -16596,6 +16793,7 @@
         <v>3613.060039456482</v>
       </c>
       <c r="AC194" t="inlineStr"/>
+      <c r="AD194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
@@ -16681,6 +16879,7 @@
         <v>3654.842570269303</v>
       </c>
       <c r="AC195" t="inlineStr"/>
+      <c r="AD195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
@@ -16766,6 +16965,7 @@
         <v>3717.320077302724</v>
       </c>
       <c r="AC196" t="inlineStr"/>
+      <c r="AD196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
@@ -16851,6 +17051,7 @@
         <v>3704.521474176185</v>
       </c>
       <c r="AC197" t="inlineStr"/>
+      <c r="AD197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
@@ -16936,6 +17137,7 @@
         <v>3735.345835779171</v>
       </c>
       <c r="AC198" t="inlineStr"/>
+      <c r="AD198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
@@ -17021,6 +17223,7 @@
         <v>4122.917512499476</v>
       </c>
       <c r="AC199" t="inlineStr"/>
+      <c r="AD199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
@@ -17106,6 +17309,7 @@
         <v>4046.535306439408</v>
       </c>
       <c r="AC200" t="inlineStr"/>
+      <c r="AD200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
@@ -17191,6 +17395,7 @@
         <v>4307.668391641832</v>
       </c>
       <c r="AC201" t="inlineStr"/>
+      <c r="AD201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
@@ -17276,6 +17481,7 @@
         <v>4297.970968177794</v>
       </c>
       <c r="AC202" t="inlineStr"/>
+      <c r="AD202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
@@ -17361,6 +17567,7 @@
         <v>4280.53989935716</v>
       </c>
       <c r="AC203" t="inlineStr"/>
+      <c r="AD203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
@@ -17446,6 +17653,7 @@
         <v>4391.852992044212</v>
       </c>
       <c r="AC204" t="inlineStr"/>
+      <c r="AD204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
@@ -17531,6 +17739,7 @@
         <v>3873.445697906959</v>
       </c>
       <c r="AC205" t="inlineStr"/>
+      <c r="AD205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
@@ -17616,6 +17825,7 @@
         <v>4042.66892224606</v>
       </c>
       <c r="AC206" t="inlineStr"/>
+      <c r="AD206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
@@ -17701,6 +17911,7 @@
         <v>4306.43557478653</v>
       </c>
       <c r="AC207" t="inlineStr"/>
+      <c r="AD207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
@@ -17786,6 +17997,7 @@
         <v>4172.341087935875</v>
       </c>
       <c r="AC208" t="inlineStr"/>
+      <c r="AD208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
@@ -17871,6 +18083,7 @@
         <v>4186.928719658819</v>
       </c>
       <c r="AC209" t="inlineStr"/>
+      <c r="AD209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
@@ -17956,6 +18169,7 @@
         <v>4120.162554930892</v>
       </c>
       <c r="AC210" t="inlineStr"/>
+      <c r="AD210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
@@ -18041,6 +18255,7 @@
         <v>4203.865080993231</v>
       </c>
       <c r="AC211" t="inlineStr"/>
+      <c r="AD211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
@@ -18126,6 +18341,7 @@
         <v>4209.438043186523</v>
       </c>
       <c r="AC212" t="inlineStr"/>
+      <c r="AD212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
@@ -18211,6 +18427,7 @@
         <v>4206.381769820491</v>
       </c>
       <c r="AC213" t="inlineStr"/>
+      <c r="AD213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
@@ -18296,6 +18513,7 @@
         <v>3990.167987831692</v>
       </c>
       <c r="AC214" t="inlineStr"/>
+      <c r="AD214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
@@ -18381,6 +18599,7 @@
         <v>3901.267683436377</v>
       </c>
       <c r="AC215" t="inlineStr"/>
+      <c r="AD215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
@@ -18466,6 +18685,7 @@
         <v>3862.490681338301</v>
       </c>
       <c r="AC216" t="inlineStr"/>
+      <c r="AD216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
@@ -18551,6 +18771,7 @@
         <v>3712.049624220427</v>
       </c>
       <c r="AC217" t="inlineStr"/>
+      <c r="AD217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
@@ -18636,6 +18857,7 @@
         <v>3697.506488785963</v>
       </c>
       <c r="AC218" t="inlineStr"/>
+      <c r="AD218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
@@ -18721,6 +18943,7 @@
         <v>3803.173159298546</v>
       </c>
       <c r="AC219" t="inlineStr"/>
+      <c r="AD219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
@@ -18806,6 +19029,7 @@
         <v>3922.158736703291</v>
       </c>
       <c r="AC220" t="inlineStr"/>
+      <c r="AD220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
@@ -18891,6 +19115,7 @@
         <v>3909.770411367536</v>
       </c>
       <c r="AC221" t="inlineStr"/>
+      <c r="AD221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
@@ -18976,6 +19201,7 @@
         <v>3744.615637943558</v>
       </c>
       <c r="AC222" t="inlineStr"/>
+      <c r="AD222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
@@ -19061,6 +19287,7 @@
         <v>3733.118302247665</v>
       </c>
       <c r="AC223" t="inlineStr"/>
+      <c r="AD223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
@@ -19146,6 +19373,7 @@
         <v>3785.662580035585</v>
       </c>
       <c r="AC224" t="inlineStr"/>
+      <c r="AD224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
@@ -19231,6 +19459,7 @@
         <v>3707.132675814005</v>
       </c>
       <c r="AC225" t="inlineStr"/>
+      <c r="AD225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
@@ -19316,6 +19545,7 @@
         <v>3593.241267282239</v>
       </c>
       <c r="AC226" t="inlineStr"/>
+      <c r="AD226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
@@ -19401,6 +19631,7 @@
         <v>3763.261013701853</v>
       </c>
       <c r="AC227" t="inlineStr"/>
+      <c r="AD227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
@@ -19486,6 +19717,7 @@
         <v>3788.91518730673</v>
       </c>
       <c r="AC228" t="inlineStr"/>
+      <c r="AD228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
@@ -19571,6 +19803,7 @@
         <v>3907.816753855594</v>
       </c>
       <c r="AC229" t="inlineStr"/>
+      <c r="AD229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
@@ -19656,6 +19889,7 @@
         <v>4008.8679964156</v>
       </c>
       <c r="AC230" t="inlineStr"/>
+      <c r="AD230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
@@ -19741,6 +19975,7 @@
         <v>4056.002482184531</v>
       </c>
       <c r="AC231" t="inlineStr"/>
+      <c r="AD231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
@@ -19826,6 +20061,7 @@
         <v>4009.122783145364</v>
       </c>
       <c r="AC232" t="inlineStr"/>
+      <c r="AD232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
@@ -19911,6 +20147,7 @@
         <v>4152.090228715961</v>
       </c>
       <c r="AC233" t="inlineStr"/>
+      <c r="AD233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
@@ -19996,6 +20233,7 @@
         <v>3866.432379613322</v>
       </c>
       <c r="AC234" t="inlineStr"/>
+      <c r="AD234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
@@ -20081,6 +20319,7 @@
         <v>3889.894028389681</v>
       </c>
       <c r="AC235" t="inlineStr"/>
+      <c r="AD235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
@@ -20166,6 +20405,7 @@
         <v>3719.587401589422</v>
       </c>
       <c r="AC236" t="inlineStr"/>
+      <c r="AD236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
@@ -20251,6 +20491,7 @@
         <v>3832.777891898353</v>
       </c>
       <c r="AC237" t="inlineStr"/>
+      <c r="AD237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
@@ -20336,6 +20577,7 @@
         <v>3778.514396440167</v>
       </c>
       <c r="AC238" t="inlineStr"/>
+      <c r="AD238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
@@ -20421,6 +20663,7 @@
         <v>3707.496000723548</v>
       </c>
       <c r="AC239" t="inlineStr"/>
+      <c r="AD239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
@@ -20506,6 +20749,7 @@
         <v>3700.003727326001</v>
       </c>
       <c r="AC240" t="inlineStr"/>
+      <c r="AD240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
@@ -20591,6 +20835,7 @@
         <v>3674.252307600644</v>
       </c>
       <c r="AC241" t="inlineStr"/>
+      <c r="AD241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
@@ -20676,6 +20921,7 @@
         <v>3891.650958879414</v>
       </c>
       <c r="AC242" t="inlineStr"/>
+      <c r="AD242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
@@ -20761,6 +21007,7 @@
         <v>3832.05142071831</v>
       </c>
       <c r="AC243" t="inlineStr"/>
+      <c r="AD243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
@@ -20846,6 +21093,7 @@
         <v>3956.798514680825</v>
       </c>
       <c r="AC244" t="inlineStr"/>
+      <c r="AD244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
@@ -20931,6 +21179,7 @@
         <v>3940.894975884295</v>
       </c>
       <c r="AC245" t="inlineStr"/>
+      <c r="AD245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
@@ -21016,6 +21265,7 @@
         <v>3741.550625400118</v>
       </c>
       <c r="AC246" t="inlineStr"/>
+      <c r="AD246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
@@ -21101,6 +21351,7 @@
         <v>3746.27866952848</v>
       </c>
       <c r="AC247" t="inlineStr"/>
+      <c r="AD247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
@@ -21186,6 +21437,7 @@
         <v>3840.005485791751</v>
       </c>
       <c r="AC248" t="inlineStr"/>
+      <c r="AD248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
@@ -21271,6 +21523,7 @@
         <v>3827.987264340374</v>
       </c>
       <c r="AC249" t="inlineStr"/>
+      <c r="AD249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
@@ -21356,6 +21609,7 @@
         <v>3814.407695292191</v>
       </c>
       <c r="AC250" t="inlineStr"/>
+      <c r="AD250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
@@ -21441,6 +21695,7 @@
         <v>3749.926813684106</v>
       </c>
       <c r="AC251" t="inlineStr"/>
+      <c r="AD251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
@@ -21526,6 +21781,7 @@
         <v>4010.36410720406</v>
       </c>
       <c r="AC252" t="inlineStr"/>
+      <c r="AD252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
@@ -21611,6 +21867,7 @@
         <v>4252.487092663298</v>
       </c>
       <c r="AC253" t="inlineStr"/>
+      <c r="AD253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
@@ -21696,6 +21953,7 @@
         <v>4204.451640838877</v>
       </c>
       <c r="AC254" t="inlineStr"/>
+      <c r="AD254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n">
@@ -21781,6 +22039,7 @@
         <v>4062.443355814687</v>
       </c>
       <c r="AC255" t="inlineStr"/>
+      <c r="AD255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
@@ -21866,6 +22125,7 @@
         <v>4173.543273843198</v>
       </c>
       <c r="AC256" t="inlineStr"/>
+      <c r="AD256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n">
@@ -21951,6 +22211,7 @@
         <v>4760.864096288815</v>
       </c>
       <c r="AC257" t="inlineStr"/>
+      <c r="AD257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
@@ -22036,6 +22297,7 @@
         <v>4597.331333739315</v>
       </c>
       <c r="AC258" t="inlineStr"/>
+      <c r="AD258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n">
@@ -22121,6 +22383,7 @@
         <v>4438.794440404017</v>
       </c>
       <c r="AC259" t="inlineStr"/>
+      <c r="AD259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
@@ -22206,6 +22469,7 @@
         <v>4189.811776013388</v>
       </c>
       <c r="AC260" t="inlineStr"/>
+      <c r="AD260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n">
@@ -22291,6 +22555,7 @@
         <v>4784.054355096489</v>
       </c>
       <c r="AC261" t="inlineStr"/>
+      <c r="AD261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n">
@@ -22376,6 +22641,7 @@
         <v>4556.513595995847</v>
       </c>
       <c r="AC262" t="inlineStr"/>
+      <c r="AD262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n">
@@ -22461,6 +22727,7 @@
         <v>4516.607426551246</v>
       </c>
       <c r="AC263" t="inlineStr"/>
+      <c r="AD263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n">
@@ -22546,6 +22813,7 @@
         <v>4513.365804078982</v>
       </c>
       <c r="AC264" t="inlineStr"/>
+      <c r="AD264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n">
@@ -22631,6 +22899,7 @@
         <v>4594.61007558094</v>
       </c>
       <c r="AC265" t="inlineStr"/>
+      <c r="AD265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n">
@@ -22716,6 +22985,7 @@
         <v>4540.535000686935</v>
       </c>
       <c r="AC266" t="inlineStr"/>
+      <c r="AD266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n">
@@ -22801,6 +23071,7 @@
         <v>4685.031333141183</v>
       </c>
       <c r="AC267" t="inlineStr"/>
+      <c r="AD267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n">
@@ -22886,6 +23157,7 @@
         <v>4669.182367313107</v>
       </c>
       <c r="AC268" t="inlineStr"/>
+      <c r="AD268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n">
@@ -22971,6 +23243,7 @@
         <v>4504.976904266347</v>
       </c>
       <c r="AC269" t="inlineStr"/>
+      <c r="AD269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n">
@@ -23056,6 +23329,7 @@
         <v>4545.17221267261</v>
       </c>
       <c r="AC270" t="inlineStr"/>
+      <c r="AD270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n">
@@ -23141,6 +23415,7 @@
         <v>4531.288715213198</v>
       </c>
       <c r="AC271" t="inlineStr"/>
+      <c r="AD271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n">
@@ -23226,6 +23501,7 @@
         <v>5123.393113105535</v>
       </c>
       <c r="AC272" t="inlineStr"/>
+      <c r="AD272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n">
@@ -23311,6 +23587,7 @@
         <v>5345.037893688335</v>
       </c>
       <c r="AC273" t="inlineStr"/>
+      <c r="AD273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">
@@ -23396,6 +23673,7 @@
         <v>5250.354731543285</v>
       </c>
       <c r="AC274" t="inlineStr"/>
+      <c r="AD274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n">
@@ -23481,6 +23759,7 @@
         <v>5142.797680975616</v>
       </c>
       <c r="AC275" t="inlineStr"/>
+      <c r="AD275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n">
@@ -23566,6 +23845,7 @@
         <v>5278.657103546437</v>
       </c>
       <c r="AC276" t="inlineStr"/>
+      <c r="AD276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n">
@@ -23651,6 +23931,7 @@
         <v>5299.841776065652</v>
       </c>
       <c r="AC277" t="inlineStr"/>
+      <c r="AD277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n">
@@ -23736,6 +24017,7 @@
         <v>5534.544518175549</v>
       </c>
       <c r="AC278" t="inlineStr"/>
+      <c r="AD278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n">
@@ -23821,6 +24103,7 @@
         <v>5265.040274359311</v>
       </c>
       <c r="AC279" t="inlineStr"/>
+      <c r="AD279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n">
@@ -23906,6 +24189,7 @@
         <v>5606.129469437133</v>
       </c>
       <c r="AC280" t="inlineStr"/>
+      <c r="AD280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n">
@@ -23991,6 +24275,7 @@
         <v>5716.417739573675</v>
       </c>
       <c r="AC281" t="inlineStr"/>
+      <c r="AD281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n">
@@ -24076,6 +24361,7 @@
         <v>5342.884252086552</v>
       </c>
       <c r="AC282" t="inlineStr"/>
+      <c r="AD282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n">
@@ -24161,6 +24447,7 @@
         <v>5197.379260240066</v>
       </c>
       <c r="AC283" t="inlineStr"/>
+      <c r="AD283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n">
@@ -24246,6 +24533,7 @@
         <v>4832.24306968837</v>
       </c>
       <c r="AC284" t="inlineStr"/>
+      <c r="AD284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="n">
@@ -24331,6 +24619,7 @@
         <v>4982.2027685086</v>
       </c>
       <c r="AC285" t="inlineStr"/>
+      <c r="AD285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n">
@@ -24416,6 +24705,7 @@
         <v>5046.179219365993</v>
       </c>
       <c r="AC286" t="inlineStr"/>
+      <c r="AD286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n">
@@ -24501,6 +24791,7 @@
         <v>5070.888092109495</v>
       </c>
       <c r="AC287" t="inlineStr"/>
+      <c r="AD287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n">
@@ -24586,6 +24877,7 @@
         <v>5288.681769792342</v>
       </c>
       <c r="AC288" t="inlineStr"/>
+      <c r="AD288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="n">
@@ -24671,6 +24963,7 @@
         <v>4851.906405440821</v>
       </c>
       <c r="AC289" t="inlineStr"/>
+      <c r="AD289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n">
@@ -24756,6 +25049,7 @@
         <v>4873.540396117998</v>
       </c>
       <c r="AC290" t="inlineStr"/>
+      <c r="AD290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="n">
@@ -24841,6 +25135,7 @@
         <v>4889.603114649651</v>
       </c>
       <c r="AC291" t="inlineStr"/>
+      <c r="AD291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n">
@@ -24926,6 +25221,7 @@
         <v>4737.495850971753</v>
       </c>
       <c r="AC292" t="inlineStr"/>
+      <c r="AD292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="2" t="n">
@@ -25011,6 +25307,7 @@
         <v>4573.718896753327</v>
       </c>
       <c r="AC293" t="inlineStr"/>
+      <c r="AD293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="n">
@@ -25096,6 +25393,7 @@
         <v>4547.916904088344</v>
       </c>
       <c r="AC294" t="inlineStr"/>
+      <c r="AD294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="2" t="n">
@@ -25181,6 +25479,7 @@
         <v>4259.109139291179</v>
       </c>
       <c r="AC295" t="inlineStr"/>
+      <c r="AD295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n">
@@ -25266,6 +25565,7 @@
         <v>4252.039769319937</v>
       </c>
       <c r="AC296" t="inlineStr"/>
+      <c r="AD296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="n">
@@ -25351,6 +25651,7 @@
         <v>4322.919547759781</v>
       </c>
       <c r="AC297" t="inlineStr"/>
+      <c r="AD297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="n">
@@ -25436,6 +25737,7 @@
         <v>4436.225037419127</v>
       </c>
       <c r="AC298" t="inlineStr"/>
+      <c r="AD298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="2" t="n">
@@ -25521,6 +25823,7 @@
         <v>4298.441789677178</v>
       </c>
       <c r="AC299" t="inlineStr"/>
+      <c r="AD299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="n">
@@ -25606,6 +25909,7 @@
         <v>4327.395333739043</v>
       </c>
       <c r="AC300" t="inlineStr"/>
+      <c r="AD300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="n">
@@ -25691,6 +25995,7 @@
         <v>4519.591167137396</v>
       </c>
       <c r="AC301" t="inlineStr"/>
+      <c r="AD301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="n">
@@ -25776,6 +26081,7 @@
         <v>4526.840725927217</v>
       </c>
       <c r="AC302" t="inlineStr"/>
+      <c r="AD302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="2" t="n">
@@ -25861,6 +26167,7 @@
         <v>4670.708111811815</v>
       </c>
       <c r="AC303" t="inlineStr"/>
+      <c r="AD303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="n">
@@ -25946,6 +26253,7 @@
         <v>4672.602112729979</v>
       </c>
       <c r="AC304" t="inlineStr"/>
+      <c r="AD304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="n">
@@ -26031,6 +26339,7 @@
         <v>4686.42061478919</v>
       </c>
       <c r="AC305" t="inlineStr"/>
+      <c r="AD305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="n">
@@ -26116,6 +26425,7 @@
         <v>4496.929766532242</v>
       </c>
       <c r="AC306" t="inlineStr"/>
+      <c r="AD306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="2" t="n">
@@ -26201,6 +26511,7 @@
         <v>4285.408677933171</v>
       </c>
       <c r="AC307" t="inlineStr"/>
+      <c r="AD307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="n">
@@ -26286,6 +26597,7 @@
         <v>4321.1389869581</v>
       </c>
       <c r="AC308" t="inlineStr"/>
+      <c r="AD308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="2" t="n">
@@ -26371,6 +26683,7 @@
         <v>4430.346073967818</v>
       </c>
       <c r="AC309" t="inlineStr"/>
+      <c r="AD309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" s="2" t="n">
@@ -26456,6 +26769,7 @@
         <v>4652.910838804879</v>
       </c>
       <c r="AC310" t="inlineStr"/>
+      <c r="AD310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" s="2" t="n">
@@ -26541,6 +26855,7 @@
         <v>4649.929105537814</v>
       </c>
       <c r="AC311" t="inlineStr"/>
+      <c r="AD311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="n">
@@ -26626,6 +26941,7 @@
         <v>4492.428553423866</v>
       </c>
       <c r="AC312" t="inlineStr"/>
+      <c r="AD312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" s="2" t="n">
@@ -26711,6 +27027,7 @@
         <v>4474.55257816678</v>
       </c>
       <c r="AC313" t="inlineStr"/>
+      <c r="AD313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="n">
@@ -26796,6 +27113,7 @@
         <v>4336.662943667785</v>
       </c>
       <c r="AC314" t="inlineStr"/>
+      <c r="AD314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="2" t="n">
@@ -26881,6 +27199,7 @@
         <v>4241.52707366968</v>
       </c>
       <c r="AC315" t="inlineStr"/>
+      <c r="AD315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" s="2" t="n">
@@ -26966,6 +27285,7 @@
         <v>4261.08379024388</v>
       </c>
       <c r="AC316" t="inlineStr"/>
+      <c r="AD316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" s="2" t="n">
@@ -27051,6 +27371,7 @@
         <v>4243.738817019343</v>
       </c>
       <c r="AC317" t="inlineStr"/>
+      <c r="AD317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" s="2" t="n">
@@ -27136,6 +27457,7 @@
         <v>4335.931887759594</v>
       </c>
       <c r="AC318" t="inlineStr"/>
+      <c r="AD318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" s="2" t="n">
@@ -27221,6 +27543,7 @@
         <v>4247.403091834195</v>
       </c>
       <c r="AC319" t="inlineStr"/>
+      <c r="AD319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" s="2" t="n">
@@ -27306,6 +27629,7 @@
         <v>4324.309625002654</v>
       </c>
       <c r="AC320" t="inlineStr"/>
+      <c r="AD320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" s="2" t="n">
@@ -27391,6 +27715,7 @@
         <v>4278.706470308329</v>
       </c>
       <c r="AC321" t="inlineStr"/>
+      <c r="AD321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" s="2" t="n">
@@ -27476,6 +27801,7 @@
         <v>4268.577786286144</v>
       </c>
       <c r="AC322" t="inlineStr"/>
+      <c r="AD322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" s="2" t="n">
@@ -27561,6 +27887,7 @@
         <v>3909.856829756804</v>
       </c>
       <c r="AC323" t="inlineStr"/>
+      <c r="AD323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" s="2" t="n">
@@ -27646,6 +27973,7 @@
         <v>4173.737399111852</v>
       </c>
       <c r="AC324" t="inlineStr"/>
+      <c r="AD324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" s="2" t="n">
@@ -27731,6 +28059,7 @@
         <v>4108.120623113469</v>
       </c>
       <c r="AC325" t="inlineStr"/>
+      <c r="AD325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="n">
@@ -27816,6 +28145,7 @@
         <v>4501.550619312428</v>
       </c>
       <c r="AC326" t="inlineStr"/>
+      <c r="AD326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" s="2" t="n">
@@ -27901,6 +28231,7 @@
         <v>4273.382738914343</v>
       </c>
       <c r="AC327" t="inlineStr"/>
+      <c r="AD327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" s="2" t="n">
@@ -27986,6 +28317,7 @@
         <v>4351.644174098879</v>
       </c>
       <c r="AC328" t="inlineStr"/>
+      <c r="AD328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" s="2" t="n">
@@ -28071,6 +28403,7 @@
         <v>4362.079372737997</v>
       </c>
       <c r="AC329" t="inlineStr"/>
+      <c r="AD329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" s="2" t="n">
@@ -28156,6 +28489,7 @@
         <v>1888.731387447118</v>
       </c>
       <c r="AC330" t="inlineStr"/>
+      <c r="AD330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" s="2" t="n">
@@ -28241,6 +28575,7 @@
         <v>1707.02523555425</v>
       </c>
       <c r="AC331" t="inlineStr"/>
+      <c r="AD331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" s="2" t="n">
@@ -28326,6 +28661,7 @@
         <v>1758.379820807363</v>
       </c>
       <c r="AC332" t="inlineStr"/>
+      <c r="AD332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" s="2" t="n">
@@ -28411,6 +28747,7 @@
         <v>1726.734412410774</v>
       </c>
       <c r="AC333" t="inlineStr"/>
+      <c r="AD333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" s="2" t="n">
@@ -28496,6 +28833,7 @@
         <v>1710.9440877206</v>
       </c>
       <c r="AC334" t="inlineStr"/>
+      <c r="AD334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" s="2" t="n">
@@ -28581,6 +28919,7 @@
         <v>1698.551119246675</v>
       </c>
       <c r="AC335" t="inlineStr"/>
+      <c r="AD335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" s="2" t="n">
@@ -28666,6 +29005,7 @@
         <v>1718.538980694891</v>
       </c>
       <c r="AC336" t="inlineStr"/>
+      <c r="AD336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" s="2" t="n">
@@ -28751,6 +29091,7 @@
         <v>1682.366088658418</v>
       </c>
       <c r="AC337" t="inlineStr"/>
+      <c r="AD337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" s="2" t="n">
@@ -28836,6 +29177,7 @@
         <v>1679.566925662685</v>
       </c>
       <c r="AC338" t="inlineStr"/>
+      <c r="AD338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" s="2" t="n">
@@ -28921,6 +29263,7 @@
         <v>1799.473675606434</v>
       </c>
       <c r="AC339" t="inlineStr"/>
+      <c r="AD339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" s="2" t="n">
@@ -29006,6 +29349,7 @@
         <v>1828.893304190438</v>
       </c>
       <c r="AC340" t="inlineStr"/>
+      <c r="AD340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" s="2" t="n">
@@ -29091,6 +29435,7 @@
         <v>1821.185372327399</v>
       </c>
       <c r="AC341" t="inlineStr"/>
+      <c r="AD341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="n">
@@ -29176,6 +29521,7 @@
         <v>1835.154335167629</v>
       </c>
       <c r="AC342" t="inlineStr"/>
+      <c r="AD342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" s="2" t="n">
@@ -29261,6 +29607,7 @@
         <v>1843.005398671573</v>
       </c>
       <c r="AC343" t="inlineStr"/>
+      <c r="AD343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" s="2" t="n">
@@ -29346,6 +29693,7 @@
         <v>1821.592947774713</v>
       </c>
       <c r="AC344" t="inlineStr"/>
+      <c r="AD344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" s="2" t="n">
@@ -29431,6 +29779,7 @@
         <v>1829.964123315499</v>
       </c>
       <c r="AC345" t="inlineStr"/>
+      <c r="AD345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="n">
@@ -29516,6 +29865,7 @@
         <v>1796.543959245806</v>
       </c>
       <c r="AC346" t="inlineStr"/>
+      <c r="AD346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" s="2" t="n">
@@ -29601,6 +29951,7 @@
         <v>1796.134474963238</v>
       </c>
       <c r="AC347" t="inlineStr"/>
+      <c r="AD347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="n">
@@ -29686,6 +30037,7 @@
         <v>1817.76759647732</v>
       </c>
       <c r="AC348" t="inlineStr"/>
+      <c r="AD348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" s="2" t="n">
@@ -29771,6 +30123,7 @@
         <v>1797.95638706648</v>
       </c>
       <c r="AC349" t="inlineStr"/>
+      <c r="AD349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" s="2" t="n">
@@ -29856,6 +30209,7 @@
         <v>1774.737641989717</v>
       </c>
       <c r="AC350" t="inlineStr"/>
+      <c r="AD350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" s="2" t="n">
@@ -29941,6 +30295,7 @@
         <v>1735.514919864315</v>
       </c>
       <c r="AC351" t="inlineStr"/>
+      <c r="AD351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" s="2" t="n">
@@ -30026,6 +30381,7 @@
         <v>1744.540533992501</v>
       </c>
       <c r="AC352" t="inlineStr"/>
+      <c r="AD352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="2" t="n">
@@ -30111,6 +30467,7 @@
         <v>1756.953691251894</v>
       </c>
       <c r="AC353" t="inlineStr"/>
+      <c r="AD353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" s="2" t="n">
@@ -30196,6 +30553,7 @@
         <v>1750.272672499825</v>
       </c>
       <c r="AC354" t="inlineStr"/>
+      <c r="AD354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" s="2" t="n">
@@ -30281,6 +30639,7 @@
         <v>1906.169460007538</v>
       </c>
       <c r="AC355" t="inlineStr"/>
+      <c r="AD355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="n">
@@ -30366,6 +30725,7 @@
         <v>1942.345699514093</v>
       </c>
       <c r="AC356" t="inlineStr"/>
+      <c r="AD356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" s="2" t="n">
@@ -30451,6 +30811,7 @@
         <v>2048.247789477522</v>
       </c>
       <c r="AC357" t="inlineStr"/>
+      <c r="AD357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="n">
@@ -30536,6 +30897,7 @@
         <v>1994.277415377649</v>
       </c>
       <c r="AC358" t="inlineStr"/>
+      <c r="AD358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" s="2" t="n">
@@ -30621,6 +30983,7 @@
         <v>2009.65429098559</v>
       </c>
       <c r="AC359" t="inlineStr"/>
+      <c r="AD359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="n">
@@ -30706,6 +31069,7 @@
         <v>2058.668608886322</v>
       </c>
       <c r="AC360" t="inlineStr"/>
+      <c r="AD360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" s="2" t="n">
@@ -30791,6 +31155,7 @@
         <v>2012.895281375721</v>
       </c>
       <c r="AC361" t="inlineStr"/>
+      <c r="AD361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="n">
@@ -30876,6 +31241,7 @@
         <v>1964.786816021098</v>
       </c>
       <c r="AC362" t="inlineStr"/>
+      <c r="AD362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" s="2" t="n">
@@ -30961,6 +31327,7 @@
         <v>1949.642223193357</v>
       </c>
       <c r="AC363" t="inlineStr"/>
+      <c r="AD363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="n">
@@ -31046,6 +31413,7 @@
         <v>1923.701520126522</v>
       </c>
       <c r="AC364" t="inlineStr"/>
+      <c r="AD364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" s="2" t="n">
@@ -31131,6 +31499,7 @@
         <v>1996.817549871139</v>
       </c>
       <c r="AC365" t="inlineStr"/>
+      <c r="AD365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="n">
@@ -31216,6 +31585,7 @@
         <v>1969.916624309911</v>
       </c>
       <c r="AC366" t="inlineStr"/>
+      <c r="AD366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" s="2" t="n">
@@ -31301,6 +31671,7 @@
         <v>1987.733674337233</v>
       </c>
       <c r="AC367" t="inlineStr"/>
+      <c r="AD367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" s="2" t="n">
@@ -31386,6 +31757,7 @@
         <v>2034.835187928205</v>
       </c>
       <c r="AC368" t="inlineStr"/>
+      <c r="AD368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" s="2" t="n">
@@ -31471,6 +31843,7 @@
         <v>2096.346375305716</v>
       </c>
       <c r="AC369" t="inlineStr"/>
+      <c r="AD369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="n">
@@ -31556,6 +31929,7 @@
         <v>1991.410011113856</v>
       </c>
       <c r="AC370" t="inlineStr"/>
+      <c r="AD370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" s="2" t="n">
@@ -31641,6 +32015,7 @@
         <v>2009.868297641777</v>
       </c>
       <c r="AC371" t="inlineStr"/>
+      <c r="AD371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="n">
@@ -31726,6 +32101,7 @@
         <v>2019.53441291209</v>
       </c>
       <c r="AC372" t="inlineStr"/>
+      <c r="AD372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" s="2" t="n">
@@ -31811,6 +32187,7 @@
         <v>2014.174193420928</v>
       </c>
       <c r="AC373" t="inlineStr"/>
+      <c r="AD373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="n">
@@ -31896,6 +32273,7 @@
         <v>2025.733766451235</v>
       </c>
       <c r="AC374" t="inlineStr"/>
+      <c r="AD374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" s="2" t="n">
@@ -31981,6 +32359,7 @@
         <v>2000.97224522705</v>
       </c>
       <c r="AC375" t="inlineStr"/>
+      <c r="AD375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="n">
@@ -32066,6 +32445,7 @@
         <v>1952.017767146737</v>
       </c>
       <c r="AC376" t="inlineStr"/>
+      <c r="AD376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" s="2" t="n">
@@ -32151,6 +32531,7 @@
         <v>1852.817149790337</v>
       </c>
       <c r="AC377" t="inlineStr"/>
+      <c r="AD377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" s="2" t="n">
@@ -32236,6 +32617,7 @@
         <v>1866.542314173201</v>
       </c>
       <c r="AC378" t="inlineStr"/>
+      <c r="AD378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" s="2" t="n">
@@ -32321,6 +32703,7 @@
         <v>1886.923106774283</v>
       </c>
       <c r="AC379" t="inlineStr"/>
+      <c r="AD379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" s="2" t="n">
@@ -32406,6 +32789,7 @@
         <v>1895.066972708612</v>
       </c>
       <c r="AC380" t="inlineStr"/>
+      <c r="AD380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" s="2" t="n">
@@ -32491,6 +32875,7 @@
         <v>1881.6273714025</v>
       </c>
       <c r="AC381" t="inlineStr"/>
+      <c r="AD381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="n">
@@ -32576,6 +32961,7 @@
         <v>1861.04850082544</v>
       </c>
       <c r="AC382" t="inlineStr"/>
+      <c r="AD382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" s="2" t="n">
@@ -32661,6 +33047,7 @@
         <v>1776.463611027368</v>
       </c>
       <c r="AC383" t="inlineStr"/>
+      <c r="AD383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" s="2" t="n">
@@ -32746,6 +33133,7 @@
         <v>1822.306292002383</v>
       </c>
       <c r="AC384" t="inlineStr"/>
+      <c r="AD384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" s="2" t="n">
@@ -32831,6 +33219,7 @@
         <v>1854.387805779093</v>
       </c>
       <c r="AC385" t="inlineStr"/>
+      <c r="AD385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" s="2" t="n">
@@ -32916,6 +33305,7 @@
         <v>1853.329812481738</v>
       </c>
       <c r="AC386" t="inlineStr"/>
+      <c r="AD386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" s="2" t="n">
@@ -33001,6 +33391,7 @@
         <v>1937.586168783248</v>
       </c>
       <c r="AC387" t="inlineStr"/>
+      <c r="AD387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="n">
@@ -33086,6 +33477,7 @@
         <v>1968.38123312765</v>
       </c>
       <c r="AC388" t="inlineStr"/>
+      <c r="AD388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="2" t="n">
@@ -33171,6 +33563,7 @@
         <v>1914.862277482596</v>
       </c>
       <c r="AC389" t="inlineStr"/>
+      <c r="AD389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="n">
@@ -33256,6 +33649,7 @@
         <v>1837.780905932288</v>
       </c>
       <c r="AC390" t="inlineStr"/>
+      <c r="AD390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" s="2" t="n">
@@ -33341,6 +33735,7 @@
         <v>1820.911793739741</v>
       </c>
       <c r="AC391" t="inlineStr"/>
+      <c r="AD391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="n">
@@ -33426,6 +33821,7 @@
         <v>1800.984752575323</v>
       </c>
       <c r="AC392" t="inlineStr"/>
+      <c r="AD392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" s="2" t="n">
@@ -33511,6 +33907,7 @@
         <v>1821.145400177821</v>
       </c>
       <c r="AC393" t="inlineStr"/>
+      <c r="AD393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="2" t="n">
@@ -33596,6 +33993,7 @@
         <v>1827.17279515241</v>
       </c>
       <c r="AC394" t="inlineStr"/>
+      <c r="AD394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" s="2" t="n">
@@ -33681,6 +34079,7 @@
         <v>1782.773899667777</v>
       </c>
       <c r="AC395" t="inlineStr"/>
+      <c r="AD395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" s="2" t="n">
@@ -33766,6 +34165,7 @@
         <v>1791.565808808047</v>
       </c>
       <c r="AC396" t="inlineStr"/>
+      <c r="AD396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" s="2" t="n">
@@ -33851,6 +34251,7 @@
         <v>1782.222746231151</v>
       </c>
       <c r="AC397" t="inlineStr"/>
+      <c r="AD397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" s="2" t="n">
@@ -33936,6 +34337,7 @@
         <v>1736.884035224253</v>
       </c>
       <c r="AC398" t="inlineStr"/>
+      <c r="AD398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" s="2" t="n">
@@ -34021,6 +34423,7 @@
         <v>1694.165997366587</v>
       </c>
       <c r="AC399" t="inlineStr"/>
+      <c r="AD399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" s="2" t="n">
@@ -34106,6 +34509,7 @@
         <v>1656.499139079557</v>
       </c>
       <c r="AC400" t="inlineStr"/>
+      <c r="AD400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" s="2" t="n">
@@ -34191,6 +34595,7 @@
         <v>1769.632685194746</v>
       </c>
       <c r="AC401" t="inlineStr"/>
+      <c r="AD401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" s="2" t="n">
@@ -34276,6 +34681,7 @@
         <v>1791.203729477166</v>
       </c>
       <c r="AC402" t="inlineStr"/>
+      <c r="AD402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" s="2" t="n">
@@ -34361,6 +34767,7 @@
         <v>1784.181586153011</v>
       </c>
       <c r="AC403" t="inlineStr"/>
+      <c r="AD403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" s="2" t="n">
@@ -34446,6 +34853,7 @@
         <v>1760.705230304047</v>
       </c>
       <c r="AC404" t="inlineStr"/>
+      <c r="AD404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" s="2" t="n">
@@ -34531,6 +34939,7 @@
         <v>1773.527305731193</v>
       </c>
       <c r="AC405" t="inlineStr"/>
+      <c r="AD405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" s="2" t="n">
@@ -34616,6 +35025,7 @@
         <v>1799.249396402272</v>
       </c>
       <c r="AC406" t="inlineStr"/>
+      <c r="AD406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" s="2" t="n">
@@ -34701,6 +35111,7 @@
         <v>1830.076791605275</v>
       </c>
       <c r="AC407" t="inlineStr"/>
+      <c r="AD407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n">
@@ -34786,6 +35197,7 @@
         <v>1808.793499714072</v>
       </c>
       <c r="AC408" t="inlineStr"/>
+      <c r="AD408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" s="2" t="n">
@@ -34871,6 +35283,7 @@
         <v>1764.533713065386</v>
       </c>
       <c r="AC409" t="inlineStr"/>
+      <c r="AD409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n">
@@ -34956,6 +35369,7 @@
         <v>1825.496228579266</v>
       </c>
       <c r="AC410" t="inlineStr"/>
+      <c r="AD410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" s="2" t="n">
@@ -35041,6 +35455,7 @@
         <v>1837.972850768102</v>
       </c>
       <c r="AC411" t="inlineStr"/>
+      <c r="AD411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" s="2" t="n">
@@ -35126,6 +35541,7 @@
         <v>1793.266442558354</v>
       </c>
       <c r="AC412" t="inlineStr"/>
+      <c r="AD412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" s="2" t="n">
@@ -35211,6 +35627,7 @@
         <v>1793.216269116398</v>
       </c>
       <c r="AC413" t="inlineStr"/>
+      <c r="AD413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" s="2" t="n">
@@ -35296,6 +35713,7 @@
         <v>1821.692056435764</v>
       </c>
       <c r="AC414" t="inlineStr"/>
+      <c r="AD414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" s="2" t="n">
@@ -35381,6 +35799,7 @@
         <v>1802.372149115527</v>
       </c>
       <c r="AC415" t="inlineStr"/>
+      <c r="AD415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n">
@@ -35466,6 +35885,7 @@
         <v>1818.489998258178</v>
       </c>
       <c r="AC416" t="inlineStr"/>
+      <c r="AD416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n">
@@ -35551,6 +35971,7 @@
         <v>1873.312843283375</v>
       </c>
       <c r="AC417" t="inlineStr"/>
+      <c r="AD417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n">
@@ -35636,6 +36057,7 @@
         <v>1964.799827977663</v>
       </c>
       <c r="AC418" t="inlineStr"/>
+      <c r="AD418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n">
@@ -35721,6 +36143,7 @@
         <v>1985.071558042214</v>
       </c>
       <c r="AC419" t="inlineStr"/>
+      <c r="AD419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" s="2" t="n">
@@ -35806,6 +36229,7 @@
         <v>1976.053406613544</v>
       </c>
       <c r="AC420" t="inlineStr"/>
+      <c r="AD420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" s="2" t="n">
@@ -35891,6 +36315,7 @@
         <v>2018.465057541782</v>
       </c>
       <c r="AC421" t="inlineStr"/>
+      <c r="AD421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" s="2" t="n">
@@ -35976,6 +36401,7 @@
         <v>2034.833244806101</v>
       </c>
       <c r="AC422" t="inlineStr"/>
+      <c r="AD422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" s="2" t="n">
@@ -36061,6 +36487,7 @@
         <v>2036.142264987879</v>
       </c>
       <c r="AC423" t="inlineStr"/>
+      <c r="AD423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" s="2" t="n">
@@ -36146,6 +36573,7 @@
         <v>2083.486409918846</v>
       </c>
       <c r="AC424" t="inlineStr"/>
+      <c r="AD424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" s="2" t="n">
@@ -36231,6 +36659,7 @@
         <v>2108.542017909009</v>
       </c>
       <c r="AC425" t="inlineStr"/>
+      <c r="AD425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" s="2" t="n">
@@ -36316,6 +36745,7 @@
         <v>2099.617238052826</v>
       </c>
       <c r="AC426" t="inlineStr"/>
+      <c r="AD426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" s="2" t="n">
@@ -36401,6 +36831,7 @@
         <v>2106.313113643076</v>
       </c>
       <c r="AC427" t="inlineStr"/>
+      <c r="AD427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" s="2" t="n">
@@ -36486,6 +36917,7 @@
         <v>2202.254843681347</v>
       </c>
       <c r="AC428" t="inlineStr"/>
+      <c r="AD428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" s="2" t="n">
@@ -36571,6 +37003,7 @@
         <v>2218.929181801444</v>
       </c>
       <c r="AC429" t="inlineStr"/>
+      <c r="AD429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" s="2" t="n">
@@ -36656,6 +37089,7 @@
         <v>2260.820887548792</v>
       </c>
       <c r="AC430" t="inlineStr"/>
+      <c r="AD430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" s="2" t="n">
@@ -36741,6 +37175,7 @@
         <v>2161.234980461623</v>
       </c>
       <c r="AC431" t="inlineStr"/>
+      <c r="AD431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" s="2" t="n">
@@ -36826,6 +37261,7 @@
         <v>2136.065559172193</v>
       </c>
       <c r="AC432" t="inlineStr"/>
+      <c r="AD432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" s="2" t="n">
@@ -36911,6 +37347,7 @@
         <v>2150.676870768801</v>
       </c>
       <c r="AC433" t="inlineStr"/>
+      <c r="AD433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" s="2" t="n">
@@ -36996,6 +37433,7 @@
         <v>2155.601022649493</v>
       </c>
       <c r="AC434" t="inlineStr"/>
+      <c r="AD434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" s="2" t="n">
@@ -37081,6 +37519,7 @@
         <v>2190.724849065359</v>
       </c>
       <c r="AC435" t="inlineStr"/>
+      <c r="AD435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" s="2" t="n">
@@ -37166,6 +37605,7 @@
         <v>2137.951849303653</v>
       </c>
       <c r="AC436" t="inlineStr"/>
+      <c r="AD436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" s="2" t="n">
@@ -37251,6 +37691,7 @@
         <v>2134.216656503218</v>
       </c>
       <c r="AC437" t="inlineStr"/>
+      <c r="AD437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" s="2" t="n">
@@ -37336,6 +37777,7 @@
         <v>2113.901535913568</v>
       </c>
       <c r="AC438" t="inlineStr"/>
+      <c r="AD438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" s="2" t="n">
@@ -37421,6 +37863,7 @@
         <v>2064.133568282727</v>
       </c>
       <c r="AC439" t="inlineStr"/>
+      <c r="AD439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" s="2" t="n">
@@ -37506,6 +37949,7 @@
         <v>2001.648729009766</v>
       </c>
       <c r="AC440" t="inlineStr"/>
+      <c r="AD440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" s="2" t="n">
@@ -37591,6 +38035,7 @@
         <v>1977.988731698533</v>
       </c>
       <c r="AC441" t="inlineStr"/>
+      <c r="AD441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" s="2" t="n">
@@ -37676,6 +38121,7 @@
         <v>2022.817950214175</v>
       </c>
       <c r="AC442" t="inlineStr"/>
+      <c r="AD442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" s="2" t="n">
@@ -37761,6 +38207,7 @@
         <v>2073.25804087796</v>
       </c>
       <c r="AC443" t="inlineStr"/>
+      <c r="AD443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" s="2" t="n">
@@ -37846,6 +38293,7 @@
         <v>2032.237986510147</v>
       </c>
       <c r="AC444" t="inlineStr"/>
+      <c r="AD444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" s="2" t="n">
@@ -37931,6 +38379,7 @@
         <v>2068.651375348304</v>
       </c>
       <c r="AC445" t="inlineStr"/>
+      <c r="AD445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" s="2" t="n">
@@ -38016,6 +38465,7 @@
         <v>2137.090642668195</v>
       </c>
       <c r="AC446" t="inlineStr"/>
+      <c r="AD446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" s="2" t="n">
@@ -38101,6 +38551,7 @@
         <v>2141.907099609411</v>
       </c>
       <c r="AC447" t="inlineStr"/>
+      <c r="AD447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" s="2" t="n">
@@ -38186,6 +38637,7 @@
         <v>2170.54574827892</v>
       </c>
       <c r="AC448" t="inlineStr"/>
+      <c r="AD448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" s="2" t="n">
@@ -38271,6 +38723,7 @@
         <v>2199.125904166428</v>
       </c>
       <c r="AC449" t="inlineStr"/>
+      <c r="AD449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" s="2" t="n">
@@ -38356,6 +38809,7 @@
         <v>2172.999846377275</v>
       </c>
       <c r="AC450" t="inlineStr"/>
+      <c r="AD450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" s="2" t="n">
@@ -38441,6 +38895,7 @@
         <v>2279.41132775804</v>
       </c>
       <c r="AC451" t="inlineStr"/>
+      <c r="AD451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" s="2" t="n">
@@ -38526,6 +38981,7 @@
         <v>2344.451602572868</v>
       </c>
       <c r="AC452" t="inlineStr"/>
+      <c r="AD452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" s="2" t="n">
@@ -38611,6 +39067,7 @@
         <v>2227.506783693061</v>
       </c>
       <c r="AC453" t="inlineStr"/>
+      <c r="AD453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" s="2" t="n">
@@ -38696,6 +39153,7 @@
         <v>2193.718081816578</v>
       </c>
       <c r="AC454" t="inlineStr"/>
+      <c r="AD454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" s="2" t="n">
@@ -38781,6 +39239,7 @@
         <v>2203.134166553241</v>
       </c>
       <c r="AC455" t="inlineStr"/>
+      <c r="AD455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" s="2" t="n">
@@ -38866,6 +39325,7 @@
         <v>2209.320570833494</v>
       </c>
       <c r="AC456" t="inlineStr"/>
+      <c r="AD456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" s="2" t="n">
@@ -38951,6 +39411,7 @@
         <v>2157.908734425898</v>
       </c>
       <c r="AC457" t="inlineStr"/>
+      <c r="AD457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" s="2" t="n">
@@ -39036,6 +39497,7 @@
         <v>2083.882573732221</v>
       </c>
       <c r="AC458" t="inlineStr"/>
+      <c r="AD458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" s="2" t="n">
@@ -39121,6 +39583,7 @@
         <v>2151.638376112543</v>
       </c>
       <c r="AC459" t="inlineStr"/>
+      <c r="AD459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" s="2" t="n">
@@ -39206,6 +39669,7 @@
         <v>1909.328991503995</v>
       </c>
       <c r="AC460" t="inlineStr"/>
+      <c r="AD460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" s="2" t="n">
@@ -39291,6 +39755,7 @@
         <v>2258.534282593445</v>
       </c>
       <c r="AC461" t="inlineStr"/>
+      <c r="AD461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" s="2" t="n">
@@ -39376,6 +39841,7 @@
         <v>2240.855547317596</v>
       </c>
       <c r="AC462" t="inlineStr"/>
+      <c r="AD462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" s="2" t="n">
@@ -39461,6 +39927,7 @@
         <v>2220.086923177616</v>
       </c>
       <c r="AC463" t="inlineStr"/>
+      <c r="AD463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" s="2" t="n">
@@ -39546,6 +40013,7 @@
         <v>2098.815578638913</v>
       </c>
       <c r="AC464" t="inlineStr"/>
+      <c r="AD464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" s="2" t="n">
@@ -39631,6 +40099,7 @@
         <v>2160.901825758922</v>
       </c>
       <c r="AC465" t="inlineStr"/>
+      <c r="AD465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" s="2" t="n">
@@ -39716,6 +40185,7 @@
         <v>2154.917159463049</v>
       </c>
       <c r="AC466" t="inlineStr"/>
+      <c r="AD466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" s="2" t="n">
@@ -39801,6 +40271,7 @@
         <v>2189.427813296947</v>
       </c>
       <c r="AC467" t="inlineStr"/>
+      <c r="AD467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" s="2" t="n">
@@ -39886,6 +40357,7 @@
         <v>2108.747062148099</v>
       </c>
       <c r="AC468" t="inlineStr"/>
+      <c r="AD468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" s="2" t="n">
@@ -39971,6 +40443,7 @@
         <v>2113.378327657218</v>
       </c>
       <c r="AC469" t="inlineStr"/>
+      <c r="AD469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" s="2" t="n">
@@ -40058,6 +40531,7 @@
         <v>2112.568267245224</v>
       </c>
       <c r="AC470" t="inlineStr"/>
+      <c r="AD470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" s="2" t="n">
@@ -40145,6 +40619,7 @@
         <v>2103.439633682087</v>
       </c>
       <c r="AC471" t="inlineStr"/>
+      <c r="AD471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" s="2" t="n">
@@ -40232,6 +40707,7 @@
         <v>2125.246919086833</v>
       </c>
       <c r="AC472" t="inlineStr"/>
+      <c r="AD472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" s="2" t="n">
@@ -40319,6 +40795,7 @@
         <v>2136.76052781092</v>
       </c>
       <c r="AC473" t="inlineStr"/>
+      <c r="AD473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" s="2" t="n">
@@ -40406,6 +40883,7 @@
         <v>2106.354530524926</v>
       </c>
       <c r="AC474" t="inlineStr"/>
+      <c r="AD474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" s="2" t="n">
@@ -40493,6 +40971,7 @@
         <v>2098.484339366055</v>
       </c>
       <c r="AC475" t="inlineStr"/>
+      <c r="AD475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" s="2" t="n">
@@ -40580,6 +41059,7 @@
         <v>2038.910042869343</v>
       </c>
       <c r="AC476" t="inlineStr"/>
+      <c r="AD476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" s="2" t="n">
@@ -40667,6 +41147,7 @@
         <v>2103.013800222152</v>
       </c>
       <c r="AC477" t="inlineStr"/>
+      <c r="AD477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" s="2" t="n">
@@ -40754,6 +41235,7 @@
         <v>2113.443417834197</v>
       </c>
       <c r="AC478" t="inlineStr"/>
+      <c r="AD478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" s="2" t="n">
@@ -40841,6 +41323,7 @@
         <v>2120.957732523177</v>
       </c>
       <c r="AC479" t="inlineStr"/>
+      <c r="AD479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" s="2" t="n">
@@ -40928,6 +41411,7 @@
         <v>2153.027616650447</v>
       </c>
       <c r="AC480" t="inlineStr"/>
+      <c r="AD480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" s="2" t="n">
@@ -41015,6 +41499,7 @@
         <v>2191.357683716839</v>
       </c>
       <c r="AC481" t="inlineStr"/>
+      <c r="AD481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" s="2" t="n">
@@ -41102,6 +41587,7 @@
         <v>2219.515515147111</v>
       </c>
       <c r="AC482" t="inlineStr"/>
+      <c r="AD482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" s="2" t="n">
@@ -41189,6 +41675,7 @@
         <v>2210.304914007587</v>
       </c>
       <c r="AC483" t="inlineStr"/>
+      <c r="AD483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" s="2" t="n">
@@ -41276,6 +41763,7 @@
         <v>2197.786462736585</v>
       </c>
       <c r="AC484" t="inlineStr"/>
+      <c r="AD484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" s="2" t="n">
@@ -41363,6 +41851,7 @@
         <v>2180.762138894472</v>
       </c>
       <c r="AC485" t="inlineStr"/>
+      <c r="AD485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" s="2" t="n">
@@ -41450,6 +41939,7 @@
         <v>2187.944303937115</v>
       </c>
       <c r="AC486" t="inlineStr"/>
+      <c r="AD486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" s="2" t="n">
@@ -41537,6 +42027,7 @@
         <v>2189.79335538551</v>
       </c>
       <c r="AC487" t="inlineStr"/>
+      <c r="AD487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" s="2" t="n">
@@ -41624,6 +42115,7 @@
         <v>2219.599413428947</v>
       </c>
       <c r="AC488" t="inlineStr"/>
+      <c r="AD488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" s="2" t="n">
@@ -41711,6 +42203,7 @@
         <v>2181.793806747809</v>
       </c>
       <c r="AC489" t="inlineStr"/>
+      <c r="AD489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" s="2" t="n">
@@ -41798,6 +42291,7 @@
         <v>2192.169618079853</v>
       </c>
       <c r="AC490" t="inlineStr"/>
+      <c r="AD490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" s="2" t="n">
@@ -41885,6 +42379,7 @@
         <v>2173.717301109536</v>
       </c>
       <c r="AC491" t="inlineStr"/>
+      <c r="AD491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" s="2" t="n">
@@ -41972,6 +42467,7 @@
         <v>2128.394173077171</v>
       </c>
       <c r="AC492" t="inlineStr"/>
+      <c r="AD492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" s="2" t="n">
@@ -42059,6 +42555,7 @@
         <v>2107.987692473656</v>
       </c>
       <c r="AC493" t="inlineStr"/>
+      <c r="AD493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" s="2" t="n">
@@ -42146,6 +42643,7 @@
         <v>2125.711910906628</v>
       </c>
       <c r="AC494" t="inlineStr"/>
+      <c r="AD494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" s="2" t="n">
@@ -42233,6 +42731,7 @@
         <v>2063.791511205991</v>
       </c>
       <c r="AC495" t="inlineStr"/>
+      <c r="AD495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" s="2" t="n">
@@ -42320,6 +42819,7 @@
         <v>2093.351415355541</v>
       </c>
       <c r="AC496" t="inlineStr"/>
+      <c r="AD496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" s="2" t="n">
@@ -42407,6 +42907,7 @@
         <v>2094.20686583158</v>
       </c>
       <c r="AC497" t="inlineStr"/>
+      <c r="AD497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" s="2" t="n">
@@ -42494,6 +42995,7 @@
         <v>2108.586190723217</v>
       </c>
       <c r="AC498" t="inlineStr"/>
+      <c r="AD498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" s="2" t="n">
@@ -42545,6 +43047,7 @@
         <v>2126.892822000505</v>
       </c>
       <c r="AC499" t="inlineStr"/>
+      <c r="AD499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" s="2" t="n">
@@ -42596,6 +43099,7 @@
         <v>2112.708343670658</v>
       </c>
       <c r="AC500" t="inlineStr"/>
+      <c r="AD500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" s="2" t="n">
@@ -42647,6 +43151,7 @@
         <v>2188.747512344298</v>
       </c>
       <c r="AC501" t="inlineStr"/>
+      <c r="AD501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" s="2" t="n">
@@ -42698,6 +43203,7 @@
         <v>2214.679924184721</v>
       </c>
       <c r="AC502" t="inlineStr"/>
+      <c r="AD502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" s="2" t="n">
@@ -42749,6 +43255,7 @@
         <v>2234.106691040385</v>
       </c>
       <c r="AC503" t="inlineStr"/>
+      <c r="AD503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" s="2" t="n">
@@ -42800,6 +43307,7 @@
         <v>2230.94269374406</v>
       </c>
       <c r="AC504" t="inlineStr"/>
+      <c r="AD504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" s="2" t="n">
@@ -42887,6 +43395,7 @@
         <v>2245.280807108615</v>
       </c>
       <c r="AC505" t="inlineStr"/>
+      <c r="AD505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" s="2" t="n">
@@ -42938,6 +43447,7 @@
         <v>2272.826653349826</v>
       </c>
       <c r="AC506" t="inlineStr"/>
+      <c r="AD506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" s="2" t="n">
@@ -42989,6 +43499,7 @@
         <v>2209.952099429805</v>
       </c>
       <c r="AC507" t="inlineStr"/>
+      <c r="AD507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" s="2" t="n">
@@ -43040,6 +43551,7 @@
         <v>2242.769565502349</v>
       </c>
       <c r="AC508" t="inlineStr"/>
+      <c r="AD508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" s="2" t="n">
@@ -43091,6 +43603,7 @@
         <v>2211.83595729533</v>
       </c>
       <c r="AC509" t="inlineStr"/>
+      <c r="AD509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" s="2" t="n">
@@ -43142,6 +43655,7 @@
         <v>2044.90734627641</v>
       </c>
       <c r="AC510" t="inlineStr"/>
+      <c r="AD510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" s="2" t="n">
@@ -43193,6 +43707,7 @@
         <v>2004.624939706665</v>
       </c>
       <c r="AC511" t="inlineStr"/>
+      <c r="AD511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" s="2" t="n">
@@ -43244,6 +43759,7 @@
         <v>2078.259690502081</v>
       </c>
       <c r="AC512" t="inlineStr"/>
+      <c r="AD512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" s="2" t="n">
@@ -43295,6 +43811,7 @@
         <v>2095.23104099705</v>
       </c>
       <c r="AC513" t="inlineStr"/>
+      <c r="AD513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" s="2" t="n">
@@ -43346,6 +43863,7 @@
         <v>2052.491069103678</v>
       </c>
       <c r="AC514" t="inlineStr"/>
+      <c r="AD514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" s="2" t="n">
@@ -43397,6 +43915,7 @@
         <v>2031.321754223382</v>
       </c>
       <c r="AC515" t="inlineStr"/>
+      <c r="AD515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" s="2" t="n">
@@ -43448,6 +43967,7 @@
         <v>1988.239313600253</v>
       </c>
       <c r="AC516" t="inlineStr"/>
+      <c r="AD516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" s="2" t="n">
@@ -43499,6 +44019,7 @@
         <v>1951.659925245096</v>
       </c>
       <c r="AC517" t="inlineStr"/>
+      <c r="AD517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" s="2" t="n">
@@ -43550,6 +44071,7 @@
         <v>1968.131915135483</v>
       </c>
       <c r="AC518" t="inlineStr"/>
+      <c r="AD518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" s="2" t="n">
@@ -43601,6 +44123,7 @@
         <v>2001.819401249928</v>
       </c>
       <c r="AC519" t="inlineStr"/>
+      <c r="AD519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" s="2" t="n">
@@ -43652,6 +44175,7 @@
         <v>2028.602035390531</v>
       </c>
       <c r="AC520" t="inlineStr"/>
+      <c r="AD520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" s="2" t="n">
@@ -43703,6 +44227,7 @@
         <v>1997.234279551072</v>
       </c>
       <c r="AC521" t="inlineStr"/>
+      <c r="AD521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" s="2" t="n">
@@ -43754,6 +44279,7 @@
         <v>1987.286762402897</v>
       </c>
       <c r="AC522" t="inlineStr"/>
+      <c r="AD522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" s="2" t="n">
@@ -43805,6 +44331,7 @@
         <v>2004.503304566288</v>
       </c>
       <c r="AC523" t="inlineStr"/>
+      <c r="AD523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" s="2" t="n">
@@ -43856,6 +44383,7 @@
         <v>1995.699205892551</v>
       </c>
       <c r="AC524" t="inlineStr"/>
+      <c r="AD524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" s="2" t="n">
@@ -43907,6 +44435,7 @@
         <v>1989.975224331769</v>
       </c>
       <c r="AC525" t="inlineStr"/>
+      <c r="AD525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" s="2" t="n">
@@ -43958,6 +44487,7 @@
         <v>2033.152258273704</v>
       </c>
       <c r="AC526" t="inlineStr"/>
+      <c r="AD526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" s="2" t="n">
@@ -44009,6 +44539,7 @@
         <v>2021.07174850717</v>
       </c>
       <c r="AC527" t="inlineStr"/>
+      <c r="AD527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" s="2" t="n">
@@ -44060,6 +44591,7 @@
         <v>1999.088476692584</v>
       </c>
       <c r="AC528" t="inlineStr"/>
+      <c r="AD528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" s="2" t="n">
@@ -44111,6 +44643,7 @@
         <v>1965.638618871186</v>
       </c>
       <c r="AC529" t="inlineStr"/>
+      <c r="AD529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" s="2" t="n">
@@ -44162,6 +44695,7 @@
         <v>1934.058865208209</v>
       </c>
       <c r="AC530" t="inlineStr"/>
+      <c r="AD530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" s="2" t="n">
@@ -44213,6 +44747,7 @@
         <v>1957.766720660573</v>
       </c>
       <c r="AC531" t="inlineStr"/>
+      <c r="AD531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" s="2" t="n">
@@ -44264,6 +44799,7 @@
         <v>1967.313415740537</v>
       </c>
       <c r="AC532" t="inlineStr"/>
+      <c r="AD532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" s="2" t="n">
@@ -44315,6 +44851,7 @@
         <v>1969.217634657179</v>
       </c>
       <c r="AC533" t="inlineStr"/>
+      <c r="AD533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" s="2" t="n">
@@ -44366,6 +44903,7 @@
         <v>1856.917316977275</v>
       </c>
       <c r="AC534" t="inlineStr"/>
+      <c r="AD534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" s="2" t="n">
@@ -44417,6 +44955,7 @@
         <v>1857.721413997464</v>
       </c>
       <c r="AC535" t="inlineStr"/>
+      <c r="AD535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" s="2" t="n">
@@ -44468,6 +45007,7 @@
         <v>1885.022302747029</v>
       </c>
       <c r="AC536" t="inlineStr"/>
+      <c r="AD536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" s="2" t="n">
@@ -44519,6 +45059,7 @@
         <v>1850.73910118266</v>
       </c>
       <c r="AC537" t="inlineStr"/>
+      <c r="AD537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" s="2" t="n">
@@ -44570,6 +45111,7 @@
         <v>1909.153827956249</v>
       </c>
       <c r="AC538" t="inlineStr"/>
+      <c r="AD538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" s="2" t="n">
@@ -44621,6 +45163,7 @@
         <v>1902.155130311744</v>
       </c>
       <c r="AC539" t="inlineStr"/>
+      <c r="AD539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" s="2" t="n">
@@ -44672,6 +45215,7 @@
         <v>1903.120766616629</v>
       </c>
       <c r="AC540" t="inlineStr"/>
+      <c r="AD540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" s="2" t="n">
@@ -44723,6 +45267,7 @@
         <v>1936.690953129875</v>
       </c>
       <c r="AC541" t="inlineStr"/>
+      <c r="AD541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" s="2" t="n">
@@ -44774,6 +45319,7 @@
         <v>1922.213313330383</v>
       </c>
       <c r="AC542" t="inlineStr"/>
+      <c r="AD542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" s="2" t="n">
@@ -44825,6 +45371,7 @@
         <v>1908.042399670285</v>
       </c>
       <c r="AC543" t="inlineStr"/>
+      <c r="AD543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" s="2" t="n">
@@ -44876,6 +45423,7 @@
         <v>1890.817313391876</v>
       </c>
       <c r="AC544" t="inlineStr"/>
+      <c r="AD544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" s="2" t="n">
@@ -44927,6 +45475,7 @@
         <v>1872.825268540986</v>
       </c>
       <c r="AC545" t="inlineStr"/>
+      <c r="AD545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" s="2" t="n">
@@ -44978,6 +45527,7 @@
         <v>1889.928171224892</v>
       </c>
       <c r="AC546" t="inlineStr"/>
+      <c r="AD546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" s="2" t="n">
@@ -45029,6 +45579,7 @@
         <v>1872.523647026367</v>
       </c>
       <c r="AC547" t="inlineStr"/>
+      <c r="AD547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" s="2" t="n">
@@ -45080,6 +45631,7 @@
         <v>1861.196582327113</v>
       </c>
       <c r="AC548" t="inlineStr"/>
+      <c r="AD548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" s="2" t="n">
@@ -45131,6 +45683,7 @@
         <v>1859.437910549965</v>
       </c>
       <c r="AC549" t="inlineStr"/>
+      <c r="AD549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" s="2" t="n">
@@ -45182,6 +45735,7 @@
         <v>1833.264346950139</v>
       </c>
       <c r="AC550" t="inlineStr"/>
+      <c r="AD550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" s="2" t="n">
@@ -45233,6 +45787,7 @@
         <v>1785.008111341774</v>
       </c>
       <c r="AC551" t="inlineStr"/>
+      <c r="AD551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" s="2" t="n">
@@ -45284,6 +45839,7 @@
         <v>1754.598070631351</v>
       </c>
       <c r="AC552" t="inlineStr"/>
+      <c r="AD552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" s="2" t="n">
@@ -45335,6 +45891,7 @@
         <v>1741.58453869891</v>
       </c>
       <c r="AC553" t="inlineStr"/>
+      <c r="AD553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" s="2" t="n">
@@ -45386,6 +45943,7 @@
         <v>1751.358384433655</v>
       </c>
       <c r="AC554" t="inlineStr"/>
+      <c r="AD554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" s="2" t="n">
@@ -45437,6 +45995,7 @@
         <v>1757.386195721643</v>
       </c>
       <c r="AC555" t="inlineStr"/>
+      <c r="AD555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" s="2" t="n">
@@ -45488,6 +46047,7 @@
         <v>1754.635400650817</v>
       </c>
       <c r="AC556" t="inlineStr"/>
+      <c r="AD556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" s="2" t="n">
@@ -45539,6 +46099,7 @@
         <v>1780.181806940675</v>
       </c>
       <c r="AC557" t="inlineStr"/>
+      <c r="AD557" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" s="2" t="n">
@@ -45590,6 +46151,7 @@
         <v>1799.491928870578</v>
       </c>
       <c r="AC558" t="inlineStr"/>
+      <c r="AD558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" s="2" t="n">
@@ -45641,6 +46203,7 @@
         <v>1801.998067405033</v>
       </c>
       <c r="AC559" t="inlineStr"/>
+      <c r="AD559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" s="2" t="n">
@@ -45694,6 +46257,7 @@
       <c r="AC560" t="n">
         <v>22.10304</v>
       </c>
+      <c r="AD560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" s="2" t="n">
@@ -45747,6 +46311,7 @@
       <c r="AC561" t="n">
         <v>20.54112</v>
       </c>
+      <c r="AD561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" s="2" t="n">
@@ -45800,6 +46365,7 @@
       <c r="AC562" t="n">
         <v>16.50768</v>
       </c>
+      <c r="AD562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" s="2" t="n">
@@ -45853,6 +46419,7 @@
       <c r="AC563" t="n">
         <v>15.01488</v>
       </c>
+      <c r="AD563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" s="2" t="n">
@@ -45906,6 +46473,7 @@
       <c r="AC564" t="n">
         <v>16.25856</v>
       </c>
+      <c r="AD564" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" s="2" t="n">
@@ -45959,6 +46527,7 @@
       <c r="AC565" t="n">
         <v>17.64336</v>
       </c>
+      <c r="AD565" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" s="2" t="n">
@@ -46012,6 +46581,7 @@
       <c r="AC566" t="n">
         <v>17.28336</v>
       </c>
+      <c r="AD566" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" s="2" t="n">
@@ -46065,6 +46635,7 @@
       <c r="AC567" t="n">
         <v>16.3944</v>
       </c>
+      <c r="AD567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" s="2" t="n">
@@ -46118,6 +46689,7 @@
       <c r="AC568" t="n">
         <v>16.45344</v>
       </c>
+      <c r="AD568" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" s="2" t="n">
@@ -46171,6 +46743,7 @@
       <c r="AC569" t="n">
         <v>19.46304</v>
       </c>
+      <c r="AD569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" s="2" t="n">
@@ -46224,6 +46797,7 @@
       <c r="AC570" t="n">
         <v>20.78496</v>
       </c>
+      <c r="AD570" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" s="2" t="n">
@@ -46277,6 +46851,7 @@
       <c r="AC571" t="n">
         <v>19.41264</v>
       </c>
+      <c r="AD571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" s="2" t="n">
@@ -46330,6 +46905,7 @@
       <c r="AC572" t="n">
         <v>21.64272</v>
       </c>
+      <c r="AD572" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" s="2" t="n">
@@ -46383,6 +46959,7 @@
       <c r="AC573" t="n">
         <v>21.83952</v>
       </c>
+      <c r="AD573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" s="2" t="n">
@@ -46436,6 +47013,7 @@
       <c r="AC574" t="n">
         <v>21.2688</v>
       </c>
+      <c r="AD574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" s="2" t="n">
@@ -46489,6 +47067,7 @@
       <c r="AC575" t="n">
         <v>19.40688</v>
       </c>
+      <c r="AD575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" s="2" t="n">
@@ -46542,6 +47121,7 @@
       <c r="AC576" t="n">
         <v>19.85136</v>
       </c>
+      <c r="AD576" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" s="2" t="n">
@@ -46595,6 +47175,7 @@
       <c r="AC577" t="n">
         <v>19.42128</v>
       </c>
+      <c r="AD577" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" s="2" t="n">
@@ -46648,6 +47229,7 @@
       <c r="AC578" t="n">
         <v>18.07776</v>
       </c>
+      <c r="AD578" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" s="2" t="n">
@@ -46701,6 +47283,7 @@
       <c r="AC579" t="n">
         <v>18.6456</v>
       </c>
+      <c r="AD579" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" s="2" t="n">
@@ -46754,6 +47337,7 @@
       <c r="AC580" t="n">
         <v>21.31296</v>
       </c>
+      <c r="AD580" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" s="2" t="n">
@@ -46807,6 +47391,7 @@
       <c r="AC581" t="n">
         <v>21.4608</v>
       </c>
+      <c r="AD581" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" s="2" t="n">
@@ -46860,6 +47445,7 @@
       <c r="AC582" t="n">
         <v>21.18336</v>
       </c>
+      <c r="AD582" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" s="2" t="n">
@@ -46913,6 +47499,7 @@
       <c r="AC583" t="n">
         <v>20.71584</v>
       </c>
+      <c r="AD583" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" s="2" t="n">
@@ -46966,6 +47553,7 @@
       <c r="AC584" t="n">
         <v>20.03568</v>
       </c>
+      <c r="AD584" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" s="2" t="n">
@@ -47019,6 +47607,7 @@
       <c r="AC585" t="n">
         <v>21.53616</v>
       </c>
+      <c r="AD585" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" s="2" t="n">
@@ -47072,6 +47661,7 @@
       <c r="AC586" t="n">
         <v>21.02784</v>
       </c>
+      <c r="AD586" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" s="2" t="n">
@@ -47125,6 +47715,7 @@
       <c r="AC587" t="n">
         <v>21.5112</v>
       </c>
+      <c r="AD587" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" s="2" t="n">
@@ -47178,6 +47769,7 @@
       <c r="AC588" t="n">
         <v>24.7728</v>
       </c>
+      <c r="AD588" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" s="2" t="n">
@@ -47231,6 +47823,7 @@
       <c r="AC589" t="n">
         <v>25.4424</v>
       </c>
+      <c r="AD589" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" s="2" t="n">
@@ -47284,6 +47877,7 @@
       <c r="AC590" t="n">
         <v>25.94352</v>
       </c>
+      <c r="AD590" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" s="2" t="n">
@@ -47337,6 +47931,7 @@
       <c r="AC591" t="n">
         <v>25.42128</v>
       </c>
+      <c r="AD591" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" s="2" t="n">
@@ -47390,6 +47985,7 @@
       <c r="AC592" t="n">
         <v>24.59088</v>
       </c>
+      <c r="AD592" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" s="2" t="n">
@@ -47441,6 +48037,7 @@
         <v>1825.091817413493</v>
       </c>
       <c r="AC593" t="inlineStr"/>
+      <c r="AD593" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" s="2" t="n">
@@ -47492,6 +48089,7 @@
         <v>1840.031392285577</v>
       </c>
       <c r="AC594" t="inlineStr"/>
+      <c r="AD594" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" s="2" t="n">
@@ -47543,6 +48141,7 @@
         <v>1876.409017168803</v>
       </c>
       <c r="AC595" t="inlineStr"/>
+      <c r="AD595" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" s="2" t="n">
@@ -47594,6 +48193,7 @@
         <v>1872.271046336702</v>
       </c>
       <c r="AC596" t="inlineStr"/>
+      <c r="AD596" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" s="2" t="n">
@@ -47645,6 +48245,7 @@
         <v>1869.418297099098</v>
       </c>
       <c r="AC597" t="inlineStr"/>
+      <c r="AD597" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" s="2" t="n">
@@ -47696,6 +48297,7 @@
         <v>1881.707956330215</v>
       </c>
       <c r="AC598" t="inlineStr"/>
+      <c r="AD598" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" s="2" t="n">
@@ -47747,6 +48349,7 @@
         <v>1895.811083908858</v>
       </c>
       <c r="AC599" t="inlineStr"/>
+      <c r="AD599" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" s="2" t="n">
@@ -47798,6 +48401,7 @@
         <v>1876.443860979936</v>
       </c>
       <c r="AC600" t="inlineStr"/>
+      <c r="AD600" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" s="2" t="n">
@@ -47849,6 +48453,7 @@
         <v>1895.026642768046</v>
       </c>
       <c r="AC601" t="inlineStr"/>
+      <c r="AD601" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" s="2" t="n">
@@ -47900,6 +48505,7 @@
         <v>1917.45840836555</v>
       </c>
       <c r="AC602" t="inlineStr"/>
+      <c r="AD602" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" s="2" t="n">
@@ -47951,6 +48557,7 @@
         <v>1901.813836812291</v>
       </c>
       <c r="AC603" t="inlineStr"/>
+      <c r="AD603" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" s="2" t="n">
@@ -48002,6 +48609,7 @@
         <v>1903.16731714994</v>
       </c>
       <c r="AC604" t="inlineStr"/>
+      <c r="AD604" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" s="2" t="n">
@@ -48053,6 +48661,7 @@
         <v>1956.137301202464</v>
       </c>
       <c r="AC605" t="inlineStr"/>
+      <c r="AD605" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" s="2" t="n">
@@ -48104,6 +48713,7 @@
         <v>1945.199593805536</v>
       </c>
       <c r="AC606" t="inlineStr"/>
+      <c r="AD606" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" s="2" t="n">
@@ -48155,6 +48765,7 @@
         <v>1981.74628812719</v>
       </c>
       <c r="AC607" t="inlineStr"/>
+      <c r="AD607" t="inlineStr"/>
     </row>
     <row r="608">
       <c r="A608" s="2" t="n">
@@ -48206,6 +48817,7 @@
         <v>1967.18215438582</v>
       </c>
       <c r="AC608" t="inlineStr"/>
+      <c r="AD608" t="inlineStr"/>
     </row>
     <row r="609">
       <c r="A609" s="2" t="n">
@@ -48257,6 +48869,7 @@
         <v>2016.639897913845</v>
       </c>
       <c r="AC609" t="inlineStr"/>
+      <c r="AD609" t="inlineStr"/>
     </row>
     <row r="610">
       <c r="A610" s="2" t="n">
@@ -48308,6 +48921,7 @@
         <v>2005.556446471525</v>
       </c>
       <c r="AC610" t="inlineStr"/>
+      <c r="AD610" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" s="2" t="n">
@@ -48359,6 +48973,7 @@
         <v>1969.650969565639</v>
       </c>
       <c r="AC611" t="inlineStr"/>
+      <c r="AD611" t="inlineStr"/>
     </row>
     <row r="612">
       <c r="A612" s="2" t="n">
@@ -48410,6 +49025,7 @@
         <v>1876.020966348472</v>
       </c>
       <c r="AC612" t="inlineStr"/>
+      <c r="AD612" t="inlineStr"/>
     </row>
     <row r="613">
       <c r="A613" s="2" t="n">
@@ -48461,6 +49077,7 @@
         <v>1890.998035065898</v>
       </c>
       <c r="AC613" t="inlineStr"/>
+      <c r="AD613" t="inlineStr"/>
     </row>
     <row r="614">
       <c r="A614" s="2" t="n">
@@ -48512,6 +49129,7 @@
         <v>1923.79195377328</v>
       </c>
       <c r="AC614" t="inlineStr"/>
+      <c r="AD614" t="inlineStr"/>
     </row>
     <row r="615">
       <c r="A615" s="2" t="n">
@@ -48563,6 +49181,7 @@
         <v>1884.269034912238</v>
       </c>
       <c r="AC615" t="inlineStr"/>
+      <c r="AD615" t="inlineStr"/>
     </row>
     <row r="616">
       <c r="A616" s="2" t="n">
@@ -48614,6 +49233,7 @@
         <v>1870.375907626861</v>
       </c>
       <c r="AC616" t="inlineStr"/>
+      <c r="AD616" t="inlineStr"/>
     </row>
     <row r="617">
       <c r="A617" s="2" t="n">
@@ -48665,6 +49285,7 @@
         <v>1863.380970903366</v>
       </c>
       <c r="AC617" t="inlineStr"/>
+      <c r="AD617" t="inlineStr"/>
     </row>
     <row r="618">
       <c r="A618" s="2" t="n">
@@ -48716,6 +49337,7 @@
         <v>1873.599736099972</v>
       </c>
       <c r="AC618" t="inlineStr"/>
+      <c r="AD618" t="inlineStr"/>
     </row>
     <row r="619">
       <c r="A619" s="2" t="n">
@@ -48767,6 +49389,7 @@
         <v>1866.58898750614</v>
       </c>
       <c r="AC619" t="inlineStr"/>
+      <c r="AD619" t="inlineStr"/>
     </row>
     <row r="620">
       <c r="A620" s="2" t="n">
@@ -48818,6 +49441,7 @@
         <v>1870.40784995795</v>
       </c>
       <c r="AC620" t="inlineStr"/>
+      <c r="AD620" t="inlineStr"/>
     </row>
     <row r="621">
       <c r="A621" s="2" t="n">
@@ -48869,6 +49493,7 @@
         <v>1854.899888365838</v>
       </c>
       <c r="AC621" t="inlineStr"/>
+      <c r="AD621" t="inlineStr"/>
     </row>
     <row r="622">
       <c r="A622" s="2" t="n">
@@ -48920,6 +49545,7 @@
         <v>1847.696939016764</v>
       </c>
       <c r="AC622" t="inlineStr"/>
+      <c r="AD622" t="inlineStr"/>
     </row>
     <row r="623">
       <c r="A623" s="2" t="n">
@@ -48971,6 +49597,7 @@
         <v>1785.913968278472</v>
       </c>
       <c r="AC623" t="inlineStr"/>
+      <c r="AD623" t="inlineStr"/>
     </row>
     <row r="624">
       <c r="A624" s="2" t="n">
@@ -49022,6 +49649,7 @@
         <v>1764.922057153506</v>
       </c>
       <c r="AC624" t="inlineStr"/>
+      <c r="AD624" t="inlineStr"/>
     </row>
     <row r="625">
       <c r="A625" s="2" t="n">
@@ -49073,6 +49701,7 @@
         <v>1773.179472100889</v>
       </c>
       <c r="AC625" t="inlineStr"/>
+      <c r="AD625" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" s="2" t="n">
@@ -49124,6 +49753,7 @@
         <v>1766.890188770043</v>
       </c>
       <c r="AC626" t="inlineStr"/>
+      <c r="AD626" t="inlineStr"/>
     </row>
     <row r="627">
       <c r="A627" s="2" t="n">
@@ -49175,6 +49805,7 @@
         <v>1710.852319470338</v>
       </c>
       <c r="AC627" t="inlineStr"/>
+      <c r="AD627" t="inlineStr"/>
     </row>
     <row r="628">
       <c r="A628" s="2" t="n">
@@ -49226,6 +49857,7 @@
         <v>1581.59666976694</v>
       </c>
       <c r="AC628" t="inlineStr"/>
+      <c r="AD628" t="inlineStr"/>
     </row>
     <row r="629">
       <c r="A629" s="2" t="n">
@@ -49277,6 +49909,7 @@
         <v>1641.780668449919</v>
       </c>
       <c r="AC629" t="inlineStr"/>
+      <c r="AD629" t="inlineStr"/>
     </row>
     <row r="630">
       <c r="A630" s="2" t="n">
@@ -49328,6 +49961,7 @@
         <v>1649.78015363296</v>
       </c>
       <c r="AC630" t="inlineStr"/>
+      <c r="AD630" t="inlineStr"/>
     </row>
     <row r="631">
       <c r="A631" s="2" t="n">
@@ -49379,6 +50013,7 @@
         <v>1642.989964420336</v>
       </c>
       <c r="AC631" t="inlineStr"/>
+      <c r="AD631" t="inlineStr"/>
     </row>
     <row r="632">
       <c r="A632" s="2" t="n">
@@ -49430,6 +50065,7 @@
         <v>1645.616580513148</v>
       </c>
       <c r="AC632" t="inlineStr"/>
+      <c r="AD632" t="inlineStr"/>
     </row>
     <row r="633">
       <c r="A633" s="2" t="n">
@@ -49481,6 +50117,7 @@
         <v>1628.484544836647</v>
       </c>
       <c r="AC633" t="inlineStr"/>
+      <c r="AD633" t="inlineStr"/>
     </row>
     <row r="634">
       <c r="A634" s="2" t="n">
@@ -49532,6 +50169,7 @@
         <v>1619.64198984929</v>
       </c>
       <c r="AC634" t="inlineStr"/>
+      <c r="AD634" t="inlineStr"/>
     </row>
     <row r="635">
       <c r="A635" s="2" t="n">
@@ -49583,6 +50221,7 @@
         <v>1631.079133145373</v>
       </c>
       <c r="AC635" t="inlineStr"/>
+      <c r="AD635" t="inlineStr"/>
     </row>
     <row r="636">
       <c r="A636" s="2" t="n">
@@ -49634,6 +50273,7 @@
         <v>1650.178098967956</v>
       </c>
       <c r="AC636" t="inlineStr"/>
+      <c r="AD636" t="inlineStr"/>
     </row>
     <row r="637">
       <c r="A637" s="2" t="n">
@@ -49685,6 +50325,7 @@
         <v>1663.98421671788</v>
       </c>
       <c r="AC637" t="inlineStr"/>
+      <c r="AD637" t="inlineStr"/>
     </row>
     <row r="638">
       <c r="A638" s="2" t="n">
@@ -49736,6 +50377,7 @@
         <v>1640.93732488906</v>
       </c>
       <c r="AC638" t="inlineStr"/>
+      <c r="AD638" t="inlineStr"/>
     </row>
     <row r="639">
       <c r="A639" s="2" t="n">
@@ -49787,6 +50429,7 @@
         <v>1668.547873587541</v>
       </c>
       <c r="AC639" t="inlineStr"/>
+      <c r="AD639" t="inlineStr"/>
     </row>
     <row r="640">
       <c r="A640" s="2" t="n">
@@ -49838,6 +50481,7 @@
         <v>1649.196952664876</v>
       </c>
       <c r="AC640" t="inlineStr"/>
+      <c r="AD640" t="inlineStr"/>
     </row>
     <row r="641">
       <c r="A641" s="2" t="n">
@@ -49889,6 +50533,7 @@
         <v>1623.72773935969</v>
       </c>
       <c r="AC641" t="inlineStr"/>
+      <c r="AD641" t="inlineStr"/>
     </row>
     <row r="642">
       <c r="A642" s="2" t="n">
@@ -49940,6 +50585,7 @@
         <v>1657.444792645828</v>
       </c>
       <c r="AC642" t="inlineStr"/>
+      <c r="AD642" t="inlineStr"/>
     </row>
     <row r="643">
       <c r="A643" s="2" t="n">
@@ -49991,6 +50637,7 @@
         <v>1672.325877213099</v>
       </c>
       <c r="AC643" t="inlineStr"/>
+      <c r="AD643" t="inlineStr"/>
     </row>
     <row r="644">
       <c r="A644" s="2" t="n">
@@ -50042,6 +50689,7 @@
         <v>1685.28113309328</v>
       </c>
       <c r="AC644" t="inlineStr"/>
+      <c r="AD644" t="inlineStr"/>
     </row>
     <row r="645">
       <c r="A645" s="2" t="n">
@@ -50093,6 +50741,7 @@
         <v>1685.81512368675</v>
       </c>
       <c r="AC645" t="inlineStr"/>
+      <c r="AD645" t="inlineStr"/>
     </row>
     <row r="646">
       <c r="A646" s="2" t="n">
@@ -50144,6 +50793,7 @@
         <v>1632.177977856067</v>
       </c>
       <c r="AC646" t="inlineStr"/>
+      <c r="AD646" t="inlineStr"/>
     </row>
     <row r="647">
       <c r="A647" s="2" t="n">
@@ -50195,6 +50845,7 @@
         <v>1629.58996786662</v>
       </c>
       <c r="AC647" t="inlineStr"/>
+      <c r="AD647" t="inlineStr"/>
     </row>
     <row r="648">
       <c r="A648" s="2" t="n">
@@ -50246,6 +50897,7 @@
         <v>1674.225695080013</v>
       </c>
       <c r="AC648" t="inlineStr"/>
+      <c r="AD648" t="inlineStr"/>
     </row>
     <row r="649">
       <c r="A649" s="2" t="n">
@@ -50297,6 +50949,7 @@
         <v>1671.098474382101</v>
       </c>
       <c r="AC649" t="inlineStr"/>
+      <c r="AD649" t="inlineStr"/>
     </row>
     <row r="650">
       <c r="A650" s="2" t="n">
@@ -50348,6 +51001,7 @@
         <v>1650.488120267825</v>
       </c>
       <c r="AC650" t="inlineStr"/>
+      <c r="AD650" t="inlineStr"/>
     </row>
     <row r="651">
       <c r="A651" s="2" t="n">
@@ -50399,6 +51053,7 @@
         <v>1637.191131844089</v>
       </c>
       <c r="AC651" t="inlineStr"/>
+      <c r="AD651" t="inlineStr"/>
     </row>
     <row r="652">
       <c r="A652" s="2" t="n">
@@ -50450,27 +51105,40 @@
         <v>1630.630912954237</v>
       </c>
       <c r="AC652" t="inlineStr"/>
+      <c r="AD652" t="inlineStr"/>
     </row>
     <row r="653">
       <c r="A653" s="2" t="n">
         <v>46083</v>
       </c>
-      <c r="B653" t="inlineStr"/>
-      <c r="C653" t="inlineStr"/>
+      <c r="B653" t="n">
+        <v>0.512783947</v>
+      </c>
+      <c r="C653" t="n">
+        <v>0.0736941725</v>
+      </c>
       <c r="D653" t="inlineStr"/>
       <c r="E653" t="inlineStr"/>
       <c r="F653" t="inlineStr"/>
       <c r="G653" t="inlineStr"/>
       <c r="H653" t="inlineStr"/>
-      <c r="I653" t="inlineStr"/>
+      <c r="I653" t="n">
+        <v>0.038390184</v>
+      </c>
       <c r="J653" t="inlineStr"/>
-      <c r="K653" t="inlineStr"/>
+      <c r="K653" t="n">
+        <v>1611.810669117936</v>
+      </c>
       <c r="L653" t="inlineStr"/>
       <c r="M653" t="inlineStr"/>
       <c r="N653" t="inlineStr"/>
-      <c r="O653" t="inlineStr"/>
+      <c r="O653" t="n">
+        <v>0.1198471189</v>
+      </c>
       <c r="P653" t="inlineStr"/>
-      <c r="Q653" t="inlineStr"/>
+      <c r="Q653" t="n">
+        <v>8.448e-07</v>
+      </c>
       <c r="R653" t="inlineStr"/>
       <c r="S653" t="inlineStr"/>
       <c r="T653" t="inlineStr"/>
@@ -50479,14 +51147,15 @@
       <c r="W653" t="inlineStr"/>
       <c r="X653" t="inlineStr"/>
       <c r="Y653" t="inlineStr"/>
-      <c r="Z653" t="n">
-        <v>31.162375408926</v>
-      </c>
-      <c r="AA653" t="inlineStr"/>
+      <c r="Z653" t="inlineStr"/>
+      <c r="AA653" t="n">
+        <v>0.008202590177000001</v>
+      </c>
       <c r="AB653" t="n">
-        <v>31.162375408926</v>
+        <v>1612.563587975313</v>
       </c>
       <c r="AC653" t="inlineStr"/>
+      <c r="AD653" t="inlineStr"/>
     </row>
     <row r="654">
       <c r="A654" s="2" t="n">
@@ -50536,6 +51205,111 @@
         <v>1597.190814256115</v>
       </c>
       <c r="AC654" t="inlineStr"/>
+      <c r="AD654" t="inlineStr"/>
+    </row>
+    <row r="655">
+      <c r="A655" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B655" t="n">
+        <v>0.5413674365</v>
+      </c>
+      <c r="C655" t="n">
+        <v>0.07732662800000001</v>
+      </c>
+      <c r="D655" t="inlineStr"/>
+      <c r="E655" t="inlineStr"/>
+      <c r="F655" t="inlineStr"/>
+      <c r="G655" t="inlineStr"/>
+      <c r="H655" t="inlineStr"/>
+      <c r="I655" t="n">
+        <v>0.040255635</v>
+      </c>
+      <c r="J655" t="inlineStr"/>
+      <c r="K655" t="n">
+        <v>1634.007214349433</v>
+      </c>
+      <c r="L655" t="inlineStr"/>
+      <c r="M655" t="inlineStr"/>
+      <c r="N655" t="inlineStr"/>
+      <c r="O655" t="n">
+        <v>0.1236429009</v>
+      </c>
+      <c r="P655" t="inlineStr"/>
+      <c r="Q655" t="n">
+        <v>8.760000000000001e-07</v>
+      </c>
+      <c r="R655" t="inlineStr"/>
+      <c r="S655" t="inlineStr"/>
+      <c r="T655" t="inlineStr"/>
+      <c r="U655" t="inlineStr"/>
+      <c r="V655" t="inlineStr"/>
+      <c r="W655" t="inlineStr"/>
+      <c r="X655" t="inlineStr"/>
+      <c r="Y655" t="inlineStr"/>
+      <c r="Z655" t="inlineStr"/>
+      <c r="AA655" t="n">
+        <v>0.008200949823000001</v>
+      </c>
+      <c r="AB655" t="n">
+        <v>1679.589847629503</v>
+      </c>
+      <c r="AC655" t="inlineStr"/>
+      <c r="AD655" t="n">
+        <v>44.7918388538464</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B656" t="n">
+        <v>0.528135864</v>
+      </c>
+      <c r="C656" t="n">
+        <v>0.07534846100000001</v>
+      </c>
+      <c r="D656" t="inlineStr"/>
+      <c r="E656" t="inlineStr"/>
+      <c r="F656" t="inlineStr"/>
+      <c r="G656" t="inlineStr"/>
+      <c r="H656" t="inlineStr"/>
+      <c r="I656" t="n">
+        <v>0.03933398699999999</v>
+      </c>
+      <c r="J656" t="inlineStr"/>
+      <c r="K656" t="n">
+        <v>1623.193512826396</v>
+      </c>
+      <c r="L656" t="inlineStr"/>
+      <c r="M656" t="inlineStr"/>
+      <c r="N656" t="inlineStr"/>
+      <c r="O656" t="n">
+        <v>0.1217374935</v>
+      </c>
+      <c r="P656" t="inlineStr"/>
+      <c r="Q656" t="n">
+        <v>8.327999999999999e-07</v>
+      </c>
+      <c r="R656" t="inlineStr"/>
+      <c r="S656" t="inlineStr"/>
+      <c r="T656" t="inlineStr"/>
+      <c r="U656" t="inlineStr"/>
+      <c r="V656" t="inlineStr"/>
+      <c r="W656" t="inlineStr"/>
+      <c r="X656" t="inlineStr"/>
+      <c r="Y656" t="inlineStr"/>
+      <c r="Z656" t="inlineStr"/>
+      <c r="AA656" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="AB656" t="n">
+        <v>1663.857838200621</v>
+      </c>
+      <c r="AC656" t="inlineStr"/>
+      <c r="AD656" t="n">
+        <v>39.8915669659256</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -51111,34 +51111,22 @@
       <c r="A653" s="2" t="n">
         <v>46083</v>
       </c>
-      <c r="B653" t="n">
-        <v>0.512783947</v>
-      </c>
-      <c r="C653" t="n">
-        <v>0.0736941725</v>
-      </c>
+      <c r="B653" t="inlineStr"/>
+      <c r="C653" t="inlineStr"/>
       <c r="D653" t="inlineStr"/>
       <c r="E653" t="inlineStr"/>
       <c r="F653" t="inlineStr"/>
       <c r="G653" t="inlineStr"/>
       <c r="H653" t="inlineStr"/>
-      <c r="I653" t="n">
-        <v>0.038390184</v>
-      </c>
+      <c r="I653" t="inlineStr"/>
       <c r="J653" t="inlineStr"/>
-      <c r="K653" t="n">
-        <v>1611.810669117936</v>
-      </c>
+      <c r="K653" t="inlineStr"/>
       <c r="L653" t="inlineStr"/>
       <c r="M653" t="inlineStr"/>
       <c r="N653" t="inlineStr"/>
-      <c r="O653" t="n">
-        <v>0.1198471189</v>
-      </c>
+      <c r="O653" t="inlineStr"/>
       <c r="P653" t="inlineStr"/>
-      <c r="Q653" t="n">
-        <v>8.448e-07</v>
-      </c>
+      <c r="Q653" t="inlineStr"/>
       <c r="R653" t="inlineStr"/>
       <c r="S653" t="inlineStr"/>
       <c r="T653" t="inlineStr"/>
@@ -51147,12 +51135,12 @@
       <c r="W653" t="inlineStr"/>
       <c r="X653" t="inlineStr"/>
       <c r="Y653" t="inlineStr"/>
-      <c r="Z653" t="inlineStr"/>
-      <c r="AA653" t="n">
-        <v>0.008202590177000001</v>
-      </c>
+      <c r="Z653" t="n">
+        <v>31.162375408926</v>
+      </c>
+      <c r="AA653" t="inlineStr"/>
       <c r="AB653" t="n">
-        <v>1612.563587975313</v>
+        <v>31.162375408926</v>
       </c>
       <c r="AC653" t="inlineStr"/>
       <c r="AD653" t="inlineStr"/>
@@ -51304,7 +51292,7 @@
         <v>0.008201770000000001</v>
       </c>
       <c r="AB656" t="n">
-        <v>1663.857838200621</v>
+        <v>1663.857838200622</v>
       </c>
       <c r="AC656" t="inlineStr"/>
       <c r="AD656" t="n">

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD656"/>
+  <dimension ref="A1:AD657"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51299,6 +51299,58 @@
         <v>39.8915669659256</v>
       </c>
     </row>
+    <row r="657">
+      <c r="A657" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B657" t="n">
+        <v>0.507449449</v>
+      </c>
+      <c r="C657" t="n">
+        <v>0.07192501800000001</v>
+      </c>
+      <c r="D657" t="inlineStr"/>
+      <c r="E657" t="inlineStr"/>
+      <c r="F657" t="inlineStr"/>
+      <c r="G657" t="inlineStr"/>
+      <c r="H657" t="inlineStr"/>
+      <c r="I657" t="n">
+        <v>0.03753057</v>
+      </c>
+      <c r="J657" t="inlineStr"/>
+      <c r="K657" t="n">
+        <v>1619.778659713858</v>
+      </c>
+      <c r="L657" t="inlineStr"/>
+      <c r="M657" t="inlineStr"/>
+      <c r="N657" t="inlineStr"/>
+      <c r="O657" t="n">
+        <v>0.1178778221</v>
+      </c>
+      <c r="P657" t="inlineStr"/>
+      <c r="Q657" t="n">
+        <v>8.136e-07</v>
+      </c>
+      <c r="R657" t="inlineStr"/>
+      <c r="S657" t="inlineStr"/>
+      <c r="T657" t="inlineStr"/>
+      <c r="U657" t="inlineStr"/>
+      <c r="V657" t="inlineStr"/>
+      <c r="W657" t="inlineStr"/>
+      <c r="X657" t="inlineStr"/>
+      <c r="Y657" t="inlineStr"/>
+      <c r="Z657" t="inlineStr"/>
+      <c r="AA657" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="AB657" t="n">
+        <v>1656.18369988462</v>
+      </c>
+      <c r="AC657" t="inlineStr"/>
+      <c r="AD657" t="n">
+        <v>35.6620547280624</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD657"/>
+  <dimension ref="A1:AD661"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51304,7 +51304,7 @@
         <v>0.008201770000000001</v>
       </c>
       <c r="AB656" t="n">
-        <v>1663.857838200622</v>
+        <v>1663.857838200621</v>
       </c>
       <c r="AC656" t="inlineStr"/>
       <c r="AD656" t="n">
@@ -51363,6 +51363,214 @@
         <v>35.6620547280624</v>
       </c>
     </row>
+    <row r="658">
+      <c r="A658" s="2" t="n">
+        <v>46088</v>
+      </c>
+      <c r="B658" t="n">
+        <v>0.5011086795</v>
+      </c>
+      <c r="C658" t="n">
+        <v>0.0715945965</v>
+      </c>
+      <c r="D658" t="inlineStr"/>
+      <c r="E658" t="inlineStr"/>
+      <c r="F658" t="inlineStr"/>
+      <c r="G658" t="inlineStr"/>
+      <c r="H658" t="inlineStr"/>
+      <c r="I658" t="n">
+        <v>0.03687478199999999</v>
+      </c>
+      <c r="J658" t="inlineStr"/>
+      <c r="K658" t="n">
+        <v>1631.161503422318</v>
+      </c>
+      <c r="L658" t="inlineStr"/>
+      <c r="M658" t="inlineStr"/>
+      <c r="N658" t="inlineStr"/>
+      <c r="O658" t="n">
+        <v>0.1165530566</v>
+      </c>
+      <c r="P658" t="inlineStr"/>
+      <c r="Q658" t="n">
+        <v>7.776e-07</v>
+      </c>
+      <c r="R658" t="inlineStr"/>
+      <c r="S658" t="inlineStr"/>
+      <c r="T658" t="inlineStr"/>
+      <c r="U658" t="inlineStr"/>
+      <c r="V658" t="inlineStr"/>
+      <c r="W658" t="inlineStr"/>
+      <c r="X658" t="inlineStr"/>
+      <c r="Y658" t="inlineStr"/>
+      <c r="Z658" t="inlineStr"/>
+      <c r="AA658" t="n">
+        <v>0.008202590177000001</v>
+      </c>
+      <c r="AB658" t="n">
+        <v>1664.688531907511</v>
+      </c>
+      <c r="AC658" t="inlineStr"/>
+      <c r="AD658" t="n">
+        <v>32.792694002816</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="2" t="n">
+        <v>46089</v>
+      </c>
+      <c r="B659" t="n">
+        <v>0.4914854399999999</v>
+      </c>
+      <c r="C659" t="n">
+        <v>0.070413585</v>
+      </c>
+      <c r="D659" t="inlineStr"/>
+      <c r="E659" t="inlineStr"/>
+      <c r="F659" t="inlineStr"/>
+      <c r="G659" t="inlineStr"/>
+      <c r="H659" t="inlineStr"/>
+      <c r="I659" t="n">
+        <v>0.036152529</v>
+      </c>
+      <c r="J659" t="inlineStr"/>
+      <c r="K659" t="n">
+        <v>1645.390058057893</v>
+      </c>
+      <c r="L659" t="inlineStr"/>
+      <c r="M659" t="inlineStr"/>
+      <c r="N659" t="inlineStr"/>
+      <c r="O659" t="n">
+        <v>0.1149971618</v>
+      </c>
+      <c r="P659" t="inlineStr"/>
+      <c r="Q659" t="n">
+        <v>7.655999999999999e-07</v>
+      </c>
+      <c r="R659" t="inlineStr"/>
+      <c r="S659" t="inlineStr"/>
+      <c r="T659" t="inlineStr"/>
+      <c r="U659" t="inlineStr"/>
+      <c r="V659" t="inlineStr"/>
+      <c r="W659" t="inlineStr"/>
+      <c r="X659" t="inlineStr"/>
+      <c r="Y659" t="inlineStr"/>
+      <c r="Z659" t="inlineStr"/>
+      <c r="AA659" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="AB659" t="n">
+        <v>1679.108957649627</v>
+      </c>
+      <c r="AC659" t="inlineStr"/>
+      <c r="AD659" t="n">
+        <v>32.9976483403336</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B660" t="n">
+        <v>0.509819592</v>
+      </c>
+      <c r="C660" t="n">
+        <v>0.07244482300000001</v>
+      </c>
+      <c r="D660" t="inlineStr"/>
+      <c r="E660" t="inlineStr"/>
+      <c r="F660" t="inlineStr"/>
+      <c r="G660" t="inlineStr"/>
+      <c r="H660" t="inlineStr"/>
+      <c r="I660" t="n">
+        <v>0.037645776</v>
+      </c>
+      <c r="J660" t="inlineStr"/>
+      <c r="K660" t="n">
+        <v>1625.470081568088</v>
+      </c>
+      <c r="L660" t="inlineStr"/>
+      <c r="M660" t="inlineStr"/>
+      <c r="N660" t="inlineStr"/>
+      <c r="O660" t="n">
+        <v>0.1192552024</v>
+      </c>
+      <c r="P660" t="inlineStr"/>
+      <c r="Q660" t="n">
+        <v>7.848e-07</v>
+      </c>
+      <c r="R660" t="inlineStr"/>
+      <c r="S660" t="inlineStr"/>
+      <c r="T660" t="inlineStr"/>
+      <c r="U660" t="inlineStr"/>
+      <c r="V660" t="inlineStr"/>
+      <c r="W660" t="inlineStr"/>
+      <c r="X660" t="inlineStr"/>
+      <c r="Y660" t="inlineStr"/>
+      <c r="Z660" t="inlineStr"/>
+      <c r="AA660" t="n">
+        <v>0.008200949823000001</v>
+      </c>
+      <c r="AB660" t="n">
+        <v>1660.295765361538</v>
+      </c>
+      <c r="AC660" t="inlineStr"/>
+      <c r="AD660" t="n">
+        <v>34.0783166654264</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B661" t="n">
+        <v>0.5211172935</v>
+      </c>
+      <c r="C661" t="n">
+        <v>0.07402713850000001</v>
+      </c>
+      <c r="D661" t="inlineStr"/>
+      <c r="E661" t="inlineStr"/>
+      <c r="F661" t="inlineStr"/>
+      <c r="G661" t="inlineStr"/>
+      <c r="H661" t="inlineStr"/>
+      <c r="I661" t="n">
+        <v>0.03805342799999999</v>
+      </c>
+      <c r="J661" t="inlineStr"/>
+      <c r="K661" t="n">
+        <v>1626.608365938934</v>
+      </c>
+      <c r="L661" t="inlineStr"/>
+      <c r="M661" t="inlineStr"/>
+      <c r="N661" t="inlineStr"/>
+      <c r="O661" t="n">
+        <v>0.12063822</v>
+      </c>
+      <c r="P661" t="inlineStr"/>
+      <c r="Q661" t="n">
+        <v>7.895999999999999e-07</v>
+      </c>
+      <c r="R661" t="inlineStr"/>
+      <c r="S661" t="inlineStr"/>
+      <c r="T661" t="inlineStr"/>
+      <c r="U661" t="inlineStr"/>
+      <c r="V661" t="inlineStr"/>
+      <c r="W661" t="inlineStr"/>
+      <c r="X661" t="inlineStr"/>
+      <c r="Y661" t="inlineStr"/>
+      <c r="Z661" t="inlineStr"/>
+      <c r="AA661" t="n">
+        <v>0.008200949823000001</v>
+      </c>
+      <c r="AB661" t="n">
+        <v>1661.709571398806</v>
+      </c>
+      <c r="AC661" t="inlineStr"/>
+      <c r="AD661" t="n">
+        <v>34.3391676404488</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -51304,7 +51304,7 @@
         <v>0.008201770000000001</v>
       </c>
       <c r="AB656" t="n">
-        <v>1663.857838200621</v>
+        <v>1663.857838200622</v>
       </c>
       <c r="AC656" t="inlineStr"/>
       <c r="AD656" t="n">

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD661"/>
+  <dimension ref="A1:AD662"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51571,6 +51571,58 @@
         <v>34.3391676404488</v>
       </c>
     </row>
+    <row r="662">
+      <c r="A662" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B662" t="n">
+        <v>0.522929357</v>
+      </c>
+      <c r="C662" t="n">
+        <v>0.0745891095</v>
+      </c>
+      <c r="D662" t="inlineStr"/>
+      <c r="E662" t="inlineStr"/>
+      <c r="F662" t="inlineStr"/>
+      <c r="G662" t="inlineStr"/>
+      <c r="H662" t="inlineStr"/>
+      <c r="I662" t="n">
+        <v>0.038363598</v>
+      </c>
+      <c r="J662" t="inlineStr"/>
+      <c r="K662" t="n">
+        <v>1657.911186137199</v>
+      </c>
+      <c r="L662" t="inlineStr"/>
+      <c r="M662" t="inlineStr"/>
+      <c r="N662" t="inlineStr"/>
+      <c r="O662" t="n">
+        <v>0.1224158486</v>
+      </c>
+      <c r="P662" t="inlineStr"/>
+      <c r="Q662" t="n">
+        <v>7.991999999999999e-07</v>
+      </c>
+      <c r="R662" t="inlineStr"/>
+      <c r="S662" t="inlineStr"/>
+      <c r="T662" t="inlineStr"/>
+      <c r="U662" t="inlineStr"/>
+      <c r="V662" t="inlineStr"/>
+      <c r="W662" t="inlineStr"/>
+      <c r="X662" t="inlineStr"/>
+      <c r="Y662" t="inlineStr"/>
+      <c r="Z662" t="inlineStr"/>
+      <c r="AA662" t="n">
+        <v>0.008200949823000001</v>
+      </c>
+      <c r="AB662" t="n">
+        <v>1689.998435014512</v>
+      </c>
+      <c r="AC662" t="inlineStr"/>
+      <c r="AD662" t="n">
+        <v>31.3207492151896</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD662"/>
+  <dimension ref="A1:AD665"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51623,6 +51623,162 @@
         <v>31.3207492151896</v>
       </c>
     </row>
+    <row r="663">
+      <c r="A663" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B663" t="n">
+        <v>0.525532983</v>
+      </c>
+      <c r="C663" t="n">
+        <v>0.07537245200000001</v>
+      </c>
+      <c r="D663" t="inlineStr"/>
+      <c r="E663" t="inlineStr"/>
+      <c r="F663" t="inlineStr"/>
+      <c r="G663" t="inlineStr"/>
+      <c r="H663" t="inlineStr"/>
+      <c r="I663" t="n">
+        <v>0.038478804</v>
+      </c>
+      <c r="J663" t="inlineStr"/>
+      <c r="K663" t="n">
+        <v>1645.390058057893</v>
+      </c>
+      <c r="L663" t="inlineStr"/>
+      <c r="M663" t="inlineStr"/>
+      <c r="N663" t="inlineStr"/>
+      <c r="O663" t="n">
+        <v>0.1224647052</v>
+      </c>
+      <c r="P663" t="inlineStr"/>
+      <c r="Q663" t="n">
+        <v>8.064e-07</v>
+      </c>
+      <c r="R663" t="inlineStr"/>
+      <c r="S663" t="inlineStr"/>
+      <c r="T663" t="inlineStr"/>
+      <c r="U663" t="inlineStr"/>
+      <c r="V663" t="inlineStr"/>
+      <c r="W663" t="inlineStr"/>
+      <c r="X663" t="inlineStr"/>
+      <c r="Y663" t="inlineStr"/>
+      <c r="Z663" t="inlineStr"/>
+      <c r="AA663" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="AB663" t="n">
+        <v>1676.362926043586</v>
+      </c>
+      <c r="AC663" t="inlineStr"/>
+      <c r="AD663" t="n">
+        <v>30.2028164650936</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B664" t="n">
+        <v>0.5284285</v>
+      </c>
+      <c r="C664" t="n">
+        <v>0.076052197</v>
+      </c>
+      <c r="D664" t="inlineStr"/>
+      <c r="E664" t="inlineStr"/>
+      <c r="F664" t="inlineStr"/>
+      <c r="G664" t="inlineStr"/>
+      <c r="H664" t="inlineStr"/>
+      <c r="I664" t="n">
+        <v>0.039072558</v>
+      </c>
+      <c r="J664" t="inlineStr"/>
+      <c r="K664" t="n">
+        <v>1669.863172031082</v>
+      </c>
+      <c r="L664" t="inlineStr"/>
+      <c r="M664" t="inlineStr"/>
+      <c r="N664" t="inlineStr"/>
+      <c r="O664" t="n">
+        <v>0.1232182243</v>
+      </c>
+      <c r="P664" t="inlineStr"/>
+      <c r="Q664" t="n">
+        <v>8.112e-07</v>
+      </c>
+      <c r="R664" t="inlineStr"/>
+      <c r="S664" t="inlineStr"/>
+      <c r="T664" t="inlineStr"/>
+      <c r="U664" t="inlineStr"/>
+      <c r="V664" t="inlineStr"/>
+      <c r="W664" t="inlineStr"/>
+      <c r="X664" t="inlineStr"/>
+      <c r="Y664" t="inlineStr"/>
+      <c r="Z664" t="inlineStr"/>
+      <c r="AA664" t="n">
+        <v>0.008200949823000001</v>
+      </c>
+      <c r="AB664" t="n">
+        <v>1699.592603498891</v>
+      </c>
+      <c r="AC664" t="inlineStr"/>
+      <c r="AD664" t="n">
+        <v>28.9544582274864</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B665" t="n">
+        <v>0.5305290275</v>
+      </c>
+      <c r="C665" t="n">
+        <v>0.076195416</v>
+      </c>
+      <c r="D665" t="inlineStr"/>
+      <c r="E665" t="inlineStr"/>
+      <c r="F665" t="inlineStr"/>
+      <c r="G665" t="inlineStr"/>
+      <c r="H665" t="inlineStr"/>
+      <c r="I665" t="n">
+        <v>0.039006093</v>
+      </c>
+      <c r="J665" t="inlineStr"/>
+      <c r="K665" t="n">
+        <v>1694.905428189694</v>
+      </c>
+      <c r="L665" t="inlineStr"/>
+      <c r="M665" t="inlineStr"/>
+      <c r="N665" t="inlineStr"/>
+      <c r="O665" t="n">
+        <v>0.123588407</v>
+      </c>
+      <c r="P665" t="inlineStr"/>
+      <c r="Q665" t="n">
+        <v>8.064e-07</v>
+      </c>
+      <c r="R665" t="inlineStr"/>
+      <c r="S665" t="inlineStr"/>
+      <c r="T665" t="inlineStr"/>
+      <c r="U665" t="inlineStr"/>
+      <c r="V665" t="inlineStr"/>
+      <c r="W665" t="inlineStr"/>
+      <c r="X665" t="inlineStr"/>
+      <c r="Y665" t="inlineStr"/>
+      <c r="Z665" t="inlineStr"/>
+      <c r="AA665" t="n">
+        <v>0.008200129646</v>
+      </c>
+      <c r="AB665" t="n">
+        <v>1724.320658684199</v>
+      </c>
+      <c r="AC665" t="inlineStr"/>
+      <c r="AD665" t="n">
+        <v>28.6377106149592</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD665"/>
+  <dimension ref="A1:AD667"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51779,6 +51779,110 @@
         <v>28.6377106149592</v>
       </c>
     </row>
+    <row r="666">
+      <c r="A666" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B666" t="n">
+        <v>0.542473538</v>
+      </c>
+      <c r="C666" t="n">
+        <v>0.07918120500000002</v>
+      </c>
+      <c r="D666" t="inlineStr"/>
+      <c r="E666" t="inlineStr"/>
+      <c r="F666" t="inlineStr"/>
+      <c r="G666" t="inlineStr"/>
+      <c r="H666" t="inlineStr"/>
+      <c r="I666" t="n">
+        <v>0.04089813</v>
+      </c>
+      <c r="J666" t="inlineStr"/>
+      <c r="K666" t="n">
+        <v>1700.027707858501</v>
+      </c>
+      <c r="L666" t="inlineStr"/>
+      <c r="M666" t="inlineStr"/>
+      <c r="N666" t="inlineStr"/>
+      <c r="O666" t="n">
+        <v>0.1266081207</v>
+      </c>
+      <c r="P666" t="inlineStr"/>
+      <c r="Q666" t="n">
+        <v>8.279999999999999e-07</v>
+      </c>
+      <c r="R666" t="inlineStr"/>
+      <c r="S666" t="inlineStr"/>
+      <c r="T666" t="inlineStr"/>
+      <c r="U666" t="inlineStr"/>
+      <c r="V666" t="inlineStr"/>
+      <c r="W666" t="inlineStr"/>
+      <c r="X666" t="inlineStr"/>
+      <c r="Y666" t="inlineStr"/>
+      <c r="Z666" t="inlineStr"/>
+      <c r="AA666" t="n">
+        <v>0.008200129646</v>
+      </c>
+      <c r="AB666" t="n">
+        <v>1729.220561662285</v>
+      </c>
+      <c r="AC666" t="inlineStr"/>
+      <c r="AD666" t="n">
+        <v>28.3954918524384</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B667" t="n">
+        <v>0.5578907915</v>
+      </c>
+      <c r="C667" t="n">
+        <v>0.0855304595</v>
+      </c>
+      <c r="D667" t="inlineStr"/>
+      <c r="E667" t="inlineStr"/>
+      <c r="F667" t="inlineStr"/>
+      <c r="G667" t="inlineStr"/>
+      <c r="H667" t="inlineStr"/>
+      <c r="I667" t="n">
+        <v>0.04262622</v>
+      </c>
+      <c r="J667" t="inlineStr"/>
+      <c r="K667" t="n">
+        <v>1682.384300110388</v>
+      </c>
+      <c r="L667" t="inlineStr"/>
+      <c r="M667" t="inlineStr"/>
+      <c r="N667" t="inlineStr"/>
+      <c r="O667" t="n">
+        <v>0.1277243061</v>
+      </c>
+      <c r="P667" t="inlineStr"/>
+      <c r="Q667" t="n">
+        <v>9.623999999999999e-07</v>
+      </c>
+      <c r="R667" t="inlineStr"/>
+      <c r="S667" t="inlineStr"/>
+      <c r="T667" t="inlineStr"/>
+      <c r="U667" t="inlineStr"/>
+      <c r="V667" t="inlineStr"/>
+      <c r="W667" t="inlineStr"/>
+      <c r="X667" t="inlineStr"/>
+      <c r="Y667" t="inlineStr"/>
+      <c r="Z667" t="inlineStr"/>
+      <c r="AA667" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="AB667" t="n">
+        <v>1712.086203997368</v>
+      </c>
+      <c r="AC667" t="inlineStr"/>
+      <c r="AD667" t="n">
+        <v>28.87992937748</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD667"/>
+  <dimension ref="A1:AD670"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51883,6 +51883,162 @@
         <v>28.87992937748</v>
       </c>
     </row>
+    <row r="668">
+      <c r="A668" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B668" t="n">
+        <v>0.550624732</v>
+      </c>
+      <c r="C668" t="n">
+        <v>0.0842371265</v>
+      </c>
+      <c r="D668" t="inlineStr"/>
+      <c r="E668" t="inlineStr"/>
+      <c r="F668" t="inlineStr"/>
+      <c r="G668" t="inlineStr"/>
+      <c r="H668" t="inlineStr"/>
+      <c r="I668" t="n">
+        <v>0.041926122</v>
+      </c>
+      <c r="J668" t="inlineStr"/>
+      <c r="K668" t="n">
+        <v>1746.128224877764</v>
+      </c>
+      <c r="L668" t="inlineStr"/>
+      <c r="M668" t="inlineStr"/>
+      <c r="N668" t="inlineStr"/>
+      <c r="O668" t="n">
+        <v>0.1256385051</v>
+      </c>
+      <c r="P668" t="inlineStr"/>
+      <c r="Q668" t="n">
+        <v>8.784e-07</v>
+      </c>
+      <c r="R668" t="inlineStr"/>
+      <c r="S668" t="inlineStr"/>
+      <c r="T668" t="inlineStr"/>
+      <c r="U668" t="inlineStr"/>
+      <c r="V668" t="inlineStr"/>
+      <c r="W668" t="inlineStr"/>
+      <c r="X668" t="inlineStr"/>
+      <c r="Y668" t="inlineStr"/>
+      <c r="Z668" t="inlineStr"/>
+      <c r="AA668" t="n">
+        <v>0.008199309469</v>
+      </c>
+      <c r="AB668" t="n">
+        <v>1774.756744816122</v>
+      </c>
+      <c r="AC668" t="inlineStr"/>
+      <c r="AD668" t="n">
+        <v>27.8178932648888</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B669" t="n">
+        <v>0.530786723</v>
+      </c>
+      <c r="C669" t="n">
+        <v>0.0800932265</v>
+      </c>
+      <c r="D669" t="inlineStr"/>
+      <c r="E669" t="inlineStr"/>
+      <c r="F669" t="inlineStr"/>
+      <c r="G669" t="inlineStr"/>
+      <c r="H669" t="inlineStr"/>
+      <c r="I669" t="n">
+        <v>0.039914448</v>
+      </c>
+      <c r="J669" t="inlineStr"/>
+      <c r="K669" t="n">
+        <v>1733.037954613035</v>
+      </c>
+      <c r="L669" t="inlineStr"/>
+      <c r="M669" t="inlineStr"/>
+      <c r="N669" t="inlineStr"/>
+      <c r="O669" t="n">
+        <v>0.1225680557</v>
+      </c>
+      <c r="P669" t="inlineStr"/>
+      <c r="Q669" t="n">
+        <v>8.448e-07</v>
+      </c>
+      <c r="R669" t="inlineStr"/>
+      <c r="S669" t="inlineStr"/>
+      <c r="T669" t="inlineStr"/>
+      <c r="U669" t="inlineStr"/>
+      <c r="V669" t="inlineStr"/>
+      <c r="W669" t="inlineStr"/>
+      <c r="X669" t="inlineStr"/>
+      <c r="Y669" t="inlineStr"/>
+      <c r="Z669" t="inlineStr"/>
+      <c r="AA669" t="n">
+        <v>0.008200949823000001</v>
+      </c>
+      <c r="AB669" t="n">
+        <v>1759.718294238082</v>
+      </c>
+      <c r="AC669" t="inlineStr"/>
+      <c r="AD669" t="n">
+        <v>25.898775377224</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B670" t="n">
+        <v>0.5209785</v>
+      </c>
+      <c r="C670" t="n">
+        <v>0.0777093935</v>
+      </c>
+      <c r="D670" t="inlineStr"/>
+      <c r="E670" t="inlineStr"/>
+      <c r="F670" t="inlineStr"/>
+      <c r="G670" t="inlineStr"/>
+      <c r="H670" t="inlineStr"/>
+      <c r="I670" t="n">
+        <v>0.039387159</v>
+      </c>
+      <c r="J670" t="inlineStr"/>
+      <c r="K670" t="n">
+        <v>1727.915674944228</v>
+      </c>
+      <c r="L670" t="inlineStr"/>
+      <c r="M670" t="inlineStr"/>
+      <c r="N670" t="inlineStr"/>
+      <c r="O670" t="n">
+        <v>0.1201026765</v>
+      </c>
+      <c r="P670" t="inlineStr"/>
+      <c r="Q670" t="n">
+        <v>8.207999999999999e-07</v>
+      </c>
+      <c r="R670" t="inlineStr"/>
+      <c r="S670" t="inlineStr"/>
+      <c r="T670" t="inlineStr"/>
+      <c r="U670" t="inlineStr"/>
+      <c r="V670" t="inlineStr"/>
+      <c r="W670" t="inlineStr"/>
+      <c r="X670" t="inlineStr"/>
+      <c r="Y670" t="inlineStr"/>
+      <c r="Z670" t="inlineStr"/>
+      <c r="AA670" t="n">
+        <v>0.008200949823000001</v>
+      </c>
+      <c r="AB670" t="n">
+        <v>1754.823048583596</v>
+      </c>
+      <c r="AC670" t="inlineStr"/>
+      <c r="AD670" t="n">
+        <v>26.1409941397448</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -51720,7 +51720,7 @@
         <v>0.008200949823000001</v>
       </c>
       <c r="AB664" t="n">
-        <v>1699.592603498891</v>
+        <v>1699.592603498892</v>
       </c>
       <c r="AC664" t="inlineStr"/>
       <c r="AD664" t="n">

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD670"/>
+  <dimension ref="A1:AD672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52039,6 +52039,110 @@
         <v>26.1409941397448</v>
       </c>
     </row>
+    <row r="671">
+      <c r="A671" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B671" t="n">
+        <v>0.5253049384999999</v>
+      </c>
+      <c r="C671" t="n">
+        <v>0.07801509699999999</v>
+      </c>
+      <c r="D671" t="inlineStr"/>
+      <c r="E671" t="inlineStr"/>
+      <c r="F671" t="inlineStr"/>
+      <c r="G671" t="inlineStr"/>
+      <c r="H671" t="inlineStr"/>
+      <c r="I671" t="n">
+        <v>0.039808104</v>
+      </c>
+      <c r="J671" t="inlineStr"/>
+      <c r="K671" t="n">
+        <v>1762.633348255031</v>
+      </c>
+      <c r="L671" t="inlineStr"/>
+      <c r="M671" t="inlineStr"/>
+      <c r="N671" t="inlineStr"/>
+      <c r="O671" t="n">
+        <v>0.1206588901</v>
+      </c>
+      <c r="P671" t="inlineStr"/>
+      <c r="Q671" t="n">
+        <v>8.184e-07</v>
+      </c>
+      <c r="R671" t="inlineStr"/>
+      <c r="S671" t="inlineStr"/>
+      <c r="T671" t="inlineStr"/>
+      <c r="U671" t="inlineStr"/>
+      <c r="V671" t="inlineStr"/>
+      <c r="W671" t="inlineStr"/>
+      <c r="X671" t="inlineStr"/>
+      <c r="Y671" t="inlineStr"/>
+      <c r="Z671" t="inlineStr"/>
+      <c r="AA671" t="n">
+        <v>0.008202590177000001</v>
+      </c>
+      <c r="AB671" t="n">
+        <v>1789.434539557943</v>
+      </c>
+      <c r="AC671" t="inlineStr"/>
+      <c r="AD671" t="n">
+        <v>26.0292008647352</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="B672" t="n">
+        <v>0.513439994</v>
+      </c>
+      <c r="C672" t="n">
+        <v>0.07578502450000001</v>
+      </c>
+      <c r="D672" t="inlineStr"/>
+      <c r="E672" t="inlineStr"/>
+      <c r="F672" t="inlineStr"/>
+      <c r="G672" t="inlineStr"/>
+      <c r="H672" t="inlineStr"/>
+      <c r="I672" t="n">
+        <v>0.038797836</v>
+      </c>
+      <c r="J672" t="inlineStr"/>
+      <c r="K672" t="n">
+        <v>1776.292760705183</v>
+      </c>
+      <c r="L672" t="inlineStr"/>
+      <c r="M672" t="inlineStr"/>
+      <c r="N672" t="inlineStr"/>
+      <c r="O672" t="n">
+        <v>0.118514837</v>
+      </c>
+      <c r="P672" t="inlineStr"/>
+      <c r="Q672" t="n">
+        <v>7.967999999999999e-07</v>
+      </c>
+      <c r="R672" t="inlineStr"/>
+      <c r="S672" t="inlineStr"/>
+      <c r="T672" t="inlineStr"/>
+      <c r="U672" t="inlineStr"/>
+      <c r="V672" t="inlineStr"/>
+      <c r="W672" t="inlineStr"/>
+      <c r="X672" t="inlineStr"/>
+      <c r="Y672" t="inlineStr"/>
+      <c r="Z672" t="inlineStr"/>
+      <c r="AA672" t="n">
+        <v>0.008203410354000001</v>
+      </c>
+      <c r="AB672" t="n">
+        <v>1801.88424186847</v>
+      </c>
+      <c r="AC672" t="inlineStr"/>
+      <c r="AD672" t="n">
+        <v>24.8367392646328</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD672"/>
+  <dimension ref="A1:AD673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51111,34 +51111,22 @@
       <c r="A653" s="2" t="n">
         <v>46083</v>
       </c>
-      <c r="B653" t="n">
-        <v>0.512783947</v>
-      </c>
-      <c r="C653" t="n">
-        <v>0.0736941725</v>
-      </c>
+      <c r="B653" t="inlineStr"/>
+      <c r="C653" t="inlineStr"/>
       <c r="D653" t="inlineStr"/>
       <c r="E653" t="inlineStr"/>
       <c r="F653" t="inlineStr"/>
       <c r="G653" t="inlineStr"/>
       <c r="H653" t="inlineStr"/>
-      <c r="I653" t="n">
-        <v>0.038390184</v>
-      </c>
+      <c r="I653" t="inlineStr"/>
       <c r="J653" t="inlineStr"/>
-      <c r="K653" t="n">
-        <v>1611.810669117936</v>
-      </c>
+      <c r="K653" t="inlineStr"/>
       <c r="L653" t="inlineStr"/>
       <c r="M653" t="inlineStr"/>
       <c r="N653" t="inlineStr"/>
-      <c r="O653" t="n">
-        <v>0.1198471189</v>
-      </c>
+      <c r="O653" t="inlineStr"/>
       <c r="P653" t="inlineStr"/>
-      <c r="Q653" t="n">
-        <v>8.448e-07</v>
-      </c>
+      <c r="Q653" t="inlineStr"/>
       <c r="R653" t="inlineStr"/>
       <c r="S653" t="inlineStr"/>
       <c r="T653" t="inlineStr"/>
@@ -51147,12 +51135,12 @@
       <c r="W653" t="inlineStr"/>
       <c r="X653" t="inlineStr"/>
       <c r="Y653" t="inlineStr"/>
-      <c r="Z653" t="inlineStr"/>
-      <c r="AA653" t="n">
-        <v>0.008202590177000001</v>
-      </c>
+      <c r="Z653" t="n">
+        <v>31.162375408926</v>
+      </c>
+      <c r="AA653" t="inlineStr"/>
       <c r="AB653" t="n">
-        <v>1612.563587975313</v>
+        <v>31.162375408926</v>
       </c>
       <c r="AC653" t="inlineStr"/>
       <c r="AD653" t="inlineStr"/>
@@ -51304,7 +51292,7 @@
         <v>0.008201770000000001</v>
       </c>
       <c r="AB656" t="n">
-        <v>1663.857838200622</v>
+        <v>1663.857838200621</v>
       </c>
       <c r="AC656" t="inlineStr"/>
       <c r="AD656" t="n">
@@ -51720,7 +51708,7 @@
         <v>0.008200949823000001</v>
       </c>
       <c r="AB664" t="n">
-        <v>1699.592603498892</v>
+        <v>1699.592603498891</v>
       </c>
       <c r="AC664" t="inlineStr"/>
       <c r="AD664" t="n">
@@ -52143,6 +52131,58 @@
         <v>24.8367392646328</v>
       </c>
     </row>
+    <row r="673">
+      <c r="A673" s="2" t="n">
+        <v>46103</v>
+      </c>
+      <c r="B673" t="n">
+        <v>0.50554955</v>
+      </c>
+      <c r="C673" t="n">
+        <v>0.0746589015</v>
+      </c>
+      <c r="D673" t="inlineStr"/>
+      <c r="E673" t="inlineStr"/>
+      <c r="F673" t="inlineStr"/>
+      <c r="G673" t="inlineStr"/>
+      <c r="H673" t="inlineStr"/>
+      <c r="I673" t="n">
+        <v>0.03819522</v>
+      </c>
+      <c r="J673" t="inlineStr"/>
+      <c r="K673" t="n">
+        <v>1766.617343552992</v>
+      </c>
+      <c r="L673" t="inlineStr"/>
+      <c r="M673" t="inlineStr"/>
+      <c r="N673" t="inlineStr"/>
+      <c r="O673" t="n">
+        <v>0.1177087031</v>
+      </c>
+      <c r="P673" t="inlineStr"/>
+      <c r="Q673" t="n">
+        <v>7.872e-07</v>
+      </c>
+      <c r="R673" t="inlineStr"/>
+      <c r="S673" t="inlineStr"/>
+      <c r="T673" t="inlineStr"/>
+      <c r="U673" t="inlineStr"/>
+      <c r="V673" t="inlineStr"/>
+      <c r="W673" t="inlineStr"/>
+      <c r="X673" t="inlineStr"/>
+      <c r="Y673" t="inlineStr"/>
+      <c r="Z673" t="inlineStr"/>
+      <c r="AA673" t="n">
+        <v>0.008203410354000001</v>
+      </c>
+      <c r="AB673" t="n">
+        <v>1789.794843977073</v>
+      </c>
+      <c r="AC673" t="inlineStr"/>
+      <c r="AD673" t="n">
+        <v>22.4331838519264</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD673"/>
+  <dimension ref="A1:AD676"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51708,7 +51708,7 @@
         <v>0.008200949823000001</v>
       </c>
       <c r="AB664" t="n">
-        <v>1699.592603498891</v>
+        <v>1699.592603498892</v>
       </c>
       <c r="AC664" t="inlineStr"/>
       <c r="AD664" t="n">
@@ -52183,6 +52183,162 @@
         <v>22.4331838519264</v>
       </c>
     </row>
+    <row r="674">
+      <c r="A674" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B674" t="n">
+        <v>0.5282530525</v>
+      </c>
+      <c r="C674" t="n">
+        <v>0.07822629050000002</v>
+      </c>
+      <c r="D674" t="inlineStr"/>
+      <c r="E674" t="inlineStr"/>
+      <c r="F674" t="inlineStr"/>
+      <c r="G674" t="inlineStr"/>
+      <c r="H674" t="inlineStr"/>
+      <c r="I674" t="n">
+        <v>0.040512633</v>
+      </c>
+      <c r="J674" t="inlineStr"/>
+      <c r="K674" t="n">
+        <v>1753.527073288263</v>
+      </c>
+      <c r="L674" t="inlineStr"/>
+      <c r="M674" t="inlineStr"/>
+      <c r="N674" t="inlineStr"/>
+      <c r="O674" t="n">
+        <v>0.1200951601</v>
+      </c>
+      <c r="P674" t="inlineStr"/>
+      <c r="Q674" t="n">
+        <v>8.303999999999999e-07</v>
+      </c>
+      <c r="R674" t="inlineStr"/>
+      <c r="S674" t="inlineStr"/>
+      <c r="T674" t="inlineStr"/>
+      <c r="U674" t="inlineStr"/>
+      <c r="V674" t="inlineStr"/>
+      <c r="W674" t="inlineStr"/>
+      <c r="X674" t="inlineStr"/>
+      <c r="Y674" t="inlineStr"/>
+      <c r="Z674" t="inlineStr"/>
+      <c r="AA674" t="n">
+        <v>0.008204230531000001</v>
+      </c>
+      <c r="AB674" t="n">
+        <v>1777.331780137271</v>
+      </c>
+      <c r="AC674" t="inlineStr"/>
+      <c r="AD674" t="n">
+        <v>23.0294146519776</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B675" t="n">
+        <v>0.525647713</v>
+      </c>
+      <c r="C675" t="n">
+        <v>0.07837896050000001</v>
+      </c>
+      <c r="D675" t="inlineStr"/>
+      <c r="E675" t="inlineStr"/>
+      <c r="F675" t="inlineStr"/>
+      <c r="G675" t="inlineStr"/>
+      <c r="H675" t="inlineStr"/>
+      <c r="I675" t="n">
+        <v>0.04023348</v>
+      </c>
+      <c r="J675" t="inlineStr"/>
+      <c r="K675" t="n">
+        <v>1742.144229579803</v>
+      </c>
+      <c r="L675" t="inlineStr"/>
+      <c r="M675" t="inlineStr"/>
+      <c r="N675" t="inlineStr"/>
+      <c r="O675" t="n">
+        <v>0.119942953</v>
+      </c>
+      <c r="P675" t="inlineStr"/>
+      <c r="Q675" t="n">
+        <v>8.472e-07</v>
+      </c>
+      <c r="R675" t="inlineStr"/>
+      <c r="S675" t="inlineStr"/>
+      <c r="T675" t="inlineStr"/>
+      <c r="U675" t="inlineStr"/>
+      <c r="V675" t="inlineStr"/>
+      <c r="W675" t="inlineStr"/>
+      <c r="X675" t="inlineStr"/>
+      <c r="Y675" t="inlineStr"/>
+      <c r="Z675" t="inlineStr"/>
+      <c r="AA675" t="n">
+        <v>0.008205050708000001</v>
+      </c>
+      <c r="AB675" t="n">
+        <v>1765.983317661192</v>
+      </c>
+      <c r="AC675" t="inlineStr"/>
+      <c r="AD675" t="n">
+        <v>23.0666790769808</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B676" t="n">
+        <v>0.5314571485</v>
+      </c>
+      <c r="C676" t="n">
+        <v>0.07884387700000001</v>
+      </c>
+      <c r="D676" t="inlineStr"/>
+      <c r="E676" t="inlineStr"/>
+      <c r="F676" t="inlineStr"/>
+      <c r="G676" t="inlineStr"/>
+      <c r="H676" t="inlineStr"/>
+      <c r="I676" t="n">
+        <v>0.04063227</v>
+      </c>
+      <c r="J676" t="inlineStr"/>
+      <c r="K676" t="n">
+        <v>1790.521315340758</v>
+      </c>
+      <c r="L676" t="inlineStr"/>
+      <c r="M676" t="inlineStr"/>
+      <c r="N676" t="inlineStr"/>
+      <c r="O676" t="n">
+        <v>0.1217017906</v>
+      </c>
+      <c r="P676" t="inlineStr"/>
+      <c r="Q676" t="n">
+        <v>8.52e-07</v>
+      </c>
+      <c r="R676" t="inlineStr"/>
+      <c r="S676" t="inlineStr"/>
+      <c r="T676" t="inlineStr"/>
+      <c r="U676" t="inlineStr"/>
+      <c r="V676" t="inlineStr"/>
+      <c r="W676" t="inlineStr"/>
+      <c r="X676" t="inlineStr"/>
+      <c r="Y676" t="inlineStr"/>
+      <c r="Z676" t="inlineStr"/>
+      <c r="AA676" t="n">
+        <v>0.008203410354000001</v>
+      </c>
+      <c r="AB676" t="n">
+        <v>1816.08299731634</v>
+      </c>
+      <c r="AC676" t="inlineStr"/>
+      <c r="AD676" t="n">
+        <v>24.780842627128</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -51292,7 +51292,7 @@
         <v>0.008201770000000001</v>
       </c>
       <c r="AB656" t="n">
-        <v>1663.857838200621</v>
+        <v>1663.857838200622</v>
       </c>
       <c r="AC656" t="inlineStr"/>
       <c r="AD656" t="n">

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD676"/>
+  <dimension ref="A1:AD681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52339,6 +52339,266 @@
         <v>24.780842627128</v>
       </c>
     </row>
+    <row r="677">
+      <c r="A677" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B677" t="n">
+        <v>0.5127113095</v>
+      </c>
+      <c r="C677" t="n">
+        <v>0.07489663050000001</v>
+      </c>
+      <c r="D677" t="inlineStr"/>
+      <c r="E677" t="inlineStr"/>
+      <c r="F677" t="inlineStr"/>
+      <c r="G677" t="inlineStr"/>
+      <c r="H677" t="inlineStr"/>
+      <c r="I677" t="n">
+        <v>0.038341443</v>
+      </c>
+      <c r="J677" t="inlineStr"/>
+      <c r="K677" t="n">
+        <v>1772.877907592645</v>
+      </c>
+      <c r="L677" t="inlineStr"/>
+      <c r="M677" t="inlineStr"/>
+      <c r="N677" t="inlineStr"/>
+      <c r="O677" t="n">
+        <v>0.1181690826</v>
+      </c>
+      <c r="P677" t="inlineStr"/>
+      <c r="Q677" t="n">
+        <v>8.184e-07</v>
+      </c>
+      <c r="R677" t="inlineStr"/>
+      <c r="S677" t="inlineStr"/>
+      <c r="T677" t="inlineStr"/>
+      <c r="U677" t="inlineStr"/>
+      <c r="V677" t="inlineStr"/>
+      <c r="W677" t="inlineStr"/>
+      <c r="X677" t="inlineStr"/>
+      <c r="Y677" t="inlineStr"/>
+      <c r="Z677" t="inlineStr"/>
+      <c r="AA677" t="n">
+        <v>0.008205870885000001</v>
+      </c>
+      <c r="AB677" t="n">
+        <v>1797.013659437038</v>
+      </c>
+      <c r="AC677" t="inlineStr"/>
+      <c r="AD677" t="n">
+        <v>23.383426689508</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B678" t="n">
+        <v>0.494734236</v>
+      </c>
+      <c r="C678" t="n">
+        <v>0.07243646250000001</v>
+      </c>
+      <c r="D678" t="inlineStr"/>
+      <c r="E678" t="inlineStr"/>
+      <c r="F678" t="inlineStr"/>
+      <c r="G678" t="inlineStr"/>
+      <c r="H678" t="inlineStr"/>
+      <c r="I678" t="n">
+        <v>0.036826041</v>
+      </c>
+      <c r="J678" t="inlineStr"/>
+      <c r="K678" t="n">
+        <v>1771.739623221799</v>
+      </c>
+      <c r="L678" t="inlineStr"/>
+      <c r="M678" t="inlineStr"/>
+      <c r="N678" t="inlineStr"/>
+      <c r="O678" t="n">
+        <v>0.1153673445</v>
+      </c>
+      <c r="P678" t="inlineStr"/>
+      <c r="Q678" t="n">
+        <v>7.872e-07</v>
+      </c>
+      <c r="R678" t="inlineStr"/>
+      <c r="S678" t="inlineStr"/>
+      <c r="T678" t="inlineStr"/>
+      <c r="U678" t="inlineStr"/>
+      <c r="V678" t="inlineStr"/>
+      <c r="W678" t="inlineStr"/>
+      <c r="X678" t="inlineStr"/>
+      <c r="Y678" t="inlineStr"/>
+      <c r="Z678" t="inlineStr"/>
+      <c r="AA678" t="n">
+        <v>0.008205870885000001</v>
+      </c>
+      <c r="AB678" t="n">
+        <v>1795.291654278344</v>
+      </c>
+      <c r="AC678" t="inlineStr"/>
+      <c r="AD678" t="n">
+        <v>22.82446031446</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="2" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B679" t="n">
+        <v>0.4945088735</v>
+      </c>
+      <c r="C679" t="n">
+        <v>0.072508799</v>
+      </c>
+      <c r="D679" t="inlineStr"/>
+      <c r="E679" t="inlineStr"/>
+      <c r="F679" t="inlineStr"/>
+      <c r="G679" t="inlineStr"/>
+      <c r="H679" t="inlineStr"/>
+      <c r="I679" t="n">
+        <v>0.036374079</v>
+      </c>
+      <c r="J679" t="inlineStr"/>
+      <c r="K679" t="n">
+        <v>1802.473301234641</v>
+      </c>
+      <c r="L679" t="inlineStr"/>
+      <c r="M679" t="inlineStr"/>
+      <c r="N679" t="inlineStr"/>
+      <c r="O679" t="n">
+        <v>0.1148280428</v>
+      </c>
+      <c r="P679" t="inlineStr"/>
+      <c r="Q679" t="n">
+        <v>7.895999999999999e-07</v>
+      </c>
+      <c r="R679" t="inlineStr"/>
+      <c r="S679" t="inlineStr"/>
+      <c r="T679" t="inlineStr"/>
+      <c r="U679" t="inlineStr"/>
+      <c r="V679" t="inlineStr"/>
+      <c r="W679" t="inlineStr"/>
+      <c r="X679" t="inlineStr"/>
+      <c r="Y679" t="inlineStr"/>
+      <c r="Z679" t="inlineStr"/>
+      <c r="AA679" t="n">
+        <v>0.008205870885000001</v>
+      </c>
+      <c r="AB679" t="n">
+        <v>1824.626772066266</v>
+      </c>
+      <c r="AC679" t="inlineStr"/>
+      <c r="AD679" t="n">
+        <v>21.42704437684</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="2" t="n">
+        <v>46110</v>
+      </c>
+      <c r="B680" t="n">
+        <v>0.4917814285</v>
+      </c>
+      <c r="C680" t="n">
+        <v>0.07214166400000001</v>
+      </c>
+      <c r="D680" t="inlineStr"/>
+      <c r="E680" t="inlineStr"/>
+      <c r="F680" t="inlineStr"/>
+      <c r="G680" t="inlineStr"/>
+      <c r="H680" t="inlineStr"/>
+      <c r="I680" t="n">
+        <v>0.036086064</v>
+      </c>
+      <c r="J680" t="inlineStr"/>
+      <c r="K680" t="n">
+        <v>1832.63783706206</v>
+      </c>
+      <c r="L680" t="inlineStr"/>
+      <c r="M680" t="inlineStr"/>
+      <c r="N680" t="inlineStr"/>
+      <c r="O680" t="n">
+        <v>0.1138903719</v>
+      </c>
+      <c r="P680" t="inlineStr"/>
+      <c r="Q680" t="n">
+        <v>7.872e-07</v>
+      </c>
+      <c r="R680" t="inlineStr"/>
+      <c r="S680" t="inlineStr"/>
+      <c r="T680" t="inlineStr"/>
+      <c r="U680" t="inlineStr"/>
+      <c r="V680" t="inlineStr"/>
+      <c r="W680" t="inlineStr"/>
+      <c r="X680" t="inlineStr"/>
+      <c r="Y680" t="inlineStr"/>
+      <c r="Z680" t="inlineStr"/>
+      <c r="AA680" t="n">
+        <v>0.008205870885000001</v>
+      </c>
+      <c r="AB680" t="n">
+        <v>1854.507504437861</v>
+      </c>
+      <c r="AC680" t="inlineStr"/>
+      <c r="AD680" t="n">
+        <v>21.147561189316</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B681" t="n">
+        <v>0.4976404065</v>
+      </c>
+      <c r="C681" t="n">
+        <v>0.07366254800000001</v>
+      </c>
+      <c r="D681" t="inlineStr"/>
+      <c r="E681" t="inlineStr"/>
+      <c r="F681" t="inlineStr"/>
+      <c r="G681" t="inlineStr"/>
+      <c r="H681" t="inlineStr"/>
+      <c r="I681" t="n">
+        <v>0.036573474</v>
+      </c>
+      <c r="J681" t="inlineStr"/>
+      <c r="K681" t="n">
+        <v>1821.2549933536</v>
+      </c>
+      <c r="L681" t="inlineStr"/>
+      <c r="M681" t="inlineStr"/>
+      <c r="N681" t="inlineStr"/>
+      <c r="O681" t="n">
+        <v>0.1144916839</v>
+      </c>
+      <c r="P681" t="inlineStr"/>
+      <c r="Q681" t="n">
+        <v>7.967999999999999e-07</v>
+      </c>
+      <c r="R681" t="inlineStr"/>
+      <c r="S681" t="inlineStr"/>
+      <c r="T681" t="inlineStr"/>
+      <c r="U681" t="inlineStr"/>
+      <c r="V681" t="inlineStr"/>
+      <c r="W681" t="inlineStr"/>
+      <c r="X681" t="inlineStr"/>
+      <c r="Y681" t="inlineStr"/>
+      <c r="Z681" t="inlineStr"/>
+      <c r="AA681" t="n">
+        <v>0.008205050708000001</v>
+      </c>
+      <c r="AB681" t="n">
+        <v>1843.133128502824</v>
+      </c>
+      <c r="AC681" t="inlineStr"/>
+      <c r="AD681" t="n">
+        <v>21.147561189316</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD681"/>
+  <dimension ref="A1:AD682"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51292,7 +51292,7 @@
         <v>0.008201770000000001</v>
       </c>
       <c r="AB656" t="n">
-        <v>1663.857838200622</v>
+        <v>1663.857838200621</v>
       </c>
       <c r="AC656" t="inlineStr"/>
       <c r="AD656" t="n">
@@ -52599,6 +52599,58 @@
         <v>21.147561189316</v>
       </c>
     </row>
+    <row r="682">
+      <c r="A682" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B682" t="n">
+        <v>0.5087193759999999</v>
+      </c>
+      <c r="C682" t="n">
+        <v>0.0765323805</v>
+      </c>
+      <c r="D682" t="inlineStr"/>
+      <c r="E682" t="inlineStr"/>
+      <c r="F682" t="inlineStr"/>
+      <c r="G682" t="inlineStr"/>
+      <c r="H682" t="inlineStr"/>
+      <c r="I682" t="n">
+        <v>0.03686592</v>
+      </c>
+      <c r="J682" t="inlineStr"/>
+      <c r="K682" t="n">
+        <v>1783.122466930259</v>
+      </c>
+      <c r="L682" t="inlineStr"/>
+      <c r="M682" t="inlineStr"/>
+      <c r="N682" t="inlineStr"/>
+      <c r="O682" t="n">
+        <v>0.1160212713</v>
+      </c>
+      <c r="P682" t="inlineStr"/>
+      <c r="Q682" t="n">
+        <v>8.184e-07</v>
+      </c>
+      <c r="R682" t="inlineStr"/>
+      <c r="S682" t="inlineStr"/>
+      <c r="T682" t="inlineStr"/>
+      <c r="U682" t="inlineStr"/>
+      <c r="V682" t="inlineStr"/>
+      <c r="W682" t="inlineStr"/>
+      <c r="X682" t="inlineStr"/>
+      <c r="Y682" t="inlineStr"/>
+      <c r="Z682" t="inlineStr"/>
+      <c r="AA682" t="n">
+        <v>0.008206691061999999</v>
+      </c>
+      <c r="AB682" t="n">
+        <v>1804.662362539307</v>
+      </c>
+      <c r="AC682" t="inlineStr"/>
+      <c r="AD682" t="n">
+        <v>20.7935491517856</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -51292,7 +51292,7 @@
         <v>0.008201770000000001</v>
       </c>
       <c r="AB656" t="n">
-        <v>1663.857838200621</v>
+        <v>1663.857838200622</v>
       </c>
       <c r="AC656" t="inlineStr"/>
       <c r="AD656" t="n">
@@ -51708,7 +51708,7 @@
         <v>0.008200949823000001</v>
       </c>
       <c r="AB664" t="n">
-        <v>1699.592603498892</v>
+        <v>1699.592603498891</v>
       </c>
       <c r="AC664" t="inlineStr"/>
       <c r="AD664" t="n">

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -51865,7 +51865,9 @@
       <c r="AD654" t="n">
         <v>44.7918388538464</v>
       </c>
-      <c r="AE654" t="inlineStr"/>
+      <c r="AE654" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="655">
       <c r="A655" s="2" t="n">
@@ -51918,7 +51920,9 @@
       <c r="AD655" t="n">
         <v>39.8915669659256</v>
       </c>
-      <c r="AE655" t="inlineStr"/>
+      <c r="AE655" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="656">
       <c r="A656" s="2" t="n">
@@ -52077,7 +52081,9 @@
       <c r="AD658" t="n">
         <v>32.9976483403336</v>
       </c>
-      <c r="AE658" t="inlineStr"/>
+      <c r="AE658" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="659">
       <c r="A659" s="2" t="n">
@@ -52183,7 +52189,9 @@
       <c r="AD660" t="n">
         <v>34.3391676404488</v>
       </c>
-      <c r="AE660" t="inlineStr"/>
+      <c r="AE660" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="661">
       <c r="A661" s="2" t="n">
@@ -52342,7 +52350,9 @@
       <c r="AD663" t="n">
         <v>28.9544582274864</v>
       </c>
-      <c r="AE663" t="inlineStr"/>
+      <c r="AE663" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="664">
       <c r="A664" s="2" t="n">
@@ -52395,7 +52405,9 @@
       <c r="AD664" t="n">
         <v>28.6377106149592</v>
       </c>
-      <c r="AE664" t="inlineStr"/>
+      <c r="AE664" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="665">
       <c r="A665" s="2" t="n">
@@ -52501,7 +52513,9 @@
       <c r="AD666" t="n">
         <v>28.87992937748</v>
       </c>
-      <c r="AE666" t="inlineStr"/>
+      <c r="AE666" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="667">
       <c r="A667" s="2" t="n">
@@ -52554,7 +52568,9 @@
       <c r="AD667" t="n">
         <v>27.8178932648888</v>
       </c>
-      <c r="AE667" t="inlineStr"/>
+      <c r="AE667" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="668">
       <c r="A668" s="2" t="n">
@@ -52925,7 +52941,9 @@
       <c r="AD674" t="n">
         <v>23.0666790769808</v>
       </c>
-      <c r="AE674" t="inlineStr"/>
+      <c r="AE674" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="675">
       <c r="A675" s="2" t="n">
@@ -53243,7 +53261,9 @@
       <c r="AD680" t="n">
         <v>21.147561189316</v>
       </c>
-      <c r="AE680" t="inlineStr"/>
+      <c r="AE680" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="681">
       <c r="A681" s="2" t="n">
@@ -53296,7 +53316,9 @@
       <c r="AD681" t="n">
         <v>20.7935491517856</v>
       </c>
-      <c r="AE681" t="inlineStr"/>
+      <c r="AE681" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="682">
       <c r="A682" s="2" t="n">

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE683"/>
+  <dimension ref="A1:AE686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52304,7 +52304,9 @@
       <c r="AC662" t="n">
         <v>31.3207492151896</v>
       </c>
-      <c r="AD662" t="inlineStr"/>
+      <c r="AD662" t="n">
+        <v>0</v>
+      </c>
       <c r="AE662" t="n">
         <v>1689.998435014512</v>
       </c>
@@ -52520,7 +52522,9 @@
       <c r="AC666" t="n">
         <v>28.3954918524384</v>
       </c>
-      <c r="AD666" t="inlineStr"/>
+      <c r="AD666" t="n">
+        <v>0</v>
+      </c>
       <c r="AE666" t="n">
         <v>1729.220561662285</v>
       </c>
@@ -52793,7 +52797,9 @@
       <c r="AC671" t="n">
         <v>26.0292008647352</v>
       </c>
-      <c r="AD671" t="inlineStr"/>
+      <c r="AD671" t="n">
+        <v>0</v>
+      </c>
       <c r="AE671" t="n">
         <v>1789.434539557943</v>
       </c>
@@ -52901,7 +52907,9 @@
       <c r="AC673" t="n">
         <v>22.4331838519264</v>
       </c>
-      <c r="AD673" t="inlineStr"/>
+      <c r="AD673" t="n">
+        <v>0</v>
+      </c>
       <c r="AE673" t="n">
         <v>1789.794843977073</v>
       </c>
@@ -53452,6 +53460,171 @@
         <v>1814.040785305502</v>
       </c>
     </row>
+    <row r="684">
+      <c r="A684" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B684" t="n">
+        <v>0.4984198255</v>
+      </c>
+      <c r="C684" t="n">
+        <v>0.07477812950000001</v>
+      </c>
+      <c r="D684" t="inlineStr"/>
+      <c r="E684" t="inlineStr"/>
+      <c r="F684" t="inlineStr"/>
+      <c r="G684" t="inlineStr"/>
+      <c r="H684" t="inlineStr"/>
+      <c r="I684" t="n">
+        <v>0.034978314</v>
+      </c>
+      <c r="J684" t="inlineStr"/>
+      <c r="K684" t="n">
+        <v>1294.438728453296</v>
+      </c>
+      <c r="L684" t="inlineStr"/>
+      <c r="M684" t="inlineStr"/>
+      <c r="N684" t="inlineStr"/>
+      <c r="O684" t="n">
+        <v>412.2818079744</v>
+      </c>
+      <c r="P684" t="inlineStr"/>
+      <c r="Q684" t="n">
+        <v>8.016e-07</v>
+      </c>
+      <c r="R684" t="inlineStr"/>
+      <c r="S684" t="inlineStr"/>
+      <c r="T684" t="inlineStr"/>
+      <c r="U684" t="inlineStr"/>
+      <c r="V684" t="inlineStr"/>
+      <c r="W684" t="inlineStr"/>
+      <c r="X684" t="inlineStr"/>
+      <c r="Y684" t="inlineStr"/>
+      <c r="Z684" t="inlineStr"/>
+      <c r="AA684" t="n">
+        <v>0.02165823</v>
+      </c>
+      <c r="AB684" t="inlineStr"/>
+      <c r="AC684" t="n">
+        <v>19.4892942766736</v>
+      </c>
+      <c r="AD684" t="n">
+        <v>63.09059999999999</v>
+      </c>
+      <c r="AE684" t="n">
+        <v>1789.930266004969</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B685" t="n">
+        <v>0.498884035</v>
+      </c>
+      <c r="C685" t="n">
+        <v>0.07465672050000001</v>
+      </c>
+      <c r="D685" t="inlineStr"/>
+      <c r="E685" t="inlineStr"/>
+      <c r="F685" t="inlineStr"/>
+      <c r="G685" t="inlineStr"/>
+      <c r="H685" t="inlineStr"/>
+      <c r="I685" t="n">
+        <v>0.03562524</v>
+      </c>
+      <c r="J685" t="inlineStr"/>
+      <c r="K685" t="n">
+        <v>1294.028056267873</v>
+      </c>
+      <c r="L685" t="inlineStr"/>
+      <c r="M685" t="inlineStr"/>
+      <c r="N685" t="inlineStr"/>
+      <c r="O685" t="n">
+        <v>415.6661476031999</v>
+      </c>
+      <c r="P685" t="inlineStr"/>
+      <c r="Q685" t="n">
+        <v>8.207999999999999e-07</v>
+      </c>
+      <c r="R685" t="inlineStr"/>
+      <c r="S685" t="inlineStr"/>
+      <c r="T685" t="inlineStr"/>
+      <c r="U685" t="inlineStr"/>
+      <c r="V685" t="inlineStr"/>
+      <c r="W685" t="inlineStr"/>
+      <c r="X685" t="inlineStr"/>
+      <c r="Y685" t="inlineStr"/>
+      <c r="Z685" t="inlineStr"/>
+      <c r="AA685" t="n">
+        <v>0.021660395823</v>
+      </c>
+      <c r="AB685" t="inlineStr"/>
+      <c r="AC685" t="n">
+        <v>20.0482606517216</v>
+      </c>
+      <c r="AD685" t="n">
+        <v>62.90599999999999</v>
+      </c>
+      <c r="AE685" t="n">
+        <v>1793.279291734917</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B686" t="n">
+        <v>0.501388129</v>
+      </c>
+      <c r="C686" t="n">
+        <v>0.075081652</v>
+      </c>
+      <c r="D686" t="inlineStr"/>
+      <c r="E686" t="inlineStr"/>
+      <c r="F686" t="inlineStr"/>
+      <c r="G686" t="inlineStr"/>
+      <c r="H686" t="inlineStr"/>
+      <c r="I686" t="n">
+        <v>0.035815773</v>
+      </c>
+      <c r="J686" t="inlineStr"/>
+      <c r="K686" t="n">
+        <v>1304.294860903448</v>
+      </c>
+      <c r="L686" t="inlineStr"/>
+      <c r="M686" t="inlineStr"/>
+      <c r="N686" t="inlineStr"/>
+      <c r="O686" t="n">
+        <v>419.2341883392</v>
+      </c>
+      <c r="P686" t="inlineStr"/>
+      <c r="Q686" t="n">
+        <v>8.16e-07</v>
+      </c>
+      <c r="R686" t="inlineStr"/>
+      <c r="S686" t="inlineStr"/>
+      <c r="T686" t="inlineStr"/>
+      <c r="U686" t="inlineStr"/>
+      <c r="V686" t="inlineStr"/>
+      <c r="W686" t="inlineStr"/>
+      <c r="X686" t="inlineStr"/>
+      <c r="Y686" t="inlineStr"/>
+      <c r="Z686" t="inlineStr"/>
+      <c r="AA686" t="n">
+        <v>0.02165823</v>
+      </c>
+      <c r="AB686" t="inlineStr"/>
+      <c r="AC686" t="n">
+        <v>19.936467376712</v>
+      </c>
+      <c r="AD686" t="n">
+        <v>62.65039999999999</v>
+      </c>
+      <c r="AE686" t="n">
+        <v>1806.74986121936</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE686"/>
+  <dimension ref="A1:AE689"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52359,7 +52359,9 @@
       <c r="AC663" t="n">
         <v>30.2028164650936</v>
       </c>
-      <c r="AD663" t="inlineStr"/>
+      <c r="AD663" t="n">
+        <v>0</v>
+      </c>
       <c r="AE663" t="n">
         <v>1676.362926043586</v>
       </c>
@@ -53072,7 +53074,9 @@
       <c r="AC676" t="n">
         <v>24.780842627128</v>
       </c>
-      <c r="AD676" t="inlineStr"/>
+      <c r="AD676" t="n">
+        <v>0</v>
+      </c>
       <c r="AE676" t="n">
         <v>1816.08299731634</v>
       </c>
@@ -53625,6 +53629,171 @@
         <v>1806.74986121936</v>
       </c>
     </row>
+    <row r="687">
+      <c r="A687" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="B687" t="n">
+        <v>0.514304641</v>
+      </c>
+      <c r="C687" t="n">
+        <v>0.07670467950000001</v>
+      </c>
+      <c r="D687" t="inlineStr"/>
+      <c r="E687" t="inlineStr"/>
+      <c r="F687" t="inlineStr"/>
+      <c r="G687" t="inlineStr"/>
+      <c r="H687" t="inlineStr"/>
+      <c r="I687" t="n">
+        <v>0.036285459</v>
+      </c>
+      <c r="J687" t="inlineStr"/>
+      <c r="K687" t="n">
+        <v>1309.633599313947</v>
+      </c>
+      <c r="L687" t="inlineStr"/>
+      <c r="M687" t="inlineStr"/>
+      <c r="N687" t="inlineStr"/>
+      <c r="O687" t="n">
+        <v>424.98544608</v>
+      </c>
+      <c r="P687" t="inlineStr"/>
+      <c r="Q687" t="n">
+        <v>8.375999999999999e-07</v>
+      </c>
+      <c r="R687" t="inlineStr"/>
+      <c r="S687" t="inlineStr"/>
+      <c r="T687" t="inlineStr"/>
+      <c r="U687" t="inlineStr"/>
+      <c r="V687" t="inlineStr"/>
+      <c r="W687" t="inlineStr"/>
+      <c r="X687" t="inlineStr"/>
+      <c r="Y687" t="inlineStr"/>
+      <c r="Z687" t="inlineStr"/>
+      <c r="AA687" t="n">
+        <v>0.021662561646</v>
+      </c>
+      <c r="AB687" t="inlineStr"/>
+      <c r="AC687" t="n">
+        <v>19.6383519766864</v>
+      </c>
+      <c r="AD687" t="n">
+        <v>60.8612</v>
+      </c>
+      <c r="AE687" t="n">
+        <v>1815.767555549379</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B688" t="n">
+        <v>0.512959767</v>
+      </c>
+      <c r="C688" t="n">
+        <v>0.076595266</v>
+      </c>
+      <c r="D688" t="inlineStr"/>
+      <c r="E688" t="inlineStr"/>
+      <c r="F688" t="inlineStr"/>
+      <c r="G688" t="inlineStr"/>
+      <c r="H688" t="inlineStr"/>
+      <c r="I688" t="n">
+        <v>0.035461293</v>
+      </c>
+      <c r="J688" t="inlineStr"/>
+      <c r="K688" t="n">
+        <v>1299.777466863795</v>
+      </c>
+      <c r="L688" t="inlineStr"/>
+      <c r="M688" t="inlineStr"/>
+      <c r="N688" t="inlineStr"/>
+      <c r="O688" t="n">
+        <v>424.0033516992</v>
+      </c>
+      <c r="P688" t="inlineStr"/>
+      <c r="Q688" t="n">
+        <v>7.967999999999999e-07</v>
+      </c>
+      <c r="R688" t="inlineStr"/>
+      <c r="S688" t="inlineStr"/>
+      <c r="T688" t="inlineStr"/>
+      <c r="U688" t="inlineStr"/>
+      <c r="V688" t="inlineStr"/>
+      <c r="W688" t="inlineStr"/>
+      <c r="X688" t="inlineStr"/>
+      <c r="Y688" t="inlineStr"/>
+      <c r="Z688" t="inlineStr"/>
+      <c r="AA688" t="n">
+        <v>0.021656064177</v>
+      </c>
+      <c r="AB688" t="inlineStr"/>
+      <c r="AC688" t="n">
+        <v>19.5265587016768</v>
+      </c>
+      <c r="AD688" t="n">
+        <v>61.7842</v>
+      </c>
+      <c r="AE688" t="n">
+        <v>1805.738250451649</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B689" t="n">
+        <v>0.535835439</v>
+      </c>
+      <c r="C689" t="n">
+        <v>0.08142436350000001</v>
+      </c>
+      <c r="D689" t="inlineStr"/>
+      <c r="E689" t="inlineStr"/>
+      <c r="F689" t="inlineStr"/>
+      <c r="G689" t="inlineStr"/>
+      <c r="H689" t="inlineStr"/>
+      <c r="I689" t="n">
+        <v>0.037911636</v>
+      </c>
+      <c r="J689" t="inlineStr"/>
+      <c r="K689" t="n">
+        <v>1296.081417194988</v>
+      </c>
+      <c r="L689" t="inlineStr"/>
+      <c r="M689" t="inlineStr"/>
+      <c r="N689" t="inlineStr"/>
+      <c r="O689" t="n">
+        <v>438.127140672</v>
+      </c>
+      <c r="P689" t="inlineStr"/>
+      <c r="Q689" t="n">
+        <v>8.904e-07</v>
+      </c>
+      <c r="R689" t="inlineStr"/>
+      <c r="S689" t="inlineStr"/>
+      <c r="T689" t="inlineStr"/>
+      <c r="U689" t="inlineStr"/>
+      <c r="V689" t="inlineStr"/>
+      <c r="W689" t="inlineStr"/>
+      <c r="X689" t="inlineStr"/>
+      <c r="Y689" t="inlineStr"/>
+      <c r="Z689" t="inlineStr"/>
+      <c r="AA689" t="n">
+        <v>0.021660395823</v>
+      </c>
+      <c r="AB689" t="inlineStr"/>
+      <c r="AC689" t="n">
+        <v>20.5513303892648</v>
+      </c>
+      <c r="AD689" t="n">
+        <v>63.31779999999999</v>
+      </c>
+      <c r="AE689" t="n">
+        <v>1818.754520980976</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE689"/>
+  <dimension ref="A1:AE691"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53794,6 +53794,116 @@
         <v>1818.754520980976</v>
       </c>
     </row>
+    <row r="690">
+      <c r="A690" s="2" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B690" t="n">
+        <v>0.5294709784999999</v>
+      </c>
+      <c r="C690" t="n">
+        <v>0.07960650000000001</v>
+      </c>
+      <c r="D690" t="inlineStr"/>
+      <c r="E690" t="inlineStr"/>
+      <c r="F690" t="inlineStr"/>
+      <c r="G690" t="inlineStr"/>
+      <c r="H690" t="inlineStr"/>
+      <c r="I690" t="n">
+        <v>0.03658676699999999</v>
+      </c>
+      <c r="J690" t="inlineStr"/>
+      <c r="K690" t="n">
+        <v>1305.93754964514</v>
+      </c>
+      <c r="L690" t="inlineStr"/>
+      <c r="M690" t="inlineStr"/>
+      <c r="N690" t="inlineStr"/>
+      <c r="O690" t="n">
+        <v>424.7452215552</v>
+      </c>
+      <c r="P690" t="inlineStr"/>
+      <c r="Q690" t="n">
+        <v>8.496e-07</v>
+      </c>
+      <c r="R690" t="inlineStr"/>
+      <c r="S690" t="inlineStr"/>
+      <c r="T690" t="inlineStr"/>
+      <c r="U690" t="inlineStr"/>
+      <c r="V690" t="inlineStr"/>
+      <c r="W690" t="inlineStr"/>
+      <c r="X690" t="inlineStr"/>
+      <c r="Y690" t="inlineStr"/>
+      <c r="Z690" t="inlineStr"/>
+      <c r="AA690" t="n">
+        <v>0.021656064177</v>
+      </c>
+      <c r="AB690" t="inlineStr"/>
+      <c r="AC690" t="n">
+        <v>19.750145251696</v>
+      </c>
+      <c r="AD690" t="n">
+        <v>62.66459999999999</v>
+      </c>
+      <c r="AE690" t="n">
+        <v>1813.764837611313</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B691" t="n">
+        <v>0.5348203765</v>
+      </c>
+      <c r="C691" t="n">
+        <v>0.07961377</v>
+      </c>
+      <c r="D691" t="inlineStr"/>
+      <c r="E691" t="inlineStr"/>
+      <c r="F691" t="inlineStr"/>
+      <c r="G691" t="inlineStr"/>
+      <c r="H691" t="inlineStr"/>
+      <c r="I691" t="n">
+        <v>0.036923523</v>
+      </c>
+      <c r="J691" t="inlineStr"/>
+      <c r="K691" t="n">
+        <v>1315.383009909869</v>
+      </c>
+      <c r="L691" t="inlineStr"/>
+      <c r="M691" t="inlineStr"/>
+      <c r="N691" t="inlineStr"/>
+      <c r="O691" t="n">
+        <v>426.0664564415999</v>
+      </c>
+      <c r="P691" t="inlineStr"/>
+      <c r="Q691" t="n">
+        <v>8.424e-07</v>
+      </c>
+      <c r="R691" t="inlineStr"/>
+      <c r="S691" t="inlineStr"/>
+      <c r="T691" t="inlineStr"/>
+      <c r="U691" t="inlineStr"/>
+      <c r="V691" t="inlineStr"/>
+      <c r="W691" t="inlineStr"/>
+      <c r="X691" t="inlineStr"/>
+      <c r="Y691" t="inlineStr"/>
+      <c r="Z691" t="inlineStr"/>
+      <c r="AA691" t="n">
+        <v>0.021656064177</v>
+      </c>
+      <c r="AB691" t="inlineStr"/>
+      <c r="AC691" t="n">
+        <v>19.8246741017024</v>
+      </c>
+      <c r="AD691" t="n">
+        <v>62.92019999999999</v>
+      </c>
+      <c r="AE691" t="n">
+        <v>1824.867355029248</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -52418,7 +52418,7 @@
         <v>0</v>
       </c>
       <c r="AE664" t="n">
-        <v>1699.592603498892</v>
+        <v>1699.592603498891</v>
       </c>
     </row>
     <row r="665">

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE691"/>
+  <dimension ref="A1:AE695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52418,7 +52418,7 @@
         <v>0</v>
       </c>
       <c r="AE664" t="n">
-        <v>1699.592603498891</v>
+        <v>1699.592603498892</v>
       </c>
     </row>
     <row r="665">
@@ -53294,7 +53294,9 @@
       <c r="AC680" t="n">
         <v>21.147561189316</v>
       </c>
-      <c r="AD680" t="inlineStr"/>
+      <c r="AD680" t="n">
+        <v>0</v>
+      </c>
       <c r="AE680" t="n">
         <v>1854.507504437861</v>
       </c>
@@ -53904,6 +53906,226 @@
         <v>1824.867355029248</v>
       </c>
     </row>
+    <row r="692">
+      <c r="A692" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B692" t="n">
+        <v>0.5435721149999999</v>
+      </c>
+      <c r="C692" t="n">
+        <v>0.08160756750000002</v>
+      </c>
+      <c r="D692" t="inlineStr"/>
+      <c r="E692" t="inlineStr"/>
+      <c r="F692" t="inlineStr"/>
+      <c r="G692" t="inlineStr"/>
+      <c r="H692" t="inlineStr"/>
+      <c r="I692" t="n">
+        <v>0.037588173</v>
+      </c>
+      <c r="J692" t="inlineStr"/>
+      <c r="K692" t="n">
+        <v>1310.865615870216</v>
+      </c>
+      <c r="L692" t="inlineStr"/>
+      <c r="M692" t="inlineStr"/>
+      <c r="N692" t="inlineStr"/>
+      <c r="O692" t="n">
+        <v>427.8398786687999</v>
+      </c>
+      <c r="P692" t="inlineStr"/>
+      <c r="Q692" t="n">
+        <v>8.711999999999999e-07</v>
+      </c>
+      <c r="R692" t="inlineStr"/>
+      <c r="S692" t="inlineStr"/>
+      <c r="T692" t="inlineStr"/>
+      <c r="U692" t="inlineStr"/>
+      <c r="V692" t="inlineStr"/>
+      <c r="W692" t="inlineStr"/>
+      <c r="X692" t="inlineStr"/>
+      <c r="Y692" t="inlineStr"/>
+      <c r="Z692" t="inlineStr"/>
+      <c r="AA692" t="n">
+        <v>0.021649566708</v>
+      </c>
+      <c r="AB692" t="inlineStr"/>
+      <c r="AC692" t="n">
+        <v>20.122789501728</v>
+      </c>
+      <c r="AD692" t="n">
+        <v>63.0196</v>
+      </c>
+      <c r="AE692" t="n">
+        <v>1822.532302334152</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="B693" t="n">
+        <v>0.5441715420000001</v>
+      </c>
+      <c r="C693" t="n">
+        <v>0.0830593865</v>
+      </c>
+      <c r="D693" t="inlineStr"/>
+      <c r="E693" t="inlineStr"/>
+      <c r="F693" t="inlineStr"/>
+      <c r="G693" t="inlineStr"/>
+      <c r="H693" t="inlineStr"/>
+      <c r="I693" t="n">
+        <v>0.037632483</v>
+      </c>
+      <c r="J693" t="inlineStr"/>
+      <c r="K693" t="n">
+        <v>1309.633599313947</v>
+      </c>
+      <c r="L693" t="inlineStr"/>
+      <c r="M693" t="inlineStr"/>
+      <c r="N693" t="inlineStr"/>
+      <c r="O693" t="n">
+        <v>428.9067581759999</v>
+      </c>
+      <c r="P693" t="inlineStr"/>
+      <c r="Q693" t="n">
+        <v>8.736e-07</v>
+      </c>
+      <c r="R693" t="inlineStr"/>
+      <c r="S693" t="inlineStr"/>
+      <c r="T693" t="inlineStr"/>
+      <c r="U693" t="inlineStr"/>
+      <c r="V693" t="inlineStr"/>
+      <c r="W693" t="inlineStr"/>
+      <c r="X693" t="inlineStr"/>
+      <c r="Y693" t="inlineStr"/>
+      <c r="Z693" t="inlineStr"/>
+      <c r="AA693" t="n">
+        <v>0.021647400885</v>
+      </c>
+      <c r="AB693" t="inlineStr"/>
+      <c r="AC693" t="n">
+        <v>19.8619385267056</v>
+      </c>
+      <c r="AD693" t="n">
+        <v>62.15339999999999</v>
+      </c>
+      <c r="AE693" t="n">
+        <v>1821.242207702637</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="2" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B694" t="n">
+        <v>0.527020301</v>
+      </c>
+      <c r="C694" t="n">
+        <v>0.07966647750000001</v>
+      </c>
+      <c r="D694" t="inlineStr"/>
+      <c r="E694" t="inlineStr"/>
+      <c r="F694" t="inlineStr"/>
+      <c r="G694" t="inlineStr"/>
+      <c r="H694" t="inlineStr"/>
+      <c r="I694" t="n">
+        <v>0.036125943</v>
+      </c>
+      <c r="J694" t="inlineStr"/>
+      <c r="K694" t="n">
+        <v>1319.489731764099</v>
+      </c>
+      <c r="L694" t="inlineStr"/>
+      <c r="M694" t="inlineStr"/>
+      <c r="N694" t="inlineStr"/>
+      <c r="O694" t="n">
+        <v>418.4075333568</v>
+      </c>
+      <c r="P694" t="inlineStr"/>
+      <c r="Q694" t="n">
+        <v>8.327999999999999e-07</v>
+      </c>
+      <c r="R694" t="inlineStr"/>
+      <c r="S694" t="inlineStr"/>
+      <c r="T694" t="inlineStr"/>
+      <c r="U694" t="inlineStr"/>
+      <c r="V694" t="inlineStr"/>
+      <c r="W694" t="inlineStr"/>
+      <c r="X694" t="inlineStr"/>
+      <c r="Y694" t="inlineStr"/>
+      <c r="Z694" t="inlineStr"/>
+      <c r="AA694" t="n">
+        <v>0.021651732531</v>
+      </c>
+      <c r="AB694" t="inlineStr"/>
+      <c r="AC694" t="n">
+        <v>19.5824553391816</v>
+      </c>
+      <c r="AD694" t="n">
+        <v>59.8246</v>
+      </c>
+      <c r="AE694" t="n">
+        <v>1817.968785746911</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B695" t="n">
+        <v>0.5544140255000001</v>
+      </c>
+      <c r="C695" t="n">
+        <v>0.08612987100000001</v>
+      </c>
+      <c r="D695" t="inlineStr"/>
+      <c r="E695" t="inlineStr"/>
+      <c r="F695" t="inlineStr"/>
+      <c r="G695" t="inlineStr"/>
+      <c r="H695" t="inlineStr"/>
+      <c r="I695" t="n">
+        <v>0.038332581</v>
+      </c>
+      <c r="J695" t="inlineStr"/>
+      <c r="K695" t="n">
+        <v>1315.793682095292</v>
+      </c>
+      <c r="L695" t="inlineStr"/>
+      <c r="M695" t="inlineStr"/>
+      <c r="N695" t="inlineStr"/>
+      <c r="O695" t="n">
+        <v>434.3188754112</v>
+      </c>
+      <c r="P695" t="inlineStr"/>
+      <c r="Q695" t="n">
+        <v>9e-07</v>
+      </c>
+      <c r="R695" t="inlineStr"/>
+      <c r="S695" t="inlineStr"/>
+      <c r="T695" t="inlineStr"/>
+      <c r="U695" t="inlineStr"/>
+      <c r="V695" t="inlineStr"/>
+      <c r="W695" t="inlineStr"/>
+      <c r="X695" t="inlineStr"/>
+      <c r="Y695" t="inlineStr"/>
+      <c r="Z695" t="inlineStr"/>
+      <c r="AA695" t="n">
+        <v>0.021647400885</v>
+      </c>
+      <c r="AB695" t="inlineStr"/>
+      <c r="AC695" t="n">
+        <v>20.2532149892392</v>
+      </c>
+      <c r="AD695" t="n">
+        <v>62.2244</v>
+      </c>
+      <c r="AE695" t="n">
+        <v>1833.290697274116</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE695"/>
+  <dimension ref="A1:AE701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54126,6 +54126,336 @@
         <v>1833.290697274116</v>
       </c>
     </row>
+    <row r="696">
+      <c r="A696" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B696" t="n">
+        <v>0.5522800475</v>
+      </c>
+      <c r="C696" t="n">
+        <v>0.084420694</v>
+      </c>
+      <c r="D696" t="inlineStr"/>
+      <c r="E696" t="inlineStr"/>
+      <c r="F696" t="inlineStr"/>
+      <c r="G696" t="inlineStr"/>
+      <c r="H696" t="inlineStr"/>
+      <c r="I696" t="n">
+        <v>0.037096332</v>
+      </c>
+      <c r="J696" t="inlineStr"/>
+      <c r="K696" t="n">
+        <v>1329.345864214251</v>
+      </c>
+      <c r="L696" t="inlineStr"/>
+      <c r="M696" t="inlineStr"/>
+      <c r="N696" t="inlineStr"/>
+      <c r="O696" t="n">
+        <v>433.6405944</v>
+      </c>
+      <c r="P696" t="inlineStr"/>
+      <c r="Q696" t="n">
+        <v>8.543999999999999e-07</v>
+      </c>
+      <c r="R696" t="inlineStr"/>
+      <c r="S696" t="inlineStr"/>
+      <c r="T696" t="inlineStr"/>
+      <c r="U696" t="inlineStr"/>
+      <c r="V696" t="inlineStr"/>
+      <c r="W696" t="inlineStr"/>
+      <c r="X696" t="inlineStr"/>
+      <c r="Y696" t="inlineStr"/>
+      <c r="Z696" t="inlineStr"/>
+      <c r="AA696" t="n">
+        <v>0.021645235062</v>
+      </c>
+      <c r="AB696" t="inlineStr"/>
+      <c r="AC696" t="n">
+        <v>19.6010875516832</v>
+      </c>
+      <c r="AD696" t="n">
+        <v>61.94039999999999</v>
+      </c>
+      <c r="AE696" t="n">
+        <v>1845.223389328896</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B697" t="n">
+        <v>0.5573344255</v>
+      </c>
+      <c r="C697" t="n">
+        <v>0.0857841825</v>
+      </c>
+      <c r="D697" t="inlineStr"/>
+      <c r="E697" t="inlineStr"/>
+      <c r="F697" t="inlineStr"/>
+      <c r="G697" t="inlineStr"/>
+      <c r="H697" t="inlineStr"/>
+      <c r="I697" t="n">
+        <v>0.03761919</v>
+      </c>
+      <c r="J697" t="inlineStr"/>
+      <c r="K697" t="n">
+        <v>1343.719390704056</v>
+      </c>
+      <c r="L697" t="inlineStr"/>
+      <c r="M697" t="inlineStr"/>
+      <c r="N697" t="inlineStr"/>
+      <c r="O697" t="n">
+        <v>439.8864320448</v>
+      </c>
+      <c r="P697" t="inlineStr"/>
+      <c r="Q697" t="n">
+        <v>8.927999999999999e-07</v>
+      </c>
+      <c r="R697" t="inlineStr"/>
+      <c r="S697" t="inlineStr"/>
+      <c r="T697" t="inlineStr"/>
+      <c r="U697" t="inlineStr"/>
+      <c r="V697" t="inlineStr"/>
+      <c r="W697" t="inlineStr"/>
+      <c r="X697" t="inlineStr"/>
+      <c r="Y697" t="inlineStr"/>
+      <c r="Z697" t="inlineStr"/>
+      <c r="AA697" t="n">
+        <v>0.0216508662018</v>
+      </c>
+      <c r="AB697" t="inlineStr"/>
+      <c r="AC697" t="n">
+        <v>19.8992029517088</v>
+      </c>
+      <c r="AD697" t="n">
+        <v>62.5936</v>
+      </c>
+      <c r="AE697" t="n">
+        <v>1866.801015257566</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B698" t="n">
+        <v>0.5598994604999999</v>
+      </c>
+      <c r="C698" t="n">
+        <v>0.08535597950000001</v>
+      </c>
+      <c r="D698" t="inlineStr"/>
+      <c r="E698" t="inlineStr"/>
+      <c r="F698" t="inlineStr"/>
+      <c r="G698" t="inlineStr"/>
+      <c r="H698" t="inlineStr"/>
+      <c r="I698" t="n">
+        <v>0.039458055</v>
+      </c>
+      <c r="J698" t="inlineStr"/>
+      <c r="K698" t="n">
+        <v>1342.89804633321</v>
+      </c>
+      <c r="L698" t="inlineStr"/>
+      <c r="M698" t="inlineStr"/>
+      <c r="N698" t="inlineStr"/>
+      <c r="O698" t="n">
+        <v>449.1986650944</v>
+      </c>
+      <c r="P698" t="inlineStr"/>
+      <c r="Q698" t="n">
+        <v>9.552e-07</v>
+      </c>
+      <c r="R698" t="inlineStr"/>
+      <c r="S698" t="inlineStr"/>
+      <c r="T698" t="inlineStr"/>
+      <c r="U698" t="inlineStr"/>
+      <c r="V698" t="inlineStr"/>
+      <c r="W698" t="inlineStr"/>
+      <c r="X698" t="inlineStr"/>
+      <c r="Y698" t="inlineStr"/>
+      <c r="Z698" t="inlineStr"/>
+      <c r="AA698" t="n">
+        <v>0.0216515159487</v>
+      </c>
+      <c r="AB698" t="inlineStr"/>
+      <c r="AC698" t="n">
+        <v>21.0730323393096</v>
+      </c>
+      <c r="AD698" t="n">
+        <v>64.5958</v>
+      </c>
+      <c r="AE698" t="n">
+        <v>1878.471909733068</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B699" t="n">
+        <v>0.5741864</v>
+      </c>
+      <c r="C699" t="n">
+        <v>0.08793065000000001</v>
+      </c>
+      <c r="D699" t="inlineStr"/>
+      <c r="E699" t="inlineStr"/>
+      <c r="F699" t="inlineStr"/>
+      <c r="G699" t="inlineStr"/>
+      <c r="H699" t="inlineStr"/>
+      <c r="I699" t="n">
+        <v>0.039329556</v>
+      </c>
+      <c r="J699" t="inlineStr"/>
+      <c r="K699" t="n">
+        <v>1346.183423816594</v>
+      </c>
+      <c r="L699" t="inlineStr"/>
+      <c r="M699" t="inlineStr"/>
+      <c r="N699" t="inlineStr"/>
+      <c r="O699" t="n">
+        <v>454.3917540864</v>
+      </c>
+      <c r="P699" t="inlineStr"/>
+      <c r="Q699" t="n">
+        <v>9.480000000000001e-07</v>
+      </c>
+      <c r="R699" t="inlineStr"/>
+      <c r="S699" t="inlineStr"/>
+      <c r="T699" t="inlineStr"/>
+      <c r="U699" t="inlineStr"/>
+      <c r="V699" t="inlineStr"/>
+      <c r="W699" t="inlineStr"/>
+      <c r="X699" t="inlineStr"/>
+      <c r="Y699" t="inlineStr"/>
+      <c r="Z699" t="inlineStr"/>
+      <c r="AA699" t="n">
+        <v>0.0216487003788</v>
+      </c>
+      <c r="AB699" t="inlineStr"/>
+      <c r="AC699" t="n">
+        <v>20.9239746392968</v>
+      </c>
+      <c r="AD699" t="n">
+        <v>64.38279999999999</v>
+      </c>
+      <c r="AE699" t="n">
+        <v>1886.60504879667</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="2" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B700" t="n">
+        <v>0.5639036119999999</v>
+      </c>
+      <c r="C700" t="n">
+        <v>0.08543413200000001</v>
+      </c>
+      <c r="D700" t="inlineStr"/>
+      <c r="E700" t="inlineStr"/>
+      <c r="F700" t="inlineStr"/>
+      <c r="G700" t="inlineStr"/>
+      <c r="H700" t="inlineStr"/>
+      <c r="I700" t="n">
+        <v>0.038177496</v>
+      </c>
+      <c r="J700" t="inlineStr"/>
+      <c r="K700" t="n">
+        <v>1353.164850968785</v>
+      </c>
+      <c r="L700" t="inlineStr"/>
+      <c r="M700" t="inlineStr"/>
+      <c r="N700" t="inlineStr"/>
+      <c r="O700" t="n">
+        <v>445.051259328</v>
+      </c>
+      <c r="P700" t="inlineStr"/>
+      <c r="Q700" t="n">
+        <v>9.047999999999999e-07</v>
+      </c>
+      <c r="R700" t="inlineStr"/>
+      <c r="S700" t="inlineStr"/>
+      <c r="T700" t="inlineStr"/>
+      <c r="U700" t="inlineStr"/>
+      <c r="V700" t="inlineStr"/>
+      <c r="W700" t="inlineStr"/>
+      <c r="X700" t="inlineStr"/>
+      <c r="Y700" t="inlineStr"/>
+      <c r="Z700" t="inlineStr"/>
+      <c r="AA700" t="n">
+        <v>0.021647400885</v>
+      </c>
+      <c r="AB700" t="inlineStr"/>
+      <c r="AC700" t="n">
+        <v>20.0855250767248</v>
+      </c>
+      <c r="AD700" t="n">
+        <v>62.977</v>
+      </c>
+      <c r="AE700" t="n">
+        <v>1881.987798919195</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="2" t="n">
+        <v>46131</v>
+      </c>
+      <c r="B701" t="n">
+        <v>0.5498233355</v>
+      </c>
+      <c r="C701" t="n">
+        <v>0.08226986450000001</v>
+      </c>
+      <c r="D701" t="inlineStr"/>
+      <c r="E701" t="inlineStr"/>
+      <c r="F701" t="inlineStr"/>
+      <c r="G701" t="inlineStr"/>
+      <c r="H701" t="inlineStr"/>
+      <c r="I701" t="n">
+        <v>0.036985557</v>
+      </c>
+      <c r="J701" t="inlineStr"/>
+      <c r="K701" t="n">
+        <v>1351.522162227093</v>
+      </c>
+      <c r="L701" t="inlineStr"/>
+      <c r="M701" t="inlineStr"/>
+      <c r="N701" t="inlineStr"/>
+      <c r="O701" t="n">
+        <v>435.2727080831999</v>
+      </c>
+      <c r="P701" t="inlineStr"/>
+      <c r="Q701" t="n">
+        <v>8.760000000000001e-07</v>
+      </c>
+      <c r="R701" t="inlineStr"/>
+      <c r="S701" t="inlineStr"/>
+      <c r="T701" t="inlineStr"/>
+      <c r="U701" t="inlineStr"/>
+      <c r="V701" t="inlineStr"/>
+      <c r="W701" t="inlineStr"/>
+      <c r="X701" t="inlineStr"/>
+      <c r="Y701" t="inlineStr"/>
+      <c r="Z701" t="inlineStr"/>
+      <c r="AA701" t="n">
+        <v>0.0216471843027</v>
+      </c>
+      <c r="AB701" t="inlineStr"/>
+      <c r="AC701" t="n">
+        <v>19.0421211766352</v>
+      </c>
+      <c r="AD701" t="n">
+        <v>61.7842</v>
+      </c>
+      <c r="AE701" t="n">
+        <v>1868.311918304231</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE701"/>
+  <dimension ref="A1:AE702"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54456,6 +54456,61 @@
         <v>1868.311918304231</v>
       </c>
     </row>
+    <row r="702">
+      <c r="A702" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B702" t="n">
+        <v>0.5650152265</v>
+      </c>
+      <c r="C702" t="n">
+        <v>0.0841084475</v>
+      </c>
+      <c r="D702" t="inlineStr"/>
+      <c r="E702" t="inlineStr"/>
+      <c r="F702" t="inlineStr"/>
+      <c r="G702" t="inlineStr"/>
+      <c r="H702" t="inlineStr"/>
+      <c r="I702" t="n">
+        <v>0.037787568</v>
+      </c>
+      <c r="J702" t="inlineStr"/>
+      <c r="K702" t="n">
+        <v>1349.879473485401</v>
+      </c>
+      <c r="L702" t="inlineStr"/>
+      <c r="M702" t="inlineStr"/>
+      <c r="N702" t="inlineStr"/>
+      <c r="O702" t="n">
+        <v>444.5990719872</v>
+      </c>
+      <c r="P702" t="inlineStr"/>
+      <c r="Q702" t="n">
+        <v>9.023999999999999e-07</v>
+      </c>
+      <c r="R702" t="inlineStr"/>
+      <c r="S702" t="inlineStr"/>
+      <c r="T702" t="inlineStr"/>
+      <c r="U702" t="inlineStr"/>
+      <c r="V702" t="inlineStr"/>
+      <c r="W702" t="inlineStr"/>
+      <c r="X702" t="inlineStr"/>
+      <c r="Y702" t="inlineStr"/>
+      <c r="Z702" t="inlineStr"/>
+      <c r="AA702" t="n">
+        <v>0.0216465345558</v>
+      </c>
+      <c r="AB702" t="inlineStr"/>
+      <c r="AC702" t="n">
+        <v>19.1166500266416</v>
+      </c>
+      <c r="AD702" t="n">
+        <v>62.9912</v>
+      </c>
+      <c r="AE702" t="n">
+        <v>1877.294954178198</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE702"/>
+  <dimension ref="A1:AE703"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54511,6 +54511,61 @@
         <v>1877.294954178198</v>
       </c>
     </row>
+    <row r="703">
+      <c r="A703" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B703" t="n">
+        <v>0.5687043174999999</v>
+      </c>
+      <c r="C703" t="n">
+        <v>0.08459153900000001</v>
+      </c>
+      <c r="D703" t="inlineStr"/>
+      <c r="E703" t="inlineStr"/>
+      <c r="F703" t="inlineStr"/>
+      <c r="G703" t="inlineStr"/>
+      <c r="H703" t="inlineStr"/>
+      <c r="I703" t="n">
+        <v>0.038119893</v>
+      </c>
+      <c r="J703" t="inlineStr"/>
+      <c r="K703" t="n">
+        <v>1367.949049644013</v>
+      </c>
+      <c r="L703" t="inlineStr"/>
+      <c r="M703" t="inlineStr"/>
+      <c r="N703" t="inlineStr"/>
+      <c r="O703" t="n">
+        <v>446.3371670784</v>
+      </c>
+      <c r="P703" t="inlineStr"/>
+      <c r="Q703" t="n">
+        <v>9.144e-07</v>
+      </c>
+      <c r="R703" t="inlineStr"/>
+      <c r="S703" t="inlineStr"/>
+      <c r="T703" t="inlineStr"/>
+      <c r="U703" t="inlineStr"/>
+      <c r="V703" t="inlineStr"/>
+      <c r="W703" t="inlineStr"/>
+      <c r="X703" t="inlineStr"/>
+      <c r="Y703" t="inlineStr"/>
+      <c r="Z703" t="inlineStr"/>
+      <c r="AA703" t="n">
+        <v>0.0216489169611</v>
+      </c>
+      <c r="AB703" t="inlineStr"/>
+      <c r="AC703" t="n">
+        <v>19.1166500266416</v>
+      </c>
+      <c r="AD703" t="n">
+        <v>63.687</v>
+      </c>
+      <c r="AE703" t="n">
+        <v>1897.802932329916</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE703"/>
+  <dimension ref="A1:AE709"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54566,6 +54566,336 @@
         <v>1897.802932329916</v>
       </c>
     </row>
+    <row r="704">
+      <c r="A704" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B704" t="n">
+        <v>0.5824278134999999</v>
+      </c>
+      <c r="C704" t="n">
+        <v>0.08629744450000001</v>
+      </c>
+      <c r="D704" t="inlineStr"/>
+      <c r="E704" t="inlineStr"/>
+      <c r="F704" t="inlineStr"/>
+      <c r="G704" t="inlineStr"/>
+      <c r="H704" t="inlineStr"/>
+      <c r="I704" t="n">
+        <v>0.038492097</v>
+      </c>
+      <c r="J704" t="inlineStr"/>
+      <c r="K704" t="n">
+        <v>1353.164850968785</v>
+      </c>
+      <c r="L704" t="inlineStr"/>
+      <c r="M704" t="inlineStr"/>
+      <c r="N704" t="inlineStr"/>
+      <c r="O704" t="n">
+        <v>450.3997877184</v>
+      </c>
+      <c r="P704" t="inlineStr"/>
+      <c r="Q704" t="n">
+        <v>9.096e-07</v>
+      </c>
+      <c r="R704" t="inlineStr"/>
+      <c r="S704" t="inlineStr"/>
+      <c r="T704" t="inlineStr"/>
+      <c r="U704" t="inlineStr"/>
+      <c r="V704" t="inlineStr"/>
+      <c r="W704" t="inlineStr"/>
+      <c r="X704" t="inlineStr"/>
+      <c r="Y704" t="inlineStr"/>
+      <c r="Z704" t="inlineStr"/>
+      <c r="AA704" t="n">
+        <v>0.0216471843027</v>
+      </c>
+      <c r="AB704" t="inlineStr"/>
+      <c r="AC704" t="n">
+        <v>19.2098110891496</v>
+      </c>
+      <c r="AD704" t="n">
+        <v>65.3626</v>
+      </c>
+      <c r="AE704" t="n">
+        <v>1888.865915225237</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="2" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B705" t="n">
+        <v>0.583018226</v>
+      </c>
+      <c r="C705" t="n">
+        <v>0.08470495100000001</v>
+      </c>
+      <c r="D705" t="inlineStr"/>
+      <c r="E705" t="inlineStr"/>
+      <c r="F705" t="inlineStr"/>
+      <c r="G705" t="inlineStr"/>
+      <c r="H705" t="inlineStr"/>
+      <c r="I705" t="n">
+        <v>0.038159772</v>
+      </c>
+      <c r="J705" t="inlineStr"/>
+      <c r="K705" t="n">
+        <v>1350.290145670824</v>
+      </c>
+      <c r="L705" t="inlineStr"/>
+      <c r="M705" t="inlineStr"/>
+      <c r="N705" t="inlineStr"/>
+      <c r="O705" t="n">
+        <v>451.1557884288</v>
+      </c>
+      <c r="P705" t="inlineStr"/>
+      <c r="Q705" t="n">
+        <v>9.168e-07</v>
+      </c>
+      <c r="R705" t="inlineStr"/>
+      <c r="S705" t="inlineStr"/>
+      <c r="T705" t="inlineStr"/>
+      <c r="U705" t="inlineStr"/>
+      <c r="V705" t="inlineStr"/>
+      <c r="W705" t="inlineStr"/>
+      <c r="X705" t="inlineStr"/>
+      <c r="Y705" t="inlineStr"/>
+      <c r="Z705" t="inlineStr"/>
+      <c r="AA705" t="n">
+        <v>0.0216482672142</v>
+      </c>
+      <c r="AB705" t="inlineStr"/>
+      <c r="AC705" t="n">
+        <v>19.2657077266544</v>
+      </c>
+      <c r="AD705" t="n">
+        <v>65.4336</v>
+      </c>
+      <c r="AE705" t="n">
+        <v>1886.872773959293</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="2" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B706" t="n">
+        <v>0.5769066185</v>
+      </c>
+      <c r="C706" t="n">
+        <v>0.08414988649999999</v>
+      </c>
+      <c r="D706" t="inlineStr"/>
+      <c r="E706" t="inlineStr"/>
+      <c r="F706" t="inlineStr"/>
+      <c r="G706" t="inlineStr"/>
+      <c r="H706" t="inlineStr"/>
+      <c r="I706" t="n">
+        <v>0.038186358</v>
+      </c>
+      <c r="J706" t="inlineStr"/>
+      <c r="K706" t="n">
+        <v>1328.113847657982</v>
+      </c>
+      <c r="L706" t="inlineStr"/>
+      <c r="M706" t="inlineStr"/>
+      <c r="N706" t="inlineStr"/>
+      <c r="O706" t="n">
+        <v>449.5095438912</v>
+      </c>
+      <c r="P706" t="inlineStr"/>
+      <c r="Q706" t="n">
+        <v>9.288e-07</v>
+      </c>
+      <c r="R706" t="inlineStr"/>
+      <c r="S706" t="inlineStr"/>
+      <c r="T706" t="inlineStr"/>
+      <c r="U706" t="inlineStr"/>
+      <c r="V706" t="inlineStr"/>
+      <c r="W706" t="inlineStr"/>
+      <c r="X706" t="inlineStr"/>
+      <c r="Y706" t="inlineStr"/>
+      <c r="Z706" t="inlineStr"/>
+      <c r="AA706" t="n">
+        <v>0.0216484837965</v>
+      </c>
+      <c r="AB706" t="inlineStr"/>
+      <c r="AC706" t="n">
+        <v>19.2284433016512</v>
+      </c>
+      <c r="AD706" t="n">
+        <v>64.78039999999999</v>
+      </c>
+      <c r="AE706" t="n">
+        <v>1862.35312712643</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="2" t="n">
+        <v>46137</v>
+      </c>
+      <c r="B707" t="n">
+        <v>0.57830625</v>
+      </c>
+      <c r="C707" t="n">
+        <v>0.08431382500000001</v>
+      </c>
+      <c r="D707" t="inlineStr"/>
+      <c r="E707" t="inlineStr"/>
+      <c r="F707" t="inlineStr"/>
+      <c r="G707" t="inlineStr"/>
+      <c r="H707" t="inlineStr"/>
+      <c r="I707" t="n">
+        <v>0.038186358</v>
+      </c>
+      <c r="J707" t="inlineStr"/>
+      <c r="K707" t="n">
+        <v>1330.167208585097</v>
+      </c>
+      <c r="L707" t="inlineStr"/>
+      <c r="M707" t="inlineStr"/>
+      <c r="N707" t="inlineStr"/>
+      <c r="O707" t="n">
+        <v>444.0832958015999</v>
+      </c>
+      <c r="P707" t="inlineStr"/>
+      <c r="Q707" t="n">
+        <v>9.240000000000001e-07</v>
+      </c>
+      <c r="R707" t="inlineStr"/>
+      <c r="S707" t="inlineStr"/>
+      <c r="T707" t="inlineStr"/>
+      <c r="U707" t="inlineStr"/>
+      <c r="V707" t="inlineStr"/>
+      <c r="W707" t="inlineStr"/>
+      <c r="X707" t="inlineStr"/>
+      <c r="Y707" t="inlineStr"/>
+      <c r="Z707" t="inlineStr"/>
+      <c r="AA707" t="n">
+        <v>0.0216493501257</v>
+      </c>
+      <c r="AB707" t="inlineStr"/>
+      <c r="AC707" t="n">
+        <v>18.9862245391304</v>
+      </c>
+      <c r="AD707" t="n">
+        <v>64.32599999999999</v>
+      </c>
+      <c r="AE707" t="n">
+        <v>1858.285185632953</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B708" t="n">
+        <v>0.5859987475</v>
+      </c>
+      <c r="C708" t="n">
+        <v>0.086129144</v>
+      </c>
+      <c r="D708" t="inlineStr"/>
+      <c r="E708" t="inlineStr"/>
+      <c r="F708" t="inlineStr"/>
+      <c r="G708" t="inlineStr"/>
+      <c r="H708" t="inlineStr"/>
+      <c r="I708" t="n">
+        <v>0.038518683</v>
+      </c>
+      <c r="J708" t="inlineStr"/>
+      <c r="K708" t="n">
+        <v>1328.113847657982</v>
+      </c>
+      <c r="L708" t="inlineStr"/>
+      <c r="M708" t="inlineStr"/>
+      <c r="N708" t="inlineStr"/>
+      <c r="O708" t="n">
+        <v>449.1915996672</v>
+      </c>
+      <c r="P708" t="inlineStr"/>
+      <c r="Q708" t="n">
+        <v>9.359999999999999e-07</v>
+      </c>
+      <c r="R708" t="inlineStr"/>
+      <c r="S708" t="inlineStr"/>
+      <c r="T708" t="inlineStr"/>
+      <c r="U708" t="inlineStr"/>
+      <c r="V708" t="inlineStr"/>
+      <c r="W708" t="inlineStr"/>
+      <c r="X708" t="inlineStr"/>
+      <c r="Y708" t="inlineStr"/>
+      <c r="Z708" t="inlineStr"/>
+      <c r="AA708" t="n">
+        <v>0.0216502164549</v>
+      </c>
+      <c r="AB708" t="inlineStr"/>
+      <c r="AC708" t="n">
+        <v>19.284339939156</v>
+      </c>
+      <c r="AD708" t="n">
+        <v>64.5958</v>
+      </c>
+      <c r="AE708" t="n">
+        <v>1861.917884991293</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B709" t="n">
+        <v>0.576416334</v>
+      </c>
+      <c r="C709" t="n">
+        <v>0.0837384045</v>
+      </c>
+      <c r="D709" t="inlineStr"/>
+      <c r="E709" t="inlineStr"/>
+      <c r="F709" t="inlineStr"/>
+      <c r="G709" t="inlineStr"/>
+      <c r="H709" t="inlineStr"/>
+      <c r="I709" t="n">
+        <v>0.037583742</v>
+      </c>
+      <c r="J709" t="inlineStr"/>
+      <c r="K709" t="n">
+        <v>1335.916619181019</v>
+      </c>
+      <c r="L709" t="inlineStr"/>
+      <c r="M709" t="inlineStr"/>
+      <c r="N709" t="inlineStr"/>
+      <c r="O709" t="n">
+        <v>442.8821731776</v>
+      </c>
+      <c r="P709" t="inlineStr"/>
+      <c r="Q709" t="n">
+        <v>9.383999999999999e-07</v>
+      </c>
+      <c r="R709" t="inlineStr"/>
+      <c r="S709" t="inlineStr"/>
+      <c r="T709" t="inlineStr"/>
+      <c r="U709" t="inlineStr"/>
+      <c r="V709" t="inlineStr"/>
+      <c r="W709" t="inlineStr"/>
+      <c r="X709" t="inlineStr"/>
+      <c r="Y709" t="inlineStr"/>
+      <c r="Z709" t="inlineStr"/>
+      <c r="AA709" t="n">
+        <v>0.0216564973416</v>
+      </c>
+      <c r="AB709" t="inlineStr"/>
+      <c r="AC709" t="n">
+        <v>19.9923640142168</v>
+      </c>
+      <c r="AD709" t="n">
+        <v>63.87159999999999</v>
+      </c>
+      <c r="AE709" t="n">
+        <v>1863.382152289077</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE709"/>
+  <dimension ref="A1:AE710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54896,6 +54896,61 @@
         <v>1863.382152289077</v>
       </c>
     </row>
+    <row r="710">
+      <c r="A710" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B710" t="n">
+        <v>0.5687536365</v>
+      </c>
+      <c r="C710" t="n">
+        <v>0.083220417</v>
+      </c>
+      <c r="D710" t="inlineStr"/>
+      <c r="E710" t="inlineStr"/>
+      <c r="F710" t="inlineStr"/>
+      <c r="G710" t="inlineStr"/>
+      <c r="H710" t="inlineStr"/>
+      <c r="I710" t="n">
+        <v>0.037246986</v>
+      </c>
+      <c r="J710" t="inlineStr"/>
+      <c r="K710" t="n">
+        <v>1326.47115891629</v>
+      </c>
+      <c r="L710" t="inlineStr"/>
+      <c r="M710" t="inlineStr"/>
+      <c r="N710" t="inlineStr"/>
+      <c r="O710" t="n">
+        <v>441.2712557759999</v>
+      </c>
+      <c r="P710" t="inlineStr"/>
+      <c r="Q710" t="n">
+        <v>9.312e-07</v>
+      </c>
+      <c r="R710" t="inlineStr"/>
+      <c r="S710" t="inlineStr"/>
+      <c r="T710" t="inlineStr"/>
+      <c r="U710" t="inlineStr"/>
+      <c r="V710" t="inlineStr"/>
+      <c r="W710" t="inlineStr"/>
+      <c r="X710" t="inlineStr"/>
+      <c r="Y710" t="inlineStr"/>
+      <c r="Z710" t="inlineStr"/>
+      <c r="AA710" t="n">
+        <v>0.0216580134177</v>
+      </c>
+      <c r="AB710" t="inlineStr"/>
+      <c r="AC710" t="n">
+        <v>19.843306314204</v>
+      </c>
+      <c r="AD710" t="n">
+        <v>64.4254</v>
+      </c>
+      <c r="AE710" t="n">
+        <v>1852.722000990612</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE710"/>
+  <dimension ref="A1:AE712"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54951,6 +54951,116 @@
         <v>1852.722000990612</v>
       </c>
     </row>
+    <row r="711">
+      <c r="A711" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B711" t="n">
+        <v>0.564561</v>
+      </c>
+      <c r="C711" t="n">
+        <v>0.08189291500000001</v>
+      </c>
+      <c r="D711" t="inlineStr"/>
+      <c r="E711" t="inlineStr"/>
+      <c r="F711" t="inlineStr"/>
+      <c r="G711" t="inlineStr"/>
+      <c r="H711" t="inlineStr"/>
+      <c r="I711" t="n">
+        <v>0.036795024</v>
+      </c>
+      <c r="J711" t="inlineStr"/>
+      <c r="K711" t="n">
+        <v>1327.292503287136</v>
+      </c>
+      <c r="L711" t="inlineStr"/>
+      <c r="M711" t="inlineStr"/>
+      <c r="N711" t="inlineStr"/>
+      <c r="O711" t="n">
+        <v>436.2124099008</v>
+      </c>
+      <c r="P711" t="inlineStr"/>
+      <c r="Q711" t="n">
+        <v>9.240000000000001e-07</v>
+      </c>
+      <c r="R711" t="inlineStr"/>
+      <c r="S711" t="inlineStr"/>
+      <c r="T711" t="inlineStr"/>
+      <c r="U711" t="inlineStr"/>
+      <c r="V711" t="inlineStr"/>
+      <c r="W711" t="inlineStr"/>
+      <c r="X711" t="inlineStr"/>
+      <c r="Y711" t="inlineStr"/>
+      <c r="Z711" t="inlineStr"/>
+      <c r="AA711" t="n">
+        <v>0.021662561646</v>
+      </c>
+      <c r="AB711" t="inlineStr"/>
+      <c r="AC711" t="n">
+        <v>19.1539144516448</v>
+      </c>
+      <c r="AD711" t="n">
+        <v>63.54499999999999</v>
+      </c>
+      <c r="AE711" t="n">
+        <v>1846.908740064227</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B712" t="n">
+        <v>0.5687819465</v>
+      </c>
+      <c r="C712" t="n">
+        <v>0.08206048850000001</v>
+      </c>
+      <c r="D712" t="inlineStr"/>
+      <c r="E712" t="inlineStr"/>
+      <c r="F712" t="inlineStr"/>
+      <c r="G712" t="inlineStr"/>
+      <c r="H712" t="inlineStr"/>
+      <c r="I712" t="n">
+        <v>0.036817179</v>
+      </c>
+      <c r="J712" t="inlineStr"/>
+      <c r="K712" t="n">
+        <v>1341.255357591518</v>
+      </c>
+      <c r="L712" t="inlineStr"/>
+      <c r="M712" t="inlineStr"/>
+      <c r="N712" t="inlineStr"/>
+      <c r="O712" t="n">
+        <v>434.7922590336</v>
+      </c>
+      <c r="P712" t="inlineStr"/>
+      <c r="Q712" t="n">
+        <v>9.312e-07</v>
+      </c>
+      <c r="R712" t="inlineStr"/>
+      <c r="S712" t="inlineStr"/>
+      <c r="T712" t="inlineStr"/>
+      <c r="U712" t="inlineStr"/>
+      <c r="V712" t="inlineStr"/>
+      <c r="W712" t="inlineStr"/>
+      <c r="X712" t="inlineStr"/>
+      <c r="Y712" t="inlineStr"/>
+      <c r="Z712" t="inlineStr"/>
+      <c r="AA712" t="n">
+        <v>0.0216610455699</v>
+      </c>
+      <c r="AB712" t="inlineStr"/>
+      <c r="AC712" t="n">
+        <v>18.3154648890728</v>
+      </c>
+      <c r="AD712" t="n">
+        <v>62.60779999999999</v>
+      </c>
+      <c r="AE712" t="n">
+        <v>1857.68020310496</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE712"/>
+  <dimension ref="A1:AG714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -583,6 +583,16 @@
       <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Total</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>DOGEUSDT</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>LTCUSDT</t>
         </is>
       </c>
     </row>
@@ -646,6 +656,8 @@
       <c r="AE2" t="n">
         <v>414.2028191822986</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -707,6 +719,8 @@
       <c r="AE3" t="n">
         <v>440.976657956838</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -768,6 +782,8 @@
       <c r="AE4" t="n">
         <v>482.4115240062466</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -829,6 +845,8 @@
       <c r="AE5" t="n">
         <v>475.1937465567585</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -890,6 +908,8 @@
       <c r="AE6" t="n">
         <v>458.9198783501148</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -951,6 +971,8 @@
       <c r="AE7" t="n">
         <v>924.4148503678907</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1022,6 +1044,8 @@
       <c r="AE8" t="n">
         <v>1398.683796258023</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1103,6 +1127,8 @@
       <c r="AE9" t="n">
         <v>2001.744690249562</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1184,6 +1210,8 @@
       <c r="AE10" t="n">
         <v>2025.291278707344</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1265,6 +1293,8 @@
       <c r="AE11" t="n">
         <v>1978.061693749934</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1346,6 +1376,8 @@
       <c r="AE12" t="n">
         <v>2018.210319210885</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1427,6 +1459,8 @@
       <c r="AE13" t="n">
         <v>2032.327032580222</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1508,6 +1542,8 @@
       <c r="AE14" t="n">
         <v>2083.189494512772</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1589,6 +1625,8 @@
       <c r="AE15" t="n">
         <v>2044.811962882468</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1670,6 +1708,8 @@
       <c r="AE16" t="n">
         <v>2046.539007685213</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1751,6 +1791,8 @@
       <c r="AE17" t="n">
         <v>2124.218449637598</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1832,6 +1874,8 @@
       <c r="AE18" t="n">
         <v>2185.074910599765</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1913,6 +1957,8 @@
       <c r="AE19" t="n">
         <v>2150.712631632542</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1994,6 +2040,8 @@
       <c r="AE20" t="n">
         <v>2053.893645518443</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -2075,6 +2123,8 @@
       <c r="AE21" t="n">
         <v>2002.784202629362</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -2156,6 +2206,8 @@
       <c r="AE22" t="n">
         <v>2037.220086254237</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -2237,6 +2289,8 @@
       <c r="AE23" t="n">
         <v>1995.540188620737</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -2318,6 +2372,8 @@
       <c r="AE24" t="n">
         <v>1895.323153052511</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -2399,6 +2455,8 @@
       <c r="AE25" t="n">
         <v>1959.431378152241</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -2480,6 +2538,8 @@
       <c r="AE26" t="n">
         <v>1866.105980793153</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -2563,6 +2623,8 @@
       <c r="AE27" t="n">
         <v>1844.123938369321</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -2646,6 +2708,8 @@
       <c r="AE28" t="n">
         <v>1881.094680427435</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -2729,6 +2793,8 @@
       <c r="AE29" t="n">
         <v>1947.481403260267</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -2812,6 +2878,8 @@
       <c r="AE30" t="n">
         <v>1863.695979417305</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -2895,6 +2963,8 @@
       <c r="AE31" t="n">
         <v>1783.929569351773</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -2978,6 +3048,8 @@
       <c r="AE32" t="n">
         <v>1774.511031343084</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -3061,6 +3133,8 @@
       <c r="AE33" t="n">
         <v>1747.892242268062</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -3144,6 +3218,8 @@
       <c r="AE34" t="n">
         <v>1748.983233372654</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -3227,6 +3303,8 @@
       <c r="AE35" t="n">
         <v>1769.219080619711</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -3310,6 +3388,8 @@
       <c r="AE36" t="n">
         <v>1707.32295914646</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -3393,6 +3473,8 @@
       <c r="AE37" t="n">
         <v>1676.997401562272</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -3476,6 +3558,8 @@
       <c r="AE38" t="n">
         <v>1748.396925472729</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -3559,6 +3643,8 @@
       <c r="AE39" t="n">
         <v>1727.0491551811</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -3642,6 +3728,8 @@
       <c r="AE40" t="n">
         <v>1789.171040149333</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -3725,6 +3813,8 @@
       <c r="AE41" t="n">
         <v>1724.731448289987</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -3808,6 +3898,8 @@
       <c r="AE42" t="n">
         <v>1719.760020017194</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -3891,6 +3983,8 @@
       <c r="AE43" t="n">
         <v>1768.990049339296</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -3974,6 +4068,8 @@
       <c r="AE44" t="n">
         <v>1756.973307325313</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -4057,6 +4153,8 @@
       <c r="AE45" t="n">
         <v>1755.089859964948</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -4140,6 +4238,8 @@
       <c r="AE46" t="n">
         <v>1643.44898702745</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -4223,6 +4323,8 @@
       <c r="AE47" t="n">
         <v>1516.727386300405</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -4306,6 +4408,8 @@
       <c r="AE48" t="n">
         <v>1523.881757983055</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -4391,6 +4495,8 @@
       <c r="AE49" t="n">
         <v>1615.573126373096</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -4476,6 +4582,8 @@
       <c r="AE50" t="n">
         <v>1563.057926854914</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -4561,6 +4669,8 @@
       <c r="AE51" t="n">
         <v>1598.582504829355</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -4646,6 +4756,8 @@
       <c r="AE52" t="n">
         <v>1635.825870428052</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -4731,6 +4843,8 @@
       <c r="AE53" t="n">
         <v>1662.413210793567</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -4816,6 +4930,8 @@
       <c r="AE54" t="n">
         <v>1658.462329568884</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -4901,6 +5017,8 @@
       <c r="AE55" t="n">
         <v>1696.094620103681</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -4986,6 +5104,8 @@
       <c r="AE56" t="n">
         <v>1736.43209753843</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -5073,6 +5193,8 @@
       <c r="AE57" t="n">
         <v>2047.915363158605</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -5160,6 +5282,8 @@
       <c r="AE58" t="n">
         <v>2208.468451581036</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -5247,6 +5371,8 @@
       <c r="AE59" t="n">
         <v>2188.694973581518</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -5334,6 +5460,8 @@
       <c r="AE60" t="n">
         <v>2148.555618956184</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -5421,6 +5549,8 @@
       <c r="AE61" t="n">
         <v>2166.049618497707</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -5508,6 +5638,8 @@
       <c r="AE62" t="n">
         <v>2217.603099576304</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -5595,6 +5727,8 @@
       <c r="AE63" t="n">
         <v>2243.740276005894</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -5682,6 +5816,8 @@
       <c r="AE64" t="n">
         <v>2296.055487460086</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -5769,6 +5905,8 @@
       <c r="AE65" t="n">
         <v>2202.520933018481</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -5856,6 +5994,8 @@
       <c r="AE66" t="n">
         <v>2147.894872443838</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -5943,6 +6083,8 @@
       <c r="AE67" t="n">
         <v>2123.107528507743</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -6030,6 +6172,8 @@
       <c r="AE68" t="n">
         <v>2106.691437310398</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -6117,6 +6261,8 @@
       <c r="AE69" t="n">
         <v>2178.200606951446</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -6204,6 +6350,8 @@
       <c r="AE70" t="n">
         <v>2214.265767905552</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -6291,6 +6439,8 @@
       <c r="AE71" t="n">
         <v>2205.220285868259</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -6378,6 +6528,8 @@
       <c r="AE72" t="n">
         <v>2179.507170052449</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -6465,6 +6617,8 @@
       <c r="AE73" t="n">
         <v>2160.633108506514</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -6552,6 +6706,8 @@
       <c r="AE74" t="n">
         <v>2100.894883890049</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -6639,6 +6795,8 @@
       <c r="AE75" t="n">
         <v>2106.60682668133</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -6726,6 +6884,8 @@
       <c r="AE76" t="n">
         <v>1947.660429315914</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -6813,6 +6973,8 @@
       <c r="AE77" t="n">
         <v>1864.557470712303</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -6900,6 +7062,8 @@
       <c r="AE78" t="n">
         <v>1773.854515639015</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -6987,6 +7151,8 @@
       <c r="AE79" t="n">
         <v>1638.700429052418</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -7074,6 +7240,8 @@
       <c r="AE80" t="n">
         <v>1728.311347301672</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -7161,6 +7329,8 @@
       <c r="AE81" t="n">
         <v>1678.161891512216</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -7248,6 +7418,8 @@
       <c r="AE82" t="n">
         <v>1884.338580626695</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -7335,6 +7507,8 @@
       <c r="AE83" t="n">
         <v>1846.134847903824</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -7422,6 +7596,8 @@
       <c r="AE84" t="n">
         <v>1841.035843902293</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -7509,6 +7685,8 @@
       <c r="AE85" t="n">
         <v>1788.254192413208</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -7596,6 +7774,8 @@
       <c r="AE86" t="n">
         <v>1819.967678508065</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -7683,6 +7863,8 @@
       <c r="AE87" t="n">
         <v>1849.931592212988</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -7770,6 +7952,8 @@
       <c r="AE88" t="n">
         <v>1804.322382743667</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -7857,6 +8041,8 @@
       <c r="AE89" t="n">
         <v>1757.263476931514</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -7944,6 +8130,8 @@
       <c r="AE90" t="n">
         <v>1758.29569435307</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
@@ -8031,6 +8219,8 @@
       <c r="AE91" t="n">
         <v>1814.077851075459</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -8118,6 +8308,8 @@
       <c r="AE92" t="n">
         <v>1799.425152668883</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
@@ -8205,6 +8397,8 @@
       <c r="AE93" t="n">
         <v>1811.69593184484</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -8292,6 +8486,8 @@
       <c r="AE94" t="n">
         <v>1782.967894516827</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
@@ -8379,6 +8575,8 @@
       <c r="AE95" t="n">
         <v>1829.669631904936</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -8466,6 +8664,8 @@
       <c r="AE96" t="n">
         <v>1839.65671112973</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
@@ -8553,6 +8753,8 @@
       <c r="AE97" t="n">
         <v>1966.666085285657</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -8640,6 +8842,8 @@
       <c r="AE98" t="n">
         <v>1978.92809330597</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -8727,6 +8931,8 @@
       <c r="AE99" t="n">
         <v>1954.423936384552</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -8814,6 +9020,8 @@
       <c r="AE100" t="n">
         <v>1890.679191920299</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -8901,6 +9109,8 @@
       <c r="AE101" t="n">
         <v>1793.88565582832</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -8988,6 +9198,8 @@
       <c r="AE102" t="n">
         <v>1782.054677750944</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
@@ -9075,6 +9287,8 @@
       <c r="AE103" t="n">
         <v>1788.549230577692</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -9162,6 +9376,8 @@
       <c r="AE104" t="n">
         <v>1787.505122272422</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
@@ -9249,6 +9465,8 @@
       <c r="AE105" t="n">
         <v>1765.332854031751</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -9336,6 +9554,8 @@
       <c r="AE106" t="n">
         <v>1708.36268931473</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
@@ -9423,6 +9643,8 @@
       <c r="AE107" t="n">
         <v>1791.782200077807</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
+      <c r="AG107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -9510,6 +9732,8 @@
       <c r="AE108" t="n">
         <v>1728.362009296126</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
+      <c r="AG108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
@@ -9597,6 +9821,8 @@
       <c r="AE109" t="n">
         <v>1758.054650898895</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
+      <c r="AG109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -9684,6 +9910,8 @@
       <c r="AE110" t="n">
         <v>1704.312100401506</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
@@ -9771,6 +9999,8 @@
       <c r="AE111" t="n">
         <v>1659.614114406377</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
+      <c r="AG111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -9858,6 +10088,8 @@
       <c r="AE112" t="n">
         <v>1671.106062509911</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
@@ -9945,6 +10177,8 @@
       <c r="AE113" t="n">
         <v>1693.928595075216</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -10032,6 +10266,8 @@
       <c r="AE114" t="n">
         <v>1772.7199894362</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
@@ -10119,6 +10355,8 @@
       <c r="AE115" t="n">
         <v>1804.089697725326</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -10206,6 +10444,8 @@
       <c r="AE116" t="n">
         <v>1791.893198358887</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
+      <c r="AG116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
@@ -10293,6 +10533,8 @@
       <c r="AE117" t="n">
         <v>1827.717367101255</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
+      <c r="AG117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -10380,6 +10622,8 @@
       <c r="AE118" t="n">
         <v>1865.580878471853</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
@@ -10467,6 +10711,8 @@
       <c r="AE119" t="n">
         <v>1839.399276753622</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -10554,6 +10800,8 @@
       <c r="AE120" t="n">
         <v>1798.636209273403</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
+      <c r="AG120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
@@ -10641,6 +10889,8 @@
       <c r="AE121" t="n">
         <v>1779.332509492657</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
+      <c r="AG121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
@@ -10728,6 +10978,8 @@
       <c r="AE122" t="n">
         <v>1814.257735874993</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
+      <c r="AG122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
@@ -10815,6 +11067,8 @@
       <c r="AE123" t="n">
         <v>1867.044037449003</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
+      <c r="AG123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
@@ -10902,6 +11156,8 @@
       <c r="AE124" t="n">
         <v>1903.88761876635</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
@@ -10989,6 +11245,8 @@
       <c r="AE125" t="n">
         <v>1932.033767786053</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -11076,6 +11334,8 @@
       <c r="AE126" t="n">
         <v>1951.108540692605</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
+      <c r="AG126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
@@ -11163,6 +11423,8 @@
       <c r="AE127" t="n">
         <v>1924.603525782934</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
+      <c r="AG127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
@@ -11250,6 +11512,8 @@
       <c r="AE128" t="n">
         <v>1959.112394769655</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
+      <c r="AG128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
@@ -11337,6 +11601,8 @@
       <c r="AE129" t="n">
         <v>1982.615733601117</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
+      <c r="AG129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
@@ -11424,6 +11690,8 @@
       <c r="AE130" t="n">
         <v>1954.489288395226</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
+      <c r="AG130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
@@ -11511,6 +11779,8 @@
       <c r="AE131" t="n">
         <v>2040.188505816031</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
+      <c r="AG131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
@@ -11598,6 +11868,8 @@
       <c r="AE132" t="n">
         <v>2066.172974482463</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
+      <c r="AG132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
@@ -11685,6 +11957,8 @@
       <c r="AE133" t="n">
         <v>2052.263681986443</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
+      <c r="AG133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
@@ -11772,6 +12046,8 @@
       <c r="AE134" t="n">
         <v>2042.780054462572</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
+      <c r="AG134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
@@ -11859,6 +12135,8 @@
       <c r="AE135" t="n">
         <v>1974.825605745772</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
+      <c r="AG135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
@@ -11946,6 +12224,8 @@
       <c r="AE136" t="n">
         <v>1909.659985546733</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
+      <c r="AG136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
@@ -12033,6 +12313,8 @@
       <c r="AE137" t="n">
         <v>1903.560005579571</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
+      <c r="AG137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
@@ -12120,6 +12402,8 @@
       <c r="AE138" t="n">
         <v>1897.949166887349</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
+      <c r="AG138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
@@ -12207,6 +12491,8 @@
       <c r="AE139" t="n">
         <v>1974.997598918299</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
+      <c r="AG139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
@@ -12294,6 +12580,8 @@
       <c r="AE140" t="n">
         <v>1960.078079167852</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
+      <c r="AG140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
@@ -12381,6 +12669,8 @@
       <c r="AE141" t="n">
         <v>1994.453855387927</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
+      <c r="AG141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
@@ -12468,6 +12758,8 @@
       <c r="AE142" t="n">
         <v>1979.320483813515</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
+      <c r="AG142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
@@ -12555,6 +12847,8 @@
       <c r="AE143" t="n">
         <v>1972.640845011033</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
+      <c r="AG143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
@@ -12642,6 +12936,8 @@
       <c r="AE144" t="n">
         <v>1941.205857739591</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
+      <c r="AG144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
@@ -12729,6 +13025,8 @@
       <c r="AE145" t="n">
         <v>1968.895198184082</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
+      <c r="AG145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
@@ -12816,6 +13114,8 @@
       <c r="AE146" t="n">
         <v>2013.864573698098</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
+      <c r="AG146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
@@ -12903,6 +13203,8 @@
       <c r="AE147" t="n">
         <v>2040.154275340067</v>
       </c>
+      <c r="AF147" t="inlineStr"/>
+      <c r="AG147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
@@ -12990,6 +13292,8 @@
       <c r="AE148" t="n">
         <v>2050.913552467494</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
+      <c r="AG148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
@@ -13077,6 +13381,8 @@
       <c r="AE149" t="n">
         <v>2174.488994447901</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
+      <c r="AG149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
@@ -13164,6 +13470,8 @@
       <c r="AE150" t="n">
         <v>2153.372857627961</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
+      <c r="AG150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
@@ -13251,6 +13559,8 @@
       <c r="AE151" t="n">
         <v>2148.396921010869</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
+      <c r="AG151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
@@ -13338,6 +13648,8 @@
       <c r="AE152" t="n">
         <v>2133.486482307773</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
+      <c r="AG152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
@@ -13425,6 +13737,8 @@
       <c r="AE153" t="n">
         <v>2140.436029363304</v>
       </c>
+      <c r="AF153" t="inlineStr"/>
+      <c r="AG153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
@@ -13512,6 +13826,8 @@
       <c r="AE154" t="n">
         <v>2135.864189933008</v>
       </c>
+      <c r="AF154" t="inlineStr"/>
+      <c r="AG154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
@@ -13599,6 +13915,8 @@
       <c r="AE155" t="n">
         <v>2172.883573141069</v>
       </c>
+      <c r="AF155" t="inlineStr"/>
+      <c r="AG155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
@@ -13686,6 +14004,8 @@
       <c r="AE156" t="n">
         <v>2130.506652155042</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
+      <c r="AG156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
@@ -13773,6 +14093,8 @@
       <c r="AE157" t="n">
         <v>2114.885537744549</v>
       </c>
+      <c r="AF157" t="inlineStr"/>
+      <c r="AG157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
@@ -13860,6 +14182,8 @@
       <c r="AE158" t="n">
         <v>2065.916524084465</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
+      <c r="AG158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
@@ -13947,6 +14271,8 @@
       <c r="AE159" t="n">
         <v>2082.712947896893</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
+      <c r="AG159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
@@ -14034,6 +14360,8 @@
       <c r="AE160" t="n">
         <v>1977.5150042717</v>
       </c>
+      <c r="AF160" t="inlineStr"/>
+      <c r="AG160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
@@ -14121,6 +14449,8 @@
       <c r="AE161" t="n">
         <v>1994.517272634397</v>
       </c>
+      <c r="AF161" t="inlineStr"/>
+      <c r="AG161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
@@ -14208,6 +14538,8 @@
       <c r="AE162" t="n">
         <v>2116.519855752097</v>
       </c>
+      <c r="AF162" t="inlineStr"/>
+      <c r="AG162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
@@ -14295,6 +14627,8 @@
       <c r="AE163" t="n">
         <v>2094.706767282208</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
+      <c r="AG163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
@@ -14382,6 +14716,8 @@
       <c r="AE164" t="n">
         <v>2156.912085067692</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
+      <c r="AG164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
@@ -14469,6 +14805,8 @@
       <c r="AE165" t="n">
         <v>2161.720775759261</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
+      <c r="AG165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
@@ -14556,6 +14894,8 @@
       <c r="AE166" t="n">
         <v>2091.875591509711</v>
       </c>
+      <c r="AF166" t="inlineStr"/>
+      <c r="AG166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
@@ -14643,6 +14983,8 @@
       <c r="AE167" t="n">
         <v>2092.090742405129</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
+      <c r="AG167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
@@ -14730,6 +15072,8 @@
       <c r="AE168" t="n">
         <v>2061.130141621632</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
+      <c r="AG168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
@@ -14817,6 +15161,8 @@
       <c r="AE169" t="n">
         <v>2023.309721719824</v>
       </c>
+      <c r="AF169" t="inlineStr"/>
+      <c r="AG169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
@@ -14904,6 +15250,8 @@
       <c r="AE170" t="n">
         <v>1961.892920094047</v>
       </c>
+      <c r="AF170" t="inlineStr"/>
+      <c r="AG170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
@@ -14991,6 +15339,8 @@
       <c r="AE171" t="n">
         <v>2021.376754376715</v>
       </c>
+      <c r="AF171" t="inlineStr"/>
+      <c r="AG171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
@@ -15078,6 +15428,8 @@
       <c r="AE172" t="n">
         <v>2239.082677776151</v>
       </c>
+      <c r="AF172" t="inlineStr"/>
+      <c r="AG172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
@@ -15165,6 +15517,8 @@
       <c r="AE173" t="n">
         <v>2259.045359940857</v>
       </c>
+      <c r="AF173" t="inlineStr"/>
+      <c r="AG173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
@@ -15252,6 +15606,8 @@
       <c r="AE174" t="n">
         <v>2252.575326503827</v>
       </c>
+      <c r="AF174" t="inlineStr"/>
+      <c r="AG174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
@@ -15339,6 +15695,8 @@
       <c r="AE175" t="n">
         <v>2298.126463476916</v>
       </c>
+      <c r="AF175" t="inlineStr"/>
+      <c r="AG175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
@@ -15426,6 +15784,8 @@
       <c r="AE176" t="n">
         <v>2386.992051961975</v>
       </c>
+      <c r="AF176" t="inlineStr"/>
+      <c r="AG176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
@@ -15513,6 +15873,8 @@
       <c r="AE177" t="n">
         <v>2545.469570580479</v>
       </c>
+      <c r="AF177" t="inlineStr"/>
+      <c r="AG177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
@@ -15600,6 +15962,8 @@
       <c r="AE178" t="n">
         <v>2492.349413082396</v>
       </c>
+      <c r="AF178" t="inlineStr"/>
+      <c r="AG178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
@@ -15687,6 +16051,8 @@
       <c r="AE179" t="n">
         <v>2436.594575187656</v>
       </c>
+      <c r="AF179" t="inlineStr"/>
+      <c r="AG179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
@@ -15774,6 +16140,8 @@
       <c r="AE180" t="n">
         <v>2528.280023111007</v>
       </c>
+      <c r="AF180" t="inlineStr"/>
+      <c r="AG180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
@@ -15861,6 +16229,8 @@
       <c r="AE181" t="n">
         <v>2951.683596514364</v>
       </c>
+      <c r="AF181" t="inlineStr"/>
+      <c r="AG181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
@@ -15948,6 +16318,8 @@
       <c r="AE182" t="n">
         <v>3027.894268540831</v>
       </c>
+      <c r="AF182" t="inlineStr"/>
+      <c r="AG182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
@@ -16035,6 +16407,8 @@
       <c r="AE183" t="n">
         <v>3808.569108247888</v>
       </c>
+      <c r="AF183" t="inlineStr"/>
+      <c r="AG183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
@@ -16122,6 +16496,8 @@
       <c r="AE184" t="n">
         <v>3634.965801965276</v>
       </c>
+      <c r="AF184" t="inlineStr"/>
+      <c r="AG184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
@@ -16209,6 +16585,8 @@
       <c r="AE185" t="n">
         <v>3655.196673489481</v>
       </c>
+      <c r="AF185" t="inlineStr"/>
+      <c r="AG185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
@@ -16296,6 +16674,8 @@
       <c r="AE186" t="n">
         <v>3620.975326277958</v>
       </c>
+      <c r="AF186" t="inlineStr"/>
+      <c r="AG186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
@@ -16383,6 +16763,8 @@
       <c r="AE187" t="n">
         <v>3691.856112529579</v>
       </c>
+      <c r="AF187" t="inlineStr"/>
+      <c r="AG187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
@@ -16470,6 +16852,8 @@
       <c r="AE188" t="n">
         <v>3751.394210964366</v>
       </c>
+      <c r="AF188" t="inlineStr"/>
+      <c r="AG188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
@@ -16557,6 +16941,8 @@
       <c r="AE189" t="n">
         <v>3735.810054974407</v>
       </c>
+      <c r="AF189" t="inlineStr"/>
+      <c r="AG189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
@@ -16644,6 +17030,8 @@
       <c r="AE190" t="n">
         <v>3722.744323097606</v>
       </c>
+      <c r="AF190" t="inlineStr"/>
+      <c r="AG190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
@@ -16731,6 +17119,8 @@
       <c r="AE191" t="n">
         <v>3552.503504069224</v>
       </c>
+      <c r="AF191" t="inlineStr"/>
+      <c r="AG191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
@@ -16818,6 +17208,8 @@
       <c r="AE192" t="n">
         <v>3597.730120016881</v>
       </c>
+      <c r="AF192" t="inlineStr"/>
+      <c r="AG192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
@@ -16905,6 +17297,8 @@
       <c r="AE193" t="n">
         <v>3643.664395245971</v>
       </c>
+      <c r="AF193" t="inlineStr"/>
+      <c r="AG193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
@@ -16992,6 +17386,8 @@
       <c r="AE194" t="n">
         <v>3613.060039456482</v>
       </c>
+      <c r="AF194" t="inlineStr"/>
+      <c r="AG194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
@@ -17079,6 +17475,8 @@
       <c r="AE195" t="n">
         <v>3654.842570269303</v>
       </c>
+      <c r="AF195" t="inlineStr"/>
+      <c r="AG195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
@@ -17166,6 +17564,8 @@
       <c r="AE196" t="n">
         <v>3717.320077302724</v>
       </c>
+      <c r="AF196" t="inlineStr"/>
+      <c r="AG196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
@@ -17253,6 +17653,8 @@
       <c r="AE197" t="n">
         <v>3704.521474176185</v>
       </c>
+      <c r="AF197" t="inlineStr"/>
+      <c r="AG197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
@@ -17340,6 +17742,8 @@
       <c r="AE198" t="n">
         <v>3735.345835779171</v>
       </c>
+      <c r="AF198" t="inlineStr"/>
+      <c r="AG198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
@@ -17427,6 +17831,8 @@
       <c r="AE199" t="n">
         <v>4122.917512499476</v>
       </c>
+      <c r="AF199" t="inlineStr"/>
+      <c r="AG199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
@@ -17514,6 +17920,8 @@
       <c r="AE200" t="n">
         <v>4046.535306439408</v>
       </c>
+      <c r="AF200" t="inlineStr"/>
+      <c r="AG200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
@@ -17601,6 +18009,8 @@
       <c r="AE201" t="n">
         <v>4307.668391641832</v>
       </c>
+      <c r="AF201" t="inlineStr"/>
+      <c r="AG201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
@@ -17688,6 +18098,8 @@
       <c r="AE202" t="n">
         <v>4297.970968177794</v>
       </c>
+      <c r="AF202" t="inlineStr"/>
+      <c r="AG202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
@@ -17775,6 +18187,8 @@
       <c r="AE203" t="n">
         <v>4280.53989935716</v>
       </c>
+      <c r="AF203" t="inlineStr"/>
+      <c r="AG203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
@@ -17862,6 +18276,8 @@
       <c r="AE204" t="n">
         <v>4391.852992044212</v>
       </c>
+      <c r="AF204" t="inlineStr"/>
+      <c r="AG204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
@@ -17949,6 +18365,8 @@
       <c r="AE205" t="n">
         <v>3873.445697906959</v>
       </c>
+      <c r="AF205" t="inlineStr"/>
+      <c r="AG205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
@@ -18036,6 +18454,8 @@
       <c r="AE206" t="n">
         <v>4042.66892224606</v>
       </c>
+      <c r="AF206" t="inlineStr"/>
+      <c r="AG206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
@@ -18123,6 +18543,8 @@
       <c r="AE207" t="n">
         <v>4306.43557478653</v>
       </c>
+      <c r="AF207" t="inlineStr"/>
+      <c r="AG207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
@@ -18210,6 +18632,8 @@
       <c r="AE208" t="n">
         <v>4172.341087935875</v>
       </c>
+      <c r="AF208" t="inlineStr"/>
+      <c r="AG208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
@@ -18297,6 +18721,8 @@
       <c r="AE209" t="n">
         <v>4186.928719658819</v>
       </c>
+      <c r="AF209" t="inlineStr"/>
+      <c r="AG209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
@@ -18384,6 +18810,8 @@
       <c r="AE210" t="n">
         <v>4120.162554930892</v>
       </c>
+      <c r="AF210" t="inlineStr"/>
+      <c r="AG210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
@@ -18471,6 +18899,8 @@
       <c r="AE211" t="n">
         <v>4203.865080993231</v>
       </c>
+      <c r="AF211" t="inlineStr"/>
+      <c r="AG211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
@@ -18558,6 +18988,8 @@
       <c r="AE212" t="n">
         <v>4209.438043186523</v>
       </c>
+      <c r="AF212" t="inlineStr"/>
+      <c r="AG212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
@@ -18645,6 +19077,8 @@
       <c r="AE213" t="n">
         <v>4206.381769820491</v>
       </c>
+      <c r="AF213" t="inlineStr"/>
+      <c r="AG213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
@@ -18732,6 +19166,8 @@
       <c r="AE214" t="n">
         <v>3990.167987831692</v>
       </c>
+      <c r="AF214" t="inlineStr"/>
+      <c r="AG214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
@@ -18819,6 +19255,8 @@
       <c r="AE215" t="n">
         <v>3901.267683436377</v>
       </c>
+      <c r="AF215" t="inlineStr"/>
+      <c r="AG215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
@@ -18906,6 +19344,8 @@
       <c r="AE216" t="n">
         <v>3862.490681338301</v>
       </c>
+      <c r="AF216" t="inlineStr"/>
+      <c r="AG216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
@@ -18993,6 +19433,8 @@
       <c r="AE217" t="n">
         <v>3712.049624220427</v>
       </c>
+      <c r="AF217" t="inlineStr"/>
+      <c r="AG217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
@@ -19080,6 +19522,8 @@
       <c r="AE218" t="n">
         <v>3697.506488785963</v>
       </c>
+      <c r="AF218" t="inlineStr"/>
+      <c r="AG218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
@@ -19167,6 +19611,8 @@
       <c r="AE219" t="n">
         <v>3803.173159298546</v>
       </c>
+      <c r="AF219" t="inlineStr"/>
+      <c r="AG219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
@@ -19254,6 +19700,8 @@
       <c r="AE220" t="n">
         <v>3922.158736703291</v>
       </c>
+      <c r="AF220" t="inlineStr"/>
+      <c r="AG220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
@@ -19341,6 +19789,8 @@
       <c r="AE221" t="n">
         <v>3909.770411367536</v>
       </c>
+      <c r="AF221" t="inlineStr"/>
+      <c r="AG221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
@@ -19428,6 +19878,8 @@
       <c r="AE222" t="n">
         <v>3744.615637943558</v>
       </c>
+      <c r="AF222" t="inlineStr"/>
+      <c r="AG222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
@@ -19515,6 +19967,8 @@
       <c r="AE223" t="n">
         <v>3733.118302247665</v>
       </c>
+      <c r="AF223" t="inlineStr"/>
+      <c r="AG223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
@@ -19602,6 +20056,8 @@
       <c r="AE224" t="n">
         <v>3785.662580035585</v>
       </c>
+      <c r="AF224" t="inlineStr"/>
+      <c r="AG224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
@@ -19689,6 +20145,8 @@
       <c r="AE225" t="n">
         <v>3707.132675814005</v>
       </c>
+      <c r="AF225" t="inlineStr"/>
+      <c r="AG225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
@@ -19776,6 +20234,8 @@
       <c r="AE226" t="n">
         <v>3593.241267282239</v>
       </c>
+      <c r="AF226" t="inlineStr"/>
+      <c r="AG226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
@@ -19863,6 +20323,8 @@
       <c r="AE227" t="n">
         <v>3763.261013701853</v>
       </c>
+      <c r="AF227" t="inlineStr"/>
+      <c r="AG227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
@@ -19950,6 +20412,8 @@
       <c r="AE228" t="n">
         <v>3788.91518730673</v>
       </c>
+      <c r="AF228" t="inlineStr"/>
+      <c r="AG228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
@@ -20037,6 +20501,8 @@
       <c r="AE229" t="n">
         <v>3907.816753855594</v>
       </c>
+      <c r="AF229" t="inlineStr"/>
+      <c r="AG229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
@@ -20124,6 +20590,8 @@
       <c r="AE230" t="n">
         <v>4008.8679964156</v>
       </c>
+      <c r="AF230" t="inlineStr"/>
+      <c r="AG230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
@@ -20211,6 +20679,8 @@
       <c r="AE231" t="n">
         <v>4056.002482184531</v>
       </c>
+      <c r="AF231" t="inlineStr"/>
+      <c r="AG231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
@@ -20298,6 +20768,8 @@
       <c r="AE232" t="n">
         <v>4009.122783145364</v>
       </c>
+      <c r="AF232" t="inlineStr"/>
+      <c r="AG232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
@@ -20385,6 +20857,8 @@
       <c r="AE233" t="n">
         <v>4152.090228715961</v>
       </c>
+      <c r="AF233" t="inlineStr"/>
+      <c r="AG233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
@@ -20472,6 +20946,8 @@
       <c r="AE234" t="n">
         <v>3866.432379613322</v>
       </c>
+      <c r="AF234" t="inlineStr"/>
+      <c r="AG234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
@@ -20559,6 +21035,8 @@
       <c r="AE235" t="n">
         <v>3889.894028389681</v>
       </c>
+      <c r="AF235" t="inlineStr"/>
+      <c r="AG235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
@@ -20646,6 +21124,8 @@
       <c r="AE236" t="n">
         <v>3719.587401589422</v>
       </c>
+      <c r="AF236" t="inlineStr"/>
+      <c r="AG236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
@@ -20733,6 +21213,8 @@
       <c r="AE237" t="n">
         <v>3832.777891898353</v>
       </c>
+      <c r="AF237" t="inlineStr"/>
+      <c r="AG237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
@@ -20820,6 +21302,8 @@
       <c r="AE238" t="n">
         <v>3778.514396440167</v>
       </c>
+      <c r="AF238" t="inlineStr"/>
+      <c r="AG238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
@@ -20907,6 +21391,8 @@
       <c r="AE239" t="n">
         <v>3707.496000723548</v>
       </c>
+      <c r="AF239" t="inlineStr"/>
+      <c r="AG239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
@@ -20994,6 +21480,8 @@
       <c r="AE240" t="n">
         <v>3700.003727326001</v>
       </c>
+      <c r="AF240" t="inlineStr"/>
+      <c r="AG240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
@@ -21081,6 +21569,8 @@
       <c r="AE241" t="n">
         <v>3674.252307600644</v>
       </c>
+      <c r="AF241" t="inlineStr"/>
+      <c r="AG241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
@@ -21168,6 +21658,8 @@
       <c r="AE242" t="n">
         <v>3891.650958879414</v>
       </c>
+      <c r="AF242" t="inlineStr"/>
+      <c r="AG242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
@@ -21255,6 +21747,8 @@
       <c r="AE243" t="n">
         <v>3832.05142071831</v>
       </c>
+      <c r="AF243" t="inlineStr"/>
+      <c r="AG243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
@@ -21342,6 +21836,8 @@
       <c r="AE244" t="n">
         <v>3956.798514680825</v>
       </c>
+      <c r="AF244" t="inlineStr"/>
+      <c r="AG244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
@@ -21429,6 +21925,8 @@
       <c r="AE245" t="n">
         <v>3940.894975884295</v>
       </c>
+      <c r="AF245" t="inlineStr"/>
+      <c r="AG245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
@@ -21516,6 +22014,8 @@
       <c r="AE246" t="n">
         <v>3741.550625400118</v>
       </c>
+      <c r="AF246" t="inlineStr"/>
+      <c r="AG246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
@@ -21603,6 +22103,8 @@
       <c r="AE247" t="n">
         <v>3746.27866952848</v>
       </c>
+      <c r="AF247" t="inlineStr"/>
+      <c r="AG247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
@@ -21690,6 +22192,8 @@
       <c r="AE248" t="n">
         <v>3840.005485791751</v>
       </c>
+      <c r="AF248" t="inlineStr"/>
+      <c r="AG248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
@@ -21777,6 +22281,8 @@
       <c r="AE249" t="n">
         <v>3827.987264340374</v>
       </c>
+      <c r="AF249" t="inlineStr"/>
+      <c r="AG249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
@@ -21864,6 +22370,8 @@
       <c r="AE250" t="n">
         <v>3814.407695292191</v>
       </c>
+      <c r="AF250" t="inlineStr"/>
+      <c r="AG250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
@@ -21951,6 +22459,8 @@
       <c r="AE251" t="n">
         <v>3749.926813684106</v>
       </c>
+      <c r="AF251" t="inlineStr"/>
+      <c r="AG251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
@@ -22038,6 +22548,8 @@
       <c r="AE252" t="n">
         <v>4010.36410720406</v>
       </c>
+      <c r="AF252" t="inlineStr"/>
+      <c r="AG252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
@@ -22125,6 +22637,8 @@
       <c r="AE253" t="n">
         <v>4252.487092663298</v>
       </c>
+      <c r="AF253" t="inlineStr"/>
+      <c r="AG253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
@@ -22212,6 +22726,8 @@
       <c r="AE254" t="n">
         <v>4204.451640838877</v>
       </c>
+      <c r="AF254" t="inlineStr"/>
+      <c r="AG254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n">
@@ -22299,6 +22815,8 @@
       <c r="AE255" t="n">
         <v>4062.443355814687</v>
       </c>
+      <c r="AF255" t="inlineStr"/>
+      <c r="AG255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
@@ -22386,6 +22904,8 @@
       <c r="AE256" t="n">
         <v>4173.543273843198</v>
       </c>
+      <c r="AF256" t="inlineStr"/>
+      <c r="AG256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n">
@@ -22473,6 +22993,8 @@
       <c r="AE257" t="n">
         <v>4760.864096288815</v>
       </c>
+      <c r="AF257" t="inlineStr"/>
+      <c r="AG257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
@@ -22560,6 +23082,8 @@
       <c r="AE258" t="n">
         <v>4597.331333739315</v>
       </c>
+      <c r="AF258" t="inlineStr"/>
+      <c r="AG258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n">
@@ -22647,6 +23171,8 @@
       <c r="AE259" t="n">
         <v>4438.794440404017</v>
       </c>
+      <c r="AF259" t="inlineStr"/>
+      <c r="AG259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
@@ -22734,6 +23260,8 @@
       <c r="AE260" t="n">
         <v>4189.811776013388</v>
       </c>
+      <c r="AF260" t="inlineStr"/>
+      <c r="AG260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n">
@@ -22821,6 +23349,8 @@
       <c r="AE261" t="n">
         <v>4784.054355096489</v>
       </c>
+      <c r="AF261" t="inlineStr"/>
+      <c r="AG261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n">
@@ -22908,6 +23438,8 @@
       <c r="AE262" t="n">
         <v>4556.513595995847</v>
       </c>
+      <c r="AF262" t="inlineStr"/>
+      <c r="AG262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n">
@@ -22995,6 +23527,8 @@
       <c r="AE263" t="n">
         <v>4516.607426551246</v>
       </c>
+      <c r="AF263" t="inlineStr"/>
+      <c r="AG263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n">
@@ -23082,6 +23616,8 @@
       <c r="AE264" t="n">
         <v>4513.365804078982</v>
       </c>
+      <c r="AF264" t="inlineStr"/>
+      <c r="AG264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n">
@@ -23169,6 +23705,8 @@
       <c r="AE265" t="n">
         <v>4594.61007558094</v>
       </c>
+      <c r="AF265" t="inlineStr"/>
+      <c r="AG265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n">
@@ -23256,6 +23794,8 @@
       <c r="AE266" t="n">
         <v>4540.535000686935</v>
       </c>
+      <c r="AF266" t="inlineStr"/>
+      <c r="AG266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n">
@@ -23343,6 +23883,8 @@
       <c r="AE267" t="n">
         <v>4685.031333141183</v>
       </c>
+      <c r="AF267" t="inlineStr"/>
+      <c r="AG267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n">
@@ -23430,6 +23972,8 @@
       <c r="AE268" t="n">
         <v>4669.182367313107</v>
       </c>
+      <c r="AF268" t="inlineStr"/>
+      <c r="AG268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n">
@@ -23517,6 +24061,8 @@
       <c r="AE269" t="n">
         <v>4504.976904266347</v>
       </c>
+      <c r="AF269" t="inlineStr"/>
+      <c r="AG269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n">
@@ -23604,6 +24150,8 @@
       <c r="AE270" t="n">
         <v>4545.17221267261</v>
       </c>
+      <c r="AF270" t="inlineStr"/>
+      <c r="AG270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n">
@@ -23691,6 +24239,8 @@
       <c r="AE271" t="n">
         <v>4531.288715213198</v>
       </c>
+      <c r="AF271" t="inlineStr"/>
+      <c r="AG271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n">
@@ -23778,6 +24328,8 @@
       <c r="AE272" t="n">
         <v>5123.393113105535</v>
       </c>
+      <c r="AF272" t="inlineStr"/>
+      <c r="AG272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n">
@@ -23865,6 +24417,8 @@
       <c r="AE273" t="n">
         <v>5345.037893688335</v>
       </c>
+      <c r="AF273" t="inlineStr"/>
+      <c r="AG273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">
@@ -23952,6 +24506,8 @@
       <c r="AE274" t="n">
         <v>5250.354731543285</v>
       </c>
+      <c r="AF274" t="inlineStr"/>
+      <c r="AG274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n">
@@ -24039,6 +24595,8 @@
       <c r="AE275" t="n">
         <v>5142.797680975616</v>
       </c>
+      <c r="AF275" t="inlineStr"/>
+      <c r="AG275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n">
@@ -24126,6 +24684,8 @@
       <c r="AE276" t="n">
         <v>5278.657103546437</v>
       </c>
+      <c r="AF276" t="inlineStr"/>
+      <c r="AG276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n">
@@ -24213,6 +24773,8 @@
       <c r="AE277" t="n">
         <v>5299.841776065652</v>
       </c>
+      <c r="AF277" t="inlineStr"/>
+      <c r="AG277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n">
@@ -24300,6 +24862,8 @@
       <c r="AE278" t="n">
         <v>5534.544518175549</v>
       </c>
+      <c r="AF278" t="inlineStr"/>
+      <c r="AG278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n">
@@ -24387,6 +24951,8 @@
       <c r="AE279" t="n">
         <v>5265.040274359311</v>
       </c>
+      <c r="AF279" t="inlineStr"/>
+      <c r="AG279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n">
@@ -24474,6 +25040,8 @@
       <c r="AE280" t="n">
         <v>5606.129469437133</v>
       </c>
+      <c r="AF280" t="inlineStr"/>
+      <c r="AG280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n">
@@ -24561,6 +25129,8 @@
       <c r="AE281" t="n">
         <v>5716.417739573675</v>
       </c>
+      <c r="AF281" t="inlineStr"/>
+      <c r="AG281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n">
@@ -24648,6 +25218,8 @@
       <c r="AE282" t="n">
         <v>5342.884252086552</v>
       </c>
+      <c r="AF282" t="inlineStr"/>
+      <c r="AG282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n">
@@ -24735,6 +25307,8 @@
       <c r="AE283" t="n">
         <v>5197.379260240066</v>
       </c>
+      <c r="AF283" t="inlineStr"/>
+      <c r="AG283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n">
@@ -24822,6 +25396,8 @@
       <c r="AE284" t="n">
         <v>4832.24306968837</v>
       </c>
+      <c r="AF284" t="inlineStr"/>
+      <c r="AG284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="n">
@@ -24909,6 +25485,8 @@
       <c r="AE285" t="n">
         <v>4982.2027685086</v>
       </c>
+      <c r="AF285" t="inlineStr"/>
+      <c r="AG285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n">
@@ -24996,6 +25574,8 @@
       <c r="AE286" t="n">
         <v>5046.179219365993</v>
       </c>
+      <c r="AF286" t="inlineStr"/>
+      <c r="AG286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n">
@@ -25083,6 +25663,8 @@
       <c r="AE287" t="n">
         <v>5070.888092109495</v>
       </c>
+      <c r="AF287" t="inlineStr"/>
+      <c r="AG287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n">
@@ -25170,6 +25752,8 @@
       <c r="AE288" t="n">
         <v>5288.681769792342</v>
       </c>
+      <c r="AF288" t="inlineStr"/>
+      <c r="AG288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="n">
@@ -25257,6 +25841,8 @@
       <c r="AE289" t="n">
         <v>4851.906405440821</v>
       </c>
+      <c r="AF289" t="inlineStr"/>
+      <c r="AG289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n">
@@ -25344,6 +25930,8 @@
       <c r="AE290" t="n">
         <v>4873.540396117998</v>
       </c>
+      <c r="AF290" t="inlineStr"/>
+      <c r="AG290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="n">
@@ -25431,6 +26019,8 @@
       <c r="AE291" t="n">
         <v>4889.603114649651</v>
       </c>
+      <c r="AF291" t="inlineStr"/>
+      <c r="AG291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n">
@@ -25518,6 +26108,8 @@
       <c r="AE292" t="n">
         <v>4737.495850971753</v>
       </c>
+      <c r="AF292" t="inlineStr"/>
+      <c r="AG292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="2" t="n">
@@ -25605,6 +26197,8 @@
       <c r="AE293" t="n">
         <v>4573.718896753327</v>
       </c>
+      <c r="AF293" t="inlineStr"/>
+      <c r="AG293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="n">
@@ -25692,6 +26286,8 @@
       <c r="AE294" t="n">
         <v>4547.916904088344</v>
       </c>
+      <c r="AF294" t="inlineStr"/>
+      <c r="AG294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="2" t="n">
@@ -25779,6 +26375,8 @@
       <c r="AE295" t="n">
         <v>4259.109139291179</v>
       </c>
+      <c r="AF295" t="inlineStr"/>
+      <c r="AG295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n">
@@ -25866,6 +26464,8 @@
       <c r="AE296" t="n">
         <v>4252.039769319937</v>
       </c>
+      <c r="AF296" t="inlineStr"/>
+      <c r="AG296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="n">
@@ -25953,6 +26553,8 @@
       <c r="AE297" t="n">
         <v>4322.919547759781</v>
       </c>
+      <c r="AF297" t="inlineStr"/>
+      <c r="AG297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="n">
@@ -26040,6 +26642,8 @@
       <c r="AE298" t="n">
         <v>4436.225037419127</v>
       </c>
+      <c r="AF298" t="inlineStr"/>
+      <c r="AG298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="2" t="n">
@@ -26127,6 +26731,8 @@
       <c r="AE299" t="n">
         <v>4298.441789677178</v>
       </c>
+      <c r="AF299" t="inlineStr"/>
+      <c r="AG299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="n">
@@ -26214,6 +26820,8 @@
       <c r="AE300" t="n">
         <v>4327.395333739043</v>
       </c>
+      <c r="AF300" t="inlineStr"/>
+      <c r="AG300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="n">
@@ -26301,6 +26909,8 @@
       <c r="AE301" t="n">
         <v>4519.591167137396</v>
       </c>
+      <c r="AF301" t="inlineStr"/>
+      <c r="AG301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="n">
@@ -26388,6 +26998,8 @@
       <c r="AE302" t="n">
         <v>4526.840725927217</v>
       </c>
+      <c r="AF302" t="inlineStr"/>
+      <c r="AG302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="2" t="n">
@@ -26475,6 +27087,8 @@
       <c r="AE303" t="n">
         <v>4670.708111811815</v>
       </c>
+      <c r="AF303" t="inlineStr"/>
+      <c r="AG303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="n">
@@ -26562,6 +27176,8 @@
       <c r="AE304" t="n">
         <v>4672.602112729979</v>
       </c>
+      <c r="AF304" t="inlineStr"/>
+      <c r="AG304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="n">
@@ -26649,6 +27265,8 @@
       <c r="AE305" t="n">
         <v>4686.42061478919</v>
       </c>
+      <c r="AF305" t="inlineStr"/>
+      <c r="AG305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="n">
@@ -26736,6 +27354,8 @@
       <c r="AE306" t="n">
         <v>4496.929766532242</v>
       </c>
+      <c r="AF306" t="inlineStr"/>
+      <c r="AG306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="2" t="n">
@@ -26823,6 +27443,8 @@
       <c r="AE307" t="n">
         <v>4285.408677933171</v>
       </c>
+      <c r="AF307" t="inlineStr"/>
+      <c r="AG307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="n">
@@ -26910,6 +27532,8 @@
       <c r="AE308" t="n">
         <v>4321.1389869581</v>
       </c>
+      <c r="AF308" t="inlineStr"/>
+      <c r="AG308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="2" t="n">
@@ -26997,6 +27621,8 @@
       <c r="AE309" t="n">
         <v>4430.346073967818</v>
       </c>
+      <c r="AF309" t="inlineStr"/>
+      <c r="AG309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" s="2" t="n">
@@ -27084,6 +27710,8 @@
       <c r="AE310" t="n">
         <v>4652.910838804879</v>
       </c>
+      <c r="AF310" t="inlineStr"/>
+      <c r="AG310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" s="2" t="n">
@@ -27171,6 +27799,8 @@
       <c r="AE311" t="n">
         <v>4649.929105537814</v>
       </c>
+      <c r="AF311" t="inlineStr"/>
+      <c r="AG311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="n">
@@ -27258,6 +27888,8 @@
       <c r="AE312" t="n">
         <v>4492.428553423866</v>
       </c>
+      <c r="AF312" t="inlineStr"/>
+      <c r="AG312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" s="2" t="n">
@@ -27345,6 +27977,8 @@
       <c r="AE313" t="n">
         <v>4474.55257816678</v>
       </c>
+      <c r="AF313" t="inlineStr"/>
+      <c r="AG313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="n">
@@ -27432,6 +28066,8 @@
       <c r="AE314" t="n">
         <v>4336.662943667785</v>
       </c>
+      <c r="AF314" t="inlineStr"/>
+      <c r="AG314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="2" t="n">
@@ -27519,6 +28155,8 @@
       <c r="AE315" t="n">
         <v>4241.52707366968</v>
       </c>
+      <c r="AF315" t="inlineStr"/>
+      <c r="AG315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" s="2" t="n">
@@ -27606,6 +28244,8 @@
       <c r="AE316" t="n">
         <v>4261.08379024388</v>
       </c>
+      <c r="AF316" t="inlineStr"/>
+      <c r="AG316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" s="2" t="n">
@@ -27693,6 +28333,8 @@
       <c r="AE317" t="n">
         <v>4243.738817019343</v>
       </c>
+      <c r="AF317" t="inlineStr"/>
+      <c r="AG317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" s="2" t="n">
@@ -27780,6 +28422,8 @@
       <c r="AE318" t="n">
         <v>4335.931887759594</v>
       </c>
+      <c r="AF318" t="inlineStr"/>
+      <c r="AG318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" s="2" t="n">
@@ -27867,6 +28511,8 @@
       <c r="AE319" t="n">
         <v>4247.403091834195</v>
       </c>
+      <c r="AF319" t="inlineStr"/>
+      <c r="AG319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" s="2" t="n">
@@ -27954,6 +28600,8 @@
       <c r="AE320" t="n">
         <v>4324.309625002654</v>
       </c>
+      <c r="AF320" t="inlineStr"/>
+      <c r="AG320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" s="2" t="n">
@@ -28041,6 +28689,8 @@
       <c r="AE321" t="n">
         <v>4278.706470308329</v>
       </c>
+      <c r="AF321" t="inlineStr"/>
+      <c r="AG321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" s="2" t="n">
@@ -28128,6 +28778,8 @@
       <c r="AE322" t="n">
         <v>4268.577786286144</v>
       </c>
+      <c r="AF322" t="inlineStr"/>
+      <c r="AG322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" s="2" t="n">
@@ -28215,6 +28867,8 @@
       <c r="AE323" t="n">
         <v>3909.856829756804</v>
       </c>
+      <c r="AF323" t="inlineStr"/>
+      <c r="AG323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" s="2" t="n">
@@ -28302,6 +28956,8 @@
       <c r="AE324" t="n">
         <v>4173.737399111852</v>
       </c>
+      <c r="AF324" t="inlineStr"/>
+      <c r="AG324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" s="2" t="n">
@@ -28389,6 +29045,8 @@
       <c r="AE325" t="n">
         <v>4108.120623113469</v>
       </c>
+      <c r="AF325" t="inlineStr"/>
+      <c r="AG325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="n">
@@ -28476,6 +29134,8 @@
       <c r="AE326" t="n">
         <v>4501.550619312428</v>
       </c>
+      <c r="AF326" t="inlineStr"/>
+      <c r="AG326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" s="2" t="n">
@@ -28563,6 +29223,8 @@
       <c r="AE327" t="n">
         <v>4273.382738914343</v>
       </c>
+      <c r="AF327" t="inlineStr"/>
+      <c r="AG327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" s="2" t="n">
@@ -28650,6 +29312,8 @@
       <c r="AE328" t="n">
         <v>4351.644174098879</v>
       </c>
+      <c r="AF328" t="inlineStr"/>
+      <c r="AG328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" s="2" t="n">
@@ -28737,6 +29401,8 @@
       <c r="AE329" t="n">
         <v>4362.079372737997</v>
       </c>
+      <c r="AF329" t="inlineStr"/>
+      <c r="AG329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" s="2" t="n">
@@ -28824,6 +29490,8 @@
       <c r="AE330" t="n">
         <v>1888.731387447118</v>
       </c>
+      <c r="AF330" t="inlineStr"/>
+      <c r="AG330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" s="2" t="n">
@@ -28911,6 +29579,8 @@
       <c r="AE331" t="n">
         <v>1707.02523555425</v>
       </c>
+      <c r="AF331" t="inlineStr"/>
+      <c r="AG331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" s="2" t="n">
@@ -28998,6 +29668,8 @@
       <c r="AE332" t="n">
         <v>1758.379820807363</v>
       </c>
+      <c r="AF332" t="inlineStr"/>
+      <c r="AG332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" s="2" t="n">
@@ -29085,6 +29757,8 @@
       <c r="AE333" t="n">
         <v>1726.734412410774</v>
       </c>
+      <c r="AF333" t="inlineStr"/>
+      <c r="AG333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" s="2" t="n">
@@ -29172,6 +29846,8 @@
       <c r="AE334" t="n">
         <v>1710.9440877206</v>
       </c>
+      <c r="AF334" t="inlineStr"/>
+      <c r="AG334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" s="2" t="n">
@@ -29259,6 +29935,8 @@
       <c r="AE335" t="n">
         <v>1698.551119246675</v>
       </c>
+      <c r="AF335" t="inlineStr"/>
+      <c r="AG335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" s="2" t="n">
@@ -29346,6 +30024,8 @@
       <c r="AE336" t="n">
         <v>1718.538980694891</v>
       </c>
+      <c r="AF336" t="inlineStr"/>
+      <c r="AG336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" s="2" t="n">
@@ -29433,6 +30113,8 @@
       <c r="AE337" t="n">
         <v>1682.366088658418</v>
       </c>
+      <c r="AF337" t="inlineStr"/>
+      <c r="AG337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" s="2" t="n">
@@ -29520,6 +30202,8 @@
       <c r="AE338" t="n">
         <v>1679.566925662685</v>
       </c>
+      <c r="AF338" t="inlineStr"/>
+      <c r="AG338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" s="2" t="n">
@@ -29607,6 +30291,8 @@
       <c r="AE339" t="n">
         <v>1799.473675606434</v>
       </c>
+      <c r="AF339" t="inlineStr"/>
+      <c r="AG339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" s="2" t="n">
@@ -29694,6 +30380,8 @@
       <c r="AE340" t="n">
         <v>1828.893304190438</v>
       </c>
+      <c r="AF340" t="inlineStr"/>
+      <c r="AG340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" s="2" t="n">
@@ -29781,6 +30469,8 @@
       <c r="AE341" t="n">
         <v>1821.185372327399</v>
       </c>
+      <c r="AF341" t="inlineStr"/>
+      <c r="AG341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="n">
@@ -29868,6 +30558,8 @@
       <c r="AE342" t="n">
         <v>1835.154335167629</v>
       </c>
+      <c r="AF342" t="inlineStr"/>
+      <c r="AG342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" s="2" t="n">
@@ -29955,6 +30647,8 @@
       <c r="AE343" t="n">
         <v>1843.005398671573</v>
       </c>
+      <c r="AF343" t="inlineStr"/>
+      <c r="AG343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" s="2" t="n">
@@ -30042,6 +30736,8 @@
       <c r="AE344" t="n">
         <v>1821.592947774713</v>
       </c>
+      <c r="AF344" t="inlineStr"/>
+      <c r="AG344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" s="2" t="n">
@@ -30129,6 +30825,8 @@
       <c r="AE345" t="n">
         <v>1829.964123315499</v>
       </c>
+      <c r="AF345" t="inlineStr"/>
+      <c r="AG345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="n">
@@ -30216,6 +30914,8 @@
       <c r="AE346" t="n">
         <v>1796.543959245806</v>
       </c>
+      <c r="AF346" t="inlineStr"/>
+      <c r="AG346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" s="2" t="n">
@@ -30303,6 +31003,8 @@
       <c r="AE347" t="n">
         <v>1796.134474963238</v>
       </c>
+      <c r="AF347" t="inlineStr"/>
+      <c r="AG347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="n">
@@ -30390,6 +31092,8 @@
       <c r="AE348" t="n">
         <v>1817.76759647732</v>
       </c>
+      <c r="AF348" t="inlineStr"/>
+      <c r="AG348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" s="2" t="n">
@@ -30477,6 +31181,8 @@
       <c r="AE349" t="n">
         <v>1797.95638706648</v>
       </c>
+      <c r="AF349" t="inlineStr"/>
+      <c r="AG349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" s="2" t="n">
@@ -30564,6 +31270,8 @@
       <c r="AE350" t="n">
         <v>1774.737641989717</v>
       </c>
+      <c r="AF350" t="inlineStr"/>
+      <c r="AG350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" s="2" t="n">
@@ -30651,6 +31359,8 @@
       <c r="AE351" t="n">
         <v>1735.514919864315</v>
       </c>
+      <c r="AF351" t="inlineStr"/>
+      <c r="AG351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" s="2" t="n">
@@ -30738,6 +31448,8 @@
       <c r="AE352" t="n">
         <v>1744.540533992501</v>
       </c>
+      <c r="AF352" t="inlineStr"/>
+      <c r="AG352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="2" t="n">
@@ -30825,6 +31537,8 @@
       <c r="AE353" t="n">
         <v>1756.953691251894</v>
       </c>
+      <c r="AF353" t="inlineStr"/>
+      <c r="AG353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" s="2" t="n">
@@ -30912,6 +31626,8 @@
       <c r="AE354" t="n">
         <v>1750.272672499825</v>
       </c>
+      <c r="AF354" t="inlineStr"/>
+      <c r="AG354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" s="2" t="n">
@@ -30999,6 +31715,8 @@
       <c r="AE355" t="n">
         <v>1906.169460007538</v>
       </c>
+      <c r="AF355" t="inlineStr"/>
+      <c r="AG355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="n">
@@ -31086,6 +31804,8 @@
       <c r="AE356" t="n">
         <v>1942.345699514093</v>
       </c>
+      <c r="AF356" t="inlineStr"/>
+      <c r="AG356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" s="2" t="n">
@@ -31173,6 +31893,8 @@
       <c r="AE357" t="n">
         <v>2048.247789477522</v>
       </c>
+      <c r="AF357" t="inlineStr"/>
+      <c r="AG357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="n">
@@ -31260,6 +31982,8 @@
       <c r="AE358" t="n">
         <v>1994.277415377649</v>
       </c>
+      <c r="AF358" t="inlineStr"/>
+      <c r="AG358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" s="2" t="n">
@@ -31347,6 +32071,8 @@
       <c r="AE359" t="n">
         <v>2009.65429098559</v>
       </c>
+      <c r="AF359" t="inlineStr"/>
+      <c r="AG359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="n">
@@ -31434,6 +32160,8 @@
       <c r="AE360" t="n">
         <v>2058.668608886322</v>
       </c>
+      <c r="AF360" t="inlineStr"/>
+      <c r="AG360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" s="2" t="n">
@@ -31521,6 +32249,8 @@
       <c r="AE361" t="n">
         <v>2012.895281375721</v>
       </c>
+      <c r="AF361" t="inlineStr"/>
+      <c r="AG361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="n">
@@ -31608,6 +32338,8 @@
       <c r="AE362" t="n">
         <v>1964.786816021098</v>
       </c>
+      <c r="AF362" t="inlineStr"/>
+      <c r="AG362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" s="2" t="n">
@@ -31695,6 +32427,8 @@
       <c r="AE363" t="n">
         <v>1949.642223193357</v>
       </c>
+      <c r="AF363" t="inlineStr"/>
+      <c r="AG363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="n">
@@ -31782,6 +32516,8 @@
       <c r="AE364" t="n">
         <v>1923.701520126522</v>
       </c>
+      <c r="AF364" t="inlineStr"/>
+      <c r="AG364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" s="2" t="n">
@@ -31869,6 +32605,8 @@
       <c r="AE365" t="n">
         <v>1996.817549871139</v>
       </c>
+      <c r="AF365" t="inlineStr"/>
+      <c r="AG365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="n">
@@ -31956,6 +32694,8 @@
       <c r="AE366" t="n">
         <v>1969.916624309911</v>
       </c>
+      <c r="AF366" t="inlineStr"/>
+      <c r="AG366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" s="2" t="n">
@@ -32043,6 +32783,8 @@
       <c r="AE367" t="n">
         <v>1987.733674337233</v>
       </c>
+      <c r="AF367" t="inlineStr"/>
+      <c r="AG367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" s="2" t="n">
@@ -32130,6 +32872,8 @@
       <c r="AE368" t="n">
         <v>2034.835187928205</v>
       </c>
+      <c r="AF368" t="inlineStr"/>
+      <c r="AG368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" s="2" t="n">
@@ -32217,6 +32961,8 @@
       <c r="AE369" t="n">
         <v>2096.346375305716</v>
       </c>
+      <c r="AF369" t="inlineStr"/>
+      <c r="AG369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="n">
@@ -32304,6 +33050,8 @@
       <c r="AE370" t="n">
         <v>1991.410011113856</v>
       </c>
+      <c r="AF370" t="inlineStr"/>
+      <c r="AG370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" s="2" t="n">
@@ -32391,6 +33139,8 @@
       <c r="AE371" t="n">
         <v>2009.868297641777</v>
       </c>
+      <c r="AF371" t="inlineStr"/>
+      <c r="AG371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="n">
@@ -32478,6 +33228,8 @@
       <c r="AE372" t="n">
         <v>2019.53441291209</v>
       </c>
+      <c r="AF372" t="inlineStr"/>
+      <c r="AG372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" s="2" t="n">
@@ -32565,6 +33317,8 @@
       <c r="AE373" t="n">
         <v>2014.174193420928</v>
       </c>
+      <c r="AF373" t="inlineStr"/>
+      <c r="AG373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="n">
@@ -32652,6 +33406,8 @@
       <c r="AE374" t="n">
         <v>2025.733766451235</v>
       </c>
+      <c r="AF374" t="inlineStr"/>
+      <c r="AG374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" s="2" t="n">
@@ -32739,6 +33495,8 @@
       <c r="AE375" t="n">
         <v>2000.97224522705</v>
       </c>
+      <c r="AF375" t="inlineStr"/>
+      <c r="AG375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="n">
@@ -32826,6 +33584,8 @@
       <c r="AE376" t="n">
         <v>1952.017767146737</v>
       </c>
+      <c r="AF376" t="inlineStr"/>
+      <c r="AG376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" s="2" t="n">
@@ -32913,6 +33673,8 @@
       <c r="AE377" t="n">
         <v>1852.817149790337</v>
       </c>
+      <c r="AF377" t="inlineStr"/>
+      <c r="AG377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" s="2" t="n">
@@ -33000,6 +33762,8 @@
       <c r="AE378" t="n">
         <v>1866.542314173201</v>
       </c>
+      <c r="AF378" t="inlineStr"/>
+      <c r="AG378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" s="2" t="n">
@@ -33087,6 +33851,8 @@
       <c r="AE379" t="n">
         <v>1886.923106774283</v>
       </c>
+      <c r="AF379" t="inlineStr"/>
+      <c r="AG379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" s="2" t="n">
@@ -33174,6 +33940,8 @@
       <c r="AE380" t="n">
         <v>1895.066972708612</v>
       </c>
+      <c r="AF380" t="inlineStr"/>
+      <c r="AG380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" s="2" t="n">
@@ -33261,6 +34029,8 @@
       <c r="AE381" t="n">
         <v>1881.6273714025</v>
       </c>
+      <c r="AF381" t="inlineStr"/>
+      <c r="AG381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="n">
@@ -33348,6 +34118,8 @@
       <c r="AE382" t="n">
         <v>1861.04850082544</v>
       </c>
+      <c r="AF382" t="inlineStr"/>
+      <c r="AG382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" s="2" t="n">
@@ -33435,6 +34207,8 @@
       <c r="AE383" t="n">
         <v>1776.463611027368</v>
       </c>
+      <c r="AF383" t="inlineStr"/>
+      <c r="AG383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" s="2" t="n">
@@ -33522,6 +34296,8 @@
       <c r="AE384" t="n">
         <v>1822.306292002383</v>
       </c>
+      <c r="AF384" t="inlineStr"/>
+      <c r="AG384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" s="2" t="n">
@@ -33609,6 +34385,8 @@
       <c r="AE385" t="n">
         <v>1854.387805779093</v>
       </c>
+      <c r="AF385" t="inlineStr"/>
+      <c r="AG385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" s="2" t="n">
@@ -33696,6 +34474,8 @@
       <c r="AE386" t="n">
         <v>1853.329812481738</v>
       </c>
+      <c r="AF386" t="inlineStr"/>
+      <c r="AG386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" s="2" t="n">
@@ -33783,6 +34563,8 @@
       <c r="AE387" t="n">
         <v>1937.586168783248</v>
       </c>
+      <c r="AF387" t="inlineStr"/>
+      <c r="AG387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="n">
@@ -33870,6 +34652,8 @@
       <c r="AE388" t="n">
         <v>1968.38123312765</v>
       </c>
+      <c r="AF388" t="inlineStr"/>
+      <c r="AG388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="2" t="n">
@@ -33957,6 +34741,8 @@
       <c r="AE389" t="n">
         <v>1914.862277482596</v>
       </c>
+      <c r="AF389" t="inlineStr"/>
+      <c r="AG389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="n">
@@ -34044,6 +34830,8 @@
       <c r="AE390" t="n">
         <v>1837.780905932288</v>
       </c>
+      <c r="AF390" t="inlineStr"/>
+      <c r="AG390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" s="2" t="n">
@@ -34131,6 +34919,8 @@
       <c r="AE391" t="n">
         <v>1820.911793739741</v>
       </c>
+      <c r="AF391" t="inlineStr"/>
+      <c r="AG391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="n">
@@ -34218,6 +35008,8 @@
       <c r="AE392" t="n">
         <v>1800.984752575323</v>
       </c>
+      <c r="AF392" t="inlineStr"/>
+      <c r="AG392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" s="2" t="n">
@@ -34305,6 +35097,8 @@
       <c r="AE393" t="n">
         <v>1821.145400177821</v>
       </c>
+      <c r="AF393" t="inlineStr"/>
+      <c r="AG393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="2" t="n">
@@ -34392,6 +35186,8 @@
       <c r="AE394" t="n">
         <v>1827.17279515241</v>
       </c>
+      <c r="AF394" t="inlineStr"/>
+      <c r="AG394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" s="2" t="n">
@@ -34479,6 +35275,8 @@
       <c r="AE395" t="n">
         <v>1782.773899667777</v>
       </c>
+      <c r="AF395" t="inlineStr"/>
+      <c r="AG395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" s="2" t="n">
@@ -34566,6 +35364,8 @@
       <c r="AE396" t="n">
         <v>1791.565808808047</v>
       </c>
+      <c r="AF396" t="inlineStr"/>
+      <c r="AG396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" s="2" t="n">
@@ -34653,6 +35453,8 @@
       <c r="AE397" t="n">
         <v>1782.222746231151</v>
       </c>
+      <c r="AF397" t="inlineStr"/>
+      <c r="AG397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" s="2" t="n">
@@ -34740,6 +35542,8 @@
       <c r="AE398" t="n">
         <v>1736.884035224253</v>
       </c>
+      <c r="AF398" t="inlineStr"/>
+      <c r="AG398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" s="2" t="n">
@@ -34827,6 +35631,8 @@
       <c r="AE399" t="n">
         <v>1694.165997366587</v>
       </c>
+      <c r="AF399" t="inlineStr"/>
+      <c r="AG399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" s="2" t="n">
@@ -34914,6 +35720,8 @@
       <c r="AE400" t="n">
         <v>1656.499139079557</v>
       </c>
+      <c r="AF400" t="inlineStr"/>
+      <c r="AG400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" s="2" t="n">
@@ -35001,6 +35809,8 @@
       <c r="AE401" t="n">
         <v>1769.632685194746</v>
       </c>
+      <c r="AF401" t="inlineStr"/>
+      <c r="AG401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" s="2" t="n">
@@ -35088,6 +35898,8 @@
       <c r="AE402" t="n">
         <v>1791.203729477166</v>
       </c>
+      <c r="AF402" t="inlineStr"/>
+      <c r="AG402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" s="2" t="n">
@@ -35175,6 +35987,8 @@
       <c r="AE403" t="n">
         <v>1784.181586153011</v>
       </c>
+      <c r="AF403" t="inlineStr"/>
+      <c r="AG403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" s="2" t="n">
@@ -35262,6 +36076,8 @@
       <c r="AE404" t="n">
         <v>1760.705230304047</v>
       </c>
+      <c r="AF404" t="inlineStr"/>
+      <c r="AG404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" s="2" t="n">
@@ -35349,6 +36165,8 @@
       <c r="AE405" t="n">
         <v>1773.527305731193</v>
       </c>
+      <c r="AF405" t="inlineStr"/>
+      <c r="AG405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" s="2" t="n">
@@ -35436,6 +36254,8 @@
       <c r="AE406" t="n">
         <v>1799.249396402272</v>
       </c>
+      <c r="AF406" t="inlineStr"/>
+      <c r="AG406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" s="2" t="n">
@@ -35523,6 +36343,8 @@
       <c r="AE407" t="n">
         <v>1830.076791605275</v>
       </c>
+      <c r="AF407" t="inlineStr"/>
+      <c r="AG407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n">
@@ -35610,6 +36432,8 @@
       <c r="AE408" t="n">
         <v>1808.793499714072</v>
       </c>
+      <c r="AF408" t="inlineStr"/>
+      <c r="AG408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" s="2" t="n">
@@ -35697,6 +36521,8 @@
       <c r="AE409" t="n">
         <v>1764.533713065386</v>
       </c>
+      <c r="AF409" t="inlineStr"/>
+      <c r="AG409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n">
@@ -35784,6 +36610,8 @@
       <c r="AE410" t="n">
         <v>1825.496228579266</v>
       </c>
+      <c r="AF410" t="inlineStr"/>
+      <c r="AG410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" s="2" t="n">
@@ -35871,6 +36699,8 @@
       <c r="AE411" t="n">
         <v>1837.972850768102</v>
       </c>
+      <c r="AF411" t="inlineStr"/>
+      <c r="AG411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" s="2" t="n">
@@ -35958,6 +36788,8 @@
       <c r="AE412" t="n">
         <v>1793.266442558354</v>
       </c>
+      <c r="AF412" t="inlineStr"/>
+      <c r="AG412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" s="2" t="n">
@@ -36045,6 +36877,8 @@
       <c r="AE413" t="n">
         <v>1793.216269116398</v>
       </c>
+      <c r="AF413" t="inlineStr"/>
+      <c r="AG413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" s="2" t="n">
@@ -36132,6 +36966,8 @@
       <c r="AE414" t="n">
         <v>1821.692056435764</v>
       </c>
+      <c r="AF414" t="inlineStr"/>
+      <c r="AG414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" s="2" t="n">
@@ -36219,6 +37055,8 @@
       <c r="AE415" t="n">
         <v>1802.372149115527</v>
       </c>
+      <c r="AF415" t="inlineStr"/>
+      <c r="AG415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n">
@@ -36306,6 +37144,8 @@
       <c r="AE416" t="n">
         <v>1818.489998258178</v>
       </c>
+      <c r="AF416" t="inlineStr"/>
+      <c r="AG416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n">
@@ -36393,6 +37233,8 @@
       <c r="AE417" t="n">
         <v>1873.312843283375</v>
       </c>
+      <c r="AF417" t="inlineStr"/>
+      <c r="AG417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n">
@@ -36480,6 +37322,8 @@
       <c r="AE418" t="n">
         <v>1964.799827977663</v>
       </c>
+      <c r="AF418" t="inlineStr"/>
+      <c r="AG418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n">
@@ -36567,6 +37411,8 @@
       <c r="AE419" t="n">
         <v>1985.071558042214</v>
       </c>
+      <c r="AF419" t="inlineStr"/>
+      <c r="AG419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" s="2" t="n">
@@ -36654,6 +37500,8 @@
       <c r="AE420" t="n">
         <v>1976.053406613544</v>
       </c>
+      <c r="AF420" t="inlineStr"/>
+      <c r="AG420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" s="2" t="n">
@@ -36741,6 +37589,8 @@
       <c r="AE421" t="n">
         <v>2018.465057541782</v>
       </c>
+      <c r="AF421" t="inlineStr"/>
+      <c r="AG421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" s="2" t="n">
@@ -36828,6 +37678,8 @@
       <c r="AE422" t="n">
         <v>2034.833244806101</v>
       </c>
+      <c r="AF422" t="inlineStr"/>
+      <c r="AG422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" s="2" t="n">
@@ -36915,6 +37767,8 @@
       <c r="AE423" t="n">
         <v>2036.142264987879</v>
       </c>
+      <c r="AF423" t="inlineStr"/>
+      <c r="AG423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" s="2" t="n">
@@ -37002,6 +37856,8 @@
       <c r="AE424" t="n">
         <v>2083.486409918846</v>
       </c>
+      <c r="AF424" t="inlineStr"/>
+      <c r="AG424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" s="2" t="n">
@@ -37089,6 +37945,8 @@
       <c r="AE425" t="n">
         <v>2108.542017909009</v>
       </c>
+      <c r="AF425" t="inlineStr"/>
+      <c r="AG425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" s="2" t="n">
@@ -37176,6 +38034,8 @@
       <c r="AE426" t="n">
         <v>2099.617238052826</v>
       </c>
+      <c r="AF426" t="inlineStr"/>
+      <c r="AG426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" s="2" t="n">
@@ -37263,6 +38123,8 @@
       <c r="AE427" t="n">
         <v>2106.313113643076</v>
       </c>
+      <c r="AF427" t="inlineStr"/>
+      <c r="AG427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" s="2" t="n">
@@ -37350,6 +38212,8 @@
       <c r="AE428" t="n">
         <v>2202.254843681347</v>
       </c>
+      <c r="AF428" t="inlineStr"/>
+      <c r="AG428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" s="2" t="n">
@@ -37437,6 +38301,8 @@
       <c r="AE429" t="n">
         <v>2218.929181801444</v>
       </c>
+      <c r="AF429" t="inlineStr"/>
+      <c r="AG429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" s="2" t="n">
@@ -37524,6 +38390,8 @@
       <c r="AE430" t="n">
         <v>2260.820887548792</v>
       </c>
+      <c r="AF430" t="inlineStr"/>
+      <c r="AG430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" s="2" t="n">
@@ -37611,6 +38479,8 @@
       <c r="AE431" t="n">
         <v>2161.234980461623</v>
       </c>
+      <c r="AF431" t="inlineStr"/>
+      <c r="AG431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" s="2" t="n">
@@ -37698,6 +38568,8 @@
       <c r="AE432" t="n">
         <v>2136.065559172193</v>
       </c>
+      <c r="AF432" t="inlineStr"/>
+      <c r="AG432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" s="2" t="n">
@@ -37785,6 +38657,8 @@
       <c r="AE433" t="n">
         <v>2150.676870768801</v>
       </c>
+      <c r="AF433" t="inlineStr"/>
+      <c r="AG433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" s="2" t="n">
@@ -37872,6 +38746,8 @@
       <c r="AE434" t="n">
         <v>2155.601022649493</v>
       </c>
+      <c r="AF434" t="inlineStr"/>
+      <c r="AG434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" s="2" t="n">
@@ -37959,6 +38835,8 @@
       <c r="AE435" t="n">
         <v>2190.724849065359</v>
       </c>
+      <c r="AF435" t="inlineStr"/>
+      <c r="AG435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" s="2" t="n">
@@ -38046,6 +38924,8 @@
       <c r="AE436" t="n">
         <v>2137.951849303653</v>
       </c>
+      <c r="AF436" t="inlineStr"/>
+      <c r="AG436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" s="2" t="n">
@@ -38133,6 +39013,8 @@
       <c r="AE437" t="n">
         <v>2134.216656503218</v>
       </c>
+      <c r="AF437" t="inlineStr"/>
+      <c r="AG437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" s="2" t="n">
@@ -38220,6 +39102,8 @@
       <c r="AE438" t="n">
         <v>2113.901535913568</v>
       </c>
+      <c r="AF438" t="inlineStr"/>
+      <c r="AG438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" s="2" t="n">
@@ -38307,6 +39191,8 @@
       <c r="AE439" t="n">
         <v>2064.133568282727</v>
       </c>
+      <c r="AF439" t="inlineStr"/>
+      <c r="AG439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" s="2" t="n">
@@ -38394,6 +39280,8 @@
       <c r="AE440" t="n">
         <v>2001.648729009766</v>
       </c>
+      <c r="AF440" t="inlineStr"/>
+      <c r="AG440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" s="2" t="n">
@@ -38481,6 +39369,8 @@
       <c r="AE441" t="n">
         <v>1977.988731698533</v>
       </c>
+      <c r="AF441" t="inlineStr"/>
+      <c r="AG441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" s="2" t="n">
@@ -38568,6 +39458,8 @@
       <c r="AE442" t="n">
         <v>2022.817950214175</v>
       </c>
+      <c r="AF442" t="inlineStr"/>
+      <c r="AG442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" s="2" t="n">
@@ -38655,6 +39547,8 @@
       <c r="AE443" t="n">
         <v>2073.25804087796</v>
       </c>
+      <c r="AF443" t="inlineStr"/>
+      <c r="AG443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" s="2" t="n">
@@ -38742,6 +39636,8 @@
       <c r="AE444" t="n">
         <v>2032.237986510147</v>
       </c>
+      <c r="AF444" t="inlineStr"/>
+      <c r="AG444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" s="2" t="n">
@@ -38829,6 +39725,8 @@
       <c r="AE445" t="n">
         <v>2068.651375348304</v>
       </c>
+      <c r="AF445" t="inlineStr"/>
+      <c r="AG445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" s="2" t="n">
@@ -38916,6 +39814,8 @@
       <c r="AE446" t="n">
         <v>2137.090642668195</v>
       </c>
+      <c r="AF446" t="inlineStr"/>
+      <c r="AG446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" s="2" t="n">
@@ -39003,6 +39903,8 @@
       <c r="AE447" t="n">
         <v>2141.907099609411</v>
       </c>
+      <c r="AF447" t="inlineStr"/>
+      <c r="AG447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" s="2" t="n">
@@ -39090,6 +39992,8 @@
       <c r="AE448" t="n">
         <v>2170.54574827892</v>
       </c>
+      <c r="AF448" t="inlineStr"/>
+      <c r="AG448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" s="2" t="n">
@@ -39177,6 +40081,8 @@
       <c r="AE449" t="n">
         <v>2199.125904166428</v>
       </c>
+      <c r="AF449" t="inlineStr"/>
+      <c r="AG449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" s="2" t="n">
@@ -39264,6 +40170,8 @@
       <c r="AE450" t="n">
         <v>2172.999846377275</v>
       </c>
+      <c r="AF450" t="inlineStr"/>
+      <c r="AG450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" s="2" t="n">
@@ -39351,6 +40259,8 @@
       <c r="AE451" t="n">
         <v>2279.41132775804</v>
       </c>
+      <c r="AF451" t="inlineStr"/>
+      <c r="AG451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" s="2" t="n">
@@ -39438,6 +40348,8 @@
       <c r="AE452" t="n">
         <v>2344.451602572868</v>
       </c>
+      <c r="AF452" t="inlineStr"/>
+      <c r="AG452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" s="2" t="n">
@@ -39525,6 +40437,8 @@
       <c r="AE453" t="n">
         <v>2227.506783693061</v>
       </c>
+      <c r="AF453" t="inlineStr"/>
+      <c r="AG453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" s="2" t="n">
@@ -39612,6 +40526,8 @@
       <c r="AE454" t="n">
         <v>2193.718081816578</v>
       </c>
+      <c r="AF454" t="inlineStr"/>
+      <c r="AG454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" s="2" t="n">
@@ -39699,6 +40615,8 @@
       <c r="AE455" t="n">
         <v>2203.134166553241</v>
       </c>
+      <c r="AF455" t="inlineStr"/>
+      <c r="AG455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" s="2" t="n">
@@ -39786,6 +40704,8 @@
       <c r="AE456" t="n">
         <v>2209.320570833494</v>
       </c>
+      <c r="AF456" t="inlineStr"/>
+      <c r="AG456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" s="2" t="n">
@@ -39873,6 +40793,8 @@
       <c r="AE457" t="n">
         <v>2157.908734425898</v>
       </c>
+      <c r="AF457" t="inlineStr"/>
+      <c r="AG457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" s="2" t="n">
@@ -39960,6 +40882,8 @@
       <c r="AE458" t="n">
         <v>2083.882573732221</v>
       </c>
+      <c r="AF458" t="inlineStr"/>
+      <c r="AG458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" s="2" t="n">
@@ -40047,6 +40971,8 @@
       <c r="AE459" t="n">
         <v>2151.638376112543</v>
       </c>
+      <c r="AF459" t="inlineStr"/>
+      <c r="AG459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" s="2" t="n">
@@ -40134,6 +41060,8 @@
       <c r="AE460" t="n">
         <v>1909.328991503995</v>
       </c>
+      <c r="AF460" t="inlineStr"/>
+      <c r="AG460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" s="2" t="n">
@@ -40221,6 +41149,8 @@
       <c r="AE461" t="n">
         <v>2258.534282593445</v>
       </c>
+      <c r="AF461" t="inlineStr"/>
+      <c r="AG461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" s="2" t="n">
@@ -40308,6 +41238,8 @@
       <c r="AE462" t="n">
         <v>2240.855547317596</v>
       </c>
+      <c r="AF462" t="inlineStr"/>
+      <c r="AG462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" s="2" t="n">
@@ -40395,6 +41327,8 @@
       <c r="AE463" t="n">
         <v>2220.086923177616</v>
       </c>
+      <c r="AF463" t="inlineStr"/>
+      <c r="AG463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" s="2" t="n">
@@ -40482,6 +41416,8 @@
       <c r="AE464" t="n">
         <v>2098.815578638913</v>
       </c>
+      <c r="AF464" t="inlineStr"/>
+      <c r="AG464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" s="2" t="n">
@@ -40569,6 +41505,8 @@
       <c r="AE465" t="n">
         <v>2160.901825758922</v>
       </c>
+      <c r="AF465" t="inlineStr"/>
+      <c r="AG465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" s="2" t="n">
@@ -40656,6 +41594,8 @@
       <c r="AE466" t="n">
         <v>2154.917159463049</v>
       </c>
+      <c r="AF466" t="inlineStr"/>
+      <c r="AG466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" s="2" t="n">
@@ -40743,6 +41683,8 @@
       <c r="AE467" t="n">
         <v>2189.427813296947</v>
       </c>
+      <c r="AF467" t="inlineStr"/>
+      <c r="AG467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" s="2" t="n">
@@ -40830,6 +41772,8 @@
       <c r="AE468" t="n">
         <v>2108.747062148099</v>
       </c>
+      <c r="AF468" t="inlineStr"/>
+      <c r="AG468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" s="2" t="n">
@@ -40917,6 +41861,8 @@
       <c r="AE469" t="n">
         <v>2113.378327657218</v>
       </c>
+      <c r="AF469" t="inlineStr"/>
+      <c r="AG469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" s="2" t="n">
@@ -41006,6 +41952,8 @@
       <c r="AE470" t="n">
         <v>2112.568267245224</v>
       </c>
+      <c r="AF470" t="inlineStr"/>
+      <c r="AG470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" s="2" t="n">
@@ -41095,6 +42043,8 @@
       <c r="AE471" t="n">
         <v>2103.439633682087</v>
       </c>
+      <c r="AF471" t="inlineStr"/>
+      <c r="AG471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" s="2" t="n">
@@ -41184,6 +42134,8 @@
       <c r="AE472" t="n">
         <v>2125.246919086833</v>
       </c>
+      <c r="AF472" t="inlineStr"/>
+      <c r="AG472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" s="2" t="n">
@@ -41273,6 +42225,8 @@
       <c r="AE473" t="n">
         <v>2136.76052781092</v>
       </c>
+      <c r="AF473" t="inlineStr"/>
+      <c r="AG473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" s="2" t="n">
@@ -41362,6 +42316,8 @@
       <c r="AE474" t="n">
         <v>2106.354530524926</v>
       </c>
+      <c r="AF474" t="inlineStr"/>
+      <c r="AG474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" s="2" t="n">
@@ -41451,6 +42407,8 @@
       <c r="AE475" t="n">
         <v>2098.484339366055</v>
       </c>
+      <c r="AF475" t="inlineStr"/>
+      <c r="AG475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" s="2" t="n">
@@ -41540,6 +42498,8 @@
       <c r="AE476" t="n">
         <v>2038.910042869343</v>
       </c>
+      <c r="AF476" t="inlineStr"/>
+      <c r="AG476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" s="2" t="n">
@@ -41629,6 +42589,8 @@
       <c r="AE477" t="n">
         <v>2103.013800222152</v>
       </c>
+      <c r="AF477" t="inlineStr"/>
+      <c r="AG477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" s="2" t="n">
@@ -41718,6 +42680,8 @@
       <c r="AE478" t="n">
         <v>2113.443417834197</v>
       </c>
+      <c r="AF478" t="inlineStr"/>
+      <c r="AG478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" s="2" t="n">
@@ -41807,6 +42771,8 @@
       <c r="AE479" t="n">
         <v>2120.957732523177</v>
       </c>
+      <c r="AF479" t="inlineStr"/>
+      <c r="AG479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" s="2" t="n">
@@ -41896,6 +42862,8 @@
       <c r="AE480" t="n">
         <v>2153.027616650447</v>
       </c>
+      <c r="AF480" t="inlineStr"/>
+      <c r="AG480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" s="2" t="n">
@@ -41985,6 +42953,8 @@
       <c r="AE481" t="n">
         <v>2191.357683716839</v>
       </c>
+      <c r="AF481" t="inlineStr"/>
+      <c r="AG481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" s="2" t="n">
@@ -42074,6 +43044,8 @@
       <c r="AE482" t="n">
         <v>2219.515515147111</v>
       </c>
+      <c r="AF482" t="inlineStr"/>
+      <c r="AG482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" s="2" t="n">
@@ -42163,6 +43135,8 @@
       <c r="AE483" t="n">
         <v>2210.304914007587</v>
       </c>
+      <c r="AF483" t="inlineStr"/>
+      <c r="AG483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" s="2" t="n">
@@ -42252,6 +43226,8 @@
       <c r="AE484" t="n">
         <v>2197.786462736585</v>
       </c>
+      <c r="AF484" t="inlineStr"/>
+      <c r="AG484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" s="2" t="n">
@@ -42341,6 +43317,8 @@
       <c r="AE485" t="n">
         <v>2180.762138894472</v>
       </c>
+      <c r="AF485" t="inlineStr"/>
+      <c r="AG485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" s="2" t="n">
@@ -42430,6 +43408,8 @@
       <c r="AE486" t="n">
         <v>2187.944303937115</v>
       </c>
+      <c r="AF486" t="inlineStr"/>
+      <c r="AG486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" s="2" t="n">
@@ -42519,6 +43499,8 @@
       <c r="AE487" t="n">
         <v>2189.79335538551</v>
       </c>
+      <c r="AF487" t="inlineStr"/>
+      <c r="AG487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" s="2" t="n">
@@ -42608,6 +43590,8 @@
       <c r="AE488" t="n">
         <v>2219.599413428947</v>
       </c>
+      <c r="AF488" t="inlineStr"/>
+      <c r="AG488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" s="2" t="n">
@@ -42697,6 +43681,8 @@
       <c r="AE489" t="n">
         <v>2181.793806747809</v>
       </c>
+      <c r="AF489" t="inlineStr"/>
+      <c r="AG489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" s="2" t="n">
@@ -42786,6 +43772,8 @@
       <c r="AE490" t="n">
         <v>2192.169618079853</v>
       </c>
+      <c r="AF490" t="inlineStr"/>
+      <c r="AG490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" s="2" t="n">
@@ -42875,6 +43863,8 @@
       <c r="AE491" t="n">
         <v>2173.717301109536</v>
       </c>
+      <c r="AF491" t="inlineStr"/>
+      <c r="AG491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" s="2" t="n">
@@ -42964,6 +43954,8 @@
       <c r="AE492" t="n">
         <v>2128.394173077171</v>
       </c>
+      <c r="AF492" t="inlineStr"/>
+      <c r="AG492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" s="2" t="n">
@@ -43053,6 +44045,8 @@
       <c r="AE493" t="n">
         <v>2107.987692473656</v>
       </c>
+      <c r="AF493" t="inlineStr"/>
+      <c r="AG493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" s="2" t="n">
@@ -43142,6 +44136,8 @@
       <c r="AE494" t="n">
         <v>2125.711910906628</v>
       </c>
+      <c r="AF494" t="inlineStr"/>
+      <c r="AG494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" s="2" t="n">
@@ -43231,6 +44227,8 @@
       <c r="AE495" t="n">
         <v>2063.791511205991</v>
       </c>
+      <c r="AF495" t="inlineStr"/>
+      <c r="AG495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" s="2" t="n">
@@ -43320,6 +44318,8 @@
       <c r="AE496" t="n">
         <v>2093.351415355541</v>
       </c>
+      <c r="AF496" t="inlineStr"/>
+      <c r="AG496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" s="2" t="n">
@@ -43409,6 +44409,8 @@
       <c r="AE497" t="n">
         <v>2094.20686583158</v>
       </c>
+      <c r="AF497" t="inlineStr"/>
+      <c r="AG497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" s="2" t="n">
@@ -43498,6 +44500,8 @@
       <c r="AE498" t="n">
         <v>2108.586190723217</v>
       </c>
+      <c r="AF498" t="inlineStr"/>
+      <c r="AG498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" s="2" t="n">
@@ -43551,6 +44555,8 @@
       <c r="AE499" t="n">
         <v>2126.892822000505</v>
       </c>
+      <c r="AF499" t="inlineStr"/>
+      <c r="AG499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" s="2" t="n">
@@ -43604,6 +44610,8 @@
       <c r="AE500" t="n">
         <v>2112.708343670658</v>
       </c>
+      <c r="AF500" t="inlineStr"/>
+      <c r="AG500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" s="2" t="n">
@@ -43657,6 +44665,8 @@
       <c r="AE501" t="n">
         <v>2188.747512344298</v>
       </c>
+      <c r="AF501" t="inlineStr"/>
+      <c r="AG501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" s="2" t="n">
@@ -43710,6 +44720,8 @@
       <c r="AE502" t="n">
         <v>2214.679924184721</v>
       </c>
+      <c r="AF502" t="inlineStr"/>
+      <c r="AG502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" s="2" t="n">
@@ -43763,6 +44775,8 @@
       <c r="AE503" t="n">
         <v>2234.106691040385</v>
       </c>
+      <c r="AF503" t="inlineStr"/>
+      <c r="AG503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" s="2" t="n">
@@ -43816,6 +44830,8 @@
       <c r="AE504" t="n">
         <v>2230.94269374406</v>
       </c>
+      <c r="AF504" t="inlineStr"/>
+      <c r="AG504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" s="2" t="n">
@@ -43905,6 +44921,8 @@
       <c r="AE505" t="n">
         <v>2245.280807108615</v>
       </c>
+      <c r="AF505" t="inlineStr"/>
+      <c r="AG505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" s="2" t="n">
@@ -43958,6 +44976,8 @@
       <c r="AE506" t="n">
         <v>2272.826653349826</v>
       </c>
+      <c r="AF506" t="inlineStr"/>
+      <c r="AG506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" s="2" t="n">
@@ -44011,6 +45031,8 @@
       <c r="AE507" t="n">
         <v>2209.952099429805</v>
       </c>
+      <c r="AF507" t="inlineStr"/>
+      <c r="AG507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" s="2" t="n">
@@ -44064,6 +45086,8 @@
       <c r="AE508" t="n">
         <v>2242.769565502349</v>
       </c>
+      <c r="AF508" t="inlineStr"/>
+      <c r="AG508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" s="2" t="n">
@@ -44117,6 +45141,8 @@
       <c r="AE509" t="n">
         <v>2211.83595729533</v>
       </c>
+      <c r="AF509" t="inlineStr"/>
+      <c r="AG509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" s="2" t="n">
@@ -44170,6 +45196,8 @@
       <c r="AE510" t="n">
         <v>2044.90734627641</v>
       </c>
+      <c r="AF510" t="inlineStr"/>
+      <c r="AG510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" s="2" t="n">
@@ -44223,6 +45251,8 @@
       <c r="AE511" t="n">
         <v>2004.624939706665</v>
       </c>
+      <c r="AF511" t="inlineStr"/>
+      <c r="AG511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" s="2" t="n">
@@ -44276,6 +45306,8 @@
       <c r="AE512" t="n">
         <v>2078.259690502081</v>
       </c>
+      <c r="AF512" t="inlineStr"/>
+      <c r="AG512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" s="2" t="n">
@@ -44329,6 +45361,8 @@
       <c r="AE513" t="n">
         <v>2095.23104099705</v>
       </c>
+      <c r="AF513" t="inlineStr"/>
+      <c r="AG513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" s="2" t="n">
@@ -44382,6 +45416,8 @@
       <c r="AE514" t="n">
         <v>2052.491069103678</v>
       </c>
+      <c r="AF514" t="inlineStr"/>
+      <c r="AG514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" s="2" t="n">
@@ -44435,6 +45471,8 @@
       <c r="AE515" t="n">
         <v>2031.321754223382</v>
       </c>
+      <c r="AF515" t="inlineStr"/>
+      <c r="AG515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" s="2" t="n">
@@ -44488,6 +45526,8 @@
       <c r="AE516" t="n">
         <v>1988.239313600253</v>
       </c>
+      <c r="AF516" t="inlineStr"/>
+      <c r="AG516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" s="2" t="n">
@@ -44541,6 +45581,8 @@
       <c r="AE517" t="n">
         <v>1951.659925245096</v>
       </c>
+      <c r="AF517" t="inlineStr"/>
+      <c r="AG517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" s="2" t="n">
@@ -44594,6 +45636,8 @@
       <c r="AE518" t="n">
         <v>1968.131915135483</v>
       </c>
+      <c r="AF518" t="inlineStr"/>
+      <c r="AG518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" s="2" t="n">
@@ -44647,6 +45691,8 @@
       <c r="AE519" t="n">
         <v>2001.819401249928</v>
       </c>
+      <c r="AF519" t="inlineStr"/>
+      <c r="AG519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" s="2" t="n">
@@ -44700,6 +45746,8 @@
       <c r="AE520" t="n">
         <v>2028.602035390531</v>
       </c>
+      <c r="AF520" t="inlineStr"/>
+      <c r="AG520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" s="2" t="n">
@@ -44753,6 +45801,8 @@
       <c r="AE521" t="n">
         <v>1997.234279551072</v>
       </c>
+      <c r="AF521" t="inlineStr"/>
+      <c r="AG521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" s="2" t="n">
@@ -44806,6 +45856,8 @@
       <c r="AE522" t="n">
         <v>1987.286762402897</v>
       </c>
+      <c r="AF522" t="inlineStr"/>
+      <c r="AG522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" s="2" t="n">
@@ -44859,6 +45911,8 @@
       <c r="AE523" t="n">
         <v>2004.503304566288</v>
       </c>
+      <c r="AF523" t="inlineStr"/>
+      <c r="AG523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" s="2" t="n">
@@ -44912,6 +45966,8 @@
       <c r="AE524" t="n">
         <v>1995.699205892551</v>
       </c>
+      <c r="AF524" t="inlineStr"/>
+      <c r="AG524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" s="2" t="n">
@@ -44965,6 +46021,8 @@
       <c r="AE525" t="n">
         <v>1989.975224331769</v>
       </c>
+      <c r="AF525" t="inlineStr"/>
+      <c r="AG525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" s="2" t="n">
@@ -45018,6 +46076,8 @@
       <c r="AE526" t="n">
         <v>2033.152258273704</v>
       </c>
+      <c r="AF526" t="inlineStr"/>
+      <c r="AG526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" s="2" t="n">
@@ -45071,6 +46131,8 @@
       <c r="AE527" t="n">
         <v>2021.07174850717</v>
       </c>
+      <c r="AF527" t="inlineStr"/>
+      <c r="AG527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" s="2" t="n">
@@ -45124,6 +46186,8 @@
       <c r="AE528" t="n">
         <v>1999.088476692584</v>
       </c>
+      <c r="AF528" t="inlineStr"/>
+      <c r="AG528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" s="2" t="n">
@@ -45177,6 +46241,8 @@
       <c r="AE529" t="n">
         <v>1965.638618871186</v>
       </c>
+      <c r="AF529" t="inlineStr"/>
+      <c r="AG529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" s="2" t="n">
@@ -45230,6 +46296,8 @@
       <c r="AE530" t="n">
         <v>1934.058865208209</v>
       </c>
+      <c r="AF530" t="inlineStr"/>
+      <c r="AG530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" s="2" t="n">
@@ -45283,6 +46351,8 @@
       <c r="AE531" t="n">
         <v>1957.766720660573</v>
       </c>
+      <c r="AF531" t="inlineStr"/>
+      <c r="AG531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" s="2" t="n">
@@ -45336,6 +46406,8 @@
       <c r="AE532" t="n">
         <v>1967.313415740537</v>
       </c>
+      <c r="AF532" t="inlineStr"/>
+      <c r="AG532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" s="2" t="n">
@@ -45389,6 +46461,8 @@
       <c r="AE533" t="n">
         <v>1969.217634657179</v>
       </c>
+      <c r="AF533" t="inlineStr"/>
+      <c r="AG533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" s="2" t="n">
@@ -45442,6 +46516,8 @@
       <c r="AE534" t="n">
         <v>1856.917316977275</v>
       </c>
+      <c r="AF534" t="inlineStr"/>
+      <c r="AG534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" s="2" t="n">
@@ -45495,6 +46571,8 @@
       <c r="AE535" t="n">
         <v>1857.721413997464</v>
       </c>
+      <c r="AF535" t="inlineStr"/>
+      <c r="AG535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" s="2" t="n">
@@ -45548,6 +46626,8 @@
       <c r="AE536" t="n">
         <v>1885.022302747029</v>
       </c>
+      <c r="AF536" t="inlineStr"/>
+      <c r="AG536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" s="2" t="n">
@@ -45601,6 +46681,8 @@
       <c r="AE537" t="n">
         <v>1850.73910118266</v>
       </c>
+      <c r="AF537" t="inlineStr"/>
+      <c r="AG537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" s="2" t="n">
@@ -45654,6 +46736,8 @@
       <c r="AE538" t="n">
         <v>1909.153827956249</v>
       </c>
+      <c r="AF538" t="inlineStr"/>
+      <c r="AG538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" s="2" t="n">
@@ -45707,6 +46791,8 @@
       <c r="AE539" t="n">
         <v>1902.155130311744</v>
       </c>
+      <c r="AF539" t="inlineStr"/>
+      <c r="AG539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" s="2" t="n">
@@ -45760,6 +46846,8 @@
       <c r="AE540" t="n">
         <v>1903.120766616629</v>
       </c>
+      <c r="AF540" t="inlineStr"/>
+      <c r="AG540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" s="2" t="n">
@@ -45813,6 +46901,8 @@
       <c r="AE541" t="n">
         <v>1936.690953129875</v>
       </c>
+      <c r="AF541" t="inlineStr"/>
+      <c r="AG541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" s="2" t="n">
@@ -45866,6 +46956,8 @@
       <c r="AE542" t="n">
         <v>1922.213313330383</v>
       </c>
+      <c r="AF542" t="inlineStr"/>
+      <c r="AG542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" s="2" t="n">
@@ -45919,6 +47011,8 @@
       <c r="AE543" t="n">
         <v>1908.042399670285</v>
       </c>
+      <c r="AF543" t="inlineStr"/>
+      <c r="AG543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" s="2" t="n">
@@ -45972,6 +47066,8 @@
       <c r="AE544" t="n">
         <v>1890.817313391876</v>
       </c>
+      <c r="AF544" t="inlineStr"/>
+      <c r="AG544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" s="2" t="n">
@@ -46025,6 +47121,8 @@
       <c r="AE545" t="n">
         <v>1872.825268540986</v>
       </c>
+      <c r="AF545" t="inlineStr"/>
+      <c r="AG545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" s="2" t="n">
@@ -46078,6 +47176,8 @@
       <c r="AE546" t="n">
         <v>1889.928171224892</v>
       </c>
+      <c r="AF546" t="inlineStr"/>
+      <c r="AG546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" s="2" t="n">
@@ -46131,6 +47231,8 @@
       <c r="AE547" t="n">
         <v>1872.523647026367</v>
       </c>
+      <c r="AF547" t="inlineStr"/>
+      <c r="AG547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" s="2" t="n">
@@ -46184,6 +47286,8 @@
       <c r="AE548" t="n">
         <v>1861.196582327113</v>
       </c>
+      <c r="AF548" t="inlineStr"/>
+      <c r="AG548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" s="2" t="n">
@@ -46237,6 +47341,8 @@
       <c r="AE549" t="n">
         <v>1859.437910549965</v>
       </c>
+      <c r="AF549" t="inlineStr"/>
+      <c r="AG549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" s="2" t="n">
@@ -46290,6 +47396,8 @@
       <c r="AE550" t="n">
         <v>1833.264346950139</v>
       </c>
+      <c r="AF550" t="inlineStr"/>
+      <c r="AG550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" s="2" t="n">
@@ -46343,6 +47451,8 @@
       <c r="AE551" t="n">
         <v>1785.008111341774</v>
       </c>
+      <c r="AF551" t="inlineStr"/>
+      <c r="AG551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" s="2" t="n">
@@ -46396,6 +47506,8 @@
       <c r="AE552" t="n">
         <v>1754.598070631351</v>
       </c>
+      <c r="AF552" t="inlineStr"/>
+      <c r="AG552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" s="2" t="n">
@@ -46449,6 +47561,8 @@
       <c r="AE553" t="n">
         <v>1741.58453869891</v>
       </c>
+      <c r="AF553" t="inlineStr"/>
+      <c r="AG553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" s="2" t="n">
@@ -46502,6 +47616,8 @@
       <c r="AE554" t="n">
         <v>1751.358384433655</v>
       </c>
+      <c r="AF554" t="inlineStr"/>
+      <c r="AG554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" s="2" t="n">
@@ -46555,6 +47671,8 @@
       <c r="AE555" t="n">
         <v>1757.386195721643</v>
       </c>
+      <c r="AF555" t="inlineStr"/>
+      <c r="AG555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" s="2" t="n">
@@ -46608,6 +47726,8 @@
       <c r="AE556" t="n">
         <v>1754.635400650817</v>
       </c>
+      <c r="AF556" t="inlineStr"/>
+      <c r="AG556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" s="2" t="n">
@@ -46661,6 +47781,8 @@
       <c r="AE557" t="n">
         <v>1780.181806940675</v>
       </c>
+      <c r="AF557" t="inlineStr"/>
+      <c r="AG557" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" s="2" t="n">
@@ -46714,6 +47836,8 @@
       <c r="AE558" t="n">
         <v>1799.491928870578</v>
       </c>
+      <c r="AF558" t="inlineStr"/>
+      <c r="AG558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" s="2" t="n">
@@ -46767,6 +47891,8 @@
       <c r="AE559" t="n">
         <v>1801.998067405033</v>
       </c>
+      <c r="AF559" t="inlineStr"/>
+      <c r="AG559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" s="2" t="n">
@@ -46822,6 +47948,8 @@
       <c r="AE560" t="n">
         <v>1797.315056585564</v>
       </c>
+      <c r="AF560" t="inlineStr"/>
+      <c r="AG560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" s="2" t="n">
@@ -46877,6 +48005,8 @@
       <c r="AE561" t="n">
         <v>1797.411494762992</v>
       </c>
+      <c r="AF561" t="inlineStr"/>
+      <c r="AG561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" s="2" t="n">
@@ -46932,6 +48062,8 @@
       <c r="AE562" t="n">
         <v>1756.188200197959</v>
       </c>
+      <c r="AF562" t="inlineStr"/>
+      <c r="AG562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" s="2" t="n">
@@ -46987,6 +48119,8 @@
       <c r="AE563" t="n">
         <v>1790.330930828904</v>
       </c>
+      <c r="AF563" t="inlineStr"/>
+      <c r="AG563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" s="2" t="n">
@@ -47042,6 +48176,8 @@
       <c r="AE564" t="n">
         <v>1795.838384195486</v>
       </c>
+      <c r="AF564" t="inlineStr"/>
+      <c r="AG564" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" s="2" t="n">
@@ -47097,6 +48233,8 @@
       <c r="AE565" t="n">
         <v>1823.665932405663</v>
       </c>
+      <c r="AF565" t="inlineStr"/>
+      <c r="AG565" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" s="2" t="n">
@@ -47152,6 +48290,8 @@
       <c r="AE566" t="n">
         <v>1812.855748625414</v>
       </c>
+      <c r="AF566" t="inlineStr"/>
+      <c r="AG566" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" s="2" t="n">
@@ -47207,6 +48347,8 @@
       <c r="AE567" t="n">
         <v>1820.212708400568</v>
       </c>
+      <c r="AF567" t="inlineStr"/>
+      <c r="AG567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" s="2" t="n">
@@ -47262,6 +48404,8 @@
       <c r="AE568" t="n">
         <v>1820.727044461298</v>
       </c>
+      <c r="AF568" t="inlineStr"/>
+      <c r="AG568" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" s="2" t="n">
@@ -47317,6 +48461,8 @@
       <c r="AE569" t="n">
         <v>1796.174453645289</v>
       </c>
+      <c r="AF569" t="inlineStr"/>
+      <c r="AG569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" s="2" t="n">
@@ -47372,6 +48518,8 @@
       <c r="AE570" t="n">
         <v>1806.978953990484</v>
       </c>
+      <c r="AF570" t="inlineStr"/>
+      <c r="AG570" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" s="2" t="n">
@@ -47427,6 +48575,8 @@
       <c r="AE571" t="n">
         <v>1791.565827491404</v>
       </c>
+      <c r="AF571" t="inlineStr"/>
+      <c r="AG571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" s="2" t="n">
@@ -47482,6 +48632,8 @@
       <c r="AE572" t="n">
         <v>1796.264079959555</v>
       </c>
+      <c r="AF572" t="inlineStr"/>
+      <c r="AG572" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" s="2" t="n">
@@ -47537,6 +48689,8 @@
       <c r="AE573" t="n">
         <v>1754.028788382367</v>
       </c>
+      <c r="AF573" t="inlineStr"/>
+      <c r="AG573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" s="2" t="n">
@@ -47592,6 +48746,8 @@
       <c r="AE574" t="n">
         <v>1739.905593606647</v>
       </c>
+      <c r="AF574" t="inlineStr"/>
+      <c r="AG574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" s="2" t="n">
@@ -47647,6 +48803,8 @@
       <c r="AE575" t="n">
         <v>1765.260524099953</v>
       </c>
+      <c r="AF575" t="inlineStr"/>
+      <c r="AG575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" s="2" t="n">
@@ -47702,6 +48860,8 @@
       <c r="AE576" t="n">
         <v>1765.140114470194</v>
       </c>
+      <c r="AF576" t="inlineStr"/>
+      <c r="AG576" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" s="2" t="n">
@@ -47757,6 +48917,8 @@
       <c r="AE577" t="n">
         <v>1782.882014793393</v>
       </c>
+      <c r="AF577" t="inlineStr"/>
+      <c r="AG577" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" s="2" t="n">
@@ -47812,6 +48974,8 @@
       <c r="AE578" t="n">
         <v>1771.871493730142</v>
       </c>
+      <c r="AF578" t="inlineStr"/>
+      <c r="AG578" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" s="2" t="n">
@@ -47867,6 +49031,8 @@
       <c r="AE579" t="n">
         <v>1767.382505818346</v>
       </c>
+      <c r="AF579" t="inlineStr"/>
+      <c r="AG579" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" s="2" t="n">
@@ -47922,6 +49088,8 @@
       <c r="AE580" t="n">
         <v>1781.504636480651</v>
       </c>
+      <c r="AF580" t="inlineStr"/>
+      <c r="AG580" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" s="2" t="n">
@@ -47977,6 +49145,8 @@
       <c r="AE581" t="n">
         <v>1793.380930511436</v>
       </c>
+      <c r="AF581" t="inlineStr"/>
+      <c r="AG581" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" s="2" t="n">
@@ -48032,6 +49202,8 @@
       <c r="AE582" t="n">
         <v>1826.568965254055</v>
       </c>
+      <c r="AF582" t="inlineStr"/>
+      <c r="AG582" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" s="2" t="n">
@@ -48087,6 +49259,8 @@
       <c r="AE583" t="n">
         <v>1805.5607369448</v>
       </c>
+      <c r="AF583" t="inlineStr"/>
+      <c r="AG583" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" s="2" t="n">
@@ -48142,6 +49316,8 @@
       <c r="AE584" t="n">
         <v>1797.694213599123</v>
       </c>
+      <c r="AF584" t="inlineStr"/>
+      <c r="AG584" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" s="2" t="n">
@@ -48197,6 +49373,8 @@
       <c r="AE585" t="n">
         <v>1782.531235131914</v>
       </c>
+      <c r="AF585" t="inlineStr"/>
+      <c r="AG585" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" s="2" t="n">
@@ -48252,6 +49430,8 @@
       <c r="AE586" t="n">
         <v>1773.187923916511</v>
       </c>
+      <c r="AF586" t="inlineStr"/>
+      <c r="AG586" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" s="2" t="n">
@@ -48307,6 +49487,8 @@
       <c r="AE587" t="n">
         <v>1777.810309009133</v>
       </c>
+      <c r="AF587" t="inlineStr"/>
+      <c r="AG587" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" s="2" t="n">
@@ -48362,6 +49544,8 @@
       <c r="AE588" t="n">
         <v>1812.680664017623</v>
       </c>
+      <c r="AF588" t="inlineStr"/>
+      <c r="AG588" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" s="2" t="n">
@@ -48417,6 +49601,8 @@
       <c r="AE589" t="n">
         <v>1814.055148165406</v>
       </c>
+      <c r="AF589" t="inlineStr"/>
+      <c r="AG589" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" s="2" t="n">
@@ -48472,6 +49658,8 @@
       <c r="AE590" t="n">
         <v>1811.947750612122</v>
       </c>
+      <c r="AF590" t="inlineStr"/>
+      <c r="AG590" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" s="2" t="n">
@@ -48527,6 +49715,8 @@
       <c r="AE591" t="n">
         <v>1820.403490321533</v>
       </c>
+      <c r="AF591" t="inlineStr"/>
+      <c r="AG591" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" s="2" t="n">
@@ -48582,6 +49772,8 @@
       <c r="AE592" t="n">
         <v>1807.686745244267</v>
       </c>
+      <c r="AF592" t="inlineStr"/>
+      <c r="AG592" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" s="2" t="n">
@@ -48635,6 +49827,8 @@
       <c r="AE593" t="n">
         <v>1825.091817413493</v>
       </c>
+      <c r="AF593" t="inlineStr"/>
+      <c r="AG593" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" s="2" t="n">
@@ -48688,6 +49882,8 @@
       <c r="AE594" t="n">
         <v>1840.031392285577</v>
       </c>
+      <c r="AF594" t="inlineStr"/>
+      <c r="AG594" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" s="2" t="n">
@@ -48741,6 +49937,8 @@
       <c r="AE595" t="n">
         <v>1876.409017168803</v>
       </c>
+      <c r="AF595" t="inlineStr"/>
+      <c r="AG595" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" s="2" t="n">
@@ -48794,6 +49992,8 @@
       <c r="AE596" t="n">
         <v>1872.271046336702</v>
       </c>
+      <c r="AF596" t="inlineStr"/>
+      <c r="AG596" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" s="2" t="n">
@@ -48847,6 +50047,8 @@
       <c r="AE597" t="n">
         <v>1869.418297099098</v>
       </c>
+      <c r="AF597" t="inlineStr"/>
+      <c r="AG597" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" s="2" t="n">
@@ -48900,6 +50102,8 @@
       <c r="AE598" t="n">
         <v>1881.707956330215</v>
       </c>
+      <c r="AF598" t="inlineStr"/>
+      <c r="AG598" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" s="2" t="n">
@@ -48953,6 +50157,8 @@
       <c r="AE599" t="n">
         <v>1895.811083908858</v>
       </c>
+      <c r="AF599" t="inlineStr"/>
+      <c r="AG599" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" s="2" t="n">
@@ -49006,6 +50212,8 @@
       <c r="AE600" t="n">
         <v>1876.443860979936</v>
       </c>
+      <c r="AF600" t="inlineStr"/>
+      <c r="AG600" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" s="2" t="n">
@@ -49059,6 +50267,8 @@
       <c r="AE601" t="n">
         <v>1895.026642768046</v>
       </c>
+      <c r="AF601" t="inlineStr"/>
+      <c r="AG601" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" s="2" t="n">
@@ -49112,6 +50322,8 @@
       <c r="AE602" t="n">
         <v>1917.45840836555</v>
       </c>
+      <c r="AF602" t="inlineStr"/>
+      <c r="AG602" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" s="2" t="n">
@@ -49165,6 +50377,8 @@
       <c r="AE603" t="n">
         <v>1901.813836812291</v>
       </c>
+      <c r="AF603" t="inlineStr"/>
+      <c r="AG603" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" s="2" t="n">
@@ -49218,6 +50432,8 @@
       <c r="AE604" t="n">
         <v>1903.16731714994</v>
       </c>
+      <c r="AF604" t="inlineStr"/>
+      <c r="AG604" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" s="2" t="n">
@@ -49271,6 +50487,8 @@
       <c r="AE605" t="n">
         <v>1956.137301202464</v>
       </c>
+      <c r="AF605" t="inlineStr"/>
+      <c r="AG605" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" s="2" t="n">
@@ -49324,6 +50542,8 @@
       <c r="AE606" t="n">
         <v>1945.199593805536</v>
       </c>
+      <c r="AF606" t="inlineStr"/>
+      <c r="AG606" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" s="2" t="n">
@@ -49377,6 +50597,8 @@
       <c r="AE607" t="n">
         <v>1981.74628812719</v>
       </c>
+      <c r="AF607" t="inlineStr"/>
+      <c r="AG607" t="inlineStr"/>
     </row>
     <row r="608">
       <c r="A608" s="2" t="n">
@@ -49430,6 +50652,8 @@
       <c r="AE608" t="n">
         <v>1967.18215438582</v>
       </c>
+      <c r="AF608" t="inlineStr"/>
+      <c r="AG608" t="inlineStr"/>
     </row>
     <row r="609">
       <c r="A609" s="2" t="n">
@@ -49483,6 +50707,8 @@
       <c r="AE609" t="n">
         <v>2016.639897913845</v>
       </c>
+      <c r="AF609" t="inlineStr"/>
+      <c r="AG609" t="inlineStr"/>
     </row>
     <row r="610">
       <c r="A610" s="2" t="n">
@@ -49536,6 +50762,8 @@
       <c r="AE610" t="n">
         <v>2005.556446471525</v>
       </c>
+      <c r="AF610" t="inlineStr"/>
+      <c r="AG610" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" s="2" t="n">
@@ -49589,6 +50817,8 @@
       <c r="AE611" t="n">
         <v>1969.650969565639</v>
       </c>
+      <c r="AF611" t="inlineStr"/>
+      <c r="AG611" t="inlineStr"/>
     </row>
     <row r="612">
       <c r="A612" s="2" t="n">
@@ -49642,6 +50872,8 @@
       <c r="AE612" t="n">
         <v>1876.020966348472</v>
       </c>
+      <c r="AF612" t="inlineStr"/>
+      <c r="AG612" t="inlineStr"/>
     </row>
     <row r="613">
       <c r="A613" s="2" t="n">
@@ -49695,6 +50927,8 @@
       <c r="AE613" t="n">
         <v>1890.998035065898</v>
       </c>
+      <c r="AF613" t="inlineStr"/>
+      <c r="AG613" t="inlineStr"/>
     </row>
     <row r="614">
       <c r="A614" s="2" t="n">
@@ -49748,6 +50982,8 @@
       <c r="AE614" t="n">
         <v>1923.79195377328</v>
       </c>
+      <c r="AF614" t="inlineStr"/>
+      <c r="AG614" t="inlineStr"/>
     </row>
     <row r="615">
       <c r="A615" s="2" t="n">
@@ -49801,6 +51037,8 @@
       <c r="AE615" t="n">
         <v>1884.269034912238</v>
       </c>
+      <c r="AF615" t="inlineStr"/>
+      <c r="AG615" t="inlineStr"/>
     </row>
     <row r="616">
       <c r="A616" s="2" t="n">
@@ -49854,6 +51092,8 @@
       <c r="AE616" t="n">
         <v>1870.375907626861</v>
       </c>
+      <c r="AF616" t="inlineStr"/>
+      <c r="AG616" t="inlineStr"/>
     </row>
     <row r="617">
       <c r="A617" s="2" t="n">
@@ -49907,6 +51147,8 @@
       <c r="AE617" t="n">
         <v>1863.380970903366</v>
       </c>
+      <c r="AF617" t="inlineStr"/>
+      <c r="AG617" t="inlineStr"/>
     </row>
     <row r="618">
       <c r="A618" s="2" t="n">
@@ -49960,6 +51202,8 @@
       <c r="AE618" t="n">
         <v>1873.599736099972</v>
       </c>
+      <c r="AF618" t="inlineStr"/>
+      <c r="AG618" t="inlineStr"/>
     </row>
     <row r="619">
       <c r="A619" s="2" t="n">
@@ -50013,6 +51257,8 @@
       <c r="AE619" t="n">
         <v>1866.58898750614</v>
       </c>
+      <c r="AF619" t="inlineStr"/>
+      <c r="AG619" t="inlineStr"/>
     </row>
     <row r="620">
       <c r="A620" s="2" t="n">
@@ -50066,6 +51312,8 @@
       <c r="AE620" t="n">
         <v>1870.40784995795</v>
       </c>
+      <c r="AF620" t="inlineStr"/>
+      <c r="AG620" t="inlineStr"/>
     </row>
     <row r="621">
       <c r="A621" s="2" t="n">
@@ -50119,6 +51367,8 @@
       <c r="AE621" t="n">
         <v>1854.899888365838</v>
       </c>
+      <c r="AF621" t="inlineStr"/>
+      <c r="AG621" t="inlineStr"/>
     </row>
     <row r="622">
       <c r="A622" s="2" t="n">
@@ -50172,6 +51422,8 @@
       <c r="AE622" t="n">
         <v>1847.696939016764</v>
       </c>
+      <c r="AF622" t="inlineStr"/>
+      <c r="AG622" t="inlineStr"/>
     </row>
     <row r="623">
       <c r="A623" s="2" t="n">
@@ -50225,6 +51477,8 @@
       <c r="AE623" t="n">
         <v>1785.913968278472</v>
       </c>
+      <c r="AF623" t="inlineStr"/>
+      <c r="AG623" t="inlineStr"/>
     </row>
     <row r="624">
       <c r="A624" s="2" t="n">
@@ -50278,6 +51532,8 @@
       <c r="AE624" t="n">
         <v>1764.922057153506</v>
       </c>
+      <c r="AF624" t="inlineStr"/>
+      <c r="AG624" t="inlineStr"/>
     </row>
     <row r="625">
       <c r="A625" s="2" t="n">
@@ -50331,6 +51587,8 @@
       <c r="AE625" t="n">
         <v>1773.179472100889</v>
       </c>
+      <c r="AF625" t="inlineStr"/>
+      <c r="AG625" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" s="2" t="n">
@@ -50384,6 +51642,8 @@
       <c r="AE626" t="n">
         <v>1766.890188770043</v>
       </c>
+      <c r="AF626" t="inlineStr"/>
+      <c r="AG626" t="inlineStr"/>
     </row>
     <row r="627">
       <c r="A627" s="2" t="n">
@@ -50437,6 +51697,8 @@
       <c r="AE627" t="n">
         <v>1710.852319470338</v>
       </c>
+      <c r="AF627" t="inlineStr"/>
+      <c r="AG627" t="inlineStr"/>
     </row>
     <row r="628">
       <c r="A628" s="2" t="n">
@@ -50490,6 +51752,8 @@
       <c r="AE628" t="n">
         <v>1581.59666976694</v>
       </c>
+      <c r="AF628" t="inlineStr"/>
+      <c r="AG628" t="inlineStr"/>
     </row>
     <row r="629">
       <c r="A629" s="2" t="n">
@@ -50543,6 +51807,8 @@
       <c r="AE629" t="n">
         <v>1641.780668449919</v>
       </c>
+      <c r="AF629" t="inlineStr"/>
+      <c r="AG629" t="inlineStr"/>
     </row>
     <row r="630">
       <c r="A630" s="2" t="n">
@@ -50596,6 +51862,8 @@
       <c r="AE630" t="n">
         <v>1649.78015363296</v>
       </c>
+      <c r="AF630" t="inlineStr"/>
+      <c r="AG630" t="inlineStr"/>
     </row>
     <row r="631">
       <c r="A631" s="2" t="n">
@@ -50649,6 +51917,8 @@
       <c r="AE631" t="n">
         <v>1642.989964420336</v>
       </c>
+      <c r="AF631" t="inlineStr"/>
+      <c r="AG631" t="inlineStr"/>
     </row>
     <row r="632">
       <c r="A632" s="2" t="n">
@@ -50702,6 +51972,8 @@
       <c r="AE632" t="n">
         <v>1645.616580513148</v>
       </c>
+      <c r="AF632" t="inlineStr"/>
+      <c r="AG632" t="inlineStr"/>
     </row>
     <row r="633">
       <c r="A633" s="2" t="n">
@@ -50755,6 +52027,8 @@
       <c r="AE633" t="n">
         <v>1628.484544836647</v>
       </c>
+      <c r="AF633" t="inlineStr"/>
+      <c r="AG633" t="inlineStr"/>
     </row>
     <row r="634">
       <c r="A634" s="2" t="n">
@@ -50808,6 +52082,8 @@
       <c r="AE634" t="n">
         <v>1619.64198984929</v>
       </c>
+      <c r="AF634" t="inlineStr"/>
+      <c r="AG634" t="inlineStr"/>
     </row>
     <row r="635">
       <c r="A635" s="2" t="n">
@@ -50861,6 +52137,8 @@
       <c r="AE635" t="n">
         <v>1631.079133145373</v>
       </c>
+      <c r="AF635" t="inlineStr"/>
+      <c r="AG635" t="inlineStr"/>
     </row>
     <row r="636">
       <c r="A636" s="2" t="n">
@@ -50914,6 +52192,8 @@
       <c r="AE636" t="n">
         <v>1650.178098967956</v>
       </c>
+      <c r="AF636" t="inlineStr"/>
+      <c r="AG636" t="inlineStr"/>
     </row>
     <row r="637">
       <c r="A637" s="2" t="n">
@@ -50967,6 +52247,8 @@
       <c r="AE637" t="n">
         <v>1663.98421671788</v>
       </c>
+      <c r="AF637" t="inlineStr"/>
+      <c r="AG637" t="inlineStr"/>
     </row>
     <row r="638">
       <c r="A638" s="2" t="n">
@@ -51020,6 +52302,8 @@
       <c r="AE638" t="n">
         <v>1640.93732488906</v>
       </c>
+      <c r="AF638" t="inlineStr"/>
+      <c r="AG638" t="inlineStr"/>
     </row>
     <row r="639">
       <c r="A639" s="2" t="n">
@@ -51073,6 +52357,8 @@
       <c r="AE639" t="n">
         <v>1668.547873587541</v>
       </c>
+      <c r="AF639" t="inlineStr"/>
+      <c r="AG639" t="inlineStr"/>
     </row>
     <row r="640">
       <c r="A640" s="2" t="n">
@@ -51126,6 +52412,8 @@
       <c r="AE640" t="n">
         <v>1649.196952664876</v>
       </c>
+      <c r="AF640" t="inlineStr"/>
+      <c r="AG640" t="inlineStr"/>
     </row>
     <row r="641">
       <c r="A641" s="2" t="n">
@@ -51179,6 +52467,8 @@
       <c r="AE641" t="n">
         <v>1623.72773935969</v>
       </c>
+      <c r="AF641" t="inlineStr"/>
+      <c r="AG641" t="inlineStr"/>
     </row>
     <row r="642">
       <c r="A642" s="2" t="n">
@@ -51232,6 +52522,8 @@
       <c r="AE642" t="n">
         <v>1657.444792645828</v>
       </c>
+      <c r="AF642" t="inlineStr"/>
+      <c r="AG642" t="inlineStr"/>
     </row>
     <row r="643">
       <c r="A643" s="2" t="n">
@@ -51285,6 +52577,8 @@
       <c r="AE643" t="n">
         <v>1672.325877213099</v>
       </c>
+      <c r="AF643" t="inlineStr"/>
+      <c r="AG643" t="inlineStr"/>
     </row>
     <row r="644">
       <c r="A644" s="2" t="n">
@@ -51338,6 +52632,8 @@
       <c r="AE644" t="n">
         <v>1685.28113309328</v>
       </c>
+      <c r="AF644" t="inlineStr"/>
+      <c r="AG644" t="inlineStr"/>
     </row>
     <row r="645">
       <c r="A645" s="2" t="n">
@@ -51391,6 +52687,8 @@
       <c r="AE645" t="n">
         <v>1685.81512368675</v>
       </c>
+      <c r="AF645" t="inlineStr"/>
+      <c r="AG645" t="inlineStr"/>
     </row>
     <row r="646">
       <c r="A646" s="2" t="n">
@@ -51444,6 +52742,8 @@
       <c r="AE646" t="n">
         <v>1632.177977856067</v>
       </c>
+      <c r="AF646" t="inlineStr"/>
+      <c r="AG646" t="inlineStr"/>
     </row>
     <row r="647">
       <c r="A647" s="2" t="n">
@@ -51497,6 +52797,8 @@
       <c r="AE647" t="n">
         <v>1629.58996786662</v>
       </c>
+      <c r="AF647" t="inlineStr"/>
+      <c r="AG647" t="inlineStr"/>
     </row>
     <row r="648">
       <c r="A648" s="2" t="n">
@@ -51550,6 +52852,8 @@
       <c r="AE648" t="n">
         <v>1674.225695080013</v>
       </c>
+      <c r="AF648" t="inlineStr"/>
+      <c r="AG648" t="inlineStr"/>
     </row>
     <row r="649">
       <c r="A649" s="2" t="n">
@@ -51603,6 +52907,8 @@
       <c r="AE649" t="n">
         <v>1671.098474382101</v>
       </c>
+      <c r="AF649" t="inlineStr"/>
+      <c r="AG649" t="inlineStr"/>
     </row>
     <row r="650">
       <c r="A650" s="2" t="n">
@@ -51656,6 +52962,8 @@
       <c r="AE650" t="n">
         <v>1650.488120267825</v>
       </c>
+      <c r="AF650" t="inlineStr"/>
+      <c r="AG650" t="inlineStr"/>
     </row>
     <row r="651">
       <c r="A651" s="2" t="n">
@@ -51709,6 +53017,8 @@
       <c r="AE651" t="n">
         <v>1637.191131844089</v>
       </c>
+      <c r="AF651" t="inlineStr"/>
+      <c r="AG651" t="inlineStr"/>
     </row>
     <row r="652">
       <c r="A652" s="2" t="n">
@@ -51762,6 +53072,8 @@
       <c r="AE652" t="n">
         <v>1630.630912954237</v>
       </c>
+      <c r="AF652" t="inlineStr"/>
+      <c r="AG652" t="inlineStr"/>
     </row>
     <row r="653">
       <c r="A653" s="2" t="n">
@@ -51821,6 +53133,8 @@
       <c r="AE653" t="n">
         <v>1643.725963384239</v>
       </c>
+      <c r="AF653" t="inlineStr"/>
+      <c r="AG653" t="inlineStr"/>
     </row>
     <row r="654">
       <c r="A654" s="2" t="n">
@@ -51872,6 +53186,8 @@
       <c r="AE654" t="n">
         <v>1597.190814256115</v>
       </c>
+      <c r="AF654" t="inlineStr"/>
+      <c r="AG654" t="inlineStr"/>
     </row>
     <row r="655">
       <c r="A655" s="2" t="n">
@@ -51927,6 +53243,8 @@
       <c r="AE655" t="n">
         <v>1679.589847629503</v>
       </c>
+      <c r="AF655" t="inlineStr"/>
+      <c r="AG655" t="inlineStr"/>
     </row>
     <row r="656">
       <c r="A656" s="2" t="n">
@@ -51982,6 +53300,8 @@
       <c r="AE656" t="n">
         <v>1663.857838200622</v>
       </c>
+      <c r="AF656" t="inlineStr"/>
+      <c r="AG656" t="inlineStr"/>
     </row>
     <row r="657">
       <c r="A657" s="2" t="n">
@@ -52037,6 +53357,8 @@
       <c r="AE657" t="n">
         <v>1656.18369988462</v>
       </c>
+      <c r="AF657" t="inlineStr"/>
+      <c r="AG657" t="inlineStr"/>
     </row>
     <row r="658">
       <c r="A658" s="2" t="n">
@@ -52090,6 +53412,8 @@
       <c r="AE658" t="n">
         <v>1664.688531907511</v>
       </c>
+      <c r="AF658" t="inlineStr"/>
+      <c r="AG658" t="inlineStr"/>
     </row>
     <row r="659">
       <c r="A659" s="2" t="n">
@@ -52145,6 +53469,8 @@
       <c r="AE659" t="n">
         <v>1679.108957649627</v>
       </c>
+      <c r="AF659" t="inlineStr"/>
+      <c r="AG659" t="inlineStr"/>
     </row>
     <row r="660">
       <c r="A660" s="2" t="n">
@@ -52200,6 +53526,8 @@
       <c r="AE660" t="n">
         <v>1660.295765361538</v>
       </c>
+      <c r="AF660" t="inlineStr"/>
+      <c r="AG660" t="inlineStr"/>
     </row>
     <row r="661">
       <c r="A661" s="2" t="n">
@@ -52255,6 +53583,8 @@
       <c r="AE661" t="n">
         <v>1661.709571398806</v>
       </c>
+      <c r="AF661" t="inlineStr"/>
+      <c r="AG661" t="inlineStr"/>
     </row>
     <row r="662">
       <c r="A662" s="2" t="n">
@@ -52310,6 +53640,8 @@
       <c r="AE662" t="n">
         <v>1689.998435014512</v>
       </c>
+      <c r="AF662" t="inlineStr"/>
+      <c r="AG662" t="inlineStr"/>
     </row>
     <row r="663">
       <c r="A663" s="2" t="n">
@@ -52365,6 +53697,8 @@
       <c r="AE663" t="n">
         <v>1676.362926043586</v>
       </c>
+      <c r="AF663" t="inlineStr"/>
+      <c r="AG663" t="inlineStr"/>
     </row>
     <row r="664">
       <c r="A664" s="2" t="n">
@@ -52420,6 +53754,8 @@
       <c r="AE664" t="n">
         <v>1699.592603498892</v>
       </c>
+      <c r="AF664" t="inlineStr"/>
+      <c r="AG664" t="inlineStr"/>
     </row>
     <row r="665">
       <c r="A665" s="2" t="n">
@@ -52475,6 +53811,8 @@
       <c r="AE665" t="n">
         <v>1724.320658684199</v>
       </c>
+      <c r="AF665" t="inlineStr"/>
+      <c r="AG665" t="inlineStr"/>
     </row>
     <row r="666">
       <c r="A666" s="2" t="n">
@@ -52530,6 +53868,8 @@
       <c r="AE666" t="n">
         <v>1729.220561662285</v>
       </c>
+      <c r="AF666" t="inlineStr"/>
+      <c r="AG666" t="inlineStr"/>
     </row>
     <row r="667">
       <c r="A667" s="2" t="n">
@@ -52585,6 +53925,8 @@
       <c r="AE667" t="n">
         <v>1712.086203997368</v>
       </c>
+      <c r="AF667" t="inlineStr"/>
+      <c r="AG667" t="inlineStr"/>
     </row>
     <row r="668">
       <c r="A668" s="2" t="n">
@@ -52640,6 +53982,8 @@
       <c r="AE668" t="n">
         <v>1774.756744816122</v>
       </c>
+      <c r="AF668" t="inlineStr"/>
+      <c r="AG668" t="inlineStr"/>
     </row>
     <row r="669">
       <c r="A669" s="2" t="n">
@@ -52695,6 +54039,8 @@
       <c r="AE669" t="n">
         <v>1759.718294238082</v>
       </c>
+      <c r="AF669" t="inlineStr"/>
+      <c r="AG669" t="inlineStr"/>
     </row>
     <row r="670">
       <c r="A670" s="2" t="n">
@@ -52750,6 +54096,8 @@
       <c r="AE670" t="n">
         <v>1754.823048583596</v>
       </c>
+      <c r="AF670" t="inlineStr"/>
+      <c r="AG670" t="inlineStr"/>
     </row>
     <row r="671">
       <c r="A671" s="2" t="n">
@@ -52805,6 +54153,8 @@
       <c r="AE671" t="n">
         <v>1789.434539557943</v>
       </c>
+      <c r="AF671" t="inlineStr"/>
+      <c r="AG671" t="inlineStr"/>
     </row>
     <row r="672">
       <c r="A672" s="2" t="n">
@@ -52860,6 +54210,8 @@
       <c r="AE672" t="n">
         <v>1801.88424186847</v>
       </c>
+      <c r="AF672" t="inlineStr"/>
+      <c r="AG672" t="inlineStr"/>
     </row>
     <row r="673">
       <c r="A673" s="2" t="n">
@@ -52915,6 +54267,8 @@
       <c r="AE673" t="n">
         <v>1789.794843977073</v>
       </c>
+      <c r="AF673" t="inlineStr"/>
+      <c r="AG673" t="inlineStr"/>
     </row>
     <row r="674">
       <c r="A674" s="2" t="n">
@@ -52970,6 +54324,8 @@
       <c r="AE674" t="n">
         <v>1777.331780137271</v>
       </c>
+      <c r="AF674" t="inlineStr"/>
+      <c r="AG674" t="inlineStr"/>
     </row>
     <row r="675">
       <c r="A675" s="2" t="n">
@@ -53025,6 +54381,8 @@
       <c r="AE675" t="n">
         <v>1765.983317661192</v>
       </c>
+      <c r="AF675" t="inlineStr"/>
+      <c r="AG675" t="inlineStr"/>
     </row>
     <row r="676">
       <c r="A676" s="2" t="n">
@@ -53080,6 +54438,8 @@
       <c r="AE676" t="n">
         <v>1816.08299731634</v>
       </c>
+      <c r="AF676" t="inlineStr"/>
+      <c r="AG676" t="inlineStr"/>
     </row>
     <row r="677">
       <c r="A677" s="2" t="n">
@@ -53135,6 +54495,8 @@
       <c r="AE677" t="n">
         <v>1797.013659437038</v>
       </c>
+      <c r="AF677" t="inlineStr"/>
+      <c r="AG677" t="inlineStr"/>
     </row>
     <row r="678">
       <c r="A678" s="2" t="n">
@@ -53190,6 +54552,8 @@
       <c r="AE678" t="n">
         <v>1795.291654278344</v>
       </c>
+      <c r="AF678" t="inlineStr"/>
+      <c r="AG678" t="inlineStr"/>
     </row>
     <row r="679">
       <c r="A679" s="2" t="n">
@@ -53245,6 +54609,8 @@
       <c r="AE679" t="n">
         <v>1824.626772066266</v>
       </c>
+      <c r="AF679" t="inlineStr"/>
+      <c r="AG679" t="inlineStr"/>
     </row>
     <row r="680">
       <c r="A680" s="2" t="n">
@@ -53300,6 +54666,8 @@
       <c r="AE680" t="n">
         <v>1854.507504437861</v>
       </c>
+      <c r="AF680" t="inlineStr"/>
+      <c r="AG680" t="inlineStr"/>
     </row>
     <row r="681">
       <c r="A681" s="2" t="n">
@@ -53355,6 +54723,8 @@
       <c r="AE681" t="n">
         <v>1843.133128502824</v>
       </c>
+      <c r="AF681" t="inlineStr"/>
+      <c r="AG681" t="inlineStr"/>
     </row>
     <row r="682">
       <c r="A682" s="2" t="n">
@@ -53410,6 +54780,8 @@
       <c r="AE682" t="n">
         <v>1804.662362539307</v>
       </c>
+      <c r="AF682" t="inlineStr"/>
+      <c r="AG682" t="inlineStr"/>
     </row>
     <row r="683">
       <c r="A683" s="2" t="n">
@@ -53465,6 +54837,8 @@
       <c r="AE683" t="n">
         <v>1814.040785305502</v>
       </c>
+      <c r="AF683" t="inlineStr"/>
+      <c r="AG683" t="inlineStr"/>
     </row>
     <row r="684">
       <c r="A684" s="2" t="n">
@@ -53520,6 +54894,8 @@
       <c r="AE684" t="n">
         <v>1789.930266004969</v>
       </c>
+      <c r="AF684" t="inlineStr"/>
+      <c r="AG684" t="inlineStr"/>
     </row>
     <row r="685">
       <c r="A685" s="2" t="n">
@@ -53575,6 +54951,8 @@
       <c r="AE685" t="n">
         <v>1793.279291734917</v>
       </c>
+      <c r="AF685" t="inlineStr"/>
+      <c r="AG685" t="inlineStr"/>
     </row>
     <row r="686">
       <c r="A686" s="2" t="n">
@@ -53630,6 +55008,12 @@
       <c r="AE686" t="n">
         <v>1806.74986121936</v>
       </c>
+      <c r="AF686" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG686" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="687">
       <c r="A687" s="2" t="n">
@@ -53685,6 +55069,8 @@
       <c r="AE687" t="n">
         <v>1815.767555549379</v>
       </c>
+      <c r="AF687" t="inlineStr"/>
+      <c r="AG687" t="inlineStr"/>
     </row>
     <row r="688">
       <c r="A688" s="2" t="n">
@@ -53740,6 +55126,8 @@
       <c r="AE688" t="n">
         <v>1805.738250451649</v>
       </c>
+      <c r="AF688" t="inlineStr"/>
+      <c r="AG688" t="inlineStr"/>
     </row>
     <row r="689">
       <c r="A689" s="2" t="n">
@@ -53795,6 +55183,12 @@
       <c r="AE689" t="n">
         <v>1818.754520980976</v>
       </c>
+      <c r="AF689" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG689" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="690">
       <c r="A690" s="2" t="n">
@@ -53850,6 +55244,8 @@
       <c r="AE690" t="n">
         <v>1813.764837611313</v>
       </c>
+      <c r="AF690" t="inlineStr"/>
+      <c r="AG690" t="inlineStr"/>
     </row>
     <row r="691">
       <c r="A691" s="2" t="n">
@@ -53905,6 +55301,8 @@
       <c r="AE691" t="n">
         <v>1824.867355029248</v>
       </c>
+      <c r="AF691" t="inlineStr"/>
+      <c r="AG691" t="inlineStr"/>
     </row>
     <row r="692">
       <c r="A692" s="2" t="n">
@@ -53960,6 +55358,8 @@
       <c r="AE692" t="n">
         <v>1822.532302334152</v>
       </c>
+      <c r="AF692" t="inlineStr"/>
+      <c r="AG692" t="inlineStr"/>
     </row>
     <row r="693">
       <c r="A693" s="2" t="n">
@@ -54015,6 +55415,12 @@
       <c r="AE693" t="n">
         <v>1821.242207702637</v>
       </c>
+      <c r="AF693" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG693" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="694">
       <c r="A694" s="2" t="n">
@@ -54070,6 +55476,12 @@
       <c r="AE694" t="n">
         <v>1817.968785746911</v>
       </c>
+      <c r="AF694" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG694" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="695">
       <c r="A695" s="2" t="n">
@@ -54125,6 +55537,8 @@
       <c r="AE695" t="n">
         <v>1833.290697274116</v>
       </c>
+      <c r="AF695" t="inlineStr"/>
+      <c r="AG695" t="inlineStr"/>
     </row>
     <row r="696">
       <c r="A696" s="2" t="n">
@@ -54180,6 +55594,8 @@
       <c r="AE696" t="n">
         <v>1845.223389328896</v>
       </c>
+      <c r="AF696" t="inlineStr"/>
+      <c r="AG696" t="inlineStr"/>
     </row>
     <row r="697">
       <c r="A697" s="2" t="n">
@@ -54235,6 +55651,8 @@
       <c r="AE697" t="n">
         <v>1866.801015257566</v>
       </c>
+      <c r="AF697" t="inlineStr"/>
+      <c r="AG697" t="inlineStr"/>
     </row>
     <row r="698">
       <c r="A698" s="2" t="n">
@@ -54290,6 +55708,8 @@
       <c r="AE698" t="n">
         <v>1878.471909733068</v>
       </c>
+      <c r="AF698" t="inlineStr"/>
+      <c r="AG698" t="inlineStr"/>
     </row>
     <row r="699">
       <c r="A699" s="2" t="n">
@@ -54345,6 +55765,8 @@
       <c r="AE699" t="n">
         <v>1886.60504879667</v>
       </c>
+      <c r="AF699" t="inlineStr"/>
+      <c r="AG699" t="inlineStr"/>
     </row>
     <row r="700">
       <c r="A700" s="2" t="n">
@@ -54400,6 +55822,8 @@
       <c r="AE700" t="n">
         <v>1881.987798919195</v>
       </c>
+      <c r="AF700" t="inlineStr"/>
+      <c r="AG700" t="inlineStr"/>
     </row>
     <row r="701">
       <c r="A701" s="2" t="n">
@@ -54455,6 +55879,8 @@
       <c r="AE701" t="n">
         <v>1868.311918304231</v>
       </c>
+      <c r="AF701" t="inlineStr"/>
+      <c r="AG701" t="inlineStr"/>
     </row>
     <row r="702">
       <c r="A702" s="2" t="n">
@@ -54510,6 +55936,8 @@
       <c r="AE702" t="n">
         <v>1877.294954178198</v>
       </c>
+      <c r="AF702" t="inlineStr"/>
+      <c r="AG702" t="inlineStr"/>
     </row>
     <row r="703">
       <c r="A703" s="2" t="n">
@@ -54565,6 +55993,8 @@
       <c r="AE703" t="n">
         <v>1897.802932329916</v>
       </c>
+      <c r="AF703" t="inlineStr"/>
+      <c r="AG703" t="inlineStr"/>
     </row>
     <row r="704">
       <c r="A704" s="2" t="n">
@@ -54620,6 +56050,8 @@
       <c r="AE704" t="n">
         <v>1888.865915225237</v>
       </c>
+      <c r="AF704" t="inlineStr"/>
+      <c r="AG704" t="inlineStr"/>
     </row>
     <row r="705">
       <c r="A705" s="2" t="n">
@@ -54675,6 +56107,8 @@
       <c r="AE705" t="n">
         <v>1886.872773959293</v>
       </c>
+      <c r="AF705" t="inlineStr"/>
+      <c r="AG705" t="inlineStr"/>
     </row>
     <row r="706">
       <c r="A706" s="2" t="n">
@@ -54730,6 +56164,8 @@
       <c r="AE706" t="n">
         <v>1862.35312712643</v>
       </c>
+      <c r="AF706" t="inlineStr"/>
+      <c r="AG706" t="inlineStr"/>
     </row>
     <row r="707">
       <c r="A707" s="2" t="n">
@@ -54785,6 +56221,8 @@
       <c r="AE707" t="n">
         <v>1858.285185632953</v>
       </c>
+      <c r="AF707" t="inlineStr"/>
+      <c r="AG707" t="inlineStr"/>
     </row>
     <row r="708">
       <c r="A708" s="2" t="n">
@@ -54840,6 +56278,8 @@
       <c r="AE708" t="n">
         <v>1861.917884991293</v>
       </c>
+      <c r="AF708" t="inlineStr"/>
+      <c r="AG708" t="inlineStr"/>
     </row>
     <row r="709">
       <c r="A709" s="2" t="n">
@@ -54895,6 +56335,8 @@
       <c r="AE709" t="n">
         <v>1863.382152289077</v>
       </c>
+      <c r="AF709" t="inlineStr"/>
+      <c r="AG709" t="inlineStr"/>
     </row>
     <row r="710">
       <c r="A710" s="2" t="n">
@@ -54950,6 +56392,8 @@
       <c r="AE710" t="n">
         <v>1852.722000990612</v>
       </c>
+      <c r="AF710" t="inlineStr"/>
+      <c r="AG710" t="inlineStr"/>
     </row>
     <row r="711">
       <c r="A711" s="2" t="n">
@@ -55005,6 +56449,12 @@
       <c r="AE711" t="n">
         <v>1846.908740064227</v>
       </c>
+      <c r="AF711" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG711" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="712">
       <c r="A712" s="2" t="n">
@@ -55058,7 +56508,131 @@
         <v>62.60779999999999</v>
       </c>
       <c r="AE712" t="n">
-        <v>1857.68020310496</v>
+        <v>1857.680203104961</v>
+      </c>
+      <c r="AF712" t="inlineStr"/>
+      <c r="AG712" t="inlineStr"/>
+    </row>
+    <row r="713">
+      <c r="A713" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B713" t="n">
+        <v>0.5828219185</v>
+      </c>
+      <c r="C713" t="n">
+        <v>0.08344615050000001</v>
+      </c>
+      <c r="D713" t="inlineStr"/>
+      <c r="E713" t="inlineStr"/>
+      <c r="F713" t="inlineStr"/>
+      <c r="G713" t="inlineStr"/>
+      <c r="H713" t="inlineStr"/>
+      <c r="I713" t="n">
+        <v>0.037114056</v>
+      </c>
+      <c r="J713" t="inlineStr"/>
+      <c r="K713" t="n">
+        <v>1463.80577476821</v>
+      </c>
+      <c r="L713" t="inlineStr"/>
+      <c r="M713" t="inlineStr"/>
+      <c r="N713" t="inlineStr"/>
+      <c r="O713" t="n">
+        <v>0.006165706800000001</v>
+      </c>
+      <c r="P713" t="inlineStr"/>
+      <c r="Q713" t="n">
+        <v>9.456000000000001e-07</v>
+      </c>
+      <c r="R713" t="inlineStr"/>
+      <c r="S713" t="inlineStr"/>
+      <c r="T713" t="inlineStr"/>
+      <c r="U713" t="inlineStr"/>
+      <c r="V713" t="inlineStr"/>
+      <c r="W713" t="inlineStr"/>
+      <c r="X713" t="inlineStr"/>
+      <c r="Y713" t="inlineStr"/>
+      <c r="Z713" t="inlineStr"/>
+      <c r="AA713" t="n">
+        <v>0.0284390831469</v>
+      </c>
+      <c r="AB713" t="inlineStr"/>
+      <c r="AC713" t="n">
+        <v>19.0607533891368</v>
+      </c>
+      <c r="AD713" t="n">
+        <v>327.718770325</v>
+      </c>
+      <c r="AE713" t="n">
+        <v>1866.491568922894</v>
+      </c>
+      <c r="AF713" t="n">
+        <v>20.07805</v>
+      </c>
+      <c r="AG713" t="n">
+        <v>35.09023258</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B714" t="n">
+        <v>0.5862170325</v>
+      </c>
+      <c r="C714" t="n">
+        <v>0.0842218595</v>
+      </c>
+      <c r="D714" t="inlineStr"/>
+      <c r="E714" t="inlineStr"/>
+      <c r="F714" t="inlineStr"/>
+      <c r="G714" t="inlineStr"/>
+      <c r="H714" t="inlineStr"/>
+      <c r="I714" t="n">
+        <v>0.037335606</v>
+      </c>
+      <c r="J714" t="inlineStr"/>
+      <c r="K714" t="n">
+        <v>1477.2351855459</v>
+      </c>
+      <c r="L714" t="inlineStr"/>
+      <c r="M714" t="inlineStr"/>
+      <c r="N714" t="inlineStr"/>
+      <c r="O714" t="n">
+        <v>0.0061926606</v>
+      </c>
+      <c r="P714" t="inlineStr"/>
+      <c r="Q714" t="n">
+        <v>9.575999999999999e-07</v>
+      </c>
+      <c r="R714" t="inlineStr"/>
+      <c r="S714" t="inlineStr"/>
+      <c r="T714" t="inlineStr"/>
+      <c r="U714" t="inlineStr"/>
+      <c r="V714" t="inlineStr"/>
+      <c r="W714" t="inlineStr"/>
+      <c r="X714" t="inlineStr"/>
+      <c r="Y714" t="inlineStr"/>
+      <c r="Z714" t="inlineStr"/>
+      <c r="AA714" t="n">
+        <v>0.02843823</v>
+      </c>
+      <c r="AB714" t="inlineStr"/>
+      <c r="AC714" t="n">
+        <v>19.56382312668</v>
+      </c>
+      <c r="AD714" t="n">
+        <v>324.226983205</v>
+      </c>
+      <c r="AE714" t="n">
+        <v>1876.92664682678</v>
+      </c>
+      <c r="AF714" t="n">
+        <v>20.07435</v>
+      </c>
+      <c r="AG714" t="n">
+        <v>35.08389860299999</v>
       </c>
     </row>
   </sheetData>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG714"/>
+  <dimension ref="A1:AG716"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55126,8 +55126,12 @@
       <c r="AE688" t="n">
         <v>1805.738250451649</v>
       </c>
-      <c r="AF688" t="inlineStr"/>
-      <c r="AG688" t="inlineStr"/>
+      <c r="AF688" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG688" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="689">
       <c r="A689" s="2" t="n">
@@ -55301,8 +55305,12 @@
       <c r="AE691" t="n">
         <v>1824.867355029248</v>
       </c>
-      <c r="AF691" t="inlineStr"/>
-      <c r="AG691" t="inlineStr"/>
+      <c r="AF691" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG691" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="692">
       <c r="A692" s="2" t="n">
@@ -55537,8 +55545,12 @@
       <c r="AE695" t="n">
         <v>1833.290697274116</v>
       </c>
-      <c r="AF695" t="inlineStr"/>
-      <c r="AG695" t="inlineStr"/>
+      <c r="AF695" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG695" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="696">
       <c r="A696" s="2" t="n">
@@ -55594,8 +55606,12 @@
       <c r="AE696" t="n">
         <v>1845.223389328896</v>
       </c>
-      <c r="AF696" t="inlineStr"/>
-      <c r="AG696" t="inlineStr"/>
+      <c r="AF696" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG696" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="697">
       <c r="A697" s="2" t="n">
@@ -56635,6 +56651,128 @@
         <v>35.08389860299999</v>
       </c>
     </row>
+    <row r="715">
+      <c r="A715" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B715" t="n">
+        <v>0.5853358465</v>
+      </c>
+      <c r="C715" t="n">
+        <v>0.08442832750000001</v>
+      </c>
+      <c r="D715" t="inlineStr"/>
+      <c r="E715" t="inlineStr"/>
+      <c r="F715" t="inlineStr"/>
+      <c r="G715" t="inlineStr"/>
+      <c r="H715" t="inlineStr"/>
+      <c r="I715" t="n">
+        <v>0.03718052099999999</v>
+      </c>
+      <c r="J715" t="inlineStr"/>
+      <c r="K715" t="n">
+        <v>1515.285182749355</v>
+      </c>
+      <c r="L715" t="inlineStr"/>
+      <c r="M715" t="inlineStr"/>
+      <c r="N715" t="inlineStr"/>
+      <c r="O715" t="n">
+        <v>0.0061850454</v>
+      </c>
+      <c r="P715" t="inlineStr"/>
+      <c r="Q715" t="n">
+        <v>9.456000000000001e-07</v>
+      </c>
+      <c r="R715" t="inlineStr"/>
+      <c r="S715" t="inlineStr"/>
+      <c r="T715" t="inlineStr"/>
+      <c r="U715" t="inlineStr"/>
+      <c r="V715" t="inlineStr"/>
+      <c r="W715" t="inlineStr"/>
+      <c r="X715" t="inlineStr"/>
+      <c r="Y715" t="inlineStr"/>
+      <c r="Z715" t="inlineStr"/>
+      <c r="AA715" t="n">
+        <v>0.0284385143823</v>
+      </c>
+      <c r="AB715" t="inlineStr"/>
+      <c r="AC715" t="n">
+        <v>18.818534626616</v>
+      </c>
+      <c r="AD715" t="n">
+        <v>322.40834408</v>
+      </c>
+      <c r="AE715" t="n">
+        <v>1912.309689489353</v>
+      </c>
+      <c r="AF715" t="n">
+        <v>20.0355</v>
+      </c>
+      <c r="AG715" t="n">
+        <v>35.020558833</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B716" t="n">
+        <v>0.5949645244999999</v>
+      </c>
+      <c r="C716" t="n">
+        <v>0.085319266</v>
+      </c>
+      <c r="D716" t="inlineStr"/>
+      <c r="E716" t="inlineStr"/>
+      <c r="F716" t="inlineStr"/>
+      <c r="G716" t="inlineStr"/>
+      <c r="H716" t="inlineStr"/>
+      <c r="I716" t="n">
+        <v>0.03726470999999999</v>
+      </c>
+      <c r="J716" t="inlineStr"/>
+      <c r="K716" t="n">
+        <v>1525.133417319661</v>
+      </c>
+      <c r="L716" t="inlineStr"/>
+      <c r="M716" t="inlineStr"/>
+      <c r="N716" t="inlineStr"/>
+      <c r="O716" t="n">
+        <v>0.0062387526</v>
+      </c>
+      <c r="P716" t="inlineStr"/>
+      <c r="Q716" t="n">
+        <v>9.575999999999999e-07</v>
+      </c>
+      <c r="R716" t="inlineStr"/>
+      <c r="S716" t="inlineStr"/>
+      <c r="T716" t="inlineStr"/>
+      <c r="U716" t="inlineStr"/>
+      <c r="V716" t="inlineStr"/>
+      <c r="W716" t="inlineStr"/>
+      <c r="X716" t="inlineStr"/>
+      <c r="Y716" t="inlineStr"/>
+      <c r="Z716" t="inlineStr"/>
+      <c r="AA716" t="n">
+        <v>0.0284387987646</v>
+      </c>
+      <c r="AB716" t="inlineStr"/>
+      <c r="AC716" t="n">
+        <v>18.7812702016128</v>
+      </c>
+      <c r="AD716" t="n">
+        <v>322.772071905</v>
+      </c>
+      <c r="AE716" t="n">
+        <v>1922.619024027739</v>
+      </c>
+      <c r="AF716" t="n">
+        <v>20.3685</v>
+      </c>
+      <c r="AG716" t="n">
+        <v>34.811537592</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG716"/>
+  <dimension ref="A1:AG719"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55366,8 +55366,12 @@
       <c r="AE692" t="n">
         <v>1822.532302334152</v>
       </c>
-      <c r="AF692" t="inlineStr"/>
-      <c r="AG692" t="inlineStr"/>
+      <c r="AF692" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG692" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="693">
       <c r="A693" s="2" t="n">
@@ -55781,8 +55785,12 @@
       <c r="AE699" t="n">
         <v>1886.60504879667</v>
       </c>
-      <c r="AF699" t="inlineStr"/>
-      <c r="AG699" t="inlineStr"/>
+      <c r="AF699" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG699" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="700">
       <c r="A700" s="2" t="n">
@@ -55838,8 +55846,12 @@
       <c r="AE700" t="n">
         <v>1881.987798919195</v>
       </c>
-      <c r="AF700" t="inlineStr"/>
-      <c r="AG700" t="inlineStr"/>
+      <c r="AF700" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG700" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="701">
       <c r="A701" s="2" t="n">
@@ -56066,8 +56078,12 @@
       <c r="AE704" t="n">
         <v>1888.865915225237</v>
       </c>
-      <c r="AF704" t="inlineStr"/>
-      <c r="AG704" t="inlineStr"/>
+      <c r="AF704" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG704" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="705">
       <c r="A705" s="2" t="n">
@@ -56180,8 +56196,12 @@
       <c r="AE706" t="n">
         <v>1862.35312712643</v>
       </c>
-      <c r="AF706" t="inlineStr"/>
-      <c r="AG706" t="inlineStr"/>
+      <c r="AF706" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG706" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="707">
       <c r="A707" s="2" t="n">
@@ -56773,6 +56793,189 @@
         <v>34.811537592</v>
       </c>
     </row>
+    <row r="717">
+      <c r="A717" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B717" t="n">
+        <v>0.602746124</v>
+      </c>
+      <c r="C717" t="n">
+        <v>0.08581398950000001</v>
+      </c>
+      <c r="D717" t="inlineStr"/>
+      <c r="E717" t="inlineStr"/>
+      <c r="F717" t="inlineStr"/>
+      <c r="G717" t="inlineStr"/>
+      <c r="H717" t="inlineStr"/>
+      <c r="I717" t="n">
+        <v>0.038235099</v>
+      </c>
+      <c r="J717" t="inlineStr"/>
+      <c r="K717" t="n">
+        <v>1543.486945382504</v>
+      </c>
+      <c r="L717" t="inlineStr"/>
+      <c r="M717" t="inlineStr"/>
+      <c r="N717" t="inlineStr"/>
+      <c r="O717" t="n">
+        <v>0.0063168084</v>
+      </c>
+      <c r="P717" t="inlineStr"/>
+      <c r="Q717" t="n">
+        <v>9.863999999999998e-07</v>
+      </c>
+      <c r="R717" t="inlineStr"/>
+      <c r="S717" t="inlineStr"/>
+      <c r="T717" t="inlineStr"/>
+      <c r="U717" t="inlineStr"/>
+      <c r="V717" t="inlineStr"/>
+      <c r="W717" t="inlineStr"/>
+      <c r="X717" t="inlineStr"/>
+      <c r="Y717" t="inlineStr"/>
+      <c r="Z717" t="inlineStr"/>
+      <c r="AA717" t="n">
+        <v>0.0284373768531</v>
+      </c>
+      <c r="AB717" t="inlineStr"/>
+      <c r="AC717" t="n">
+        <v>18.911695689124</v>
+      </c>
+      <c r="AD717" t="n">
+        <v>335.64803691</v>
+      </c>
+      <c r="AE717" t="n">
+        <v>1955.739254783781</v>
+      </c>
+      <c r="AF717" t="n">
+        <v>21.2454</v>
+      </c>
+      <c r="AG717" t="n">
+        <v>35.685626418</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B718" t="n">
+        <v>0.6067802244999999</v>
+      </c>
+      <c r="C718" t="n">
+        <v>0.08545303400000001</v>
+      </c>
+      <c r="D718" t="inlineStr"/>
+      <c r="E718" t="inlineStr"/>
+      <c r="F718" t="inlineStr"/>
+      <c r="G718" t="inlineStr"/>
+      <c r="H718" t="inlineStr"/>
+      <c r="I718" t="n">
+        <v>0.039506796</v>
+      </c>
+      <c r="J718" t="inlineStr"/>
+      <c r="K718" t="n">
+        <v>1550.201650771349</v>
+      </c>
+      <c r="L718" t="inlineStr"/>
+      <c r="M718" t="inlineStr"/>
+      <c r="N718" t="inlineStr"/>
+      <c r="O718" t="n">
+        <v>0.006490354800000001</v>
+      </c>
+      <c r="P718" t="inlineStr"/>
+      <c r="Q718" t="n">
+        <v>9.984e-07</v>
+      </c>
+      <c r="R718" t="inlineStr"/>
+      <c r="S718" t="inlineStr"/>
+      <c r="T718" t="inlineStr"/>
+      <c r="U718" t="inlineStr"/>
+      <c r="V718" t="inlineStr"/>
+      <c r="W718" t="inlineStr"/>
+      <c r="X718" t="inlineStr"/>
+      <c r="Y718" t="inlineStr"/>
+      <c r="Z718" t="inlineStr"/>
+      <c r="AA718" t="n">
+        <v>0.0284379456177</v>
+      </c>
+      <c r="AB718" t="inlineStr"/>
+      <c r="AC718" t="n">
+        <v>19.1539144516448</v>
+      </c>
+      <c r="AD718" t="n">
+        <v>338.776096205</v>
+      </c>
+      <c r="AE718" t="n">
+        <v>1965.634232302311</v>
+      </c>
+      <c r="AF718" t="n">
+        <v>20.80325</v>
+      </c>
+      <c r="AG718" t="n">
+        <v>35.932651521</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B719" t="n">
+        <v>0.5960447</v>
+      </c>
+      <c r="C719" t="n">
+        <v>0.083280031</v>
+      </c>
+      <c r="D719" t="inlineStr"/>
+      <c r="E719" t="inlineStr"/>
+      <c r="F719" t="inlineStr"/>
+      <c r="G719" t="inlineStr"/>
+      <c r="H719" t="inlineStr"/>
+      <c r="I719" t="n">
+        <v>0.039178902</v>
+      </c>
+      <c r="J719" t="inlineStr"/>
+      <c r="K719" t="n">
+        <v>1562.28812047127</v>
+      </c>
+      <c r="L719" t="inlineStr"/>
+      <c r="M719" t="inlineStr"/>
+      <c r="N719" t="inlineStr"/>
+      <c r="O719" t="n">
+        <v>0.0063829404</v>
+      </c>
+      <c r="P719" t="inlineStr"/>
+      <c r="Q719" t="n">
+        <v>9.960000000000001e-07</v>
+      </c>
+      <c r="R719" t="inlineStr"/>
+      <c r="S719" t="inlineStr"/>
+      <c r="T719" t="inlineStr"/>
+      <c r="U719" t="inlineStr"/>
+      <c r="V719" t="inlineStr"/>
+      <c r="W719" t="inlineStr"/>
+      <c r="X719" t="inlineStr"/>
+      <c r="Y719" t="inlineStr"/>
+      <c r="Z719" t="inlineStr"/>
+      <c r="AA719" t="n">
+        <v>0.02843823</v>
+      </c>
+      <c r="AB719" t="inlineStr"/>
+      <c r="AC719" t="n">
+        <v>19.2470755141528</v>
+      </c>
+      <c r="AD719" t="n">
+        <v>327.50053363</v>
+      </c>
+      <c r="AE719" t="n">
+        <v>1965.473903648823</v>
+      </c>
+      <c r="AF719" t="n">
+        <v>19.94855</v>
+      </c>
+      <c r="AG719" t="n">
+        <v>35.736298234</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG719"/>
+  <dimension ref="A1:AG721"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55907,8 +55907,12 @@
       <c r="AE701" t="n">
         <v>1868.311918304231</v>
       </c>
-      <c r="AF701" t="inlineStr"/>
-      <c r="AG701" t="inlineStr"/>
+      <c r="AF701" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG701" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="702">
       <c r="A702" s="2" t="n">
@@ -56976,6 +56980,128 @@
         <v>35.736298234</v>
       </c>
     </row>
+    <row r="720">
+      <c r="A720" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B720" t="n">
+        <v>0.5974391164999999</v>
+      </c>
+      <c r="C720" t="n">
+        <v>0.08386163100000001</v>
+      </c>
+      <c r="D720" t="inlineStr"/>
+      <c r="E720" t="inlineStr"/>
+      <c r="F720" t="inlineStr"/>
+      <c r="G720" t="inlineStr"/>
+      <c r="H720" t="inlineStr"/>
+      <c r="I720" t="n">
+        <v>0.040769631</v>
+      </c>
+      <c r="J720" t="inlineStr"/>
+      <c r="K720" t="n">
+        <v>1567.659884782346</v>
+      </c>
+      <c r="L720" t="inlineStr"/>
+      <c r="M720" t="inlineStr"/>
+      <c r="N720" t="inlineStr"/>
+      <c r="O720" t="n">
+        <v>0.0065065872</v>
+      </c>
+      <c r="P720" t="inlineStr"/>
+      <c r="Q720" t="n">
+        <v>1.0368e-06</v>
+      </c>
+      <c r="R720" t="inlineStr"/>
+      <c r="S720" t="inlineStr"/>
+      <c r="T720" t="inlineStr"/>
+      <c r="U720" t="inlineStr"/>
+      <c r="V720" t="inlineStr"/>
+      <c r="W720" t="inlineStr"/>
+      <c r="X720" t="inlineStr"/>
+      <c r="Y720" t="inlineStr"/>
+      <c r="Z720" t="inlineStr"/>
+      <c r="AA720" t="n">
+        <v>0.0284365237062</v>
+      </c>
+      <c r="AB720" t="inlineStr"/>
+      <c r="AC720" t="n">
+        <v>20.215950564236</v>
+      </c>
+      <c r="AD720" t="n">
+        <v>327.718770325</v>
+      </c>
+      <c r="AE720" t="n">
+        <v>1973.552574061788</v>
+      </c>
+      <c r="AF720" t="n">
+        <v>20.2612</v>
+      </c>
+      <c r="AG720" t="n">
+        <v>36.939753864</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B721" t="n">
+        <v>0.6010540799999999</v>
+      </c>
+      <c r="C721" t="n">
+        <v>0.08456609400000001</v>
+      </c>
+      <c r="D721" t="inlineStr"/>
+      <c r="E721" t="inlineStr"/>
+      <c r="F721" t="inlineStr"/>
+      <c r="G721" t="inlineStr"/>
+      <c r="H721" t="inlineStr"/>
+      <c r="I721" t="n">
+        <v>0.041265903</v>
+      </c>
+      <c r="J721" t="inlineStr"/>
+      <c r="K721" t="n">
+        <v>1567.659884782346</v>
+      </c>
+      <c r="L721" t="inlineStr"/>
+      <c r="M721" t="inlineStr"/>
+      <c r="N721" t="inlineStr"/>
+      <c r="O721" t="n">
+        <v>0.006510495000000001</v>
+      </c>
+      <c r="P721" t="inlineStr"/>
+      <c r="Q721" t="n">
+        <v>1.02e-06</v>
+      </c>
+      <c r="R721" t="inlineStr"/>
+      <c r="S721" t="inlineStr"/>
+      <c r="T721" t="inlineStr"/>
+      <c r="U721" t="inlineStr"/>
+      <c r="V721" t="inlineStr"/>
+      <c r="W721" t="inlineStr"/>
+      <c r="X721" t="inlineStr"/>
+      <c r="Y721" t="inlineStr"/>
+      <c r="Z721" t="inlineStr"/>
+      <c r="AA721" t="n">
+        <v>0.0284385143823</v>
+      </c>
+      <c r="AB721" t="inlineStr"/>
+      <c r="AC721" t="n">
+        <v>20.3277438392456</v>
+      </c>
+      <c r="AD721" t="n">
+        <v>327.20955137</v>
+      </c>
+      <c r="AE721" t="n">
+        <v>1972.812982697974</v>
+      </c>
+      <c r="AF721" t="n">
+        <v>20.1169</v>
+      </c>
+      <c r="AG721" t="n">
+        <v>36.7370666</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -55671,8 +55671,12 @@
       <c r="AE697" t="n">
         <v>1866.801015257566</v>
       </c>
-      <c r="AF697" t="inlineStr"/>
-      <c r="AG697" t="inlineStr"/>
+      <c r="AF697" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG697" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="698">
       <c r="A698" s="2" t="n">
@@ -55968,8 +55972,12 @@
       <c r="AE702" t="n">
         <v>1877.294954178198</v>
       </c>
-      <c r="AF702" t="inlineStr"/>
-      <c r="AG702" t="inlineStr"/>
+      <c r="AF702" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG702" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="703">
       <c r="A703" s="2" t="n">
@@ -56025,8 +56033,12 @@
       <c r="AE703" t="n">
         <v>1897.802932329916</v>
       </c>
-      <c r="AF703" t="inlineStr"/>
-      <c r="AG703" t="inlineStr"/>
+      <c r="AF703" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG703" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="704">
       <c r="A704" s="2" t="n">
@@ -56143,8 +56155,12 @@
       <c r="AE705" t="n">
         <v>1886.872773959293</v>
       </c>
-      <c r="AF705" t="inlineStr"/>
-      <c r="AG705" t="inlineStr"/>
+      <c r="AF705" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG705" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="706">
       <c r="A706" s="2" t="n">

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG721"/>
+  <dimension ref="A1:AG725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56448,8 +56448,12 @@
       <c r="AE710" t="n">
         <v>1852.722000990612</v>
       </c>
-      <c r="AF710" t="inlineStr"/>
-      <c r="AG710" t="inlineStr"/>
+      <c r="AF710" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG710" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="711">
       <c r="A711" s="2" t="n">
@@ -57118,6 +57122,250 @@
         <v>36.7370666</v>
       </c>
     </row>
+    <row r="722">
+      <c r="A722" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B722" t="n">
+        <v>0.6124650215</v>
+      </c>
+      <c r="C722" t="n">
+        <v>0.0861956645</v>
+      </c>
+      <c r="D722" t="inlineStr"/>
+      <c r="E722" t="inlineStr"/>
+      <c r="F722" t="inlineStr"/>
+      <c r="G722" t="inlineStr"/>
+      <c r="H722" t="inlineStr"/>
+      <c r="I722" t="n">
+        <v>0.042745857</v>
+      </c>
+      <c r="J722" t="inlineStr"/>
+      <c r="K722" t="n">
+        <v>1569.450472886038</v>
+      </c>
+      <c r="L722" t="inlineStr"/>
+      <c r="M722" t="inlineStr"/>
+      <c r="N722" t="inlineStr"/>
+      <c r="O722" t="n">
+        <v>0.006648771</v>
+      </c>
+      <c r="P722" t="inlineStr"/>
+      <c r="Q722" t="n">
+        <v>1.0584e-06</v>
+      </c>
+      <c r="R722" t="inlineStr"/>
+      <c r="S722" t="inlineStr"/>
+      <c r="T722" t="inlineStr"/>
+      <c r="U722" t="inlineStr"/>
+      <c r="V722" t="inlineStr"/>
+      <c r="W722" t="inlineStr"/>
+      <c r="X722" t="inlineStr"/>
+      <c r="Y722" t="inlineStr"/>
+      <c r="Z722" t="inlineStr"/>
+      <c r="AA722" t="n">
+        <v>0.0284373768531</v>
+      </c>
+      <c r="AB722" t="inlineStr"/>
+      <c r="AC722" t="n">
+        <v>20.774916939284</v>
+      </c>
+      <c r="AD722" t="n">
+        <v>337.757658295</v>
+      </c>
+      <c r="AE722" t="n">
+        <v>1987.840864880575</v>
+      </c>
+      <c r="AF722" t="n">
+        <v>20.8051</v>
+      </c>
+      <c r="AG722" t="n">
+        <v>38.276223011</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B723" t="n">
+        <v>0.6090050924999999</v>
+      </c>
+      <c r="C723" t="n">
+        <v>0.0850542745</v>
+      </c>
+      <c r="D723" t="inlineStr"/>
+      <c r="E723" t="inlineStr"/>
+      <c r="F723" t="inlineStr"/>
+      <c r="G723" t="inlineStr"/>
+      <c r="H723" t="inlineStr"/>
+      <c r="I723" t="n">
+        <v>0.043144647</v>
+      </c>
+      <c r="J723" t="inlineStr"/>
+      <c r="K723" t="n">
+        <v>1571.688708015653</v>
+      </c>
+      <c r="L723" t="inlineStr"/>
+      <c r="M723" t="inlineStr"/>
+      <c r="N723" t="inlineStr"/>
+      <c r="O723" t="n">
+        <v>0.006719412000000001</v>
+      </c>
+      <c r="P723" t="inlineStr"/>
+      <c r="Q723" t="n">
+        <v>1.044e-06</v>
+      </c>
+      <c r="R723" t="inlineStr"/>
+      <c r="S723" t="inlineStr"/>
+      <c r="T723" t="inlineStr"/>
+      <c r="U723" t="inlineStr"/>
+      <c r="V723" t="inlineStr"/>
+      <c r="W723" t="inlineStr"/>
+      <c r="X723" t="inlineStr"/>
+      <c r="Y723" t="inlineStr"/>
+      <c r="Z723" t="inlineStr"/>
+      <c r="AA723" t="n">
+        <v>0.0284405050584</v>
+      </c>
+      <c r="AB723" t="inlineStr"/>
+      <c r="AC723" t="n">
+        <v>20.49543375176</v>
+      </c>
+      <c r="AD723" t="n">
+        <v>327.50053363</v>
+      </c>
+      <c r="AE723" t="n">
+        <v>1978.117673776472</v>
+      </c>
+      <c r="AF723" t="n">
+        <v>20.5942</v>
+      </c>
+      <c r="AG723" t="n">
+        <v>37.066433404</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B724" t="n">
+        <v>0.5997583015</v>
+      </c>
+      <c r="C724" t="n">
+        <v>0.082694796</v>
+      </c>
+      <c r="D724" t="inlineStr"/>
+      <c r="E724" t="inlineStr"/>
+      <c r="F724" t="inlineStr"/>
+      <c r="G724" t="inlineStr"/>
+      <c r="H724" t="inlineStr"/>
+      <c r="I724" t="n">
+        <v>0.041775468</v>
+      </c>
+      <c r="J724" t="inlineStr"/>
+      <c r="K724" t="n">
+        <v>1562.735767497193</v>
+      </c>
+      <c r="L724" t="inlineStr"/>
+      <c r="M724" t="inlineStr"/>
+      <c r="N724" t="inlineStr"/>
+      <c r="O724" t="n">
+        <v>0.006662799</v>
+      </c>
+      <c r="P724" t="inlineStr"/>
+      <c r="Q724" t="n">
+        <v>9.936000000000001e-07</v>
+      </c>
+      <c r="R724" t="inlineStr"/>
+      <c r="S724" t="inlineStr"/>
+      <c r="T724" t="inlineStr"/>
+      <c r="U724" t="inlineStr"/>
+      <c r="V724" t="inlineStr"/>
+      <c r="W724" t="inlineStr"/>
+      <c r="X724" t="inlineStr"/>
+      <c r="Y724" t="inlineStr"/>
+      <c r="Z724" t="inlineStr"/>
+      <c r="AA724" t="n">
+        <v>0.0284385143823</v>
+      </c>
+      <c r="AB724" t="inlineStr"/>
+      <c r="AC724" t="n">
+        <v>21.240722251824</v>
+      </c>
+      <c r="AD724" t="n">
+        <v>319.78950374</v>
+      </c>
+      <c r="AE724" t="n">
+        <v>1961.7161486855</v>
+      </c>
+      <c r="AF724" t="n">
+        <v>20.37775</v>
+      </c>
+      <c r="AG724" t="n">
+        <v>36.813074324</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B725" t="n">
+        <v>0.5908863945</v>
+      </c>
+      <c r="C725" t="n">
+        <v>0.0821019275</v>
+      </c>
+      <c r="D725" t="inlineStr"/>
+      <c r="E725" t="inlineStr"/>
+      <c r="F725" t="inlineStr"/>
+      <c r="G725" t="inlineStr"/>
+      <c r="H725" t="inlineStr"/>
+      <c r="I725" t="n">
+        <v>0.040397427</v>
+      </c>
+      <c r="J725" t="inlineStr"/>
+      <c r="K725" t="n">
+        <v>1565.421649652731</v>
+      </c>
+      <c r="L725" t="inlineStr"/>
+      <c r="M725" t="inlineStr"/>
+      <c r="N725" t="inlineStr"/>
+      <c r="O725" t="n">
+        <v>0.0067302336</v>
+      </c>
+      <c r="P725" t="inlineStr"/>
+      <c r="Q725" t="n">
+        <v>9.72e-07</v>
+      </c>
+      <c r="R725" t="inlineStr"/>
+      <c r="S725" t="inlineStr"/>
+      <c r="T725" t="inlineStr"/>
+      <c r="U725" t="inlineStr"/>
+      <c r="V725" t="inlineStr"/>
+      <c r="W725" t="inlineStr"/>
+      <c r="X725" t="inlineStr"/>
+      <c r="Y725" t="inlineStr"/>
+      <c r="Z725" t="inlineStr"/>
+      <c r="AA725" t="n">
+        <v>0.0284433488814</v>
+      </c>
+      <c r="AB725" t="inlineStr"/>
+      <c r="AC725" t="n">
+        <v>20.02962843922</v>
+      </c>
+      <c r="AD725" t="n">
+        <v>315.788497665</v>
+      </c>
+      <c r="AE725" t="n">
+        <v>1958.945988937433</v>
+      </c>
+      <c r="AF725" t="n">
+        <v>20.84765</v>
+      </c>
+      <c r="AG725" t="n">
+        <v>36.110002877</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG725"/>
+  <dimension ref="A1:AG726"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55732,8 +55732,12 @@
       <c r="AE698" t="n">
         <v>1878.471909733068</v>
       </c>
-      <c r="AF698" t="inlineStr"/>
-      <c r="AG698" t="inlineStr"/>
+      <c r="AF698" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG698" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="699">
       <c r="A699" s="2" t="n">
@@ -56277,8 +56281,12 @@
       <c r="AE707" t="n">
         <v>1858.285185632953</v>
       </c>
-      <c r="AF707" t="inlineStr"/>
-      <c r="AG707" t="inlineStr"/>
+      <c r="AF707" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG707" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="708">
       <c r="A708" s="2" t="n">
@@ -56391,8 +56399,12 @@
       <c r="AE709" t="n">
         <v>1863.382152289077</v>
       </c>
-      <c r="AF709" t="inlineStr"/>
-      <c r="AG709" t="inlineStr"/>
+      <c r="AF709" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG709" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="710">
       <c r="A710" s="2" t="n">
@@ -57366,6 +57378,67 @@
         <v>36.110002877</v>
       </c>
     </row>
+    <row r="726">
+      <c r="A726" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B726" t="n">
+        <v>0.6041204255</v>
+      </c>
+      <c r="C726" t="n">
+        <v>0.08299613750000001</v>
+      </c>
+      <c r="D726" t="inlineStr"/>
+      <c r="E726" t="inlineStr"/>
+      <c r="F726" t="inlineStr"/>
+      <c r="G726" t="inlineStr"/>
+      <c r="H726" t="inlineStr"/>
+      <c r="I726" t="n">
+        <v>0.040831665</v>
+      </c>
+      <c r="J726" t="inlineStr"/>
+      <c r="K726" t="n">
+        <v>1583.775177715574</v>
+      </c>
+      <c r="L726" t="inlineStr"/>
+      <c r="M726" t="inlineStr"/>
+      <c r="N726" t="inlineStr"/>
+      <c r="O726" t="n">
+        <v>0.0067962654</v>
+      </c>
+      <c r="P726" t="inlineStr"/>
+      <c r="Q726" t="n">
+        <v>9.839999999999998e-07</v>
+      </c>
+      <c r="R726" t="inlineStr"/>
+      <c r="S726" t="inlineStr"/>
+      <c r="T726" t="inlineStr"/>
+      <c r="U726" t="inlineStr"/>
+      <c r="V726" t="inlineStr"/>
+      <c r="W726" t="inlineStr"/>
+      <c r="X726" t="inlineStr"/>
+      <c r="Y726" t="inlineStr"/>
+      <c r="Z726" t="inlineStr"/>
+      <c r="AA726" t="n">
+        <v>0.02843823</v>
+      </c>
+      <c r="AB726" t="inlineStr"/>
+      <c r="AC726" t="n">
+        <v>20.0109962267184</v>
+      </c>
+      <c r="AD726" t="n">
+        <v>316.44320775</v>
+      </c>
+      <c r="AE726" t="n">
+        <v>1979.222745516693</v>
+      </c>
+      <c r="AF726" t="n">
+        <v>21.3601</v>
+      </c>
+      <c r="AG726" t="n">
+        <v>36.870080117</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG726"/>
+  <dimension ref="A1:AG728"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56342,8 +56342,12 @@
       <c r="AE708" t="n">
         <v>1861.917884991293</v>
       </c>
-      <c r="AF708" t="inlineStr"/>
-      <c r="AG708" t="inlineStr"/>
+      <c r="AF708" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG708" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="709">
       <c r="A709" s="2" t="n">
@@ -57247,7 +57251,7 @@
         <v>327.50053363</v>
       </c>
       <c r="AE723" t="n">
-        <v>1978.117673776472</v>
+        <v>1978.117673776471</v>
       </c>
       <c r="AF723" t="n">
         <v>20.5942</v>
@@ -57308,7 +57312,7 @@
         <v>319.78950374</v>
       </c>
       <c r="AE724" t="n">
-        <v>1961.7161486855</v>
+        <v>1961.716148685499</v>
       </c>
       <c r="AF724" t="n">
         <v>20.37775</v>
@@ -57439,6 +57443,128 @@
         <v>36.870080117</v>
       </c>
     </row>
+    <row r="727">
+      <c r="A727" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B727" t="n">
+        <v>0.5893934145</v>
+      </c>
+      <c r="C727" t="n">
+        <v>0.080866391</v>
+      </c>
+      <c r="D727" t="inlineStr"/>
+      <c r="E727" t="inlineStr"/>
+      <c r="F727" t="inlineStr"/>
+      <c r="G727" t="inlineStr"/>
+      <c r="H727" t="inlineStr"/>
+      <c r="I727" t="n">
+        <v>0.039542244</v>
+      </c>
+      <c r="J727" t="inlineStr"/>
+      <c r="K727" t="n">
+        <v>1576.165178274883</v>
+      </c>
+      <c r="L727" t="inlineStr"/>
+      <c r="M727" t="inlineStr"/>
+      <c r="N727" t="inlineStr"/>
+      <c r="O727" t="n">
+        <v>0.0067372476</v>
+      </c>
+      <c r="P727" t="inlineStr"/>
+      <c r="Q727" t="n">
+        <v>9.383999999999999e-07</v>
+      </c>
+      <c r="R727" t="inlineStr"/>
+      <c r="S727" t="inlineStr"/>
+      <c r="T727" t="inlineStr"/>
+      <c r="U727" t="inlineStr"/>
+      <c r="V727" t="inlineStr"/>
+      <c r="W727" t="inlineStr"/>
+      <c r="X727" t="inlineStr"/>
+      <c r="Y727" t="inlineStr"/>
+      <c r="Z727" t="inlineStr"/>
+      <c r="AA727" t="n">
+        <v>0.0284478989982</v>
+      </c>
+      <c r="AB727" t="inlineStr"/>
+      <c r="AC727" t="n">
+        <v>18.6881091391048</v>
+      </c>
+      <c r="AD727" t="n">
+        <v>310.47807142</v>
+      </c>
+      <c r="AE727" t="n">
+        <v>1963.468314718486</v>
+      </c>
+      <c r="AF727" t="n">
+        <v>20.9716</v>
+      </c>
+      <c r="AG727" t="n">
+        <v>36.42036775</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B728" t="n">
+        <v>0.5822029725</v>
+      </c>
+      <c r="C728" t="n">
+        <v>0.0792709895</v>
+      </c>
+      <c r="D728" t="inlineStr"/>
+      <c r="E728" t="inlineStr"/>
+      <c r="F728" t="inlineStr"/>
+      <c r="G728" t="inlineStr"/>
+      <c r="H728" t="inlineStr"/>
+      <c r="I728" t="n">
+        <v>0.038345874</v>
+      </c>
+      <c r="J728" t="inlineStr"/>
+      <c r="K728" t="n">
+        <v>1590.042236078496</v>
+      </c>
+      <c r="L728" t="inlineStr"/>
+      <c r="M728" t="inlineStr"/>
+      <c r="N728" t="inlineStr"/>
+      <c r="O728" t="n">
+        <v>0.006575124000000001</v>
+      </c>
+      <c r="P728" t="inlineStr"/>
+      <c r="Q728" t="n">
+        <v>9.023999999999999e-07</v>
+      </c>
+      <c r="R728" t="inlineStr"/>
+      <c r="S728" t="inlineStr"/>
+      <c r="T728" t="inlineStr"/>
+      <c r="U728" t="inlineStr"/>
+      <c r="V728" t="inlineStr"/>
+      <c r="W728" t="inlineStr"/>
+      <c r="X728" t="inlineStr"/>
+      <c r="Y728" t="inlineStr"/>
+      <c r="Z728" t="inlineStr"/>
+      <c r="AA728" t="n">
+        <v>0.0284447707929</v>
+      </c>
+      <c r="AB728" t="inlineStr"/>
+      <c r="AC728" t="n">
+        <v>18.0359817015488</v>
+      </c>
+      <c r="AD728" t="n">
+        <v>302.47605927</v>
+      </c>
+      <c r="AE728" t="n">
+        <v>1967.081514561237</v>
+      </c>
+      <c r="AF728" t="n">
+        <v>20.23345</v>
+      </c>
+      <c r="AG728" t="n">
+        <v>35.558946878</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG728"/>
+  <dimension ref="A1:AG731"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56584,10 +56584,14 @@
         <v>62.60779999999999</v>
       </c>
       <c r="AE712" t="n">
-        <v>1857.680203104961</v>
-      </c>
-      <c r="AF712" t="inlineStr"/>
-      <c r="AG712" t="inlineStr"/>
+        <v>1857.68020310496</v>
+      </c>
+      <c r="AF712" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG712" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="713">
       <c r="A713" s="2" t="n">
@@ -57251,7 +57255,7 @@
         <v>327.50053363</v>
       </c>
       <c r="AE723" t="n">
-        <v>1978.117673776471</v>
+        <v>1978.117673776472</v>
       </c>
       <c r="AF723" t="n">
         <v>20.5942</v>
@@ -57565,6 +57569,189 @@
         <v>35.558946878</v>
       </c>
     </row>
+    <row r="729">
+      <c r="A729" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B729" t="n">
+        <v>0.5770596415</v>
+      </c>
+      <c r="C729" t="n">
+        <v>0.07746185</v>
+      </c>
+      <c r="D729" t="inlineStr"/>
+      <c r="E729" t="inlineStr"/>
+      <c r="F729" t="inlineStr"/>
+      <c r="G729" t="inlineStr"/>
+      <c r="H729" t="inlineStr"/>
+      <c r="I729" t="n">
+        <v>0.037769844</v>
+      </c>
+      <c r="J729" t="inlineStr"/>
+      <c r="K729" t="n">
+        <v>1590.489883104419</v>
+      </c>
+      <c r="L729" t="inlineStr"/>
+      <c r="M729" t="inlineStr"/>
+      <c r="N729" t="inlineStr"/>
+      <c r="O729" t="n">
+        <v>0.006507789600000001</v>
+      </c>
+      <c r="P729" t="inlineStr"/>
+      <c r="Q729" t="n">
+        <v>8.832e-07</v>
+      </c>
+      <c r="R729" t="inlineStr"/>
+      <c r="S729" t="inlineStr"/>
+      <c r="T729" t="inlineStr"/>
+      <c r="U729" t="inlineStr"/>
+      <c r="V729" t="inlineStr"/>
+      <c r="W729" t="inlineStr"/>
+      <c r="X729" t="inlineStr"/>
+      <c r="Y729" t="inlineStr"/>
+      <c r="Z729" t="inlineStr"/>
+      <c r="AA729" t="n">
+        <v>0.0284478989982</v>
+      </c>
+      <c r="AB729" t="inlineStr"/>
+      <c r="AC729" t="n">
+        <v>17.7192340890216</v>
+      </c>
+      <c r="AD729" t="n">
+        <v>294.47404712</v>
+      </c>
+      <c r="AE729" t="n">
+        <v>1958.138074709739</v>
+      </c>
+      <c r="AF729" t="n">
+        <v>20.16315</v>
+      </c>
+      <c r="AG729" t="n">
+        <v>34.56451248899999</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B730" t="n">
+        <v>0.5736639314999999</v>
+      </c>
+      <c r="C730" t="n">
+        <v>0.077428408</v>
+      </c>
+      <c r="D730" t="inlineStr"/>
+      <c r="E730" t="inlineStr"/>
+      <c r="F730" t="inlineStr"/>
+      <c r="G730" t="inlineStr"/>
+      <c r="H730" t="inlineStr"/>
+      <c r="I730" t="n">
+        <v>0.037831878</v>
+      </c>
+      <c r="J730" t="inlineStr"/>
+      <c r="K730" t="n">
+        <v>1592.280471208111</v>
+      </c>
+      <c r="L730" t="inlineStr"/>
+      <c r="M730" t="inlineStr"/>
+      <c r="N730" t="inlineStr"/>
+      <c r="O730" t="n">
+        <v>0.0064481706</v>
+      </c>
+      <c r="P730" t="inlineStr"/>
+      <c r="Q730" t="n">
+        <v>8.88e-07</v>
+      </c>
+      <c r="R730" t="inlineStr"/>
+      <c r="S730" t="inlineStr"/>
+      <c r="T730" t="inlineStr"/>
+      <c r="U730" t="inlineStr"/>
+      <c r="V730" t="inlineStr"/>
+      <c r="W730" t="inlineStr"/>
+      <c r="X730" t="inlineStr"/>
+      <c r="Y730" t="inlineStr"/>
+      <c r="Z730" t="inlineStr"/>
+      <c r="AA730" t="n">
+        <v>0.0284510272035</v>
+      </c>
+      <c r="AB730" t="inlineStr"/>
+      <c r="AC730" t="n">
+        <v>17.2906932014848</v>
+      </c>
+      <c r="AD730" t="n">
+        <v>275.56020022</v>
+      </c>
+      <c r="AE730" t="n">
+        <v>1939.6754718819</v>
+      </c>
+      <c r="AF730" t="n">
+        <v>19.38245</v>
+      </c>
+      <c r="AG730" t="n">
+        <v>34.437832949</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B731" t="n">
+        <v>0.572415982</v>
+      </c>
+      <c r="C731" t="n">
+        <v>0.0767686555</v>
+      </c>
+      <c r="D731" t="inlineStr"/>
+      <c r="E731" t="inlineStr"/>
+      <c r="F731" t="inlineStr"/>
+      <c r="G731" t="inlineStr"/>
+      <c r="H731" t="inlineStr"/>
+      <c r="I731" t="n">
+        <v>0.037348899</v>
+      </c>
+      <c r="J731" t="inlineStr"/>
+      <c r="K731" t="n">
+        <v>1595.414000389572</v>
+      </c>
+      <c r="L731" t="inlineStr"/>
+      <c r="M731" t="inlineStr"/>
+      <c r="N731" t="inlineStr"/>
+      <c r="O731" t="n">
+        <v>0.0064130004</v>
+      </c>
+      <c r="P731" t="inlineStr"/>
+      <c r="Q731" t="n">
+        <v>8.760000000000001e-07</v>
+      </c>
+      <c r="R731" t="inlineStr"/>
+      <c r="S731" t="inlineStr"/>
+      <c r="T731" t="inlineStr"/>
+      <c r="U731" t="inlineStr"/>
+      <c r="V731" t="inlineStr"/>
+      <c r="W731" t="inlineStr"/>
+      <c r="X731" t="inlineStr"/>
+      <c r="Y731" t="inlineStr"/>
+      <c r="Z731" t="inlineStr"/>
+      <c r="AA731" t="n">
+        <v>0.0284564304672</v>
+      </c>
+      <c r="AB731" t="inlineStr"/>
+      <c r="AC731" t="n">
+        <v>16.6013013389256</v>
+      </c>
+      <c r="AD731" t="n">
+        <v>269.44957276</v>
+      </c>
+      <c r="AE731" t="n">
+        <v>1935.761452981865</v>
+      </c>
+      <c r="AF731" t="n">
+        <v>19.055</v>
+      </c>
+      <c r="AG731" t="n">
+        <v>34.52017464999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG731"/>
+  <dimension ref="A1:AG732"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57752,6 +57752,67 @@
         <v>34.52017464999999</v>
       </c>
     </row>
+    <row r="732">
+      <c r="A732" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B732" t="n">
+        <v>0.5777641135</v>
+      </c>
+      <c r="C732" t="n">
+        <v>0.07740514400000001</v>
+      </c>
+      <c r="D732" t="inlineStr"/>
+      <c r="E732" t="inlineStr"/>
+      <c r="F732" t="inlineStr"/>
+      <c r="G732" t="inlineStr"/>
+      <c r="H732" t="inlineStr"/>
+      <c r="I732" t="n">
+        <v>0.038181927</v>
+      </c>
+      <c r="J732" t="inlineStr"/>
+      <c r="K732" t="n">
+        <v>1607.948117115416</v>
+      </c>
+      <c r="L732" t="inlineStr"/>
+      <c r="M732" t="inlineStr"/>
+      <c r="N732" t="inlineStr"/>
+      <c r="O732" t="n">
+        <v>0.006507990000000001</v>
+      </c>
+      <c r="P732" t="inlineStr"/>
+      <c r="Q732" t="n">
+        <v>8.927999999999999e-07</v>
+      </c>
+      <c r="R732" t="inlineStr"/>
+      <c r="S732" t="inlineStr"/>
+      <c r="T732" t="inlineStr"/>
+      <c r="U732" t="inlineStr"/>
+      <c r="V732" t="inlineStr"/>
+      <c r="W732" t="inlineStr"/>
+      <c r="X732" t="inlineStr"/>
+      <c r="Y732" t="inlineStr"/>
+      <c r="Z732" t="inlineStr"/>
+      <c r="AA732" t="n">
+        <v>0.0284567148495</v>
+      </c>
+      <c r="AB732" t="inlineStr"/>
+      <c r="AC732" t="n">
+        <v>17.607440814012</v>
+      </c>
+      <c r="AD732" t="n">
+        <v>271.413703015</v>
+      </c>
+      <c r="AE732" t="n">
+        <v>1951.062067618578</v>
+      </c>
+      <c r="AF732" t="n">
+        <v>19.18635</v>
+      </c>
+      <c r="AG732" t="n">
+        <v>34.178139892</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG732"/>
+  <dimension ref="A1:AG733"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56584,7 +56584,7 @@
         <v>62.60779999999999</v>
       </c>
       <c r="AE712" t="n">
-        <v>1857.68020310496</v>
+        <v>1857.680203104961</v>
       </c>
       <c r="AF712" t="n">
         <v>0</v>
@@ -57316,7 +57316,7 @@
         <v>319.78950374</v>
       </c>
       <c r="AE724" t="n">
-        <v>1961.716148685499</v>
+        <v>1961.7161486855</v>
       </c>
       <c r="AF724" t="n">
         <v>20.37775</v>
@@ -57804,13 +57804,74 @@
         <v>271.413703015</v>
       </c>
       <c r="AE732" t="n">
-        <v>1951.062067618578</v>
+        <v>1951.062067618577</v>
       </c>
       <c r="AF732" t="n">
         <v>19.18635</v>
       </c>
       <c r="AG732" t="n">
         <v>34.178139892</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B733" t="n">
+        <v>0.5782356240000001</v>
+      </c>
+      <c r="C733" t="n">
+        <v>0.07756217600000001</v>
+      </c>
+      <c r="D733" t="inlineStr"/>
+      <c r="E733" t="inlineStr"/>
+      <c r="F733" t="inlineStr"/>
+      <c r="G733" t="inlineStr"/>
+      <c r="H733" t="inlineStr"/>
+      <c r="I733" t="n">
+        <v>0.038709216</v>
+      </c>
+      <c r="J733" t="inlineStr"/>
+      <c r="K733" t="n">
+        <v>1635.702232722642</v>
+      </c>
+      <c r="L733" t="inlineStr"/>
+      <c r="M733" t="inlineStr"/>
+      <c r="N733" t="inlineStr"/>
+      <c r="O733" t="n">
+        <v>0.006598971600000001</v>
+      </c>
+      <c r="P733" t="inlineStr"/>
+      <c r="Q733" t="n">
+        <v>9.144e-07</v>
+      </c>
+      <c r="R733" t="inlineStr"/>
+      <c r="S733" t="inlineStr"/>
+      <c r="T733" t="inlineStr"/>
+      <c r="U733" t="inlineStr"/>
+      <c r="V733" t="inlineStr"/>
+      <c r="W733" t="inlineStr"/>
+      <c r="X733" t="inlineStr"/>
+      <c r="Y733" t="inlineStr"/>
+      <c r="Z733" t="inlineStr"/>
+      <c r="AA733" t="n">
+        <v>0.0284572836141</v>
+      </c>
+      <c r="AB733" t="inlineStr"/>
+      <c r="AC733" t="n">
+        <v>18.2782004640696</v>
+      </c>
+      <c r="AD733" t="n">
+        <v>276.72412926</v>
+      </c>
+      <c r="AE733" t="n">
+        <v>1985.302414018325</v>
+      </c>
+      <c r="AF733" t="n">
+        <v>19.5508</v>
+      </c>
+      <c r="AG733" t="n">
+        <v>34.317487386</v>
       </c>
     </row>
   </sheetData>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG733"/>
+  <dimension ref="A1:AG736"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56584,7 +56584,7 @@
         <v>62.60779999999999</v>
       </c>
       <c r="AE712" t="n">
-        <v>1857.680203104961</v>
+        <v>1857.68020310496</v>
       </c>
       <c r="AF712" t="n">
         <v>0</v>
@@ -57316,7 +57316,7 @@
         <v>319.78950374</v>
       </c>
       <c r="AE724" t="n">
-        <v>1961.7161486855</v>
+        <v>1961.716148685499</v>
       </c>
       <c r="AF724" t="n">
         <v>20.37775</v>
@@ -57804,7 +57804,7 @@
         <v>271.413703015</v>
       </c>
       <c r="AE732" t="n">
-        <v>1951.062067618577</v>
+        <v>1951.062067618578</v>
       </c>
       <c r="AF732" t="n">
         <v>19.18635</v>
@@ -57874,6 +57874,189 @@
         <v>34.317487386</v>
       </c>
     </row>
+    <row r="734">
+      <c r="A734" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B734" t="n">
+        <v>0.562769275</v>
+      </c>
+      <c r="C734" t="n">
+        <v>0.0750936475</v>
+      </c>
+      <c r="D734" t="inlineStr"/>
+      <c r="E734" t="inlineStr"/>
+      <c r="F734" t="inlineStr"/>
+      <c r="G734" t="inlineStr"/>
+      <c r="H734" t="inlineStr"/>
+      <c r="I734" t="n">
+        <v>0.03739764</v>
+      </c>
+      <c r="J734" t="inlineStr"/>
+      <c r="K734" t="n">
+        <v>1621.825174919029</v>
+      </c>
+      <c r="L734" t="inlineStr"/>
+      <c r="M734" t="inlineStr"/>
+      <c r="N734" t="inlineStr"/>
+      <c r="O734" t="n">
+        <v>0.006517408800000001</v>
+      </c>
+      <c r="P734" t="inlineStr"/>
+      <c r="Q734" t="n">
+        <v>8.664e-07</v>
+      </c>
+      <c r="R734" t="inlineStr"/>
+      <c r="S734" t="inlineStr"/>
+      <c r="T734" t="inlineStr"/>
+      <c r="U734" t="inlineStr"/>
+      <c r="V734" t="inlineStr"/>
+      <c r="W734" t="inlineStr"/>
+      <c r="X734" t="inlineStr"/>
+      <c r="Y734" t="inlineStr"/>
+      <c r="Z734" t="inlineStr"/>
+      <c r="AA734" t="n">
+        <v>0.0284621181132</v>
+      </c>
+      <c r="AB734" t="inlineStr"/>
+      <c r="AC734" t="n">
+        <v>16.8994167389512</v>
+      </c>
+      <c r="AD734" t="n">
+        <v>262.393252955</v>
+      </c>
+      <c r="AE734" t="n">
+        <v>1954.109374473793</v>
+      </c>
+      <c r="AF734" t="n">
+        <v>18.9329</v>
+      </c>
+      <c r="AG734" t="n">
+        <v>33.34838890499999</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B735" t="n">
+        <v>0.5718024745</v>
+      </c>
+      <c r="C735" t="n">
+        <v>0.076977668</v>
+      </c>
+      <c r="D735" t="inlineStr"/>
+      <c r="E735" t="inlineStr"/>
+      <c r="F735" t="inlineStr"/>
+      <c r="G735" t="inlineStr"/>
+      <c r="H735" t="inlineStr"/>
+      <c r="I735" t="n">
+        <v>0.037995825</v>
+      </c>
+      <c r="J735" t="inlineStr"/>
+      <c r="K735" t="n">
+        <v>1624.511057074567</v>
+      </c>
+      <c r="L735" t="inlineStr"/>
+      <c r="M735" t="inlineStr"/>
+      <c r="N735" t="inlineStr"/>
+      <c r="O735" t="n">
+        <v>0.0065757252</v>
+      </c>
+      <c r="P735" t="inlineStr"/>
+      <c r="Q735" t="n">
+        <v>8.760000000000001e-07</v>
+      </c>
+      <c r="R735" t="inlineStr"/>
+      <c r="S735" t="inlineStr"/>
+      <c r="T735" t="inlineStr"/>
+      <c r="U735" t="inlineStr"/>
+      <c r="V735" t="inlineStr"/>
+      <c r="W735" t="inlineStr"/>
+      <c r="X735" t="inlineStr"/>
+      <c r="Y735" t="inlineStr"/>
+      <c r="Z735" t="inlineStr"/>
+      <c r="AA735" t="n">
+        <v>0.0284655307008</v>
+      </c>
+      <c r="AB735" t="inlineStr"/>
+      <c r="AC735" t="n">
+        <v>17.4024864764944</v>
+      </c>
+      <c r="AD735" t="n">
+        <v>258.610483575</v>
+      </c>
+      <c r="AE735" t="n">
+        <v>1954.194238198462</v>
+      </c>
+      <c r="AF735" t="n">
+        <v>19.06795</v>
+      </c>
+      <c r="AG735" t="n">
+        <v>33.880442973</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B736" t="n">
+        <v>0.5741339520000001</v>
+      </c>
+      <c r="C736" t="n">
+        <v>0.0763295475</v>
+      </c>
+      <c r="D736" t="inlineStr"/>
+      <c r="E736" t="inlineStr"/>
+      <c r="F736" t="inlineStr"/>
+      <c r="G736" t="inlineStr"/>
+      <c r="H736" t="inlineStr"/>
+      <c r="I736" t="n">
+        <v>0.03778313699999999</v>
+      </c>
+      <c r="J736" t="inlineStr"/>
+      <c r="K736" t="n">
+        <v>1637.045173800411</v>
+      </c>
+      <c r="L736" t="inlineStr"/>
+      <c r="M736" t="inlineStr"/>
+      <c r="N736" t="inlineStr"/>
+      <c r="O736" t="n">
+        <v>0.006578831400000001</v>
+      </c>
+      <c r="P736" t="inlineStr"/>
+      <c r="Q736" t="n">
+        <v>8.592e-07</v>
+      </c>
+      <c r="R736" t="inlineStr"/>
+      <c r="S736" t="inlineStr"/>
+      <c r="T736" t="inlineStr"/>
+      <c r="U736" t="inlineStr"/>
+      <c r="V736" t="inlineStr"/>
+      <c r="W736" t="inlineStr"/>
+      <c r="X736" t="inlineStr"/>
+      <c r="Y736" t="inlineStr"/>
+      <c r="Z736" t="inlineStr"/>
+      <c r="AA736" t="n">
+        <v>0.0284646775539</v>
+      </c>
+      <c r="AB736" t="inlineStr"/>
+      <c r="AC736" t="n">
+        <v>17.1788999264752</v>
+      </c>
+      <c r="AD736" t="n">
+        <v>252.42711055</v>
+      </c>
+      <c r="AE736" t="n">
+        <v>1959.71248793354</v>
+      </c>
+      <c r="AF736" t="n">
+        <v>18.91995</v>
+      </c>
+      <c r="AG736" t="n">
+        <v>33.418062652</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG736"/>
+  <dimension ref="A1:AG737"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57255,7 +57255,7 @@
         <v>327.50053363</v>
       </c>
       <c r="AE723" t="n">
-        <v>1978.117673776472</v>
+        <v>1978.117673776471</v>
       </c>
       <c r="AF723" t="n">
         <v>20.5942</v>
@@ -57804,7 +57804,7 @@
         <v>271.413703015</v>
       </c>
       <c r="AE732" t="n">
-        <v>1951.062067618578</v>
+        <v>1951.062067618577</v>
       </c>
       <c r="AF732" t="n">
         <v>19.18635</v>
@@ -58057,6 +58057,67 @@
         <v>33.418062652</v>
       </c>
     </row>
+    <row r="737">
+      <c r="A737" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B737" t="n">
+        <v>0.5760489744999999</v>
+      </c>
+      <c r="C737" t="n">
+        <v>0.07680791350000002</v>
+      </c>
+      <c r="D737" t="inlineStr"/>
+      <c r="E737" t="inlineStr"/>
+      <c r="F737" t="inlineStr"/>
+      <c r="G737" t="inlineStr"/>
+      <c r="H737" t="inlineStr"/>
+      <c r="I737" t="n">
+        <v>0.037690086</v>
+      </c>
+      <c r="J737" t="inlineStr"/>
+      <c r="K737" t="n">
+        <v>1664.351642381714</v>
+      </c>
+      <c r="L737" t="inlineStr"/>
+      <c r="M737" t="inlineStr"/>
+      <c r="N737" t="inlineStr"/>
+      <c r="O737" t="n">
+        <v>0.006644763000000001</v>
+      </c>
+      <c r="P737" t="inlineStr"/>
+      <c r="Q737" t="n">
+        <v>8.639999999999999e-07</v>
+      </c>
+      <c r="R737" t="inlineStr"/>
+      <c r="S737" t="inlineStr"/>
+      <c r="T737" t="inlineStr"/>
+      <c r="U737" t="inlineStr"/>
+      <c r="V737" t="inlineStr"/>
+      <c r="W737" t="inlineStr"/>
+      <c r="X737" t="inlineStr"/>
+      <c r="Y737" t="inlineStr"/>
+      <c r="Z737" t="inlineStr"/>
+      <c r="AA737" t="n">
+        <v>0.02845614608489999</v>
+      </c>
+      <c r="AB737" t="inlineStr"/>
+      <c r="AC737" t="n">
+        <v>17.23479656398</v>
+      </c>
+      <c r="AD737" t="n">
+        <v>255.846152105</v>
+      </c>
+      <c r="AE737" t="n">
+        <v>1990.453200518779</v>
+      </c>
+      <c r="AF737" t="n">
+        <v>18.8959</v>
+      </c>
+      <c r="AG737" t="n">
+        <v>33.399060721</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG737"/>
+  <dimension ref="A1:AG738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57804,7 +57804,7 @@
         <v>271.413703015</v>
       </c>
       <c r="AE732" t="n">
-        <v>1951.062067618577</v>
+        <v>1951.062067618578</v>
       </c>
       <c r="AF732" t="n">
         <v>19.18635</v>
@@ -58118,6 +58118,67 @@
         <v>33.399060721</v>
       </c>
     </row>
+    <row r="738">
+      <c r="A738" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B738" t="n">
+        <v>0.5656785744999999</v>
+      </c>
+      <c r="C738" t="n">
+        <v>0.07538153950000001</v>
+      </c>
+      <c r="D738" t="inlineStr"/>
+      <c r="E738" t="inlineStr"/>
+      <c r="F738" t="inlineStr"/>
+      <c r="G738" t="inlineStr"/>
+      <c r="H738" t="inlineStr"/>
+      <c r="I738" t="n">
+        <v>0.037096332</v>
+      </c>
+      <c r="J738" t="inlineStr"/>
+      <c r="K738" t="n">
+        <v>1681.362229366788</v>
+      </c>
+      <c r="L738" t="inlineStr"/>
+      <c r="M738" t="inlineStr"/>
+      <c r="N738" t="inlineStr"/>
+      <c r="O738" t="n">
+        <v>0.0065774286</v>
+      </c>
+      <c r="P738" t="inlineStr"/>
+      <c r="Q738" t="n">
+        <v>8.448e-07</v>
+      </c>
+      <c r="R738" t="inlineStr"/>
+      <c r="S738" t="inlineStr"/>
+      <c r="T738" t="inlineStr"/>
+      <c r="U738" t="inlineStr"/>
+      <c r="V738" t="inlineStr"/>
+      <c r="W738" t="inlineStr"/>
+      <c r="X738" t="inlineStr"/>
+      <c r="Y738" t="inlineStr"/>
+      <c r="Z738" t="inlineStr"/>
+      <c r="AA738" t="n">
+        <v>0.028469512053</v>
+      </c>
+      <c r="AB738" t="inlineStr"/>
+      <c r="AC738" t="n">
+        <v>16.9180489514528</v>
+      </c>
+      <c r="AD738" t="n">
+        <v>249.80827021</v>
+      </c>
+      <c r="AE738" t="n">
+        <v>2000.382011343694</v>
+      </c>
+      <c r="AF738" t="n">
+        <v>18.69425</v>
+      </c>
+      <c r="AG738" t="n">
+        <v>32.886008584</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG738"/>
+  <dimension ref="A1:AG739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57804,7 +57804,7 @@
         <v>271.413703015</v>
       </c>
       <c r="AE732" t="n">
-        <v>1951.062067618578</v>
+        <v>1951.062067618577</v>
       </c>
       <c r="AF732" t="n">
         <v>19.18635</v>
@@ -58179,6 +58179,67 @@
         <v>32.886008584</v>
       </c>
     </row>
+    <row r="739">
+      <c r="A739" s="2" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B739" t="n">
+        <v>0.554647285</v>
+      </c>
+      <c r="C739" t="n">
+        <v>0.07360293400000001</v>
+      </c>
+      <c r="D739" t="inlineStr"/>
+      <c r="E739" t="inlineStr"/>
+      <c r="F739" t="inlineStr"/>
+      <c r="G739" t="inlineStr"/>
+      <c r="H739" t="inlineStr"/>
+      <c r="I739" t="n">
+        <v>0.036529164</v>
+      </c>
+      <c r="J739" t="inlineStr"/>
+      <c r="K739" t="n">
+        <v>1647.788702422563</v>
+      </c>
+      <c r="L739" t="inlineStr"/>
+      <c r="M739" t="inlineStr"/>
+      <c r="N739" t="inlineStr"/>
+      <c r="O739" t="n">
+        <v>0.006501376800000001</v>
+      </c>
+      <c r="P739" t="inlineStr"/>
+      <c r="Q739" t="n">
+        <v>8.352e-07</v>
+      </c>
+      <c r="R739" t="inlineStr"/>
+      <c r="S739" t="inlineStr"/>
+      <c r="T739" t="inlineStr"/>
+      <c r="U739" t="inlineStr"/>
+      <c r="V739" t="inlineStr"/>
+      <c r="W739" t="inlineStr"/>
+      <c r="X739" t="inlineStr"/>
+      <c r="Y739" t="inlineStr"/>
+      <c r="Z739" t="inlineStr"/>
+      <c r="AA739" t="n">
+        <v>0.0284703651999</v>
+      </c>
+      <c r="AB739" t="inlineStr"/>
+      <c r="AC739" t="n">
+        <v>15.8001162013568</v>
+      </c>
+      <c r="AD739" t="n">
+        <v>243.55215162</v>
+      </c>
+      <c r="AE739" t="n">
+        <v>1959.34905067312</v>
+      </c>
+      <c r="AF739" t="n">
+        <v>18.59065</v>
+      </c>
+      <c r="AG739" t="n">
+        <v>32.91767846899999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG739"/>
+  <dimension ref="A1:AG742"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56584,7 +56584,7 @@
         <v>62.60779999999999</v>
       </c>
       <c r="AE712" t="n">
-        <v>1857.68020310496</v>
+        <v>1857.680203104961</v>
       </c>
       <c r="AF712" t="n">
         <v>0</v>
@@ -57255,7 +57255,7 @@
         <v>327.50053363</v>
       </c>
       <c r="AE723" t="n">
-        <v>1978.117673776471</v>
+        <v>1978.117673776472</v>
       </c>
       <c r="AF723" t="n">
         <v>20.5942</v>
@@ -58240,6 +58240,189 @@
         <v>32.91767846899999</v>
       </c>
     </row>
+    <row r="740">
+      <c r="A740" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B740" t="n">
+        <v>0.5484504495</v>
+      </c>
+      <c r="C740" t="n">
+        <v>0.07305986500000002</v>
+      </c>
+      <c r="D740" t="inlineStr"/>
+      <c r="E740" t="inlineStr"/>
+      <c r="F740" t="inlineStr"/>
+      <c r="G740" t="inlineStr"/>
+      <c r="H740" t="inlineStr"/>
+      <c r="I740" t="n">
+        <v>0.036382941</v>
+      </c>
+      <c r="J740" t="inlineStr"/>
+      <c r="K740" t="n">
+        <v>1580.19400150819</v>
+      </c>
+      <c r="L740" t="inlineStr"/>
+      <c r="M740" t="inlineStr"/>
+      <c r="N740" t="inlineStr"/>
+      <c r="O740" t="n">
+        <v>0.0063951648</v>
+      </c>
+      <c r="P740" t="inlineStr"/>
+      <c r="Q740" t="n">
+        <v>8.136e-07</v>
+      </c>
+      <c r="R740" t="inlineStr"/>
+      <c r="S740" t="inlineStr"/>
+      <c r="T740" t="inlineStr"/>
+      <c r="U740" t="inlineStr"/>
+      <c r="V740" t="inlineStr"/>
+      <c r="W740" t="inlineStr"/>
+      <c r="X740" t="inlineStr"/>
+      <c r="Y740" t="inlineStr"/>
+      <c r="Z740" t="inlineStr"/>
+      <c r="AA740" t="n">
+        <v>0.0284655307008</v>
+      </c>
+      <c r="AB740" t="inlineStr"/>
+      <c r="AC740" t="n">
+        <v>15.092092126296</v>
+      </c>
+      <c r="AD740" t="n">
+        <v>218.454931695</v>
+      </c>
+      <c r="AE740" t="n">
+        <v>1865.581889253087</v>
+      </c>
+      <c r="AF740" t="n">
+        <v>18.42045</v>
+      </c>
+      <c r="AG740" t="n">
+        <v>32.727659159</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B741" t="n">
+        <v>0.547282811</v>
+      </c>
+      <c r="C741" t="n">
+        <v>0.073228529</v>
+      </c>
+      <c r="D741" t="inlineStr"/>
+      <c r="E741" t="inlineStr"/>
+      <c r="F741" t="inlineStr"/>
+      <c r="G741" t="inlineStr"/>
+      <c r="H741" t="inlineStr"/>
+      <c r="I741" t="n">
+        <v>0.036351924</v>
+      </c>
+      <c r="J741" t="inlineStr"/>
+      <c r="K741" t="n">
+        <v>1541.696357278812</v>
+      </c>
+      <c r="L741" t="inlineStr"/>
+      <c r="M741" t="inlineStr"/>
+      <c r="N741" t="inlineStr"/>
+      <c r="O741" t="n">
+        <v>0.006443862000000001</v>
+      </c>
+      <c r="P741" t="inlineStr"/>
+      <c r="Q741" t="n">
+        <v>8.136e-07</v>
+      </c>
+      <c r="R741" t="inlineStr"/>
+      <c r="S741" t="inlineStr"/>
+      <c r="T741" t="inlineStr"/>
+      <c r="U741" t="inlineStr"/>
+      <c r="V741" t="inlineStr"/>
+      <c r="W741" t="inlineStr"/>
+      <c r="X741" t="inlineStr"/>
+      <c r="Y741" t="inlineStr"/>
+      <c r="Z741" t="inlineStr"/>
+      <c r="AA741" t="n">
+        <v>0.0284635400247</v>
+      </c>
+      <c r="AB741" t="inlineStr"/>
+      <c r="AC741" t="n">
+        <v>15.278414251312</v>
+      </c>
+      <c r="AD741" t="n">
+        <v>219.909842995</v>
+      </c>
+      <c r="AE741" t="n">
+        <v>1828.887892657749</v>
+      </c>
+      <c r="AF741" t="n">
+        <v>18.4445</v>
+      </c>
+      <c r="AG741" t="n">
+        <v>32.867006653</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B742" t="n">
+        <v>0.550438631</v>
+      </c>
+      <c r="C742" t="n">
+        <v>0.07351569400000001</v>
+      </c>
+      <c r="D742" t="inlineStr"/>
+      <c r="E742" t="inlineStr"/>
+      <c r="F742" t="inlineStr"/>
+      <c r="G742" t="inlineStr"/>
+      <c r="H742" t="inlineStr"/>
+      <c r="I742" t="n">
+        <v>0.036657663</v>
+      </c>
+      <c r="J742" t="inlineStr"/>
+      <c r="K742" t="n">
+        <v>1558.259297237963</v>
+      </c>
+      <c r="L742" t="inlineStr"/>
+      <c r="M742" t="inlineStr"/>
+      <c r="N742" t="inlineStr"/>
+      <c r="O742" t="n">
+        <v>0.0072017748</v>
+      </c>
+      <c r="P742" t="inlineStr"/>
+      <c r="Q742" t="n">
+        <v>8.184e-07</v>
+      </c>
+      <c r="R742" t="inlineStr"/>
+      <c r="S742" t="inlineStr"/>
+      <c r="T742" t="inlineStr"/>
+      <c r="U742" t="inlineStr"/>
+      <c r="V742" t="inlineStr"/>
+      <c r="W742" t="inlineStr"/>
+      <c r="X742" t="inlineStr"/>
+      <c r="Y742" t="inlineStr"/>
+      <c r="Z742" t="inlineStr"/>
+      <c r="AA742" t="n">
+        <v>0.0284680901415</v>
+      </c>
+      <c r="AB742" t="inlineStr"/>
+      <c r="AC742" t="n">
+        <v>15.3529431013184</v>
+      </c>
+      <c r="AD742" t="n">
+        <v>220.928280905</v>
+      </c>
+      <c r="AE742" t="n">
+        <v>1847.071363280623</v>
+      </c>
+      <c r="AF742" t="n">
+        <v>18.61285</v>
+      </c>
+      <c r="AG742" t="n">
+        <v>33.221709365</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -57316,7 +57316,7 @@
         <v>319.78950374</v>
       </c>
       <c r="AE724" t="n">
-        <v>1961.716148685499</v>
+        <v>1961.7161486855</v>
       </c>
       <c r="AF724" t="n">
         <v>20.37775</v>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG742"/>
+  <dimension ref="A1:AH745"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -593,6 +593,11 @@
       <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>LTCUSDT</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>XLMUSDT</t>
         </is>
       </c>
     </row>
@@ -658,6 +663,7 @@
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -721,6 +727,7 @@
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -784,6 +791,7 @@
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -847,6 +855,7 @@
       </c>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -910,6 +919,7 @@
       </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -973,6 +983,7 @@
       </c>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1046,6 +1057,7 @@
       </c>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1129,6 +1141,7 @@
       </c>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1212,6 +1225,7 @@
       </c>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1295,6 +1309,7 @@
       </c>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1378,6 +1393,7 @@
       </c>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1461,6 +1477,7 @@
       </c>
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1544,6 +1561,7 @@
       </c>
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1627,6 +1645,7 @@
       </c>
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1710,6 +1729,7 @@
       </c>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1793,6 +1813,7 @@
       </c>
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1876,6 +1897,7 @@
       </c>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1959,6 +1981,7 @@
       </c>
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -2042,6 +2065,7 @@
       </c>
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -2125,6 +2149,7 @@
       </c>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -2208,6 +2233,7 @@
       </c>
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -2291,6 +2317,7 @@
       </c>
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -2374,6 +2401,7 @@
       </c>
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -2457,6 +2485,7 @@
       </c>
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -2540,6 +2569,7 @@
       </c>
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -2625,6 +2655,7 @@
       </c>
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -2710,6 +2741,7 @@
       </c>
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -2795,6 +2827,7 @@
       </c>
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -2880,6 +2913,7 @@
       </c>
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -2965,6 +2999,7 @@
       </c>
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -3050,6 +3085,7 @@
       </c>
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -3135,6 +3171,7 @@
       </c>
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -3220,6 +3257,7 @@
       </c>
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -3305,6 +3343,7 @@
       </c>
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -3390,6 +3429,7 @@
       </c>
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -3475,6 +3515,7 @@
       </c>
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -3560,6 +3601,7 @@
       </c>
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -3645,6 +3687,7 @@
       </c>
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -3730,6 +3773,7 @@
       </c>
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -3815,6 +3859,7 @@
       </c>
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -3900,6 +3945,7 @@
       </c>
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -3985,6 +4031,7 @@
       </c>
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -4070,6 +4117,7 @@
       </c>
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -4155,6 +4203,7 @@
       </c>
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -4240,6 +4289,7 @@
       </c>
       <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -4325,6 +4375,7 @@
       </c>
       <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -4410,6 +4461,7 @@
       </c>
       <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -4497,6 +4549,7 @@
       </c>
       <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -4584,6 +4637,7 @@
       </c>
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -4671,6 +4725,7 @@
       </c>
       <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -4758,6 +4813,7 @@
       </c>
       <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -4845,6 +4901,7 @@
       </c>
       <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -4932,6 +4989,7 @@
       </c>
       <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -5019,6 +5077,7 @@
       </c>
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -5106,6 +5165,7 @@
       </c>
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -5195,6 +5255,7 @@
       </c>
       <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="inlineStr"/>
+      <c r="AH57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -5284,6 +5345,7 @@
       </c>
       <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="inlineStr"/>
+      <c r="AH58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -5373,6 +5435,7 @@
       </c>
       <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="inlineStr"/>
+      <c r="AH59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -5462,6 +5525,7 @@
       </c>
       <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="inlineStr"/>
+      <c r="AH60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -5551,6 +5615,7 @@
       </c>
       <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -5640,6 +5705,7 @@
       </c>
       <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -5729,6 +5795,7 @@
       </c>
       <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="inlineStr"/>
+      <c r="AH63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -5818,6 +5885,7 @@
       </c>
       <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="inlineStr"/>
+      <c r="AH64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -5903,10 +5971,11 @@
       <c r="AC65" t="inlineStr"/>
       <c r="AD65" t="inlineStr"/>
       <c r="AE65" t="n">
-        <v>2202.520933018481</v>
+        <v>2202.520933018482</v>
       </c>
       <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="inlineStr"/>
+      <c r="AH65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -5996,6 +6065,7 @@
       </c>
       <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="inlineStr"/>
+      <c r="AH66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -6085,6 +6155,7 @@
       </c>
       <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="inlineStr"/>
+      <c r="AH67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -6174,6 +6245,7 @@
       </c>
       <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="inlineStr"/>
+      <c r="AH68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -6263,6 +6335,7 @@
       </c>
       <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="inlineStr"/>
+      <c r="AH69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -6352,6 +6425,7 @@
       </c>
       <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="inlineStr"/>
+      <c r="AH70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -6441,6 +6515,7 @@
       </c>
       <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="inlineStr"/>
+      <c r="AH71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -6530,6 +6605,7 @@
       </c>
       <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="inlineStr"/>
+      <c r="AH72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -6619,6 +6695,7 @@
       </c>
       <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="inlineStr"/>
+      <c r="AH73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -6708,6 +6785,7 @@
       </c>
       <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="inlineStr"/>
+      <c r="AH74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -6797,6 +6875,7 @@
       </c>
       <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="inlineStr"/>
+      <c r="AH75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -6882,10 +6961,11 @@
       <c r="AC76" t="inlineStr"/>
       <c r="AD76" t="inlineStr"/>
       <c r="AE76" t="n">
-        <v>1947.660429315914</v>
+        <v>1947.660429315913</v>
       </c>
       <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="inlineStr"/>
+      <c r="AH76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -6975,6 +7055,7 @@
       </c>
       <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="inlineStr"/>
+      <c r="AH77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -7064,6 +7145,7 @@
       </c>
       <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="inlineStr"/>
+      <c r="AH78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -7153,6 +7235,7 @@
       </c>
       <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="inlineStr"/>
+      <c r="AH79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -7242,6 +7325,7 @@
       </c>
       <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="inlineStr"/>
+      <c r="AH80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -7331,6 +7415,7 @@
       </c>
       <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="inlineStr"/>
+      <c r="AH81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -7420,6 +7505,7 @@
       </c>
       <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="inlineStr"/>
+      <c r="AH82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -7509,6 +7595,7 @@
       </c>
       <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="inlineStr"/>
+      <c r="AH83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -7598,6 +7685,7 @@
       </c>
       <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="inlineStr"/>
+      <c r="AH84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -7683,10 +7771,11 @@
       <c r="AC85" t="inlineStr"/>
       <c r="AD85" t="inlineStr"/>
       <c r="AE85" t="n">
-        <v>1788.254192413208</v>
+        <v>1788.254192413207</v>
       </c>
       <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="inlineStr"/>
+      <c r="AH85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -7776,6 +7865,7 @@
       </c>
       <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="inlineStr"/>
+      <c r="AH86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -7865,6 +7955,7 @@
       </c>
       <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="inlineStr"/>
+      <c r="AH87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -7954,6 +8045,7 @@
       </c>
       <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="inlineStr"/>
+      <c r="AH88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -8043,6 +8135,7 @@
       </c>
       <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="inlineStr"/>
+      <c r="AH89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -8132,6 +8225,7 @@
       </c>
       <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="inlineStr"/>
+      <c r="AH90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
@@ -8221,6 +8315,7 @@
       </c>
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="inlineStr"/>
+      <c r="AH91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -8306,10 +8401,11 @@
       <c r="AC92" t="inlineStr"/>
       <c r="AD92" t="inlineStr"/>
       <c r="AE92" t="n">
-        <v>1799.425152668883</v>
+        <v>1799.425152668884</v>
       </c>
       <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="inlineStr"/>
+      <c r="AH92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
@@ -8399,6 +8495,7 @@
       </c>
       <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="inlineStr"/>
+      <c r="AH93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -8488,6 +8585,7 @@
       </c>
       <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="inlineStr"/>
+      <c r="AH94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
@@ -8577,6 +8675,7 @@
       </c>
       <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="inlineStr"/>
+      <c r="AH95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -8666,6 +8765,7 @@
       </c>
       <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="inlineStr"/>
+      <c r="AH96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
@@ -8755,6 +8855,7 @@
       </c>
       <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="inlineStr"/>
+      <c r="AH97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -8844,6 +8945,7 @@
       </c>
       <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="inlineStr"/>
+      <c r="AH98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -8933,6 +9035,7 @@
       </c>
       <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="inlineStr"/>
+      <c r="AH99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -9022,6 +9125,7 @@
       </c>
       <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="inlineStr"/>
+      <c r="AH100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -9111,6 +9215,7 @@
       </c>
       <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="inlineStr"/>
+      <c r="AH101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -9200,6 +9305,7 @@
       </c>
       <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="inlineStr"/>
+      <c r="AH102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
@@ -9289,6 +9395,7 @@
       </c>
       <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="inlineStr"/>
+      <c r="AH103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -9378,6 +9485,7 @@
       </c>
       <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="inlineStr"/>
+      <c r="AH104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
@@ -9467,6 +9575,7 @@
       </c>
       <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="inlineStr"/>
+      <c r="AH105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -9556,6 +9665,7 @@
       </c>
       <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="inlineStr"/>
+      <c r="AH106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
@@ -9645,6 +9755,7 @@
       </c>
       <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="inlineStr"/>
+      <c r="AH107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -9734,6 +9845,7 @@
       </c>
       <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="inlineStr"/>
+      <c r="AH108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
@@ -9823,6 +9935,7 @@
       </c>
       <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="inlineStr"/>
+      <c r="AH109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -9912,6 +10025,7 @@
       </c>
       <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="inlineStr"/>
+      <c r="AH110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
@@ -10001,6 +10115,7 @@
       </c>
       <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="inlineStr"/>
+      <c r="AH111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -10090,6 +10205,7 @@
       </c>
       <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="inlineStr"/>
+      <c r="AH112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
@@ -10179,6 +10295,7 @@
       </c>
       <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="inlineStr"/>
+      <c r="AH113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -10268,6 +10385,7 @@
       </c>
       <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="inlineStr"/>
+      <c r="AH114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
@@ -10357,6 +10475,7 @@
       </c>
       <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="inlineStr"/>
+      <c r="AH115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -10442,10 +10561,11 @@
       <c r="AC116" t="inlineStr"/>
       <c r="AD116" t="inlineStr"/>
       <c r="AE116" t="n">
-        <v>1791.893198358887</v>
+        <v>1791.893198358888</v>
       </c>
       <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="inlineStr"/>
+      <c r="AH116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
@@ -10535,6 +10655,7 @@
       </c>
       <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="inlineStr"/>
+      <c r="AH117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -10624,6 +10745,7 @@
       </c>
       <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="inlineStr"/>
+      <c r="AH118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
@@ -10713,6 +10835,7 @@
       </c>
       <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="inlineStr"/>
+      <c r="AH119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -10802,6 +10925,7 @@
       </c>
       <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="inlineStr"/>
+      <c r="AH120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
@@ -10891,6 +11015,7 @@
       </c>
       <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="inlineStr"/>
+      <c r="AH121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
@@ -10980,6 +11105,7 @@
       </c>
       <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="inlineStr"/>
+      <c r="AH122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
@@ -11065,10 +11191,11 @@
       <c r="AC123" t="inlineStr"/>
       <c r="AD123" t="inlineStr"/>
       <c r="AE123" t="n">
-        <v>1867.044037449003</v>
+        <v>1867.044037449004</v>
       </c>
       <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="inlineStr"/>
+      <c r="AH123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
@@ -11158,6 +11285,7 @@
       </c>
       <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="inlineStr"/>
+      <c r="AH124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
@@ -11247,6 +11375,7 @@
       </c>
       <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="inlineStr"/>
+      <c r="AH125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -11336,6 +11465,7 @@
       </c>
       <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="inlineStr"/>
+      <c r="AH126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
@@ -11421,10 +11551,11 @@
       <c r="AC127" t="inlineStr"/>
       <c r="AD127" t="inlineStr"/>
       <c r="AE127" t="n">
-        <v>1924.603525782934</v>
+        <v>1924.603525782933</v>
       </c>
       <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="inlineStr"/>
+      <c r="AH127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
@@ -11514,6 +11645,7 @@
       </c>
       <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="inlineStr"/>
+      <c r="AH128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
@@ -11603,6 +11735,7 @@
       </c>
       <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="inlineStr"/>
+      <c r="AH129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
@@ -11688,10 +11821,11 @@
       <c r="AC130" t="inlineStr"/>
       <c r="AD130" t="inlineStr"/>
       <c r="AE130" t="n">
-        <v>1954.489288395226</v>
+        <v>1954.489288395225</v>
       </c>
       <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="inlineStr"/>
+      <c r="AH130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
@@ -11777,10 +11911,11 @@
       <c r="AC131" t="inlineStr"/>
       <c r="AD131" t="inlineStr"/>
       <c r="AE131" t="n">
-        <v>2040.188505816031</v>
+        <v>2040.188505816032</v>
       </c>
       <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="inlineStr"/>
+      <c r="AH131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
@@ -11870,6 +12005,7 @@
       </c>
       <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="inlineStr"/>
+      <c r="AH132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
@@ -11959,6 +12095,7 @@
       </c>
       <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="inlineStr"/>
+      <c r="AH133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
@@ -12048,6 +12185,7 @@
       </c>
       <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="inlineStr"/>
+      <c r="AH134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
@@ -12137,6 +12275,7 @@
       </c>
       <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="inlineStr"/>
+      <c r="AH135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
@@ -12226,6 +12365,7 @@
       </c>
       <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="inlineStr"/>
+      <c r="AH136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
@@ -12315,6 +12455,7 @@
       </c>
       <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="inlineStr"/>
+      <c r="AH137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
@@ -12404,6 +12545,7 @@
       </c>
       <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="inlineStr"/>
+      <c r="AH138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
@@ -12493,6 +12635,7 @@
       </c>
       <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="inlineStr"/>
+      <c r="AH139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
@@ -12582,6 +12725,7 @@
       </c>
       <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="inlineStr"/>
+      <c r="AH140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
@@ -12671,6 +12815,7 @@
       </c>
       <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="inlineStr"/>
+      <c r="AH141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
@@ -12760,6 +12905,7 @@
       </c>
       <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="inlineStr"/>
+      <c r="AH142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
@@ -12849,6 +12995,7 @@
       </c>
       <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="inlineStr"/>
+      <c r="AH143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
@@ -12938,6 +13085,7 @@
       </c>
       <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="inlineStr"/>
+      <c r="AH144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
@@ -13023,10 +13171,11 @@
       <c r="AC145" t="inlineStr"/>
       <c r="AD145" t="inlineStr"/>
       <c r="AE145" t="n">
-        <v>1968.895198184082</v>
+        <v>1968.895198184083</v>
       </c>
       <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="inlineStr"/>
+      <c r="AH145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
@@ -13116,6 +13265,7 @@
       </c>
       <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="inlineStr"/>
+      <c r="AH146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
@@ -13205,6 +13355,7 @@
       </c>
       <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="inlineStr"/>
+      <c r="AH147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
@@ -13294,6 +13445,7 @@
       </c>
       <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="inlineStr"/>
+      <c r="AH148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
@@ -13383,6 +13535,7 @@
       </c>
       <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="inlineStr"/>
+      <c r="AH149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
@@ -13468,10 +13621,11 @@
       <c r="AC150" t="inlineStr"/>
       <c r="AD150" t="inlineStr"/>
       <c r="AE150" t="n">
-        <v>2153.372857627961</v>
+        <v>2153.372857627962</v>
       </c>
       <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="inlineStr"/>
+      <c r="AH150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
@@ -13561,6 +13715,7 @@
       </c>
       <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="inlineStr"/>
+      <c r="AH151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
@@ -13650,6 +13805,7 @@
       </c>
       <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="inlineStr"/>
+      <c r="AH152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
@@ -13739,6 +13895,7 @@
       </c>
       <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="inlineStr"/>
+      <c r="AH153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
@@ -13828,6 +13985,7 @@
       </c>
       <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="inlineStr"/>
+      <c r="AH154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
@@ -13917,6 +14075,7 @@
       </c>
       <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="inlineStr"/>
+      <c r="AH155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
@@ -14006,6 +14165,7 @@
       </c>
       <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="inlineStr"/>
+      <c r="AH156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
@@ -14095,6 +14255,7 @@
       </c>
       <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="inlineStr"/>
+      <c r="AH157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
@@ -14184,6 +14345,7 @@
       </c>
       <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="inlineStr"/>
+      <c r="AH158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
@@ -14273,6 +14435,7 @@
       </c>
       <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="inlineStr"/>
+      <c r="AH159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
@@ -14362,6 +14525,7 @@
       </c>
       <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="inlineStr"/>
+      <c r="AH160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
@@ -14447,10 +14611,11 @@
       <c r="AC161" t="inlineStr"/>
       <c r="AD161" t="inlineStr"/>
       <c r="AE161" t="n">
-        <v>1994.517272634397</v>
+        <v>1994.517272634398</v>
       </c>
       <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="inlineStr"/>
+      <c r="AH161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
@@ -14540,6 +14705,7 @@
       </c>
       <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="inlineStr"/>
+      <c r="AH162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
@@ -14629,6 +14795,7 @@
       </c>
       <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="inlineStr"/>
+      <c r="AH163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
@@ -14718,6 +14885,7 @@
       </c>
       <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="inlineStr"/>
+      <c r="AH164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
@@ -14803,10 +14971,11 @@
       <c r="AC165" t="inlineStr"/>
       <c r="AD165" t="inlineStr"/>
       <c r="AE165" t="n">
-        <v>2161.720775759261</v>
+        <v>2161.72077575926</v>
       </c>
       <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="inlineStr"/>
+      <c r="AH165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
@@ -14896,6 +15065,7 @@
       </c>
       <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="inlineStr"/>
+      <c r="AH166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
@@ -14985,6 +15155,7 @@
       </c>
       <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="inlineStr"/>
+      <c r="AH167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
@@ -15074,6 +15245,7 @@
       </c>
       <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="inlineStr"/>
+      <c r="AH168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
@@ -15163,6 +15335,7 @@
       </c>
       <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="inlineStr"/>
+      <c r="AH169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
@@ -15252,6 +15425,7 @@
       </c>
       <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="inlineStr"/>
+      <c r="AH170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
@@ -15341,6 +15515,7 @@
       </c>
       <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="inlineStr"/>
+      <c r="AH171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
@@ -15426,10 +15601,11 @@
       <c r="AC172" t="inlineStr"/>
       <c r="AD172" t="inlineStr"/>
       <c r="AE172" t="n">
-        <v>2239.082677776151</v>
+        <v>2239.082677776152</v>
       </c>
       <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="inlineStr"/>
+      <c r="AH172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
@@ -15519,6 +15695,7 @@
       </c>
       <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="inlineStr"/>
+      <c r="AH173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
@@ -15608,6 +15785,7 @@
       </c>
       <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="inlineStr"/>
+      <c r="AH174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
@@ -15697,6 +15875,7 @@
       </c>
       <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="inlineStr"/>
+      <c r="AH175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
@@ -15786,6 +15965,7 @@
       </c>
       <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="inlineStr"/>
+      <c r="AH176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
@@ -15871,10 +16051,11 @@
       <c r="AC177" t="inlineStr"/>
       <c r="AD177" t="inlineStr"/>
       <c r="AE177" t="n">
-        <v>2545.469570580479</v>
+        <v>2545.469570580478</v>
       </c>
       <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="inlineStr"/>
+      <c r="AH177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
@@ -15964,6 +16145,7 @@
       </c>
       <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="inlineStr"/>
+      <c r="AH178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
@@ -16053,6 +16235,7 @@
       </c>
       <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="inlineStr"/>
+      <c r="AH179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
@@ -16142,6 +16325,7 @@
       </c>
       <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="inlineStr"/>
+      <c r="AH180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
@@ -16231,6 +16415,7 @@
       </c>
       <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="inlineStr"/>
+      <c r="AH181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
@@ -16320,6 +16505,7 @@
       </c>
       <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="inlineStr"/>
+      <c r="AH182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
@@ -16409,6 +16595,7 @@
       </c>
       <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="inlineStr"/>
+      <c r="AH183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
@@ -16498,6 +16685,7 @@
       </c>
       <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="inlineStr"/>
+      <c r="AH184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
@@ -16583,10 +16771,11 @@
       <c r="AC185" t="inlineStr"/>
       <c r="AD185" t="inlineStr"/>
       <c r="AE185" t="n">
-        <v>3655.196673489481</v>
+        <v>3655.196673489482</v>
       </c>
       <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="inlineStr"/>
+      <c r="AH185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
@@ -16672,10 +16861,11 @@
       <c r="AC186" t="inlineStr"/>
       <c r="AD186" t="inlineStr"/>
       <c r="AE186" t="n">
-        <v>3620.975326277958</v>
+        <v>3620.975326277957</v>
       </c>
       <c r="AF186" t="inlineStr"/>
       <c r="AG186" t="inlineStr"/>
+      <c r="AH186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
@@ -16765,6 +16955,7 @@
       </c>
       <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="inlineStr"/>
+      <c r="AH187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
@@ -16854,6 +17045,7 @@
       </c>
       <c r="AF188" t="inlineStr"/>
       <c r="AG188" t="inlineStr"/>
+      <c r="AH188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
@@ -16943,6 +17135,7 @@
       </c>
       <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="inlineStr"/>
+      <c r="AH189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
@@ -17032,6 +17225,7 @@
       </c>
       <c r="AF190" t="inlineStr"/>
       <c r="AG190" t="inlineStr"/>
+      <c r="AH190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
@@ -17121,6 +17315,7 @@
       </c>
       <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="inlineStr"/>
+      <c r="AH191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
@@ -17210,6 +17405,7 @@
       </c>
       <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="inlineStr"/>
+      <c r="AH192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
@@ -17295,10 +17491,11 @@
       <c r="AC193" t="inlineStr"/>
       <c r="AD193" t="inlineStr"/>
       <c r="AE193" t="n">
-        <v>3643.664395245971</v>
+        <v>3643.66439524597</v>
       </c>
       <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="inlineStr"/>
+      <c r="AH193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
@@ -17388,6 +17585,7 @@
       </c>
       <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="inlineStr"/>
+      <c r="AH194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
@@ -17477,6 +17675,7 @@
       </c>
       <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="inlineStr"/>
+      <c r="AH195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
@@ -17566,6 +17765,7 @@
       </c>
       <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="inlineStr"/>
+      <c r="AH196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
@@ -17655,6 +17855,7 @@
       </c>
       <c r="AF197" t="inlineStr"/>
       <c r="AG197" t="inlineStr"/>
+      <c r="AH197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
@@ -17744,6 +17945,7 @@
       </c>
       <c r="AF198" t="inlineStr"/>
       <c r="AG198" t="inlineStr"/>
+      <c r="AH198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
@@ -17829,10 +18031,11 @@
       <c r="AC199" t="inlineStr"/>
       <c r="AD199" t="inlineStr"/>
       <c r="AE199" t="n">
-        <v>4122.917512499476</v>
+        <v>4122.917512499475</v>
       </c>
       <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="inlineStr"/>
+      <c r="AH199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
@@ -17918,10 +18121,11 @@
       <c r="AC200" t="inlineStr"/>
       <c r="AD200" t="inlineStr"/>
       <c r="AE200" t="n">
-        <v>4046.535306439408</v>
+        <v>4046.535306439409</v>
       </c>
       <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="inlineStr"/>
+      <c r="AH200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
@@ -18007,10 +18211,11 @@
       <c r="AC201" t="inlineStr"/>
       <c r="AD201" t="inlineStr"/>
       <c r="AE201" t="n">
-        <v>4307.668391641832</v>
+        <v>4307.668391641831</v>
       </c>
       <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="inlineStr"/>
+      <c r="AH201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
@@ -18100,6 +18305,7 @@
       </c>
       <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="inlineStr"/>
+      <c r="AH202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
@@ -18189,6 +18395,7 @@
       </c>
       <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="inlineStr"/>
+      <c r="AH203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
@@ -18278,6 +18485,7 @@
       </c>
       <c r="AF204" t="inlineStr"/>
       <c r="AG204" t="inlineStr"/>
+      <c r="AH204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
@@ -18367,6 +18575,7 @@
       </c>
       <c r="AF205" t="inlineStr"/>
       <c r="AG205" t="inlineStr"/>
+      <c r="AH205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
@@ -18456,6 +18665,7 @@
       </c>
       <c r="AF206" t="inlineStr"/>
       <c r="AG206" t="inlineStr"/>
+      <c r="AH206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
@@ -18545,6 +18755,7 @@
       </c>
       <c r="AF207" t="inlineStr"/>
       <c r="AG207" t="inlineStr"/>
+      <c r="AH207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
@@ -18630,10 +18841,11 @@
       <c r="AC208" t="inlineStr"/>
       <c r="AD208" t="inlineStr"/>
       <c r="AE208" t="n">
-        <v>4172.341087935875</v>
+        <v>4172.341087935874</v>
       </c>
       <c r="AF208" t="inlineStr"/>
       <c r="AG208" t="inlineStr"/>
+      <c r="AH208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
@@ -18723,6 +18935,7 @@
       </c>
       <c r="AF209" t="inlineStr"/>
       <c r="AG209" t="inlineStr"/>
+      <c r="AH209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
@@ -18812,6 +19025,7 @@
       </c>
       <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="inlineStr"/>
+      <c r="AH210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
@@ -18901,6 +19115,7 @@
       </c>
       <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="inlineStr"/>
+      <c r="AH211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
@@ -18986,10 +19201,11 @@
       <c r="AC212" t="inlineStr"/>
       <c r="AD212" t="inlineStr"/>
       <c r="AE212" t="n">
-        <v>4209.438043186523</v>
+        <v>4209.438043186524</v>
       </c>
       <c r="AF212" t="inlineStr"/>
       <c r="AG212" t="inlineStr"/>
+      <c r="AH212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
@@ -19079,6 +19295,7 @@
       </c>
       <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="inlineStr"/>
+      <c r="AH213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
@@ -19168,6 +19385,7 @@
       </c>
       <c r="AF214" t="inlineStr"/>
       <c r="AG214" t="inlineStr"/>
+      <c r="AH214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
@@ -19257,6 +19475,7 @@
       </c>
       <c r="AF215" t="inlineStr"/>
       <c r="AG215" t="inlineStr"/>
+      <c r="AH215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
@@ -19346,6 +19565,7 @@
       </c>
       <c r="AF216" t="inlineStr"/>
       <c r="AG216" t="inlineStr"/>
+      <c r="AH216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
@@ -19431,10 +19651,11 @@
       <c r="AC217" t="inlineStr"/>
       <c r="AD217" t="inlineStr"/>
       <c r="AE217" t="n">
-        <v>3712.049624220427</v>
+        <v>3712.049624220426</v>
       </c>
       <c r="AF217" t="inlineStr"/>
       <c r="AG217" t="inlineStr"/>
+      <c r="AH217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
@@ -19524,6 +19745,7 @@
       </c>
       <c r="AF218" t="inlineStr"/>
       <c r="AG218" t="inlineStr"/>
+      <c r="AH218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
@@ -19609,10 +19831,11 @@
       <c r="AC219" t="inlineStr"/>
       <c r="AD219" t="inlineStr"/>
       <c r="AE219" t="n">
-        <v>3803.173159298546</v>
+        <v>3803.173159298547</v>
       </c>
       <c r="AF219" t="inlineStr"/>
       <c r="AG219" t="inlineStr"/>
+      <c r="AH219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
@@ -19698,10 +19921,11 @@
       <c r="AC220" t="inlineStr"/>
       <c r="AD220" t="inlineStr"/>
       <c r="AE220" t="n">
-        <v>3922.158736703291</v>
+        <v>3922.15873670329</v>
       </c>
       <c r="AF220" t="inlineStr"/>
       <c r="AG220" t="inlineStr"/>
+      <c r="AH220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
@@ -19791,6 +20015,7 @@
       </c>
       <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="inlineStr"/>
+      <c r="AH221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
@@ -19880,6 +20105,7 @@
       </c>
       <c r="AF222" t="inlineStr"/>
       <c r="AG222" t="inlineStr"/>
+      <c r="AH222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
@@ -19965,10 +20191,11 @@
       <c r="AC223" t="inlineStr"/>
       <c r="AD223" t="inlineStr"/>
       <c r="AE223" t="n">
-        <v>3733.118302247665</v>
+        <v>3733.118302247666</v>
       </c>
       <c r="AF223" t="inlineStr"/>
       <c r="AG223" t="inlineStr"/>
+      <c r="AH223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
@@ -20058,6 +20285,7 @@
       </c>
       <c r="AF224" t="inlineStr"/>
       <c r="AG224" t="inlineStr"/>
+      <c r="AH224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
@@ -20147,6 +20375,7 @@
       </c>
       <c r="AF225" t="inlineStr"/>
       <c r="AG225" t="inlineStr"/>
+      <c r="AH225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
@@ -20232,10 +20461,11 @@
       <c r="AC226" t="inlineStr"/>
       <c r="AD226" t="inlineStr"/>
       <c r="AE226" t="n">
-        <v>3593.241267282239</v>
+        <v>3593.24126728224</v>
       </c>
       <c r="AF226" t="inlineStr"/>
       <c r="AG226" t="inlineStr"/>
+      <c r="AH226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
@@ -20325,6 +20555,7 @@
       </c>
       <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="inlineStr"/>
+      <c r="AH227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
@@ -20414,6 +20645,7 @@
       </c>
       <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="inlineStr"/>
+      <c r="AH228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
@@ -20503,6 +20735,7 @@
       </c>
       <c r="AF229" t="inlineStr"/>
       <c r="AG229" t="inlineStr"/>
+      <c r="AH229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
@@ -20592,6 +20825,7 @@
       </c>
       <c r="AF230" t="inlineStr"/>
       <c r="AG230" t="inlineStr"/>
+      <c r="AH230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
@@ -20681,6 +20915,7 @@
       </c>
       <c r="AF231" t="inlineStr"/>
       <c r="AG231" t="inlineStr"/>
+      <c r="AH231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
@@ -20770,6 +21005,7 @@
       </c>
       <c r="AF232" t="inlineStr"/>
       <c r="AG232" t="inlineStr"/>
+      <c r="AH232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
@@ -20855,10 +21091,11 @@
       <c r="AC233" t="inlineStr"/>
       <c r="AD233" t="inlineStr"/>
       <c r="AE233" t="n">
-        <v>4152.090228715961</v>
+        <v>4152.09022871596</v>
       </c>
       <c r="AF233" t="inlineStr"/>
       <c r="AG233" t="inlineStr"/>
+      <c r="AH233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
@@ -20948,6 +21185,7 @@
       </c>
       <c r="AF234" t="inlineStr"/>
       <c r="AG234" t="inlineStr"/>
+      <c r="AH234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
@@ -21033,10 +21271,11 @@
       <c r="AC235" t="inlineStr"/>
       <c r="AD235" t="inlineStr"/>
       <c r="AE235" t="n">
-        <v>3889.894028389681</v>
+        <v>3889.89402838968</v>
       </c>
       <c r="AF235" t="inlineStr"/>
       <c r="AG235" t="inlineStr"/>
+      <c r="AH235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
@@ -21126,6 +21365,7 @@
       </c>
       <c r="AF236" t="inlineStr"/>
       <c r="AG236" t="inlineStr"/>
+      <c r="AH236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
@@ -21215,6 +21455,7 @@
       </c>
       <c r="AF237" t="inlineStr"/>
       <c r="AG237" t="inlineStr"/>
+      <c r="AH237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
@@ -21300,10 +21541,11 @@
       <c r="AC238" t="inlineStr"/>
       <c r="AD238" t="inlineStr"/>
       <c r="AE238" t="n">
-        <v>3778.514396440167</v>
+        <v>3778.514396440166</v>
       </c>
       <c r="AF238" t="inlineStr"/>
       <c r="AG238" t="inlineStr"/>
+      <c r="AH238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
@@ -21393,6 +21635,7 @@
       </c>
       <c r="AF239" t="inlineStr"/>
       <c r="AG239" t="inlineStr"/>
+      <c r="AH239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
@@ -21478,10 +21721,11 @@
       <c r="AC240" t="inlineStr"/>
       <c r="AD240" t="inlineStr"/>
       <c r="AE240" t="n">
-        <v>3700.003727326001</v>
+        <v>3700.003727326002</v>
       </c>
       <c r="AF240" t="inlineStr"/>
       <c r="AG240" t="inlineStr"/>
+      <c r="AH240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
@@ -21571,6 +21815,7 @@
       </c>
       <c r="AF241" t="inlineStr"/>
       <c r="AG241" t="inlineStr"/>
+      <c r="AH241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
@@ -21656,10 +21901,11 @@
       <c r="AC242" t="inlineStr"/>
       <c r="AD242" t="inlineStr"/>
       <c r="AE242" t="n">
-        <v>3891.650958879414</v>
+        <v>3891.650958879415</v>
       </c>
       <c r="AF242" t="inlineStr"/>
       <c r="AG242" t="inlineStr"/>
+      <c r="AH242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
@@ -21749,6 +21995,7 @@
       </c>
       <c r="AF243" t="inlineStr"/>
       <c r="AG243" t="inlineStr"/>
+      <c r="AH243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
@@ -21838,6 +22085,7 @@
       </c>
       <c r="AF244" t="inlineStr"/>
       <c r="AG244" t="inlineStr"/>
+      <c r="AH244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
@@ -21927,6 +22175,7 @@
       </c>
       <c r="AF245" t="inlineStr"/>
       <c r="AG245" t="inlineStr"/>
+      <c r="AH245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
@@ -22016,6 +22265,7 @@
       </c>
       <c r="AF246" t="inlineStr"/>
       <c r="AG246" t="inlineStr"/>
+      <c r="AH246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
@@ -22105,6 +22355,7 @@
       </c>
       <c r="AF247" t="inlineStr"/>
       <c r="AG247" t="inlineStr"/>
+      <c r="AH247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
@@ -22194,6 +22445,7 @@
       </c>
       <c r="AF248" t="inlineStr"/>
       <c r="AG248" t="inlineStr"/>
+      <c r="AH248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
@@ -22283,6 +22535,7 @@
       </c>
       <c r="AF249" t="inlineStr"/>
       <c r="AG249" t="inlineStr"/>
+      <c r="AH249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
@@ -22368,10 +22621,11 @@
       <c r="AC250" t="inlineStr"/>
       <c r="AD250" t="inlineStr"/>
       <c r="AE250" t="n">
-        <v>3814.407695292191</v>
+        <v>3814.407695292192</v>
       </c>
       <c r="AF250" t="inlineStr"/>
       <c r="AG250" t="inlineStr"/>
+      <c r="AH250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
@@ -22461,6 +22715,7 @@
       </c>
       <c r="AF251" t="inlineStr"/>
       <c r="AG251" t="inlineStr"/>
+      <c r="AH251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
@@ -22550,6 +22805,7 @@
       </c>
       <c r="AF252" t="inlineStr"/>
       <c r="AG252" t="inlineStr"/>
+      <c r="AH252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
@@ -22639,6 +22895,7 @@
       </c>
       <c r="AF253" t="inlineStr"/>
       <c r="AG253" t="inlineStr"/>
+      <c r="AH253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
@@ -22728,6 +22985,7 @@
       </c>
       <c r="AF254" t="inlineStr"/>
       <c r="AG254" t="inlineStr"/>
+      <c r="AH254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n">
@@ -22817,6 +23075,7 @@
       </c>
       <c r="AF255" t="inlineStr"/>
       <c r="AG255" t="inlineStr"/>
+      <c r="AH255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
@@ -22906,6 +23165,7 @@
       </c>
       <c r="AF256" t="inlineStr"/>
       <c r="AG256" t="inlineStr"/>
+      <c r="AH256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n">
@@ -22995,6 +23255,7 @@
       </c>
       <c r="AF257" t="inlineStr"/>
       <c r="AG257" t="inlineStr"/>
+      <c r="AH257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
@@ -23084,6 +23345,7 @@
       </c>
       <c r="AF258" t="inlineStr"/>
       <c r="AG258" t="inlineStr"/>
+      <c r="AH258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n">
@@ -23169,10 +23431,11 @@
       <c r="AC259" t="inlineStr"/>
       <c r="AD259" t="inlineStr"/>
       <c r="AE259" t="n">
-        <v>4438.794440404017</v>
+        <v>4438.794440404016</v>
       </c>
       <c r="AF259" t="inlineStr"/>
       <c r="AG259" t="inlineStr"/>
+      <c r="AH259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
@@ -23262,6 +23525,7 @@
       </c>
       <c r="AF260" t="inlineStr"/>
       <c r="AG260" t="inlineStr"/>
+      <c r="AH260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n">
@@ -23351,6 +23615,7 @@
       </c>
       <c r="AF261" t="inlineStr"/>
       <c r="AG261" t="inlineStr"/>
+      <c r="AH261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n">
@@ -23440,6 +23705,7 @@
       </c>
       <c r="AF262" t="inlineStr"/>
       <c r="AG262" t="inlineStr"/>
+      <c r="AH262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n">
@@ -23525,10 +23791,11 @@
       <c r="AC263" t="inlineStr"/>
       <c r="AD263" t="inlineStr"/>
       <c r="AE263" t="n">
-        <v>4516.607426551246</v>
+        <v>4516.607426551247</v>
       </c>
       <c r="AF263" t="inlineStr"/>
       <c r="AG263" t="inlineStr"/>
+      <c r="AH263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n">
@@ -23618,6 +23885,7 @@
       </c>
       <c r="AF264" t="inlineStr"/>
       <c r="AG264" t="inlineStr"/>
+      <c r="AH264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n">
@@ -23707,6 +23975,7 @@
       </c>
       <c r="AF265" t="inlineStr"/>
       <c r="AG265" t="inlineStr"/>
+      <c r="AH265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n">
@@ -23796,6 +24065,7 @@
       </c>
       <c r="AF266" t="inlineStr"/>
       <c r="AG266" t="inlineStr"/>
+      <c r="AH266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n">
@@ -23881,10 +24151,11 @@
       <c r="AC267" t="inlineStr"/>
       <c r="AD267" t="inlineStr"/>
       <c r="AE267" t="n">
-        <v>4685.031333141183</v>
+        <v>4685.031333141184</v>
       </c>
       <c r="AF267" t="inlineStr"/>
       <c r="AG267" t="inlineStr"/>
+      <c r="AH267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n">
@@ -23970,10 +24241,11 @@
       <c r="AC268" t="inlineStr"/>
       <c r="AD268" t="inlineStr"/>
       <c r="AE268" t="n">
-        <v>4669.182367313107</v>
+        <v>4669.182367313108</v>
       </c>
       <c r="AF268" t="inlineStr"/>
       <c r="AG268" t="inlineStr"/>
+      <c r="AH268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n">
@@ -24063,6 +24335,7 @@
       </c>
       <c r="AF269" t="inlineStr"/>
       <c r="AG269" t="inlineStr"/>
+      <c r="AH269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n">
@@ -24152,6 +24425,7 @@
       </c>
       <c r="AF270" t="inlineStr"/>
       <c r="AG270" t="inlineStr"/>
+      <c r="AH270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n">
@@ -24241,6 +24515,7 @@
       </c>
       <c r="AF271" t="inlineStr"/>
       <c r="AG271" t="inlineStr"/>
+      <c r="AH271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n">
@@ -24326,10 +24601,11 @@
       <c r="AC272" t="inlineStr"/>
       <c r="AD272" t="inlineStr"/>
       <c r="AE272" t="n">
-        <v>5123.393113105535</v>
+        <v>5123.393113105534</v>
       </c>
       <c r="AF272" t="inlineStr"/>
       <c r="AG272" t="inlineStr"/>
+      <c r="AH272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n">
@@ -24419,6 +24695,7 @@
       </c>
       <c r="AF273" t="inlineStr"/>
       <c r="AG273" t="inlineStr"/>
+      <c r="AH273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">
@@ -24504,10 +24781,11 @@
       <c r="AC274" t="inlineStr"/>
       <c r="AD274" t="inlineStr"/>
       <c r="AE274" t="n">
-        <v>5250.354731543285</v>
+        <v>5250.354731543284</v>
       </c>
       <c r="AF274" t="inlineStr"/>
       <c r="AG274" t="inlineStr"/>
+      <c r="AH274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n">
@@ -24597,6 +24875,7 @@
       </c>
       <c r="AF275" t="inlineStr"/>
       <c r="AG275" t="inlineStr"/>
+      <c r="AH275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n">
@@ -24686,6 +24965,7 @@
       </c>
       <c r="AF276" t="inlineStr"/>
       <c r="AG276" t="inlineStr"/>
+      <c r="AH276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n">
@@ -24771,10 +25051,11 @@
       <c r="AC277" t="inlineStr"/>
       <c r="AD277" t="inlineStr"/>
       <c r="AE277" t="n">
-        <v>5299.841776065652</v>
+        <v>5299.841776065653</v>
       </c>
       <c r="AF277" t="inlineStr"/>
       <c r="AG277" t="inlineStr"/>
+      <c r="AH277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n">
@@ -24864,6 +25145,7 @@
       </c>
       <c r="AF278" t="inlineStr"/>
       <c r="AG278" t="inlineStr"/>
+      <c r="AH278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n">
@@ -24953,6 +25235,7 @@
       </c>
       <c r="AF279" t="inlineStr"/>
       <c r="AG279" t="inlineStr"/>
+      <c r="AH279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n">
@@ -25038,10 +25321,11 @@
       <c r="AC280" t="inlineStr"/>
       <c r="AD280" t="inlineStr"/>
       <c r="AE280" t="n">
-        <v>5606.129469437133</v>
+        <v>5606.129469437134</v>
       </c>
       <c r="AF280" t="inlineStr"/>
       <c r="AG280" t="inlineStr"/>
+      <c r="AH280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n">
@@ -25127,10 +25411,11 @@
       <c r="AC281" t="inlineStr"/>
       <c r="AD281" t="inlineStr"/>
       <c r="AE281" t="n">
-        <v>5716.417739573675</v>
+        <v>5716.417739573674</v>
       </c>
       <c r="AF281" t="inlineStr"/>
       <c r="AG281" t="inlineStr"/>
+      <c r="AH281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n">
@@ -25220,6 +25505,7 @@
       </c>
       <c r="AF282" t="inlineStr"/>
       <c r="AG282" t="inlineStr"/>
+      <c r="AH282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n">
@@ -25309,6 +25595,7 @@
       </c>
       <c r="AF283" t="inlineStr"/>
       <c r="AG283" t="inlineStr"/>
+      <c r="AH283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n">
@@ -25394,10 +25681,11 @@
       <c r="AC284" t="inlineStr"/>
       <c r="AD284" t="inlineStr"/>
       <c r="AE284" t="n">
-        <v>4832.24306968837</v>
+        <v>4832.243069688369</v>
       </c>
       <c r="AF284" t="inlineStr"/>
       <c r="AG284" t="inlineStr"/>
+      <c r="AH284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="n">
@@ -25487,6 +25775,7 @@
       </c>
       <c r="AF285" t="inlineStr"/>
       <c r="AG285" t="inlineStr"/>
+      <c r="AH285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n">
@@ -25576,6 +25865,7 @@
       </c>
       <c r="AF286" t="inlineStr"/>
       <c r="AG286" t="inlineStr"/>
+      <c r="AH286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n">
@@ -25661,10 +25951,11 @@
       <c r="AC287" t="inlineStr"/>
       <c r="AD287" t="inlineStr"/>
       <c r="AE287" t="n">
-        <v>5070.888092109495</v>
+        <v>5070.888092109496</v>
       </c>
       <c r="AF287" t="inlineStr"/>
       <c r="AG287" t="inlineStr"/>
+      <c r="AH287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n">
@@ -25754,6 +26045,7 @@
       </c>
       <c r="AF288" t="inlineStr"/>
       <c r="AG288" t="inlineStr"/>
+      <c r="AH288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="n">
@@ -25839,10 +26131,11 @@
       <c r="AC289" t="inlineStr"/>
       <c r="AD289" t="inlineStr"/>
       <c r="AE289" t="n">
-        <v>4851.906405440821</v>
+        <v>4851.906405440822</v>
       </c>
       <c r="AF289" t="inlineStr"/>
       <c r="AG289" t="inlineStr"/>
+      <c r="AH289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n">
@@ -25928,10 +26221,11 @@
       <c r="AC290" t="inlineStr"/>
       <c r="AD290" t="inlineStr"/>
       <c r="AE290" t="n">
-        <v>4873.540396117998</v>
+        <v>4873.540396117999</v>
       </c>
       <c r="AF290" t="inlineStr"/>
       <c r="AG290" t="inlineStr"/>
+      <c r="AH290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="n">
@@ -26021,6 +26315,7 @@
       </c>
       <c r="AF291" t="inlineStr"/>
       <c r="AG291" t="inlineStr"/>
+      <c r="AH291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n">
@@ -26110,6 +26405,7 @@
       </c>
       <c r="AF292" t="inlineStr"/>
       <c r="AG292" t="inlineStr"/>
+      <c r="AH292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="2" t="n">
@@ -26199,6 +26495,7 @@
       </c>
       <c r="AF293" t="inlineStr"/>
       <c r="AG293" t="inlineStr"/>
+      <c r="AH293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="n">
@@ -26288,6 +26585,7 @@
       </c>
       <c r="AF294" t="inlineStr"/>
       <c r="AG294" t="inlineStr"/>
+      <c r="AH294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="2" t="n">
@@ -26377,6 +26675,7 @@
       </c>
       <c r="AF295" t="inlineStr"/>
       <c r="AG295" t="inlineStr"/>
+      <c r="AH295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n">
@@ -26462,10 +26761,11 @@
       <c r="AC296" t="inlineStr"/>
       <c r="AD296" t="inlineStr"/>
       <c r="AE296" t="n">
-        <v>4252.039769319937</v>
+        <v>4252.039769319938</v>
       </c>
       <c r="AF296" t="inlineStr"/>
       <c r="AG296" t="inlineStr"/>
+      <c r="AH296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="n">
@@ -26555,6 +26855,7 @@
       </c>
       <c r="AF297" t="inlineStr"/>
       <c r="AG297" t="inlineStr"/>
+      <c r="AH297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="n">
@@ -26644,6 +26945,7 @@
       </c>
       <c r="AF298" t="inlineStr"/>
       <c r="AG298" t="inlineStr"/>
+      <c r="AH298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="2" t="n">
@@ -26733,6 +27035,7 @@
       </c>
       <c r="AF299" t="inlineStr"/>
       <c r="AG299" t="inlineStr"/>
+      <c r="AH299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="n">
@@ -26822,6 +27125,7 @@
       </c>
       <c r="AF300" t="inlineStr"/>
       <c r="AG300" t="inlineStr"/>
+      <c r="AH300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="n">
@@ -26911,6 +27215,7 @@
       </c>
       <c r="AF301" t="inlineStr"/>
       <c r="AG301" t="inlineStr"/>
+      <c r="AH301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="n">
@@ -27000,6 +27305,7 @@
       </c>
       <c r="AF302" t="inlineStr"/>
       <c r="AG302" t="inlineStr"/>
+      <c r="AH302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="2" t="n">
@@ -27089,6 +27395,7 @@
       </c>
       <c r="AF303" t="inlineStr"/>
       <c r="AG303" t="inlineStr"/>
+      <c r="AH303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="n">
@@ -27178,6 +27485,7 @@
       </c>
       <c r="AF304" t="inlineStr"/>
       <c r="AG304" t="inlineStr"/>
+      <c r="AH304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="n">
@@ -27267,6 +27575,7 @@
       </c>
       <c r="AF305" t="inlineStr"/>
       <c r="AG305" t="inlineStr"/>
+      <c r="AH305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="n">
@@ -27356,6 +27665,7 @@
       </c>
       <c r="AF306" t="inlineStr"/>
       <c r="AG306" t="inlineStr"/>
+      <c r="AH306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="2" t="n">
@@ -27445,6 +27755,7 @@
       </c>
       <c r="AF307" t="inlineStr"/>
       <c r="AG307" t="inlineStr"/>
+      <c r="AH307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="n">
@@ -27534,6 +27845,7 @@
       </c>
       <c r="AF308" t="inlineStr"/>
       <c r="AG308" t="inlineStr"/>
+      <c r="AH308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="2" t="n">
@@ -27623,6 +27935,7 @@
       </c>
       <c r="AF309" t="inlineStr"/>
       <c r="AG309" t="inlineStr"/>
+      <c r="AH309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" s="2" t="n">
@@ -27712,6 +28025,7 @@
       </c>
       <c r="AF310" t="inlineStr"/>
       <c r="AG310" t="inlineStr"/>
+      <c r="AH310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" s="2" t="n">
@@ -27797,10 +28111,11 @@
       <c r="AC311" t="inlineStr"/>
       <c r="AD311" t="inlineStr"/>
       <c r="AE311" t="n">
-        <v>4649.929105537814</v>
+        <v>4649.929105537815</v>
       </c>
       <c r="AF311" t="inlineStr"/>
       <c r="AG311" t="inlineStr"/>
+      <c r="AH311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="n">
@@ -27890,6 +28205,7 @@
       </c>
       <c r="AF312" t="inlineStr"/>
       <c r="AG312" t="inlineStr"/>
+      <c r="AH312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" s="2" t="n">
@@ -27979,6 +28295,7 @@
       </c>
       <c r="AF313" t="inlineStr"/>
       <c r="AG313" t="inlineStr"/>
+      <c r="AH313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="n">
@@ -28068,6 +28385,7 @@
       </c>
       <c r="AF314" t="inlineStr"/>
       <c r="AG314" t="inlineStr"/>
+      <c r="AH314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="2" t="n">
@@ -28157,6 +28475,7 @@
       </c>
       <c r="AF315" t="inlineStr"/>
       <c r="AG315" t="inlineStr"/>
+      <c r="AH315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" s="2" t="n">
@@ -28242,10 +28561,11 @@
       <c r="AC316" t="inlineStr"/>
       <c r="AD316" t="inlineStr"/>
       <c r="AE316" t="n">
-        <v>4261.08379024388</v>
+        <v>4261.083790243879</v>
       </c>
       <c r="AF316" t="inlineStr"/>
       <c r="AG316" t="inlineStr"/>
+      <c r="AH316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" s="2" t="n">
@@ -28335,6 +28655,7 @@
       </c>
       <c r="AF317" t="inlineStr"/>
       <c r="AG317" t="inlineStr"/>
+      <c r="AH317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" s="2" t="n">
@@ -28424,6 +28745,7 @@
       </c>
       <c r="AF318" t="inlineStr"/>
       <c r="AG318" t="inlineStr"/>
+      <c r="AH318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" s="2" t="n">
@@ -28513,6 +28835,7 @@
       </c>
       <c r="AF319" t="inlineStr"/>
       <c r="AG319" t="inlineStr"/>
+      <c r="AH319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" s="2" t="n">
@@ -28602,6 +28925,7 @@
       </c>
       <c r="AF320" t="inlineStr"/>
       <c r="AG320" t="inlineStr"/>
+      <c r="AH320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" s="2" t="n">
@@ -28691,6 +29015,7 @@
       </c>
       <c r="AF321" t="inlineStr"/>
       <c r="AG321" t="inlineStr"/>
+      <c r="AH321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" s="2" t="n">
@@ -28780,6 +29105,7 @@
       </c>
       <c r="AF322" t="inlineStr"/>
       <c r="AG322" t="inlineStr"/>
+      <c r="AH322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" s="2" t="n">
@@ -28869,6 +29195,7 @@
       </c>
       <c r="AF323" t="inlineStr"/>
       <c r="AG323" t="inlineStr"/>
+      <c r="AH323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" s="2" t="n">
@@ -28958,6 +29285,7 @@
       </c>
       <c r="AF324" t="inlineStr"/>
       <c r="AG324" t="inlineStr"/>
+      <c r="AH324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" s="2" t="n">
@@ -29043,10 +29371,11 @@
       <c r="AC325" t="inlineStr"/>
       <c r="AD325" t="inlineStr"/>
       <c r="AE325" t="n">
-        <v>4108.120623113469</v>
+        <v>4108.12062311347</v>
       </c>
       <c r="AF325" t="inlineStr"/>
       <c r="AG325" t="inlineStr"/>
+      <c r="AH325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="n">
@@ -29136,6 +29465,7 @@
       </c>
       <c r="AF326" t="inlineStr"/>
       <c r="AG326" t="inlineStr"/>
+      <c r="AH326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" s="2" t="n">
@@ -29225,6 +29555,7 @@
       </c>
       <c r="AF327" t="inlineStr"/>
       <c r="AG327" t="inlineStr"/>
+      <c r="AH327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" s="2" t="n">
@@ -29314,6 +29645,7 @@
       </c>
       <c r="AF328" t="inlineStr"/>
       <c r="AG328" t="inlineStr"/>
+      <c r="AH328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" s="2" t="n">
@@ -29403,6 +29735,7 @@
       </c>
       <c r="AF329" t="inlineStr"/>
       <c r="AG329" t="inlineStr"/>
+      <c r="AH329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" s="2" t="n">
@@ -29492,6 +29825,7 @@
       </c>
       <c r="AF330" t="inlineStr"/>
       <c r="AG330" t="inlineStr"/>
+      <c r="AH330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" s="2" t="n">
@@ -29581,6 +29915,7 @@
       </c>
       <c r="AF331" t="inlineStr"/>
       <c r="AG331" t="inlineStr"/>
+      <c r="AH331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" s="2" t="n">
@@ -29670,6 +30005,7 @@
       </c>
       <c r="AF332" t="inlineStr"/>
       <c r="AG332" t="inlineStr"/>
+      <c r="AH332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" s="2" t="n">
@@ -29759,6 +30095,7 @@
       </c>
       <c r="AF333" t="inlineStr"/>
       <c r="AG333" t="inlineStr"/>
+      <c r="AH333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" s="2" t="n">
@@ -29848,6 +30185,7 @@
       </c>
       <c r="AF334" t="inlineStr"/>
       <c r="AG334" t="inlineStr"/>
+      <c r="AH334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" s="2" t="n">
@@ -29937,6 +30275,7 @@
       </c>
       <c r="AF335" t="inlineStr"/>
       <c r="AG335" t="inlineStr"/>
+      <c r="AH335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" s="2" t="n">
@@ -30026,6 +30365,7 @@
       </c>
       <c r="AF336" t="inlineStr"/>
       <c r="AG336" t="inlineStr"/>
+      <c r="AH336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" s="2" t="n">
@@ -30115,6 +30455,7 @@
       </c>
       <c r="AF337" t="inlineStr"/>
       <c r="AG337" t="inlineStr"/>
+      <c r="AH337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" s="2" t="n">
@@ -30204,6 +30545,7 @@
       </c>
       <c r="AF338" t="inlineStr"/>
       <c r="AG338" t="inlineStr"/>
+      <c r="AH338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" s="2" t="n">
@@ -30293,6 +30635,7 @@
       </c>
       <c r="AF339" t="inlineStr"/>
       <c r="AG339" t="inlineStr"/>
+      <c r="AH339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" s="2" t="n">
@@ -30382,6 +30725,7 @@
       </c>
       <c r="AF340" t="inlineStr"/>
       <c r="AG340" t="inlineStr"/>
+      <c r="AH340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" s="2" t="n">
@@ -30471,6 +30815,7 @@
       </c>
       <c r="AF341" t="inlineStr"/>
       <c r="AG341" t="inlineStr"/>
+      <c r="AH341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="n">
@@ -30560,6 +30905,7 @@
       </c>
       <c r="AF342" t="inlineStr"/>
       <c r="AG342" t="inlineStr"/>
+      <c r="AH342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" s="2" t="n">
@@ -30649,6 +30995,7 @@
       </c>
       <c r="AF343" t="inlineStr"/>
       <c r="AG343" t="inlineStr"/>
+      <c r="AH343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" s="2" t="n">
@@ -30738,6 +31085,7 @@
       </c>
       <c r="AF344" t="inlineStr"/>
       <c r="AG344" t="inlineStr"/>
+      <c r="AH344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" s="2" t="n">
@@ -30827,6 +31175,7 @@
       </c>
       <c r="AF345" t="inlineStr"/>
       <c r="AG345" t="inlineStr"/>
+      <c r="AH345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="n">
@@ -30916,6 +31265,7 @@
       </c>
       <c r="AF346" t="inlineStr"/>
       <c r="AG346" t="inlineStr"/>
+      <c r="AH346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" s="2" t="n">
@@ -31005,6 +31355,7 @@
       </c>
       <c r="AF347" t="inlineStr"/>
       <c r="AG347" t="inlineStr"/>
+      <c r="AH347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="n">
@@ -31094,6 +31445,7 @@
       </c>
       <c r="AF348" t="inlineStr"/>
       <c r="AG348" t="inlineStr"/>
+      <c r="AH348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" s="2" t="n">
@@ -31183,6 +31535,7 @@
       </c>
       <c r="AF349" t="inlineStr"/>
       <c r="AG349" t="inlineStr"/>
+      <c r="AH349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" s="2" t="n">
@@ -31272,6 +31625,7 @@
       </c>
       <c r="AF350" t="inlineStr"/>
       <c r="AG350" t="inlineStr"/>
+      <c r="AH350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" s="2" t="n">
@@ -31361,6 +31715,7 @@
       </c>
       <c r="AF351" t="inlineStr"/>
       <c r="AG351" t="inlineStr"/>
+      <c r="AH351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" s="2" t="n">
@@ -31450,6 +31805,7 @@
       </c>
       <c r="AF352" t="inlineStr"/>
       <c r="AG352" t="inlineStr"/>
+      <c r="AH352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="2" t="n">
@@ -31539,6 +31895,7 @@
       </c>
       <c r="AF353" t="inlineStr"/>
       <c r="AG353" t="inlineStr"/>
+      <c r="AH353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" s="2" t="n">
@@ -31628,6 +31985,7 @@
       </c>
       <c r="AF354" t="inlineStr"/>
       <c r="AG354" t="inlineStr"/>
+      <c r="AH354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" s="2" t="n">
@@ -31717,6 +32075,7 @@
       </c>
       <c r="AF355" t="inlineStr"/>
       <c r="AG355" t="inlineStr"/>
+      <c r="AH355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="n">
@@ -31806,6 +32165,7 @@
       </c>
       <c r="AF356" t="inlineStr"/>
       <c r="AG356" t="inlineStr"/>
+      <c r="AH356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" s="2" t="n">
@@ -31895,6 +32255,7 @@
       </c>
       <c r="AF357" t="inlineStr"/>
       <c r="AG357" t="inlineStr"/>
+      <c r="AH357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="n">
@@ -31984,6 +32345,7 @@
       </c>
       <c r="AF358" t="inlineStr"/>
       <c r="AG358" t="inlineStr"/>
+      <c r="AH358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" s="2" t="n">
@@ -32073,6 +32435,7 @@
       </c>
       <c r="AF359" t="inlineStr"/>
       <c r="AG359" t="inlineStr"/>
+      <c r="AH359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="n">
@@ -32162,6 +32525,7 @@
       </c>
       <c r="AF360" t="inlineStr"/>
       <c r="AG360" t="inlineStr"/>
+      <c r="AH360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" s="2" t="n">
@@ -32251,6 +32615,7 @@
       </c>
       <c r="AF361" t="inlineStr"/>
       <c r="AG361" t="inlineStr"/>
+      <c r="AH361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="n">
@@ -32336,10 +32701,11 @@
       <c r="AC362" t="inlineStr"/>
       <c r="AD362" t="inlineStr"/>
       <c r="AE362" t="n">
-        <v>1964.786816021098</v>
+        <v>1964.786816021097</v>
       </c>
       <c r="AF362" t="inlineStr"/>
       <c r="AG362" t="inlineStr"/>
+      <c r="AH362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" s="2" t="n">
@@ -32429,6 +32795,7 @@
       </c>
       <c r="AF363" t="inlineStr"/>
       <c r="AG363" t="inlineStr"/>
+      <c r="AH363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="n">
@@ -32518,6 +32885,7 @@
       </c>
       <c r="AF364" t="inlineStr"/>
       <c r="AG364" t="inlineStr"/>
+      <c r="AH364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" s="2" t="n">
@@ -32607,6 +32975,7 @@
       </c>
       <c r="AF365" t="inlineStr"/>
       <c r="AG365" t="inlineStr"/>
+      <c r="AH365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="n">
@@ -32696,6 +33065,7 @@
       </c>
       <c r="AF366" t="inlineStr"/>
       <c r="AG366" t="inlineStr"/>
+      <c r="AH366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" s="2" t="n">
@@ -32785,6 +33155,7 @@
       </c>
       <c r="AF367" t="inlineStr"/>
       <c r="AG367" t="inlineStr"/>
+      <c r="AH367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" s="2" t="n">
@@ -32874,6 +33245,7 @@
       </c>
       <c r="AF368" t="inlineStr"/>
       <c r="AG368" t="inlineStr"/>
+      <c r="AH368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" s="2" t="n">
@@ -32963,6 +33335,7 @@
       </c>
       <c r="AF369" t="inlineStr"/>
       <c r="AG369" t="inlineStr"/>
+      <c r="AH369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="n">
@@ -33052,6 +33425,7 @@
       </c>
       <c r="AF370" t="inlineStr"/>
       <c r="AG370" t="inlineStr"/>
+      <c r="AH370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" s="2" t="n">
@@ -33141,6 +33515,7 @@
       </c>
       <c r="AF371" t="inlineStr"/>
       <c r="AG371" t="inlineStr"/>
+      <c r="AH371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="n">
@@ -33230,6 +33605,7 @@
       </c>
       <c r="AF372" t="inlineStr"/>
       <c r="AG372" t="inlineStr"/>
+      <c r="AH372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" s="2" t="n">
@@ -33319,6 +33695,7 @@
       </c>
       <c r="AF373" t="inlineStr"/>
       <c r="AG373" t="inlineStr"/>
+      <c r="AH373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="n">
@@ -33408,6 +33785,7 @@
       </c>
       <c r="AF374" t="inlineStr"/>
       <c r="AG374" t="inlineStr"/>
+      <c r="AH374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" s="2" t="n">
@@ -33497,6 +33875,7 @@
       </c>
       <c r="AF375" t="inlineStr"/>
       <c r="AG375" t="inlineStr"/>
+      <c r="AH375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="n">
@@ -33586,6 +33965,7 @@
       </c>
       <c r="AF376" t="inlineStr"/>
       <c r="AG376" t="inlineStr"/>
+      <c r="AH376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" s="2" t="n">
@@ -33675,6 +34055,7 @@
       </c>
       <c r="AF377" t="inlineStr"/>
       <c r="AG377" t="inlineStr"/>
+      <c r="AH377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" s="2" t="n">
@@ -33764,6 +34145,7 @@
       </c>
       <c r="AF378" t="inlineStr"/>
       <c r="AG378" t="inlineStr"/>
+      <c r="AH378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" s="2" t="n">
@@ -33853,6 +34235,7 @@
       </c>
       <c r="AF379" t="inlineStr"/>
       <c r="AG379" t="inlineStr"/>
+      <c r="AH379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" s="2" t="n">
@@ -33942,6 +34325,7 @@
       </c>
       <c r="AF380" t="inlineStr"/>
       <c r="AG380" t="inlineStr"/>
+      <c r="AH380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" s="2" t="n">
@@ -34031,6 +34415,7 @@
       </c>
       <c r="AF381" t="inlineStr"/>
       <c r="AG381" t="inlineStr"/>
+      <c r="AH381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="n">
@@ -34120,6 +34505,7 @@
       </c>
       <c r="AF382" t="inlineStr"/>
       <c r="AG382" t="inlineStr"/>
+      <c r="AH382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" s="2" t="n">
@@ -34209,6 +34595,7 @@
       </c>
       <c r="AF383" t="inlineStr"/>
       <c r="AG383" t="inlineStr"/>
+      <c r="AH383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" s="2" t="n">
@@ -34298,6 +34685,7 @@
       </c>
       <c r="AF384" t="inlineStr"/>
       <c r="AG384" t="inlineStr"/>
+      <c r="AH384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" s="2" t="n">
@@ -34387,6 +34775,7 @@
       </c>
       <c r="AF385" t="inlineStr"/>
       <c r="AG385" t="inlineStr"/>
+      <c r="AH385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" s="2" t="n">
@@ -34476,6 +34865,7 @@
       </c>
       <c r="AF386" t="inlineStr"/>
       <c r="AG386" t="inlineStr"/>
+      <c r="AH386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" s="2" t="n">
@@ -34565,6 +34955,7 @@
       </c>
       <c r="AF387" t="inlineStr"/>
       <c r="AG387" t="inlineStr"/>
+      <c r="AH387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="n">
@@ -34654,6 +35045,7 @@
       </c>
       <c r="AF388" t="inlineStr"/>
       <c r="AG388" t="inlineStr"/>
+      <c r="AH388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="2" t="n">
@@ -34743,6 +35135,7 @@
       </c>
       <c r="AF389" t="inlineStr"/>
       <c r="AG389" t="inlineStr"/>
+      <c r="AH389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="n">
@@ -34832,6 +35225,7 @@
       </c>
       <c r="AF390" t="inlineStr"/>
       <c r="AG390" t="inlineStr"/>
+      <c r="AH390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" s="2" t="n">
@@ -34921,6 +35315,7 @@
       </c>
       <c r="AF391" t="inlineStr"/>
       <c r="AG391" t="inlineStr"/>
+      <c r="AH391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="n">
@@ -35010,6 +35405,7 @@
       </c>
       <c r="AF392" t="inlineStr"/>
       <c r="AG392" t="inlineStr"/>
+      <c r="AH392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" s="2" t="n">
@@ -35099,6 +35495,7 @@
       </c>
       <c r="AF393" t="inlineStr"/>
       <c r="AG393" t="inlineStr"/>
+      <c r="AH393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="2" t="n">
@@ -35188,6 +35585,7 @@
       </c>
       <c r="AF394" t="inlineStr"/>
       <c r="AG394" t="inlineStr"/>
+      <c r="AH394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" s="2" t="n">
@@ -35277,6 +35675,7 @@
       </c>
       <c r="AF395" t="inlineStr"/>
       <c r="AG395" t="inlineStr"/>
+      <c r="AH395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" s="2" t="n">
@@ -35366,6 +35765,7 @@
       </c>
       <c r="AF396" t="inlineStr"/>
       <c r="AG396" t="inlineStr"/>
+      <c r="AH396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" s="2" t="n">
@@ -35455,6 +35855,7 @@
       </c>
       <c r="AF397" t="inlineStr"/>
       <c r="AG397" t="inlineStr"/>
+      <c r="AH397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" s="2" t="n">
@@ -35544,6 +35945,7 @@
       </c>
       <c r="AF398" t="inlineStr"/>
       <c r="AG398" t="inlineStr"/>
+      <c r="AH398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" s="2" t="n">
@@ -35633,6 +36035,7 @@
       </c>
       <c r="AF399" t="inlineStr"/>
       <c r="AG399" t="inlineStr"/>
+      <c r="AH399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" s="2" t="n">
@@ -35722,6 +36125,7 @@
       </c>
       <c r="AF400" t="inlineStr"/>
       <c r="AG400" t="inlineStr"/>
+      <c r="AH400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" s="2" t="n">
@@ -35811,6 +36215,7 @@
       </c>
       <c r="AF401" t="inlineStr"/>
       <c r="AG401" t="inlineStr"/>
+      <c r="AH401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" s="2" t="n">
@@ -35900,6 +36305,7 @@
       </c>
       <c r="AF402" t="inlineStr"/>
       <c r="AG402" t="inlineStr"/>
+      <c r="AH402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" s="2" t="n">
@@ -35989,6 +36395,7 @@
       </c>
       <c r="AF403" t="inlineStr"/>
       <c r="AG403" t="inlineStr"/>
+      <c r="AH403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" s="2" t="n">
@@ -36078,6 +36485,7 @@
       </c>
       <c r="AF404" t="inlineStr"/>
       <c r="AG404" t="inlineStr"/>
+      <c r="AH404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" s="2" t="n">
@@ -36167,6 +36575,7 @@
       </c>
       <c r="AF405" t="inlineStr"/>
       <c r="AG405" t="inlineStr"/>
+      <c r="AH405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" s="2" t="n">
@@ -36256,6 +36665,7 @@
       </c>
       <c r="AF406" t="inlineStr"/>
       <c r="AG406" t="inlineStr"/>
+      <c r="AH406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" s="2" t="n">
@@ -36345,6 +36755,7 @@
       </c>
       <c r="AF407" t="inlineStr"/>
       <c r="AG407" t="inlineStr"/>
+      <c r="AH407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n">
@@ -36434,6 +36845,7 @@
       </c>
       <c r="AF408" t="inlineStr"/>
       <c r="AG408" t="inlineStr"/>
+      <c r="AH408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" s="2" t="n">
@@ -36519,10 +36931,11 @@
       <c r="AC409" t="inlineStr"/>
       <c r="AD409" t="inlineStr"/>
       <c r="AE409" t="n">
-        <v>1764.533713065386</v>
+        <v>1764.533713065387</v>
       </c>
       <c r="AF409" t="inlineStr"/>
       <c r="AG409" t="inlineStr"/>
+      <c r="AH409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n">
@@ -36608,10 +37021,11 @@
       <c r="AC410" t="inlineStr"/>
       <c r="AD410" t="inlineStr"/>
       <c r="AE410" t="n">
-        <v>1825.496228579266</v>
+        <v>1825.496228579267</v>
       </c>
       <c r="AF410" t="inlineStr"/>
       <c r="AG410" t="inlineStr"/>
+      <c r="AH410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" s="2" t="n">
@@ -36701,6 +37115,7 @@
       </c>
       <c r="AF411" t="inlineStr"/>
       <c r="AG411" t="inlineStr"/>
+      <c r="AH411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" s="2" t="n">
@@ -36790,6 +37205,7 @@
       </c>
       <c r="AF412" t="inlineStr"/>
       <c r="AG412" t="inlineStr"/>
+      <c r="AH412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" s="2" t="n">
@@ -36879,6 +37295,7 @@
       </c>
       <c r="AF413" t="inlineStr"/>
       <c r="AG413" t="inlineStr"/>
+      <c r="AH413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" s="2" t="n">
@@ -36968,6 +37385,7 @@
       </c>
       <c r="AF414" t="inlineStr"/>
       <c r="AG414" t="inlineStr"/>
+      <c r="AH414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" s="2" t="n">
@@ -37057,6 +37475,7 @@
       </c>
       <c r="AF415" t="inlineStr"/>
       <c r="AG415" t="inlineStr"/>
+      <c r="AH415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n">
@@ -37146,6 +37565,7 @@
       </c>
       <c r="AF416" t="inlineStr"/>
       <c r="AG416" t="inlineStr"/>
+      <c r="AH416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n">
@@ -37235,6 +37655,7 @@
       </c>
       <c r="AF417" t="inlineStr"/>
       <c r="AG417" t="inlineStr"/>
+      <c r="AH417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n">
@@ -37324,6 +37745,7 @@
       </c>
       <c r="AF418" t="inlineStr"/>
       <c r="AG418" t="inlineStr"/>
+      <c r="AH418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n">
@@ -37413,6 +37835,7 @@
       </c>
       <c r="AF419" t="inlineStr"/>
       <c r="AG419" t="inlineStr"/>
+      <c r="AH419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" s="2" t="n">
@@ -37502,6 +37925,7 @@
       </c>
       <c r="AF420" t="inlineStr"/>
       <c r="AG420" t="inlineStr"/>
+      <c r="AH420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" s="2" t="n">
@@ -37587,10 +38011,11 @@
       <c r="AC421" t="inlineStr"/>
       <c r="AD421" t="inlineStr"/>
       <c r="AE421" t="n">
-        <v>2018.465057541782</v>
+        <v>2018.465057541781</v>
       </c>
       <c r="AF421" t="inlineStr"/>
       <c r="AG421" t="inlineStr"/>
+      <c r="AH421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" s="2" t="n">
@@ -37680,6 +38105,7 @@
       </c>
       <c r="AF422" t="inlineStr"/>
       <c r="AG422" t="inlineStr"/>
+      <c r="AH422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" s="2" t="n">
@@ -37769,6 +38195,7 @@
       </c>
       <c r="AF423" t="inlineStr"/>
       <c r="AG423" t="inlineStr"/>
+      <c r="AH423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" s="2" t="n">
@@ -37858,6 +38285,7 @@
       </c>
       <c r="AF424" t="inlineStr"/>
       <c r="AG424" t="inlineStr"/>
+      <c r="AH424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" s="2" t="n">
@@ -37947,6 +38375,7 @@
       </c>
       <c r="AF425" t="inlineStr"/>
       <c r="AG425" t="inlineStr"/>
+      <c r="AH425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" s="2" t="n">
@@ -38036,6 +38465,7 @@
       </c>
       <c r="AF426" t="inlineStr"/>
       <c r="AG426" t="inlineStr"/>
+      <c r="AH426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" s="2" t="n">
@@ -38125,6 +38555,7 @@
       </c>
       <c r="AF427" t="inlineStr"/>
       <c r="AG427" t="inlineStr"/>
+      <c r="AH427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" s="2" t="n">
@@ -38214,6 +38645,7 @@
       </c>
       <c r="AF428" t="inlineStr"/>
       <c r="AG428" t="inlineStr"/>
+      <c r="AH428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" s="2" t="n">
@@ -38303,6 +38735,7 @@
       </c>
       <c r="AF429" t="inlineStr"/>
       <c r="AG429" t="inlineStr"/>
+      <c r="AH429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" s="2" t="n">
@@ -38392,6 +38825,7 @@
       </c>
       <c r="AF430" t="inlineStr"/>
       <c r="AG430" t="inlineStr"/>
+      <c r="AH430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" s="2" t="n">
@@ -38481,6 +38915,7 @@
       </c>
       <c r="AF431" t="inlineStr"/>
       <c r="AG431" t="inlineStr"/>
+      <c r="AH431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" s="2" t="n">
@@ -38570,6 +39005,7 @@
       </c>
       <c r="AF432" t="inlineStr"/>
       <c r="AG432" t="inlineStr"/>
+      <c r="AH432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" s="2" t="n">
@@ -38659,6 +39095,7 @@
       </c>
       <c r="AF433" t="inlineStr"/>
       <c r="AG433" t="inlineStr"/>
+      <c r="AH433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" s="2" t="n">
@@ -38748,6 +39185,7 @@
       </c>
       <c r="AF434" t="inlineStr"/>
       <c r="AG434" t="inlineStr"/>
+      <c r="AH434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" s="2" t="n">
@@ -38833,10 +39271,11 @@
       <c r="AC435" t="inlineStr"/>
       <c r="AD435" t="inlineStr"/>
       <c r="AE435" t="n">
-        <v>2190.724849065359</v>
+        <v>2190.72484906536</v>
       </c>
       <c r="AF435" t="inlineStr"/>
       <c r="AG435" t="inlineStr"/>
+      <c r="AH435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" s="2" t="n">
@@ -38926,6 +39365,7 @@
       </c>
       <c r="AF436" t="inlineStr"/>
       <c r="AG436" t="inlineStr"/>
+      <c r="AH436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" s="2" t="n">
@@ -39015,6 +39455,7 @@
       </c>
       <c r="AF437" t="inlineStr"/>
       <c r="AG437" t="inlineStr"/>
+      <c r="AH437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" s="2" t="n">
@@ -39104,6 +39545,7 @@
       </c>
       <c r="AF438" t="inlineStr"/>
       <c r="AG438" t="inlineStr"/>
+      <c r="AH438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" s="2" t="n">
@@ -39193,6 +39635,7 @@
       </c>
       <c r="AF439" t="inlineStr"/>
       <c r="AG439" t="inlineStr"/>
+      <c r="AH439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" s="2" t="n">
@@ -39282,6 +39725,7 @@
       </c>
       <c r="AF440" t="inlineStr"/>
       <c r="AG440" t="inlineStr"/>
+      <c r="AH440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" s="2" t="n">
@@ -39371,6 +39815,7 @@
       </c>
       <c r="AF441" t="inlineStr"/>
       <c r="AG441" t="inlineStr"/>
+      <c r="AH441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" s="2" t="n">
@@ -39460,6 +39905,7 @@
       </c>
       <c r="AF442" t="inlineStr"/>
       <c r="AG442" t="inlineStr"/>
+      <c r="AH442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" s="2" t="n">
@@ -39549,6 +39995,7 @@
       </c>
       <c r="AF443" t="inlineStr"/>
       <c r="AG443" t="inlineStr"/>
+      <c r="AH443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" s="2" t="n">
@@ -39638,6 +40085,7 @@
       </c>
       <c r="AF444" t="inlineStr"/>
       <c r="AG444" t="inlineStr"/>
+      <c r="AH444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" s="2" t="n">
@@ -39727,6 +40175,7 @@
       </c>
       <c r="AF445" t="inlineStr"/>
       <c r="AG445" t="inlineStr"/>
+      <c r="AH445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" s="2" t="n">
@@ -39816,6 +40265,7 @@
       </c>
       <c r="AF446" t="inlineStr"/>
       <c r="AG446" t="inlineStr"/>
+      <c r="AH446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" s="2" t="n">
@@ -39905,6 +40355,7 @@
       </c>
       <c r="AF447" t="inlineStr"/>
       <c r="AG447" t="inlineStr"/>
+      <c r="AH447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" s="2" t="n">
@@ -39994,6 +40445,7 @@
       </c>
       <c r="AF448" t="inlineStr"/>
       <c r="AG448" t="inlineStr"/>
+      <c r="AH448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" s="2" t="n">
@@ -40083,6 +40535,7 @@
       </c>
       <c r="AF449" t="inlineStr"/>
       <c r="AG449" t="inlineStr"/>
+      <c r="AH449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" s="2" t="n">
@@ -40172,6 +40625,7 @@
       </c>
       <c r="AF450" t="inlineStr"/>
       <c r="AG450" t="inlineStr"/>
+      <c r="AH450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" s="2" t="n">
@@ -40261,6 +40715,7 @@
       </c>
       <c r="AF451" t="inlineStr"/>
       <c r="AG451" t="inlineStr"/>
+      <c r="AH451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" s="2" t="n">
@@ -40350,6 +40805,7 @@
       </c>
       <c r="AF452" t="inlineStr"/>
       <c r="AG452" t="inlineStr"/>
+      <c r="AH452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" s="2" t="n">
@@ -40439,6 +40895,7 @@
       </c>
       <c r="AF453" t="inlineStr"/>
       <c r="AG453" t="inlineStr"/>
+      <c r="AH453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" s="2" t="n">
@@ -40528,6 +40985,7 @@
       </c>
       <c r="AF454" t="inlineStr"/>
       <c r="AG454" t="inlineStr"/>
+      <c r="AH454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" s="2" t="n">
@@ -40613,10 +41071,11 @@
       <c r="AC455" t="inlineStr"/>
       <c r="AD455" t="inlineStr"/>
       <c r="AE455" t="n">
-        <v>2203.134166553241</v>
+        <v>2203.134166553242</v>
       </c>
       <c r="AF455" t="inlineStr"/>
       <c r="AG455" t="inlineStr"/>
+      <c r="AH455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" s="2" t="n">
@@ -40706,6 +41165,7 @@
       </c>
       <c r="AF456" t="inlineStr"/>
       <c r="AG456" t="inlineStr"/>
+      <c r="AH456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" s="2" t="n">
@@ -40795,6 +41255,7 @@
       </c>
       <c r="AF457" t="inlineStr"/>
       <c r="AG457" t="inlineStr"/>
+      <c r="AH457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" s="2" t="n">
@@ -40880,10 +41341,11 @@
       <c r="AC458" t="inlineStr"/>
       <c r="AD458" t="inlineStr"/>
       <c r="AE458" t="n">
-        <v>2083.882573732221</v>
+        <v>2083.88257373222</v>
       </c>
       <c r="AF458" t="inlineStr"/>
       <c r="AG458" t="inlineStr"/>
+      <c r="AH458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" s="2" t="n">
@@ -40973,6 +41435,7 @@
       </c>
       <c r="AF459" t="inlineStr"/>
       <c r="AG459" t="inlineStr"/>
+      <c r="AH459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" s="2" t="n">
@@ -41062,6 +41525,7 @@
       </c>
       <c r="AF460" t="inlineStr"/>
       <c r="AG460" t="inlineStr"/>
+      <c r="AH460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" s="2" t="n">
@@ -41151,6 +41615,7 @@
       </c>
       <c r="AF461" t="inlineStr"/>
       <c r="AG461" t="inlineStr"/>
+      <c r="AH461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" s="2" t="n">
@@ -41240,6 +41705,7 @@
       </c>
       <c r="AF462" t="inlineStr"/>
       <c r="AG462" t="inlineStr"/>
+      <c r="AH462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" s="2" t="n">
@@ -41329,6 +41795,7 @@
       </c>
       <c r="AF463" t="inlineStr"/>
       <c r="AG463" t="inlineStr"/>
+      <c r="AH463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" s="2" t="n">
@@ -41418,6 +41885,7 @@
       </c>
       <c r="AF464" t="inlineStr"/>
       <c r="AG464" t="inlineStr"/>
+      <c r="AH464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" s="2" t="n">
@@ -41507,6 +41975,7 @@
       </c>
       <c r="AF465" t="inlineStr"/>
       <c r="AG465" t="inlineStr"/>
+      <c r="AH465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" s="2" t="n">
@@ -41596,6 +42065,7 @@
       </c>
       <c r="AF466" t="inlineStr"/>
       <c r="AG466" t="inlineStr"/>
+      <c r="AH466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" s="2" t="n">
@@ -41685,6 +42155,7 @@
       </c>
       <c r="AF467" t="inlineStr"/>
       <c r="AG467" t="inlineStr"/>
+      <c r="AH467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" s="2" t="n">
@@ -41774,6 +42245,7 @@
       </c>
       <c r="AF468" t="inlineStr"/>
       <c r="AG468" t="inlineStr"/>
+      <c r="AH468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" s="2" t="n">
@@ -41863,6 +42335,7 @@
       </c>
       <c r="AF469" t="inlineStr"/>
       <c r="AG469" t="inlineStr"/>
+      <c r="AH469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" s="2" t="n">
@@ -41954,6 +42427,7 @@
       </c>
       <c r="AF470" t="inlineStr"/>
       <c r="AG470" t="inlineStr"/>
+      <c r="AH470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" s="2" t="n">
@@ -42045,6 +42519,7 @@
       </c>
       <c r="AF471" t="inlineStr"/>
       <c r="AG471" t="inlineStr"/>
+      <c r="AH471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" s="2" t="n">
@@ -42136,6 +42611,7 @@
       </c>
       <c r="AF472" t="inlineStr"/>
       <c r="AG472" t="inlineStr"/>
+      <c r="AH472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" s="2" t="n">
@@ -42227,6 +42703,7 @@
       </c>
       <c r="AF473" t="inlineStr"/>
       <c r="AG473" t="inlineStr"/>
+      <c r="AH473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" s="2" t="n">
@@ -42318,6 +42795,7 @@
       </c>
       <c r="AF474" t="inlineStr"/>
       <c r="AG474" t="inlineStr"/>
+      <c r="AH474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" s="2" t="n">
@@ -42409,6 +42887,7 @@
       </c>
       <c r="AF475" t="inlineStr"/>
       <c r="AG475" t="inlineStr"/>
+      <c r="AH475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" s="2" t="n">
@@ -42500,6 +42979,7 @@
       </c>
       <c r="AF476" t="inlineStr"/>
       <c r="AG476" t="inlineStr"/>
+      <c r="AH476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" s="2" t="n">
@@ -42591,6 +43071,7 @@
       </c>
       <c r="AF477" t="inlineStr"/>
       <c r="AG477" t="inlineStr"/>
+      <c r="AH477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" s="2" t="n">
@@ -42682,6 +43163,7 @@
       </c>
       <c r="AF478" t="inlineStr"/>
       <c r="AG478" t="inlineStr"/>
+      <c r="AH478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" s="2" t="n">
@@ -42773,6 +43255,7 @@
       </c>
       <c r="AF479" t="inlineStr"/>
       <c r="AG479" t="inlineStr"/>
+      <c r="AH479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" s="2" t="n">
@@ -42864,6 +43347,7 @@
       </c>
       <c r="AF480" t="inlineStr"/>
       <c r="AG480" t="inlineStr"/>
+      <c r="AH480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" s="2" t="n">
@@ -42955,6 +43439,7 @@
       </c>
       <c r="AF481" t="inlineStr"/>
       <c r="AG481" t="inlineStr"/>
+      <c r="AH481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" s="2" t="n">
@@ -43046,6 +43531,7 @@
       </c>
       <c r="AF482" t="inlineStr"/>
       <c r="AG482" t="inlineStr"/>
+      <c r="AH482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" s="2" t="n">
@@ -43137,6 +43623,7 @@
       </c>
       <c r="AF483" t="inlineStr"/>
       <c r="AG483" t="inlineStr"/>
+      <c r="AH483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" s="2" t="n">
@@ -43228,6 +43715,7 @@
       </c>
       <c r="AF484" t="inlineStr"/>
       <c r="AG484" t="inlineStr"/>
+      <c r="AH484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" s="2" t="n">
@@ -43319,6 +43807,7 @@
       </c>
       <c r="AF485" t="inlineStr"/>
       <c r="AG485" t="inlineStr"/>
+      <c r="AH485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" s="2" t="n">
@@ -43410,6 +43899,7 @@
       </c>
       <c r="AF486" t="inlineStr"/>
       <c r="AG486" t="inlineStr"/>
+      <c r="AH486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" s="2" t="n">
@@ -43497,10 +43987,11 @@
       <c r="AC487" t="inlineStr"/>
       <c r="AD487" t="inlineStr"/>
       <c r="AE487" t="n">
-        <v>2189.79335538551</v>
+        <v>2189.793355385511</v>
       </c>
       <c r="AF487" t="inlineStr"/>
       <c r="AG487" t="inlineStr"/>
+      <c r="AH487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" s="2" t="n">
@@ -43592,6 +44083,7 @@
       </c>
       <c r="AF488" t="inlineStr"/>
       <c r="AG488" t="inlineStr"/>
+      <c r="AH488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" s="2" t="n">
@@ -43683,6 +44175,7 @@
       </c>
       <c r="AF489" t="inlineStr"/>
       <c r="AG489" t="inlineStr"/>
+      <c r="AH489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" s="2" t="n">
@@ -43770,10 +44263,11 @@
       <c r="AC490" t="inlineStr"/>
       <c r="AD490" t="inlineStr"/>
       <c r="AE490" t="n">
-        <v>2192.169618079853</v>
+        <v>2192.169618079854</v>
       </c>
       <c r="AF490" t="inlineStr"/>
       <c r="AG490" t="inlineStr"/>
+      <c r="AH490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" s="2" t="n">
@@ -43865,6 +44359,7 @@
       </c>
       <c r="AF491" t="inlineStr"/>
       <c r="AG491" t="inlineStr"/>
+      <c r="AH491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" s="2" t="n">
@@ -43956,6 +44451,7 @@
       </c>
       <c r="AF492" t="inlineStr"/>
       <c r="AG492" t="inlineStr"/>
+      <c r="AH492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" s="2" t="n">
@@ -44047,6 +44543,7 @@
       </c>
       <c r="AF493" t="inlineStr"/>
       <c r="AG493" t="inlineStr"/>
+      <c r="AH493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" s="2" t="n">
@@ -44138,6 +44635,7 @@
       </c>
       <c r="AF494" t="inlineStr"/>
       <c r="AG494" t="inlineStr"/>
+      <c r="AH494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" s="2" t="n">
@@ -44229,6 +44727,7 @@
       </c>
       <c r="AF495" t="inlineStr"/>
       <c r="AG495" t="inlineStr"/>
+      <c r="AH495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" s="2" t="n">
@@ -44320,6 +44819,7 @@
       </c>
       <c r="AF496" t="inlineStr"/>
       <c r="AG496" t="inlineStr"/>
+      <c r="AH496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" s="2" t="n">
@@ -44411,6 +44911,7 @@
       </c>
       <c r="AF497" t="inlineStr"/>
       <c r="AG497" t="inlineStr"/>
+      <c r="AH497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" s="2" t="n">
@@ -44502,6 +45003,7 @@
       </c>
       <c r="AF498" t="inlineStr"/>
       <c r="AG498" t="inlineStr"/>
+      <c r="AH498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" s="2" t="n">
@@ -44557,6 +45059,7 @@
       </c>
       <c r="AF499" t="inlineStr"/>
       <c r="AG499" t="inlineStr"/>
+      <c r="AH499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" s="2" t="n">
@@ -44612,6 +45115,7 @@
       </c>
       <c r="AF500" t="inlineStr"/>
       <c r="AG500" t="inlineStr"/>
+      <c r="AH500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" s="2" t="n">
@@ -44667,6 +45171,7 @@
       </c>
       <c r="AF501" t="inlineStr"/>
       <c r="AG501" t="inlineStr"/>
+      <c r="AH501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" s="2" t="n">
@@ -44722,6 +45227,7 @@
       </c>
       <c r="AF502" t="inlineStr"/>
       <c r="AG502" t="inlineStr"/>
+      <c r="AH502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" s="2" t="n">
@@ -44777,6 +45283,7 @@
       </c>
       <c r="AF503" t="inlineStr"/>
       <c r="AG503" t="inlineStr"/>
+      <c r="AH503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" s="2" t="n">
@@ -44832,6 +45339,7 @@
       </c>
       <c r="AF504" t="inlineStr"/>
       <c r="AG504" t="inlineStr"/>
+      <c r="AH504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" s="2" t="n">
@@ -44923,6 +45431,7 @@
       </c>
       <c r="AF505" t="inlineStr"/>
       <c r="AG505" t="inlineStr"/>
+      <c r="AH505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" s="2" t="n">
@@ -44978,6 +45487,7 @@
       </c>
       <c r="AF506" t="inlineStr"/>
       <c r="AG506" t="inlineStr"/>
+      <c r="AH506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" s="2" t="n">
@@ -45033,6 +45543,7 @@
       </c>
       <c r="AF507" t="inlineStr"/>
       <c r="AG507" t="inlineStr"/>
+      <c r="AH507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" s="2" t="n">
@@ -45088,6 +45599,7 @@
       </c>
       <c r="AF508" t="inlineStr"/>
       <c r="AG508" t="inlineStr"/>
+      <c r="AH508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" s="2" t="n">
@@ -45143,6 +45655,7 @@
       </c>
       <c r="AF509" t="inlineStr"/>
       <c r="AG509" t="inlineStr"/>
+      <c r="AH509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" s="2" t="n">
@@ -45198,6 +45711,7 @@
       </c>
       <c r="AF510" t="inlineStr"/>
       <c r="AG510" t="inlineStr"/>
+      <c r="AH510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" s="2" t="n">
@@ -45253,6 +45767,7 @@
       </c>
       <c r="AF511" t="inlineStr"/>
       <c r="AG511" t="inlineStr"/>
+      <c r="AH511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" s="2" t="n">
@@ -45308,6 +45823,7 @@
       </c>
       <c r="AF512" t="inlineStr"/>
       <c r="AG512" t="inlineStr"/>
+      <c r="AH512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" s="2" t="n">
@@ -45363,6 +45879,7 @@
       </c>
       <c r="AF513" t="inlineStr"/>
       <c r="AG513" t="inlineStr"/>
+      <c r="AH513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" s="2" t="n">
@@ -45418,6 +45935,7 @@
       </c>
       <c r="AF514" t="inlineStr"/>
       <c r="AG514" t="inlineStr"/>
+      <c r="AH514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" s="2" t="n">
@@ -45473,6 +45991,7 @@
       </c>
       <c r="AF515" t="inlineStr"/>
       <c r="AG515" t="inlineStr"/>
+      <c r="AH515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" s="2" t="n">
@@ -45528,6 +46047,7 @@
       </c>
       <c r="AF516" t="inlineStr"/>
       <c r="AG516" t="inlineStr"/>
+      <c r="AH516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" s="2" t="n">
@@ -45583,6 +46103,7 @@
       </c>
       <c r="AF517" t="inlineStr"/>
       <c r="AG517" t="inlineStr"/>
+      <c r="AH517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" s="2" t="n">
@@ -45638,6 +46159,7 @@
       </c>
       <c r="AF518" t="inlineStr"/>
       <c r="AG518" t="inlineStr"/>
+      <c r="AH518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" s="2" t="n">
@@ -45693,6 +46215,7 @@
       </c>
       <c r="AF519" t="inlineStr"/>
       <c r="AG519" t="inlineStr"/>
+      <c r="AH519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" s="2" t="n">
@@ -45748,6 +46271,7 @@
       </c>
       <c r="AF520" t="inlineStr"/>
       <c r="AG520" t="inlineStr"/>
+      <c r="AH520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" s="2" t="n">
@@ -45803,6 +46327,7 @@
       </c>
       <c r="AF521" t="inlineStr"/>
       <c r="AG521" t="inlineStr"/>
+      <c r="AH521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" s="2" t="n">
@@ -45858,6 +46383,7 @@
       </c>
       <c r="AF522" t="inlineStr"/>
       <c r="AG522" t="inlineStr"/>
+      <c r="AH522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" s="2" t="n">
@@ -45913,6 +46439,7 @@
       </c>
       <c r="AF523" t="inlineStr"/>
       <c r="AG523" t="inlineStr"/>
+      <c r="AH523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" s="2" t="n">
@@ -45968,6 +46495,7 @@
       </c>
       <c r="AF524" t="inlineStr"/>
       <c r="AG524" t="inlineStr"/>
+      <c r="AH524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" s="2" t="n">
@@ -46023,6 +46551,7 @@
       </c>
       <c r="AF525" t="inlineStr"/>
       <c r="AG525" t="inlineStr"/>
+      <c r="AH525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" s="2" t="n">
@@ -46078,6 +46607,7 @@
       </c>
       <c r="AF526" t="inlineStr"/>
       <c r="AG526" t="inlineStr"/>
+      <c r="AH526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" s="2" t="n">
@@ -46133,6 +46663,7 @@
       </c>
       <c r="AF527" t="inlineStr"/>
       <c r="AG527" t="inlineStr"/>
+      <c r="AH527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" s="2" t="n">
@@ -46188,6 +46719,7 @@
       </c>
       <c r="AF528" t="inlineStr"/>
       <c r="AG528" t="inlineStr"/>
+      <c r="AH528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" s="2" t="n">
@@ -46243,6 +46775,7 @@
       </c>
       <c r="AF529" t="inlineStr"/>
       <c r="AG529" t="inlineStr"/>
+      <c r="AH529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" s="2" t="n">
@@ -46298,6 +46831,7 @@
       </c>
       <c r="AF530" t="inlineStr"/>
       <c r="AG530" t="inlineStr"/>
+      <c r="AH530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" s="2" t="n">
@@ -46353,6 +46887,7 @@
       </c>
       <c r="AF531" t="inlineStr"/>
       <c r="AG531" t="inlineStr"/>
+      <c r="AH531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" s="2" t="n">
@@ -46408,6 +46943,7 @@
       </c>
       <c r="AF532" t="inlineStr"/>
       <c r="AG532" t="inlineStr"/>
+      <c r="AH532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" s="2" t="n">
@@ -46463,6 +46999,7 @@
       </c>
       <c r="AF533" t="inlineStr"/>
       <c r="AG533" t="inlineStr"/>
+      <c r="AH533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" s="2" t="n">
@@ -46518,6 +47055,7 @@
       </c>
       <c r="AF534" t="inlineStr"/>
       <c r="AG534" t="inlineStr"/>
+      <c r="AH534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" s="2" t="n">
@@ -46573,6 +47111,7 @@
       </c>
       <c r="AF535" t="inlineStr"/>
       <c r="AG535" t="inlineStr"/>
+      <c r="AH535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" s="2" t="n">
@@ -46628,6 +47167,7 @@
       </c>
       <c r="AF536" t="inlineStr"/>
       <c r="AG536" t="inlineStr"/>
+      <c r="AH536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" s="2" t="n">
@@ -46683,6 +47223,7 @@
       </c>
       <c r="AF537" t="inlineStr"/>
       <c r="AG537" t="inlineStr"/>
+      <c r="AH537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" s="2" t="n">
@@ -46738,6 +47279,7 @@
       </c>
       <c r="AF538" t="inlineStr"/>
       <c r="AG538" t="inlineStr"/>
+      <c r="AH538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" s="2" t="n">
@@ -46793,6 +47335,7 @@
       </c>
       <c r="AF539" t="inlineStr"/>
       <c r="AG539" t="inlineStr"/>
+      <c r="AH539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" s="2" t="n">
@@ -46848,6 +47391,7 @@
       </c>
       <c r="AF540" t="inlineStr"/>
       <c r="AG540" t="inlineStr"/>
+      <c r="AH540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" s="2" t="n">
@@ -46903,6 +47447,7 @@
       </c>
       <c r="AF541" t="inlineStr"/>
       <c r="AG541" t="inlineStr"/>
+      <c r="AH541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" s="2" t="n">
@@ -46958,6 +47503,7 @@
       </c>
       <c r="AF542" t="inlineStr"/>
       <c r="AG542" t="inlineStr"/>
+      <c r="AH542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" s="2" t="n">
@@ -47013,6 +47559,7 @@
       </c>
       <c r="AF543" t="inlineStr"/>
       <c r="AG543" t="inlineStr"/>
+      <c r="AH543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" s="2" t="n">
@@ -47068,6 +47615,7 @@
       </c>
       <c r="AF544" t="inlineStr"/>
       <c r="AG544" t="inlineStr"/>
+      <c r="AH544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" s="2" t="n">
@@ -47123,6 +47671,7 @@
       </c>
       <c r="AF545" t="inlineStr"/>
       <c r="AG545" t="inlineStr"/>
+      <c r="AH545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" s="2" t="n">
@@ -47178,6 +47727,7 @@
       </c>
       <c r="AF546" t="inlineStr"/>
       <c r="AG546" t="inlineStr"/>
+      <c r="AH546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" s="2" t="n">
@@ -47233,6 +47783,7 @@
       </c>
       <c r="AF547" t="inlineStr"/>
       <c r="AG547" t="inlineStr"/>
+      <c r="AH547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" s="2" t="n">
@@ -47288,6 +47839,7 @@
       </c>
       <c r="AF548" t="inlineStr"/>
       <c r="AG548" t="inlineStr"/>
+      <c r="AH548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" s="2" t="n">
@@ -47343,6 +47895,7 @@
       </c>
       <c r="AF549" t="inlineStr"/>
       <c r="AG549" t="inlineStr"/>
+      <c r="AH549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" s="2" t="n">
@@ -47398,6 +47951,7 @@
       </c>
       <c r="AF550" t="inlineStr"/>
       <c r="AG550" t="inlineStr"/>
+      <c r="AH550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" s="2" t="n">
@@ -47453,6 +48007,7 @@
       </c>
       <c r="AF551" t="inlineStr"/>
       <c r="AG551" t="inlineStr"/>
+      <c r="AH551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" s="2" t="n">
@@ -47508,6 +48063,7 @@
       </c>
       <c r="AF552" t="inlineStr"/>
       <c r="AG552" t="inlineStr"/>
+      <c r="AH552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" s="2" t="n">
@@ -47563,6 +48119,7 @@
       </c>
       <c r="AF553" t="inlineStr"/>
       <c r="AG553" t="inlineStr"/>
+      <c r="AH553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" s="2" t="n">
@@ -47618,6 +48175,7 @@
       </c>
       <c r="AF554" t="inlineStr"/>
       <c r="AG554" t="inlineStr"/>
+      <c r="AH554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" s="2" t="n">
@@ -47673,6 +48231,7 @@
       </c>
       <c r="AF555" t="inlineStr"/>
       <c r="AG555" t="inlineStr"/>
+      <c r="AH555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" s="2" t="n">
@@ -47728,6 +48287,7 @@
       </c>
       <c r="AF556" t="inlineStr"/>
       <c r="AG556" t="inlineStr"/>
+      <c r="AH556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" s="2" t="n">
@@ -47783,6 +48343,7 @@
       </c>
       <c r="AF557" t="inlineStr"/>
       <c r="AG557" t="inlineStr"/>
+      <c r="AH557" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" s="2" t="n">
@@ -47838,6 +48399,7 @@
       </c>
       <c r="AF558" t="inlineStr"/>
       <c r="AG558" t="inlineStr"/>
+      <c r="AH558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" s="2" t="n">
@@ -47893,6 +48455,7 @@
       </c>
       <c r="AF559" t="inlineStr"/>
       <c r="AG559" t="inlineStr"/>
+      <c r="AH559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" s="2" t="n">
@@ -47950,6 +48513,7 @@
       </c>
       <c r="AF560" t="inlineStr"/>
       <c r="AG560" t="inlineStr"/>
+      <c r="AH560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" s="2" t="n">
@@ -48007,6 +48571,7 @@
       </c>
       <c r="AF561" t="inlineStr"/>
       <c r="AG561" t="inlineStr"/>
+      <c r="AH561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" s="2" t="n">
@@ -48064,6 +48629,7 @@
       </c>
       <c r="AF562" t="inlineStr"/>
       <c r="AG562" t="inlineStr"/>
+      <c r="AH562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" s="2" t="n">
@@ -48121,6 +48687,7 @@
       </c>
       <c r="AF563" t="inlineStr"/>
       <c r="AG563" t="inlineStr"/>
+      <c r="AH563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" s="2" t="n">
@@ -48178,6 +48745,7 @@
       </c>
       <c r="AF564" t="inlineStr"/>
       <c r="AG564" t="inlineStr"/>
+      <c r="AH564" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" s="2" t="n">
@@ -48235,6 +48803,7 @@
       </c>
       <c r="AF565" t="inlineStr"/>
       <c r="AG565" t="inlineStr"/>
+      <c r="AH565" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" s="2" t="n">
@@ -48292,6 +48861,7 @@
       </c>
       <c r="AF566" t="inlineStr"/>
       <c r="AG566" t="inlineStr"/>
+      <c r="AH566" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" s="2" t="n">
@@ -48349,6 +48919,7 @@
       </c>
       <c r="AF567" t="inlineStr"/>
       <c r="AG567" t="inlineStr"/>
+      <c r="AH567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" s="2" t="n">
@@ -48406,6 +48977,7 @@
       </c>
       <c r="AF568" t="inlineStr"/>
       <c r="AG568" t="inlineStr"/>
+      <c r="AH568" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" s="2" t="n">
@@ -48463,6 +49035,7 @@
       </c>
       <c r="AF569" t="inlineStr"/>
       <c r="AG569" t="inlineStr"/>
+      <c r="AH569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" s="2" t="n">
@@ -48520,6 +49093,7 @@
       </c>
       <c r="AF570" t="inlineStr"/>
       <c r="AG570" t="inlineStr"/>
+      <c r="AH570" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" s="2" t="n">
@@ -48577,6 +49151,7 @@
       </c>
       <c r="AF571" t="inlineStr"/>
       <c r="AG571" t="inlineStr"/>
+      <c r="AH571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" s="2" t="n">
@@ -48634,6 +49209,7 @@
       </c>
       <c r="AF572" t="inlineStr"/>
       <c r="AG572" t="inlineStr"/>
+      <c r="AH572" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" s="2" t="n">
@@ -48691,6 +49267,7 @@
       </c>
       <c r="AF573" t="inlineStr"/>
       <c r="AG573" t="inlineStr"/>
+      <c r="AH573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" s="2" t="n">
@@ -48748,6 +49325,7 @@
       </c>
       <c r="AF574" t="inlineStr"/>
       <c r="AG574" t="inlineStr"/>
+      <c r="AH574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" s="2" t="n">
@@ -48805,6 +49383,7 @@
       </c>
       <c r="AF575" t="inlineStr"/>
       <c r="AG575" t="inlineStr"/>
+      <c r="AH575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" s="2" t="n">
@@ -48862,6 +49441,7 @@
       </c>
       <c r="AF576" t="inlineStr"/>
       <c r="AG576" t="inlineStr"/>
+      <c r="AH576" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" s="2" t="n">
@@ -48919,6 +49499,7 @@
       </c>
       <c r="AF577" t="inlineStr"/>
       <c r="AG577" t="inlineStr"/>
+      <c r="AH577" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" s="2" t="n">
@@ -48976,6 +49557,7 @@
       </c>
       <c r="AF578" t="inlineStr"/>
       <c r="AG578" t="inlineStr"/>
+      <c r="AH578" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" s="2" t="n">
@@ -49033,6 +49615,7 @@
       </c>
       <c r="AF579" t="inlineStr"/>
       <c r="AG579" t="inlineStr"/>
+      <c r="AH579" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" s="2" t="n">
@@ -49090,6 +49673,7 @@
       </c>
       <c r="AF580" t="inlineStr"/>
       <c r="AG580" t="inlineStr"/>
+      <c r="AH580" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" s="2" t="n">
@@ -49147,6 +49731,7 @@
       </c>
       <c r="AF581" t="inlineStr"/>
       <c r="AG581" t="inlineStr"/>
+      <c r="AH581" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" s="2" t="n">
@@ -49204,6 +49789,7 @@
       </c>
       <c r="AF582" t="inlineStr"/>
       <c r="AG582" t="inlineStr"/>
+      <c r="AH582" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" s="2" t="n">
@@ -49261,6 +49847,7 @@
       </c>
       <c r="AF583" t="inlineStr"/>
       <c r="AG583" t="inlineStr"/>
+      <c r="AH583" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" s="2" t="n">
@@ -49318,6 +49905,7 @@
       </c>
       <c r="AF584" t="inlineStr"/>
       <c r="AG584" t="inlineStr"/>
+      <c r="AH584" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" s="2" t="n">
@@ -49375,6 +49963,7 @@
       </c>
       <c r="AF585" t="inlineStr"/>
       <c r="AG585" t="inlineStr"/>
+      <c r="AH585" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" s="2" t="n">
@@ -49432,6 +50021,7 @@
       </c>
       <c r="AF586" t="inlineStr"/>
       <c r="AG586" t="inlineStr"/>
+      <c r="AH586" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" s="2" t="n">
@@ -49489,6 +50079,7 @@
       </c>
       <c r="AF587" t="inlineStr"/>
       <c r="AG587" t="inlineStr"/>
+      <c r="AH587" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" s="2" t="n">
@@ -49546,6 +50137,7 @@
       </c>
       <c r="AF588" t="inlineStr"/>
       <c r="AG588" t="inlineStr"/>
+      <c r="AH588" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" s="2" t="n">
@@ -49603,6 +50195,7 @@
       </c>
       <c r="AF589" t="inlineStr"/>
       <c r="AG589" t="inlineStr"/>
+      <c r="AH589" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" s="2" t="n">
@@ -49660,6 +50253,7 @@
       </c>
       <c r="AF590" t="inlineStr"/>
       <c r="AG590" t="inlineStr"/>
+      <c r="AH590" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" s="2" t="n">
@@ -49717,6 +50311,7 @@
       </c>
       <c r="AF591" t="inlineStr"/>
       <c r="AG591" t="inlineStr"/>
+      <c r="AH591" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" s="2" t="n">
@@ -49774,6 +50369,7 @@
       </c>
       <c r="AF592" t="inlineStr"/>
       <c r="AG592" t="inlineStr"/>
+      <c r="AH592" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" s="2" t="n">
@@ -49829,6 +50425,7 @@
       </c>
       <c r="AF593" t="inlineStr"/>
       <c r="AG593" t="inlineStr"/>
+      <c r="AH593" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" s="2" t="n">
@@ -49884,6 +50481,7 @@
       </c>
       <c r="AF594" t="inlineStr"/>
       <c r="AG594" t="inlineStr"/>
+      <c r="AH594" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" s="2" t="n">
@@ -49939,6 +50537,7 @@
       </c>
       <c r="AF595" t="inlineStr"/>
       <c r="AG595" t="inlineStr"/>
+      <c r="AH595" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" s="2" t="n">
@@ -49994,6 +50593,7 @@
       </c>
       <c r="AF596" t="inlineStr"/>
       <c r="AG596" t="inlineStr"/>
+      <c r="AH596" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" s="2" t="n">
@@ -50049,6 +50649,7 @@
       </c>
       <c r="AF597" t="inlineStr"/>
       <c r="AG597" t="inlineStr"/>
+      <c r="AH597" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" s="2" t="n">
@@ -50104,6 +50705,7 @@
       </c>
       <c r="AF598" t="inlineStr"/>
       <c r="AG598" t="inlineStr"/>
+      <c r="AH598" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" s="2" t="n">
@@ -50159,6 +50761,7 @@
       </c>
       <c r="AF599" t="inlineStr"/>
       <c r="AG599" t="inlineStr"/>
+      <c r="AH599" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" s="2" t="n">
@@ -50214,6 +50817,7 @@
       </c>
       <c r="AF600" t="inlineStr"/>
       <c r="AG600" t="inlineStr"/>
+      <c r="AH600" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" s="2" t="n">
@@ -50269,6 +50873,7 @@
       </c>
       <c r="AF601" t="inlineStr"/>
       <c r="AG601" t="inlineStr"/>
+      <c r="AH601" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" s="2" t="n">
@@ -50324,6 +50929,7 @@
       </c>
       <c r="AF602" t="inlineStr"/>
       <c r="AG602" t="inlineStr"/>
+      <c r="AH602" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" s="2" t="n">
@@ -50379,6 +50985,7 @@
       </c>
       <c r="AF603" t="inlineStr"/>
       <c r="AG603" t="inlineStr"/>
+      <c r="AH603" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" s="2" t="n">
@@ -50434,6 +51041,7 @@
       </c>
       <c r="AF604" t="inlineStr"/>
       <c r="AG604" t="inlineStr"/>
+      <c r="AH604" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" s="2" t="n">
@@ -50489,6 +51097,7 @@
       </c>
       <c r="AF605" t="inlineStr"/>
       <c r="AG605" t="inlineStr"/>
+      <c r="AH605" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" s="2" t="n">
@@ -50544,6 +51153,7 @@
       </c>
       <c r="AF606" t="inlineStr"/>
       <c r="AG606" t="inlineStr"/>
+      <c r="AH606" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" s="2" t="n">
@@ -50599,6 +51209,7 @@
       </c>
       <c r="AF607" t="inlineStr"/>
       <c r="AG607" t="inlineStr"/>
+      <c r="AH607" t="inlineStr"/>
     </row>
     <row r="608">
       <c r="A608" s="2" t="n">
@@ -50654,6 +51265,7 @@
       </c>
       <c r="AF608" t="inlineStr"/>
       <c r="AG608" t="inlineStr"/>
+      <c r="AH608" t="inlineStr"/>
     </row>
     <row r="609">
       <c r="A609" s="2" t="n">
@@ -50709,6 +51321,7 @@
       </c>
       <c r="AF609" t="inlineStr"/>
       <c r="AG609" t="inlineStr"/>
+      <c r="AH609" t="inlineStr"/>
     </row>
     <row r="610">
       <c r="A610" s="2" t="n">
@@ -50764,6 +51377,7 @@
       </c>
       <c r="AF610" t="inlineStr"/>
       <c r="AG610" t="inlineStr"/>
+      <c r="AH610" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" s="2" t="n">
@@ -50819,6 +51433,7 @@
       </c>
       <c r="AF611" t="inlineStr"/>
       <c r="AG611" t="inlineStr"/>
+      <c r="AH611" t="inlineStr"/>
     </row>
     <row r="612">
       <c r="A612" s="2" t="n">
@@ -50874,6 +51489,7 @@
       </c>
       <c r="AF612" t="inlineStr"/>
       <c r="AG612" t="inlineStr"/>
+      <c r="AH612" t="inlineStr"/>
     </row>
     <row r="613">
       <c r="A613" s="2" t="n">
@@ -50929,6 +51545,7 @@
       </c>
       <c r="AF613" t="inlineStr"/>
       <c r="AG613" t="inlineStr"/>
+      <c r="AH613" t="inlineStr"/>
     </row>
     <row r="614">
       <c r="A614" s="2" t="n">
@@ -50984,6 +51601,7 @@
       </c>
       <c r="AF614" t="inlineStr"/>
       <c r="AG614" t="inlineStr"/>
+      <c r="AH614" t="inlineStr"/>
     </row>
     <row r="615">
       <c r="A615" s="2" t="n">
@@ -51039,6 +51657,7 @@
       </c>
       <c r="AF615" t="inlineStr"/>
       <c r="AG615" t="inlineStr"/>
+      <c r="AH615" t="inlineStr"/>
     </row>
     <row r="616">
       <c r="A616" s="2" t="n">
@@ -51094,6 +51713,7 @@
       </c>
       <c r="AF616" t="inlineStr"/>
       <c r="AG616" t="inlineStr"/>
+      <c r="AH616" t="inlineStr"/>
     </row>
     <row r="617">
       <c r="A617" s="2" t="n">
@@ -51149,6 +51769,7 @@
       </c>
       <c r="AF617" t="inlineStr"/>
       <c r="AG617" t="inlineStr"/>
+      <c r="AH617" t="inlineStr"/>
     </row>
     <row r="618">
       <c r="A618" s="2" t="n">
@@ -51204,6 +51825,7 @@
       </c>
       <c r="AF618" t="inlineStr"/>
       <c r="AG618" t="inlineStr"/>
+      <c r="AH618" t="inlineStr"/>
     </row>
     <row r="619">
       <c r="A619" s="2" t="n">
@@ -51259,6 +51881,7 @@
       </c>
       <c r="AF619" t="inlineStr"/>
       <c r="AG619" t="inlineStr"/>
+      <c r="AH619" t="inlineStr"/>
     </row>
     <row r="620">
       <c r="A620" s="2" t="n">
@@ -51314,6 +51937,7 @@
       </c>
       <c r="AF620" t="inlineStr"/>
       <c r="AG620" t="inlineStr"/>
+      <c r="AH620" t="inlineStr"/>
     </row>
     <row r="621">
       <c r="A621" s="2" t="n">
@@ -51369,6 +51993,7 @@
       </c>
       <c r="AF621" t="inlineStr"/>
       <c r="AG621" t="inlineStr"/>
+      <c r="AH621" t="inlineStr"/>
     </row>
     <row r="622">
       <c r="A622" s="2" t="n">
@@ -51424,6 +52049,7 @@
       </c>
       <c r="AF622" t="inlineStr"/>
       <c r="AG622" t="inlineStr"/>
+      <c r="AH622" t="inlineStr"/>
     </row>
     <row r="623">
       <c r="A623" s="2" t="n">
@@ -51479,6 +52105,7 @@
       </c>
       <c r="AF623" t="inlineStr"/>
       <c r="AG623" t="inlineStr"/>
+      <c r="AH623" t="inlineStr"/>
     </row>
     <row r="624">
       <c r="A624" s="2" t="n">
@@ -51534,6 +52161,7 @@
       </c>
       <c r="AF624" t="inlineStr"/>
       <c r="AG624" t="inlineStr"/>
+      <c r="AH624" t="inlineStr"/>
     </row>
     <row r="625">
       <c r="A625" s="2" t="n">
@@ -51589,6 +52217,7 @@
       </c>
       <c r="AF625" t="inlineStr"/>
       <c r="AG625" t="inlineStr"/>
+      <c r="AH625" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" s="2" t="n">
@@ -51644,6 +52273,7 @@
       </c>
       <c r="AF626" t="inlineStr"/>
       <c r="AG626" t="inlineStr"/>
+      <c r="AH626" t="inlineStr"/>
     </row>
     <row r="627">
       <c r="A627" s="2" t="n">
@@ -51699,6 +52329,7 @@
       </c>
       <c r="AF627" t="inlineStr"/>
       <c r="AG627" t="inlineStr"/>
+      <c r="AH627" t="inlineStr"/>
     </row>
     <row r="628">
       <c r="A628" s="2" t="n">
@@ -51754,6 +52385,7 @@
       </c>
       <c r="AF628" t="inlineStr"/>
       <c r="AG628" t="inlineStr"/>
+      <c r="AH628" t="inlineStr"/>
     </row>
     <row r="629">
       <c r="A629" s="2" t="n">
@@ -51809,6 +52441,7 @@
       </c>
       <c r="AF629" t="inlineStr"/>
       <c r="AG629" t="inlineStr"/>
+      <c r="AH629" t="inlineStr"/>
     </row>
     <row r="630">
       <c r="A630" s="2" t="n">
@@ -51864,6 +52497,7 @@
       </c>
       <c r="AF630" t="inlineStr"/>
       <c r="AG630" t="inlineStr"/>
+      <c r="AH630" t="inlineStr"/>
     </row>
     <row r="631">
       <c r="A631" s="2" t="n">
@@ -51919,6 +52553,7 @@
       </c>
       <c r="AF631" t="inlineStr"/>
       <c r="AG631" t="inlineStr"/>
+      <c r="AH631" t="inlineStr"/>
     </row>
     <row r="632">
       <c r="A632" s="2" t="n">
@@ -51974,6 +52609,7 @@
       </c>
       <c r="AF632" t="inlineStr"/>
       <c r="AG632" t="inlineStr"/>
+      <c r="AH632" t="inlineStr"/>
     </row>
     <row r="633">
       <c r="A633" s="2" t="n">
@@ -52029,6 +52665,7 @@
       </c>
       <c r="AF633" t="inlineStr"/>
       <c r="AG633" t="inlineStr"/>
+      <c r="AH633" t="inlineStr"/>
     </row>
     <row r="634">
       <c r="A634" s="2" t="n">
@@ -52084,6 +52721,7 @@
       </c>
       <c r="AF634" t="inlineStr"/>
       <c r="AG634" t="inlineStr"/>
+      <c r="AH634" t="inlineStr"/>
     </row>
     <row r="635">
       <c r="A635" s="2" t="n">
@@ -52139,6 +52777,7 @@
       </c>
       <c r="AF635" t="inlineStr"/>
       <c r="AG635" t="inlineStr"/>
+      <c r="AH635" t="inlineStr"/>
     </row>
     <row r="636">
       <c r="A636" s="2" t="n">
@@ -52194,6 +52833,7 @@
       </c>
       <c r="AF636" t="inlineStr"/>
       <c r="AG636" t="inlineStr"/>
+      <c r="AH636" t="inlineStr"/>
     </row>
     <row r="637">
       <c r="A637" s="2" t="n">
@@ -52249,6 +52889,7 @@
       </c>
       <c r="AF637" t="inlineStr"/>
       <c r="AG637" t="inlineStr"/>
+      <c r="AH637" t="inlineStr"/>
     </row>
     <row r="638">
       <c r="A638" s="2" t="n">
@@ -52304,6 +52945,7 @@
       </c>
       <c r="AF638" t="inlineStr"/>
       <c r="AG638" t="inlineStr"/>
+      <c r="AH638" t="inlineStr"/>
     </row>
     <row r="639">
       <c r="A639" s="2" t="n">
@@ -52359,6 +53001,7 @@
       </c>
       <c r="AF639" t="inlineStr"/>
       <c r="AG639" t="inlineStr"/>
+      <c r="AH639" t="inlineStr"/>
     </row>
     <row r="640">
       <c r="A640" s="2" t="n">
@@ -52414,6 +53057,7 @@
       </c>
       <c r="AF640" t="inlineStr"/>
       <c r="AG640" t="inlineStr"/>
+      <c r="AH640" t="inlineStr"/>
     </row>
     <row r="641">
       <c r="A641" s="2" t="n">
@@ -52469,6 +53113,7 @@
       </c>
       <c r="AF641" t="inlineStr"/>
       <c r="AG641" t="inlineStr"/>
+      <c r="AH641" t="inlineStr"/>
     </row>
     <row r="642">
       <c r="A642" s="2" t="n">
@@ -52524,6 +53169,7 @@
       </c>
       <c r="AF642" t="inlineStr"/>
       <c r="AG642" t="inlineStr"/>
+      <c r="AH642" t="inlineStr"/>
     </row>
     <row r="643">
       <c r="A643" s="2" t="n">
@@ -52579,6 +53225,7 @@
       </c>
       <c r="AF643" t="inlineStr"/>
       <c r="AG643" t="inlineStr"/>
+      <c r="AH643" t="inlineStr"/>
     </row>
     <row r="644">
       <c r="A644" s="2" t="n">
@@ -52634,6 +53281,7 @@
       </c>
       <c r="AF644" t="inlineStr"/>
       <c r="AG644" t="inlineStr"/>
+      <c r="AH644" t="inlineStr"/>
     </row>
     <row r="645">
       <c r="A645" s="2" t="n">
@@ -52689,6 +53337,7 @@
       </c>
       <c r="AF645" t="inlineStr"/>
       <c r="AG645" t="inlineStr"/>
+      <c r="AH645" t="inlineStr"/>
     </row>
     <row r="646">
       <c r="A646" s="2" t="n">
@@ -52744,6 +53393,7 @@
       </c>
       <c r="AF646" t="inlineStr"/>
       <c r="AG646" t="inlineStr"/>
+      <c r="AH646" t="inlineStr"/>
     </row>
     <row r="647">
       <c r="A647" s="2" t="n">
@@ -52799,6 +53449,7 @@
       </c>
       <c r="AF647" t="inlineStr"/>
       <c r="AG647" t="inlineStr"/>
+      <c r="AH647" t="inlineStr"/>
     </row>
     <row r="648">
       <c r="A648" s="2" t="n">
@@ -52854,6 +53505,7 @@
       </c>
       <c r="AF648" t="inlineStr"/>
       <c r="AG648" t="inlineStr"/>
+      <c r="AH648" t="inlineStr"/>
     </row>
     <row r="649">
       <c r="A649" s="2" t="n">
@@ -52909,6 +53561,7 @@
       </c>
       <c r="AF649" t="inlineStr"/>
       <c r="AG649" t="inlineStr"/>
+      <c r="AH649" t="inlineStr"/>
     </row>
     <row r="650">
       <c r="A650" s="2" t="n">
@@ -52964,6 +53617,7 @@
       </c>
       <c r="AF650" t="inlineStr"/>
       <c r="AG650" t="inlineStr"/>
+      <c r="AH650" t="inlineStr"/>
     </row>
     <row r="651">
       <c r="A651" s="2" t="n">
@@ -53019,6 +53673,7 @@
       </c>
       <c r="AF651" t="inlineStr"/>
       <c r="AG651" t="inlineStr"/>
+      <c r="AH651" t="inlineStr"/>
     </row>
     <row r="652">
       <c r="A652" s="2" t="n">
@@ -53074,6 +53729,7 @@
       </c>
       <c r="AF652" t="inlineStr"/>
       <c r="AG652" t="inlineStr"/>
+      <c r="AH652" t="inlineStr"/>
     </row>
     <row r="653">
       <c r="A653" s="2" t="n">
@@ -53135,6 +53791,7 @@
       </c>
       <c r="AF653" t="inlineStr"/>
       <c r="AG653" t="inlineStr"/>
+      <c r="AH653" t="inlineStr"/>
     </row>
     <row r="654">
       <c r="A654" s="2" t="n">
@@ -53188,6 +53845,7 @@
       </c>
       <c r="AF654" t="inlineStr"/>
       <c r="AG654" t="inlineStr"/>
+      <c r="AH654" t="inlineStr"/>
     </row>
     <row r="655">
       <c r="A655" s="2" t="n">
@@ -53245,6 +53903,7 @@
       </c>
       <c r="AF655" t="inlineStr"/>
       <c r="AG655" t="inlineStr"/>
+      <c r="AH655" t="inlineStr"/>
     </row>
     <row r="656">
       <c r="A656" s="2" t="n">
@@ -53302,6 +53961,7 @@
       </c>
       <c r="AF656" t="inlineStr"/>
       <c r="AG656" t="inlineStr"/>
+      <c r="AH656" t="inlineStr"/>
     </row>
     <row r="657">
       <c r="A657" s="2" t="n">
@@ -53359,6 +54019,7 @@
       </c>
       <c r="AF657" t="inlineStr"/>
       <c r="AG657" t="inlineStr"/>
+      <c r="AH657" t="inlineStr"/>
     </row>
     <row r="658">
       <c r="A658" s="2" t="n">
@@ -53414,6 +54075,7 @@
       </c>
       <c r="AF658" t="inlineStr"/>
       <c r="AG658" t="inlineStr"/>
+      <c r="AH658" t="inlineStr"/>
     </row>
     <row r="659">
       <c r="A659" s="2" t="n">
@@ -53471,6 +54133,7 @@
       </c>
       <c r="AF659" t="inlineStr"/>
       <c r="AG659" t="inlineStr"/>
+      <c r="AH659" t="inlineStr"/>
     </row>
     <row r="660">
       <c r="A660" s="2" t="n">
@@ -53528,6 +54191,7 @@
       </c>
       <c r="AF660" t="inlineStr"/>
       <c r="AG660" t="inlineStr"/>
+      <c r="AH660" t="inlineStr"/>
     </row>
     <row r="661">
       <c r="A661" s="2" t="n">
@@ -53585,6 +54249,7 @@
       </c>
       <c r="AF661" t="inlineStr"/>
       <c r="AG661" t="inlineStr"/>
+      <c r="AH661" t="inlineStr"/>
     </row>
     <row r="662">
       <c r="A662" s="2" t="n">
@@ -53642,6 +54307,7 @@
       </c>
       <c r="AF662" t="inlineStr"/>
       <c r="AG662" t="inlineStr"/>
+      <c r="AH662" t="inlineStr"/>
     </row>
     <row r="663">
       <c r="A663" s="2" t="n">
@@ -53699,6 +54365,7 @@
       </c>
       <c r="AF663" t="inlineStr"/>
       <c r="AG663" t="inlineStr"/>
+      <c r="AH663" t="inlineStr"/>
     </row>
     <row r="664">
       <c r="A664" s="2" t="n">
@@ -53756,6 +54423,7 @@
       </c>
       <c r="AF664" t="inlineStr"/>
       <c r="AG664" t="inlineStr"/>
+      <c r="AH664" t="inlineStr"/>
     </row>
     <row r="665">
       <c r="A665" s="2" t="n">
@@ -53813,6 +54481,7 @@
       </c>
       <c r="AF665" t="inlineStr"/>
       <c r="AG665" t="inlineStr"/>
+      <c r="AH665" t="inlineStr"/>
     </row>
     <row r="666">
       <c r="A666" s="2" t="n">
@@ -53870,6 +54539,7 @@
       </c>
       <c r="AF666" t="inlineStr"/>
       <c r="AG666" t="inlineStr"/>
+      <c r="AH666" t="inlineStr"/>
     </row>
     <row r="667">
       <c r="A667" s="2" t="n">
@@ -53927,6 +54597,7 @@
       </c>
       <c r="AF667" t="inlineStr"/>
       <c r="AG667" t="inlineStr"/>
+      <c r="AH667" t="inlineStr"/>
     </row>
     <row r="668">
       <c r="A668" s="2" t="n">
@@ -53984,6 +54655,7 @@
       </c>
       <c r="AF668" t="inlineStr"/>
       <c r="AG668" t="inlineStr"/>
+      <c r="AH668" t="inlineStr"/>
     </row>
     <row r="669">
       <c r="A669" s="2" t="n">
@@ -54041,6 +54713,7 @@
       </c>
       <c r="AF669" t="inlineStr"/>
       <c r="AG669" t="inlineStr"/>
+      <c r="AH669" t="inlineStr"/>
     </row>
     <row r="670">
       <c r="A670" s="2" t="n">
@@ -54098,6 +54771,7 @@
       </c>
       <c r="AF670" t="inlineStr"/>
       <c r="AG670" t="inlineStr"/>
+      <c r="AH670" t="inlineStr"/>
     </row>
     <row r="671">
       <c r="A671" s="2" t="n">
@@ -54155,6 +54829,7 @@
       </c>
       <c r="AF671" t="inlineStr"/>
       <c r="AG671" t="inlineStr"/>
+      <c r="AH671" t="inlineStr"/>
     </row>
     <row r="672">
       <c r="A672" s="2" t="n">
@@ -54212,6 +54887,7 @@
       </c>
       <c r="AF672" t="inlineStr"/>
       <c r="AG672" t="inlineStr"/>
+      <c r="AH672" t="inlineStr"/>
     </row>
     <row r="673">
       <c r="A673" s="2" t="n">
@@ -54269,6 +54945,7 @@
       </c>
       <c r="AF673" t="inlineStr"/>
       <c r="AG673" t="inlineStr"/>
+      <c r="AH673" t="inlineStr"/>
     </row>
     <row r="674">
       <c r="A674" s="2" t="n">
@@ -54326,6 +55003,7 @@
       </c>
       <c r="AF674" t="inlineStr"/>
       <c r="AG674" t="inlineStr"/>
+      <c r="AH674" t="inlineStr"/>
     </row>
     <row r="675">
       <c r="A675" s="2" t="n">
@@ -54383,6 +55061,7 @@
       </c>
       <c r="AF675" t="inlineStr"/>
       <c r="AG675" t="inlineStr"/>
+      <c r="AH675" t="inlineStr"/>
     </row>
     <row r="676">
       <c r="A676" s="2" t="n">
@@ -54440,6 +55119,7 @@
       </c>
       <c r="AF676" t="inlineStr"/>
       <c r="AG676" t="inlineStr"/>
+      <c r="AH676" t="inlineStr"/>
     </row>
     <row r="677">
       <c r="A677" s="2" t="n">
@@ -54497,6 +55177,7 @@
       </c>
       <c r="AF677" t="inlineStr"/>
       <c r="AG677" t="inlineStr"/>
+      <c r="AH677" t="inlineStr"/>
     </row>
     <row r="678">
       <c r="A678" s="2" t="n">
@@ -54554,6 +55235,7 @@
       </c>
       <c r="AF678" t="inlineStr"/>
       <c r="AG678" t="inlineStr"/>
+      <c r="AH678" t="inlineStr"/>
     </row>
     <row r="679">
       <c r="A679" s="2" t="n">
@@ -54611,6 +55293,7 @@
       </c>
       <c r="AF679" t="inlineStr"/>
       <c r="AG679" t="inlineStr"/>
+      <c r="AH679" t="inlineStr"/>
     </row>
     <row r="680">
       <c r="A680" s="2" t="n">
@@ -54668,6 +55351,7 @@
       </c>
       <c r="AF680" t="inlineStr"/>
       <c r="AG680" t="inlineStr"/>
+      <c r="AH680" t="inlineStr"/>
     </row>
     <row r="681">
       <c r="A681" s="2" t="n">
@@ -54725,6 +55409,7 @@
       </c>
       <c r="AF681" t="inlineStr"/>
       <c r="AG681" t="inlineStr"/>
+      <c r="AH681" t="inlineStr"/>
     </row>
     <row r="682">
       <c r="A682" s="2" t="n">
@@ -54782,6 +55467,7 @@
       </c>
       <c r="AF682" t="inlineStr"/>
       <c r="AG682" t="inlineStr"/>
+      <c r="AH682" t="inlineStr"/>
     </row>
     <row r="683">
       <c r="A683" s="2" t="n">
@@ -54839,6 +55525,7 @@
       </c>
       <c r="AF683" t="inlineStr"/>
       <c r="AG683" t="inlineStr"/>
+      <c r="AH683" t="inlineStr"/>
     </row>
     <row r="684">
       <c r="A684" s="2" t="n">
@@ -54896,6 +55583,7 @@
       </c>
       <c r="AF684" t="inlineStr"/>
       <c r="AG684" t="inlineStr"/>
+      <c r="AH684" t="inlineStr"/>
     </row>
     <row r="685">
       <c r="A685" s="2" t="n">
@@ -54953,6 +55641,7 @@
       </c>
       <c r="AF685" t="inlineStr"/>
       <c r="AG685" t="inlineStr"/>
+      <c r="AH685" t="inlineStr"/>
     </row>
     <row r="686">
       <c r="A686" s="2" t="n">
@@ -55014,6 +55703,7 @@
       <c r="AG686" t="n">
         <v>0</v>
       </c>
+      <c r="AH686" t="inlineStr"/>
     </row>
     <row r="687">
       <c r="A687" s="2" t="n">
@@ -55071,6 +55761,7 @@
       </c>
       <c r="AF687" t="inlineStr"/>
       <c r="AG687" t="inlineStr"/>
+      <c r="AH687" t="inlineStr"/>
     </row>
     <row r="688">
       <c r="A688" s="2" t="n">
@@ -55132,6 +55823,7 @@
       <c r="AG688" t="n">
         <v>0</v>
       </c>
+      <c r="AH688" t="inlineStr"/>
     </row>
     <row r="689">
       <c r="A689" s="2" t="n">
@@ -55193,6 +55885,7 @@
       <c r="AG689" t="n">
         <v>0</v>
       </c>
+      <c r="AH689" t="inlineStr"/>
     </row>
     <row r="690">
       <c r="A690" s="2" t="n">
@@ -55250,6 +55943,7 @@
       </c>
       <c r="AF690" t="inlineStr"/>
       <c r="AG690" t="inlineStr"/>
+      <c r="AH690" t="inlineStr"/>
     </row>
     <row r="691">
       <c r="A691" s="2" t="n">
@@ -55311,6 +56005,7 @@
       <c r="AG691" t="n">
         <v>0</v>
       </c>
+      <c r="AH691" t="inlineStr"/>
     </row>
     <row r="692">
       <c r="A692" s="2" t="n">
@@ -55372,6 +56067,7 @@
       <c r="AG692" t="n">
         <v>0</v>
       </c>
+      <c r="AH692" t="inlineStr"/>
     </row>
     <row r="693">
       <c r="A693" s="2" t="n">
@@ -55425,7 +56121,7 @@
         <v>62.15339999999999</v>
       </c>
       <c r="AE693" t="n">
-        <v>1821.242207702637</v>
+        <v>1821.242207702638</v>
       </c>
       <c r="AF693" t="n">
         <v>0</v>
@@ -55433,6 +56129,7 @@
       <c r="AG693" t="n">
         <v>0</v>
       </c>
+      <c r="AH693" t="inlineStr"/>
     </row>
     <row r="694">
       <c r="A694" s="2" t="n">
@@ -55486,7 +56183,7 @@
         <v>59.8246</v>
       </c>
       <c r="AE694" t="n">
-        <v>1817.968785746911</v>
+        <v>1817.968785746912</v>
       </c>
       <c r="AF694" t="n">
         <v>0</v>
@@ -55494,6 +56191,7 @@
       <c r="AG694" t="n">
         <v>0</v>
       </c>
+      <c r="AH694" t="inlineStr"/>
     </row>
     <row r="695">
       <c r="A695" s="2" t="n">
@@ -55555,6 +56253,7 @@
       <c r="AG695" t="n">
         <v>0</v>
       </c>
+      <c r="AH695" t="inlineStr"/>
     </row>
     <row r="696">
       <c r="A696" s="2" t="n">
@@ -55616,6 +56315,7 @@
       <c r="AG696" t="n">
         <v>0</v>
       </c>
+      <c r="AH696" t="inlineStr"/>
     </row>
     <row r="697">
       <c r="A697" s="2" t="n">
@@ -55677,6 +56377,7 @@
       <c r="AG697" t="n">
         <v>0</v>
       </c>
+      <c r="AH697" t="inlineStr"/>
     </row>
     <row r="698">
       <c r="A698" s="2" t="n">
@@ -55738,6 +56439,7 @@
       <c r="AG698" t="n">
         <v>0</v>
       </c>
+      <c r="AH698" t="inlineStr"/>
     </row>
     <row r="699">
       <c r="A699" s="2" t="n">
@@ -55799,6 +56501,7 @@
       <c r="AG699" t="n">
         <v>0</v>
       </c>
+      <c r="AH699" t="inlineStr"/>
     </row>
     <row r="700">
       <c r="A700" s="2" t="n">
@@ -55860,6 +56563,7 @@
       <c r="AG700" t="n">
         <v>0</v>
       </c>
+      <c r="AH700" t="inlineStr"/>
     </row>
     <row r="701">
       <c r="A701" s="2" t="n">
@@ -55921,6 +56625,7 @@
       <c r="AG701" t="n">
         <v>0</v>
       </c>
+      <c r="AH701" t="inlineStr"/>
     </row>
     <row r="702">
       <c r="A702" s="2" t="n">
@@ -55982,6 +56687,7 @@
       <c r="AG702" t="n">
         <v>0</v>
       </c>
+      <c r="AH702" t="inlineStr"/>
     </row>
     <row r="703">
       <c r="A703" s="2" t="n">
@@ -56043,6 +56749,7 @@
       <c r="AG703" t="n">
         <v>0</v>
       </c>
+      <c r="AH703" t="inlineStr"/>
     </row>
     <row r="704">
       <c r="A704" s="2" t="n">
@@ -56104,6 +56811,7 @@
       <c r="AG704" t="n">
         <v>0</v>
       </c>
+      <c r="AH704" t="inlineStr"/>
     </row>
     <row r="705">
       <c r="A705" s="2" t="n">
@@ -56165,6 +56873,7 @@
       <c r="AG705" t="n">
         <v>0</v>
       </c>
+      <c r="AH705" t="inlineStr"/>
     </row>
     <row r="706">
       <c r="A706" s="2" t="n">
@@ -56226,6 +56935,7 @@
       <c r="AG706" t="n">
         <v>0</v>
       </c>
+      <c r="AH706" t="inlineStr"/>
     </row>
     <row r="707">
       <c r="A707" s="2" t="n">
@@ -56287,6 +56997,7 @@
       <c r="AG707" t="n">
         <v>0</v>
       </c>
+      <c r="AH707" t="inlineStr"/>
     </row>
     <row r="708">
       <c r="A708" s="2" t="n">
@@ -56348,6 +57059,7 @@
       <c r="AG708" t="n">
         <v>0</v>
       </c>
+      <c r="AH708" t="inlineStr"/>
     </row>
     <row r="709">
       <c r="A709" s="2" t="n">
@@ -56401,7 +57113,7 @@
         <v>63.87159999999999</v>
       </c>
       <c r="AE709" t="n">
-        <v>1863.382152289077</v>
+        <v>1863.382152289078</v>
       </c>
       <c r="AF709" t="n">
         <v>0</v>
@@ -56409,6 +57121,7 @@
       <c r="AG709" t="n">
         <v>0</v>
       </c>
+      <c r="AH709" t="inlineStr"/>
     </row>
     <row r="710">
       <c r="A710" s="2" t="n">
@@ -56470,6 +57183,7 @@
       <c r="AG710" t="n">
         <v>0</v>
       </c>
+      <c r="AH710" t="inlineStr"/>
     </row>
     <row r="711">
       <c r="A711" s="2" t="n">
@@ -56531,6 +57245,7 @@
       <c r="AG711" t="n">
         <v>0</v>
       </c>
+      <c r="AH711" t="inlineStr"/>
     </row>
     <row r="712">
       <c r="A712" s="2" t="n">
@@ -56592,6 +57307,7 @@
       <c r="AG712" t="n">
         <v>0</v>
       </c>
+      <c r="AH712" t="inlineStr"/>
     </row>
     <row r="713">
       <c r="A713" s="2" t="n">
@@ -56653,6 +57369,7 @@
       <c r="AG713" t="n">
         <v>35.09023258</v>
       </c>
+      <c r="AH713" t="inlineStr"/>
     </row>
     <row r="714">
       <c r="A714" s="2" t="n">
@@ -56714,6 +57431,7 @@
       <c r="AG714" t="n">
         <v>35.08389860299999</v>
       </c>
+      <c r="AH714" t="inlineStr"/>
     </row>
     <row r="715">
       <c r="A715" s="2" t="n">
@@ -56775,6 +57493,7 @@
       <c r="AG715" t="n">
         <v>35.020558833</v>
       </c>
+      <c r="AH715" t="inlineStr"/>
     </row>
     <row r="716">
       <c r="A716" s="2" t="n">
@@ -56836,6 +57555,7 @@
       <c r="AG716" t="n">
         <v>34.811537592</v>
       </c>
+      <c r="AH716" t="inlineStr"/>
     </row>
     <row r="717">
       <c r="A717" s="2" t="n">
@@ -56897,6 +57617,7 @@
       <c r="AG717" t="n">
         <v>35.685626418</v>
       </c>
+      <c r="AH717" t="inlineStr"/>
     </row>
     <row r="718">
       <c r="A718" s="2" t="n">
@@ -56942,7 +57663,9 @@
       <c r="AA718" t="n">
         <v>0.0284379456177</v>
       </c>
-      <c r="AB718" t="inlineStr"/>
+      <c r="AB718" t="n">
+        <v>0</v>
+      </c>
       <c r="AC718" t="n">
         <v>19.1539144516448</v>
       </c>
@@ -56950,13 +57673,16 @@
         <v>338.776096205</v>
       </c>
       <c r="AE718" t="n">
-        <v>1965.634232302311</v>
+        <v>1965.634232302312</v>
       </c>
       <c r="AF718" t="n">
         <v>20.80325</v>
       </c>
       <c r="AG718" t="n">
         <v>35.932651521</v>
+      </c>
+      <c r="AH718" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="719">
@@ -57003,7 +57729,9 @@
       <c r="AA719" t="n">
         <v>0.02843823</v>
       </c>
-      <c r="AB719" t="inlineStr"/>
+      <c r="AB719" t="n">
+        <v>0</v>
+      </c>
       <c r="AC719" t="n">
         <v>19.2470755141528</v>
       </c>
@@ -57011,13 +57739,16 @@
         <v>327.50053363</v>
       </c>
       <c r="AE719" t="n">
-        <v>1965.473903648823</v>
+        <v>1965.473903648822</v>
       </c>
       <c r="AF719" t="n">
         <v>19.94855</v>
       </c>
       <c r="AG719" t="n">
         <v>35.736298234</v>
+      </c>
+      <c r="AH719" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="720">
@@ -57080,6 +57811,7 @@
       <c r="AG720" t="n">
         <v>36.939753864</v>
       </c>
+      <c r="AH720" t="inlineStr"/>
     </row>
     <row r="721">
       <c r="A721" s="2" t="n">
@@ -57125,7 +57857,9 @@
       <c r="AA721" t="n">
         <v>0.0284385143823</v>
       </c>
-      <c r="AB721" t="inlineStr"/>
+      <c r="AB721" t="n">
+        <v>0</v>
+      </c>
       <c r="AC721" t="n">
         <v>20.3277438392456</v>
       </c>
@@ -57140,6 +57874,9 @@
       </c>
       <c r="AG721" t="n">
         <v>36.7370666</v>
+      </c>
+      <c r="AH721" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="722">
@@ -57202,6 +57939,7 @@
       <c r="AG722" t="n">
         <v>38.276223011</v>
       </c>
+      <c r="AH722" t="inlineStr"/>
     </row>
     <row r="723">
       <c r="A723" s="2" t="n">
@@ -57255,7 +57993,7 @@
         <v>327.50053363</v>
       </c>
       <c r="AE723" t="n">
-        <v>1978.117673776472</v>
+        <v>1978.117673776471</v>
       </c>
       <c r="AF723" t="n">
         <v>20.5942</v>
@@ -57263,6 +58001,7 @@
       <c r="AG723" t="n">
         <v>37.066433404</v>
       </c>
+      <c r="AH723" t="inlineStr"/>
     </row>
     <row r="724">
       <c r="A724" s="2" t="n">
@@ -57316,7 +58055,7 @@
         <v>319.78950374</v>
       </c>
       <c r="AE724" t="n">
-        <v>1961.7161486855</v>
+        <v>1961.716148685499</v>
       </c>
       <c r="AF724" t="n">
         <v>20.37775</v>
@@ -57324,6 +58063,7 @@
       <c r="AG724" t="n">
         <v>36.813074324</v>
       </c>
+      <c r="AH724" t="inlineStr"/>
     </row>
     <row r="725">
       <c r="A725" s="2" t="n">
@@ -57369,7 +58109,9 @@
       <c r="AA725" t="n">
         <v>0.0284433488814</v>
       </c>
-      <c r="AB725" t="inlineStr"/>
+      <c r="AB725" t="n">
+        <v>0</v>
+      </c>
       <c r="AC725" t="n">
         <v>20.02962843922</v>
       </c>
@@ -57384,6 +58126,9 @@
       </c>
       <c r="AG725" t="n">
         <v>36.110002877</v>
+      </c>
+      <c r="AH725" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="726">
@@ -57430,7 +58175,9 @@
       <c r="AA726" t="n">
         <v>0.02843823</v>
       </c>
-      <c r="AB726" t="inlineStr"/>
+      <c r="AB726" t="n">
+        <v>0</v>
+      </c>
       <c r="AC726" t="n">
         <v>20.0109962267184</v>
       </c>
@@ -57438,13 +58185,16 @@
         <v>316.44320775</v>
       </c>
       <c r="AE726" t="n">
-        <v>1979.222745516693</v>
+        <v>1979.222745516692</v>
       </c>
       <c r="AF726" t="n">
         <v>21.3601</v>
       </c>
       <c r="AG726" t="n">
         <v>36.870080117</v>
+      </c>
+      <c r="AH726" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="727">
@@ -57507,6 +58257,7 @@
       <c r="AG727" t="n">
         <v>36.42036775</v>
       </c>
+      <c r="AH727" t="inlineStr"/>
     </row>
     <row r="728">
       <c r="A728" s="2" t="n">
@@ -57560,7 +58311,7 @@
         <v>302.47605927</v>
       </c>
       <c r="AE728" t="n">
-        <v>1967.081514561237</v>
+        <v>1967.081514561238</v>
       </c>
       <c r="AF728" t="n">
         <v>20.23345</v>
@@ -57568,6 +58319,7 @@
       <c r="AG728" t="n">
         <v>35.558946878</v>
       </c>
+      <c r="AH728" t="inlineStr"/>
     </row>
     <row r="729">
       <c r="A729" s="2" t="n">
@@ -57629,6 +58381,7 @@
       <c r="AG729" t="n">
         <v>34.56451248899999</v>
       </c>
+      <c r="AH729" t="inlineStr"/>
     </row>
     <row r="730">
       <c r="A730" s="2" t="n">
@@ -57674,7 +58427,9 @@
       <c r="AA730" t="n">
         <v>0.0284510272035</v>
       </c>
-      <c r="AB730" t="inlineStr"/>
+      <c r="AB730" t="n">
+        <v>0</v>
+      </c>
       <c r="AC730" t="n">
         <v>17.2906932014848</v>
       </c>
@@ -57689,6 +58444,9 @@
       </c>
       <c r="AG730" t="n">
         <v>34.437832949</v>
+      </c>
+      <c r="AH730" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="731">
@@ -57751,6 +58509,7 @@
       <c r="AG731" t="n">
         <v>34.52017464999999</v>
       </c>
+      <c r="AH731" t="inlineStr"/>
     </row>
     <row r="732">
       <c r="A732" s="2" t="n">
@@ -57796,7 +58555,9 @@
       <c r="AA732" t="n">
         <v>0.0284567148495</v>
       </c>
-      <c r="AB732" t="inlineStr"/>
+      <c r="AB732" t="n">
+        <v>0</v>
+      </c>
       <c r="AC732" t="n">
         <v>17.607440814012</v>
       </c>
@@ -57804,13 +58565,16 @@
         <v>271.413703015</v>
       </c>
       <c r="AE732" t="n">
-        <v>1951.062067618577</v>
+        <v>1951.062067618578</v>
       </c>
       <c r="AF732" t="n">
         <v>19.18635</v>
       </c>
       <c r="AG732" t="n">
         <v>34.178139892</v>
+      </c>
+      <c r="AH732" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="733">
@@ -57865,7 +58629,7 @@
         <v>276.72412926</v>
       </c>
       <c r="AE733" t="n">
-        <v>1985.302414018325</v>
+        <v>1985.302414018326</v>
       </c>
       <c r="AF733" t="n">
         <v>19.5508</v>
@@ -57873,6 +58637,7 @@
       <c r="AG733" t="n">
         <v>34.317487386</v>
       </c>
+      <c r="AH733" t="inlineStr"/>
     </row>
     <row r="734">
       <c r="A734" s="2" t="n">
@@ -57934,6 +58699,7 @@
       <c r="AG734" t="n">
         <v>33.34838890499999</v>
       </c>
+      <c r="AH734" t="inlineStr"/>
     </row>
     <row r="735">
       <c r="A735" s="2" t="n">
@@ -57995,6 +58761,7 @@
       <c r="AG735" t="n">
         <v>33.880442973</v>
       </c>
+      <c r="AH735" t="inlineStr"/>
     </row>
     <row r="736">
       <c r="A736" s="2" t="n">
@@ -58056,6 +58823,7 @@
       <c r="AG736" t="n">
         <v>33.418062652</v>
       </c>
+      <c r="AH736" t="inlineStr"/>
     </row>
     <row r="737">
       <c r="A737" s="2" t="n">
@@ -58101,7 +58869,9 @@
       <c r="AA737" t="n">
         <v>0.02845614608489999</v>
       </c>
-      <c r="AB737" t="inlineStr"/>
+      <c r="AB737" t="n">
+        <v>0</v>
+      </c>
       <c r="AC737" t="n">
         <v>17.23479656398</v>
       </c>
@@ -58116,6 +58886,9 @@
       </c>
       <c r="AG737" t="n">
         <v>33.399060721</v>
+      </c>
+      <c r="AH737" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="738">
@@ -58178,6 +58951,7 @@
       <c r="AG738" t="n">
         <v>32.886008584</v>
       </c>
+      <c r="AH738" t="inlineStr"/>
     </row>
     <row r="739">
       <c r="A739" s="2" t="n">
@@ -58239,6 +59013,7 @@
       <c r="AG739" t="n">
         <v>32.91767846899999</v>
       </c>
+      <c r="AH739" t="inlineStr"/>
     </row>
     <row r="740">
       <c r="A740" s="2" t="n">
@@ -58300,6 +59075,7 @@
       <c r="AG740" t="n">
         <v>32.727659159</v>
       </c>
+      <c r="AH740" t="inlineStr"/>
     </row>
     <row r="741">
       <c r="A741" s="2" t="n">
@@ -58345,7 +59121,9 @@
       <c r="AA741" t="n">
         <v>0.0284635400247</v>
       </c>
-      <c r="AB741" t="inlineStr"/>
+      <c r="AB741" t="n">
+        <v>0</v>
+      </c>
       <c r="AC741" t="n">
         <v>15.278414251312</v>
       </c>
@@ -58360,6 +59138,9 @@
       </c>
       <c r="AG741" t="n">
         <v>32.867006653</v>
+      </c>
+      <c r="AH741" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="742">
@@ -58422,6 +59203,205 @@
       <c r="AG742" t="n">
         <v>33.221709365</v>
       </c>
+      <c r="AH742" t="inlineStr"/>
+    </row>
+    <row r="743">
+      <c r="A743" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B743" t="n">
+        <v>0.5488742055</v>
+      </c>
+      <c r="C743" t="n">
+        <v>0.07295481350000001</v>
+      </c>
+      <c r="D743" t="inlineStr"/>
+      <c r="E743" t="inlineStr"/>
+      <c r="F743" t="inlineStr"/>
+      <c r="G743" t="inlineStr"/>
+      <c r="H743" t="inlineStr"/>
+      <c r="I743" t="n">
+        <v>0.036529164</v>
+      </c>
+      <c r="J743" t="inlineStr"/>
+      <c r="K743" t="n">
+        <v>1423.651509093422</v>
+      </c>
+      <c r="L743" t="inlineStr"/>
+      <c r="M743" t="inlineStr"/>
+      <c r="N743" t="inlineStr"/>
+      <c r="O743" t="n">
+        <v>179.477952399</v>
+      </c>
+      <c r="P743" t="inlineStr"/>
+      <c r="Q743" t="n">
+        <v>8.232e-07</v>
+      </c>
+      <c r="R743" t="inlineStr"/>
+      <c r="S743" t="inlineStr"/>
+      <c r="T743" t="inlineStr"/>
+      <c r="U743" t="inlineStr"/>
+      <c r="V743" t="inlineStr"/>
+      <c r="W743" t="inlineStr"/>
+      <c r="X743" t="inlineStr"/>
+      <c r="Y743" t="inlineStr"/>
+      <c r="Z743" t="inlineStr"/>
+      <c r="AA743" t="n">
+        <v>0.4908735533015999</v>
+      </c>
+      <c r="AB743" t="n">
+        <v>59.17704</v>
+      </c>
+      <c r="AC743" t="n">
+        <v>16.2286570888936</v>
+      </c>
+      <c r="AD743" t="n">
+        <v>0.138016385</v>
+      </c>
+      <c r="AE743" t="n">
+        <v>1866.711215764817</v>
+      </c>
+      <c r="AF743" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG743" t="n">
+        <v>0.020708239</v>
+      </c>
+      <c r="AH743" t="n">
+        <v>186.8681</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B744" t="n">
+        <v>0.5319963049999999</v>
+      </c>
+      <c r="C744" t="n">
+        <v>0.07294463550000001</v>
+      </c>
+      <c r="D744" t="inlineStr"/>
+      <c r="E744" t="inlineStr"/>
+      <c r="F744" t="inlineStr"/>
+      <c r="G744" t="inlineStr"/>
+      <c r="H744" t="inlineStr"/>
+      <c r="I744" t="n">
+        <v>0.036015168</v>
+      </c>
+      <c r="J744" t="inlineStr"/>
+      <c r="K744" t="n">
+        <v>1392.050821071428</v>
+      </c>
+      <c r="L744" t="inlineStr"/>
+      <c r="M744" t="inlineStr"/>
+      <c r="N744" t="inlineStr"/>
+      <c r="O744" t="n">
+        <v>175.070253758</v>
+      </c>
+      <c r="P744" t="inlineStr"/>
+      <c r="Q744" t="n">
+        <v>8.207999999999999e-07</v>
+      </c>
+      <c r="R744" t="inlineStr"/>
+      <c r="S744" t="inlineStr"/>
+      <c r="T744" t="inlineStr"/>
+      <c r="U744" t="inlineStr"/>
+      <c r="V744" t="inlineStr"/>
+      <c r="W744" t="inlineStr"/>
+      <c r="X744" t="inlineStr"/>
+      <c r="Y744" t="inlineStr"/>
+      <c r="Z744" t="inlineStr"/>
+      <c r="AA744" t="n">
+        <v>0.4908049044584</v>
+      </c>
+      <c r="AB744" t="n">
+        <v>56.63736</v>
+      </c>
+      <c r="AC744" t="n">
+        <v>15.37157531382</v>
+      </c>
+      <c r="AD744" t="n">
+        <v>0.13386997</v>
+      </c>
+      <c r="AE744" t="n">
+        <v>1815.204741130007</v>
+      </c>
+      <c r="AF744" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG744" t="n">
+        <v>0.020199183</v>
+      </c>
+      <c r="AH744" t="n">
+        <v>174.7889</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="2" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B745" t="n">
+        <v>0.4973681835</v>
+      </c>
+      <c r="C745" t="n">
+        <v>0.067605184</v>
+      </c>
+      <c r="D745" t="inlineStr"/>
+      <c r="E745" t="inlineStr"/>
+      <c r="F745" t="inlineStr"/>
+      <c r="G745" t="inlineStr"/>
+      <c r="H745" t="inlineStr"/>
+      <c r="I745" t="n">
+        <v>0.032891313</v>
+      </c>
+      <c r="J745" t="inlineStr"/>
+      <c r="K745" t="n">
+        <v>1347.890885245821</v>
+      </c>
+      <c r="L745" t="inlineStr"/>
+      <c r="M745" t="inlineStr"/>
+      <c r="N745" t="inlineStr"/>
+      <c r="O745" t="n">
+        <v>164.3579042242</v>
+      </c>
+      <c r="P745" t="inlineStr"/>
+      <c r="Q745" t="n">
+        <v>7.488e-07</v>
+      </c>
+      <c r="R745" t="inlineStr"/>
+      <c r="S745" t="inlineStr"/>
+      <c r="T745" t="inlineStr"/>
+      <c r="U745" t="inlineStr"/>
+      <c r="V745" t="inlineStr"/>
+      <c r="W745" t="inlineStr"/>
+      <c r="X745" t="inlineStr"/>
+      <c r="Y745" t="inlineStr"/>
+      <c r="Z745" t="inlineStr"/>
+      <c r="AA745" t="n">
+        <v>0.4908441323688</v>
+      </c>
+      <c r="AB745" t="n">
+        <v>63.40776</v>
+      </c>
+      <c r="AC745" t="n">
+        <v>14.7008156637624</v>
+      </c>
+      <c r="AD745" t="n">
+        <v>0.122433155</v>
+      </c>
+      <c r="AE745" t="n">
+        <v>1751.636563957452</v>
+      </c>
+      <c r="AF745" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG745" t="n">
+        <v>0.018656107</v>
+      </c>
+      <c r="AH745" t="n">
+        <v>160.0494</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH745"/>
+  <dimension ref="A1:AH746"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57795,7 +57795,9 @@
       <c r="AA720" t="n">
         <v>0.0284365237062</v>
       </c>
-      <c r="AB720" t="inlineStr"/>
+      <c r="AB720" t="n">
+        <v>0</v>
+      </c>
       <c r="AC720" t="n">
         <v>20.215950564236</v>
       </c>
@@ -57811,7 +57813,9 @@
       <c r="AG720" t="n">
         <v>36.939753864</v>
       </c>
-      <c r="AH720" t="inlineStr"/>
+      <c r="AH720" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="721">
       <c r="A721" s="2" t="n">
@@ -57923,7 +57927,9 @@
       <c r="AA722" t="n">
         <v>0.0284373768531</v>
       </c>
-      <c r="AB722" t="inlineStr"/>
+      <c r="AB722" t="n">
+        <v>0</v>
+      </c>
       <c r="AC722" t="n">
         <v>20.774916939284</v>
       </c>
@@ -57939,7 +57945,9 @@
       <c r="AG722" t="n">
         <v>38.276223011</v>
       </c>
-      <c r="AH722" t="inlineStr"/>
+      <c r="AH722" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="723">
       <c r="A723" s="2" t="n">
@@ -58047,7 +58055,9 @@
       <c r="AA724" t="n">
         <v>0.0284385143823</v>
       </c>
-      <c r="AB724" t="inlineStr"/>
+      <c r="AB724" t="n">
+        <v>0</v>
+      </c>
       <c r="AC724" t="n">
         <v>21.240722251824</v>
       </c>
@@ -58055,7 +58065,7 @@
         <v>319.78950374</v>
       </c>
       <c r="AE724" t="n">
-        <v>1961.716148685499</v>
+        <v>1961.7161486855</v>
       </c>
       <c r="AF724" t="n">
         <v>20.37775</v>
@@ -58063,7 +58073,9 @@
       <c r="AG724" t="n">
         <v>36.813074324</v>
       </c>
-      <c r="AH724" t="inlineStr"/>
+      <c r="AH724" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="725">
       <c r="A725" s="2" t="n">
@@ -58241,7 +58253,9 @@
       <c r="AA727" t="n">
         <v>0.0284478989982</v>
       </c>
-      <c r="AB727" t="inlineStr"/>
+      <c r="AB727" t="n">
+        <v>0</v>
+      </c>
       <c r="AC727" t="n">
         <v>18.6881091391048</v>
       </c>
@@ -58257,7 +58271,9 @@
       <c r="AG727" t="n">
         <v>36.42036775</v>
       </c>
-      <c r="AH727" t="inlineStr"/>
+      <c r="AH727" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="728">
       <c r="A728" s="2" t="n">
@@ -58365,7 +58381,9 @@
       <c r="AA729" t="n">
         <v>0.0284478989982</v>
       </c>
-      <c r="AB729" t="inlineStr"/>
+      <c r="AB729" t="n">
+        <v>0</v>
+      </c>
       <c r="AC729" t="n">
         <v>17.7192340890216</v>
       </c>
@@ -58381,7 +58399,9 @@
       <c r="AG729" t="n">
         <v>34.56451248899999</v>
       </c>
-      <c r="AH729" t="inlineStr"/>
+      <c r="AH729" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="730">
       <c r="A730" s="2" t="n">
@@ -58683,7 +58703,9 @@
       <c r="AA734" t="n">
         <v>0.0284621181132</v>
       </c>
-      <c r="AB734" t="inlineStr"/>
+      <c r="AB734" t="n">
+        <v>0</v>
+      </c>
       <c r="AC734" t="n">
         <v>16.8994167389512</v>
       </c>
@@ -58699,7 +58721,9 @@
       <c r="AG734" t="n">
         <v>33.34838890499999</v>
       </c>
-      <c r="AH734" t="inlineStr"/>
+      <c r="AH734" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="735">
       <c r="A735" s="2" t="n">
@@ -58807,7 +58831,9 @@
       <c r="AA736" t="n">
         <v>0.0284646775539</v>
       </c>
-      <c r="AB736" t="inlineStr"/>
+      <c r="AB736" t="n">
+        <v>0</v>
+      </c>
       <c r="AC736" t="n">
         <v>17.1788999264752</v>
       </c>
@@ -58823,7 +58849,9 @@
       <c r="AG736" t="n">
         <v>33.418062652</v>
       </c>
-      <c r="AH736" t="inlineStr"/>
+      <c r="AH736" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="737">
       <c r="A737" s="2" t="n">
@@ -59059,7 +59087,9 @@
       <c r="AA740" t="n">
         <v>0.0284655307008</v>
       </c>
-      <c r="AB740" t="inlineStr"/>
+      <c r="AB740" t="n">
+        <v>0</v>
+      </c>
       <c r="AC740" t="n">
         <v>15.092092126296</v>
       </c>
@@ -59075,7 +59105,9 @@
       <c r="AG740" t="n">
         <v>32.727659159</v>
       </c>
-      <c r="AH740" t="inlineStr"/>
+      <c r="AH740" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="741">
       <c r="A741" s="2" t="n">
@@ -59403,6 +59435,72 @@
         <v>160.0494</v>
       </c>
     </row>
+    <row r="746">
+      <c r="A746" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B746" t="n">
+        <v>0.4778634875</v>
+      </c>
+      <c r="C746" t="n">
+        <v>0.06590436750000001</v>
+      </c>
+      <c r="D746" t="inlineStr"/>
+      <c r="E746" t="inlineStr"/>
+      <c r="F746" t="inlineStr"/>
+      <c r="G746" t="inlineStr"/>
+      <c r="H746" t="inlineStr"/>
+      <c r="I746" t="n">
+        <v>0.031730391</v>
+      </c>
+      <c r="J746" t="inlineStr"/>
+      <c r="K746" t="n">
+        <v>1350.726844427282</v>
+      </c>
+      <c r="L746" t="inlineStr"/>
+      <c r="M746" t="inlineStr"/>
+      <c r="N746" t="inlineStr"/>
+      <c r="O746" t="n">
+        <v>156.7650434134</v>
+      </c>
+      <c r="P746" t="inlineStr"/>
+      <c r="Q746" t="n">
+        <v>7.488e-07</v>
+      </c>
+      <c r="R746" t="inlineStr"/>
+      <c r="S746" t="inlineStr"/>
+      <c r="T746" t="inlineStr"/>
+      <c r="U746" t="inlineStr"/>
+      <c r="V746" t="inlineStr"/>
+      <c r="W746" t="inlineStr"/>
+      <c r="X746" t="inlineStr"/>
+      <c r="Y746" t="inlineStr"/>
+      <c r="Z746" t="inlineStr"/>
+      <c r="AA746" t="n">
+        <v>0.4908588428351999</v>
+      </c>
+      <c r="AB746" t="n">
+        <v>64.53616</v>
+      </c>
+      <c r="AC746" t="n">
+        <v>14.9244022137816</v>
+      </c>
+      <c r="AD746" t="n">
+        <v>0.110859645</v>
+      </c>
+      <c r="AE746" t="n">
+        <v>1738.275615115099</v>
+      </c>
+      <c r="AF746" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG746" t="n">
+        <v>0.018747578</v>
+      </c>
+      <c r="AH746" t="n">
+        <v>150.1272</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH746"/>
+  <dimension ref="A1:AH748"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57739,7 +57739,7 @@
         <v>327.50053363</v>
       </c>
       <c r="AE719" t="n">
-        <v>1965.473903648822</v>
+        <v>1965.473903648823</v>
       </c>
       <c r="AF719" t="n">
         <v>19.94855</v>
@@ -57993,7 +57993,9 @@
       <c r="AA723" t="n">
         <v>0.0284405050584</v>
       </c>
-      <c r="AB723" t="inlineStr"/>
+      <c r="AB723" t="n">
+        <v>0</v>
+      </c>
       <c r="AC723" t="n">
         <v>20.49543375176</v>
       </c>
@@ -58001,7 +58003,7 @@
         <v>327.50053363</v>
       </c>
       <c r="AE723" t="n">
-        <v>1978.117673776471</v>
+        <v>1978.117673776472</v>
       </c>
       <c r="AF723" t="n">
         <v>20.5942</v>
@@ -58009,7 +58011,9 @@
       <c r="AG723" t="n">
         <v>37.066433404</v>
       </c>
-      <c r="AH723" t="inlineStr"/>
+      <c r="AH723" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="724">
       <c r="A724" s="2" t="n">
@@ -58065,7 +58069,7 @@
         <v>319.78950374</v>
       </c>
       <c r="AE724" t="n">
-        <v>1961.7161486855</v>
+        <v>1961.716148685499</v>
       </c>
       <c r="AF724" t="n">
         <v>20.37775</v>
@@ -58319,7 +58323,9 @@
       <c r="AA728" t="n">
         <v>0.0284447707929</v>
       </c>
-      <c r="AB728" t="inlineStr"/>
+      <c r="AB728" t="n">
+        <v>0</v>
+      </c>
       <c r="AC728" t="n">
         <v>18.0359817015488</v>
       </c>
@@ -58335,7 +58341,9 @@
       <c r="AG728" t="n">
         <v>35.558946878</v>
       </c>
-      <c r="AH728" t="inlineStr"/>
+      <c r="AH728" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="729">
       <c r="A729" s="2" t="n">
@@ -59357,7 +59365,7 @@
         <v>0.13386997</v>
       </c>
       <c r="AE744" t="n">
-        <v>1815.204741130007</v>
+        <v>1815.204741130006</v>
       </c>
       <c r="AF744" t="n">
         <v>0</v>
@@ -59501,6 +59509,138 @@
         <v>150.1272</v>
       </c>
     </row>
+    <row r="747">
+      <c r="A747" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B747" t="n">
+        <v>0.4759506254999999</v>
+      </c>
+      <c r="C747" t="n">
+        <v>0.0643674895</v>
+      </c>
+      <c r="D747" t="inlineStr"/>
+      <c r="E747" t="inlineStr"/>
+      <c r="F747" t="inlineStr"/>
+      <c r="G747" t="inlineStr"/>
+      <c r="H747" t="inlineStr"/>
+      <c r="I747" t="n">
+        <v>0.030520728</v>
+      </c>
+      <c r="J747" t="inlineStr"/>
+      <c r="K747" t="n">
+        <v>1347.080611193975</v>
+      </c>
+      <c r="L747" t="inlineStr"/>
+      <c r="M747" t="inlineStr"/>
+      <c r="N747" t="inlineStr"/>
+      <c r="O747" t="n">
+        <v>152.6983415154</v>
+      </c>
+      <c r="P747" t="inlineStr"/>
+      <c r="Q747" t="n">
+        <v>7.104e-07</v>
+      </c>
+      <c r="R747" t="inlineStr"/>
+      <c r="S747" t="inlineStr"/>
+      <c r="T747" t="inlineStr"/>
+      <c r="U747" t="inlineStr"/>
+      <c r="V747" t="inlineStr"/>
+      <c r="W747" t="inlineStr"/>
+      <c r="X747" t="inlineStr"/>
+      <c r="Y747" t="inlineStr"/>
+      <c r="Z747" t="inlineStr"/>
+      <c r="AA747" t="n">
+        <v>0.49071664166</v>
+      </c>
+      <c r="AB747" t="n">
+        <v>47.78176</v>
+      </c>
+      <c r="AC747" t="n">
+        <v>13.9555271636984</v>
+      </c>
+      <c r="AD747" t="n">
+        <v>0.11190764</v>
+      </c>
+      <c r="AE747" t="n">
+        <v>1707.730154736133</v>
+      </c>
+      <c r="AF747" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG747" t="n">
+        <v>0.018151028</v>
+      </c>
+      <c r="AH747" t="n">
+        <v>145.0223</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B748" t="n">
+        <v>0.4548707015</v>
+      </c>
+      <c r="C748" t="n">
+        <v>0.05755659</v>
+      </c>
+      <c r="D748" t="inlineStr"/>
+      <c r="E748" t="inlineStr"/>
+      <c r="F748" t="inlineStr"/>
+      <c r="G748" t="inlineStr"/>
+      <c r="H748" t="inlineStr"/>
+      <c r="I748" t="n">
+        <v>0.028198884</v>
+      </c>
+      <c r="J748" t="inlineStr"/>
+      <c r="K748" t="n">
+        <v>1297.653894031369</v>
+      </c>
+      <c r="L748" t="inlineStr"/>
+      <c r="M748" t="inlineStr"/>
+      <c r="N748" t="inlineStr"/>
+      <c r="O748" t="n">
+        <v>144.5371527996</v>
+      </c>
+      <c r="P748" t="inlineStr"/>
+      <c r="Q748" t="n">
+        <v>6.48e-07</v>
+      </c>
+      <c r="R748" t="inlineStr"/>
+      <c r="S748" t="inlineStr"/>
+      <c r="T748" t="inlineStr"/>
+      <c r="U748" t="inlineStr"/>
+      <c r="V748" t="inlineStr"/>
+      <c r="W748" t="inlineStr"/>
+      <c r="X748" t="inlineStr"/>
+      <c r="Y748" t="inlineStr"/>
+      <c r="Z748" t="inlineStr"/>
+      <c r="AA748" t="n">
+        <v>0.4903537834888</v>
+      </c>
+      <c r="AB748" t="n">
+        <v>40.50072</v>
+      </c>
+      <c r="AC748" t="n">
+        <v>12.7816977760976</v>
+      </c>
+      <c r="AD748" t="n">
+        <v>0.09568649999999999</v>
+      </c>
+      <c r="AE748" t="n">
+        <v>1642.790060078056</v>
+      </c>
+      <c r="AF748" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG748" t="n">
+        <v>0.017228364</v>
+      </c>
+      <c r="AH748" t="n">
+        <v>146.1727</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH748"/>
+  <dimension ref="A1:AH751"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58003,7 +58003,7 @@
         <v>327.50053363</v>
       </c>
       <c r="AE723" t="n">
-        <v>1978.117673776472</v>
+        <v>1978.117673776471</v>
       </c>
       <c r="AF723" t="n">
         <v>20.5942</v>
@@ -58069,7 +58069,7 @@
         <v>319.78950374</v>
       </c>
       <c r="AE724" t="n">
-        <v>1961.716148685499</v>
+        <v>1961.7161486855</v>
       </c>
       <c r="AF724" t="n">
         <v>20.37775</v>
@@ -58521,7 +58521,9 @@
       <c r="AA731" t="n">
         <v>0.0284564304672</v>
       </c>
-      <c r="AB731" t="inlineStr"/>
+      <c r="AB731" t="n">
+        <v>0</v>
+      </c>
       <c r="AC731" t="n">
         <v>16.6013013389256</v>
       </c>
@@ -58537,7 +58539,9 @@
       <c r="AG731" t="n">
         <v>34.52017464999999</v>
       </c>
-      <c r="AH731" t="inlineStr"/>
+      <c r="AH731" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="732">
       <c r="A732" s="2" t="n">
@@ -58971,7 +58975,9 @@
       <c r="AA738" t="n">
         <v>0.028469512053</v>
       </c>
-      <c r="AB738" t="inlineStr"/>
+      <c r="AB738" t="n">
+        <v>0</v>
+      </c>
       <c r="AC738" t="n">
         <v>16.9180489514528</v>
       </c>
@@ -58987,7 +58993,9 @@
       <c r="AG738" t="n">
         <v>32.886008584</v>
       </c>
-      <c r="AH738" t="inlineStr"/>
+      <c r="AH738" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="739">
       <c r="A739" s="2" t="n">
@@ -59641,6 +59649,204 @@
         <v>146.1727</v>
       </c>
     </row>
+    <row r="749">
+      <c r="A749" s="2" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B749" t="n">
+        <v>0.453590419</v>
+      </c>
+      <c r="C749" t="n">
+        <v>0.05705823150000001</v>
+      </c>
+      <c r="D749" t="inlineStr"/>
+      <c r="E749" t="inlineStr"/>
+      <c r="F749" t="inlineStr"/>
+      <c r="G749" t="inlineStr"/>
+      <c r="H749" t="inlineStr"/>
+      <c r="I749" t="n">
+        <v>0.02756082</v>
+      </c>
+      <c r="J749" t="inlineStr"/>
+      <c r="K749" t="n">
+        <v>1313.454238042366</v>
+      </c>
+      <c r="L749" t="inlineStr"/>
+      <c r="M749" t="inlineStr"/>
+      <c r="N749" t="inlineStr"/>
+      <c r="O749" t="n">
+        <v>145.1206361154</v>
+      </c>
+      <c r="P749" t="inlineStr"/>
+      <c r="Q749" t="n">
+        <v>6.456e-07</v>
+      </c>
+      <c r="R749" t="inlineStr"/>
+      <c r="S749" t="inlineStr"/>
+      <c r="T749" t="inlineStr"/>
+      <c r="U749" t="inlineStr"/>
+      <c r="V749" t="inlineStr"/>
+      <c r="W749" t="inlineStr"/>
+      <c r="X749" t="inlineStr"/>
+      <c r="Y749" t="inlineStr"/>
+      <c r="Z749" t="inlineStr"/>
+      <c r="AA749" t="n">
+        <v>0.4904322393096</v>
+      </c>
+      <c r="AB749" t="n">
+        <v>37.68544</v>
+      </c>
+      <c r="AC749" t="n">
+        <v>12.9307554761104</v>
+      </c>
+      <c r="AD749" t="n">
+        <v>0.09905831</v>
+      </c>
+      <c r="AE749" t="n">
+        <v>1662.835131102286</v>
+      </c>
+      <c r="AF749" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG749" t="n">
+        <v>0.016460803</v>
+      </c>
+      <c r="AH749" t="n">
+        <v>152.4999</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="2" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B750" t="n">
+        <v>0.4718234745</v>
+      </c>
+      <c r="C750" t="n">
+        <v>0.06145003850000001</v>
+      </c>
+      <c r="D750" t="inlineStr"/>
+      <c r="E750" t="inlineStr"/>
+      <c r="F750" t="inlineStr"/>
+      <c r="G750" t="inlineStr"/>
+      <c r="H750" t="inlineStr"/>
+      <c r="I750" t="n">
+        <v>0.02946615</v>
+      </c>
+      <c r="J750" t="inlineStr"/>
+      <c r="K750" t="n">
+        <v>1323.987800716364</v>
+      </c>
+      <c r="L750" t="inlineStr"/>
+      <c r="M750" t="inlineStr"/>
+      <c r="N750" t="inlineStr"/>
+      <c r="O750" t="n">
+        <v>152.6756083992</v>
+      </c>
+      <c r="P750" t="inlineStr"/>
+      <c r="Q750" t="n">
+        <v>6.744000000000001e-07</v>
+      </c>
+      <c r="R750" t="inlineStr"/>
+      <c r="S750" t="inlineStr"/>
+      <c r="T750" t="inlineStr"/>
+      <c r="U750" t="inlineStr"/>
+      <c r="V750" t="inlineStr"/>
+      <c r="W750" t="inlineStr"/>
+      <c r="X750" t="inlineStr"/>
+      <c r="Y750" t="inlineStr"/>
+      <c r="Z750" t="inlineStr"/>
+      <c r="AA750" t="n">
+        <v>0.4904273358207999</v>
+      </c>
+      <c r="AB750" t="n">
+        <v>45.8224</v>
+      </c>
+      <c r="AC750" t="n">
+        <v>13.8064694636856</v>
+      </c>
+      <c r="AD750" t="n">
+        <v>0.104936195</v>
+      </c>
+      <c r="AE750" t="n">
+        <v>1685.50951593847</v>
+      </c>
+      <c r="AF750" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG750" t="n">
+        <v>0.017033491</v>
+      </c>
+      <c r="AH750" t="n">
+        <v>148.0421</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B751" t="n">
+        <v>0.4699906255</v>
+      </c>
+      <c r="C751" t="n">
+        <v>0.06144931150000001</v>
+      </c>
+      <c r="D751" t="inlineStr"/>
+      <c r="E751" t="inlineStr"/>
+      <c r="F751" t="inlineStr"/>
+      <c r="G751" t="inlineStr"/>
+      <c r="H751" t="inlineStr"/>
+      <c r="I751" t="n">
+        <v>0.02960794199999999</v>
+      </c>
+      <c r="J751" t="inlineStr"/>
+      <c r="K751" t="n">
+        <v>1323.987800716364</v>
+      </c>
+      <c r="L751" t="inlineStr"/>
+      <c r="M751" t="inlineStr"/>
+      <c r="N751" t="inlineStr"/>
+      <c r="O751" t="n">
+        <v>152.0239257348</v>
+      </c>
+      <c r="P751" t="inlineStr"/>
+      <c r="Q751" t="n">
+        <v>6.744000000000001e-07</v>
+      </c>
+      <c r="R751" t="inlineStr"/>
+      <c r="S751" t="inlineStr"/>
+      <c r="T751" t="inlineStr"/>
+      <c r="U751" t="inlineStr"/>
+      <c r="V751" t="inlineStr"/>
+      <c r="W751" t="inlineStr"/>
+      <c r="X751" t="inlineStr"/>
+      <c r="Y751" t="inlineStr"/>
+      <c r="Z751" t="inlineStr"/>
+      <c r="AA751" t="n">
+        <v>0.4903832044216</v>
+      </c>
+      <c r="AB751" t="n">
+        <v>47.74016</v>
+      </c>
+      <c r="AC751" t="n">
+        <v>13.6574117636728</v>
+      </c>
+      <c r="AD751" t="n">
+        <v>0.09541311</v>
+      </c>
+      <c r="AE751" t="n">
+        <v>1684.242656113659</v>
+      </c>
+      <c r="AF751" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG751" t="n">
+        <v>0.017113031</v>
+      </c>
+      <c r="AH751" t="n">
+        <v>145.6694</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH751"/>
+  <dimension ref="A1:AH752"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58653,7 +58653,9 @@
       <c r="AA733" t="n">
         <v>0.0284572836141</v>
       </c>
-      <c r="AB733" t="inlineStr"/>
+      <c r="AB733" t="n">
+        <v>0</v>
+      </c>
       <c r="AC733" t="n">
         <v>18.2782004640696</v>
       </c>
@@ -58669,7 +58671,9 @@
       <c r="AG733" t="n">
         <v>34.317487386</v>
       </c>
-      <c r="AH733" t="inlineStr"/>
+      <c r="AH733" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="734">
       <c r="A734" s="2" t="n">
@@ -58781,7 +58785,9 @@
       <c r="AA735" t="n">
         <v>0.0284655307008</v>
       </c>
-      <c r="AB735" t="inlineStr"/>
+      <c r="AB735" t="n">
+        <v>0</v>
+      </c>
       <c r="AC735" t="n">
         <v>17.4024864764944</v>
       </c>
@@ -58797,7 +58803,9 @@
       <c r="AG735" t="n">
         <v>33.880442973</v>
       </c>
-      <c r="AH735" t="inlineStr"/>
+      <c r="AH735" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="736">
       <c r="A736" s="2" t="n">
@@ -59235,7 +59243,9 @@
       <c r="AA742" t="n">
         <v>0.0284680901415</v>
       </c>
-      <c r="AB742" t="inlineStr"/>
+      <c r="AB742" t="n">
+        <v>0</v>
+      </c>
       <c r="AC742" t="n">
         <v>15.3529431013184</v>
       </c>
@@ -59251,7 +59261,9 @@
       <c r="AG742" t="n">
         <v>33.221709365</v>
       </c>
-      <c r="AH742" t="inlineStr"/>
+      <c r="AH742" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="743">
       <c r="A743" s="2" t="n">
@@ -59847,6 +59859,72 @@
         <v>145.6694</v>
       </c>
     </row>
+    <row r="752">
+      <c r="A752" s="2" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B752" t="n">
+        <v>0.4598885</v>
+      </c>
+      <c r="C752" t="n">
+        <v>0.059596552</v>
+      </c>
+      <c r="D752" t="inlineStr"/>
+      <c r="E752" t="inlineStr"/>
+      <c r="F752" t="inlineStr"/>
+      <c r="G752" t="inlineStr"/>
+      <c r="H752" t="inlineStr"/>
+      <c r="I752" t="n">
+        <v>0.028783776</v>
+      </c>
+      <c r="J752" t="inlineStr"/>
+      <c r="K752" t="n">
+        <v>1308.187456705367</v>
+      </c>
+      <c r="L752" t="inlineStr"/>
+      <c r="M752" t="inlineStr"/>
+      <c r="N752" t="inlineStr"/>
+      <c r="O752" t="n">
+        <v>149.8971164192</v>
+      </c>
+      <c r="P752" t="inlineStr"/>
+      <c r="Q752" t="n">
+        <v>6.648e-07</v>
+      </c>
+      <c r="R752" t="inlineStr"/>
+      <c r="S752" t="inlineStr"/>
+      <c r="T752" t="inlineStr"/>
+      <c r="U752" t="inlineStr"/>
+      <c r="V752" t="inlineStr"/>
+      <c r="W752" t="inlineStr"/>
+      <c r="X752" t="inlineStr"/>
+      <c r="Y752" t="inlineStr"/>
+      <c r="Z752" t="inlineStr"/>
+      <c r="AA752" t="n">
+        <v>0.490545019552</v>
+      </c>
+      <c r="AB752" t="n">
+        <v>44.72208</v>
+      </c>
+      <c r="AC752" t="n">
+        <v>13.2661353011392</v>
+      </c>
+      <c r="AD752" t="n">
+        <v>0.09267921</v>
+      </c>
+      <c r="AE752" t="n">
+        <v>1655.485095179058</v>
+      </c>
+      <c r="AF752" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG752" t="n">
+        <v>0.017113031</v>
+      </c>
+      <c r="AH752" t="n">
+        <v>138.2637</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH752"/>
+  <dimension ref="A1:AH754"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58069,7 +58069,7 @@
         <v>319.78950374</v>
       </c>
       <c r="AE724" t="n">
-        <v>1961.7161486855</v>
+        <v>1961.716148685499</v>
       </c>
       <c r="AF724" t="n">
         <v>20.37775</v>
@@ -59925,6 +59925,138 @@
         <v>138.2637</v>
       </c>
     </row>
+    <row r="753">
+      <c r="A753" s="2" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B753" t="n">
+        <v>0.4582568755</v>
+      </c>
+      <c r="C753" t="n">
+        <v>0.0589447965</v>
+      </c>
+      <c r="D753" t="inlineStr"/>
+      <c r="E753" t="inlineStr"/>
+      <c r="F753" t="inlineStr"/>
+      <c r="G753" t="inlineStr"/>
+      <c r="H753" t="inlineStr"/>
+      <c r="I753" t="n">
+        <v>0.027999489</v>
+      </c>
+      <c r="J753" t="inlineStr"/>
+      <c r="K753" t="n">
+        <v>1300.894990238753</v>
+      </c>
+      <c r="L753" t="inlineStr"/>
+      <c r="M753" t="inlineStr"/>
+      <c r="N753" t="inlineStr"/>
+      <c r="O753" t="n">
+        <v>148.1517182754</v>
+      </c>
+      <c r="P753" t="inlineStr"/>
+      <c r="Q753" t="n">
+        <v>6.48e-07</v>
+      </c>
+      <c r="R753" t="inlineStr"/>
+      <c r="S753" t="inlineStr"/>
+      <c r="T753" t="inlineStr"/>
+      <c r="U753" t="inlineStr"/>
+      <c r="V753" t="inlineStr"/>
+      <c r="W753" t="inlineStr"/>
+      <c r="X753" t="inlineStr"/>
+      <c r="Y753" t="inlineStr"/>
+      <c r="Z753" t="inlineStr"/>
+      <c r="AA753" t="n">
+        <v>0.4906872207272</v>
+      </c>
+      <c r="AB753" t="n">
+        <v>42.49544</v>
+      </c>
+      <c r="AC753" t="n">
+        <v>14.1418492887144</v>
+      </c>
+      <c r="AD753" t="n">
+        <v>0.08862392499999999</v>
+      </c>
+      <c r="AE753" t="n">
+        <v>1638.330210755595</v>
+      </c>
+      <c r="AF753" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG753" t="n">
+        <v>0.016599998</v>
+      </c>
+      <c r="AH753" t="n">
+        <v>131.5051</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B754" t="n">
+        <v>0.4740136255</v>
+      </c>
+      <c r="C754" t="n">
+        <v>0.06083027100000001</v>
+      </c>
+      <c r="D754" t="inlineStr"/>
+      <c r="E754" t="inlineStr"/>
+      <c r="F754" t="inlineStr"/>
+      <c r="G754" t="inlineStr"/>
+      <c r="H754" t="inlineStr"/>
+      <c r="I754" t="n">
+        <v>0.029656683</v>
+      </c>
+      <c r="J754" t="inlineStr"/>
+      <c r="K754" t="n">
+        <v>1284.28437217591</v>
+      </c>
+      <c r="L754" t="inlineStr"/>
+      <c r="M754" t="inlineStr"/>
+      <c r="N754" t="inlineStr"/>
+      <c r="O754" t="n">
+        <v>153.0090274368</v>
+      </c>
+      <c r="P754" t="inlineStr"/>
+      <c r="Q754" t="n">
+        <v>6.696e-07</v>
+      </c>
+      <c r="R754" t="inlineStr"/>
+      <c r="S754" t="inlineStr"/>
+      <c r="T754" t="inlineStr"/>
+      <c r="U754" t="inlineStr"/>
+      <c r="V754" t="inlineStr"/>
+      <c r="W754" t="inlineStr"/>
+      <c r="X754" t="inlineStr"/>
+      <c r="Y754" t="inlineStr"/>
+      <c r="Z754" t="inlineStr"/>
+      <c r="AA754" t="n">
+        <v>0.4907068346824</v>
+      </c>
+      <c r="AB754" t="n">
+        <v>44.53904</v>
+      </c>
+      <c r="AC754" t="n">
+        <v>14.3840680512352</v>
+      </c>
+      <c r="AD754" t="n">
+        <v>0.093544945</v>
+      </c>
+      <c r="AE754" t="n">
+        <v>1635.430151011728</v>
+      </c>
+      <c r="AF754" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG754" t="n">
+        <v>0.016890319</v>
+      </c>
+      <c r="AH754" t="n">
+        <v>138.048</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH754"/>
+  <dimension ref="A1:AH756"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60057,6 +60057,138 @@
         <v>138.048</v>
       </c>
     </row>
+    <row r="755">
+      <c r="A755" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B755" t="n">
+        <v>0.4736710745</v>
+      </c>
+      <c r="C755" t="n">
+        <v>0.06057400350000001</v>
+      </c>
+      <c r="D755" t="inlineStr"/>
+      <c r="E755" t="inlineStr"/>
+      <c r="F755" t="inlineStr"/>
+      <c r="G755" t="inlineStr"/>
+      <c r="H755" t="inlineStr"/>
+      <c r="I755" t="n">
+        <v>0.02960794199999999</v>
+      </c>
+      <c r="J755" t="inlineStr"/>
+      <c r="K755" t="n">
+        <v>1277.802179761142</v>
+      </c>
+      <c r="L755" t="inlineStr"/>
+      <c r="M755" t="inlineStr"/>
+      <c r="N755" t="inlineStr"/>
+      <c r="O755" t="n">
+        <v>152.5215283894</v>
+      </c>
+      <c r="P755" t="inlineStr"/>
+      <c r="Q755" t="n">
+        <v>6.744000000000001e-07</v>
+      </c>
+      <c r="R755" t="inlineStr"/>
+      <c r="S755" t="inlineStr"/>
+      <c r="T755" t="inlineStr"/>
+      <c r="U755" t="inlineStr"/>
+      <c r="V755" t="inlineStr"/>
+      <c r="W755" t="inlineStr"/>
+      <c r="X755" t="inlineStr"/>
+      <c r="Y755" t="inlineStr"/>
+      <c r="Z755" t="inlineStr"/>
+      <c r="AA755" t="n">
+        <v>0.490495984664</v>
+      </c>
+      <c r="AB755" t="n">
+        <v>42.84383999999999</v>
+      </c>
+      <c r="AC755" t="n">
+        <v>14.1418492887144</v>
+      </c>
+      <c r="AD755" t="n">
+        <v>0.09213242999999999</v>
+      </c>
+      <c r="AE755" t="n">
+        <v>1623.716908487321</v>
+      </c>
+      <c r="AF755" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG755" t="n">
+        <v>0.017128939</v>
+      </c>
+      <c r="AH755" t="n">
+        <v>135.2439</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B756" t="n">
+        <v>0.4802121745</v>
+      </c>
+      <c r="C756" t="n">
+        <v>0.06111089300000001</v>
+      </c>
+      <c r="D756" t="inlineStr"/>
+      <c r="E756" t="inlineStr"/>
+      <c r="F756" t="inlineStr"/>
+      <c r="G756" t="inlineStr"/>
+      <c r="H756" t="inlineStr"/>
+      <c r="I756" t="n">
+        <v>0.030547314</v>
+      </c>
+      <c r="J756" t="inlineStr"/>
+      <c r="K756" t="n">
+        <v>1285.094646227756</v>
+      </c>
+      <c r="L756" t="inlineStr"/>
+      <c r="M756" t="inlineStr"/>
+      <c r="N756" t="inlineStr"/>
+      <c r="O756" t="n">
+        <v>153.991603237</v>
+      </c>
+      <c r="P756" t="inlineStr"/>
+      <c r="Q756" t="n">
+        <v>6.864e-07</v>
+      </c>
+      <c r="R756" t="inlineStr"/>
+      <c r="S756" t="inlineStr"/>
+      <c r="T756" t="inlineStr"/>
+      <c r="U756" t="inlineStr"/>
+      <c r="V756" t="inlineStr"/>
+      <c r="W756" t="inlineStr"/>
+      <c r="X756" t="inlineStr"/>
+      <c r="Y756" t="inlineStr"/>
+      <c r="Z756" t="inlineStr"/>
+      <c r="AA756" t="n">
+        <v>0.4904518532648</v>
+      </c>
+      <c r="AB756" t="n">
+        <v>43.784</v>
+      </c>
+      <c r="AC756" t="n">
+        <v>15.1666209763024</v>
+      </c>
+      <c r="AD756" t="n">
+        <v>0.09509415499999999</v>
+      </c>
+      <c r="AE756" t="n">
+        <v>1633.736817558223</v>
+      </c>
+      <c r="AF756" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG756" t="n">
+        <v>0.017630041</v>
+      </c>
+      <c r="AH756" t="n">
+        <v>134.5249</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH756"/>
+  <dimension ref="A1:AH759"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59049,7 +59049,9 @@
       <c r="AA739" t="n">
         <v>0.0284703651999</v>
       </c>
-      <c r="AB739" t="inlineStr"/>
+      <c r="AB739" t="n">
+        <v>0</v>
+      </c>
       <c r="AC739" t="n">
         <v>15.8001162013568</v>
       </c>
@@ -59065,7 +59067,9 @@
       <c r="AG739" t="n">
         <v>32.91767846899999</v>
       </c>
-      <c r="AH739" t="inlineStr"/>
+      <c r="AH739" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="740">
       <c r="A740" s="2" t="n">
@@ -59385,7 +59389,7 @@
         <v>0.13386997</v>
       </c>
       <c r="AE744" t="n">
-        <v>1815.204741130006</v>
+        <v>1815.204741130007</v>
       </c>
       <c r="AF744" t="n">
         <v>0</v>
@@ -60189,6 +60193,204 @@
         <v>134.5249</v>
       </c>
     </row>
+    <row r="757">
+      <c r="A757" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B757" t="n">
+        <v>0.4898110525</v>
+      </c>
+      <c r="C757" t="n">
+        <v>0.06272628700000001</v>
+      </c>
+      <c r="D757" t="inlineStr"/>
+      <c r="E757" t="inlineStr"/>
+      <c r="F757" t="inlineStr"/>
+      <c r="G757" t="inlineStr"/>
+      <c r="H757" t="inlineStr"/>
+      <c r="I757" t="n">
+        <v>0.031584168</v>
+      </c>
+      <c r="J757" t="inlineStr"/>
+      <c r="K757" t="n">
+        <v>1303.730949420214</v>
+      </c>
+      <c r="L757" t="inlineStr"/>
+      <c r="M757" t="inlineStr"/>
+      <c r="N757" t="inlineStr"/>
+      <c r="O757" t="n">
+        <v>155.7950971222</v>
+      </c>
+      <c r="P757" t="inlineStr"/>
+      <c r="Q757" t="n">
+        <v>7.007999999999999e-07</v>
+      </c>
+      <c r="R757" t="inlineStr"/>
+      <c r="S757" t="inlineStr"/>
+      <c r="T757" t="inlineStr"/>
+      <c r="U757" t="inlineStr"/>
+      <c r="V757" t="inlineStr"/>
+      <c r="W757" t="inlineStr"/>
+      <c r="X757" t="inlineStr"/>
+      <c r="Y757" t="inlineStr"/>
+      <c r="Z757" t="inlineStr"/>
+      <c r="AA757" t="n">
+        <v>0.4905155986192</v>
+      </c>
+      <c r="AB757" t="n">
+        <v>49.15456</v>
+      </c>
+      <c r="AC757" t="n">
+        <v>15.0361954887912</v>
+      </c>
+      <c r="AD757" t="n">
+        <v>0.09600545499999999</v>
+      </c>
+      <c r="AE757" t="n">
+        <v>1662.234504850124</v>
+      </c>
+      <c r="AF757" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG757" t="n">
+        <v>0.018059557</v>
+      </c>
+      <c r="AH757" t="n">
+        <v>137.329</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B758" t="n">
+        <v>0.494149113</v>
+      </c>
+      <c r="C758" t="n">
+        <v>0.06528932550000001</v>
+      </c>
+      <c r="D758" t="inlineStr"/>
+      <c r="E758" t="inlineStr"/>
+      <c r="F758" t="inlineStr"/>
+      <c r="G758" t="inlineStr"/>
+      <c r="H758" t="inlineStr"/>
+      <c r="I758" t="n">
+        <v>0.032780538</v>
+      </c>
+      <c r="J758" t="inlineStr"/>
+      <c r="K758" t="n">
+        <v>1289.956290538832</v>
+      </c>
+      <c r="L758" t="inlineStr"/>
+      <c r="M758" t="inlineStr"/>
+      <c r="N758" t="inlineStr"/>
+      <c r="O758" t="n">
+        <v>156.0678945166</v>
+      </c>
+      <c r="P758" t="inlineStr"/>
+      <c r="Q758" t="n">
+        <v>7.056e-07</v>
+      </c>
+      <c r="R758" t="inlineStr"/>
+      <c r="S758" t="inlineStr"/>
+      <c r="T758" t="inlineStr"/>
+      <c r="U758" t="inlineStr"/>
+      <c r="V758" t="inlineStr"/>
+      <c r="W758" t="inlineStr"/>
+      <c r="X758" t="inlineStr"/>
+      <c r="Y758" t="inlineStr"/>
+      <c r="Z758" t="inlineStr"/>
+      <c r="AA758" t="n">
+        <v>0.490520502108</v>
+      </c>
+      <c r="AB758" t="n">
+        <v>53.94271999999999</v>
+      </c>
+      <c r="AC758" t="n">
+        <v>14.8312411512736</v>
+      </c>
+      <c r="AD758" t="n">
+        <v>0.10233899</v>
+      </c>
+      <c r="AE758" t="n">
+        <v>1669.579824132914</v>
+      </c>
+      <c r="AF758" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG758" t="n">
+        <v>0.018198752</v>
+      </c>
+      <c r="AH758" t="n">
+        <v>153.5784</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="2" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B759" t="n">
+        <v>0.4892788244999999</v>
+      </c>
+      <c r="C759" t="n">
+        <v>0.06517518650000001</v>
+      </c>
+      <c r="D759" t="inlineStr"/>
+      <c r="E759" t="inlineStr"/>
+      <c r="F759" t="inlineStr"/>
+      <c r="G759" t="inlineStr"/>
+      <c r="H759" t="inlineStr"/>
+      <c r="I759" t="n">
+        <v>0.03257671199999999</v>
+      </c>
+      <c r="J759" t="inlineStr"/>
+      <c r="K759" t="n">
+        <v>0</v>
+      </c>
+      <c r="L759" t="inlineStr"/>
+      <c r="M759" t="inlineStr"/>
+      <c r="N759" t="inlineStr"/>
+      <c r="O759" t="n">
+        <v>0</v>
+      </c>
+      <c r="P759" t="inlineStr"/>
+      <c r="Q759" t="n">
+        <v>7.08e-07</v>
+      </c>
+      <c r="R759" t="inlineStr"/>
+      <c r="S759" t="inlineStr"/>
+      <c r="T759" t="inlineStr"/>
+      <c r="U759" t="inlineStr"/>
+      <c r="V759" t="inlineStr"/>
+      <c r="W759" t="inlineStr"/>
+      <c r="X759" t="inlineStr"/>
+      <c r="Y759" t="inlineStr"/>
+      <c r="Z759" t="inlineStr"/>
+      <c r="AA759" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB759" t="n">
+        <v>52.52936</v>
+      </c>
+      <c r="AC759" t="n">
+        <v>15.557897438836</v>
+      </c>
+      <c r="AD759" t="n">
+        <v>0.097554665</v>
+      </c>
+      <c r="AE759" t="n">
+        <v>224.597314447836</v>
+      </c>
+      <c r="AF759" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG759" t="n">
+        <v>0.018170913</v>
+      </c>
+      <c r="AH759" t="n">
+        <v>155.8073</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -60345,13 +60345,13 @@
       </c>
       <c r="J759" t="inlineStr"/>
       <c r="K759" t="n">
-        <v>0</v>
+        <v>1284.689509201833</v>
       </c>
       <c r="L759" t="inlineStr"/>
       <c r="M759" t="inlineStr"/>
       <c r="N759" t="inlineStr"/>
       <c r="O759" t="n">
-        <v>0</v>
+        <v>152.8019034892</v>
       </c>
       <c r="P759" t="inlineStr"/>
       <c r="Q759" t="n">
@@ -60367,7 +60367,7 @@
       <c r="Y759" t="inlineStr"/>
       <c r="Z759" t="inlineStr"/>
       <c r="AA759" t="n">
-        <v>0</v>
+        <v>0.4906921242159999</v>
       </c>
       <c r="AB759" t="n">
         <v>52.52936</v>
@@ -60379,7 +60379,7 @@
         <v>0.097554665</v>
       </c>
       <c r="AE759" t="n">
-        <v>224.597314447836</v>
+        <v>1662.579419263085</v>
       </c>
       <c r="AF759" t="n">
         <v>0</v>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH759"/>
+  <dimension ref="A1:AH762"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59389,7 +59389,7 @@
         <v>0.13386997</v>
       </c>
       <c r="AE744" t="n">
-        <v>1815.204741130007</v>
+        <v>1815.204741130006</v>
       </c>
       <c r="AF744" t="n">
         <v>0</v>
@@ -60391,6 +60391,204 @@
         <v>155.8073</v>
       </c>
     </row>
+    <row r="760">
+      <c r="A760" s="2" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B760" t="n">
+        <v>0.48059503</v>
+      </c>
+      <c r="C760" t="n">
+        <v>0.06363431</v>
+      </c>
+      <c r="D760" t="inlineStr"/>
+      <c r="E760" t="inlineStr"/>
+      <c r="F760" t="inlineStr"/>
+      <c r="G760" t="inlineStr"/>
+      <c r="H760" t="inlineStr"/>
+      <c r="I760" t="n">
+        <v>0.031925355</v>
+      </c>
+      <c r="J760" t="inlineStr"/>
+      <c r="K760" t="n">
+        <v>1303.730949420214</v>
+      </c>
+      <c r="L760" t="inlineStr"/>
+      <c r="M760" t="inlineStr"/>
+      <c r="N760" t="inlineStr"/>
+      <c r="O760" t="n">
+        <v>151.9658299934</v>
+      </c>
+      <c r="P760" t="inlineStr"/>
+      <c r="Q760" t="n">
+        <v>7.08e-07</v>
+      </c>
+      <c r="R760" t="inlineStr"/>
+      <c r="S760" t="inlineStr"/>
+      <c r="T760" t="inlineStr"/>
+      <c r="U760" t="inlineStr"/>
+      <c r="V760" t="inlineStr"/>
+      <c r="W760" t="inlineStr"/>
+      <c r="X760" t="inlineStr"/>
+      <c r="Y760" t="inlineStr"/>
+      <c r="Z760" t="inlineStr"/>
+      <c r="AA760" t="n">
+        <v>0.4906577997943999</v>
+      </c>
+      <c r="AB760" t="n">
+        <v>49.63192</v>
+      </c>
+      <c r="AC760" t="n">
+        <v>15.3156786763152</v>
+      </c>
+      <c r="AD760" t="n">
+        <v>0.096825625</v>
+      </c>
+      <c r="AE760" t="n">
+        <v>1684.032281601723</v>
+      </c>
+      <c r="AF760" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG760" t="n">
+        <v>0.017864684</v>
+      </c>
+      <c r="AH760" t="n">
+        <v>162.2064</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="2" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B761" t="n">
+        <v>0.4690371745</v>
+      </c>
+      <c r="C761" t="n">
+        <v>0.0621988485</v>
+      </c>
+      <c r="D761" t="inlineStr"/>
+      <c r="E761" t="inlineStr"/>
+      <c r="F761" t="inlineStr"/>
+      <c r="G761" t="inlineStr"/>
+      <c r="H761" t="inlineStr"/>
+      <c r="I761" t="n">
+        <v>0.030888501</v>
+      </c>
+      <c r="J761" t="inlineStr"/>
+      <c r="K761" t="n">
+        <v>1299.679579160984</v>
+      </c>
+      <c r="L761" t="inlineStr"/>
+      <c r="M761" t="inlineStr"/>
+      <c r="N761" t="inlineStr"/>
+      <c r="O761" t="n">
+        <v>146.1183673264</v>
+      </c>
+      <c r="P761" t="inlineStr"/>
+      <c r="Q761" t="n">
+        <v>6.816e-07</v>
+      </c>
+      <c r="R761" t="inlineStr"/>
+      <c r="S761" t="inlineStr"/>
+      <c r="T761" t="inlineStr"/>
+      <c r="U761" t="inlineStr"/>
+      <c r="V761" t="inlineStr"/>
+      <c r="W761" t="inlineStr"/>
+      <c r="X761" t="inlineStr"/>
+      <c r="Y761" t="inlineStr"/>
+      <c r="Z761" t="inlineStr"/>
+      <c r="AA761" t="n">
+        <v>0.4907852905032</v>
+      </c>
+      <c r="AB761" t="n">
+        <v>47.40736</v>
+      </c>
+      <c r="AC761" t="n">
+        <v>14.533125751248</v>
+      </c>
+      <c r="AD761" t="n">
+        <v>0.090993305</v>
+      </c>
+      <c r="AE761" t="n">
+        <v>1677.505279161735</v>
+      </c>
+      <c r="AF761" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG761" t="n">
+        <v>0.017443122</v>
+      </c>
+      <c r="AH761" t="n">
+        <v>168.6055</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="2" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B762" t="n">
+        <v>0.4734021295</v>
+      </c>
+      <c r="C762" t="n">
+        <v>0.0622017565</v>
+      </c>
+      <c r="D762" t="inlineStr"/>
+      <c r="E762" t="inlineStr"/>
+      <c r="F762" t="inlineStr"/>
+      <c r="G762" t="inlineStr"/>
+      <c r="H762" t="inlineStr"/>
+      <c r="I762" t="n">
+        <v>0.030901794</v>
+      </c>
+      <c r="J762" t="inlineStr"/>
+      <c r="K762" t="n">
+        <v>1312.238826964597</v>
+      </c>
+      <c r="L762" t="inlineStr"/>
+      <c r="M762" t="inlineStr"/>
+      <c r="N762" t="inlineStr"/>
+      <c r="O762" t="n">
+        <v>146.8609824556</v>
+      </c>
+      <c r="P762" t="inlineStr"/>
+      <c r="Q762" t="n">
+        <v>6.768e-07</v>
+      </c>
+      <c r="R762" t="inlineStr"/>
+      <c r="S762" t="inlineStr"/>
+      <c r="T762" t="inlineStr"/>
+      <c r="U762" t="inlineStr"/>
+      <c r="V762" t="inlineStr"/>
+      <c r="W762" t="inlineStr"/>
+      <c r="X762" t="inlineStr"/>
+      <c r="Y762" t="inlineStr"/>
+      <c r="Z762" t="inlineStr"/>
+      <c r="AA762" t="n">
+        <v>0.4906823172384</v>
+      </c>
+      <c r="AB762" t="n">
+        <v>49.5872</v>
+      </c>
+      <c r="AC762" t="n">
+        <v>13.9927915887016</v>
+      </c>
+      <c r="AD762" t="n">
+        <v>0.09049209</v>
+      </c>
+      <c r="AE762" t="n">
+        <v>1680.802708411937</v>
+      </c>
+      <c r="AF762" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG762" t="n">
+        <v>0.017526639</v>
+      </c>
+      <c r="AH762" t="n">
+        <v>156.9577</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH762"/>
+  <dimension ref="A1:AH764"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59389,7 +59389,7 @@
         <v>0.13386997</v>
       </c>
       <c r="AE744" t="n">
-        <v>1815.204741130006</v>
+        <v>1815.204741130007</v>
       </c>
       <c r="AF744" t="n">
         <v>0</v>
@@ -60445,7 +60445,7 @@
         <v>0.096825625</v>
       </c>
       <c r="AE760" t="n">
-        <v>1684.032281601723</v>
+        <v>1684.032281601724</v>
       </c>
       <c r="AF760" t="n">
         <v>0</v>
@@ -60589,6 +60589,138 @@
         <v>156.9577</v>
       </c>
     </row>
+    <row r="763">
+      <c r="A763" s="2" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B763" t="n">
+        <v>0.4790201745</v>
+      </c>
+      <c r="C763" t="n">
+        <v>0.063288258</v>
+      </c>
+      <c r="D763" t="inlineStr"/>
+      <c r="E763" t="inlineStr"/>
+      <c r="F763" t="inlineStr"/>
+      <c r="G763" t="inlineStr"/>
+      <c r="H763" t="inlineStr"/>
+      <c r="I763" t="n">
+        <v>0.032443782</v>
+      </c>
+      <c r="J763" t="inlineStr"/>
+      <c r="K763" t="n">
+        <v>1323.987800716364</v>
+      </c>
+      <c r="L763" t="inlineStr"/>
+      <c r="M763" t="inlineStr"/>
+      <c r="N763" t="inlineStr"/>
+      <c r="O763" t="n">
+        <v>148.5306035454</v>
+      </c>
+      <c r="P763" t="inlineStr"/>
+      <c r="Q763" t="n">
+        <v>6.792e-07</v>
+      </c>
+      <c r="R763" t="inlineStr"/>
+      <c r="S763" t="inlineStr"/>
+      <c r="T763" t="inlineStr"/>
+      <c r="U763" t="inlineStr"/>
+      <c r="V763" t="inlineStr"/>
+      <c r="W763" t="inlineStr"/>
+      <c r="X763" t="inlineStr"/>
+      <c r="Y763" t="inlineStr"/>
+      <c r="Z763" t="inlineStr"/>
+      <c r="AA763" t="n">
+        <v>0.4908049044584</v>
+      </c>
+      <c r="AB763" t="n">
+        <v>48.97776</v>
+      </c>
+      <c r="AC763" t="n">
+        <v>13.8064694636856</v>
+      </c>
+      <c r="AD763" t="n">
+        <v>0.091175565</v>
+      </c>
+      <c r="AE763" t="n">
+        <v>1691.924876669608</v>
+      </c>
+      <c r="AF763" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG763" t="n">
+        <v>0.017709581</v>
+      </c>
+      <c r="AH763" t="n">
+        <v>155.4478</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B764" t="n">
+        <v>0.4716743255</v>
+      </c>
+      <c r="C764" t="n">
+        <v>0.06204726900000001</v>
+      </c>
+      <c r="D764" t="inlineStr"/>
+      <c r="E764" t="inlineStr"/>
+      <c r="F764" t="inlineStr"/>
+      <c r="G764" t="inlineStr"/>
+      <c r="H764" t="inlineStr"/>
+      <c r="I764" t="n">
+        <v>0.032107026</v>
+      </c>
+      <c r="J764" t="inlineStr"/>
+      <c r="K764" t="n">
+        <v>1328.039170975594</v>
+      </c>
+      <c r="L764" t="inlineStr"/>
+      <c r="M764" t="inlineStr"/>
+      <c r="N764" t="inlineStr"/>
+      <c r="O764" t="n">
+        <v>147.5707608614</v>
+      </c>
+      <c r="P764" t="inlineStr"/>
+      <c r="Q764" t="n">
+        <v>6.671999999999999e-07</v>
+      </c>
+      <c r="R764" t="inlineStr"/>
+      <c r="S764" t="inlineStr"/>
+      <c r="T764" t="inlineStr"/>
+      <c r="U764" t="inlineStr"/>
+      <c r="V764" t="inlineStr"/>
+      <c r="W764" t="inlineStr"/>
+      <c r="X764" t="inlineStr"/>
+      <c r="Y764" t="inlineStr"/>
+      <c r="Z764" t="inlineStr"/>
+      <c r="AA764" t="n">
+        <v>0.4908196149248</v>
+      </c>
+      <c r="AB764" t="n">
+        <v>45.17655999999999</v>
+      </c>
+      <c r="AC764" t="n">
+        <v>13.7319406136792</v>
+      </c>
+      <c r="AD764" t="n">
+        <v>0.088806185</v>
+      </c>
+      <c r="AE764" t="n">
+        <v>1686.527773257298</v>
+      </c>
+      <c r="AF764" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG764" t="n">
+        <v>0.017685719</v>
+      </c>
+      <c r="AH764" t="n">
+        <v>150.8462</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH764"/>
+  <dimension ref="A1:AH766"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59389,7 +59389,7 @@
         <v>0.13386997</v>
       </c>
       <c r="AE744" t="n">
-        <v>1815.204741130007</v>
+        <v>1815.204741130006</v>
       </c>
       <c r="AF744" t="n">
         <v>0</v>
@@ -60721,6 +60721,138 @@
         <v>150.8462</v>
       </c>
     </row>
+    <row r="765">
+      <c r="A765" s="2" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B765" t="n">
+        <v>0.4769490745</v>
+      </c>
+      <c r="C765" t="n">
+        <v>0.0628197065</v>
+      </c>
+      <c r="D765" t="inlineStr"/>
+      <c r="E765" t="inlineStr"/>
+      <c r="F765" t="inlineStr"/>
+      <c r="G765" t="inlineStr"/>
+      <c r="H765" t="inlineStr"/>
+      <c r="I765" t="n">
+        <v>0.031881045</v>
+      </c>
+      <c r="J765" t="inlineStr"/>
+      <c r="K765" t="n">
+        <v>1353.562803608743</v>
+      </c>
+      <c r="L765" t="inlineStr"/>
+      <c r="M765" t="inlineStr"/>
+      <c r="N765" t="inlineStr"/>
+      <c r="O765" t="n">
+        <v>149.066094727</v>
+      </c>
+      <c r="P765" t="inlineStr"/>
+      <c r="Q765" t="n">
+        <v>6.744000000000001e-07</v>
+      </c>
+      <c r="R765" t="inlineStr"/>
+      <c r="S765" t="inlineStr"/>
+      <c r="T765" t="inlineStr"/>
+      <c r="U765" t="inlineStr"/>
+      <c r="V765" t="inlineStr"/>
+      <c r="W765" t="inlineStr"/>
+      <c r="X765" t="inlineStr"/>
+      <c r="Y765" t="inlineStr"/>
+      <c r="Z765" t="inlineStr"/>
+      <c r="AA765" t="n">
+        <v>0.4907705800368</v>
+      </c>
+      <c r="AB765" t="n">
+        <v>45.99608</v>
+      </c>
+      <c r="AC765" t="n">
+        <v>13.8437338886888</v>
+      </c>
+      <c r="AD765" t="n">
+        <v>0.09008200499999999</v>
+      </c>
+      <c r="AE765" t="n">
+        <v>1709.524036821868</v>
+      </c>
+      <c r="AF765" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG765" t="n">
+        <v>0.017721512</v>
+      </c>
+      <c r="AH765" t="n">
+        <v>145.8851</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="2" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B766" t="n">
+        <v>0.4673725465</v>
+      </c>
+      <c r="C766" t="n">
+        <v>0.06060017550000001</v>
+      </c>
+      <c r="D766" t="inlineStr"/>
+      <c r="E766" t="inlineStr"/>
+      <c r="F766" t="inlineStr"/>
+      <c r="G766" t="inlineStr"/>
+      <c r="H766" t="inlineStr"/>
+      <c r="I766" t="n">
+        <v>0.030888501</v>
+      </c>
+      <c r="J766" t="inlineStr"/>
+      <c r="K766" t="n">
+        <v>1334.116226364439</v>
+      </c>
+      <c r="L766" t="inlineStr"/>
+      <c r="M766" t="inlineStr"/>
+      <c r="N766" t="inlineStr"/>
+      <c r="O766" t="n">
+        <v>146.0173312544</v>
+      </c>
+      <c r="P766" t="inlineStr"/>
+      <c r="Q766" t="n">
+        <v>6.48e-07</v>
+      </c>
+      <c r="R766" t="inlineStr"/>
+      <c r="S766" t="inlineStr"/>
+      <c r="T766" t="inlineStr"/>
+      <c r="U766" t="inlineStr"/>
+      <c r="V766" t="inlineStr"/>
+      <c r="W766" t="inlineStr"/>
+      <c r="X766" t="inlineStr"/>
+      <c r="Y766" t="inlineStr"/>
+      <c r="Z766" t="inlineStr"/>
+      <c r="AA766" t="n">
+        <v>0.4908196149248</v>
+      </c>
+      <c r="AB766" t="n">
+        <v>43.27231999999999</v>
+      </c>
+      <c r="AC766" t="n">
+        <v>13.135709813628</v>
+      </c>
+      <c r="AD766" t="n">
+        <v>0.08866948999999999</v>
+      </c>
+      <c r="AE766" t="n">
+        <v>1678.045509417392</v>
+      </c>
+      <c r="AF766" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG766" t="n">
+        <v>0.016771009</v>
+      </c>
+      <c r="AH766" t="n">
+        <v>140.3488</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH766"/>
+  <dimension ref="A1:AH767"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60853,6 +60853,72 @@
         <v>140.3488</v>
       </c>
     </row>
+    <row r="767">
+      <c r="A767" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B767" t="n">
+        <v>0.4550310255</v>
+      </c>
+      <c r="C767" t="n">
+        <v>0.05896587950000001</v>
+      </c>
+      <c r="D767" t="inlineStr"/>
+      <c r="E767" t="inlineStr"/>
+      <c r="F767" t="inlineStr"/>
+      <c r="G767" t="inlineStr"/>
+      <c r="H767" t="inlineStr"/>
+      <c r="I767" t="n">
+        <v>0.030179541</v>
+      </c>
+      <c r="J767" t="inlineStr"/>
+      <c r="K767" t="n">
+        <v>1326.418622871902</v>
+      </c>
+      <c r="L767" t="inlineStr"/>
+      <c r="M767" t="inlineStr"/>
+      <c r="N767" t="inlineStr"/>
+      <c r="O767" t="n">
+        <v>142.6300969406</v>
+      </c>
+      <c r="P767" t="inlineStr"/>
+      <c r="Q767" t="n">
+        <v>6.072e-07</v>
+      </c>
+      <c r="R767" t="inlineStr"/>
+      <c r="S767" t="inlineStr"/>
+      <c r="T767" t="inlineStr"/>
+      <c r="U767" t="inlineStr"/>
+      <c r="V767" t="inlineStr"/>
+      <c r="W767" t="inlineStr"/>
+      <c r="X767" t="inlineStr"/>
+      <c r="Y767" t="inlineStr"/>
+      <c r="Z767" t="inlineStr"/>
+      <c r="AA767" t="n">
+        <v>0.4909814300552</v>
+      </c>
+      <c r="AB767" t="n">
+        <v>43.3524</v>
+      </c>
+      <c r="AC767" t="n">
+        <v>12.483582376072</v>
+      </c>
+      <c r="AD767" t="n">
+        <v>0.08675576</v>
+      </c>
+      <c r="AE767" t="n">
+        <v>1659.397497694829</v>
+      </c>
+      <c r="AF767" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG767" t="n">
+        <v>0.016381263</v>
+      </c>
+      <c r="AH767" t="n">
+        <v>133.3745</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH767"/>
+  <dimension ref="A1:AH769"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59389,7 +59389,7 @@
         <v>0.13386997</v>
       </c>
       <c r="AE744" t="n">
-        <v>1815.204741130006</v>
+        <v>1815.204741130007</v>
       </c>
       <c r="AF744" t="n">
         <v>0</v>
@@ -60919,6 +60919,138 @@
         <v>133.3745</v>
       </c>
     </row>
+    <row r="768">
+      <c r="A768" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B768" t="n">
+        <v>0.4454653</v>
+      </c>
+      <c r="C768" t="n">
+        <v>0.056990984</v>
+      </c>
+      <c r="D768" t="inlineStr"/>
+      <c r="E768" t="inlineStr"/>
+      <c r="F768" t="inlineStr"/>
+      <c r="G768" t="inlineStr"/>
+      <c r="H768" t="inlineStr"/>
+      <c r="I768" t="n">
+        <v>0.030006732</v>
+      </c>
+      <c r="J768" t="inlineStr"/>
+      <c r="K768" t="n">
+        <v>1311.833689938674</v>
+      </c>
+      <c r="L768" t="inlineStr"/>
+      <c r="M768" t="inlineStr"/>
+      <c r="N768" t="inlineStr"/>
+      <c r="O768" t="n">
+        <v>141.6071067116</v>
+      </c>
+      <c r="P768" t="inlineStr"/>
+      <c r="Q768" t="n">
+        <v>5.664e-07</v>
+      </c>
+      <c r="R768" t="inlineStr"/>
+      <c r="S768" t="inlineStr"/>
+      <c r="T768" t="inlineStr"/>
+      <c r="U768" t="inlineStr"/>
+      <c r="V768" t="inlineStr"/>
+      <c r="W768" t="inlineStr"/>
+      <c r="X768" t="inlineStr"/>
+      <c r="Y768" t="inlineStr"/>
+      <c r="Z768" t="inlineStr"/>
+      <c r="AA768" t="n">
+        <v>0.4909176847008</v>
+      </c>
+      <c r="AB768" t="n">
+        <v>43.342</v>
+      </c>
+      <c r="AC768" t="n">
+        <v>12.5022145885736</v>
+      </c>
+      <c r="AD768" t="n">
+        <v>0.087986015</v>
+      </c>
+      <c r="AE768" t="n">
+        <v>1639.041752404949</v>
+      </c>
+      <c r="AF768" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG768" t="n">
+        <v>0.016273884</v>
+      </c>
+      <c r="AH768" t="n">
+        <v>128.6291</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="2" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B769" t="n">
+        <v>0.4477246615</v>
+      </c>
+      <c r="C769" t="n">
+        <v>0.05738501800000001</v>
+      </c>
+      <c r="D769" t="inlineStr"/>
+      <c r="E769" t="inlineStr"/>
+      <c r="F769" t="inlineStr"/>
+      <c r="G769" t="inlineStr"/>
+      <c r="H769" t="inlineStr"/>
+      <c r="I769" t="n">
+        <v>0.03185889</v>
+      </c>
+      <c r="J769" t="inlineStr"/>
+      <c r="K769" t="n">
+        <v>1298.869305109138</v>
+      </c>
+      <c r="L769" t="inlineStr"/>
+      <c r="M769" t="inlineStr"/>
+      <c r="N769" t="inlineStr"/>
+      <c r="O769" t="n">
+        <v>143.3802897752</v>
+      </c>
+      <c r="P769" t="inlineStr"/>
+      <c r="Q769" t="n">
+        <v>5.736e-07</v>
+      </c>
+      <c r="R769" t="inlineStr"/>
+      <c r="S769" t="inlineStr"/>
+      <c r="T769" t="inlineStr"/>
+      <c r="U769" t="inlineStr"/>
+      <c r="V769" t="inlineStr"/>
+      <c r="W769" t="inlineStr"/>
+      <c r="X769" t="inlineStr"/>
+      <c r="Y769" t="inlineStr"/>
+      <c r="Z769" t="inlineStr"/>
+      <c r="AA769" t="n">
+        <v>0.4908784567904</v>
+      </c>
+      <c r="AB769" t="n">
+        <v>43.60408</v>
+      </c>
+      <c r="AC769" t="n">
+        <v>12.3531568885608</v>
+      </c>
+      <c r="AD769" t="n">
+        <v>0.089899745</v>
+      </c>
+      <c r="AE769" t="n">
+        <v>1627.251346724789</v>
+      </c>
+      <c r="AF769" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG769" t="n">
+        <v>0.016667607</v>
+      </c>
+      <c r="AH769" t="n">
+        <v>127.9101</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH769"/>
+  <dimension ref="A1:AH772"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59389,7 +59389,7 @@
         <v>0.13386997</v>
       </c>
       <c r="AE744" t="n">
-        <v>1815.204741130007</v>
+        <v>1815.204741130006</v>
       </c>
       <c r="AF744" t="n">
         <v>0</v>
@@ -59457,9 +59457,7 @@
       <c r="AE745" t="n">
         <v>1751.636563957452</v>
       </c>
-      <c r="AF745" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF745" t="inlineStr"/>
       <c r="AG745" t="n">
         <v>0.018656107</v>
       </c>
@@ -59523,9 +59521,7 @@
       <c r="AE746" t="n">
         <v>1738.275615115099</v>
       </c>
-      <c r="AF746" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF746" t="inlineStr"/>
       <c r="AG746" t="n">
         <v>0.018747578</v>
       </c>
@@ -59655,9 +59651,7 @@
       <c r="AE748" t="n">
         <v>1642.790060078056</v>
       </c>
-      <c r="AF748" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF748" t="inlineStr"/>
       <c r="AG748" t="n">
         <v>0.017228364</v>
       </c>
@@ -59919,9 +59913,7 @@
       <c r="AE752" t="n">
         <v>1655.485095179058</v>
       </c>
-      <c r="AF752" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF752" t="inlineStr"/>
       <c r="AG752" t="n">
         <v>0.017113031</v>
       </c>
@@ -59985,9 +59977,7 @@
       <c r="AE753" t="n">
         <v>1638.330210755595</v>
       </c>
-      <c r="AF753" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF753" t="inlineStr"/>
       <c r="AG753" t="n">
         <v>0.016599998</v>
       </c>
@@ -60249,9 +60239,7 @@
       <c r="AE757" t="n">
         <v>1662.234504850124</v>
       </c>
-      <c r="AF757" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF757" t="inlineStr"/>
       <c r="AG757" t="n">
         <v>0.018059557</v>
       </c>
@@ -60381,9 +60369,7 @@
       <c r="AE759" t="n">
         <v>1662.579419263085</v>
       </c>
-      <c r="AF759" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF759" t="inlineStr"/>
       <c r="AG759" t="n">
         <v>0.018170913</v>
       </c>
@@ -60711,9 +60697,7 @@
       <c r="AE764" t="n">
         <v>1686.527773257298</v>
       </c>
-      <c r="AF764" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF764" t="inlineStr"/>
       <c r="AG764" t="n">
         <v>0.017685719</v>
       </c>
@@ -60975,9 +60959,7 @@
       <c r="AE768" t="n">
         <v>1639.041752404949</v>
       </c>
-      <c r="AF768" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF768" t="inlineStr"/>
       <c r="AG768" t="n">
         <v>0.016273884</v>
       </c>
@@ -61051,6 +61033,198 @@
         <v>127.9101</v>
       </c>
     </row>
+    <row r="770">
+      <c r="A770" s="2" t="n">
+        <v>46200</v>
+      </c>
+      <c r="B770" t="n">
+        <v>0.44721605</v>
+      </c>
+      <c r="C770" t="n">
+        <v>0.0572145365</v>
+      </c>
+      <c r="D770" t="inlineStr"/>
+      <c r="E770" t="inlineStr"/>
+      <c r="F770" t="inlineStr"/>
+      <c r="G770" t="inlineStr"/>
+      <c r="H770" t="inlineStr"/>
+      <c r="I770" t="n">
+        <v>0.03123855</v>
+      </c>
+      <c r="J770" t="inlineStr"/>
+      <c r="K770" t="n">
+        <v>1301.705264290599</v>
+      </c>
+      <c r="L770" t="inlineStr"/>
+      <c r="M770" t="inlineStr"/>
+      <c r="N770" t="inlineStr"/>
+      <c r="O770" t="n">
+        <v>140.743248296</v>
+      </c>
+      <c r="P770" t="inlineStr"/>
+      <c r="Q770" t="n">
+        <v>5.712e-07</v>
+      </c>
+      <c r="R770" t="inlineStr"/>
+      <c r="S770" t="inlineStr"/>
+      <c r="T770" t="inlineStr"/>
+      <c r="U770" t="inlineStr"/>
+      <c r="V770" t="inlineStr"/>
+      <c r="W770" t="inlineStr"/>
+      <c r="X770" t="inlineStr"/>
+      <c r="Y770" t="inlineStr"/>
+      <c r="Z770" t="inlineStr"/>
+      <c r="AA770" t="n">
+        <v>0.4909176847008</v>
+      </c>
+      <c r="AB770" t="n">
+        <v>41.16944</v>
+      </c>
+      <c r="AC770" t="n">
+        <v>12.5394790135768</v>
+      </c>
+      <c r="AD770" t="n">
+        <v>0.08907957499999999</v>
+      </c>
+      <c r="AE770" t="n">
+        <v>1622.395869576577</v>
+      </c>
+      <c r="AF770" t="inlineStr"/>
+      <c r="AG770" t="n">
+        <v>0.016771009</v>
+      </c>
+      <c r="AH770" t="n">
+        <v>125.106</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B771" t="n">
+        <v>0.4438487245</v>
+      </c>
+      <c r="C771" t="n">
+        <v>0.05714074600000001</v>
+      </c>
+      <c r="D771" t="inlineStr"/>
+      <c r="E771" t="inlineStr"/>
+      <c r="F771" t="inlineStr"/>
+      <c r="G771" t="inlineStr"/>
+      <c r="H771" t="inlineStr"/>
+      <c r="I771" t="n">
+        <v>0.03162847799999999</v>
+      </c>
+      <c r="J771" t="inlineStr"/>
+      <c r="K771" t="n">
+        <v>1305.351497523906</v>
+      </c>
+      <c r="L771" t="inlineStr"/>
+      <c r="M771" t="inlineStr"/>
+      <c r="N771" t="inlineStr"/>
+      <c r="O771" t="n">
+        <v>139.1948704926</v>
+      </c>
+      <c r="P771" t="inlineStr"/>
+      <c r="Q771" t="n">
+        <v>5.664e-07</v>
+      </c>
+      <c r="R771" t="inlineStr"/>
+      <c r="S771" t="inlineStr"/>
+      <c r="T771" t="inlineStr"/>
+      <c r="U771" t="inlineStr"/>
+      <c r="V771" t="inlineStr"/>
+      <c r="W771" t="inlineStr"/>
+      <c r="X771" t="inlineStr"/>
+      <c r="Y771" t="inlineStr"/>
+      <c r="Z771" t="inlineStr"/>
+      <c r="AA771" t="n">
+        <v>0.4909225881895999</v>
+      </c>
+      <c r="AB771" t="n">
+        <v>39.14664</v>
+      </c>
+      <c r="AC771" t="n">
+        <v>12.4463179510688</v>
+      </c>
+      <c r="AD771" t="n">
+        <v>0.08702915</v>
+      </c>
+      <c r="AE771" t="n">
+        <v>1621.653810401664</v>
+      </c>
+      <c r="AF771" t="inlineStr"/>
+      <c r="AG771" t="n">
+        <v>0.016914181</v>
+      </c>
+      <c r="AH771" t="n">
+        <v>124.387</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="2" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B772" t="n">
+        <v>0.4489385645</v>
+      </c>
+      <c r="C772" t="n">
+        <v>0.05863509450000001</v>
+      </c>
+      <c r="D772" t="inlineStr"/>
+      <c r="E772" t="inlineStr"/>
+      <c r="F772" t="inlineStr"/>
+      <c r="G772" t="inlineStr"/>
+      <c r="H772" t="inlineStr"/>
+      <c r="I772" t="n">
+        <v>0.033303396</v>
+      </c>
+      <c r="J772" t="inlineStr"/>
+      <c r="K772" t="n">
+        <v>1302.110401316522</v>
+      </c>
+      <c r="L772" t="inlineStr"/>
+      <c r="M772" t="inlineStr"/>
+      <c r="N772" t="inlineStr"/>
+      <c r="O772" t="n">
+        <v>141.3292575136</v>
+      </c>
+      <c r="P772" t="inlineStr"/>
+      <c r="Q772" t="n">
+        <v>5.664e-07</v>
+      </c>
+      <c r="R772" t="inlineStr"/>
+      <c r="S772" t="inlineStr"/>
+      <c r="T772" t="inlineStr"/>
+      <c r="U772" t="inlineStr"/>
+      <c r="V772" t="inlineStr"/>
+      <c r="W772" t="inlineStr"/>
+      <c r="X772" t="inlineStr"/>
+      <c r="Y772" t="inlineStr"/>
+      <c r="Z772" t="inlineStr"/>
+      <c r="AA772" t="n">
+        <v>0.4908686498128</v>
+      </c>
+      <c r="AB772" t="n">
+        <v>42.38</v>
+      </c>
+      <c r="AC772" t="n">
+        <v>12.4090535260656</v>
+      </c>
+      <c r="AD772" t="n">
+        <v>0.09167678</v>
+      </c>
+      <c r="AE772" t="n">
+        <v>1625.266216047401</v>
+      </c>
+      <c r="AF772" t="inlineStr"/>
+      <c r="AG772" t="n">
+        <v>0.01718064</v>
+      </c>
+      <c r="AH772" t="n">
+        <v>125.8969</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH772"/>
+  <dimension ref="A1:AH773"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59585,9 +59585,7 @@
       <c r="AE747" t="n">
         <v>1707.730154736133</v>
       </c>
-      <c r="AF747" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF747" t="inlineStr"/>
       <c r="AG747" t="n">
         <v>0.018151028</v>
       </c>
@@ -59715,9 +59713,7 @@
       <c r="AE749" t="n">
         <v>1662.835131102286</v>
       </c>
-      <c r="AF749" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF749" t="inlineStr"/>
       <c r="AG749" t="n">
         <v>0.016460803</v>
       </c>
@@ -59847,9 +59843,7 @@
       <c r="AE751" t="n">
         <v>1684.242656113659</v>
       </c>
-      <c r="AF751" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF751" t="inlineStr"/>
       <c r="AG751" t="n">
         <v>0.017113031</v>
       </c>
@@ -60041,9 +60035,7 @@
       <c r="AE754" t="n">
         <v>1635.430151011728</v>
       </c>
-      <c r="AF754" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF754" t="inlineStr"/>
       <c r="AG754" t="n">
         <v>0.016890319</v>
       </c>
@@ -60173,9 +60165,7 @@
       <c r="AE756" t="n">
         <v>1633.736817558223</v>
       </c>
-      <c r="AF756" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF756" t="inlineStr"/>
       <c r="AG756" t="n">
         <v>0.017630041</v>
       </c>
@@ -60499,9 +60489,7 @@
       <c r="AE761" t="n">
         <v>1677.505279161735</v>
       </c>
-      <c r="AF761" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF761" t="inlineStr"/>
       <c r="AG761" t="n">
         <v>0.017443122</v>
       </c>
@@ -60631,9 +60619,7 @@
       <c r="AE763" t="n">
         <v>1691.924876669608</v>
       </c>
-      <c r="AF763" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF763" t="inlineStr"/>
       <c r="AG763" t="n">
         <v>0.017709581</v>
       </c>
@@ -60893,9 +60879,7 @@
       <c r="AE767" t="n">
         <v>1659.397497694829</v>
       </c>
-      <c r="AF767" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF767" t="inlineStr"/>
       <c r="AG767" t="n">
         <v>0.016381263</v>
       </c>
@@ -61225,6 +61209,70 @@
         <v>125.8969</v>
       </c>
     </row>
+    <row r="773">
+      <c r="A773" s="2" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B773" t="n">
+        <v>0.4367540895</v>
+      </c>
+      <c r="C773" t="n">
+        <v>0.05714256350000001</v>
+      </c>
+      <c r="D773" t="inlineStr"/>
+      <c r="E773" t="inlineStr"/>
+      <c r="F773" t="inlineStr"/>
+      <c r="G773" t="inlineStr"/>
+      <c r="H773" t="inlineStr"/>
+      <c r="I773" t="n">
+        <v>0.032643177</v>
+      </c>
+      <c r="J773" t="inlineStr"/>
+      <c r="K773" t="n">
+        <v>1547.887942030719</v>
+      </c>
+      <c r="L773" t="inlineStr"/>
+      <c r="M773" t="inlineStr"/>
+      <c r="N773" t="inlineStr"/>
+      <c r="O773" t="n">
+        <v>0.1298968736</v>
+      </c>
+      <c r="P773" t="inlineStr"/>
+      <c r="Q773" t="n">
+        <v>5.592e-07</v>
+      </c>
+      <c r="R773" t="inlineStr"/>
+      <c r="S773" t="inlineStr"/>
+      <c r="T773" t="inlineStr"/>
+      <c r="U773" t="inlineStr"/>
+      <c r="V773" t="inlineStr"/>
+      <c r="W773" t="inlineStr"/>
+      <c r="X773" t="inlineStr"/>
+      <c r="Y773" t="inlineStr"/>
+      <c r="Z773" t="inlineStr"/>
+      <c r="AA773" t="n">
+        <v>0.0238956131456</v>
+      </c>
+      <c r="AB773" t="n">
+        <v>41.54799999999999</v>
+      </c>
+      <c r="AC773" t="n">
+        <v>12.204099188548</v>
+      </c>
+      <c r="AD773" t="n">
+        <v>0.09113</v>
+      </c>
+      <c r="AE773" t="n">
+        <v>1602.428179656213</v>
+      </c>
+      <c r="AF773" t="inlineStr"/>
+      <c r="AG773" t="n">
+        <v>0.016675561</v>
+      </c>
+      <c r="AH773" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH773"/>
+  <dimension ref="A1:AH776"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59777,9 +59777,7 @@
       <c r="AE750" t="n">
         <v>1685.50951593847</v>
       </c>
-      <c r="AF750" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF750" t="inlineStr"/>
       <c r="AG750" t="n">
         <v>0.017033491</v>
       </c>
@@ -61273,6 +61271,198 @@
         <v>0</v>
       </c>
     </row>
+    <row r="774">
+      <c r="A774" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B774" t="n">
+        <v>0.4471788</v>
+      </c>
+      <c r="C774" t="n">
+        <v>0.058508233</v>
+      </c>
+      <c r="D774" t="inlineStr"/>
+      <c r="E774" t="inlineStr"/>
+      <c r="F774" t="inlineStr"/>
+      <c r="G774" t="inlineStr"/>
+      <c r="H774" t="inlineStr"/>
+      <c r="I774" t="n">
+        <v>0.034322526</v>
+      </c>
+      <c r="J774" t="inlineStr"/>
+      <c r="K774" t="n">
+        <v>1551.815345626103</v>
+      </c>
+      <c r="L774" t="inlineStr"/>
+      <c r="M774" t="inlineStr"/>
+      <c r="N774" t="inlineStr"/>
+      <c r="O774" t="n">
+        <v>0.1308285792</v>
+      </c>
+      <c r="P774" t="inlineStr"/>
+      <c r="Q774" t="n">
+        <v>5.592e-07</v>
+      </c>
+      <c r="R774" t="inlineStr"/>
+      <c r="S774" t="inlineStr"/>
+      <c r="T774" t="inlineStr"/>
+      <c r="U774" t="inlineStr"/>
+      <c r="V774" t="inlineStr"/>
+      <c r="W774" t="inlineStr"/>
+      <c r="X774" t="inlineStr"/>
+      <c r="Y774" t="inlineStr"/>
+      <c r="Z774" t="inlineStr"/>
+      <c r="AA774" t="n">
+        <v>0.02388678166</v>
+      </c>
+      <c r="AB774" t="n">
+        <v>43.38983999999999</v>
+      </c>
+      <c r="AC774" t="n">
+        <v>12.2599958260528</v>
+      </c>
+      <c r="AD774" t="n">
+        <v>0.09573206499999999</v>
+      </c>
+      <c r="AE774" t="n">
+        <v>1608.272624763216</v>
+      </c>
+      <c r="AF774" t="inlineStr"/>
+      <c r="AG774" t="n">
+        <v>0.016985767</v>
+      </c>
+      <c r="AH774" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B775" t="n">
+        <v>0.458622</v>
+      </c>
+      <c r="C775" t="n">
+        <v>0.0618157195</v>
+      </c>
+      <c r="D775" t="inlineStr"/>
+      <c r="E775" t="inlineStr"/>
+      <c r="F775" t="inlineStr"/>
+      <c r="G775" t="inlineStr"/>
+      <c r="H775" t="inlineStr"/>
+      <c r="I775" t="n">
+        <v>0.035771463</v>
+      </c>
+      <c r="J775" t="inlineStr"/>
+      <c r="K775" t="n">
+        <v>1559.179227367448</v>
+      </c>
+      <c r="L775" t="inlineStr"/>
+      <c r="M775" t="inlineStr"/>
+      <c r="N775" t="inlineStr"/>
+      <c r="O775" t="n">
+        <v>0.1328536128</v>
+      </c>
+      <c r="P775" t="inlineStr"/>
+      <c r="Q775" t="n">
+        <v>5.879999999999999e-07</v>
+      </c>
+      <c r="R775" t="inlineStr"/>
+      <c r="S775" t="inlineStr"/>
+      <c r="T775" t="inlineStr"/>
+      <c r="U775" t="inlineStr"/>
+      <c r="V775" t="inlineStr"/>
+      <c r="W775" t="inlineStr"/>
+      <c r="X775" t="inlineStr"/>
+      <c r="Y775" t="inlineStr"/>
+      <c r="Z775" t="inlineStr"/>
+      <c r="AA775" t="n">
+        <v>0.0238917941248</v>
+      </c>
+      <c r="AB775" t="n">
+        <v>45.18904</v>
+      </c>
+      <c r="AC775" t="n">
+        <v>12.5581112260784</v>
+      </c>
+      <c r="AD775" t="n">
+        <v>0.10042526</v>
+      </c>
+      <c r="AE775" t="n">
+        <v>1617.757074888951</v>
+      </c>
+      <c r="AF775" t="inlineStr"/>
+      <c r="AG775" t="n">
+        <v>0.017315858</v>
+      </c>
+      <c r="AH775" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="2" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B776" t="n">
+        <v>0.466245287</v>
+      </c>
+      <c r="C776" t="n">
+        <v>0.0639109335</v>
+      </c>
+      <c r="D776" t="inlineStr"/>
+      <c r="E776" t="inlineStr"/>
+      <c r="F776" t="inlineStr"/>
+      <c r="G776" t="inlineStr"/>
+      <c r="H776" t="inlineStr"/>
+      <c r="I776" t="n">
+        <v>0.036484854</v>
+      </c>
+      <c r="J776" t="inlineStr"/>
+      <c r="K776" t="n">
+        <v>1587.652903433982</v>
+      </c>
+      <c r="L776" t="inlineStr"/>
+      <c r="M776" t="inlineStr"/>
+      <c r="N776" t="inlineStr"/>
+      <c r="O776" t="n">
+        <v>0.1363831608</v>
+      </c>
+      <c r="P776" t="inlineStr"/>
+      <c r="Q776" t="n">
+        <v>6.671999999999999e-07</v>
+      </c>
+      <c r="R776" t="inlineStr"/>
+      <c r="S776" t="inlineStr"/>
+      <c r="T776" t="inlineStr"/>
+      <c r="U776" t="inlineStr"/>
+      <c r="V776" t="inlineStr"/>
+      <c r="W776" t="inlineStr"/>
+      <c r="X776" t="inlineStr"/>
+      <c r="Y776" t="inlineStr"/>
+      <c r="Z776" t="inlineStr"/>
+      <c r="AA776" t="n">
+        <v>0.0238874977264</v>
+      </c>
+      <c r="AB776" t="n">
+        <v>47.9336</v>
+      </c>
+      <c r="AC776" t="n">
+        <v>12.763065563596</v>
+      </c>
+      <c r="AD776" t="n">
+        <v>0.104571675</v>
+      </c>
+      <c r="AE776" t="n">
+        <v>1649.198877986805</v>
+      </c>
+      <c r="AF776" t="inlineStr"/>
+      <c r="AG776" t="n">
+        <v>0.017824914</v>
+      </c>
+      <c r="AH776" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH776"/>
+  <dimension ref="A1:AH780"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60745,9 +60745,7 @@
       <c r="AE765" t="n">
         <v>1709.524036821868</v>
       </c>
-      <c r="AF765" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF765" t="inlineStr"/>
       <c r="AG765" t="n">
         <v>0.017721512</v>
       </c>
@@ -60811,9 +60809,7 @@
       <c r="AE766" t="n">
         <v>1678.045509417392</v>
       </c>
-      <c r="AF766" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF766" t="inlineStr"/>
       <c r="AG766" t="n">
         <v>0.016771009</v>
       </c>
@@ -61463,6 +61459,262 @@
         <v>0</v>
       </c>
     </row>
+    <row r="777">
+      <c r="A777" s="2" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B777" t="n">
+        <v>0.4704228745</v>
+      </c>
+      <c r="C777" t="n">
+        <v>0.06472626400000001</v>
+      </c>
+      <c r="D777" t="inlineStr"/>
+      <c r="E777" t="inlineStr"/>
+      <c r="F777" t="inlineStr"/>
+      <c r="G777" t="inlineStr"/>
+      <c r="H777" t="inlineStr"/>
+      <c r="I777" t="n">
+        <v>0.03624558</v>
+      </c>
+      <c r="J777" t="inlineStr"/>
+      <c r="K777" t="n">
+        <v>1596.489561523596</v>
+      </c>
+      <c r="L777" t="inlineStr"/>
+      <c r="M777" t="inlineStr"/>
+      <c r="N777" t="inlineStr"/>
+      <c r="O777" t="n">
+        <v>0.1367539416</v>
+      </c>
+      <c r="P777" t="inlineStr"/>
+      <c r="Q777" t="n">
+        <v>6.552e-07</v>
+      </c>
+      <c r="R777" t="inlineStr"/>
+      <c r="S777" t="inlineStr"/>
+      <c r="T777" t="inlineStr"/>
+      <c r="U777" t="inlineStr"/>
+      <c r="V777" t="inlineStr"/>
+      <c r="W777" t="inlineStr"/>
+      <c r="X777" t="inlineStr"/>
+      <c r="Y777" t="inlineStr"/>
+      <c r="Z777" t="inlineStr"/>
+      <c r="AA777" t="n">
+        <v>0.023884394772</v>
+      </c>
+      <c r="AB777" t="n">
+        <v>48.19672</v>
+      </c>
+      <c r="AC777" t="n">
+        <v>12.7816977760976</v>
+      </c>
+      <c r="AD777" t="n">
+        <v>0.107578965</v>
+      </c>
+      <c r="AE777" t="n">
+        <v>1658.325432796765</v>
+      </c>
+      <c r="AF777" t="inlineStr"/>
+      <c r="AG777" t="n">
+        <v>0.017840822</v>
+      </c>
+      <c r="AH777" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="2" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B778" t="n">
+        <v>0.4741925</v>
+      </c>
+      <c r="C778" t="n">
+        <v>0.0649083775</v>
+      </c>
+      <c r="D778" t="inlineStr"/>
+      <c r="E778" t="inlineStr"/>
+      <c r="F778" t="inlineStr"/>
+      <c r="G778" t="inlineStr"/>
+      <c r="H778" t="inlineStr"/>
+      <c r="I778" t="n">
+        <v>0.036152529</v>
+      </c>
+      <c r="J778" t="inlineStr"/>
+      <c r="K778" t="n">
+        <v>1616.126579500516</v>
+      </c>
+      <c r="L778" t="inlineStr"/>
+      <c r="M778" t="inlineStr"/>
+      <c r="N778" t="inlineStr"/>
+      <c r="O778" t="n">
+        <v>0.1402003016</v>
+      </c>
+      <c r="P778" t="inlineStr"/>
+      <c r="Q778" t="n">
+        <v>6.599999999999999e-07</v>
+      </c>
+      <c r="R778" t="inlineStr"/>
+      <c r="S778" t="inlineStr"/>
+      <c r="T778" t="inlineStr"/>
+      <c r="U778" t="inlineStr"/>
+      <c r="V778" t="inlineStr"/>
+      <c r="W778" t="inlineStr"/>
+      <c r="X778" t="inlineStr"/>
+      <c r="Y778" t="inlineStr"/>
+      <c r="Z778" t="inlineStr"/>
+      <c r="AA778" t="n">
+        <v>0.0238851108384</v>
+      </c>
+      <c r="AB778" t="n">
+        <v>48.07192</v>
+      </c>
+      <c r="AC778" t="n">
+        <v>12.5953756510816</v>
+      </c>
+      <c r="AD778" t="n">
+        <v>0.11136086</v>
+      </c>
+      <c r="AE778" t="n">
+        <v>1677.662798104536</v>
+      </c>
+      <c r="AF778" t="inlineStr"/>
+      <c r="AG778" t="n">
+        <v>0.018222614</v>
+      </c>
+      <c r="AH778" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B779" t="n">
+        <v>0.477113049</v>
+      </c>
+      <c r="C779" t="n">
+        <v>0.065414006</v>
+      </c>
+      <c r="D779" t="inlineStr"/>
+      <c r="E779" t="inlineStr"/>
+      <c r="F779" t="inlineStr"/>
+      <c r="G779" t="inlineStr"/>
+      <c r="H779" t="inlineStr"/>
+      <c r="I779" t="n">
+        <v>0.036307614</v>
+      </c>
+      <c r="J779" t="inlineStr"/>
+      <c r="K779" t="n">
+        <v>1618.581206747631</v>
+      </c>
+      <c r="L779" t="inlineStr"/>
+      <c r="M779" t="inlineStr"/>
+      <c r="N779" t="inlineStr"/>
+      <c r="O779" t="n">
+        <v>0.1392828568</v>
+      </c>
+      <c r="P779" t="inlineStr"/>
+      <c r="Q779" t="n">
+        <v>6.552e-07</v>
+      </c>
+      <c r="R779" t="inlineStr"/>
+      <c r="S779" t="inlineStr"/>
+      <c r="T779" t="inlineStr"/>
+      <c r="U779" t="inlineStr"/>
+      <c r="V779" t="inlineStr"/>
+      <c r="W779" t="inlineStr"/>
+      <c r="X779" t="inlineStr"/>
+      <c r="Y779" t="inlineStr"/>
+      <c r="Z779" t="inlineStr"/>
+      <c r="AA779" t="n">
+        <v>0.0238805757512</v>
+      </c>
+      <c r="AB779" t="n">
+        <v>47.0808</v>
+      </c>
+      <c r="AC779" t="n">
+        <v>12.949387688612</v>
+      </c>
+      <c r="AD779" t="n">
+        <v>0.110312865</v>
+      </c>
+      <c r="AE779" t="n">
+        <v>1679.481538925995</v>
+      </c>
+      <c r="AF779" t="inlineStr"/>
+      <c r="AG779" t="n">
+        <v>0.017832868</v>
+      </c>
+      <c r="AH779" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="2" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B780" t="n">
+        <v>0.4720617255</v>
+      </c>
+      <c r="C780" t="n">
+        <v>0.06439220750000001</v>
+      </c>
+      <c r="D780" t="inlineStr"/>
+      <c r="E780" t="inlineStr"/>
+      <c r="F780" t="inlineStr"/>
+      <c r="G780" t="inlineStr"/>
+      <c r="H780" t="inlineStr"/>
+      <c r="I780" t="n">
+        <v>0.03570499799999999</v>
+      </c>
+      <c r="J780" t="inlineStr"/>
+      <c r="K780" t="n">
+        <v>1628.399715736091</v>
+      </c>
+      <c r="L780" t="inlineStr"/>
+      <c r="M780" t="inlineStr"/>
+      <c r="N780" t="inlineStr"/>
+      <c r="O780" t="n">
+        <v>0.1370985776</v>
+      </c>
+      <c r="P780" t="inlineStr"/>
+      <c r="Q780" t="n">
+        <v>6.384e-07</v>
+      </c>
+      <c r="R780" t="inlineStr"/>
+      <c r="S780" t="inlineStr"/>
+      <c r="T780" t="inlineStr"/>
+      <c r="U780" t="inlineStr"/>
+      <c r="V780" t="inlineStr"/>
+      <c r="W780" t="inlineStr"/>
+      <c r="X780" t="inlineStr"/>
+      <c r="Y780" t="inlineStr"/>
+      <c r="Z780" t="inlineStr"/>
+      <c r="AA780" t="n">
+        <v>0.0238810531288</v>
+      </c>
+      <c r="AB780" t="n">
+        <v>50.2944</v>
+      </c>
+      <c r="AC780" t="n">
+        <v>12.390421313564</v>
+      </c>
+      <c r="AD780" t="n">
+        <v>0.10908261</v>
+      </c>
+      <c r="AE780" t="n">
+        <v>1691.944221866784</v>
+      </c>
+      <c r="AF780" t="inlineStr"/>
+      <c r="AG780" t="n">
+        <v>0.017463007</v>
+      </c>
+      <c r="AH780" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH780"/>
+  <dimension ref="A1:AH782"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60551,9 +60551,7 @@
       <c r="AE762" t="n">
         <v>1680.802708411937</v>
       </c>
-      <c r="AF762" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF762" t="inlineStr"/>
       <c r="AG762" t="n">
         <v>0.017526639</v>
       </c>
@@ -61715,6 +61713,134 @@
         <v>0</v>
       </c>
     </row>
+    <row r="781">
+      <c r="A781" s="2" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B781" t="n">
+        <v>0.4640605</v>
+      </c>
+      <c r="C781" t="n">
+        <v>0.06337767900000001</v>
+      </c>
+      <c r="D781" t="inlineStr"/>
+      <c r="E781" t="inlineStr"/>
+      <c r="F781" t="inlineStr"/>
+      <c r="G781" t="inlineStr"/>
+      <c r="H781" t="inlineStr"/>
+      <c r="I781" t="n">
+        <v>0.034486473</v>
+      </c>
+      <c r="J781" t="inlineStr"/>
+      <c r="K781" t="n">
+        <v>1612.690101354555</v>
+      </c>
+      <c r="L781" t="inlineStr"/>
+      <c r="M781" t="inlineStr"/>
+      <c r="N781" t="inlineStr"/>
+      <c r="O781" t="n">
+        <v>0.1351591088</v>
+      </c>
+      <c r="P781" t="inlineStr"/>
+      <c r="Q781" t="n">
+        <v>6.263999999999999e-07</v>
+      </c>
+      <c r="R781" t="inlineStr"/>
+      <c r="S781" t="inlineStr"/>
+      <c r="T781" t="inlineStr"/>
+      <c r="U781" t="inlineStr"/>
+      <c r="V781" t="inlineStr"/>
+      <c r="W781" t="inlineStr"/>
+      <c r="X781" t="inlineStr"/>
+      <c r="Y781" t="inlineStr"/>
+      <c r="Z781" t="inlineStr"/>
+      <c r="AA781" t="n">
+        <v>0.0238834400168</v>
+      </c>
+      <c r="AB781" t="n">
+        <v>48.46296</v>
+      </c>
+      <c r="AC781" t="n">
+        <v>12.0736737010368</v>
+      </c>
+      <c r="AD781" t="n">
+        <v>0.10726001</v>
+      </c>
+      <c r="AE781" t="n">
+        <v>1674.072326474809</v>
+      </c>
+      <c r="AF781" t="inlineStr"/>
+      <c r="AG781" t="n">
+        <v>0.017363582</v>
+      </c>
+      <c r="AH781" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B782" t="n">
+        <v>0.4710635</v>
+      </c>
+      <c r="C782" t="n">
+        <v>0.06343656600000001</v>
+      </c>
+      <c r="D782" t="inlineStr"/>
+      <c r="E782" t="inlineStr"/>
+      <c r="F782" t="inlineStr"/>
+      <c r="G782" t="inlineStr"/>
+      <c r="H782" t="inlineStr"/>
+      <c r="I782" t="n">
+        <v>0.034579524</v>
+      </c>
+      <c r="J782" t="inlineStr"/>
+      <c r="K782" t="n">
+        <v>1630.854342983206</v>
+      </c>
+      <c r="L782" t="inlineStr"/>
+      <c r="M782" t="inlineStr"/>
+      <c r="N782" t="inlineStr"/>
+      <c r="O782" t="n">
+        <v>0.1351733696</v>
+      </c>
+      <c r="P782" t="inlineStr"/>
+      <c r="Q782" t="n">
+        <v>6.263999999999999e-07</v>
+      </c>
+      <c r="R782" t="inlineStr"/>
+      <c r="S782" t="inlineStr"/>
+      <c r="T782" t="inlineStr"/>
+      <c r="U782" t="inlineStr"/>
+      <c r="V782" t="inlineStr"/>
+      <c r="W782" t="inlineStr"/>
+      <c r="X782" t="inlineStr"/>
+      <c r="Y782" t="inlineStr"/>
+      <c r="Z782" t="inlineStr"/>
+      <c r="AA782" t="n">
+        <v>0.0238822465728</v>
+      </c>
+      <c r="AB782" t="n">
+        <v>50.08016</v>
+      </c>
+      <c r="AC782" t="n">
+        <v>12.1482025510432</v>
+      </c>
+      <c r="AD782" t="n">
+        <v>0.10835357</v>
+      </c>
+      <c r="AE782" t="n">
+        <v>1693.936614196822</v>
+      </c>
+      <c r="AF782" t="inlineStr"/>
+      <c r="AG782" t="n">
+        <v>0.01741926</v>
+      </c>
+      <c r="AH782" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH782"/>
+  <dimension ref="A1:AH783"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60291,9 +60291,7 @@
       <c r="AE758" t="n">
         <v>1669.579824132914</v>
       </c>
-      <c r="AF758" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF758" t="inlineStr"/>
       <c r="AG758" t="n">
         <v>0.018198752</v>
       </c>
@@ -61841,6 +61839,70 @@
         <v>0</v>
       </c>
     </row>
+    <row r="783">
+      <c r="A783" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B783" t="n">
+        <v>0.478004814</v>
+      </c>
+      <c r="C783" t="n">
+        <v>0.0653154975</v>
+      </c>
+      <c r="D783" t="inlineStr"/>
+      <c r="E783" t="inlineStr"/>
+      <c r="F783" t="inlineStr"/>
+      <c r="G783" t="inlineStr"/>
+      <c r="H783" t="inlineStr"/>
+      <c r="I783" t="n">
+        <v>0.034619403</v>
+      </c>
+      <c r="J783" t="inlineStr"/>
+      <c r="K783" t="n">
+        <v>1622.017684893592</v>
+      </c>
+      <c r="L783" t="inlineStr"/>
+      <c r="M783" t="inlineStr"/>
+      <c r="N783" t="inlineStr"/>
+      <c r="O783" t="n">
+        <v>0.1367682024</v>
+      </c>
+      <c r="P783" t="inlineStr"/>
+      <c r="Q783" t="n">
+        <v>6.696e-07</v>
+      </c>
+      <c r="R783" t="inlineStr"/>
+      <c r="S783" t="inlineStr"/>
+      <c r="T783" t="inlineStr"/>
+      <c r="U783" t="inlineStr"/>
+      <c r="V783" t="inlineStr"/>
+      <c r="W783" t="inlineStr"/>
+      <c r="X783" t="inlineStr"/>
+      <c r="Y783" t="inlineStr"/>
+      <c r="Z783" t="inlineStr"/>
+      <c r="AA783" t="n">
+        <v>0.0238810531288</v>
+      </c>
+      <c r="AB783" t="n">
+        <v>51.90952</v>
+      </c>
+      <c r="AC783" t="n">
+        <v>12.297260251056</v>
+      </c>
+      <c r="AD783" t="n">
+        <v>0.11172538</v>
+      </c>
+      <c r="AE783" t="n">
+        <v>1687.092589170277</v>
+      </c>
+      <c r="AF783" t="inlineStr"/>
+      <c r="AG783" t="n">
+        <v>0.017809006</v>
+      </c>
+      <c r="AH783" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH783"/>
+  <dimension ref="A1:AH784"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60417,11 +60417,9 @@
         <v>0.096825625</v>
       </c>
       <c r="AE760" t="n">
-        <v>1684.032281601724</v>
-      </c>
-      <c r="AF760" t="n">
-        <v>0</v>
-      </c>
+        <v>1684.032281601723</v>
+      </c>
+      <c r="AF760" t="inlineStr"/>
       <c r="AG760" t="n">
         <v>0.017864684</v>
       </c>
@@ -61903,6 +61901,70 @@
         <v>0</v>
       </c>
     </row>
+    <row r="784">
+      <c r="A784" s="2" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B784" t="n">
+        <v>0.47545155</v>
+      </c>
+      <c r="C784" t="n">
+        <v>0.064985076</v>
+      </c>
+      <c r="D784" t="inlineStr"/>
+      <c r="E784" t="inlineStr"/>
+      <c r="F784" t="inlineStr"/>
+      <c r="G784" t="inlineStr"/>
+      <c r="H784" t="inlineStr"/>
+      <c r="I784" t="n">
+        <v>0.034025649</v>
+      </c>
+      <c r="J784" t="inlineStr"/>
+      <c r="K784" t="n">
+        <v>1619.563057646477</v>
+      </c>
+      <c r="L784" t="inlineStr"/>
+      <c r="M784" t="inlineStr"/>
+      <c r="N784" t="inlineStr"/>
+      <c r="O784" t="n">
+        <v>0.136582812</v>
+      </c>
+      <c r="P784" t="inlineStr"/>
+      <c r="Q784" t="n">
+        <v>6.503999999999999e-07</v>
+      </c>
+      <c r="R784" t="inlineStr"/>
+      <c r="S784" t="inlineStr"/>
+      <c r="T784" t="inlineStr"/>
+      <c r="U784" t="inlineStr"/>
+      <c r="V784" t="inlineStr"/>
+      <c r="W784" t="inlineStr"/>
+      <c r="X784" t="inlineStr"/>
+      <c r="Y784" t="inlineStr"/>
+      <c r="Z784" t="inlineStr"/>
+      <c r="AA784" t="n">
+        <v>0.0238805757512</v>
+      </c>
+      <c r="AB784" t="n">
+        <v>52.90376</v>
+      </c>
+      <c r="AC784" t="n">
+        <v>12.1482025510432</v>
+      </c>
+      <c r="AD784" t="n">
+        <v>0.1111786</v>
+      </c>
+      <c r="AE784" t="n">
+        <v>1685.478882415672</v>
+      </c>
+      <c r="AF784" t="inlineStr"/>
+      <c r="AG784" t="n">
+        <v>0.017757305</v>
+      </c>
+      <c r="AH784" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH784"/>
+  <dimension ref="A1:AH786"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60417,7 +60417,7 @@
         <v>0.096825625</v>
       </c>
       <c r="AE760" t="n">
-        <v>1684.032281601723</v>
+        <v>1684.032281601724</v>
       </c>
       <c r="AF760" t="inlineStr"/>
       <c r="AG760" t="n">
@@ -61965,6 +61965,134 @@
         <v>0</v>
       </c>
     </row>
+    <row r="785">
+      <c r="A785" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B785" t="n">
+        <v>0.475161</v>
+      </c>
+      <c r="C785" t="n">
+        <v>0.06567718</v>
+      </c>
+      <c r="D785" t="inlineStr"/>
+      <c r="E785" t="inlineStr"/>
+      <c r="F785" t="inlineStr"/>
+      <c r="G785" t="inlineStr"/>
+      <c r="H785" t="inlineStr"/>
+      <c r="I785" t="n">
+        <v>0.034083252</v>
+      </c>
+      <c r="J785" t="inlineStr"/>
+      <c r="K785" t="n">
+        <v>1627.908790286668</v>
+      </c>
+      <c r="L785" t="inlineStr"/>
+      <c r="M785" t="inlineStr"/>
+      <c r="N785" t="inlineStr"/>
+      <c r="O785" t="n">
+        <v>0.1364069288</v>
+      </c>
+      <c r="P785" t="inlineStr"/>
+      <c r="Q785" t="n">
+        <v>6.648e-07</v>
+      </c>
+      <c r="R785" t="inlineStr"/>
+      <c r="S785" t="inlineStr"/>
+      <c r="T785" t="inlineStr"/>
+      <c r="U785" t="inlineStr"/>
+      <c r="V785" t="inlineStr"/>
+      <c r="W785" t="inlineStr"/>
+      <c r="X785" t="inlineStr"/>
+      <c r="Y785" t="inlineStr"/>
+      <c r="Z785" t="inlineStr"/>
+      <c r="AA785" t="n">
+        <v>0.0238789049296</v>
+      </c>
+      <c r="AB785" t="n">
+        <v>55.48712</v>
+      </c>
+      <c r="AC785" t="n">
+        <v>12.017777063532</v>
+      </c>
+      <c r="AD785" t="n">
+        <v>0.109492695</v>
+      </c>
+      <c r="AE785" t="n">
+        <v>1696.27589075273</v>
+      </c>
+      <c r="AF785" t="inlineStr"/>
+      <c r="AG785" t="n">
+        <v>0.017502777</v>
+      </c>
+      <c r="AH785" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="2" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B786" t="n">
+        <v>0.464392174</v>
+      </c>
+      <c r="C786" t="n">
+        <v>0.06458377200000001</v>
+      </c>
+      <c r="D786" t="inlineStr"/>
+      <c r="E786" t="inlineStr"/>
+      <c r="F786" t="inlineStr"/>
+      <c r="G786" t="inlineStr"/>
+      <c r="H786" t="inlineStr"/>
+      <c r="I786" t="n">
+        <v>0.033236931</v>
+      </c>
+      <c r="J786" t="inlineStr"/>
+      <c r="K786" t="n">
+        <v>1592.562157928212</v>
+      </c>
+      <c r="L786" t="inlineStr"/>
+      <c r="M786" t="inlineStr"/>
+      <c r="N786" t="inlineStr"/>
+      <c r="O786" t="n">
+        <v>0.1348810232</v>
+      </c>
+      <c r="P786" t="inlineStr"/>
+      <c r="Q786" t="n">
+        <v>6.552e-07</v>
+      </c>
+      <c r="R786" t="inlineStr"/>
+      <c r="S786" t="inlineStr"/>
+      <c r="T786" t="inlineStr"/>
+      <c r="U786" t="inlineStr"/>
+      <c r="V786" t="inlineStr"/>
+      <c r="W786" t="inlineStr"/>
+      <c r="X786" t="inlineStr"/>
+      <c r="Y786" t="inlineStr"/>
+      <c r="Z786" t="inlineStr"/>
+      <c r="AA786" t="n">
+        <v>0.0238941810128</v>
+      </c>
+      <c r="AB786" t="n">
+        <v>51.53928</v>
+      </c>
+      <c r="AC786" t="n">
+        <v>11.4401784759824</v>
+      </c>
+      <c r="AD786" t="n">
+        <v>0.107761225</v>
+      </c>
+      <c r="AE786" t="n">
+        <v>1656.387694154608</v>
+      </c>
+      <c r="AF786" t="inlineStr"/>
+      <c r="AG786" t="n">
+        <v>0.017327789</v>
+      </c>
+      <c r="AH786" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH786"/>
+  <dimension ref="A1:AH787"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60417,7 +60417,7 @@
         <v>0.096825625</v>
       </c>
       <c r="AE760" t="n">
-        <v>1684.032281601724</v>
+        <v>1684.032281601723</v>
       </c>
       <c r="AF760" t="inlineStr"/>
       <c r="AG760" t="n">
@@ -62083,13 +62083,77 @@
         <v>0.107761225</v>
       </c>
       <c r="AE786" t="n">
-        <v>1656.387694154608</v>
+        <v>1656.387694154607</v>
       </c>
       <c r="AF786" t="inlineStr"/>
       <c r="AG786" t="n">
         <v>0.017327789</v>
       </c>
       <c r="AH786" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B787" t="n">
+        <v>0.484577651</v>
+      </c>
+      <c r="C787" t="n">
+        <v>0.0687694745</v>
+      </c>
+      <c r="D787" t="inlineStr"/>
+      <c r="E787" t="inlineStr"/>
+      <c r="F787" t="inlineStr"/>
+      <c r="G787" t="inlineStr"/>
+      <c r="H787" t="inlineStr"/>
+      <c r="I787" t="n">
+        <v>0.034504197</v>
+      </c>
+      <c r="J787" t="inlineStr"/>
+      <c r="K787" t="n">
+        <v>1599.926039669557</v>
+      </c>
+      <c r="L787" t="inlineStr"/>
+      <c r="M787" t="inlineStr"/>
+      <c r="N787" t="inlineStr"/>
+      <c r="O787" t="n">
+        <v>0.1382988616</v>
+      </c>
+      <c r="P787" t="inlineStr"/>
+      <c r="Q787" t="n">
+        <v>6.744000000000001e-07</v>
+      </c>
+      <c r="R787" t="inlineStr"/>
+      <c r="S787" t="inlineStr"/>
+      <c r="T787" t="inlineStr"/>
+      <c r="U787" t="inlineStr"/>
+      <c r="V787" t="inlineStr"/>
+      <c r="W787" t="inlineStr"/>
+      <c r="X787" t="inlineStr"/>
+      <c r="Y787" t="inlineStr"/>
+      <c r="Z787" t="inlineStr"/>
+      <c r="AA787" t="n">
+        <v>0.0238815305064</v>
+      </c>
+      <c r="AB787" t="n">
+        <v>58.68823999999999</v>
+      </c>
+      <c r="AC787" t="n">
+        <v>11.8128227260144</v>
+      </c>
+      <c r="AD787" t="n">
+        <v>0.10789792</v>
+      </c>
+      <c r="AE787" t="n">
+        <v>1671.303092261578</v>
+      </c>
+      <c r="AF787" t="inlineStr"/>
+      <c r="AG787" t="n">
+        <v>0.018059557</v>
+      </c>
+      <c r="AH787" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH787"/>
+  <dimension ref="A1:AH789"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60417,7 +60417,7 @@
         <v>0.096825625</v>
       </c>
       <c r="AE760" t="n">
-        <v>1684.032281601723</v>
+        <v>1684.032281601724</v>
       </c>
       <c r="AF760" t="inlineStr"/>
       <c r="AG760" t="n">
@@ -60995,9 +60995,7 @@
       <c r="AE769" t="n">
         <v>1627.251346724789</v>
       </c>
-      <c r="AF769" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF769" t="inlineStr"/>
       <c r="AG769" t="n">
         <v>0.016667607</v>
       </c>
@@ -62083,7 +62081,7 @@
         <v>0.107761225</v>
       </c>
       <c r="AE786" t="n">
-        <v>1656.387694154607</v>
+        <v>1656.387694154608</v>
       </c>
       <c r="AF786" t="inlineStr"/>
       <c r="AG786" t="n">
@@ -62157,6 +62155,134 @@
         <v>0</v>
       </c>
     </row>
+    <row r="788">
+      <c r="A788" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B788" t="n">
+        <v>0.482434286</v>
+      </c>
+      <c r="C788" t="n">
+        <v>0.069714211</v>
+      </c>
+      <c r="D788" t="inlineStr"/>
+      <c r="E788" t="inlineStr"/>
+      <c r="F788" t="inlineStr"/>
+      <c r="G788" t="inlineStr"/>
+      <c r="H788" t="inlineStr"/>
+      <c r="I788" t="n">
+        <v>0.034247199</v>
+      </c>
+      <c r="J788" t="inlineStr"/>
+      <c r="K788" t="n">
+        <v>1593.053083377635</v>
+      </c>
+      <c r="L788" t="inlineStr"/>
+      <c r="M788" t="inlineStr"/>
+      <c r="N788" t="inlineStr"/>
+      <c r="O788" t="n">
+        <v>0.137985124</v>
+      </c>
+      <c r="P788" t="inlineStr"/>
+      <c r="Q788" t="n">
+        <v>6.696e-07</v>
+      </c>
+      <c r="R788" t="inlineStr"/>
+      <c r="S788" t="inlineStr"/>
+      <c r="T788" t="inlineStr"/>
+      <c r="U788" t="inlineStr"/>
+      <c r="V788" t="inlineStr"/>
+      <c r="W788" t="inlineStr"/>
+      <c r="X788" t="inlineStr"/>
+      <c r="Y788" t="inlineStr"/>
+      <c r="Z788" t="inlineStr"/>
+      <c r="AA788" t="n">
+        <v>0.0238803370624</v>
+      </c>
+      <c r="AB788" t="n">
+        <v>59.33615999999999</v>
+      </c>
+      <c r="AC788" t="n">
+        <v>11.924616001024</v>
+      </c>
+      <c r="AD788" t="n">
+        <v>0.101655515</v>
+      </c>
+      <c r="AE788" t="n">
+        <v>1665.181744806321</v>
+      </c>
+      <c r="AF788" t="inlineStr"/>
+      <c r="AG788" t="n">
+        <v>0.017968086</v>
+      </c>
+      <c r="AH788" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B789" t="n">
+        <v>0.47553499</v>
+      </c>
+      <c r="C789" t="n">
+        <v>0.06778220850000001</v>
+      </c>
+      <c r="D789" t="inlineStr"/>
+      <c r="E789" t="inlineStr"/>
+      <c r="F789" t="inlineStr"/>
+      <c r="G789" t="inlineStr"/>
+      <c r="H789" t="inlineStr"/>
+      <c r="I789" t="n">
+        <v>0.03337429199999999</v>
+      </c>
+      <c r="J789" t="inlineStr"/>
+      <c r="K789" t="n">
+        <v>1587.161977984559</v>
+      </c>
+      <c r="L789" t="inlineStr"/>
+      <c r="M789" t="inlineStr"/>
+      <c r="N789" t="inlineStr"/>
+      <c r="O789" t="n">
+        <v>0.136059916</v>
+      </c>
+      <c r="P789" t="inlineStr"/>
+      <c r="Q789" t="n">
+        <v>6.527999999999999e-07</v>
+      </c>
+      <c r="R789" t="inlineStr"/>
+      <c r="S789" t="inlineStr"/>
+      <c r="T789" t="inlineStr"/>
+      <c r="U789" t="inlineStr"/>
+      <c r="V789" t="inlineStr"/>
+      <c r="W789" t="inlineStr"/>
+      <c r="X789" t="inlineStr"/>
+      <c r="Y789" t="inlineStr"/>
+      <c r="Z789" t="inlineStr"/>
+      <c r="AA789" t="n">
+        <v>0.0238851108384</v>
+      </c>
+      <c r="AB789" t="n">
+        <v>54.46688</v>
+      </c>
+      <c r="AC789" t="n">
+        <v>13.0239165386184</v>
+      </c>
+      <c r="AD789" t="n">
+        <v>0.101108735</v>
+      </c>
+      <c r="AE789" t="n">
+        <v>1655.508393066316</v>
+      </c>
+      <c r="AF789" t="inlineStr"/>
+      <c r="AG789" t="n">
+        <v>0.017872638</v>
+      </c>
+      <c r="AH789" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH789"/>
+  <dimension ref="A1:AH790"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62081,7 +62081,7 @@
         <v>0.107761225</v>
       </c>
       <c r="AE786" t="n">
-        <v>1656.387694154608</v>
+        <v>1656.387694154607</v>
       </c>
       <c r="AF786" t="inlineStr"/>
       <c r="AG786" t="n">
@@ -62283,6 +62283,70 @@
         <v>0</v>
       </c>
     </row>
+    <row r="790">
+      <c r="A790" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B790" t="n">
+        <v>0.4762909415</v>
+      </c>
+      <c r="C790" t="n">
+        <v>0.0669541555</v>
+      </c>
+      <c r="D790" t="inlineStr"/>
+      <c r="E790" t="inlineStr"/>
+      <c r="F790" t="inlineStr"/>
+      <c r="G790" t="inlineStr"/>
+      <c r="H790" t="inlineStr"/>
+      <c r="I790" t="n">
+        <v>0.033250224</v>
+      </c>
+      <c r="J790" t="inlineStr"/>
+      <c r="K790" t="n">
+        <v>1584.216425288021</v>
+      </c>
+      <c r="L790" t="inlineStr"/>
+      <c r="M790" t="inlineStr"/>
+      <c r="N790" t="inlineStr"/>
+      <c r="O790" t="n">
+        <v>0.1350236312</v>
+      </c>
+      <c r="P790" t="inlineStr"/>
+      <c r="Q790" t="n">
+        <v>6.576e-07</v>
+      </c>
+      <c r="R790" t="inlineStr"/>
+      <c r="S790" t="inlineStr"/>
+      <c r="T790" t="inlineStr"/>
+      <c r="U790" t="inlineStr"/>
+      <c r="V790" t="inlineStr"/>
+      <c r="W790" t="inlineStr"/>
+      <c r="X790" t="inlineStr"/>
+      <c r="Y790" t="inlineStr"/>
+      <c r="Z790" t="inlineStr"/>
+      <c r="AA790" t="n">
+        <v>0.0238824852616</v>
+      </c>
+      <c r="AB790" t="n">
+        <v>56.93688</v>
+      </c>
+      <c r="AC790" t="n">
+        <v>12.3158924635576</v>
+      </c>
+      <c r="AD790" t="n">
+        <v>0.100106305</v>
+      </c>
+      <c r="AE790" t="n">
+        <v>1654.32267026064</v>
+      </c>
+      <c r="AF790" t="inlineStr"/>
+      <c r="AG790" t="n">
+        <v>0.017964109</v>
+      </c>
+      <c r="AH790" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH790"/>
+  <dimension ref="A1:AH792"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62347,6 +62347,134 @@
         <v>0</v>
       </c>
     </row>
+    <row r="791">
+      <c r="A791" s="2" t="n">
+        <v>46221</v>
+      </c>
+      <c r="B791" t="n">
+        <v>0.483014939</v>
+      </c>
+      <c r="C791" t="n">
+        <v>0.0677058735</v>
+      </c>
+      <c r="D791" t="inlineStr"/>
+      <c r="E791" t="inlineStr"/>
+      <c r="F791" t="inlineStr"/>
+      <c r="G791" t="inlineStr"/>
+      <c r="H791" t="inlineStr"/>
+      <c r="I791" t="n">
+        <v>0.033462912</v>
+      </c>
+      <c r="J791" t="inlineStr"/>
+      <c r="K791" t="n">
+        <v>1599.435114220134</v>
+      </c>
+      <c r="L791" t="inlineStr"/>
+      <c r="M791" t="inlineStr"/>
+      <c r="N791" t="inlineStr"/>
+      <c r="O791" t="n">
+        <v>0.135632092</v>
+      </c>
+      <c r="P791" t="inlineStr"/>
+      <c r="Q791" t="n">
+        <v>6.599999999999999e-07</v>
+      </c>
+      <c r="R791" t="inlineStr"/>
+      <c r="S791" t="inlineStr"/>
+      <c r="T791" t="inlineStr"/>
+      <c r="U791" t="inlineStr"/>
+      <c r="V791" t="inlineStr"/>
+      <c r="W791" t="inlineStr"/>
+      <c r="X791" t="inlineStr"/>
+      <c r="Y791" t="inlineStr"/>
+      <c r="Z791" t="inlineStr"/>
+      <c r="AA791" t="n">
+        <v>0.0238815305064</v>
+      </c>
+      <c r="AB791" t="n">
+        <v>58.1048</v>
+      </c>
+      <c r="AC791" t="n">
+        <v>11.6823972385032</v>
+      </c>
+      <c r="AD791" t="n">
+        <v>0.10033413</v>
+      </c>
+      <c r="AE791" t="n">
+        <v>1670.085039472644</v>
+      </c>
+      <c r="AF791" t="inlineStr"/>
+      <c r="AG791" t="n">
+        <v>0.018695877</v>
+      </c>
+      <c r="AH791" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B792" t="n">
+        <v>0.482182923</v>
+      </c>
+      <c r="C792" t="n">
+        <v>0.0680555605</v>
+      </c>
+      <c r="D792" t="inlineStr"/>
+      <c r="E792" t="inlineStr"/>
+      <c r="F792" t="inlineStr"/>
+      <c r="G792" t="inlineStr"/>
+      <c r="H792" t="inlineStr"/>
+      <c r="I792" t="n">
+        <v>0.033843978</v>
+      </c>
+      <c r="J792" t="inlineStr"/>
+      <c r="K792" t="n">
+        <v>1605.32621961321</v>
+      </c>
+      <c r="L792" t="inlineStr"/>
+      <c r="M792" t="inlineStr"/>
+      <c r="N792" t="inlineStr"/>
+      <c r="O792" t="n">
+        <v>0.1357295408</v>
+      </c>
+      <c r="P792" t="inlineStr"/>
+      <c r="Q792" t="n">
+        <v>6.816e-07</v>
+      </c>
+      <c r="R792" t="inlineStr"/>
+      <c r="S792" t="inlineStr"/>
+      <c r="T792" t="inlineStr"/>
+      <c r="U792" t="inlineStr"/>
+      <c r="V792" t="inlineStr"/>
+      <c r="W792" t="inlineStr"/>
+      <c r="X792" t="inlineStr"/>
+      <c r="Y792" t="inlineStr"/>
+      <c r="Z792" t="inlineStr"/>
+      <c r="AA792" t="n">
+        <v>0.0238834400168</v>
+      </c>
+      <c r="AB792" t="n">
+        <v>57.01384</v>
+      </c>
+      <c r="AC792" t="n">
+        <v>11.7941905135128</v>
+      </c>
+      <c r="AD792" t="n">
+        <v>0.09810144500000001</v>
+      </c>
+      <c r="AE792" t="n">
+        <v>1674.99476743464</v>
+      </c>
+      <c r="AF792" t="inlineStr"/>
+      <c r="AG792" t="n">
+        <v>0.018719739</v>
+      </c>
+      <c r="AH792" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH792"/>
+  <dimension ref="A1:AH793"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62475,6 +62475,70 @@
         <v>0</v>
       </c>
     </row>
+    <row r="793">
+      <c r="A793" s="2" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B793" t="n">
+        <v>0.4861535495</v>
+      </c>
+      <c r="C793" t="n">
+        <v>0.06923838950000001</v>
+      </c>
+      <c r="D793" t="inlineStr"/>
+      <c r="E793" t="inlineStr"/>
+      <c r="F793" t="inlineStr"/>
+      <c r="G793" t="inlineStr"/>
+      <c r="H793" t="inlineStr"/>
+      <c r="I793" t="n">
+        <v>0.034495335</v>
+      </c>
+      <c r="J793" t="inlineStr"/>
+      <c r="K793" t="n">
+        <v>1604.835294163787</v>
+      </c>
+      <c r="L793" t="inlineStr"/>
+      <c r="M793" t="inlineStr"/>
+      <c r="N793" t="inlineStr"/>
+      <c r="O793" t="n">
+        <v>0.1357794536</v>
+      </c>
+      <c r="P793" t="inlineStr"/>
+      <c r="Q793" t="n">
+        <v>7.007999999999999e-07</v>
+      </c>
+      <c r="R793" t="inlineStr"/>
+      <c r="S793" t="inlineStr"/>
+      <c r="T793" t="inlineStr"/>
+      <c r="U793" t="inlineStr"/>
+      <c r="V793" t="inlineStr"/>
+      <c r="W793" t="inlineStr"/>
+      <c r="X793" t="inlineStr"/>
+      <c r="Y793" t="inlineStr"/>
+      <c r="Z793" t="inlineStr"/>
+      <c r="AA793" t="n">
+        <v>0.023883201328</v>
+      </c>
+      <c r="AB793" t="n">
+        <v>56.5604</v>
+      </c>
+      <c r="AC793" t="n">
+        <v>12.483582376072</v>
+      </c>
+      <c r="AD793" t="n">
+        <v>0.100197435</v>
+      </c>
+      <c r="AE793" t="n">
+        <v>1674.747863653587</v>
+      </c>
+      <c r="AF793" t="inlineStr"/>
+      <c r="AG793" t="n">
+        <v>0.018839049</v>
+      </c>
+      <c r="AH793" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH793"/>
+  <dimension ref="A1:AH797"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62539,6 +62539,262 @@
         <v>0</v>
       </c>
     </row>
+    <row r="794">
+      <c r="A794" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B794" t="n">
+        <v>0.495843392</v>
+      </c>
+      <c r="C794" t="n">
+        <v>0.07015877150000001</v>
+      </c>
+      <c r="D794" t="inlineStr"/>
+      <c r="E794" t="inlineStr"/>
+      <c r="F794" t="inlineStr"/>
+      <c r="G794" t="inlineStr"/>
+      <c r="H794" t="inlineStr"/>
+      <c r="I794" t="n">
+        <v>0.034614972</v>
+      </c>
+      <c r="J794" t="inlineStr"/>
+      <c r="K794" t="n">
+        <v>1618.581206747631</v>
+      </c>
+      <c r="L794" t="inlineStr"/>
+      <c r="M794" t="inlineStr"/>
+      <c r="N794" t="inlineStr"/>
+      <c r="O794" t="n">
+        <v>0.136416436</v>
+      </c>
+      <c r="P794" t="inlineStr"/>
+      <c r="Q794" t="n">
+        <v>6.911999999999999e-07</v>
+      </c>
+      <c r="R794" t="inlineStr"/>
+      <c r="S794" t="inlineStr"/>
+      <c r="T794" t="inlineStr"/>
+      <c r="U794" t="inlineStr"/>
+      <c r="V794" t="inlineStr"/>
+      <c r="W794" t="inlineStr"/>
+      <c r="X794" t="inlineStr"/>
+      <c r="Y794" t="inlineStr"/>
+      <c r="Z794" t="inlineStr"/>
+      <c r="AA794" t="n">
+        <v>0.023882007884</v>
+      </c>
+      <c r="AB794" t="n">
+        <v>55.41328</v>
+      </c>
+      <c r="AC794" t="n">
+        <v>12.3345246760592</v>
+      </c>
+      <c r="AD794" t="n">
+        <v>0.102020035</v>
+      </c>
+      <c r="AE794" t="n">
+        <v>1687.210587928274</v>
+      </c>
+      <c r="AF794" t="inlineStr"/>
+      <c r="AG794" t="n">
+        <v>0.018640199</v>
+      </c>
+      <c r="AH794" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="2" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B795" t="n">
+        <v>0.4925529505</v>
+      </c>
+      <c r="C795" t="n">
+        <v>0.0703099875</v>
+      </c>
+      <c r="D795" t="inlineStr"/>
+      <c r="E795" t="inlineStr"/>
+      <c r="F795" t="inlineStr"/>
+      <c r="G795" t="inlineStr"/>
+      <c r="H795" t="inlineStr"/>
+      <c r="I795" t="n">
+        <v>0.034548507</v>
+      </c>
+      <c r="J795" t="inlineStr"/>
+      <c r="K795" t="n">
+        <v>1614.653803152247</v>
+      </c>
+      <c r="L795" t="inlineStr"/>
+      <c r="M795" t="inlineStr"/>
+      <c r="N795" t="inlineStr"/>
+      <c r="O795" t="n">
+        <v>0.1357342944</v>
+      </c>
+      <c r="P795" t="inlineStr"/>
+      <c r="Q795" t="n">
+        <v>6.935999999999999e-07</v>
+      </c>
+      <c r="R795" t="inlineStr"/>
+      <c r="S795" t="inlineStr"/>
+      <c r="T795" t="inlineStr"/>
+      <c r="U795" t="inlineStr"/>
+      <c r="V795" t="inlineStr"/>
+      <c r="W795" t="inlineStr"/>
+      <c r="X795" t="inlineStr"/>
+      <c r="Y795" t="inlineStr"/>
+      <c r="Z795" t="inlineStr"/>
+      <c r="AA795" t="n">
+        <v>0.0238803370624</v>
+      </c>
+      <c r="AB795" t="n">
+        <v>53.60992</v>
+      </c>
+      <c r="AC795" t="n">
+        <v>12.0736737010368</v>
+      </c>
+      <c r="AD795" t="n">
+        <v>0.100243</v>
+      </c>
+      <c r="AE795" t="n">
+        <v>1681.213414201346</v>
+      </c>
+      <c r="AF795" t="inlineStr"/>
+      <c r="AG795" t="n">
+        <v>0.018747578</v>
+      </c>
+      <c r="AH795" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="2" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B796" t="n">
+        <v>0.4849873265</v>
+      </c>
+      <c r="C796" t="n">
+        <v>0.068279113</v>
+      </c>
+      <c r="D796" t="inlineStr"/>
+      <c r="E796" t="inlineStr"/>
+      <c r="F796" t="inlineStr"/>
+      <c r="G796" t="inlineStr"/>
+      <c r="H796" t="inlineStr"/>
+      <c r="I796" t="n">
+        <v>0.033622428</v>
+      </c>
+      <c r="J796" t="inlineStr"/>
+      <c r="K796" t="n">
+        <v>1614.653803152247</v>
+      </c>
+      <c r="L796" t="inlineStr"/>
+      <c r="M796" t="inlineStr"/>
+      <c r="N796" t="inlineStr"/>
+      <c r="O796" t="n">
+        <v>0.1348620088</v>
+      </c>
+      <c r="P796" t="inlineStr"/>
+      <c r="Q796" t="n">
+        <v>6.696e-07</v>
+      </c>
+      <c r="R796" t="inlineStr"/>
+      <c r="S796" t="inlineStr"/>
+      <c r="T796" t="inlineStr"/>
+      <c r="U796" t="inlineStr"/>
+      <c r="V796" t="inlineStr"/>
+      <c r="W796" t="inlineStr"/>
+      <c r="X796" t="inlineStr"/>
+      <c r="Y796" t="inlineStr"/>
+      <c r="Z796" t="inlineStr"/>
+      <c r="AA796" t="n">
+        <v>0.0238846334608</v>
+      </c>
+      <c r="AB796" t="n">
+        <v>52.50648</v>
+      </c>
+      <c r="AC796" t="n">
+        <v>11.8687193635192</v>
+      </c>
+      <c r="AD796" t="n">
+        <v>0.09650667</v>
+      </c>
+      <c r="AE796" t="n">
+        <v>1679.889821357127</v>
+      </c>
+      <c r="AF796" t="inlineStr"/>
+      <c r="AG796" t="n">
+        <v>0.018675992</v>
+      </c>
+      <c r="AH796" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="2" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B797" t="n">
+        <v>0.4778429255</v>
+      </c>
+      <c r="C797" t="n">
+        <v>0.067663344</v>
+      </c>
+      <c r="D797" t="inlineStr"/>
+      <c r="E797" t="inlineStr"/>
+      <c r="F797" t="inlineStr"/>
+      <c r="G797" t="inlineStr"/>
+      <c r="H797" t="inlineStr"/>
+      <c r="I797" t="n">
+        <v>0.03277167599999999</v>
+      </c>
+      <c r="J797" t="inlineStr"/>
+      <c r="K797" t="n">
+        <v>1624.472312140707</v>
+      </c>
+      <c r="L797" t="inlineStr"/>
+      <c r="M797" t="inlineStr"/>
+      <c r="N797" t="inlineStr"/>
+      <c r="O797" t="n">
+        <v>0.134265432</v>
+      </c>
+      <c r="P797" t="inlineStr"/>
+      <c r="Q797" t="n">
+        <v>6.527999999999999e-07</v>
+      </c>
+      <c r="R797" t="inlineStr"/>
+      <c r="S797" t="inlineStr"/>
+      <c r="T797" t="inlineStr"/>
+      <c r="U797" t="inlineStr"/>
+      <c r="V797" t="inlineStr"/>
+      <c r="W797" t="inlineStr"/>
+      <c r="X797" t="inlineStr"/>
+      <c r="Y797" t="inlineStr"/>
+      <c r="Z797" t="inlineStr"/>
+      <c r="AA797" t="n">
+        <v>0.0238889298592</v>
+      </c>
+      <c r="AB797" t="n">
+        <v>50.81856</v>
+      </c>
+      <c r="AC797" t="n">
+        <v>11.7010294510048</v>
+      </c>
+      <c r="AD797" t="n">
+        <v>0.09614215</v>
+      </c>
+      <c r="AE797" t="n">
+        <v>1687.842914073871</v>
+      </c>
+      <c r="AF797" t="inlineStr"/>
+      <c r="AG797" t="n">
+        <v>0.018437372</v>
+      </c>
+      <c r="AH797" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH797"/>
+  <dimension ref="A1:AH801"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61575,9 +61575,7 @@
       <c r="AG778" t="n">
         <v>0.018222614</v>
       </c>
-      <c r="AH778" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH778" t="inlineStr"/>
     </row>
     <row r="779">
       <c r="A779" s="2" t="n">
@@ -61703,9 +61701,7 @@
       <c r="AG780" t="n">
         <v>0.017463007</v>
       </c>
-      <c r="AH780" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH780" t="inlineStr"/>
     </row>
     <row r="781">
       <c r="A781" s="2" t="n">
@@ -62081,15 +62077,13 @@
         <v>0.107761225</v>
       </c>
       <c r="AE786" t="n">
-        <v>1656.387694154607</v>
+        <v>1656.387694154608</v>
       </c>
       <c r="AF786" t="inlineStr"/>
       <c r="AG786" t="n">
         <v>0.017327789</v>
       </c>
-      <c r="AH786" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH786" t="inlineStr"/>
     </row>
     <row r="787">
       <c r="A787" s="2" t="n">
@@ -62151,9 +62145,7 @@
       <c r="AG787" t="n">
         <v>0.018059557</v>
       </c>
-      <c r="AH787" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH787" t="inlineStr"/>
     </row>
     <row r="788">
       <c r="A788" s="2" t="n">
@@ -62727,9 +62719,7 @@
       <c r="AG796" t="n">
         <v>0.018675992</v>
       </c>
-      <c r="AH796" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH796" t="inlineStr"/>
     </row>
     <row r="797">
       <c r="A797" s="2" t="n">
@@ -62795,6 +62785,254 @@
         <v>0</v>
       </c>
     </row>
+    <row r="798">
+      <c r="A798" s="2" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B798" t="n">
+        <v>0.47959375</v>
+      </c>
+      <c r="C798" t="n">
+        <v>0.06815225150000001</v>
+      </c>
+      <c r="D798" t="inlineStr"/>
+      <c r="E798" t="inlineStr"/>
+      <c r="F798" t="inlineStr"/>
+      <c r="G798" t="inlineStr"/>
+      <c r="H798" t="inlineStr"/>
+      <c r="I798" t="n">
+        <v>0.033019812</v>
+      </c>
+      <c r="J798" t="inlineStr"/>
+      <c r="K798" t="n">
+        <v>1627.908790286668</v>
+      </c>
+      <c r="L798" t="inlineStr"/>
+      <c r="M798" t="inlineStr"/>
+      <c r="N798" t="inlineStr"/>
+      <c r="O798" t="n">
+        <v>0.1352256592</v>
+      </c>
+      <c r="P798" t="inlineStr"/>
+      <c r="Q798" t="n">
+        <v>6.576e-07</v>
+      </c>
+      <c r="R798" t="inlineStr"/>
+      <c r="S798" t="inlineStr"/>
+      <c r="T798" t="inlineStr"/>
+      <c r="U798" t="inlineStr"/>
+      <c r="V798" t="inlineStr"/>
+      <c r="W798" t="inlineStr"/>
+      <c r="X798" t="inlineStr"/>
+      <c r="Y798" t="inlineStr"/>
+      <c r="Z798" t="inlineStr"/>
+      <c r="AA798" t="n">
+        <v>0.0238898846144</v>
+      </c>
+      <c r="AB798" t="n">
+        <v>50.48264</v>
+      </c>
+      <c r="AC798" t="n">
+        <v>11.4960751134872</v>
+      </c>
+      <c r="AD798" t="n">
+        <v>0.09559537</v>
+      </c>
+      <c r="AE798" t="n">
+        <v>1690.74149969707</v>
+      </c>
+      <c r="AF798" t="inlineStr"/>
+      <c r="AG798" t="n">
+        <v>0.018516912</v>
+      </c>
+      <c r="AH798" t="inlineStr"/>
+    </row>
+    <row r="799">
+      <c r="A799" s="2" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B799" t="n">
+        <v>0.4872299255</v>
+      </c>
+      <c r="C799" t="n">
+        <v>0.07105407200000001</v>
+      </c>
+      <c r="D799" t="inlineStr"/>
+      <c r="E799" t="inlineStr"/>
+      <c r="F799" t="inlineStr"/>
+      <c r="G799" t="inlineStr"/>
+      <c r="H799" t="inlineStr"/>
+      <c r="I799" t="n">
+        <v>0.034012356</v>
+      </c>
+      <c r="J799" t="inlineStr"/>
+      <c r="K799" t="n">
+        <v>1631.836193882052</v>
+      </c>
+      <c r="L799" t="inlineStr"/>
+      <c r="M799" t="inlineStr"/>
+      <c r="N799" t="inlineStr"/>
+      <c r="O799" t="n">
+        <v>0.1367420576</v>
+      </c>
+      <c r="P799" t="inlineStr"/>
+      <c r="Q799" t="n">
+        <v>7.151999999999999e-07</v>
+      </c>
+      <c r="R799" t="inlineStr"/>
+      <c r="S799" t="inlineStr"/>
+      <c r="T799" t="inlineStr"/>
+      <c r="U799" t="inlineStr"/>
+      <c r="V799" t="inlineStr"/>
+      <c r="W799" t="inlineStr"/>
+      <c r="X799" t="inlineStr"/>
+      <c r="Y799" t="inlineStr"/>
+      <c r="Z799" t="inlineStr"/>
+      <c r="AA799" t="n">
+        <v>0.023889168548</v>
+      </c>
+      <c r="AB799" t="n">
+        <v>52.86424</v>
+      </c>
+      <c r="AC799" t="n">
+        <v>11.831454938516</v>
+      </c>
+      <c r="AD799" t="n">
+        <v>0.09892161499999999</v>
+      </c>
+      <c r="AE799" t="n">
+        <v>1697.402764698416</v>
+      </c>
+      <c r="AF799" t="inlineStr"/>
+      <c r="AG799" t="n">
+        <v>0.019025968</v>
+      </c>
+      <c r="AH799" t="inlineStr"/>
+    </row>
+    <row r="800">
+      <c r="A800" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B800" t="n">
+        <v>0.474981157</v>
+      </c>
+      <c r="C800" t="n">
+        <v>0.0687934655</v>
+      </c>
+      <c r="D800" t="inlineStr"/>
+      <c r="E800" t="inlineStr"/>
+      <c r="F800" t="inlineStr"/>
+      <c r="G800" t="inlineStr"/>
+      <c r="H800" t="inlineStr"/>
+      <c r="I800" t="n">
+        <v>0.03287802</v>
+      </c>
+      <c r="J800" t="inlineStr"/>
+      <c r="K800" t="n">
+        <v>1595.998636074173</v>
+      </c>
+      <c r="L800" t="inlineStr"/>
+      <c r="M800" t="inlineStr"/>
+      <c r="N800" t="inlineStr"/>
+      <c r="O800" t="n">
+        <v>0.1345934304</v>
+      </c>
+      <c r="P800" t="inlineStr"/>
+      <c r="Q800" t="n">
+        <v>6.792e-07</v>
+      </c>
+      <c r="R800" t="inlineStr"/>
+      <c r="S800" t="inlineStr"/>
+      <c r="T800" t="inlineStr"/>
+      <c r="U800" t="inlineStr"/>
+      <c r="V800" t="inlineStr"/>
+      <c r="W800" t="inlineStr"/>
+      <c r="X800" t="inlineStr"/>
+      <c r="Y800" t="inlineStr"/>
+      <c r="Z800" t="inlineStr"/>
+      <c r="AA800" t="n">
+        <v>0.023889168548</v>
+      </c>
+      <c r="AB800" t="n">
+        <v>49.58304</v>
+      </c>
+      <c r="AC800" t="n">
+        <v>11.1979597134616</v>
+      </c>
+      <c r="AD800" t="n">
+        <v>0.09650667</v>
+      </c>
+      <c r="AE800" t="n">
+        <v>1657.629592463283</v>
+      </c>
+      <c r="AF800" t="inlineStr"/>
+      <c r="AG800" t="n">
+        <v>0.018314085</v>
+      </c>
+      <c r="AH800" t="inlineStr"/>
+    </row>
+    <row r="801">
+      <c r="A801" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B801" t="n">
+        <v>0.47616675</v>
+      </c>
+      <c r="C801" t="n">
+        <v>0.0698730605</v>
+      </c>
+      <c r="D801" t="inlineStr"/>
+      <c r="E801" t="inlineStr"/>
+      <c r="F801" t="inlineStr"/>
+      <c r="G801" t="inlineStr"/>
+      <c r="H801" t="inlineStr"/>
+      <c r="I801" t="n">
+        <v>0.032714073</v>
+      </c>
+      <c r="J801" t="inlineStr"/>
+      <c r="K801" t="n">
+        <v>1594.525859725904</v>
+      </c>
+      <c r="L801" t="inlineStr"/>
+      <c r="M801" t="inlineStr"/>
+      <c r="N801" t="inlineStr"/>
+      <c r="O801" t="n">
+        <v>0.1357842072</v>
+      </c>
+      <c r="P801" t="inlineStr"/>
+      <c r="Q801" t="n">
+        <v>6.72e-07</v>
+      </c>
+      <c r="R801" t="inlineStr"/>
+      <c r="S801" t="inlineStr"/>
+      <c r="T801" t="inlineStr"/>
+      <c r="U801" t="inlineStr"/>
+      <c r="V801" t="inlineStr"/>
+      <c r="W801" t="inlineStr"/>
+      <c r="X801" t="inlineStr"/>
+      <c r="Y801" t="inlineStr"/>
+      <c r="Z801" t="inlineStr"/>
+      <c r="AA801" t="n">
+        <v>0.023893942324</v>
+      </c>
+      <c r="AB801" t="n">
+        <v>48.438</v>
+      </c>
+      <c r="AC801" t="n">
+        <v>10.9557409509408</v>
+      </c>
+      <c r="AD801" t="n">
+        <v>0.09764579500000001</v>
+      </c>
+      <c r="AE801" t="n">
+        <v>1654.774056893869</v>
+      </c>
+      <c r="AF801" t="inlineStr"/>
+      <c r="AG801" t="n">
+        <v>0.018377717</v>
+      </c>
+      <c r="AH801" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH801"/>
+  <dimension ref="A1:AH802"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61383,9 +61383,7 @@
       <c r="AG775" t="n">
         <v>0.017315858</v>
       </c>
-      <c r="AH775" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH775" t="inlineStr"/>
     </row>
     <row r="776">
       <c r="A776" s="2" t="n">
@@ -61447,9 +61445,7 @@
       <c r="AG776" t="n">
         <v>0.017824914</v>
       </c>
-      <c r="AH776" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH776" t="inlineStr"/>
     </row>
     <row r="777">
       <c r="A777" s="2" t="n">
@@ -61511,9 +61507,7 @@
       <c r="AG777" t="n">
         <v>0.017840822</v>
       </c>
-      <c r="AH777" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH777" t="inlineStr"/>
     </row>
     <row r="778">
       <c r="A778" s="2" t="n">
@@ -61827,9 +61821,7 @@
       <c r="AG782" t="n">
         <v>0.01741926</v>
       </c>
-      <c r="AH782" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH782" t="inlineStr"/>
     </row>
     <row r="783">
       <c r="A783" s="2" t="n">
@@ -61891,9 +61883,7 @@
       <c r="AG783" t="n">
         <v>0.017809006</v>
       </c>
-      <c r="AH783" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH783" t="inlineStr"/>
     </row>
     <row r="784">
       <c r="A784" s="2" t="n">
@@ -62077,7 +62067,7 @@
         <v>0.107761225</v>
       </c>
       <c r="AE786" t="n">
-        <v>1656.387694154608</v>
+        <v>1656.387694154607</v>
       </c>
       <c r="AF786" t="inlineStr"/>
       <c r="AG786" t="n">
@@ -62335,9 +62325,7 @@
       <c r="AG790" t="n">
         <v>0.017964109</v>
       </c>
-      <c r="AH790" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH790" t="inlineStr"/>
     </row>
     <row r="791">
       <c r="A791" s="2" t="n">
@@ -62399,9 +62387,7 @@
       <c r="AG791" t="n">
         <v>0.018695877</v>
       </c>
-      <c r="AH791" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH791" t="inlineStr"/>
     </row>
     <row r="792">
       <c r="A792" s="2" t="n">
@@ -62591,9 +62577,7 @@
       <c r="AG794" t="n">
         <v>0.018640199</v>
       </c>
-      <c r="AH794" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH794" t="inlineStr"/>
     </row>
     <row r="795">
       <c r="A795" s="2" t="n">
@@ -62655,9 +62639,7 @@
       <c r="AG795" t="n">
         <v>0.018747578</v>
       </c>
-      <c r="AH795" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH795" t="inlineStr"/>
     </row>
     <row r="796">
       <c r="A796" s="2" t="n">
@@ -62839,7 +62821,7 @@
         <v>0.09559537</v>
       </c>
       <c r="AE798" t="n">
-        <v>1690.74149969707</v>
+        <v>1690.741499697069</v>
       </c>
       <c r="AF798" t="inlineStr"/>
       <c r="AG798" t="n">
@@ -63033,6 +63015,68 @@
       </c>
       <c r="AH801" t="inlineStr"/>
     </row>
+    <row r="802">
+      <c r="A802" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B802" t="n">
+        <v>0.476682886</v>
+      </c>
+      <c r="C802" t="n">
+        <v>0.06945467200000001</v>
+      </c>
+      <c r="D802" t="inlineStr"/>
+      <c r="E802" t="inlineStr"/>
+      <c r="F802" t="inlineStr"/>
+      <c r="G802" t="inlineStr"/>
+      <c r="H802" t="inlineStr"/>
+      <c r="I802" t="n">
+        <v>0.032647608</v>
+      </c>
+      <c r="J802" t="inlineStr"/>
+      <c r="K802" t="n">
+        <v>1599.435114220134</v>
+      </c>
+      <c r="L802" t="inlineStr"/>
+      <c r="M802" t="inlineStr"/>
+      <c r="N802" t="inlineStr"/>
+      <c r="O802" t="n">
+        <v>0.1359505832</v>
+      </c>
+      <c r="P802" t="inlineStr"/>
+      <c r="Q802" t="n">
+        <v>6.527999999999999e-07</v>
+      </c>
+      <c r="R802" t="inlineStr"/>
+      <c r="S802" t="inlineStr"/>
+      <c r="T802" t="inlineStr"/>
+      <c r="U802" t="inlineStr"/>
+      <c r="V802" t="inlineStr"/>
+      <c r="W802" t="inlineStr"/>
+      <c r="X802" t="inlineStr"/>
+      <c r="Y802" t="inlineStr"/>
+      <c r="Z802" t="inlineStr"/>
+      <c r="AA802" t="n">
+        <v>0.0238932262576</v>
+      </c>
+      <c r="AB802" t="n">
+        <v>48.62</v>
+      </c>
+      <c r="AC802" t="n">
+        <v>9.930969263352798</v>
+      </c>
+      <c r="AD802" t="n">
+        <v>0.096369975</v>
+      </c>
+      <c r="AE802" t="n">
+        <v>1658.839158551744</v>
+      </c>
+      <c r="AF802" t="inlineStr"/>
+      <c r="AG802" t="n">
+        <v>0.018075465</v>
+      </c>
+      <c r="AH802" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH802"/>
+  <dimension ref="A1:AH803"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61631,9 +61631,7 @@
       <c r="AG779" t="n">
         <v>0.017832868</v>
       </c>
-      <c r="AH779" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH779" t="inlineStr"/>
     </row>
     <row r="780">
       <c r="A780" s="2" t="n">
@@ -61757,9 +61755,7 @@
       <c r="AG781" t="n">
         <v>0.017363582</v>
       </c>
-      <c r="AH781" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH781" t="inlineStr"/>
     </row>
     <row r="782">
       <c r="A782" s="2" t="n">
@@ -61945,9 +61941,7 @@
       <c r="AG784" t="n">
         <v>0.017757305</v>
       </c>
-      <c r="AH784" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH784" t="inlineStr"/>
     </row>
     <row r="785">
       <c r="A785" s="2" t="n">
@@ -62067,7 +62061,7 @@
         <v>0.107761225</v>
       </c>
       <c r="AE786" t="n">
-        <v>1656.387694154607</v>
+        <v>1656.387694154608</v>
       </c>
       <c r="AF786" t="inlineStr"/>
       <c r="AG786" t="n">
@@ -62513,9 +62507,7 @@
       <c r="AG793" t="n">
         <v>0.018839049</v>
       </c>
-      <c r="AH793" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH793" t="inlineStr"/>
     </row>
     <row r="794">
       <c r="A794" s="2" t="n">
@@ -62763,9 +62755,7 @@
       <c r="AG797" t="n">
         <v>0.018437372</v>
       </c>
-      <c r="AH797" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH797" t="inlineStr"/>
     </row>
     <row r="798">
       <c r="A798" s="2" t="n">
@@ -63077,6 +63067,68 @@
       </c>
       <c r="AH802" t="inlineStr"/>
     </row>
+    <row r="803">
+      <c r="A803" s="2" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B803" t="n">
+        <v>0.482611149</v>
+      </c>
+      <c r="C803" t="n">
+        <v>0.06973056850000001</v>
+      </c>
+      <c r="D803" t="inlineStr"/>
+      <c r="E803" t="inlineStr"/>
+      <c r="F803" t="inlineStr"/>
+      <c r="G803" t="inlineStr"/>
+      <c r="H803" t="inlineStr"/>
+      <c r="I803" t="n">
+        <v>0.033015381</v>
+      </c>
+      <c r="J803" t="inlineStr"/>
+      <c r="K803" t="n">
+        <v>1613.671952253401</v>
+      </c>
+      <c r="L803" t="inlineStr"/>
+      <c r="M803" t="inlineStr"/>
+      <c r="N803" t="inlineStr"/>
+      <c r="O803" t="n">
+        <v>0.1407041832</v>
+      </c>
+      <c r="P803" t="inlineStr"/>
+      <c r="Q803" t="n">
+        <v>6.623999999999999e-07</v>
+      </c>
+      <c r="R803" t="inlineStr"/>
+      <c r="S803" t="inlineStr"/>
+      <c r="T803" t="inlineStr"/>
+      <c r="U803" t="inlineStr"/>
+      <c r="V803" t="inlineStr"/>
+      <c r="W803" t="inlineStr"/>
+      <c r="X803" t="inlineStr"/>
+      <c r="Y803" t="inlineStr"/>
+      <c r="Z803" t="inlineStr"/>
+      <c r="AA803" t="n">
+        <v>0.023883201328</v>
+      </c>
+      <c r="AB803" t="n">
+        <v>48.89559999999999</v>
+      </c>
+      <c r="AC803" t="n">
+        <v>9.819175988343201</v>
+      </c>
+      <c r="AD803" t="n">
+        <v>0.09887604999999999</v>
+      </c>
+      <c r="AE803" t="n">
+        <v>1673.253676603172</v>
+      </c>
+      <c r="AF803" t="inlineStr"/>
+      <c r="AG803" t="n">
+        <v>0.018127166</v>
+      </c>
+      <c r="AH803" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH803"/>
+  <dimension ref="A1:AH804"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62003,9 +62003,7 @@
       <c r="AG785" t="n">
         <v>0.017502777</v>
       </c>
-      <c r="AH785" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH785" t="inlineStr"/>
     </row>
     <row r="786">
       <c r="A786" s="2" t="n">
@@ -62061,7 +62059,7 @@
         <v>0.107761225</v>
       </c>
       <c r="AE786" t="n">
-        <v>1656.387694154608</v>
+        <v>1656.387694154607</v>
       </c>
       <c r="AF786" t="inlineStr"/>
       <c r="AG786" t="n">
@@ -62443,9 +62441,7 @@
       <c r="AG792" t="n">
         <v>0.018719739</v>
       </c>
-      <c r="AH792" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH792" t="inlineStr"/>
     </row>
     <row r="793">
       <c r="A793" s="2" t="n">
@@ -62811,7 +62807,7 @@
         <v>0.09559537</v>
       </c>
       <c r="AE798" t="n">
-        <v>1690.741499697069</v>
+        <v>1690.74149969707</v>
       </c>
       <c r="AF798" t="inlineStr"/>
       <c r="AG798" t="n">
@@ -63129,6 +63125,68 @@
       </c>
       <c r="AH803" t="inlineStr"/>
     </row>
+    <row r="804">
+      <c r="A804" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B804" t="n">
+        <v>0.4685147059999999</v>
+      </c>
+      <c r="C804" t="n">
+        <v>0.06770551</v>
+      </c>
+      <c r="D804" t="inlineStr"/>
+      <c r="E804" t="inlineStr"/>
+      <c r="F804" t="inlineStr"/>
+      <c r="G804" t="inlineStr"/>
+      <c r="H804" t="inlineStr"/>
+      <c r="I804" t="n">
+        <v>0.032288697</v>
+      </c>
+      <c r="J804" t="inlineStr"/>
+      <c r="K804" t="n">
+        <v>1600.907890568403</v>
+      </c>
+      <c r="L804" t="inlineStr"/>
+      <c r="M804" t="inlineStr"/>
+      <c r="N804" t="inlineStr"/>
+      <c r="O804" t="n">
+        <v>0.1395205368</v>
+      </c>
+      <c r="P804" t="inlineStr"/>
+      <c r="Q804" t="n">
+        <v>6.599999999999999e-07</v>
+      </c>
+      <c r="R804" t="inlineStr"/>
+      <c r="S804" t="inlineStr"/>
+      <c r="T804" t="inlineStr"/>
+      <c r="U804" t="inlineStr"/>
+      <c r="V804" t="inlineStr"/>
+      <c r="W804" t="inlineStr"/>
+      <c r="X804" t="inlineStr"/>
+      <c r="Y804" t="inlineStr"/>
+      <c r="Z804" t="inlineStr"/>
+      <c r="AA804" t="n">
+        <v>0.023889168548</v>
+      </c>
+      <c r="AB804" t="n">
+        <v>47.6008</v>
+      </c>
+      <c r="AC804" t="n">
+        <v>9.949601475854401</v>
+      </c>
+      <c r="AD804" t="n">
+        <v>0.09568649999999999</v>
+      </c>
+      <c r="AE804" t="n">
+        <v>1659.303519909605</v>
+      </c>
+      <c r="AF804" t="inlineStr"/>
+      <c r="AG804" t="n">
+        <v>0.017622087</v>
+      </c>
+      <c r="AH804" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH804"/>
+  <dimension ref="A1:AH806"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62059,7 +62059,7 @@
         <v>0.107761225</v>
       </c>
       <c r="AE786" t="n">
-        <v>1656.387694154607</v>
+        <v>1656.387694154608</v>
       </c>
       <c r="AF786" t="inlineStr"/>
       <c r="AG786" t="n">
@@ -62807,7 +62807,7 @@
         <v>0.09559537</v>
       </c>
       <c r="AE798" t="n">
-        <v>1690.74149969707</v>
+        <v>1690.741499697069</v>
       </c>
       <c r="AF798" t="inlineStr"/>
       <c r="AG798" t="n">
@@ -63187,6 +63187,130 @@
       </c>
       <c r="AH804" t="inlineStr"/>
     </row>
+    <row r="805">
+      <c r="A805" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B805" t="n">
+        <v>0.468036118</v>
+      </c>
+      <c r="C805" t="n">
+        <v>0.067063569</v>
+      </c>
+      <c r="D805" t="inlineStr"/>
+      <c r="E805" t="inlineStr"/>
+      <c r="F805" t="inlineStr"/>
+      <c r="G805" t="inlineStr"/>
+      <c r="H805" t="inlineStr"/>
+      <c r="I805" t="n">
+        <v>0.031881045</v>
+      </c>
+      <c r="J805" t="inlineStr"/>
+      <c r="K805" t="n">
+        <v>1609.744548658017</v>
+      </c>
+      <c r="L805" t="inlineStr"/>
+      <c r="M805" t="inlineStr"/>
+      <c r="N805" t="inlineStr"/>
+      <c r="O805" t="n">
+        <v>0.1366968984</v>
+      </c>
+      <c r="P805" t="inlineStr"/>
+      <c r="Q805" t="n">
+        <v>6.648e-07</v>
+      </c>
+      <c r="R805" t="inlineStr"/>
+      <c r="S805" t="inlineStr"/>
+      <c r="T805" t="inlineStr"/>
+      <c r="U805" t="inlineStr"/>
+      <c r="V805" t="inlineStr"/>
+      <c r="W805" t="inlineStr"/>
+      <c r="X805" t="inlineStr"/>
+      <c r="Y805" t="inlineStr"/>
+      <c r="Z805" t="inlineStr"/>
+      <c r="AA805" t="n">
+        <v>0.0238872590376</v>
+      </c>
+      <c r="AB805" t="n">
+        <v>48.01783999999999</v>
+      </c>
+      <c r="AC805" t="n">
+        <v>9.614221650825598</v>
+      </c>
+      <c r="AD805" t="n">
+        <v>0.094820765</v>
+      </c>
+      <c r="AE805" t="n">
+        <v>1668.21659485308</v>
+      </c>
+      <c r="AF805" t="inlineStr"/>
+      <c r="AG805" t="n">
+        <v>0.017598225</v>
+      </c>
+      <c r="AH805" t="inlineStr"/>
+    </row>
+    <row r="806">
+      <c r="A806" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B806" t="n">
+        <v>0.4735965</v>
+      </c>
+      <c r="C806" t="n">
+        <v>0.068532836</v>
+      </c>
+      <c r="D806" t="inlineStr"/>
+      <c r="E806" t="inlineStr"/>
+      <c r="F806" t="inlineStr"/>
+      <c r="G806" t="inlineStr"/>
+      <c r="H806" t="inlineStr"/>
+      <c r="I806" t="n">
+        <v>0.032625453</v>
+      </c>
+      <c r="J806" t="inlineStr"/>
+      <c r="K806" t="n">
+        <v>1604.344368714364</v>
+      </c>
+      <c r="L806" t="inlineStr"/>
+      <c r="M806" t="inlineStr"/>
+      <c r="N806" t="inlineStr"/>
+      <c r="O806" t="n">
+        <v>0.1398651728</v>
+      </c>
+      <c r="P806" t="inlineStr"/>
+      <c r="Q806" t="n">
+        <v>6.984e-07</v>
+      </c>
+      <c r="R806" t="inlineStr"/>
+      <c r="S806" t="inlineStr"/>
+      <c r="T806" t="inlineStr"/>
+      <c r="U806" t="inlineStr"/>
+      <c r="V806" t="inlineStr"/>
+      <c r="W806" t="inlineStr"/>
+      <c r="X806" t="inlineStr"/>
+      <c r="Y806" t="inlineStr"/>
+      <c r="Z806" t="inlineStr"/>
+      <c r="AA806" t="n">
+        <v>0.0238908393696</v>
+      </c>
+      <c r="AB806" t="n">
+        <v>50.94128</v>
+      </c>
+      <c r="AC806" t="n">
+        <v>11.1047986509536</v>
+      </c>
+      <c r="AD806" t="n">
+        <v>0.097007885</v>
+      </c>
+      <c r="AE806" t="n">
+        <v>1667.243739962887</v>
+      </c>
+      <c r="AF806" t="inlineStr"/>
+      <c r="AG806" t="n">
+        <v>0.017773213</v>
+      </c>
+      <c r="AH806" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH806"/>
+  <dimension ref="A1:AH808"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62059,7 +62059,7 @@
         <v>0.107761225</v>
       </c>
       <c r="AE786" t="n">
-        <v>1656.387694154608</v>
+        <v>1656.387694154607</v>
       </c>
       <c r="AF786" t="inlineStr"/>
       <c r="AG786" t="n">
@@ -62189,9 +62189,7 @@
       <c r="AG788" t="n">
         <v>0.017968086</v>
       </c>
-      <c r="AH788" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH788" t="inlineStr"/>
     </row>
     <row r="789">
       <c r="A789" s="2" t="n">
@@ -63311,6 +63309,130 @@
       </c>
       <c r="AH806" t="inlineStr"/>
     </row>
+    <row r="807">
+      <c r="A807" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B807" t="n">
+        <v>0.473224</v>
+      </c>
+      <c r="C807" t="n">
+        <v>0.067629175</v>
+      </c>
+      <c r="D807" t="inlineStr"/>
+      <c r="E807" t="inlineStr"/>
+      <c r="F807" t="inlineStr"/>
+      <c r="G807" t="inlineStr"/>
+      <c r="H807" t="inlineStr"/>
+      <c r="I807" t="n">
+        <v>0.032594436</v>
+      </c>
+      <c r="J807" t="inlineStr"/>
+      <c r="K807" t="n">
+        <v>1614.162877702824</v>
+      </c>
+      <c r="L807" t="inlineStr"/>
+      <c r="M807" t="inlineStr"/>
+      <c r="N807" t="inlineStr"/>
+      <c r="O807" t="n">
+        <v>0.140076708</v>
+      </c>
+      <c r="P807" t="inlineStr"/>
+      <c r="Q807" t="n">
+        <v>6.984e-07</v>
+      </c>
+      <c r="R807" t="inlineStr"/>
+      <c r="S807" t="inlineStr"/>
+      <c r="T807" t="inlineStr"/>
+      <c r="U807" t="inlineStr"/>
+      <c r="V807" t="inlineStr"/>
+      <c r="W807" t="inlineStr"/>
+      <c r="X807" t="inlineStr"/>
+      <c r="Y807" t="inlineStr"/>
+      <c r="Z807" t="inlineStr"/>
+      <c r="AA807" t="n">
+        <v>0.0238872590376</v>
+      </c>
+      <c r="AB807" t="n">
+        <v>50.26736</v>
+      </c>
+      <c r="AC807" t="n">
+        <v>10.2290846633784</v>
+      </c>
+      <c r="AD807" t="n">
+        <v>0.09714457999999999</v>
+      </c>
+      <c r="AE807" t="n">
+        <v>1675.51149733264</v>
+      </c>
+      <c r="AF807" t="inlineStr"/>
+      <c r="AG807" t="n">
+        <v>0.01761811</v>
+      </c>
+      <c r="AH807" t="inlineStr"/>
+    </row>
+    <row r="808">
+      <c r="A808" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B808" t="n">
+        <v>0.477593872</v>
+      </c>
+      <c r="C808" t="n">
+        <v>0.0679654125</v>
+      </c>
+      <c r="D808" t="inlineStr"/>
+      <c r="E808" t="inlineStr"/>
+      <c r="F808" t="inlineStr"/>
+      <c r="G808" t="inlineStr"/>
+      <c r="H808" t="inlineStr"/>
+      <c r="I808" t="n">
+        <v>0.032678625</v>
+      </c>
+      <c r="J808" t="inlineStr"/>
+      <c r="K808" t="n">
+        <v>1606.798995961479</v>
+      </c>
+      <c r="L808" t="inlineStr"/>
+      <c r="M808" t="inlineStr"/>
+      <c r="N808" t="inlineStr"/>
+      <c r="O808" t="n">
+        <v>0.1409870224</v>
+      </c>
+      <c r="P808" t="inlineStr"/>
+      <c r="Q808" t="n">
+        <v>6.911999999999999e-07</v>
+      </c>
+      <c r="R808" t="inlineStr"/>
+      <c r="S808" t="inlineStr"/>
+      <c r="T808" t="inlineStr"/>
+      <c r="U808" t="inlineStr"/>
+      <c r="V808" t="inlineStr"/>
+      <c r="W808" t="inlineStr"/>
+      <c r="X808" t="inlineStr"/>
+      <c r="Y808" t="inlineStr"/>
+      <c r="Z808" t="inlineStr"/>
+      <c r="AA808" t="n">
+        <v>0.0238841560832</v>
+      </c>
+      <c r="AB808" t="n">
+        <v>52.68328</v>
+      </c>
+      <c r="AC808" t="n">
+        <v>10.1731880258736</v>
+      </c>
+      <c r="AD808" t="n">
+        <v>0.09723571</v>
+      </c>
+      <c r="AE808" t="n">
+        <v>1670.513646321536</v>
+      </c>
+      <c r="AF808" t="inlineStr"/>
+      <c r="AG808" t="n">
+        <v>0.017836845</v>
+      </c>
+      <c r="AH808" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH808"/>
+  <dimension ref="A1:AH810"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62251,9 +62251,7 @@
       <c r="AG789" t="n">
         <v>0.017872638</v>
       </c>
-      <c r="AH789" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH789" t="inlineStr"/>
     </row>
     <row r="790">
       <c r="A790" s="2" t="n">
@@ -63433,6 +63431,130 @@
       </c>
       <c r="AH808" t="inlineStr"/>
     </row>
+    <row r="809">
+      <c r="A809" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B809" t="n">
+        <v>0.4817559635</v>
+      </c>
+      <c r="C809" t="n">
+        <v>0.06938851500000001</v>
+      </c>
+      <c r="D809" t="inlineStr"/>
+      <c r="E809" t="inlineStr"/>
+      <c r="F809" t="inlineStr"/>
+      <c r="G809" t="inlineStr"/>
+      <c r="H809" t="inlineStr"/>
+      <c r="I809" t="n">
+        <v>0.032807124</v>
+      </c>
+      <c r="J809" t="inlineStr"/>
+      <c r="K809" t="n">
+        <v>1607.289921410902</v>
+      </c>
+      <c r="L809" t="inlineStr"/>
+      <c r="M809" t="inlineStr"/>
+      <c r="N809" t="inlineStr"/>
+      <c r="O809" t="n">
+        <v>0.141146268</v>
+      </c>
+      <c r="P809" t="inlineStr"/>
+      <c r="Q809" t="n">
+        <v>6.911999999999999e-07</v>
+      </c>
+      <c r="R809" t="inlineStr"/>
+      <c r="S809" t="inlineStr"/>
+      <c r="T809" t="inlineStr"/>
+      <c r="U809" t="inlineStr"/>
+      <c r="V809" t="inlineStr"/>
+      <c r="W809" t="inlineStr"/>
+      <c r="X809" t="inlineStr"/>
+      <c r="Y809" t="inlineStr"/>
+      <c r="Z809" t="inlineStr"/>
+      <c r="AA809" t="n">
+        <v>0.0238889298592</v>
+      </c>
+      <c r="AB809" t="n">
+        <v>53.274</v>
+      </c>
+      <c r="AC809" t="n">
+        <v>10.0054981133592</v>
+      </c>
+      <c r="AD809" t="n">
+        <v>0.09778249</v>
+      </c>
+      <c r="AE809" t="n">
+        <v>1671.434217246821</v>
+      </c>
+      <c r="AF809" t="inlineStr"/>
+      <c r="AG809" t="n">
+        <v>0.018027741</v>
+      </c>
+      <c r="AH809" t="inlineStr"/>
+    </row>
+    <row r="810">
+      <c r="A810" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B810" t="n">
+        <v>0.4792108945</v>
+      </c>
+      <c r="C810" t="n">
+        <v>0.06921403500000001</v>
+      </c>
+      <c r="D810" t="inlineStr"/>
+      <c r="E810" t="inlineStr"/>
+      <c r="F810" t="inlineStr"/>
+      <c r="G810" t="inlineStr"/>
+      <c r="H810" t="inlineStr"/>
+      <c r="I810" t="n">
+        <v>0.03221337</v>
+      </c>
+      <c r="J810" t="inlineStr"/>
+      <c r="K810" t="n">
+        <v>1606.308070512056</v>
+      </c>
+      <c r="L810" t="inlineStr"/>
+      <c r="M810" t="inlineStr"/>
+      <c r="N810" t="inlineStr"/>
+      <c r="O810" t="n">
+        <v>0.1407992552</v>
+      </c>
+      <c r="P810" t="inlineStr"/>
+      <c r="Q810" t="n">
+        <v>6.744000000000001e-07</v>
+      </c>
+      <c r="R810" t="inlineStr"/>
+      <c r="S810" t="inlineStr"/>
+      <c r="T810" t="inlineStr"/>
+      <c r="U810" t="inlineStr"/>
+      <c r="V810" t="inlineStr"/>
+      <c r="W810" t="inlineStr"/>
+      <c r="X810" t="inlineStr"/>
+      <c r="Y810" t="inlineStr"/>
+      <c r="Z810" t="inlineStr"/>
+      <c r="AA810" t="n">
+        <v>0.0238865429712</v>
+      </c>
+      <c r="AB810" t="n">
+        <v>52.26</v>
+      </c>
+      <c r="AC810" t="n">
+        <v>10.0241303258608</v>
+      </c>
+      <c r="AD810" t="n">
+        <v>0.09696232</v>
+      </c>
+      <c r="AE810" t="n">
+        <v>1669.452563394988</v>
+      </c>
+      <c r="AF810" t="inlineStr"/>
+      <c r="AG810" t="n">
+        <v>0.018075465</v>
+      </c>
+      <c r="AH810" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH810"/>
+  <dimension ref="A1:AH811"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62059,7 +62059,7 @@
         <v>0.107761225</v>
       </c>
       <c r="AE786" t="n">
-        <v>1656.387694154607</v>
+        <v>1656.387694154608</v>
       </c>
       <c r="AF786" t="inlineStr"/>
       <c r="AG786" t="n">
@@ -63555,6 +63555,68 @@
       </c>
       <c r="AH810" t="inlineStr"/>
     </row>
+    <row r="811">
+      <c r="A811" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B811" t="n">
+        <v>0.4836777655</v>
+      </c>
+      <c r="C811" t="n">
+        <v>0.06958044300000001</v>
+      </c>
+      <c r="D811" t="inlineStr"/>
+      <c r="E811" t="inlineStr"/>
+      <c r="F811" t="inlineStr"/>
+      <c r="G811" t="inlineStr"/>
+      <c r="H811" t="inlineStr"/>
+      <c r="I811" t="n">
+        <v>0.032638746</v>
+      </c>
+      <c r="J811" t="inlineStr"/>
+      <c r="K811" t="n">
+        <v>1607.780846860325</v>
+      </c>
+      <c r="L811" t="inlineStr"/>
+      <c r="M811" t="inlineStr"/>
+      <c r="N811" t="inlineStr"/>
+      <c r="O811" t="n">
+        <v>0.1408420376</v>
+      </c>
+      <c r="P811" t="inlineStr"/>
+      <c r="Q811" t="n">
+        <v>6.744000000000001e-07</v>
+      </c>
+      <c r="R811" t="inlineStr"/>
+      <c r="S811" t="inlineStr"/>
+      <c r="T811" t="inlineStr"/>
+      <c r="U811" t="inlineStr"/>
+      <c r="V811" t="inlineStr"/>
+      <c r="W811" t="inlineStr"/>
+      <c r="X811" t="inlineStr"/>
+      <c r="Y811" t="inlineStr"/>
+      <c r="Z811" t="inlineStr"/>
+      <c r="AA811" t="n">
+        <v>0.0238786662408</v>
+      </c>
+      <c r="AB811" t="n">
+        <v>53.19911999999999</v>
+      </c>
+      <c r="AC811" t="n">
+        <v>10.3222457258864</v>
+      </c>
+      <c r="AD811" t="n">
+        <v>0.09787362000000001</v>
+      </c>
+      <c r="AE811" t="n">
+        <v>1672.168815796952</v>
+      </c>
+      <c r="AF811" t="inlineStr"/>
+      <c r="AG811" t="n">
+        <v>0.018111258</v>
+      </c>
+      <c r="AH811" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH811"/>
+  <dimension ref="A1:AH812"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63617,6 +63617,68 @@
       </c>
       <c r="AH811" t="inlineStr"/>
     </row>
+    <row r="812">
+      <c r="A812" s="2" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B812" t="n">
+        <v>0.48397137</v>
+      </c>
+      <c r="C812" t="n">
+        <v>0.069673499</v>
+      </c>
+      <c r="D812" t="inlineStr"/>
+      <c r="E812" t="inlineStr"/>
+      <c r="F812" t="inlineStr"/>
+      <c r="G812" t="inlineStr"/>
+      <c r="H812" t="inlineStr"/>
+      <c r="I812" t="n">
+        <v>0.033680031</v>
+      </c>
+      <c r="J812" t="inlineStr"/>
+      <c r="K812" t="n">
+        <v>1615.635654051093</v>
+      </c>
+      <c r="L812" t="inlineStr"/>
+      <c r="M812" t="inlineStr"/>
+      <c r="N812" t="inlineStr"/>
+      <c r="O812" t="n">
+        <v>0.1427648688</v>
+      </c>
+      <c r="P812" t="inlineStr"/>
+      <c r="Q812" t="n">
+        <v>6.839999999999999e-07</v>
+      </c>
+      <c r="R812" t="inlineStr"/>
+      <c r="S812" t="inlineStr"/>
+      <c r="T812" t="inlineStr"/>
+      <c r="U812" t="inlineStr"/>
+      <c r="V812" t="inlineStr"/>
+      <c r="W812" t="inlineStr"/>
+      <c r="X812" t="inlineStr"/>
+      <c r="Y812" t="inlineStr"/>
+      <c r="Z812" t="inlineStr"/>
+      <c r="AA812" t="n">
+        <v>0.023885588216</v>
+      </c>
+      <c r="AB812" t="n">
+        <v>52.85592</v>
+      </c>
+      <c r="AC812" t="n">
+        <v>10.527200063404</v>
+      </c>
+      <c r="AD812" t="n">
+        <v>0.09851152999999999</v>
+      </c>
+      <c r="AE812" t="n">
+        <v>1679.889563839513</v>
+      </c>
+      <c r="AF812" t="inlineStr"/>
+      <c r="AG812" t="n">
+        <v>0.018302154</v>
+      </c>
+      <c r="AH812" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH812"/>
+  <dimension ref="A1:AH814"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63485,7 +63485,7 @@
         <v>0.09778249</v>
       </c>
       <c r="AE809" t="n">
-        <v>1671.434217246821</v>
+        <v>1671.43421724682</v>
       </c>
       <c r="AF809" t="inlineStr"/>
       <c r="AG809" t="n">
@@ -63679,6 +63679,130 @@
       </c>
       <c r="AH812" t="inlineStr"/>
     </row>
+    <row r="813">
+      <c r="A813" s="2" t="n">
+        <v>46243</v>
+      </c>
+      <c r="B813" t="n">
+        <v>0.4835168455</v>
+      </c>
+      <c r="C813" t="n">
+        <v>0.0694521275</v>
+      </c>
+      <c r="D813" t="inlineStr"/>
+      <c r="E813" t="inlineStr"/>
+      <c r="F813" t="inlineStr"/>
+      <c r="G813" t="inlineStr"/>
+      <c r="H813" t="inlineStr"/>
+      <c r="I813" t="n">
+        <v>0.033795237</v>
+      </c>
+      <c r="J813" t="inlineStr"/>
+      <c r="K813" t="n">
+        <v>1619.563057646477</v>
+      </c>
+      <c r="L813" t="inlineStr"/>
+      <c r="M813" t="inlineStr"/>
+      <c r="N813" t="inlineStr"/>
+      <c r="O813" t="n">
+        <v>0.1431380264</v>
+      </c>
+      <c r="P813" t="inlineStr"/>
+      <c r="Q813" t="n">
+        <v>6.911999999999999e-07</v>
+      </c>
+      <c r="R813" t="inlineStr"/>
+      <c r="S813" t="inlineStr"/>
+      <c r="T813" t="inlineStr"/>
+      <c r="U813" t="inlineStr"/>
+      <c r="V813" t="inlineStr"/>
+      <c r="W813" t="inlineStr"/>
+      <c r="X813" t="inlineStr"/>
+      <c r="Y813" t="inlineStr"/>
+      <c r="Z813" t="inlineStr"/>
+      <c r="AA813" t="n">
+        <v>0.0238846334608</v>
+      </c>
+      <c r="AB813" t="n">
+        <v>53.02856</v>
+      </c>
+      <c r="AC813" t="n">
+        <v>10.6017289134104</v>
+      </c>
+      <c r="AD813" t="n">
+        <v>0.09787362000000001</v>
+      </c>
+      <c r="AE813" t="n">
+        <v>1684.063087182948</v>
+      </c>
+      <c r="AF813" t="inlineStr"/>
+      <c r="AG813" t="n">
+        <v>0.018079442</v>
+      </c>
+      <c r="AH813" t="inlineStr"/>
+    </row>
+    <row r="814">
+      <c r="A814" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B814" t="n">
+        <v>0.4765765745</v>
+      </c>
+      <c r="C814" t="n">
+        <v>0.06808936600000001</v>
+      </c>
+      <c r="D814" t="inlineStr"/>
+      <c r="E814" t="inlineStr"/>
+      <c r="F814" t="inlineStr"/>
+      <c r="G814" t="inlineStr"/>
+      <c r="H814" t="inlineStr"/>
+      <c r="I814" t="n">
+        <v>0.03367116899999999</v>
+      </c>
+      <c r="J814" t="inlineStr"/>
+      <c r="K814" t="n">
+        <v>1624.472312140707</v>
+      </c>
+      <c r="L814" t="inlineStr"/>
+      <c r="M814" t="inlineStr"/>
+      <c r="N814" t="inlineStr"/>
+      <c r="O814" t="n">
+        <v>0.1424249864</v>
+      </c>
+      <c r="P814" t="inlineStr"/>
+      <c r="Q814" t="n">
+        <v>6.888e-07</v>
+      </c>
+      <c r="R814" t="inlineStr"/>
+      <c r="S814" t="inlineStr"/>
+      <c r="T814" t="inlineStr"/>
+      <c r="U814" t="inlineStr"/>
+      <c r="V814" t="inlineStr"/>
+      <c r="W814" t="inlineStr"/>
+      <c r="X814" t="inlineStr"/>
+      <c r="Y814" t="inlineStr"/>
+      <c r="Z814" t="inlineStr"/>
+      <c r="AA814" t="n">
+        <v>0.023889168548</v>
+      </c>
+      <c r="AB814" t="n">
+        <v>51.6204</v>
+      </c>
+      <c r="AC814" t="n">
+        <v>10.1359236008704</v>
+      </c>
+      <c r="AD814" t="n">
+        <v>0.09719014500000001</v>
+      </c>
+      <c r="AE814" t="n">
+        <v>1687.088430017826</v>
+      </c>
+      <c r="AF814" t="inlineStr"/>
+      <c r="AG814" t="n">
+        <v>0.017952178</v>
+      </c>
+      <c r="AH814" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH814"/>
+  <dimension ref="A1:AH817"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62059,7 +62059,7 @@
         <v>0.107761225</v>
       </c>
       <c r="AE786" t="n">
-        <v>1656.387694154608</v>
+        <v>1656.387694154607</v>
       </c>
       <c r="AF786" t="inlineStr"/>
       <c r="AG786" t="n">
@@ -62803,7 +62803,7 @@
         <v>0.09559537</v>
       </c>
       <c r="AE798" t="n">
-        <v>1690.741499697069</v>
+        <v>1690.74149969707</v>
       </c>
       <c r="AF798" t="inlineStr"/>
       <c r="AG798" t="n">
@@ -63485,7 +63485,7 @@
         <v>0.09778249</v>
       </c>
       <c r="AE809" t="n">
-        <v>1671.43421724682</v>
+        <v>1671.434217246821</v>
       </c>
       <c r="AF809" t="inlineStr"/>
       <c r="AG809" t="n">
@@ -63803,6 +63803,192 @@
       </c>
       <c r="AH814" t="inlineStr"/>
     </row>
+    <row r="815">
+      <c r="A815" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B815" t="n">
+        <v>0.47382</v>
+      </c>
+      <c r="C815" t="n">
+        <v>0.0684321465</v>
+      </c>
+      <c r="D815" t="inlineStr"/>
+      <c r="E815" t="inlineStr"/>
+      <c r="F815" t="inlineStr"/>
+      <c r="G815" t="inlineStr"/>
+      <c r="H815" t="inlineStr"/>
+      <c r="I815" t="n">
+        <v>0.03380853</v>
+      </c>
+      <c r="J815" t="inlineStr"/>
+      <c r="K815" t="n">
+        <v>1645.582106465896</v>
+      </c>
+      <c r="L815" t="inlineStr"/>
+      <c r="M815" t="inlineStr"/>
+      <c r="N815" t="inlineStr"/>
+      <c r="O815" t="n">
+        <v>0.1465748792</v>
+      </c>
+      <c r="P815" t="inlineStr"/>
+      <c r="Q815" t="n">
+        <v>6.816e-07</v>
+      </c>
+      <c r="R815" t="inlineStr"/>
+      <c r="S815" t="inlineStr"/>
+      <c r="T815" t="inlineStr"/>
+      <c r="U815" t="inlineStr"/>
+      <c r="V815" t="inlineStr"/>
+      <c r="W815" t="inlineStr"/>
+      <c r="X815" t="inlineStr"/>
+      <c r="Y815" t="inlineStr"/>
+      <c r="Z815" t="inlineStr"/>
+      <c r="AA815" t="n">
+        <v>0.02388678166</v>
+      </c>
+      <c r="AB815" t="n">
+        <v>50.07496</v>
+      </c>
+      <c r="AC815" t="n">
+        <v>9.968233688355999</v>
+      </c>
+      <c r="AD815" t="n">
+        <v>0.09741797000000001</v>
+      </c>
+      <c r="AE815" t="n">
+        <v>1706.487336493212</v>
+      </c>
+      <c r="AF815" t="inlineStr"/>
+      <c r="AG815" t="n">
+        <v>0.01809535</v>
+      </c>
+      <c r="AH815" t="inlineStr"/>
+    </row>
+    <row r="816">
+      <c r="A816" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B816" t="n">
+        <v>0.4729259255</v>
+      </c>
+      <c r="C816" t="n">
+        <v>0.06833109350000001</v>
+      </c>
+      <c r="D816" t="inlineStr"/>
+      <c r="E816" t="inlineStr"/>
+      <c r="F816" t="inlineStr"/>
+      <c r="G816" t="inlineStr"/>
+      <c r="H816" t="inlineStr"/>
+      <c r="I816" t="n">
+        <v>0.033511653</v>
+      </c>
+      <c r="J816" t="inlineStr"/>
+      <c r="K816" t="n">
+        <v>1650.982286409549</v>
+      </c>
+      <c r="L816" t="inlineStr"/>
+      <c r="M816" t="inlineStr"/>
+      <c r="N816" t="inlineStr"/>
+      <c r="O816" t="n">
+        <v>0.1450893792</v>
+      </c>
+      <c r="P816" t="inlineStr"/>
+      <c r="Q816" t="n">
+        <v>6.432e-07</v>
+      </c>
+      <c r="R816" t="inlineStr"/>
+      <c r="S816" t="inlineStr"/>
+      <c r="T816" t="inlineStr"/>
+      <c r="U816" t="inlineStr"/>
+      <c r="V816" t="inlineStr"/>
+      <c r="W816" t="inlineStr"/>
+      <c r="X816" t="inlineStr"/>
+      <c r="Y816" t="inlineStr"/>
+      <c r="Z816" t="inlineStr"/>
+      <c r="AA816" t="n">
+        <v>0.0238910780584</v>
+      </c>
+      <c r="AB816" t="n">
+        <v>50.9808</v>
+      </c>
+      <c r="AC816" t="n">
+        <v>9.595589438324</v>
+      </c>
+      <c r="AD816" t="n">
+        <v>0.097007885</v>
+      </c>
+      <c r="AE816" t="n">
+        <v>1712.417286258331</v>
+      </c>
+      <c r="AF816" t="inlineStr"/>
+      <c r="AG816" t="n">
+        <v>0.017852753</v>
+      </c>
+      <c r="AH816" t="inlineStr"/>
+    </row>
+    <row r="817">
+      <c r="A817" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B817" t="n">
+        <v>0.473006907</v>
+      </c>
+      <c r="C817" t="n">
+        <v>0.06856155250000001</v>
+      </c>
+      <c r="D817" t="inlineStr"/>
+      <c r="E817" t="inlineStr"/>
+      <c r="F817" t="inlineStr"/>
+      <c r="G817" t="inlineStr"/>
+      <c r="H817" t="inlineStr"/>
+      <c r="I817" t="n">
+        <v>0.033799668</v>
+      </c>
+      <c r="J817" t="inlineStr"/>
+      <c r="K817" t="n">
+        <v>1642.145628319935</v>
+      </c>
+      <c r="L817" t="inlineStr"/>
+      <c r="M817" t="inlineStr"/>
+      <c r="N817" t="inlineStr"/>
+      <c r="O817" t="n">
+        <v>0.1451535528</v>
+      </c>
+      <c r="P817" t="inlineStr"/>
+      <c r="Q817" t="n">
+        <v>6.456e-07</v>
+      </c>
+      <c r="R817" t="inlineStr"/>
+      <c r="S817" t="inlineStr"/>
+      <c r="T817" t="inlineStr"/>
+      <c r="U817" t="inlineStr"/>
+      <c r="V817" t="inlineStr"/>
+      <c r="W817" t="inlineStr"/>
+      <c r="X817" t="inlineStr"/>
+      <c r="Y817" t="inlineStr"/>
+      <c r="Z817" t="inlineStr"/>
+      <c r="AA817" t="n">
+        <v>0.0238884524816</v>
+      </c>
+      <c r="AB817" t="n">
+        <v>51.05672</v>
+      </c>
+      <c r="AC817" t="n">
+        <v>9.409267313308</v>
+      </c>
+      <c r="AD817" t="n">
+        <v>0.09413729</v>
+      </c>
+      <c r="AE817" t="n">
+        <v>1703.467988615625</v>
+      </c>
+      <c r="AF817" t="inlineStr"/>
+      <c r="AG817" t="n">
+        <v>0.017824914</v>
+      </c>
+      <c r="AH817" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH817"/>
+  <dimension ref="A1:AH819"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63485,7 +63485,7 @@
         <v>0.09778249</v>
       </c>
       <c r="AE809" t="n">
-        <v>1671.434217246821</v>
+        <v>1671.43421724682</v>
       </c>
       <c r="AF809" t="inlineStr"/>
       <c r="AG809" t="n">
@@ -63981,13 +63981,137 @@
         <v>0.09413729</v>
       </c>
       <c r="AE817" t="n">
-        <v>1703.467988615625</v>
+        <v>1703.467988615624</v>
       </c>
       <c r="AF817" t="inlineStr"/>
       <c r="AG817" t="n">
         <v>0.017824914</v>
       </c>
       <c r="AH817" t="inlineStr"/>
+    </row>
+    <row r="818">
+      <c r="A818" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B818" t="n">
+        <v>0.469674522</v>
+      </c>
+      <c r="C818" t="n">
+        <v>0.06841797000000001</v>
+      </c>
+      <c r="D818" t="inlineStr"/>
+      <c r="E818" t="inlineStr"/>
+      <c r="F818" t="inlineStr"/>
+      <c r="G818" t="inlineStr"/>
+      <c r="H818" t="inlineStr"/>
+      <c r="I818" t="n">
+        <v>0.03340974</v>
+      </c>
+      <c r="J818" t="inlineStr"/>
+      <c r="K818" t="n">
+        <v>1633.308970230321</v>
+      </c>
+      <c r="L818" t="inlineStr"/>
+      <c r="M818" t="inlineStr"/>
+      <c r="N818" t="inlineStr"/>
+      <c r="O818" t="n">
+        <v>0.1444999328</v>
+      </c>
+      <c r="P818" t="inlineStr"/>
+      <c r="Q818" t="n">
+        <v>6.408e-07</v>
+      </c>
+      <c r="R818" t="inlineStr"/>
+      <c r="S818" t="inlineStr"/>
+      <c r="T818" t="inlineStr"/>
+      <c r="U818" t="inlineStr"/>
+      <c r="V818" t="inlineStr"/>
+      <c r="W818" t="inlineStr"/>
+      <c r="X818" t="inlineStr"/>
+      <c r="Y818" t="inlineStr"/>
+      <c r="Z818" t="inlineStr"/>
+      <c r="AA818" t="n">
+        <v>0.0238896459256</v>
+      </c>
+      <c r="AB818" t="n">
+        <v>51.30007999999999</v>
+      </c>
+      <c r="AC818" t="n">
+        <v>9.372002888304799</v>
+      </c>
+      <c r="AD818" t="n">
+        <v>0.093362685</v>
+      </c>
+      <c r="AE818" t="n">
+        <v>1694.831751377151</v>
+      </c>
+      <c r="AF818" t="inlineStr"/>
+      <c r="AG818" t="n">
+        <v>0.017443122</v>
+      </c>
+      <c r="AH818" t="inlineStr"/>
+    </row>
+    <row r="819">
+      <c r="A819" s="2" t="n">
+        <v>46249</v>
+      </c>
+      <c r="B819" t="n">
+        <v>0.4699907745</v>
+      </c>
+      <c r="C819" t="n">
+        <v>0.06843396400000001</v>
+      </c>
+      <c r="D819" t="inlineStr"/>
+      <c r="E819" t="inlineStr"/>
+      <c r="F819" t="inlineStr"/>
+      <c r="G819" t="inlineStr"/>
+      <c r="H819" t="inlineStr"/>
+      <c r="I819" t="n">
+        <v>0.033387585</v>
+      </c>
+      <c r="J819" t="inlineStr"/>
+      <c r="K819" t="n">
+        <v>1625.945088488976</v>
+      </c>
+      <c r="L819" t="inlineStr"/>
+      <c r="M819" t="inlineStr"/>
+      <c r="N819" t="inlineStr"/>
+      <c r="O819" t="n">
+        <v>0.1444523968</v>
+      </c>
+      <c r="P819" t="inlineStr"/>
+      <c r="Q819" t="n">
+        <v>6.287999999999999e-07</v>
+      </c>
+      <c r="R819" t="inlineStr"/>
+      <c r="S819" t="inlineStr"/>
+      <c r="T819" t="inlineStr"/>
+      <c r="U819" t="inlineStr"/>
+      <c r="V819" t="inlineStr"/>
+      <c r="W819" t="inlineStr"/>
+      <c r="X819" t="inlineStr"/>
+      <c r="Y819" t="inlineStr"/>
+      <c r="Z819" t="inlineStr"/>
+      <c r="AA819" t="n">
+        <v>0.0238910780584</v>
+      </c>
+      <c r="AB819" t="n">
+        <v>50.74784</v>
+      </c>
+      <c r="AC819" t="n">
+        <v>9.2788418257968</v>
+      </c>
+      <c r="AD819" t="n">
+        <v>0.09281590499999999</v>
+      </c>
+      <c r="AE819" t="n">
+        <v>1686.822289170931</v>
+      </c>
+      <c r="AF819" t="inlineStr"/>
+      <c r="AG819" t="n">
+        <v>0.017546524</v>
+      </c>
+      <c r="AH819" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH819"/>
+  <dimension ref="A1:AH820"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63981,7 +63981,7 @@
         <v>0.09413729</v>
       </c>
       <c r="AE817" t="n">
-        <v>1703.467988615624</v>
+        <v>1703.467988615625</v>
       </c>
       <c r="AF817" t="inlineStr"/>
       <c r="AG817" t="n">
@@ -64113,6 +64113,68 @@
       </c>
       <c r="AH819" t="inlineStr"/>
     </row>
+    <row r="820">
+      <c r="A820" s="2" t="n">
+        <v>46250</v>
+      </c>
+      <c r="B820" t="n">
+        <v>0.468605</v>
+      </c>
+      <c r="C820" t="n">
+        <v>0.06819260000000001</v>
+      </c>
+      <c r="D820" t="inlineStr"/>
+      <c r="E820" t="inlineStr"/>
+      <c r="F820" t="inlineStr"/>
+      <c r="G820" t="inlineStr"/>
+      <c r="H820" t="inlineStr"/>
+      <c r="I820" t="n">
+        <v>0.033059691</v>
+      </c>
+      <c r="J820" t="inlineStr"/>
+      <c r="K820" t="n">
+        <v>1625.945088488976</v>
+      </c>
+      <c r="L820" t="inlineStr"/>
+      <c r="M820" t="inlineStr"/>
+      <c r="N820" t="inlineStr"/>
+      <c r="O820" t="n">
+        <v>0.1433162864</v>
+      </c>
+      <c r="P820" t="inlineStr"/>
+      <c r="Q820" t="n">
+        <v>6.168e-07</v>
+      </c>
+      <c r="R820" t="inlineStr"/>
+      <c r="S820" t="inlineStr"/>
+      <c r="T820" t="inlineStr"/>
+      <c r="U820" t="inlineStr"/>
+      <c r="V820" t="inlineStr"/>
+      <c r="W820" t="inlineStr"/>
+      <c r="X820" t="inlineStr"/>
+      <c r="Y820" t="inlineStr"/>
+      <c r="Z820" t="inlineStr"/>
+      <c r="AA820" t="n">
+        <v>0.0238913167472</v>
+      </c>
+      <c r="AB820" t="n">
+        <v>50.58559999999999</v>
+      </c>
+      <c r="AC820" t="n">
+        <v>8.999358638272801</v>
+      </c>
+      <c r="AD820" t="n">
+        <v>0.0929526</v>
+      </c>
+      <c r="AE820" t="n">
+        <v>1686.377627670196</v>
+      </c>
+      <c r="AF820" t="inlineStr"/>
+      <c r="AG820" t="n">
+        <v>0.017562432</v>
+      </c>
+      <c r="AH820" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH820"/>
+  <dimension ref="A1:AH821"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62803,7 +62803,7 @@
         <v>0.09559537</v>
       </c>
       <c r="AE798" t="n">
-        <v>1690.74149969707</v>
+        <v>1690.741499697069</v>
       </c>
       <c r="AF798" t="inlineStr"/>
       <c r="AG798" t="n">
@@ -63485,7 +63485,7 @@
         <v>0.09778249</v>
       </c>
       <c r="AE809" t="n">
-        <v>1671.43421724682</v>
+        <v>1671.434217246821</v>
       </c>
       <c r="AF809" t="inlineStr"/>
       <c r="AG809" t="n">
@@ -63981,7 +63981,7 @@
         <v>0.09413729</v>
       </c>
       <c r="AE817" t="n">
-        <v>1703.467988615625</v>
+        <v>1703.467988615624</v>
       </c>
       <c r="AF817" t="inlineStr"/>
       <c r="AG817" t="n">
@@ -64175,6 +64175,68 @@
       </c>
       <c r="AH820" t="inlineStr"/>
     </row>
+    <row r="821">
+      <c r="A821" s="2" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B821" t="n">
+        <v>0.480764145</v>
+      </c>
+      <c r="C821" t="n">
+        <v>0.06955936</v>
+      </c>
+      <c r="D821" t="inlineStr"/>
+      <c r="E821" t="inlineStr"/>
+      <c r="F821" t="inlineStr"/>
+      <c r="G821" t="inlineStr"/>
+      <c r="H821" t="inlineStr"/>
+      <c r="I821" t="n">
+        <v>0.033684462</v>
+      </c>
+      <c r="J821" t="inlineStr"/>
+      <c r="K821" t="n">
+        <v>1626.436013938399</v>
+      </c>
+      <c r="L821" t="inlineStr"/>
+      <c r="M821" t="inlineStr"/>
+      <c r="N821" t="inlineStr"/>
+      <c r="O821" t="n">
+        <v>0.143986544</v>
+      </c>
+      <c r="P821" t="inlineStr"/>
+      <c r="Q821" t="n">
+        <v>6.216e-07</v>
+      </c>
+      <c r="R821" t="inlineStr"/>
+      <c r="S821" t="inlineStr"/>
+      <c r="T821" t="inlineStr"/>
+      <c r="U821" t="inlineStr"/>
+      <c r="V821" t="inlineStr"/>
+      <c r="W821" t="inlineStr"/>
+      <c r="X821" t="inlineStr"/>
+      <c r="Y821" t="inlineStr"/>
+      <c r="Z821" t="inlineStr"/>
+      <c r="AA821" t="n">
+        <v>0.02388797510399999</v>
+      </c>
+      <c r="AB821" t="n">
+        <v>53.46432</v>
+      </c>
+      <c r="AC821" t="n">
+        <v>8.813036513256799</v>
+      </c>
+      <c r="AD821" t="n">
+        <v>0.093636075</v>
+      </c>
+      <c r="AE821" t="n">
+        <v>1689.57661512336</v>
+      </c>
+      <c r="AF821" t="inlineStr"/>
+      <c r="AG821" t="n">
+        <v>0.017725489</v>
+      </c>
+      <c r="AH821" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH821"/>
+  <dimension ref="A1:AH822"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62803,7 +62803,7 @@
         <v>0.09559537</v>
       </c>
       <c r="AE798" t="n">
-        <v>1690.741499697069</v>
+        <v>1690.74149969707</v>
       </c>
       <c r="AF798" t="inlineStr"/>
       <c r="AG798" t="n">
@@ -63485,7 +63485,7 @@
         <v>0.09778249</v>
       </c>
       <c r="AE809" t="n">
-        <v>1671.434217246821</v>
+        <v>1671.43421724682</v>
       </c>
       <c r="AF809" t="inlineStr"/>
       <c r="AG809" t="n">
@@ -64237,6 +64237,68 @@
       </c>
       <c r="AH821" t="inlineStr"/>
     </row>
+    <row r="822">
+      <c r="A822" s="2" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B822" t="n">
+        <v>0.482204379</v>
+      </c>
+      <c r="C822" t="n">
+        <v>0.0697138475</v>
+      </c>
+      <c r="D822" t="inlineStr"/>
+      <c r="E822" t="inlineStr"/>
+      <c r="F822" t="inlineStr"/>
+      <c r="G822" t="inlineStr"/>
+      <c r="H822" t="inlineStr"/>
+      <c r="I822" t="n">
+        <v>0.034140855</v>
+      </c>
+      <c r="J822" t="inlineStr"/>
+      <c r="K822" t="n">
+        <v>1634.290821129167</v>
+      </c>
+      <c r="L822" t="inlineStr"/>
+      <c r="M822" t="inlineStr"/>
+      <c r="N822" t="inlineStr"/>
+      <c r="O822" t="n">
+        <v>0.1435444592</v>
+      </c>
+      <c r="P822" t="inlineStr"/>
+      <c r="Q822" t="n">
+        <v>6.191999999999999e-07</v>
+      </c>
+      <c r="R822" t="inlineStr"/>
+      <c r="S822" t="inlineStr"/>
+      <c r="T822" t="inlineStr"/>
+      <c r="U822" t="inlineStr"/>
+      <c r="V822" t="inlineStr"/>
+      <c r="W822" t="inlineStr"/>
+      <c r="X822" t="inlineStr"/>
+      <c r="Y822" t="inlineStr"/>
+      <c r="Z822" t="inlineStr"/>
+      <c r="AA822" t="n">
+        <v>0.0238836787056</v>
+      </c>
+      <c r="AB822" t="n">
+        <v>52.9256</v>
+      </c>
+      <c r="AC822" t="n">
+        <v>8.7012432382472</v>
+      </c>
+      <c r="AD822" t="n">
+        <v>0.09281590499999999</v>
+      </c>
+      <c r="AE822" t="n">
+        <v>1696.78161803702</v>
+      </c>
+      <c r="AF822" t="inlineStr"/>
+      <c r="AG822" t="n">
+        <v>0.017649926</v>
+      </c>
+      <c r="AH822" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -63485,7 +63485,7 @@
         <v>0.09778249</v>
       </c>
       <c r="AE809" t="n">
-        <v>1671.43421724682</v>
+        <v>1671.434217246821</v>
       </c>
       <c r="AF809" t="inlineStr"/>
       <c r="AG809" t="n">
@@ -63981,7 +63981,7 @@
         <v>0.09413729</v>
       </c>
       <c r="AE817" t="n">
-        <v>1703.467988615624</v>
+        <v>1703.467988615625</v>
       </c>
       <c r="AF817" t="inlineStr"/>
       <c r="AG817" t="n">

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH822"/>
+  <dimension ref="A1:AH825"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63485,7 +63485,7 @@
         <v>0.09778249</v>
       </c>
       <c r="AE809" t="n">
-        <v>1671.434217246821</v>
+        <v>1671.43421724682</v>
       </c>
       <c r="AF809" t="inlineStr"/>
       <c r="AG809" t="n">
@@ -64299,6 +64299,192 @@
       </c>
       <c r="AH822" t="inlineStr"/>
     </row>
+    <row r="823">
+      <c r="A823" s="2" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B823" t="n">
+        <v>0.5165441854999999</v>
+      </c>
+      <c r="C823" t="n">
+        <v>0.08188928000000001</v>
+      </c>
+      <c r="D823" t="inlineStr"/>
+      <c r="E823" t="inlineStr"/>
+      <c r="F823" t="inlineStr"/>
+      <c r="G823" t="inlineStr"/>
+      <c r="H823" t="inlineStr"/>
+      <c r="I823" t="n">
+        <v>0.037831878</v>
+      </c>
+      <c r="J823" t="inlineStr"/>
+      <c r="K823" t="n">
+        <v>1641.654702870512</v>
+      </c>
+      <c r="L823" t="inlineStr"/>
+      <c r="M823" t="inlineStr"/>
+      <c r="N823" t="inlineStr"/>
+      <c r="O823" t="n">
+        <v>0.10730421</v>
+      </c>
+      <c r="P823" t="inlineStr"/>
+      <c r="Q823" t="n">
+        <v>6.888e-07</v>
+      </c>
+      <c r="R823" t="inlineStr"/>
+      <c r="S823" t="inlineStr"/>
+      <c r="T823" t="inlineStr"/>
+      <c r="U823" t="inlineStr"/>
+      <c r="V823" t="inlineStr"/>
+      <c r="W823" t="inlineStr"/>
+      <c r="X823" t="inlineStr"/>
+      <c r="Y823" t="inlineStr"/>
+      <c r="Z823" t="inlineStr"/>
+      <c r="AA823" t="n">
+        <v>58.6733047187512</v>
+      </c>
+      <c r="AB823" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC823" t="n">
+        <v>9.055255275777599</v>
+      </c>
+      <c r="AD823" t="n">
+        <v>0.09719014500000001</v>
+      </c>
+      <c r="AE823" t="n">
+        <v>1710.242635612341</v>
+      </c>
+      <c r="AF823" t="inlineStr"/>
+      <c r="AG823" t="n">
+        <v>0.01861236</v>
+      </c>
+      <c r="AH823" t="inlineStr"/>
+    </row>
+    <row r="824">
+      <c r="A824" s="2" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B824" t="n">
+        <v>0.5440373675</v>
+      </c>
+      <c r="C824" t="n">
+        <v>0.08457990700000001</v>
+      </c>
+      <c r="D824" t="inlineStr"/>
+      <c r="E824" t="inlineStr"/>
+      <c r="F824" t="inlineStr"/>
+      <c r="G824" t="inlineStr"/>
+      <c r="H824" t="inlineStr"/>
+      <c r="I824" t="n">
+        <v>0.03884214599999999</v>
+      </c>
+      <c r="J824" t="inlineStr"/>
+      <c r="K824" t="n">
+        <v>1656.873391802625</v>
+      </c>
+      <c r="L824" t="inlineStr"/>
+      <c r="M824" t="inlineStr"/>
+      <c r="N824" t="inlineStr"/>
+      <c r="O824" t="n">
+        <v>0.1119708</v>
+      </c>
+      <c r="P824" t="inlineStr"/>
+      <c r="Q824" t="n">
+        <v>7.704e-07</v>
+      </c>
+      <c r="R824" t="inlineStr"/>
+      <c r="S824" t="inlineStr"/>
+      <c r="T824" t="inlineStr"/>
+      <c r="U824" t="inlineStr"/>
+      <c r="V824" t="inlineStr"/>
+      <c r="W824" t="inlineStr"/>
+      <c r="X824" t="inlineStr"/>
+      <c r="Y824" t="inlineStr"/>
+      <c r="Z824" t="inlineStr"/>
+      <c r="AA824" t="n">
+        <v>58.65512490239841</v>
+      </c>
+      <c r="AB824" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC824" t="n">
+        <v>8.1609090757008</v>
+      </c>
+      <c r="AD824" t="n">
+        <v>0.101655515</v>
+      </c>
+      <c r="AE824" t="n">
+        <v>1724.589530300625</v>
+      </c>
+      <c r="AF824" t="inlineStr"/>
+      <c r="AG824" t="n">
+        <v>0.019018014</v>
+      </c>
+      <c r="AH824" t="inlineStr"/>
+    </row>
+    <row r="825">
+      <c r="A825" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B825" t="n">
+        <v>0.5836183235</v>
+      </c>
+      <c r="C825" t="n">
+        <v>0.09146750500000002</v>
+      </c>
+      <c r="D825" t="inlineStr"/>
+      <c r="E825" t="inlineStr"/>
+      <c r="F825" t="inlineStr"/>
+      <c r="G825" t="inlineStr"/>
+      <c r="H825" t="inlineStr"/>
+      <c r="I825" t="n">
+        <v>0.041527332</v>
+      </c>
+      <c r="J825" t="inlineStr"/>
+      <c r="K825" t="n">
+        <v>1685.837993318582</v>
+      </c>
+      <c r="L825" t="inlineStr"/>
+      <c r="M825" t="inlineStr"/>
+      <c r="N825" t="inlineStr"/>
+      <c r="O825" t="n">
+        <v>0.117477</v>
+      </c>
+      <c r="P825" t="inlineStr"/>
+      <c r="Q825" t="n">
+        <v>9.888e-07</v>
+      </c>
+      <c r="R825" t="inlineStr"/>
+      <c r="S825" t="inlineStr"/>
+      <c r="T825" t="inlineStr"/>
+      <c r="U825" t="inlineStr"/>
+      <c r="V825" t="inlineStr"/>
+      <c r="W825" t="inlineStr"/>
+      <c r="X825" t="inlineStr"/>
+      <c r="Y825" t="inlineStr"/>
+      <c r="Z825" t="inlineStr"/>
+      <c r="AA825" t="n">
+        <v>58.65277911964321</v>
+      </c>
+      <c r="AB825" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC825" t="n">
+        <v>8.9248297882664</v>
+      </c>
+      <c r="AD825" t="n">
+        <v>0.131455025</v>
+      </c>
+      <c r="AE825" t="n">
+        <v>1754.402294109792</v>
+      </c>
+      <c r="AF825" t="inlineStr"/>
+      <c r="AG825" t="n">
+        <v>0.021145709</v>
+      </c>
+      <c r="AH825" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -63485,7 +63485,7 @@
         <v>0.09778249</v>
       </c>
       <c r="AE809" t="n">
-        <v>1671.43421724682</v>
+        <v>1671.434217246821</v>
       </c>
       <c r="AF809" t="inlineStr"/>
       <c r="AG809" t="n">

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH825"/>
+  <dimension ref="A1:AH826"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64485,6 +64485,68 @@
       </c>
       <c r="AH825" t="inlineStr"/>
     </row>
+    <row r="826">
+      <c r="A826" s="2" t="n">
+        <v>46256</v>
+      </c>
+      <c r="B826" t="n">
+        <v>0.5742082285</v>
+      </c>
+      <c r="C826" t="n">
+        <v>0.08806151000000001</v>
+      </c>
+      <c r="D826" t="inlineStr"/>
+      <c r="E826" t="inlineStr"/>
+      <c r="F826" t="inlineStr"/>
+      <c r="G826" t="inlineStr"/>
+      <c r="H826" t="inlineStr"/>
+      <c r="I826" t="n">
+        <v>0.04157164199999999</v>
+      </c>
+      <c r="J826" t="inlineStr"/>
+      <c r="K826" t="n">
+        <v>1689.765396913966</v>
+      </c>
+      <c r="L826" t="inlineStr"/>
+      <c r="M826" t="inlineStr"/>
+      <c r="N826" t="inlineStr"/>
+      <c r="O826" t="n">
+        <v>0.11889288</v>
+      </c>
+      <c r="P826" t="inlineStr"/>
+      <c r="Q826" t="n">
+        <v>9.743999999999999e-07</v>
+      </c>
+      <c r="R826" t="inlineStr"/>
+      <c r="S826" t="inlineStr"/>
+      <c r="T826" t="inlineStr"/>
+      <c r="U826" t="inlineStr"/>
+      <c r="V826" t="inlineStr"/>
+      <c r="W826" t="inlineStr"/>
+      <c r="X826" t="inlineStr"/>
+      <c r="Y826" t="inlineStr"/>
+      <c r="Z826" t="inlineStr"/>
+      <c r="AA826" t="n">
+        <v>58.65336556533201</v>
+      </c>
+      <c r="AB826" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC826" t="n">
+        <v>8.2540701382088</v>
+      </c>
+      <c r="AD826" t="n">
+        <v>0.12603279</v>
+      </c>
+      <c r="AE826" t="n">
+        <v>1757.642460007407</v>
+      </c>
+      <c r="AF826" t="inlineStr"/>
+      <c r="AG826" t="n">
+        <v>0.020859365</v>
+      </c>
+      <c r="AH826" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH826"/>
+  <dimension ref="A1:AH827"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62803,7 +62803,7 @@
         <v>0.09559537</v>
       </c>
       <c r="AE798" t="n">
-        <v>1690.74149969707</v>
+        <v>1690.741499697069</v>
       </c>
       <c r="AF798" t="inlineStr"/>
       <c r="AG798" t="n">
@@ -63485,7 +63485,7 @@
         <v>0.09778249</v>
       </c>
       <c r="AE809" t="n">
-        <v>1671.434217246821</v>
+        <v>1671.43421724682</v>
       </c>
       <c r="AF809" t="inlineStr"/>
       <c r="AG809" t="n">
@@ -64547,6 +64547,68 @@
       </c>
       <c r="AH826" t="inlineStr"/>
     </row>
+    <row r="827">
+      <c r="A827" s="2" t="n">
+        <v>46257</v>
+      </c>
+      <c r="B827" t="n">
+        <v>0.5791183</v>
+      </c>
+      <c r="C827" t="n">
+        <v>0.0895449535</v>
+      </c>
+      <c r="D827" t="inlineStr"/>
+      <c r="E827" t="inlineStr"/>
+      <c r="F827" t="inlineStr"/>
+      <c r="G827" t="inlineStr"/>
+      <c r="H827" t="inlineStr"/>
+      <c r="I827" t="n">
+        <v>0.042285033</v>
+      </c>
+      <c r="J827" t="inlineStr"/>
+      <c r="K827" t="n">
+        <v>1688.292620565697</v>
+      </c>
+      <c r="L827" t="inlineStr"/>
+      <c r="M827" t="inlineStr"/>
+      <c r="N827" t="inlineStr"/>
+      <c r="O827" t="n">
+        <v>0.12010527</v>
+      </c>
+      <c r="P827" t="inlineStr"/>
+      <c r="Q827" t="n">
+        <v>9.839999999999998e-07</v>
+      </c>
+      <c r="R827" t="inlineStr"/>
+      <c r="S827" t="inlineStr"/>
+      <c r="T827" t="inlineStr"/>
+      <c r="U827" t="inlineStr"/>
+      <c r="V827" t="inlineStr"/>
+      <c r="W827" t="inlineStr"/>
+      <c r="X827" t="inlineStr"/>
+      <c r="Y827" t="inlineStr"/>
+      <c r="Z827" t="inlineStr"/>
+      <c r="AA827" t="n">
+        <v>58.6451553256888</v>
+      </c>
+      <c r="AB827" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC827" t="n">
+        <v>8.2540701382088</v>
+      </c>
+      <c r="AD827" t="n">
+        <v>0.12493923</v>
+      </c>
+      <c r="AE827" t="n">
+        <v>1756.168631556095</v>
+      </c>
+      <c r="AF827" t="inlineStr"/>
+      <c r="AG827" t="n">
+        <v>0.020791756</v>
+      </c>
+      <c r="AH827" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH827"/>
+  <dimension ref="A1:AH828"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63485,7 +63485,7 @@
         <v>0.09778249</v>
       </c>
       <c r="AE809" t="n">
-        <v>1671.43421724682</v>
+        <v>1671.434217246821</v>
       </c>
       <c r="AF809" t="inlineStr"/>
       <c r="AG809" t="n">
@@ -63981,7 +63981,7 @@
         <v>0.09413729</v>
       </c>
       <c r="AE817" t="n">
-        <v>1703.467988615625</v>
+        <v>1703.467988615624</v>
       </c>
       <c r="AF817" t="inlineStr"/>
       <c r="AG817" t="n">
@@ -64609,6 +64609,68 @@
       </c>
       <c r="AH827" t="inlineStr"/>
     </row>
+    <row r="828">
+      <c r="A828" s="2" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B828" t="n">
+        <v>0.5884959875</v>
+      </c>
+      <c r="C828" t="n">
+        <v>0.09023196850000001</v>
+      </c>
+      <c r="D828" t="inlineStr"/>
+      <c r="E828" t="inlineStr"/>
+      <c r="F828" t="inlineStr"/>
+      <c r="G828" t="inlineStr"/>
+      <c r="H828" t="inlineStr"/>
+      <c r="I828" t="n">
+        <v>0.043853607</v>
+      </c>
+      <c r="J828" t="inlineStr"/>
+      <c r="K828" t="n">
+        <v>1693.201875059927</v>
+      </c>
+      <c r="L828" t="inlineStr"/>
+      <c r="M828" t="inlineStr"/>
+      <c r="N828" t="inlineStr"/>
+      <c r="O828" t="n">
+        <v>0.12043701</v>
+      </c>
+      <c r="P828" t="inlineStr"/>
+      <c r="Q828" t="n">
+        <v>9.72e-07</v>
+      </c>
+      <c r="R828" t="inlineStr"/>
+      <c r="S828" t="inlineStr"/>
+      <c r="T828" t="inlineStr"/>
+      <c r="U828" t="inlineStr"/>
+      <c r="V828" t="inlineStr"/>
+      <c r="W828" t="inlineStr"/>
+      <c r="X828" t="inlineStr"/>
+      <c r="Y828" t="inlineStr"/>
+      <c r="Z828" t="inlineStr"/>
+      <c r="AA828" t="n">
+        <v>58.650433336888</v>
+      </c>
+      <c r="AB828" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC828" t="n">
+        <v>7.900058100678399</v>
+      </c>
+      <c r="AD828" t="n">
+        <v>0.12348115</v>
+      </c>
+      <c r="AE828" t="n">
+        <v>1760.739412374493</v>
+      </c>
+      <c r="AF828" t="inlineStr"/>
+      <c r="AG828" t="n">
+        <v>0.020545182</v>
+      </c>
+      <c r="AH828" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH828"/>
+  <dimension ref="A1:AH829"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63981,7 +63981,7 @@
         <v>0.09413729</v>
       </c>
       <c r="AE817" t="n">
-        <v>1703.467988615624</v>
+        <v>1703.467988615625</v>
       </c>
       <c r="AF817" t="inlineStr"/>
       <c r="AG817" t="n">
@@ -64671,6 +64671,68 @@
       </c>
       <c r="AH828" t="inlineStr"/>
     </row>
+    <row r="829">
+      <c r="A829" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B829" t="n">
+        <v>0.585116593</v>
+      </c>
+      <c r="C829" t="n">
+        <v>0.088789964</v>
+      </c>
+      <c r="D829" t="inlineStr"/>
+      <c r="E829" t="inlineStr"/>
+      <c r="F829" t="inlineStr"/>
+      <c r="G829" t="inlineStr"/>
+      <c r="H829" t="inlineStr"/>
+      <c r="I829" t="n">
+        <v>0.04280345999999999</v>
+      </c>
+      <c r="J829" t="inlineStr"/>
+      <c r="K829" t="n">
+        <v>1650.982286409549</v>
+      </c>
+      <c r="L829" t="inlineStr"/>
+      <c r="M829" t="inlineStr"/>
+      <c r="N829" t="inlineStr"/>
+      <c r="O829" t="n">
+        <v>0.11874411</v>
+      </c>
+      <c r="P829" t="inlineStr"/>
+      <c r="Q829" t="n">
+        <v>9.168e-07</v>
+      </c>
+      <c r="R829" t="inlineStr"/>
+      <c r="S829" t="inlineStr"/>
+      <c r="T829" t="inlineStr"/>
+      <c r="U829" t="inlineStr"/>
+      <c r="V829" t="inlineStr"/>
+      <c r="W829" t="inlineStr"/>
+      <c r="X829" t="inlineStr"/>
+      <c r="Y829" t="inlineStr"/>
+      <c r="Z829" t="inlineStr"/>
+      <c r="AA829" t="n">
+        <v>58.6480875541328</v>
+      </c>
+      <c r="AB829" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC829" t="n">
+        <v>7.6578393381576</v>
+      </c>
+      <c r="AD829" t="n">
+        <v>0.121157335</v>
+      </c>
+      <c r="AE829" t="n">
+        <v>1718.26469079564</v>
+      </c>
+      <c r="AF829" t="inlineStr"/>
+      <c r="AG829" t="n">
+        <v>0.019865115</v>
+      </c>
+      <c r="AH829" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH829"/>
+  <dimension ref="A1:AH830"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63485,7 +63485,7 @@
         <v>0.09778249</v>
       </c>
       <c r="AE809" t="n">
-        <v>1671.434217246821</v>
+        <v>1671.43421724682</v>
       </c>
       <c r="AF809" t="inlineStr"/>
       <c r="AG809" t="n">
@@ -63981,7 +63981,7 @@
         <v>0.09413729</v>
       </c>
       <c r="AE817" t="n">
-        <v>1703.467988615625</v>
+        <v>1703.467988615624</v>
       </c>
       <c r="AF817" t="inlineStr"/>
       <c r="AG817" t="n">
@@ -64733,6 +64733,68 @@
       </c>
       <c r="AH829" t="inlineStr"/>
     </row>
+    <row r="830">
+      <c r="A830" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B830" t="n">
+        <v>0.5887269374999999</v>
+      </c>
+      <c r="C830" t="n">
+        <v>0.09112145300000002</v>
+      </c>
+      <c r="D830" t="inlineStr"/>
+      <c r="E830" t="inlineStr"/>
+      <c r="F830" t="inlineStr"/>
+      <c r="G830" t="inlineStr"/>
+      <c r="H830" t="inlineStr"/>
+      <c r="I830" t="n">
+        <v>0.04522721699999999</v>
+      </c>
+      <c r="J830" t="inlineStr"/>
+      <c r="K830" t="n">
+        <v>1649.50951006128</v>
+      </c>
+      <c r="L830" t="inlineStr"/>
+      <c r="M830" t="inlineStr"/>
+      <c r="N830" t="inlineStr"/>
+      <c r="O830" t="n">
+        <v>0.12098592</v>
+      </c>
+      <c r="P830" t="inlineStr"/>
+      <c r="Q830" t="n">
+        <v>9.240000000000001e-07</v>
+      </c>
+      <c r="R830" t="inlineStr"/>
+      <c r="S830" t="inlineStr"/>
+      <c r="T830" t="inlineStr"/>
+      <c r="U830" t="inlineStr"/>
+      <c r="V830" t="inlineStr"/>
+      <c r="W830" t="inlineStr"/>
+      <c r="X830" t="inlineStr"/>
+      <c r="Y830" t="inlineStr"/>
+      <c r="Z830" t="inlineStr"/>
+      <c r="AA830" t="n">
+        <v>58.64398243431121</v>
+      </c>
+      <c r="AB830" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC830" t="n">
+        <v>7.6764715506592</v>
+      </c>
+      <c r="AD830" t="n">
+        <v>0.122524285</v>
+      </c>
+      <c r="AE830" t="n">
+        <v>1716.81863860975</v>
+      </c>
+      <c r="AF830" t="inlineStr"/>
+      <c r="AG830" t="n">
+        <v>0.020087827</v>
+      </c>
+      <c r="AH830" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH830"/>
+  <dimension ref="A1:AH831"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63485,7 +63485,7 @@
         <v>0.09778249</v>
       </c>
       <c r="AE809" t="n">
-        <v>1671.43421724682</v>
+        <v>1671.434217246821</v>
       </c>
       <c r="AF809" t="inlineStr"/>
       <c r="AG809" t="n">
@@ -64795,6 +64795,68 @@
       </c>
       <c r="AH830" t="inlineStr"/>
     </row>
+    <row r="831">
+      <c r="A831" s="2" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B831" t="n">
+        <v>0.597859371</v>
+      </c>
+      <c r="C831" t="n">
+        <v>0.09127266900000001</v>
+      </c>
+      <c r="D831" t="inlineStr"/>
+      <c r="E831" t="inlineStr"/>
+      <c r="F831" t="inlineStr"/>
+      <c r="G831" t="inlineStr"/>
+      <c r="H831" t="inlineStr"/>
+      <c r="I831" t="n">
+        <v>0.048359934</v>
+      </c>
+      <c r="J831" t="inlineStr"/>
+      <c r="K831" t="n">
+        <v>1657.855242701471</v>
+      </c>
+      <c r="L831" t="inlineStr"/>
+      <c r="M831" t="inlineStr"/>
+      <c r="N831" t="inlineStr"/>
+      <c r="O831" t="n">
+        <v>0.12172635</v>
+      </c>
+      <c r="P831" t="inlineStr"/>
+      <c r="Q831" t="n">
+        <v>9.359999999999999e-07</v>
+      </c>
+      <c r="R831" t="inlineStr"/>
+      <c r="S831" t="inlineStr"/>
+      <c r="T831" t="inlineStr"/>
+      <c r="U831" t="inlineStr"/>
+      <c r="V831" t="inlineStr"/>
+      <c r="W831" t="inlineStr"/>
+      <c r="X831" t="inlineStr"/>
+      <c r="Y831" t="inlineStr"/>
+      <c r="Z831" t="inlineStr"/>
+      <c r="AA831" t="n">
+        <v>58.6340128576016</v>
+      </c>
+      <c r="AB831" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC831" t="n">
+        <v>7.788264825668799</v>
+      </c>
+      <c r="AD831" t="n">
+        <v>0.122888805</v>
+      </c>
+      <c r="AE831" t="n">
+        <v>1725.279481633742</v>
+      </c>
+      <c r="AF831" t="inlineStr"/>
+      <c r="AG831" t="n">
+        <v>0.019853184</v>
+      </c>
+      <c r="AH831" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH831"/>
+  <dimension ref="A1:AH832"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63485,7 +63485,7 @@
         <v>0.09778249</v>
       </c>
       <c r="AE809" t="n">
-        <v>1671.434217246821</v>
+        <v>1671.43421724682</v>
       </c>
       <c r="AF809" t="inlineStr"/>
       <c r="AG809" t="n">
@@ -64857,6 +64857,68 @@
       </c>
       <c r="AH831" t="inlineStr"/>
     </row>
+    <row r="832">
+      <c r="A832" s="2" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B832" t="n">
+        <v>0.5799517314999999</v>
+      </c>
+      <c r="C832" t="n">
+        <v>0.08879578000000002</v>
+      </c>
+      <c r="D832" t="inlineStr"/>
+      <c r="E832" t="inlineStr"/>
+      <c r="F832" t="inlineStr"/>
+      <c r="G832" t="inlineStr"/>
+      <c r="H832" t="inlineStr"/>
+      <c r="I832" t="n">
+        <v>0.046148865</v>
+      </c>
+      <c r="J832" t="inlineStr"/>
+      <c r="K832" t="n">
+        <v>1675.528558880699</v>
+      </c>
+      <c r="L832" t="inlineStr"/>
+      <c r="M832" t="inlineStr"/>
+      <c r="N832" t="inlineStr"/>
+      <c r="O832" t="n">
+        <v>0.07745155470000001</v>
+      </c>
+      <c r="P832" t="inlineStr"/>
+      <c r="Q832" t="n">
+        <v>8.88e-07</v>
+      </c>
+      <c r="R832" t="inlineStr"/>
+      <c r="S832" t="inlineStr"/>
+      <c r="T832" t="inlineStr"/>
+      <c r="U832" t="inlineStr"/>
+      <c r="V832" t="inlineStr"/>
+      <c r="W832" t="inlineStr"/>
+      <c r="X832" t="inlineStr"/>
+      <c r="Y832" t="inlineStr"/>
+      <c r="Z832" t="inlineStr"/>
+      <c r="AA832" t="n">
+        <v>0.3214978121992</v>
+      </c>
+      <c r="AB832" t="n">
+        <v>59.2333</v>
+      </c>
+      <c r="AC832" t="n">
+        <v>7.9745869506848</v>
+      </c>
+      <c r="AD832" t="n">
+        <v>0.113046765</v>
+      </c>
+      <c r="AE832" t="n">
+        <v>1743.982957768783</v>
+      </c>
+      <c r="AF832" t="inlineStr"/>
+      <c r="AG832" t="n">
+        <v>0.019618541</v>
+      </c>
+      <c r="AH832" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH832"/>
+  <dimension ref="A1:AH833"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63485,7 +63485,7 @@
         <v>0.09778249</v>
       </c>
       <c r="AE809" t="n">
-        <v>1671.43421724682</v>
+        <v>1671.434217246821</v>
       </c>
       <c r="AF809" t="inlineStr"/>
       <c r="AG809" t="n">
@@ -64919,6 +64919,68 @@
       </c>
       <c r="AH832" t="inlineStr"/>
     </row>
+    <row r="833">
+      <c r="A833" s="2" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B833" t="n">
+        <v>0.5828135</v>
+      </c>
+      <c r="C833" t="n">
+        <v>0.08933630450000001</v>
+      </c>
+      <c r="D833" t="inlineStr"/>
+      <c r="E833" t="inlineStr"/>
+      <c r="F833" t="inlineStr"/>
+      <c r="G833" t="inlineStr"/>
+      <c r="H833" t="inlineStr"/>
+      <c r="I833" t="n">
+        <v>0.046795791</v>
+      </c>
+      <c r="J833" t="inlineStr"/>
+      <c r="K833" t="n">
+        <v>1673.564857083007</v>
+      </c>
+      <c r="L833" t="inlineStr"/>
+      <c r="M833" t="inlineStr"/>
+      <c r="N833" t="inlineStr"/>
+      <c r="O833" t="n">
+        <v>0.07757588580000001</v>
+      </c>
+      <c r="P833" t="inlineStr"/>
+      <c r="Q833" t="n">
+        <v>8.760000000000001e-07</v>
+      </c>
+      <c r="R833" t="inlineStr"/>
+      <c r="S833" t="inlineStr"/>
+      <c r="T833" t="inlineStr"/>
+      <c r="U833" t="inlineStr"/>
+      <c r="V833" t="inlineStr"/>
+      <c r="W833" t="inlineStr"/>
+      <c r="X833" t="inlineStr"/>
+      <c r="Y833" t="inlineStr"/>
+      <c r="Z833" t="inlineStr"/>
+      <c r="AA833" t="n">
+        <v>0.3214624506224</v>
+      </c>
+      <c r="AB833" t="n">
+        <v>62.2784</v>
+      </c>
+      <c r="AC833" t="n">
+        <v>8.1422768631992</v>
+      </c>
+      <c r="AD833" t="n">
+        <v>0.11263668</v>
+      </c>
+      <c r="AE833" t="n">
+        <v>1745.235650688128</v>
+      </c>
+      <c r="AF833" t="inlineStr"/>
+      <c r="AG833" t="n">
+        <v>0.019495254</v>
+      </c>
+      <c r="AH833" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -63981,7 +63981,7 @@
         <v>0.09413729</v>
       </c>
       <c r="AE817" t="n">
-        <v>1703.467988615624</v>
+        <v>1703.467988615625</v>
       </c>
       <c r="AF817" t="inlineStr"/>
       <c r="AG817" t="n">

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH833"/>
+  <dimension ref="A1:AH834"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64981,6 +64981,68 @@
       </c>
       <c r="AH833" t="inlineStr"/>
     </row>
+    <row r="834">
+      <c r="A834" s="2" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B834" t="n">
+        <v>0.5787308999999999</v>
+      </c>
+      <c r="C834" t="n">
+        <v>0.08785358800000001</v>
+      </c>
+      <c r="D834" t="inlineStr"/>
+      <c r="E834" t="inlineStr"/>
+      <c r="F834" t="inlineStr"/>
+      <c r="G834" t="inlineStr"/>
+      <c r="H834" t="inlineStr"/>
+      <c r="I834" t="n">
+        <v>0.045085425</v>
+      </c>
+      <c r="J834" t="inlineStr"/>
+      <c r="K834" t="n">
+        <v>1650.000435510703</v>
+      </c>
+      <c r="L834" t="inlineStr"/>
+      <c r="M834" t="inlineStr"/>
+      <c r="N834" t="inlineStr"/>
+      <c r="O834" t="n">
+        <v>0.0766977274</v>
+      </c>
+      <c r="P834" t="inlineStr"/>
+      <c r="Q834" t="n">
+        <v>8.16e-07</v>
+      </c>
+      <c r="R834" t="inlineStr"/>
+      <c r="S834" t="inlineStr"/>
+      <c r="T834" t="inlineStr"/>
+      <c r="U834" t="inlineStr"/>
+      <c r="V834" t="inlineStr"/>
+      <c r="W834" t="inlineStr"/>
+      <c r="X834" t="inlineStr"/>
+      <c r="Y834" t="inlineStr"/>
+      <c r="Z834" t="inlineStr"/>
+      <c r="AA834" t="n">
+        <v>0.3214785240664</v>
+      </c>
+      <c r="AB834" t="n">
+        <v>61.81146</v>
+      </c>
+      <c r="AC834" t="n">
+        <v>7.844161463173601</v>
+      </c>
+      <c r="AD834" t="n">
+        <v>0.11090521</v>
+      </c>
+      <c r="AE834" t="n">
+        <v>1720.895874902343</v>
+      </c>
+      <c r="AF834" t="inlineStr"/>
+      <c r="AG834" t="n">
+        <v>0.019065738</v>
+      </c>
+      <c r="AH834" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH834"/>
+  <dimension ref="A1:AH836"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63485,7 +63485,7 @@
         <v>0.09778249</v>
       </c>
       <c r="AE809" t="n">
-        <v>1671.434217246821</v>
+        <v>1671.43421724682</v>
       </c>
       <c r="AF809" t="inlineStr"/>
       <c r="AG809" t="n">
@@ -63981,7 +63981,7 @@
         <v>0.09413729</v>
       </c>
       <c r="AE817" t="n">
-        <v>1703.467988615625</v>
+        <v>1703.467988615624</v>
       </c>
       <c r="AF817" t="inlineStr"/>
       <c r="AG817" t="n">
@@ -65043,6 +65043,130 @@
       </c>
       <c r="AH834" t="inlineStr"/>
     </row>
+    <row r="835">
+      <c r="A835" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B835" t="n">
+        <v>0.5854306104999999</v>
+      </c>
+      <c r="C835" t="n">
+        <v>0.08969907750000002</v>
+      </c>
+      <c r="D835" t="inlineStr"/>
+      <c r="E835" t="inlineStr"/>
+      <c r="F835" t="inlineStr"/>
+      <c r="G835" t="inlineStr"/>
+      <c r="H835" t="inlineStr"/>
+      <c r="I835" t="n">
+        <v>0.045665886</v>
+      </c>
+      <c r="J835" t="inlineStr"/>
+      <c r="K835" t="n">
+        <v>1632.818044780898</v>
+      </c>
+      <c r="L835" t="inlineStr"/>
+      <c r="M835" t="inlineStr"/>
+      <c r="N835" t="inlineStr"/>
+      <c r="O835" t="n">
+        <v>0.07744819440000002</v>
+      </c>
+      <c r="P835" t="inlineStr"/>
+      <c r="Q835" t="n">
+        <v>8.52e-07</v>
+      </c>
+      <c r="R835" t="inlineStr"/>
+      <c r="S835" t="inlineStr"/>
+      <c r="T835" t="inlineStr"/>
+      <c r="U835" t="inlineStr"/>
+      <c r="V835" t="inlineStr"/>
+      <c r="W835" t="inlineStr"/>
+      <c r="X835" t="inlineStr"/>
+      <c r="Y835" t="inlineStr"/>
+      <c r="Z835" t="inlineStr"/>
+      <c r="AA835" t="n">
+        <v>0.3215460325312</v>
+      </c>
+      <c r="AB835" t="n">
+        <v>62.7594</v>
+      </c>
+      <c r="AC835" t="n">
+        <v>8.198173500704</v>
+      </c>
+      <c r="AD835" t="n">
+        <v>0.11263668</v>
+      </c>
+      <c r="AE835" t="n">
+        <v>1705.027353949533</v>
+      </c>
+      <c r="AF835" t="inlineStr"/>
+      <c r="AG835" t="n">
+        <v>0.019308335</v>
+      </c>
+      <c r="AH835" t="inlineStr"/>
+    </row>
+    <row r="836">
+      <c r="A836" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B836" t="n">
+        <v>0.57692055</v>
+      </c>
+      <c r="C836" t="n">
+        <v>0.08791501950000001</v>
+      </c>
+      <c r="D836" t="inlineStr"/>
+      <c r="E836" t="inlineStr"/>
+      <c r="F836" t="inlineStr"/>
+      <c r="G836" t="inlineStr"/>
+      <c r="H836" t="inlineStr"/>
+      <c r="I836" t="n">
+        <v>0.04431</v>
+      </c>
+      <c r="J836" t="inlineStr"/>
+      <c r="K836" t="n">
+        <v>1582.252723490329</v>
+      </c>
+      <c r="L836" t="inlineStr"/>
+      <c r="M836" t="inlineStr"/>
+      <c r="N836" t="inlineStr"/>
+      <c r="O836" t="n">
+        <v>0.07650283000000001</v>
+      </c>
+      <c r="P836" t="inlineStr"/>
+      <c r="Q836" t="n">
+        <v>8.327999999999999e-07</v>
+      </c>
+      <c r="R836" t="inlineStr"/>
+      <c r="S836" t="inlineStr"/>
+      <c r="T836" t="inlineStr"/>
+      <c r="U836" t="inlineStr"/>
+      <c r="V836" t="inlineStr"/>
+      <c r="W836" t="inlineStr"/>
+      <c r="X836" t="inlineStr"/>
+      <c r="Y836" t="inlineStr"/>
+      <c r="Z836" t="inlineStr"/>
+      <c r="AA836" t="n">
+        <v>0.321597467552</v>
+      </c>
+      <c r="AB836" t="n">
+        <v>61.40668</v>
+      </c>
+      <c r="AC836" t="n">
+        <v>8.0677480131928</v>
+      </c>
+      <c r="AD836" t="n">
+        <v>0.1120899</v>
+      </c>
+      <c r="AE836" t="n">
+        <v>1652.966202092374</v>
+      </c>
+      <c r="AF836" t="inlineStr"/>
+      <c r="AG836" t="n">
+        <v>0.019713989</v>
+      </c>
+      <c r="AH836" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH836"/>
+  <dimension ref="A1:AH837"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63485,7 +63485,7 @@
         <v>0.09778249</v>
       </c>
       <c r="AE809" t="n">
-        <v>1671.43421724682</v>
+        <v>1671.434217246821</v>
       </c>
       <c r="AF809" t="inlineStr"/>
       <c r="AG809" t="n">
@@ -63981,7 +63981,7 @@
         <v>0.09413729</v>
       </c>
       <c r="AE817" t="n">
-        <v>1703.467988615624</v>
+        <v>1703.467988615625</v>
       </c>
       <c r="AF817" t="inlineStr"/>
       <c r="AG817" t="n">
@@ -65167,6 +65167,68 @@
       </c>
       <c r="AH836" t="inlineStr"/>
     </row>
+    <row r="837">
+      <c r="A837" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B837" t="n">
+        <v>0.5761830744999999</v>
+      </c>
+      <c r="C837" t="n">
+        <v>0.08694629200000001</v>
+      </c>
+      <c r="D837" t="inlineStr"/>
+      <c r="E837" t="inlineStr"/>
+      <c r="F837" t="inlineStr"/>
+      <c r="G837" t="inlineStr"/>
+      <c r="H837" t="inlineStr"/>
+      <c r="I837" t="n">
+        <v>0.044500533</v>
+      </c>
+      <c r="J837" t="inlineStr"/>
+      <c r="K837" t="n">
+        <v>1596.489561523596</v>
+      </c>
+      <c r="L837" t="inlineStr"/>
+      <c r="M837" t="inlineStr"/>
+      <c r="N837" t="inlineStr"/>
+      <c r="O837" t="n">
+        <v>0.07715696840000001</v>
+      </c>
+      <c r="P837" t="inlineStr"/>
+      <c r="Q837" t="n">
+        <v>8.232e-07</v>
+      </c>
+      <c r="R837" t="inlineStr"/>
+      <c r="S837" t="inlineStr"/>
+      <c r="T837" t="inlineStr"/>
+      <c r="U837" t="inlineStr"/>
+      <c r="V837" t="inlineStr"/>
+      <c r="W837" t="inlineStr"/>
+      <c r="X837" t="inlineStr"/>
+      <c r="Y837" t="inlineStr"/>
+      <c r="Z837" t="inlineStr"/>
+      <c r="AA837" t="n">
+        <v>0.3215460325312</v>
+      </c>
+      <c r="AB837" t="n">
+        <v>60.34922</v>
+      </c>
+      <c r="AC837" t="n">
+        <v>8.105012438195999</v>
+      </c>
+      <c r="AD837" t="n">
+        <v>0.11145199</v>
+      </c>
+      <c r="AE837" t="n">
+        <v>1666.181341388423</v>
+      </c>
+      <c r="AF837" t="inlineStr"/>
+      <c r="AG837" t="n">
+        <v>0.019761713</v>
+      </c>
+      <c r="AH837" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH837"/>
+  <dimension ref="A1:AH838"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63485,7 +63485,7 @@
         <v>0.09778249</v>
       </c>
       <c r="AE809" t="n">
-        <v>1671.434217246821</v>
+        <v>1671.43421724682</v>
       </c>
       <c r="AF809" t="inlineStr"/>
       <c r="AG809" t="n">
@@ -63981,7 +63981,7 @@
         <v>0.09413729</v>
       </c>
       <c r="AE817" t="n">
-        <v>1703.467988615625</v>
+        <v>1703.467988615624</v>
       </c>
       <c r="AF817" t="inlineStr"/>
       <c r="AG817" t="n">
@@ -65229,6 +65229,68 @@
       </c>
       <c r="AH837" t="inlineStr"/>
     </row>
+    <row r="838">
+      <c r="A838" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B838" t="n">
+        <v>0.6054642564999999</v>
+      </c>
+      <c r="C838" t="n">
+        <v>0.09114798850000001</v>
+      </c>
+      <c r="D838" t="inlineStr"/>
+      <c r="E838" t="inlineStr"/>
+      <c r="F838" t="inlineStr"/>
+      <c r="G838" t="inlineStr"/>
+      <c r="H838" t="inlineStr"/>
+      <c r="I838" t="n">
+        <v>0.046055814</v>
+      </c>
+      <c r="J838" t="inlineStr"/>
+      <c r="K838" t="n">
+        <v>1624.472312140707</v>
+      </c>
+      <c r="L838" t="inlineStr"/>
+      <c r="M838" t="inlineStr"/>
+      <c r="N838" t="inlineStr"/>
+      <c r="O838" t="n">
+        <v>0.0812318922</v>
+      </c>
+      <c r="P838" t="inlineStr"/>
+      <c r="Q838" t="n">
+        <v>8.904e-07</v>
+      </c>
+      <c r="R838" t="inlineStr"/>
+      <c r="S838" t="inlineStr"/>
+      <c r="T838" t="inlineStr"/>
+      <c r="U838" t="inlineStr"/>
+      <c r="V838" t="inlineStr"/>
+      <c r="W838" t="inlineStr"/>
+      <c r="X838" t="inlineStr"/>
+      <c r="Y838" t="inlineStr"/>
+      <c r="Z838" t="inlineStr"/>
+      <c r="AA838" t="n">
+        <v>0.321436733112</v>
+      </c>
+      <c r="AB838" t="n">
+        <v>70.49906</v>
+      </c>
+      <c r="AC838" t="n">
+        <v>8.5149211132312</v>
+      </c>
+      <c r="AD838" t="n">
+        <v>0.11691979</v>
+      </c>
+      <c r="AE838" t="n">
+        <v>1704.76902819165</v>
+      </c>
+      <c r="AF838" t="inlineStr"/>
+      <c r="AG838" t="n">
+        <v>0.020477573</v>
+      </c>
+      <c r="AH838" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH838"/>
+  <dimension ref="A1:AH839"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63981,7 +63981,7 @@
         <v>0.09413729</v>
       </c>
       <c r="AE817" t="n">
-        <v>1703.467988615624</v>
+        <v>1703.467988615625</v>
       </c>
       <c r="AF817" t="inlineStr"/>
       <c r="AG817" t="n">
@@ -65291,6 +65291,68 @@
       </c>
       <c r="AH838" t="inlineStr"/>
     </row>
+    <row r="839">
+      <c r="A839" s="2" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B839" t="n">
+        <v>0.5934727365</v>
+      </c>
+      <c r="C839" t="n">
+        <v>0.08927014750000001</v>
+      </c>
+      <c r="D839" t="inlineStr"/>
+      <c r="E839" t="inlineStr"/>
+      <c r="F839" t="inlineStr"/>
+      <c r="G839" t="inlineStr"/>
+      <c r="H839" t="inlineStr"/>
+      <c r="I839" t="n">
+        <v>0.045165183</v>
+      </c>
+      <c r="J839" t="inlineStr"/>
+      <c r="K839" t="n">
+        <v>1626.926939387822</v>
+      </c>
+      <c r="L839" t="inlineStr"/>
+      <c r="M839" t="inlineStr"/>
+      <c r="N839" t="inlineStr"/>
+      <c r="O839" t="n">
+        <v>0.0808006537</v>
+      </c>
+      <c r="P839" t="inlineStr"/>
+      <c r="Q839" t="n">
+        <v>8.472e-07</v>
+      </c>
+      <c r="R839" t="inlineStr"/>
+      <c r="S839" t="inlineStr"/>
+      <c r="T839" t="inlineStr"/>
+      <c r="U839" t="inlineStr"/>
+      <c r="V839" t="inlineStr"/>
+      <c r="W839" t="inlineStr"/>
+      <c r="X839" t="inlineStr"/>
+      <c r="Y839" t="inlineStr"/>
+      <c r="Z839" t="inlineStr"/>
+      <c r="AA839" t="n">
+        <v>0.321356365892</v>
+      </c>
+      <c r="AB839" t="n">
+        <v>75.69756</v>
+      </c>
+      <c r="AC839" t="n">
+        <v>8.38449562572</v>
+      </c>
+      <c r="AD839" t="n">
+        <v>0.11309233</v>
+      </c>
+      <c r="AE839" t="n">
+        <v>1712.272340529334</v>
+      </c>
+      <c r="AF839" t="inlineStr"/>
+      <c r="AG839" t="n">
+        <v>0.020187252</v>
+      </c>
+      <c r="AH839" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH839"/>
+  <dimension ref="A1:AH840"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63981,7 +63981,7 @@
         <v>0.09413729</v>
       </c>
       <c r="AE817" t="n">
-        <v>1703.467988615625</v>
+        <v>1703.467988615624</v>
       </c>
       <c r="AF817" t="inlineStr"/>
       <c r="AG817" t="n">
@@ -65353,6 +65353,68 @@
       </c>
       <c r="AH839" t="inlineStr"/>
     </row>
+    <row r="840">
+      <c r="A840" s="2" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B840" t="n">
+        <v>0.5947465374999999</v>
+      </c>
+      <c r="C840" t="n">
+        <v>0.09016035900000001</v>
+      </c>
+      <c r="D840" t="inlineStr"/>
+      <c r="E840" t="inlineStr"/>
+      <c r="F840" t="inlineStr"/>
+      <c r="G840" t="inlineStr"/>
+      <c r="H840" t="inlineStr"/>
+      <c r="I840" t="n">
+        <v>0.045719058</v>
+      </c>
+      <c r="J840" t="inlineStr"/>
+      <c r="K840" t="n">
+        <v>1638.709150173974</v>
+      </c>
+      <c r="L840" t="inlineStr"/>
+      <c r="M840" t="inlineStr"/>
+      <c r="N840" t="inlineStr"/>
+      <c r="O840" t="n">
+        <v>0.0858590253</v>
+      </c>
+      <c r="P840" t="inlineStr"/>
+      <c r="Q840" t="n">
+        <v>8.664e-07</v>
+      </c>
+      <c r="R840" t="inlineStr"/>
+      <c r="S840" t="inlineStr"/>
+      <c r="T840" t="inlineStr"/>
+      <c r="U840" t="inlineStr"/>
+      <c r="V840" t="inlineStr"/>
+      <c r="W840" t="inlineStr"/>
+      <c r="X840" t="inlineStr"/>
+      <c r="Y840" t="inlineStr"/>
+      <c r="Z840" t="inlineStr"/>
+      <c r="AA840" t="n">
+        <v>0.3214142302904</v>
+      </c>
+      <c r="AB840" t="n">
+        <v>75.9203</v>
+      </c>
+      <c r="AC840" t="n">
+        <v>8.291334563212001</v>
+      </c>
+      <c r="AD840" t="n">
+        <v>0.116691965</v>
+      </c>
+      <c r="AE840" t="n">
+        <v>1724.197126991676</v>
+      </c>
+      <c r="AF840" t="inlineStr"/>
+      <c r="AG840" t="n">
+        <v>0.021750213</v>
+      </c>
+      <c r="AH840" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH840"/>
+  <dimension ref="A1:AH841"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63981,7 +63981,7 @@
         <v>0.09413729</v>
       </c>
       <c r="AE817" t="n">
-        <v>1703.467988615624</v>
+        <v>1703.467988615625</v>
       </c>
       <c r="AF817" t="inlineStr"/>
       <c r="AG817" t="n">
@@ -65415,6 +65415,68 @@
       </c>
       <c r="AH840" t="inlineStr"/>
     </row>
+    <row r="841">
+      <c r="A841" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B841" t="n">
+        <v>0.5985466335</v>
+      </c>
+      <c r="C841" t="n">
+        <v>0.09140134800000001</v>
+      </c>
+      <c r="D841" t="inlineStr"/>
+      <c r="E841" t="inlineStr"/>
+      <c r="F841" t="inlineStr"/>
+      <c r="G841" t="inlineStr"/>
+      <c r="H841" t="inlineStr"/>
+      <c r="I841" t="n">
+        <v>0.047212305</v>
+      </c>
+      <c r="J841" t="inlineStr"/>
+      <c r="K841" t="n">
+        <v>1645.582106465896</v>
+      </c>
+      <c r="L841" t="inlineStr"/>
+      <c r="M841" t="inlineStr"/>
+      <c r="N841" t="inlineStr"/>
+      <c r="O841" t="n">
+        <v>0.08434353</v>
+      </c>
+      <c r="P841" t="inlineStr"/>
+      <c r="Q841" t="n">
+        <v>8.760000000000001e-07</v>
+      </c>
+      <c r="R841" t="inlineStr"/>
+      <c r="S841" t="inlineStr"/>
+      <c r="T841" t="inlineStr"/>
+      <c r="U841" t="inlineStr"/>
+      <c r="V841" t="inlineStr"/>
+      <c r="W841" t="inlineStr"/>
+      <c r="X841" t="inlineStr"/>
+      <c r="Y841" t="inlineStr"/>
+      <c r="Z841" t="inlineStr"/>
+      <c r="AA841" t="n">
+        <v>0.3214592359336</v>
+      </c>
+      <c r="AB841" t="n">
+        <v>90.84239999999998</v>
+      </c>
+      <c r="AC841" t="n">
+        <v>8.38449562572</v>
+      </c>
+      <c r="AD841" t="n">
+        <v>0.11892465</v>
+      </c>
+      <c r="AE841" t="n">
+        <v>1746.09275223905</v>
+      </c>
+      <c r="AF841" t="inlineStr"/>
+      <c r="AG841" t="n">
+        <v>0.021861569</v>
+      </c>
+      <c r="AH841" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH841"/>
+  <dimension ref="A1:AH842"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65477,6 +65477,68 @@
       </c>
       <c r="AH841" t="inlineStr"/>
     </row>
+    <row r="842">
+      <c r="A842" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B842" t="n">
+        <v>0.5893844745</v>
+      </c>
+      <c r="C842" t="n">
+        <v>0.090517316</v>
+      </c>
+      <c r="D842" t="inlineStr"/>
+      <c r="E842" t="inlineStr"/>
+      <c r="F842" t="inlineStr"/>
+      <c r="G842" t="inlineStr"/>
+      <c r="H842" t="inlineStr"/>
+      <c r="I842" t="n">
+        <v>0.04599378</v>
+      </c>
+      <c r="J842" t="inlineStr"/>
+      <c r="K842" t="n">
+        <v>1642.636553769358</v>
+      </c>
+      <c r="L842" t="inlineStr"/>
+      <c r="M842" t="inlineStr"/>
+      <c r="N842" t="inlineStr"/>
+      <c r="O842" t="n">
+        <v>0.08288515980000001</v>
+      </c>
+      <c r="P842" t="inlineStr"/>
+      <c r="Q842" t="n">
+        <v>8.711999999999999e-07</v>
+      </c>
+      <c r="R842" t="inlineStr"/>
+      <c r="S842" t="inlineStr"/>
+      <c r="T842" t="inlineStr"/>
+      <c r="U842" t="inlineStr"/>
+      <c r="V842" t="inlineStr"/>
+      <c r="W842" t="inlineStr"/>
+      <c r="X842" t="inlineStr"/>
+      <c r="Y842" t="inlineStr"/>
+      <c r="Z842" t="inlineStr"/>
+      <c r="AA842" t="n">
+        <v>0.321501026888</v>
+      </c>
+      <c r="AB842" t="n">
+        <v>84.37184000000001</v>
+      </c>
+      <c r="AC842" t="n">
+        <v>8.440392263224799</v>
+      </c>
+      <c r="AD842" t="n">
+        <v>0.11801335</v>
+      </c>
+      <c r="AE842" t="n">
+        <v>1736.719039027971</v>
+      </c>
+      <c r="AF842" t="inlineStr"/>
+      <c r="AG842" t="n">
+        <v>0.021957017</v>
+      </c>
+      <c r="AH842" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH842"/>
+  <dimension ref="A1:AH843"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65539,6 +65539,68 @@
       </c>
       <c r="AH842" t="inlineStr"/>
     </row>
+    <row r="843">
+      <c r="A843" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B843" t="n">
+        <v>0.58449571</v>
+      </c>
+      <c r="C843" t="n">
+        <v>0.090331931</v>
+      </c>
+      <c r="D843" t="inlineStr"/>
+      <c r="E843" t="inlineStr"/>
+      <c r="F843" t="inlineStr"/>
+      <c r="G843" t="inlineStr"/>
+      <c r="H843" t="inlineStr"/>
+      <c r="I843" t="n">
+        <v>0.045803247</v>
+      </c>
+      <c r="J843" t="inlineStr"/>
+      <c r="K843" t="n">
+        <v>1580.113902645124</v>
+      </c>
+      <c r="L843" t="inlineStr"/>
+      <c r="M843" t="inlineStr"/>
+      <c r="N843" t="inlineStr"/>
+      <c r="O843" t="n">
+        <v>0.009099441999999999</v>
+      </c>
+      <c r="P843" t="inlineStr"/>
+      <c r="Q843" t="n">
+        <v>8.784e-07</v>
+      </c>
+      <c r="R843" t="inlineStr"/>
+      <c r="S843" t="inlineStr"/>
+      <c r="T843" t="inlineStr"/>
+      <c r="U843" t="inlineStr"/>
+      <c r="V843" t="inlineStr"/>
+      <c r="W843" t="inlineStr"/>
+      <c r="X843" t="inlineStr"/>
+      <c r="Y843" t="inlineStr"/>
+      <c r="Z843" t="inlineStr"/>
+      <c r="AA843" t="n">
+        <v>0.8383524127552</v>
+      </c>
+      <c r="AB843" t="n">
+        <v>173.080236763</v>
+      </c>
+      <c r="AC843" t="n">
+        <v>8.198173500704</v>
+      </c>
+      <c r="AD843" t="n">
+        <v>0.117694395</v>
+      </c>
+      <c r="AE843" t="n">
+        <v>1763.099686034983</v>
+      </c>
+      <c r="AF843" t="inlineStr"/>
+      <c r="AG843" t="n">
+        <v>0.02159511</v>
+      </c>
+      <c r="AH843" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH843"/>
+  <dimension ref="A1:AH845"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65601,6 +65601,130 @@
       </c>
       <c r="AH843" t="inlineStr"/>
     </row>
+    <row r="844">
+      <c r="A844" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B844" t="n">
+        <v>0.5833829034999999</v>
+      </c>
+      <c r="C844" t="n">
+        <v>0.08971652550000001</v>
+      </c>
+      <c r="D844" t="inlineStr"/>
+      <c r="E844" t="inlineStr"/>
+      <c r="F844" t="inlineStr"/>
+      <c r="G844" t="inlineStr"/>
+      <c r="H844" t="inlineStr"/>
+      <c r="I844" t="n">
+        <v>0.04500566699999999</v>
+      </c>
+      <c r="J844" t="inlineStr"/>
+      <c r="K844" t="n">
+        <v>1580.580288094547</v>
+      </c>
+      <c r="L844" t="inlineStr"/>
+      <c r="M844" t="inlineStr"/>
+      <c r="N844" t="inlineStr"/>
+      <c r="O844" t="n">
+        <v>0.008743944</v>
+      </c>
+      <c r="P844" t="inlineStr"/>
+      <c r="Q844" t="n">
+        <v>8.352e-07</v>
+      </c>
+      <c r="R844" t="inlineStr"/>
+      <c r="S844" t="inlineStr"/>
+      <c r="T844" t="inlineStr"/>
+      <c r="U844" t="inlineStr"/>
+      <c r="V844" t="inlineStr"/>
+      <c r="W844" t="inlineStr"/>
+      <c r="X844" t="inlineStr"/>
+      <c r="Y844" t="inlineStr"/>
+      <c r="Z844" t="inlineStr"/>
+      <c r="AA844" t="n">
+        <v>0.8384613942096</v>
+      </c>
+      <c r="AB844" t="n">
+        <v>182.846510502</v>
+      </c>
+      <c r="AC844" t="n">
+        <v>7.3783561506336</v>
+      </c>
+      <c r="AD844" t="n">
+        <v>0.114778235</v>
+      </c>
+      <c r="AE844" t="n">
+        <v>1772.50640189159</v>
+      </c>
+      <c r="AF844" t="inlineStr"/>
+      <c r="AG844" t="n">
+        <v>0.02115764</v>
+      </c>
+      <c r="AH844" t="inlineStr"/>
+    </row>
+    <row r="845">
+      <c r="A845" s="2" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B845" t="n">
+        <v>0.570436964</v>
+      </c>
+      <c r="C845" t="n">
+        <v>0.08863111450000001</v>
+      </c>
+      <c r="D845" t="inlineStr"/>
+      <c r="E845" t="inlineStr"/>
+      <c r="F845" t="inlineStr"/>
+      <c r="G845" t="inlineStr"/>
+      <c r="H845" t="inlineStr"/>
+      <c r="I845" t="n">
+        <v>0.043720677</v>
+      </c>
+      <c r="J845" t="inlineStr"/>
+      <c r="K845" t="n">
+        <v>1585.7105280382</v>
+      </c>
+      <c r="L845" t="inlineStr"/>
+      <c r="M845" t="inlineStr"/>
+      <c r="N845" t="inlineStr"/>
+      <c r="O845" t="n">
+        <v>0.008575512</v>
+      </c>
+      <c r="P845" t="inlineStr"/>
+      <c r="Q845" t="n">
+        <v>7.776e-07</v>
+      </c>
+      <c r="R845" t="inlineStr"/>
+      <c r="S845" t="inlineStr"/>
+      <c r="T845" t="inlineStr"/>
+      <c r="U845" t="inlineStr"/>
+      <c r="V845" t="inlineStr"/>
+      <c r="W845" t="inlineStr"/>
+      <c r="X845" t="inlineStr"/>
+      <c r="Y845" t="inlineStr"/>
+      <c r="Z845" t="inlineStr"/>
+      <c r="AA845" t="n">
+        <v>0.8385116933423999</v>
+      </c>
+      <c r="AB845" t="n">
+        <v>158.699744014</v>
+      </c>
+      <c r="AC845" t="n">
+        <v>7.3038273006272</v>
+      </c>
+      <c r="AD845" t="n">
+        <v>0.10197447</v>
+      </c>
+      <c r="AE845" t="n">
+        <v>1753.38667868527</v>
+      </c>
+      <c r="AF845" t="inlineStr"/>
+      <c r="AG845" t="n">
+        <v>0.020728124</v>
+      </c>
+      <c r="AH845" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH845"/>
+  <dimension ref="A1:AH846"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63981,7 +63981,7 @@
         <v>0.09413729</v>
       </c>
       <c r="AE817" t="n">
-        <v>1703.467988615625</v>
+        <v>1703.467988615624</v>
       </c>
       <c r="AF817" t="inlineStr"/>
       <c r="AG817" t="n">
@@ -65725,6 +65725,68 @@
       </c>
       <c r="AH845" t="inlineStr"/>
     </row>
+    <row r="846">
+      <c r="A846" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B846" t="n">
+        <v>0.575331465</v>
+      </c>
+      <c r="C846" t="n">
+        <v>0.0914722305</v>
+      </c>
+      <c r="D846" t="inlineStr"/>
+      <c r="E846" t="inlineStr"/>
+      <c r="F846" t="inlineStr"/>
+      <c r="G846" t="inlineStr"/>
+      <c r="H846" t="inlineStr"/>
+      <c r="I846" t="n">
+        <v>0.045400026</v>
+      </c>
+      <c r="J846" t="inlineStr"/>
+      <c r="K846" t="n">
+        <v>1579.181131746278</v>
+      </c>
+      <c r="L846" t="inlineStr"/>
+      <c r="M846" t="inlineStr"/>
+      <c r="N846" t="inlineStr"/>
+      <c r="O846" t="n">
+        <v>0.008793674999999999</v>
+      </c>
+      <c r="P846" t="inlineStr"/>
+      <c r="Q846" t="n">
+        <v>7.944e-07</v>
+      </c>
+      <c r="R846" t="inlineStr"/>
+      <c r="S846" t="inlineStr"/>
+      <c r="T846" t="inlineStr"/>
+      <c r="U846" t="inlineStr"/>
+      <c r="V846" t="inlineStr"/>
+      <c r="W846" t="inlineStr"/>
+      <c r="X846" t="inlineStr"/>
+      <c r="Y846" t="inlineStr"/>
+      <c r="Z846" t="inlineStr"/>
+      <c r="AA846" t="n">
+        <v>0.8383943286991999</v>
+      </c>
+      <c r="AB846" t="n">
+        <v>171.1772387955</v>
+      </c>
+      <c r="AC846" t="n">
+        <v>7.5646782756496</v>
+      </c>
+      <c r="AD846" t="n">
+        <v>0.10397933</v>
+      </c>
+      <c r="AE846" t="n">
+        <v>1759.607614100027</v>
+      </c>
+      <c r="AF846" t="inlineStr"/>
+      <c r="AG846" t="n">
+        <v>0.021193433</v>
+      </c>
+      <c r="AH846" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
